--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="103">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,75 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
+    <t>Egyptian Premier</t>
+  </si>
+  <si>
+    <t>Spanish La Liga</t>
+  </si>
+  <si>
+    <t>Bolivian Liga de Futbol Profesional</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>01:30:00</t>
+  </si>
+  <si>
+    <t>14:00:00</t>
+  </si>
+  <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
+    <t>18:30:00</t>
+  </si>
+  <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
+    <t>Atletico Nacional Medellin</t>
+  </si>
+  <si>
+    <t>Modern Sport FC</t>
+  </si>
+  <si>
+    <t>Al Mokawloon</t>
+  </si>
+  <si>
+    <t>Celta Vigo</t>
+  </si>
+  <si>
+    <t>Always Ready</t>
+  </si>
+  <si>
+    <t>Barcelona</t>
+  </si>
+  <si>
+    <t>Deportivo Cali</t>
+  </si>
+  <si>
+    <t>Ghazl El Mahallah</t>
+  </si>
+  <si>
+    <t>Al-Masry</t>
+  </si>
+  <si>
+    <t>Osasuna</t>
+  </si>
+  <si>
+    <t>Aurora</t>
+  </si>
+  <si>
+    <t>Athletic Bilbao</t>
+  </si>
+  <si>
+    <t>2026-08-25 02:26:08</t>
   </si>
 </sst>
 </file>
@@ -585,7 +654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -828,6 +897,1458 @@
       </c>
       <c r="CB1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F2">
+        <v>1.48</v>
+      </c>
+      <c r="G2">
+        <v>1.78</v>
+      </c>
+      <c r="H2">
+        <v>5.5</v>
+      </c>
+      <c r="I2">
+        <v>990</v>
+      </c>
+      <c r="J2">
+        <v>2.32</v>
+      </c>
+      <c r="K2">
+        <v>950</v>
+      </c>
+      <c r="L2">
+        <v>1.01</v>
+      </c>
+      <c r="M2">
+        <v>1.01</v>
+      </c>
+      <c r="N2">
+        <v>3.1</v>
+      </c>
+      <c r="O2">
+        <v>1.35</v>
+      </c>
+      <c r="P2">
+        <v>1.76</v>
+      </c>
+      <c r="Q2">
+        <v>2.02</v>
+      </c>
+      <c r="R2">
+        <v>1.13</v>
+      </c>
+      <c r="S2">
+        <v>2.32</v>
+      </c>
+      <c r="T2">
+        <v>1.11</v>
+      </c>
+      <c r="U2">
+        <v>1.11</v>
+      </c>
+      <c r="V2">
+        <v>1.06</v>
+      </c>
+      <c r="W2">
+        <v>2.28</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>1000</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>1000</v>
+      </c>
+      <c r="AC2">
+        <v>1000</v>
+      </c>
+      <c r="AD2">
+        <v>1000</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>1000</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>1.01</v>
+      </c>
+      <c r="AQ2">
+        <v>1.01</v>
+      </c>
+      <c r="AR2">
+        <v>1.01</v>
+      </c>
+      <c r="AS2">
+        <v>1.01</v>
+      </c>
+      <c r="AT2">
+        <v>1.01</v>
+      </c>
+      <c r="AU2">
+        <v>1.01</v>
+      </c>
+      <c r="AV2">
+        <v>1.01</v>
+      </c>
+      <c r="AW2">
+        <v>1.01</v>
+      </c>
+      <c r="AX2">
+        <v>1.01</v>
+      </c>
+      <c r="AY2">
+        <v>1.01</v>
+      </c>
+      <c r="AZ2">
+        <v>1.01</v>
+      </c>
+      <c r="BA2">
+        <v>1.01</v>
+      </c>
+      <c r="BB2">
+        <v>1.01</v>
+      </c>
+      <c r="BC2">
+        <v>1.01</v>
+      </c>
+      <c r="BD2">
+        <v>1.01</v>
+      </c>
+      <c r="BE2">
+        <v>1.01</v>
+      </c>
+      <c r="BF2">
+        <v>1.01</v>
+      </c>
+      <c r="BG2">
+        <v>1.01</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>1.04</v>
+      </c>
+      <c r="BJ2">
+        <v>1000</v>
+      </c>
+      <c r="BK2">
+        <v>1.04</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.04</v>
+      </c>
+      <c r="BN2">
+        <v>1000</v>
+      </c>
+      <c r="BO2">
+        <v>1.04</v>
+      </c>
+      <c r="BP2">
+        <v>1000</v>
+      </c>
+      <c r="BQ2">
+        <v>1.04</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.04</v>
+      </c>
+      <c r="BT2">
+        <v>1000</v>
+      </c>
+      <c r="BU2">
+        <v>1.04</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>1.04</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>1.04</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
+        <v>1.04</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F3">
+        <v>2.34</v>
+      </c>
+      <c r="G3">
+        <v>2.6</v>
+      </c>
+      <c r="H3">
+        <v>3.75</v>
+      </c>
+      <c r="I3">
+        <v>6</v>
+      </c>
+      <c r="J3">
+        <v>2.22</v>
+      </c>
+      <c r="K3">
+        <v>3.3</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>1.26</v>
+      </c>
+      <c r="Q3">
+        <v>3</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <v>0</v>
+      </c>
+      <c r="BA3">
+        <v>0</v>
+      </c>
+      <c r="BB3">
+        <v>0</v>
+      </c>
+      <c r="BC3">
+        <v>0</v>
+      </c>
+      <c r="BD3">
+        <v>0</v>
+      </c>
+      <c r="BE3">
+        <v>0</v>
+      </c>
+      <c r="BF3">
+        <v>0</v>
+      </c>
+      <c r="BG3">
+        <v>0</v>
+      </c>
+      <c r="BH3">
+        <v>0</v>
+      </c>
+      <c r="BI3">
+        <v>0</v>
+      </c>
+      <c r="BJ3">
+        <v>0</v>
+      </c>
+      <c r="BK3">
+        <v>0</v>
+      </c>
+      <c r="BL3">
+        <v>0</v>
+      </c>
+      <c r="BM3">
+        <v>0</v>
+      </c>
+      <c r="BN3">
+        <v>0</v>
+      </c>
+      <c r="BO3">
+        <v>0</v>
+      </c>
+      <c r="BP3">
+        <v>0</v>
+      </c>
+      <c r="BQ3">
+        <v>0</v>
+      </c>
+      <c r="BR3">
+        <v>0</v>
+      </c>
+      <c r="BS3">
+        <v>0</v>
+      </c>
+      <c r="BT3">
+        <v>0</v>
+      </c>
+      <c r="BU3">
+        <v>0</v>
+      </c>
+      <c r="BV3">
+        <v>0</v>
+      </c>
+      <c r="BW3">
+        <v>0</v>
+      </c>
+      <c r="BX3">
+        <v>0</v>
+      </c>
+      <c r="BY3">
+        <v>0</v>
+      </c>
+      <c r="BZ3">
+        <v>0</v>
+      </c>
+      <c r="CA3">
+        <v>0</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F4">
+        <v>3.55</v>
+      </c>
+      <c r="G4">
+        <v>4.1</v>
+      </c>
+      <c r="H4">
+        <v>2.36</v>
+      </c>
+      <c r="I4">
+        <v>2.64</v>
+      </c>
+      <c r="J4">
+        <v>2.86</v>
+      </c>
+      <c r="K4">
+        <v>3.25</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>1.47</v>
+      </c>
+      <c r="Q4">
+        <v>2.68</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <v>0</v>
+      </c>
+      <c r="BA4">
+        <v>0</v>
+      </c>
+      <c r="BB4">
+        <v>0</v>
+      </c>
+      <c r="BC4">
+        <v>0</v>
+      </c>
+      <c r="BD4">
+        <v>0</v>
+      </c>
+      <c r="BE4">
+        <v>0</v>
+      </c>
+      <c r="BF4">
+        <v>0</v>
+      </c>
+      <c r="BG4">
+        <v>0</v>
+      </c>
+      <c r="BH4">
+        <v>0</v>
+      </c>
+      <c r="BI4">
+        <v>0</v>
+      </c>
+      <c r="BJ4">
+        <v>0</v>
+      </c>
+      <c r="BK4">
+        <v>0</v>
+      </c>
+      <c r="BL4">
+        <v>0</v>
+      </c>
+      <c r="BM4">
+        <v>0</v>
+      </c>
+      <c r="BN4">
+        <v>0</v>
+      </c>
+      <c r="BO4">
+        <v>0</v>
+      </c>
+      <c r="BP4">
+        <v>0</v>
+      </c>
+      <c r="BQ4">
+        <v>0</v>
+      </c>
+      <c r="BR4">
+        <v>0</v>
+      </c>
+      <c r="BS4">
+        <v>0</v>
+      </c>
+      <c r="BT4">
+        <v>0</v>
+      </c>
+      <c r="BU4">
+        <v>0</v>
+      </c>
+      <c r="BV4">
+        <v>0</v>
+      </c>
+      <c r="BW4">
+        <v>0</v>
+      </c>
+      <c r="BX4">
+        <v>0</v>
+      </c>
+      <c r="BY4">
+        <v>0</v>
+      </c>
+      <c r="BZ4">
+        <v>0</v>
+      </c>
+      <c r="CA4">
+        <v>0</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F5">
+        <v>2.02</v>
+      </c>
+      <c r="G5">
+        <v>2.06</v>
+      </c>
+      <c r="H5">
+        <v>4.2</v>
+      </c>
+      <c r="I5">
+        <v>4.4</v>
+      </c>
+      <c r="J5">
+        <v>3.6</v>
+      </c>
+      <c r="K5">
+        <v>3.65</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>1.09</v>
+      </c>
+      <c r="N5">
+        <v>3.3</v>
+      </c>
+      <c r="O5">
+        <v>1.41</v>
+      </c>
+      <c r="P5">
+        <v>1.77</v>
+      </c>
+      <c r="Q5">
+        <v>2.22</v>
+      </c>
+      <c r="R5">
+        <v>1.29</v>
+      </c>
+      <c r="S5">
+        <v>4.2</v>
+      </c>
+      <c r="T5">
+        <v>2</v>
+      </c>
+      <c r="U5">
+        <v>1.94</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>12</v>
+      </c>
+      <c r="Y5">
+        <v>13.5</v>
+      </c>
+      <c r="Z5">
+        <v>32</v>
+      </c>
+      <c r="AA5">
+        <v>120</v>
+      </c>
+      <c r="AB5">
+        <v>8</v>
+      </c>
+      <c r="AC5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD5">
+        <v>17.5</v>
+      </c>
+      <c r="AE5">
+        <v>65</v>
+      </c>
+      <c r="AF5">
+        <v>11.5</v>
+      </c>
+      <c r="AG5">
+        <v>11</v>
+      </c>
+      <c r="AH5">
+        <v>21</v>
+      </c>
+      <c r="AI5">
+        <v>85</v>
+      </c>
+      <c r="AJ5">
+        <v>25</v>
+      </c>
+      <c r="AK5">
+        <v>24</v>
+      </c>
+      <c r="AL5">
+        <v>44</v>
+      </c>
+      <c r="AM5">
+        <v>160</v>
+      </c>
+      <c r="AN5">
+        <v>18</v>
+      </c>
+      <c r="AO5">
+        <v>90</v>
+      </c>
+      <c r="AP5">
+        <v>10.5</v>
+      </c>
+      <c r="AQ5">
+        <v>12</v>
+      </c>
+      <c r="AR5">
+        <v>19.5</v>
+      </c>
+      <c r="AS5">
+        <v>36</v>
+      </c>
+      <c r="AT5">
+        <v>7.4</v>
+      </c>
+      <c r="AU5">
+        <v>7.4</v>
+      </c>
+      <c r="AV5">
+        <v>15.5</v>
+      </c>
+      <c r="AW5">
+        <v>30</v>
+      </c>
+      <c r="AX5">
+        <v>10.5</v>
+      </c>
+      <c r="AY5">
+        <v>10</v>
+      </c>
+      <c r="AZ5">
+        <v>19</v>
+      </c>
+      <c r="BA5">
+        <v>34</v>
+      </c>
+      <c r="BB5">
+        <v>21</v>
+      </c>
+      <c r="BC5">
+        <v>20</v>
+      </c>
+      <c r="BD5">
+        <v>36</v>
+      </c>
+      <c r="BE5">
+        <v>14</v>
+      </c>
+      <c r="BF5">
+        <v>16</v>
+      </c>
+      <c r="BG5">
+        <v>34</v>
+      </c>
+      <c r="BH5">
+        <v>3.35</v>
+      </c>
+      <c r="BI5">
+        <v>2.54</v>
+      </c>
+      <c r="BJ5">
+        <v>12.5</v>
+      </c>
+      <c r="BK5">
+        <v>4.1</v>
+      </c>
+      <c r="BL5">
+        <v>180</v>
+      </c>
+      <c r="BM5">
+        <v>6</v>
+      </c>
+      <c r="BN5">
+        <v>5.2</v>
+      </c>
+      <c r="BO5">
+        <v>3.75</v>
+      </c>
+      <c r="BP5">
+        <v>18</v>
+      </c>
+      <c r="BQ5">
+        <v>4.6</v>
+      </c>
+      <c r="BR5">
+        <v>38</v>
+      </c>
+      <c r="BS5">
+        <v>5.3</v>
+      </c>
+      <c r="BT5">
+        <v>8.6</v>
+      </c>
+      <c r="BU5">
+        <v>6</v>
+      </c>
+      <c r="BV5">
+        <v>46</v>
+      </c>
+      <c r="BW5">
+        <v>5.4</v>
+      </c>
+      <c r="BX5">
+        <v>65</v>
+      </c>
+      <c r="BY5">
+        <v>5.6</v>
+      </c>
+      <c r="BZ5">
+        <v>36</v>
+      </c>
+      <c r="CA5">
+        <v>5.3</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" t="s">
+        <v>100</v>
+      </c>
+      <c r="F6">
+        <v>1.04</v>
+      </c>
+      <c r="G6">
+        <v>1000</v>
+      </c>
+      <c r="H6">
+        <v>1.04</v>
+      </c>
+      <c r="I6">
+        <v>1000</v>
+      </c>
+      <c r="J6">
+        <v>1.04</v>
+      </c>
+      <c r="K6">
+        <v>950</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>1.24</v>
+      </c>
+      <c r="Q6">
+        <v>1.01</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <v>0</v>
+      </c>
+      <c r="BD6">
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <v>0</v>
+      </c>
+      <c r="BF6">
+        <v>0</v>
+      </c>
+      <c r="BG6">
+        <v>0</v>
+      </c>
+      <c r="BH6">
+        <v>0</v>
+      </c>
+      <c r="BI6">
+        <v>0</v>
+      </c>
+      <c r="BJ6">
+        <v>0</v>
+      </c>
+      <c r="BK6">
+        <v>0</v>
+      </c>
+      <c r="BL6">
+        <v>0</v>
+      </c>
+      <c r="BM6">
+        <v>0</v>
+      </c>
+      <c r="BN6">
+        <v>0</v>
+      </c>
+      <c r="BO6">
+        <v>0</v>
+      </c>
+      <c r="BP6">
+        <v>0</v>
+      </c>
+      <c r="BQ6">
+        <v>0</v>
+      </c>
+      <c r="BR6">
+        <v>0</v>
+      </c>
+      <c r="BS6">
+        <v>0</v>
+      </c>
+      <c r="BT6">
+        <v>0</v>
+      </c>
+      <c r="BU6">
+        <v>0</v>
+      </c>
+      <c r="BV6">
+        <v>0</v>
+      </c>
+      <c r="BW6">
+        <v>0</v>
+      </c>
+      <c r="BX6">
+        <v>0</v>
+      </c>
+      <c r="BY6">
+        <v>0</v>
+      </c>
+      <c r="BZ6">
+        <v>0</v>
+      </c>
+      <c r="CA6">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E7" t="s">
+        <v>101</v>
+      </c>
+      <c r="F7">
+        <v>1.36</v>
+      </c>
+      <c r="G7">
+        <v>1.37</v>
+      </c>
+      <c r="H7">
+        <v>9.4</v>
+      </c>
+      <c r="I7">
+        <v>10</v>
+      </c>
+      <c r="J7">
+        <v>6</v>
+      </c>
+      <c r="K7">
+        <v>6.2</v>
+      </c>
+      <c r="L7">
+        <v>1.01</v>
+      </c>
+      <c r="M7">
+        <v>1.03</v>
+      </c>
+      <c r="N7">
+        <v>6.4</v>
+      </c>
+      <c r="O7">
+        <v>1.16</v>
+      </c>
+      <c r="P7">
+        <v>2.88</v>
+      </c>
+      <c r="Q7">
+        <v>1.5</v>
+      </c>
+      <c r="R7">
+        <v>1.76</v>
+      </c>
+      <c r="S7">
+        <v>2.22</v>
+      </c>
+      <c r="T7">
+        <v>1.82</v>
+      </c>
+      <c r="U7">
+        <v>2.14</v>
+      </c>
+      <c r="V7">
+        <v>1.11</v>
+      </c>
+      <c r="W7">
+        <v>3.7</v>
+      </c>
+      <c r="X7">
+        <v>32</v>
+      </c>
+      <c r="Y7">
+        <v>40</v>
+      </c>
+      <c r="Z7">
+        <v>110</v>
+      </c>
+      <c r="AA7">
+        <v>340</v>
+      </c>
+      <c r="AB7">
+        <v>12</v>
+      </c>
+      <c r="AC7">
+        <v>14</v>
+      </c>
+      <c r="AD7">
+        <v>36</v>
+      </c>
+      <c r="AE7">
+        <v>140</v>
+      </c>
+      <c r="AF7">
+        <v>10</v>
+      </c>
+      <c r="AG7">
+        <v>10.5</v>
+      </c>
+      <c r="AH7">
+        <v>25</v>
+      </c>
+      <c r="AI7">
+        <v>110</v>
+      </c>
+      <c r="AJ7">
+        <v>12</v>
+      </c>
+      <c r="AK7">
+        <v>13.5</v>
+      </c>
+      <c r="AL7">
+        <v>28</v>
+      </c>
+      <c r="AM7">
+        <v>130</v>
+      </c>
+      <c r="AN7">
+        <v>4.4</v>
+      </c>
+      <c r="AO7">
+        <v>140</v>
+      </c>
+      <c r="AP7">
+        <v>28</v>
+      </c>
+      <c r="AQ7">
+        <v>34</v>
+      </c>
+      <c r="AR7">
+        <v>36</v>
+      </c>
+      <c r="AS7">
+        <v>16.5</v>
+      </c>
+      <c r="AT7">
+        <v>11</v>
+      </c>
+      <c r="AU7">
+        <v>12.5</v>
+      </c>
+      <c r="AV7">
+        <v>30</v>
+      </c>
+      <c r="AW7">
+        <v>40</v>
+      </c>
+      <c r="AX7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY7">
+        <v>9.6</v>
+      </c>
+      <c r="AZ7">
+        <v>23</v>
+      </c>
+      <c r="BA7">
+        <v>36</v>
+      </c>
+      <c r="BB7">
+        <v>11</v>
+      </c>
+      <c r="BC7">
+        <v>12</v>
+      </c>
+      <c r="BD7">
+        <v>25</v>
+      </c>
+      <c r="BE7">
+        <v>38</v>
+      </c>
+      <c r="BF7">
+        <v>4.2</v>
+      </c>
+      <c r="BG7">
+        <v>40</v>
+      </c>
+      <c r="BH7">
+        <v>5.6</v>
+      </c>
+      <c r="BI7">
+        <v>3.75</v>
+      </c>
+      <c r="BJ7">
+        <v>13</v>
+      </c>
+      <c r="BK7">
+        <v>3.5</v>
+      </c>
+      <c r="BL7">
+        <v>130</v>
+      </c>
+      <c r="BM7">
+        <v>4.6</v>
+      </c>
+      <c r="BN7">
+        <v>4.9</v>
+      </c>
+      <c r="BO7">
+        <v>3.3</v>
+      </c>
+      <c r="BP7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BQ7">
+        <v>3.15</v>
+      </c>
+      <c r="BR7">
+        <v>24</v>
+      </c>
+      <c r="BS7">
+        <v>4</v>
+      </c>
+      <c r="BT7">
+        <v>15</v>
+      </c>
+      <c r="BU7">
+        <v>3.65</v>
+      </c>
+      <c r="BV7">
+        <v>80</v>
+      </c>
+      <c r="BW7">
+        <v>4.5</v>
+      </c>
+      <c r="BX7">
+        <v>70</v>
+      </c>
+      <c r="BY7">
+        <v>4.5</v>
+      </c>
+      <c r="BZ7">
+        <v>12</v>
+      </c>
+      <c r="CA7">
+        <v>3.45</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
@@ -322,7 +322,7 @@
     <t>Athletic Bilbao</t>
   </si>
   <si>
-    <t>2026-08-25 02:26:08</t>
+    <t>2026-08-25 04:44:01</t>
   </si>
 </sst>
 </file>
@@ -916,166 +916,166 @@
         <v>96</v>
       </c>
       <c r="F2">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="G2">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="H2">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="I2">
-        <v>990</v>
+        <v>7.4</v>
       </c>
       <c r="J2">
-        <v>2.32</v>
+        <v>3.65</v>
       </c>
       <c r="K2">
-        <v>950</v>
+        <v>4.4</v>
       </c>
       <c r="L2">
         <v>1.01</v>
       </c>
       <c r="M2">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O2">
         <v>1.35</v>
       </c>
       <c r="P2">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q2">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R2">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="S2">
+        <v>3.7</v>
+      </c>
+      <c r="T2">
+        <v>2</v>
+      </c>
+      <c r="U2">
+        <v>1.82</v>
+      </c>
+      <c r="V2">
+        <v>1.16</v>
+      </c>
+      <c r="W2">
         <v>2.32</v>
       </c>
-      <c r="T2">
-        <v>1.11</v>
-      </c>
-      <c r="U2">
-        <v>1.11</v>
-      </c>
-      <c r="V2">
-        <v>1.06</v>
-      </c>
-      <c r="W2">
-        <v>2.28</v>
-      </c>
       <c r="X2">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AB2">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AP2">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ2">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AR2">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AS2">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AT2">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU2">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AV2">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AW2">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AX2">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AY2">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ2">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BA2">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB2">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BC2">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BD2">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE2">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF2">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG2">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1161,7 +1161,7 @@
         <v>2.34</v>
       </c>
       <c r="G3">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="H3">
         <v>3.75</v>
@@ -1170,7 +1170,7 @@
         <v>6</v>
       </c>
       <c r="J3">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="K3">
         <v>3.3</v>
@@ -1666,7 +1666,7 @@
         <v>1.09</v>
       </c>
       <c r="N5">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O5">
         <v>1.41</v>
@@ -1696,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="X5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y5">
         <v>13.5</v>
@@ -2126,16 +2126,16 @@
         <v>101</v>
       </c>
       <c r="F7">
+        <v>1.35</v>
+      </c>
+      <c r="G7">
         <v>1.36</v>
       </c>
-      <c r="G7">
-        <v>1.37</v>
-      </c>
       <c r="H7">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -2144,7 +2144,7 @@
         <v>6.2</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M7">
         <v>1.03</v>
@@ -2156,7 +2156,7 @@
         <v>1.16</v>
       </c>
       <c r="P7">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="Q7">
         <v>1.5</v>
@@ -2177,10 +2177,10 @@
         <v>1.11</v>
       </c>
       <c r="W7">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="X7">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y7">
         <v>40</v>
@@ -2201,10 +2201,10 @@
         <v>36</v>
       </c>
       <c r="AE7">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AF7">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG7">
         <v>10.5</v>
@@ -2225,10 +2225,10 @@
         <v>28</v>
       </c>
       <c r="AM7">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN7">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AO7">
         <v>140</v>
@@ -2243,16 +2243,16 @@
         <v>36</v>
       </c>
       <c r="AS7">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AT7">
         <v>11</v>
       </c>
       <c r="AU7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AV7">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AW7">
         <v>40</v>
@@ -2264,25 +2264,25 @@
         <v>9.6</v>
       </c>
       <c r="AZ7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA7">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="BB7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BC7">
         <v>12</v>
       </c>
       <c r="BD7">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="BE7">
         <v>38</v>
       </c>
       <c r="BF7">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BG7">
         <v>40</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
@@ -322,7 +322,7 @@
     <t>Athletic Bilbao</t>
   </si>
   <si>
-    <t>2026-08-25 04:44:01</t>
+    <t>2026-08-25 06:53:18</t>
   </si>
 </sst>
 </file>
@@ -919,7 +919,7 @@
         <v>1.61</v>
       </c>
       <c r="G2">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="H2">
         <v>5.9</v>
@@ -934,7 +934,7 @@
         <v>4.4</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M2">
         <v>1.07</v>
@@ -949,25 +949,25 @@
         <v>1.78</v>
       </c>
       <c r="Q2">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R2">
         <v>1.29</v>
       </c>
       <c r="S2">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="T2">
         <v>2</v>
       </c>
       <c r="U2">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="V2">
         <v>1.16</v>
       </c>
       <c r="W2">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="X2">
         <v>15.5</v>
@@ -982,7 +982,7 @@
         <v>240</v>
       </c>
       <c r="AB2">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AC2">
         <v>10.5</v>
@@ -1030,22 +1030,22 @@
         <v>14</v>
       </c>
       <c r="AR2">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AS2">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AT2">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AU2">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AV2">
         <v>19</v>
       </c>
       <c r="AW2">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AX2">
         <v>8</v>
@@ -1054,10 +1054,10 @@
         <v>8.6</v>
       </c>
       <c r="AZ2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA2">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BB2">
         <v>12.5</v>
@@ -1066,76 +1066,76 @@
         <v>16</v>
       </c>
       <c r="BD2">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BE2">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BF2">
         <v>9.199999999999999</v>
       </c>
       <c r="BG2">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI2">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BO2">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ2">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS2">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU2">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW2">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY2">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="CA2">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="CB2" t="s">
         <v>102</v>
@@ -1173,7 +1173,7 @@
         <v>2.2</v>
       </c>
       <c r="K3">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>3.55</v>
       </c>
       <c r="G4">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="H4">
         <v>2.36</v>
@@ -1415,7 +1415,7 @@
         <v>2.86</v>
       </c>
       <c r="K4">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -1430,7 +1430,7 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="Q4">
         <v>2.68</v>
@@ -1648,46 +1648,46 @@
         <v>2.06</v>
       </c>
       <c r="H5">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I5">
+        <v>4.5</v>
+      </c>
+      <c r="J5">
+        <v>3.5</v>
+      </c>
+      <c r="K5">
+        <v>3.55</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>1.1</v>
+      </c>
+      <c r="N5">
+        <v>3.15</v>
+      </c>
+      <c r="O5">
+        <v>1.44</v>
+      </c>
+      <c r="P5">
+        <v>1.73</v>
+      </c>
+      <c r="Q5">
+        <v>2.28</v>
+      </c>
+      <c r="R5">
+        <v>1.27</v>
+      </c>
+      <c r="S5">
         <v>4.4</v>
       </c>
-      <c r="J5">
-        <v>3.6</v>
-      </c>
-      <c r="K5">
-        <v>3.65</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>1.09</v>
-      </c>
-      <c r="N5">
-        <v>3.25</v>
-      </c>
-      <c r="O5">
-        <v>1.41</v>
-      </c>
-      <c r="P5">
-        <v>1.77</v>
-      </c>
-      <c r="Q5">
-        <v>2.22</v>
-      </c>
-      <c r="R5">
-        <v>1.29</v>
-      </c>
-      <c r="S5">
-        <v>4.2</v>
-      </c>
       <c r="T5">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U5">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="V5">
         <v>0</v>
@@ -1696,10 +1696,10 @@
         <v>0</v>
       </c>
       <c r="X5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y5">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z5">
         <v>32</v>
@@ -1708,13 +1708,13 @@
         <v>120</v>
       </c>
       <c r="AB5">
+        <v>7.6</v>
+      </c>
+      <c r="AC5">
         <v>8</v>
       </c>
-      <c r="AC5">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AD5">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE5">
         <v>65</v>
@@ -1726,52 +1726,52 @@
         <v>11</v>
       </c>
       <c r="AH5">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI5">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AJ5">
         <v>25</v>
       </c>
       <c r="AK5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL5">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AM5">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AN5">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AO5">
         <v>90</v>
       </c>
       <c r="AP5">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR5">
         <v>19.5</v>
       </c>
       <c r="AS5">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AT5">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU5">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV5">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX5">
         <v>10.5</v>
@@ -1780,88 +1780,88 @@
         <v>10</v>
       </c>
       <c r="AZ5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA5">
         <v>34</v>
       </c>
       <c r="BB5">
+        <v>22</v>
+      </c>
+      <c r="BC5">
         <v>21</v>
       </c>
-      <c r="BC5">
-        <v>20</v>
-      </c>
       <c r="BD5">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="BE5">
         <v>14</v>
       </c>
       <c r="BF5">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BG5">
         <v>34</v>
       </c>
       <c r="BH5">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BI5">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="BJ5">
         <v>12.5</v>
       </c>
       <c r="BK5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BL5">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="BM5">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BN5">
         <v>5.2</v>
       </c>
       <c r="BO5">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BP5">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BQ5">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BR5">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BS5">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BT5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU5">
         <v>6</v>
       </c>
       <c r="BV5">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BW5">
+        <v>5.2</v>
+      </c>
+      <c r="BX5">
+        <v>70</v>
+      </c>
+      <c r="BY5">
         <v>5.4</v>
       </c>
-      <c r="BX5">
-        <v>65</v>
-      </c>
-      <c r="BY5">
-        <v>5.6</v>
-      </c>
       <c r="BZ5">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="CA5">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="CB5" t="s">
         <v>102</v>
@@ -1887,16 +1887,16 @@
         <v>1.04</v>
       </c>
       <c r="G6">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H6">
         <v>1.04</v>
       </c>
       <c r="I6">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J6">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -2126,16 +2126,16 @@
         <v>101</v>
       </c>
       <c r="F7">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="G7">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="H7">
+        <v>9.6</v>
+      </c>
+      <c r="I7">
         <v>10</v>
-      </c>
-      <c r="I7">
-        <v>10.5</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -2150,7 +2150,7 @@
         <v>1.03</v>
       </c>
       <c r="N7">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O7">
         <v>1.16</v>
@@ -2159,16 +2159,16 @@
         <v>2.9</v>
       </c>
       <c r="Q7">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="R7">
         <v>1.76</v>
       </c>
       <c r="S7">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T7">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U7">
         <v>2.14</v>
@@ -2183,22 +2183,22 @@
         <v>30</v>
       </c>
       <c r="Y7">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Z7">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AA7">
         <v>340</v>
       </c>
       <c r="AB7">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC7">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AD7">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AE7">
         <v>150</v>
@@ -2210,16 +2210,16 @@
         <v>10.5</v>
       </c>
       <c r="AH7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI7">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ7">
         <v>12</v>
       </c>
       <c r="AK7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AL7">
         <v>28</v>
@@ -2237,13 +2237,13 @@
         <v>28</v>
       </c>
       <c r="AQ7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AR7">
         <v>36</v>
       </c>
       <c r="AS7">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT7">
         <v>11</v>
@@ -2252,7 +2252,7 @@
         <v>13</v>
       </c>
       <c r="AV7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW7">
         <v>40</v>
@@ -2267,7 +2267,7 @@
         <v>22</v>
       </c>
       <c r="BA7">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="BB7">
         <v>10.5</v>
@@ -2276,7 +2276,7 @@
         <v>12</v>
       </c>
       <c r="BD7">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="BE7">
         <v>38</v>
@@ -2285,13 +2285,13 @@
         <v>4.1</v>
       </c>
       <c r="BG7">
-        <v>40</v>
+        <v>16.5</v>
       </c>
       <c r="BH7">
         <v>5.6</v>
       </c>
       <c r="BI7">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BJ7">
         <v>13</v>
@@ -2309,10 +2309,10 @@
         <v>4.9</v>
       </c>
       <c r="BO7">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BP7">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BQ7">
         <v>3.15</v>
@@ -2327,7 +2327,7 @@
         <v>15</v>
       </c>
       <c r="BU7">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BV7">
         <v>80</v>
@@ -2345,7 +2345,7 @@
         <v>12</v>
       </c>
       <c r="CA7">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="CB7" t="s">
         <v>102</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
@@ -322,7 +322,7 @@
     <t>Athletic Bilbao</t>
   </si>
   <si>
-    <t>2026-08-25 06:53:18</t>
+    <t>2026-08-25 09:02:57</t>
   </si>
 </sst>
 </file>
@@ -919,7 +919,7 @@
         <v>1.61</v>
       </c>
       <c r="G2">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="H2">
         <v>5.9</v>
@@ -934,7 +934,7 @@
         <v>4.4</v>
       </c>
       <c r="L2">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="M2">
         <v>1.07</v>
@@ -949,25 +949,25 @@
         <v>1.78</v>
       </c>
       <c r="Q2">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R2">
         <v>1.29</v>
       </c>
       <c r="S2">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="T2">
         <v>2</v>
       </c>
       <c r="U2">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="V2">
         <v>1.16</v>
       </c>
       <c r="W2">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="X2">
         <v>15.5</v>
@@ -1048,10 +1048,10 @@
         <v>4.8</v>
       </c>
       <c r="AX2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AY2">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AZ2">
         <v>18</v>
@@ -1063,7 +1063,7 @@
         <v>12.5</v>
       </c>
       <c r="BC2">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BD2">
         <v>4.5</v>
@@ -1158,19 +1158,19 @@
         <v>97</v>
       </c>
       <c r="F3">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="G3">
         <v>2.64</v>
       </c>
       <c r="H3">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J3">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="K3">
         <v>3.1</v>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Q3">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>3.55</v>
       </c>
       <c r="G4">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H4">
         <v>2.36</v>
@@ -1412,7 +1412,7 @@
         <v>2.64</v>
       </c>
       <c r="J4">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="K4">
         <v>3.4</v>
@@ -1430,7 +1430,7 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="Q4">
         <v>2.68</v>
@@ -1642,16 +1642,16 @@
         <v>99</v>
       </c>
       <c r="F5">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G5">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H5">
         <v>4.3</v>
       </c>
       <c r="I5">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J5">
         <v>3.5</v>
@@ -1669,13 +1669,13 @@
         <v>3.15</v>
       </c>
       <c r="O5">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P5">
         <v>1.73</v>
       </c>
       <c r="Q5">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R5">
         <v>1.27</v>
@@ -1705,7 +1705,7 @@
         <v>32</v>
       </c>
       <c r="AA5">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB5">
         <v>7.6</v>
@@ -1717,7 +1717,7 @@
         <v>18</v>
       </c>
       <c r="AE5">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AF5">
         <v>11.5</v>
@@ -1729,7 +1729,7 @@
         <v>23</v>
       </c>
       <c r="AI5">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ5">
         <v>25</v>
@@ -1741,16 +1741,16 @@
         <v>48</v>
       </c>
       <c r="AM5">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AN5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO5">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AP5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ5">
         <v>11.5</v>
@@ -1768,13 +1768,13 @@
         <v>7.2</v>
       </c>
       <c r="AV5">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW5">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AX5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY5">
         <v>10</v>
@@ -1783,13 +1783,13 @@
         <v>20</v>
       </c>
       <c r="BA5">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BB5">
         <v>22</v>
       </c>
       <c r="BC5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD5">
         <v>26</v>
@@ -1798,7 +1798,7 @@
         <v>14</v>
       </c>
       <c r="BF5">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BG5">
         <v>34</v>
@@ -1807,7 +1807,7 @@
         <v>3.3</v>
       </c>
       <c r="BI5">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="BJ5">
         <v>12.5</v>
@@ -1819,49 +1819,49 @@
         <v>200</v>
       </c>
       <c r="BM5">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BN5">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO5">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BP5">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BQ5">
         <v>4.4</v>
       </c>
       <c r="BR5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BS5">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BT5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BU5">
         <v>6</v>
       </c>
       <c r="BV5">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BW5">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BX5">
         <v>70</v>
       </c>
       <c r="BY5">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BZ5">
         <v>40</v>
       </c>
       <c r="CA5">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="CB5" t="s">
         <v>102</v>
@@ -1896,7 +1896,7 @@
         <v>870</v>
       </c>
       <c r="J6">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -2126,22 +2126,22 @@
         <v>101</v>
       </c>
       <c r="F7">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="G7">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="H7">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="J7">
         <v>6</v>
       </c>
       <c r="K7">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="L7">
         <v>1.21</v>
@@ -2156,31 +2156,31 @@
         <v>1.16</v>
       </c>
       <c r="P7">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="Q7">
         <v>1.49</v>
       </c>
       <c r="R7">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="S7">
         <v>2.2</v>
       </c>
       <c r="T7">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U7">
         <v>2.14</v>
       </c>
       <c r="V7">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W7">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="X7">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y7">
         <v>42</v>
@@ -2189,61 +2189,61 @@
         <v>120</v>
       </c>
       <c r="AA7">
-        <v>340</v>
+        <v>410</v>
       </c>
       <c r="AB7">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC7">
         <v>14.5</v>
       </c>
       <c r="AD7">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AE7">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="AF7">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG7">
         <v>10.5</v>
       </c>
       <c r="AH7">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI7">
         <v>120</v>
       </c>
       <c r="AJ7">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AK7">
         <v>13</v>
       </c>
       <c r="AL7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM7">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN7">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AO7">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AP7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ7">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AR7">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AS7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AT7">
         <v>11</v>
@@ -2252,7 +2252,7 @@
         <v>13</v>
       </c>
       <c r="AV7">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="AW7">
         <v>40</v>
@@ -2264,10 +2264,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA7">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BB7">
         <v>10.5</v>
@@ -2276,16 +2276,16 @@
         <v>12</v>
       </c>
       <c r="BD7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE7">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="BF7">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BG7">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BH7">
         <v>5.6</v>
@@ -2297,13 +2297,13 @@
         <v>13</v>
       </c>
       <c r="BK7">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BL7">
         <v>130</v>
       </c>
       <c r="BM7">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BN7">
         <v>4.9</v>
@@ -2315,37 +2315,37 @@
         <v>9.4</v>
       </c>
       <c r="BQ7">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BR7">
         <v>24</v>
       </c>
       <c r="BS7">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BT7">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BU7">
         <v>3.6</v>
       </c>
       <c r="BV7">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BW7">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BX7">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BY7">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BZ7">
         <v>12</v>
       </c>
       <c r="CA7">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="CB7" t="s">
         <v>102</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="105">
   <si>
     <t>League</t>
   </si>
@@ -292,6 +292,9 @@
     <t>Modern Sport FC</t>
   </si>
   <si>
+    <t>Pyramids</t>
+  </si>
+  <si>
     <t>Al Mokawloon</t>
   </si>
   <si>
@@ -310,6 +313,9 @@
     <t>Ghazl El Mahallah</t>
   </si>
   <si>
+    <t>Abo Qair Semads</t>
+  </si>
+  <si>
     <t>Al-Masry</t>
   </si>
   <si>
@@ -322,7 +328,7 @@
     <t>Athletic Bilbao</t>
   </si>
   <si>
-    <t>2026-08-25 09:02:57</t>
+    <t>2026-08-25 11:12:55</t>
   </si>
 </sst>
 </file>
@@ -654,7 +660,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB7"/>
+  <dimension ref="A1:CB8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -913,181 +919,181 @@
         <v>90</v>
       </c>
       <c r="E2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F2">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="G2">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="H2">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="I2">
-        <v>7.4</v>
+        <v>990</v>
       </c>
       <c r="J2">
-        <v>3.65</v>
+        <v>2.36</v>
       </c>
       <c r="K2">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L2">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="M2">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="N2">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="O2">
         <v>1.35</v>
       </c>
       <c r="P2">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
       <c r="Q2">
-        <v>2.04</v>
+        <v>1.79</v>
       </c>
       <c r="R2">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S2">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="T2">
-        <v>2</v>
+        <v>1.11</v>
       </c>
       <c r="U2">
-        <v>1.82</v>
+        <v>1.11</v>
       </c>
       <c r="V2">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="W2">
         <v>2.32</v>
       </c>
       <c r="X2">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AC2">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD2">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AE2">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG2">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH2">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI2">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AK2">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL2">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM2">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AO2">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AR2">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS2">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AT2">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU2">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV2">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AW2">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX2">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY2">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA2">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB2">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC2">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD2">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE2">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BF2">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG2">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BH2">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BI2">
         <v>2.7</v>
       </c>
       <c r="BJ2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK2">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1120,7 +1126,7 @@
         <v>5.2</v>
       </c>
       <c r="BV2">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
         <v>9.199999999999999</v>
@@ -1135,10 +1141,10 @@
         <v>25</v>
       </c>
       <c r="CA2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1155,7 +1161,7 @@
         <v>91</v>
       </c>
       <c r="E3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F3">
         <v>2.3</v>
@@ -1164,223 +1170,223 @@
         <v>2.64</v>
       </c>
       <c r="H3">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="I3">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="J3">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="K3">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P3">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Q3">
         <v>3.05</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1397,25 +1403,25 @@
         <v>92</v>
       </c>
       <c r="E4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F4">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="G4">
+        <v>1.36</v>
+      </c>
+      <c r="H4">
+        <v>11</v>
+      </c>
+      <c r="I4">
+        <v>870</v>
+      </c>
+      <c r="J4">
         <v>4.4</v>
       </c>
-      <c r="H4">
-        <v>2.36</v>
-      </c>
-      <c r="I4">
-        <v>2.64</v>
-      </c>
-      <c r="J4">
-        <v>2.9</v>
-      </c>
       <c r="K4">
-        <v>3.4</v>
+        <v>500</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -1430,10 +1436,10 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>1.41</v>
+        <v>1.7</v>
       </c>
       <c r="Q4">
-        <v>2.68</v>
+        <v>1.81</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -1622,72 +1628,72 @@
         <v>0</v>
       </c>
       <c r="CB4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B5" t="s">
         <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
         <v>93</v>
       </c>
       <c r="E5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F5">
-        <v>2.04</v>
+        <v>3.55</v>
       </c>
       <c r="G5">
-        <v>2.08</v>
+        <v>4.5</v>
       </c>
       <c r="H5">
-        <v>4.3</v>
+        <v>2.36</v>
       </c>
       <c r="I5">
-        <v>4.4</v>
+        <v>2.74</v>
       </c>
       <c r="J5">
-        <v>3.5</v>
+        <v>2.72</v>
       </c>
       <c r="K5">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="Q5">
-        <v>2.3</v>
+        <v>2.78</v>
       </c>
       <c r="R5">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V5">
         <v>0</v>
@@ -1696,240 +1702,240 @@
         <v>0</v>
       </c>
       <c r="X5">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Y5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z5">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AC5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AH5">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AK5">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AL5">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AN5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AO5">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AP5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AQ5">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AR5">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AS5">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AT5">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AU5">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AV5">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AW5">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AX5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AY5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AZ5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BA5">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BB5">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BC5">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BD5">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BE5">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BF5">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BG5">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BH5">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BI5">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="BJ5">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BK5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BL5">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="BM5">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BN5">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BO5">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="BP5">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BQ5">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BR5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BS5">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BT5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BU5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BV5">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BW5">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BX5">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="BY5">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BZ5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="CA5">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B6" t="s">
         <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
         <v>94</v>
       </c>
       <c r="E6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F6">
-        <v>1.04</v>
+        <v>2.04</v>
       </c>
       <c r="G6">
-        <v>600</v>
+        <v>2.06</v>
       </c>
       <c r="H6">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="I6">
-        <v>870</v>
+        <v>4.4</v>
       </c>
       <c r="J6">
+        <v>3.5</v>
+      </c>
+      <c r="K6">
+        <v>3.55</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
         <v>1.09</v>
       </c>
-      <c r="K6">
-        <v>950</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
       <c r="N6">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P6">
-        <v>1.24</v>
+        <v>1.73</v>
       </c>
       <c r="Q6">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V6">
         <v>0</v>
@@ -1938,180 +1944,180 @@
         <v>0</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AO6">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AU6">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV6">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AW6">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AX6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AY6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ6">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BA6">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BD6">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BE6">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BF6">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BG6">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BH6">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BI6">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BJ6">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BK6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BL6">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="BM6">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BN6">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BO6">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BP6">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BQ6">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BR6">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BS6">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BT6">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU6">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BV6">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BW6">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BX6">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="BY6">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BZ6">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="CA6">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="CB6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B7" t="s">
         <v>84</v>
@@ -2123,232 +2129,474 @@
         <v>95</v>
       </c>
       <c r="E7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F7">
-        <v>1.34</v>
+        <v>1.04</v>
       </c>
       <c r="G7">
+        <v>600</v>
+      </c>
+      <c r="H7">
+        <v>1.04</v>
+      </c>
+      <c r="I7">
+        <v>870</v>
+      </c>
+      <c r="J7">
+        <v>1.09</v>
+      </c>
+      <c r="K7">
+        <v>950</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>1.24</v>
+      </c>
+      <c r="Q7">
+        <v>1.01</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+      <c r="BG7">
+        <v>0</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BM7">
+        <v>0</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <v>0</v>
+      </c>
+      <c r="BR7">
+        <v>0</v>
+      </c>
+      <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>0</v>
+      </c>
+      <c r="BU7">
+        <v>0</v>
+      </c>
+      <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
+        <v>0</v>
+      </c>
+      <c r="BX7">
+        <v>0</v>
+      </c>
+      <c r="BY7">
+        <v>0</v>
+      </c>
+      <c r="BZ7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E8" t="s">
+        <v>103</v>
+      </c>
+      <c r="F8">
+        <v>1.33</v>
+      </c>
+      <c r="G8">
         <v>1.35</v>
       </c>
-      <c r="H7">
+      <c r="H8">
         <v>10</v>
       </c>
-      <c r="I7">
+      <c r="I8">
         <v>10.5</v>
       </c>
-      <c r="J7">
-        <v>6</v>
-      </c>
-      <c r="K7">
+      <c r="J8">
+        <v>6.2</v>
+      </c>
+      <c r="K8">
         <v>6.4</v>
       </c>
-      <c r="L7">
+      <c r="L8">
         <v>1.21</v>
       </c>
-      <c r="M7">
+      <c r="M8">
         <v>1.03</v>
       </c>
-      <c r="N7">
-        <v>6.6</v>
-      </c>
-      <c r="O7">
+      <c r="N8">
+        <v>6.2</v>
+      </c>
+      <c r="O8">
         <v>1.16</v>
       </c>
-      <c r="P7">
+      <c r="P8">
         <v>2.92</v>
       </c>
-      <c r="Q7">
+      <c r="Q8">
         <v>1.49</v>
       </c>
-      <c r="R7">
-        <v>1.77</v>
-      </c>
-      <c r="S7">
-        <v>2.2</v>
-      </c>
-      <c r="T7">
-        <v>1.82</v>
-      </c>
-      <c r="U7">
+      <c r="R8">
+        <v>1.76</v>
+      </c>
+      <c r="S8">
         <v>2.14</v>
       </c>
-      <c r="V7">
+      <c r="T8">
+        <v>1.78</v>
+      </c>
+      <c r="U8">
+        <v>2.16</v>
+      </c>
+      <c r="V8">
         <v>1.1</v>
       </c>
-      <c r="W7">
+      <c r="W8">
         <v>3.85</v>
       </c>
-      <c r="X7">
+      <c r="X8">
         <v>32</v>
       </c>
-      <c r="Y7">
+      <c r="Y8">
+        <v>48</v>
+      </c>
+      <c r="Z8">
+        <v>1000</v>
+      </c>
+      <c r="AA8">
+        <v>1000</v>
+      </c>
+      <c r="AB8">
+        <v>12.5</v>
+      </c>
+      <c r="AC8">
+        <v>15</v>
+      </c>
+      <c r="AD8">
         <v>42</v>
       </c>
-      <c r="Z7">
+      <c r="AE8">
+        <v>180</v>
+      </c>
+      <c r="AF8">
+        <v>9.6</v>
+      </c>
+      <c r="AG8">
+        <v>10.5</v>
+      </c>
+      <c r="AH8">
+        <v>26</v>
+      </c>
+      <c r="AI8">
         <v>120</v>
       </c>
-      <c r="AA7">
-        <v>410</v>
-      </c>
-      <c r="AB7">
+      <c r="AJ8">
         <v>12</v>
       </c>
-      <c r="AC7">
-        <v>14.5</v>
-      </c>
-      <c r="AD7">
+      <c r="AK8">
+        <v>13</v>
+      </c>
+      <c r="AL8">
+        <v>30</v>
+      </c>
+      <c r="AM8">
+        <v>1000</v>
+      </c>
+      <c r="AN8">
+        <v>4.2</v>
+      </c>
+      <c r="AO8">
+        <v>170</v>
+      </c>
+      <c r="AP8">
+        <v>28</v>
+      </c>
+      <c r="AQ8">
+        <v>32</v>
+      </c>
+      <c r="AR8">
         <v>38</v>
       </c>
-      <c r="AE7">
-        <v>180</v>
-      </c>
-      <c r="AF7">
+      <c r="AS8">
+        <v>60</v>
+      </c>
+      <c r="AT8">
+        <v>11</v>
+      </c>
+      <c r="AU8">
+        <v>13</v>
+      </c>
+      <c r="AV8">
+        <v>30</v>
+      </c>
+      <c r="AW8">
+        <v>40</v>
+      </c>
+      <c r="AX8">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY8">
         <v>9.6</v>
       </c>
-      <c r="AG7">
+      <c r="AZ8">
+        <v>22</v>
+      </c>
+      <c r="BA8">
+        <v>48</v>
+      </c>
+      <c r="BB8">
         <v>10.5</v>
       </c>
-      <c r="AH7">
+      <c r="BC8">
+        <v>11.5</v>
+      </c>
+      <c r="BD8">
         <v>25</v>
       </c>
-      <c r="AI7">
-        <v>120</v>
-      </c>
-      <c r="AJ7">
-        <v>11.5</v>
-      </c>
-      <c r="AK7">
+      <c r="BE8">
+        <v>50</v>
+      </c>
+      <c r="BF8">
+        <v>3.95</v>
+      </c>
+      <c r="BG8">
+        <v>42</v>
+      </c>
+      <c r="BH8">
+        <v>5.6</v>
+      </c>
+      <c r="BI8">
+        <v>3.7</v>
+      </c>
+      <c r="BJ8">
         <v>13</v>
       </c>
-      <c r="AL7">
-        <v>29</v>
-      </c>
-      <c r="AM7">
-        <v>130</v>
-      </c>
-      <c r="AN7">
-        <v>4.2</v>
-      </c>
-      <c r="AO7">
-        <v>170</v>
-      </c>
-      <c r="AP7">
-        <v>29</v>
-      </c>
-      <c r="AQ7">
-        <v>36</v>
-      </c>
-      <c r="AR7">
-        <v>38</v>
-      </c>
-      <c r="AS7">
-        <v>20</v>
-      </c>
-      <c r="AT7">
-        <v>11</v>
-      </c>
-      <c r="AU7">
-        <v>13</v>
-      </c>
-      <c r="AV7">
-        <v>32</v>
-      </c>
-      <c r="AW7">
-        <v>40</v>
-      </c>
-      <c r="AX7">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY7">
-        <v>9.6</v>
-      </c>
-      <c r="AZ7">
-        <v>23</v>
-      </c>
-      <c r="BA7">
-        <v>55</v>
-      </c>
-      <c r="BB7">
-        <v>10.5</v>
-      </c>
-      <c r="BC7">
+      <c r="BK8">
+        <v>2.14</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>2.56</v>
+      </c>
+      <c r="BN8">
+        <v>4.9</v>
+      </c>
+      <c r="BO8">
+        <v>3.25</v>
+      </c>
+      <c r="BP8">
+        <v>1000</v>
+      </c>
+      <c r="BQ8">
+        <v>2.56</v>
+      </c>
+      <c r="BR8">
+        <v>24</v>
+      </c>
+      <c r="BS8">
+        <v>2.32</v>
+      </c>
+      <c r="BT8">
+        <v>1000</v>
+      </c>
+      <c r="BU8">
+        <v>2.56</v>
+      </c>
+      <c r="BV8">
+        <v>85</v>
+      </c>
+      <c r="BW8">
+        <v>2.5</v>
+      </c>
+      <c r="BX8">
+        <v>75</v>
+      </c>
+      <c r="BY8">
+        <v>2.48</v>
+      </c>
+      <c r="BZ8">
         <v>12</v>
       </c>
-      <c r="BD7">
-        <v>26</v>
-      </c>
-      <c r="BE7">
-        <v>60</v>
-      </c>
-      <c r="BF7">
-        <v>4</v>
-      </c>
-      <c r="BG7">
-        <v>19</v>
-      </c>
-      <c r="BH7">
-        <v>5.6</v>
-      </c>
-      <c r="BI7">
-        <v>3.7</v>
-      </c>
-      <c r="BJ7">
-        <v>13</v>
-      </c>
-      <c r="BK7">
-        <v>3.45</v>
-      </c>
-      <c r="BL7">
-        <v>130</v>
-      </c>
-      <c r="BM7">
-        <v>4.5</v>
-      </c>
-      <c r="BN7">
-        <v>4.9</v>
-      </c>
-      <c r="BO7">
-        <v>3.25</v>
-      </c>
-      <c r="BP7">
-        <v>9.4</v>
-      </c>
-      <c r="BQ7">
-        <v>3.1</v>
-      </c>
-      <c r="BR7">
-        <v>24</v>
-      </c>
-      <c r="BS7">
-        <v>3.9</v>
-      </c>
-      <c r="BT7">
-        <v>15.5</v>
-      </c>
-      <c r="BU7">
-        <v>3.6</v>
-      </c>
-      <c r="BV7">
-        <v>85</v>
-      </c>
-      <c r="BW7">
-        <v>4.4</v>
-      </c>
-      <c r="BX7">
-        <v>75</v>
-      </c>
-      <c r="BY7">
-        <v>4.4</v>
-      </c>
-      <c r="BZ7">
-        <v>12</v>
-      </c>
-      <c r="CA7">
-        <v>3.35</v>
-      </c>
-      <c r="CB7" t="s">
-        <v>102</v>
+      <c r="CA8">
+        <v>2.12</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
@@ -328,7 +328,7 @@
     <t>Athletic Bilbao</t>
   </si>
   <si>
-    <t>2026-08-25 11:12:55</t>
+    <t>2026-08-25 13:22:45</t>
   </si>
 </sst>
 </file>
@@ -922,166 +922,166 @@
         <v>97</v>
       </c>
       <c r="F2">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="G2">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H2">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="I2">
-        <v>990</v>
+        <v>7.2</v>
       </c>
       <c r="J2">
-        <v>2.36</v>
+        <v>3.7</v>
       </c>
       <c r="K2">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L2">
         <v>1.38</v>
       </c>
       <c r="M2">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O2">
         <v>1.35</v>
       </c>
       <c r="P2">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="Q2">
-        <v>1.79</v>
+        <v>2.02</v>
       </c>
       <c r="R2">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S2">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="T2">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="U2">
-        <v>1.11</v>
+        <v>1.82</v>
       </c>
       <c r="V2">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="W2">
         <v>2.32</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AB2">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AP2">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ2">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AR2">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AS2">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT2">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AU2">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV2">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AW2">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX2">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AY2">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ2">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BA2">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB2">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BC2">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BD2">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE2">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF2">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG2">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH2">
         <v>3.35</v>
@@ -1167,7 +1167,7 @@
         <v>2.3</v>
       </c>
       <c r="G3">
-        <v>2.64</v>
+        <v>3.1</v>
       </c>
       <c r="H3">
         <v>3.7</v>
@@ -1176,7 +1176,7 @@
         <v>5.6</v>
       </c>
       <c r="J3">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="K3">
         <v>3.05</v>
@@ -1188,13 +1188,13 @@
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>1.24</v>
+        <v>1.85</v>
       </c>
       <c r="O3">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="P3">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Q3">
         <v>3.05</v>
@@ -1203,22 +1203,22 @@
         <v>1.08</v>
       </c>
       <c r="S3">
-        <v>3.05</v>
+        <v>5.9</v>
       </c>
       <c r="T3">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U3">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="V3">
         <v>1.21</v>
       </c>
       <c r="W3">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="Y3">
         <v>1000</v>
@@ -1272,7 +1272,7 @@
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AQ3">
         <v>1.01</v>
@@ -1326,64 +1326,64 @@
         <v>1.01</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>2.64</v>
       </c>
       <c r="BI3">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="BN3">
         <v>1000</v>
       </c>
       <c r="BO3">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="BT3">
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="CB3" t="s">
         <v>104</v>
@@ -1406,10 +1406,10 @@
         <v>99</v>
       </c>
       <c r="F4">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="G4">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="H4">
         <v>11</v>
@@ -1421,7 +1421,7 @@
         <v>4.4</v>
       </c>
       <c r="K4">
-        <v>500</v>
+        <v>8.4</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -1648,40 +1648,40 @@
         <v>100</v>
       </c>
       <c r="F5">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="G5">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H5">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="I5">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="J5">
+        <v>2.84</v>
+      </c>
+      <c r="K5">
+        <v>3.15</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>1.41</v>
+      </c>
+      <c r="Q5">
         <v>2.72</v>
-      </c>
-      <c r="K5">
-        <v>3.4</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>1.4</v>
-      </c>
-      <c r="Q5">
-        <v>2.78</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -1899,7 +1899,7 @@
         <v>4.3</v>
       </c>
       <c r="I6">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J6">
         <v>3.5</v>
@@ -1911,7 +1911,7 @@
         <v>0</v>
       </c>
       <c r="M6">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N6">
         <v>3.15</v>
@@ -1932,7 +1932,7 @@
         <v>4.4</v>
       </c>
       <c r="T6">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U6">
         <v>1.91</v>
@@ -1944,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="X6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y6">
         <v>13</v>
@@ -1959,13 +1959,13 @@
         <v>7.6</v>
       </c>
       <c r="AC6">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD6">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE6">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AF6">
         <v>11.5</v>
@@ -2004,10 +2004,10 @@
         <v>11.5</v>
       </c>
       <c r="AR6">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AS6">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="AT6">
         <v>7.2</v>
@@ -2040,16 +2040,16 @@
         <v>22</v>
       </c>
       <c r="BD6">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="BE6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BF6">
         <v>17.5</v>
       </c>
       <c r="BG6">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BH6">
         <v>3.35</v>
@@ -2377,79 +2377,79 @@
         <v>1.33</v>
       </c>
       <c r="G8">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="H8">
         <v>10</v>
       </c>
       <c r="I8">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="J8">
         <v>6.2</v>
       </c>
       <c r="K8">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="L8">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M8">
         <v>1.03</v>
       </c>
       <c r="N8">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="O8">
         <v>1.16</v>
       </c>
       <c r="P8">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="Q8">
         <v>1.49</v>
       </c>
       <c r="R8">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="S8">
+        <v>2.2</v>
+      </c>
+      <c r="T8">
+        <v>1.83</v>
+      </c>
+      <c r="U8">
         <v>2.14</v>
-      </c>
-      <c r="T8">
-        <v>1.78</v>
-      </c>
-      <c r="U8">
-        <v>2.16</v>
       </c>
       <c r="V8">
         <v>1.1</v>
       </c>
       <c r="W8">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="X8">
         <v>32</v>
       </c>
       <c r="Y8">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>410</v>
       </c>
       <c r="AB8">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC8">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AD8">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AE8">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AF8">
         <v>9.6</v>
@@ -2470,22 +2470,22 @@
         <v>13</v>
       </c>
       <c r="AL8">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN8">
         <v>4.2</v>
       </c>
       <c r="AO8">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AP8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ8">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AR8">
         <v>38</v>
@@ -2500,7 +2500,7 @@
         <v>13</v>
       </c>
       <c r="AV8">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AW8">
         <v>40</v>
@@ -2512,16 +2512,16 @@
         <v>9.6</v>
       </c>
       <c r="AZ8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BB8">
         <v>10.5</v>
       </c>
       <c r="BC8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD8">
         <v>25</v>
@@ -2530,28 +2530,28 @@
         <v>50</v>
       </c>
       <c r="BF8">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BG8">
         <v>42</v>
       </c>
       <c r="BH8">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BI8">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BJ8">
         <v>13</v>
       </c>
       <c r="BK8">
-        <v>2.14</v>
+        <v>3.5</v>
       </c>
       <c r="BL8">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM8">
-        <v>2.56</v>
+        <v>4.6</v>
       </c>
       <c r="BN8">
         <v>4.9</v>
@@ -2560,40 +2560,40 @@
         <v>3.25</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ8">
-        <v>2.56</v>
+        <v>3.15</v>
       </c>
       <c r="BR8">
         <v>24</v>
       </c>
       <c r="BS8">
-        <v>2.32</v>
+        <v>4</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BU8">
-        <v>2.56</v>
+        <v>3.65</v>
       </c>
       <c r="BV8">
         <v>85</v>
       </c>
       <c r="BW8">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="BX8">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BY8">
-        <v>2.48</v>
+        <v>4.5</v>
       </c>
       <c r="BZ8">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CA8">
-        <v>2.12</v>
+        <v>3.4</v>
       </c>
       <c r="CB8" t="s">
         <v>104</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="109">
   <si>
     <t>League</t>
   </si>
@@ -262,6 +262,9 @@
     <t>Egyptian Premier</t>
   </si>
   <si>
+    <t>Qatari Stars League</t>
+  </si>
+  <si>
     <t>Spanish La Liga</t>
   </si>
   <si>
@@ -277,6 +280,9 @@
     <t>14:00:00</t>
   </si>
   <si>
+    <t>16:30:00</t>
+  </si>
+  <si>
     <t>17:00:00</t>
   </si>
   <si>
@@ -292,6 +298,9 @@
     <t>Modern Sport FC</t>
   </si>
   <si>
+    <t>Al-Wakra</t>
+  </si>
+  <si>
     <t>Pyramids</t>
   </si>
   <si>
@@ -313,6 +322,9 @@
     <t>Ghazl El Mahallah</t>
   </si>
   <si>
+    <t>Al Rayyan</t>
+  </si>
+  <si>
     <t>Abo Qair Semads</t>
   </si>
   <si>
@@ -328,7 +340,7 @@
     <t>Athletic Bilbao</t>
   </si>
   <si>
-    <t>2026-08-25 13:22:45</t>
+    <t>2026-08-25 15:31:23</t>
   </si>
 </sst>
 </file>
@@ -660,7 +672,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB8"/>
+  <dimension ref="A1:CB9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -910,19 +922,19 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F2">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G2">
         <v>1.75</v>
@@ -943,13 +955,13 @@
         <v>1.38</v>
       </c>
       <c r="M2">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N2">
         <v>3.3</v>
       </c>
       <c r="O2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P2">
         <v>1.79</v>
@@ -961,7 +973,7 @@
         <v>1.29</v>
       </c>
       <c r="S2">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T2">
         <v>2</v>
@@ -985,7 +997,7 @@
         <v>60</v>
       </c>
       <c r="AA2">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AB2">
         <v>8.4</v>
@@ -1144,7 +1156,7 @@
         <v>7.6</v>
       </c>
       <c r="CB2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1152,16 +1164,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F3">
         <v>2.3</v>
@@ -1275,55 +1287,55 @@
         <v>4.1</v>
       </c>
       <c r="AQ3">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AR3">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AS3">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AT3">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AU3">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AV3">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AW3">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AX3">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AY3">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AZ3">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BA3">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BB3">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BC3">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BD3">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BE3">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BF3">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BG3">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BH3">
         <v>2.64</v>
@@ -1386,249 +1398,249 @@
         <v>1.63</v>
       </c>
       <c r="CB3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:80">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F4">
-        <v>1.22</v>
+        <v>3.35</v>
       </c>
       <c r="G4">
-        <v>1.42</v>
+        <v>3.75</v>
       </c>
       <c r="H4">
+        <v>2.1</v>
+      </c>
+      <c r="I4">
+        <v>2.22</v>
+      </c>
+      <c r="J4">
+        <v>3.65</v>
+      </c>
+      <c r="K4">
+        <v>4.4</v>
+      </c>
+      <c r="L4">
+        <v>1.01</v>
+      </c>
+      <c r="M4">
+        <v>1.01</v>
+      </c>
+      <c r="N4">
+        <v>5</v>
+      </c>
+      <c r="O4">
+        <v>1.2</v>
+      </c>
+      <c r="P4">
+        <v>2.36</v>
+      </c>
+      <c r="Q4">
+        <v>1.59</v>
+      </c>
+      <c r="R4">
+        <v>1.55</v>
+      </c>
+      <c r="S4">
+        <v>2.46</v>
+      </c>
+      <c r="T4">
+        <v>1.54</v>
+      </c>
+      <c r="U4">
+        <v>2.48</v>
+      </c>
+      <c r="V4">
+        <v>1.82</v>
+      </c>
+      <c r="W4">
+        <v>1.36</v>
+      </c>
+      <c r="X4">
+        <v>28</v>
+      </c>
+      <c r="Y4">
+        <v>16</v>
+      </c>
+      <c r="Z4">
+        <v>19</v>
+      </c>
+      <c r="AA4">
+        <v>32</v>
+      </c>
+      <c r="AB4">
+        <v>24</v>
+      </c>
+      <c r="AC4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD4">
+        <v>13</v>
+      </c>
+      <c r="AE4">
+        <v>22</v>
+      </c>
+      <c r="AF4">
+        <v>30</v>
+      </c>
+      <c r="AG4">
+        <v>19.5</v>
+      </c>
+      <c r="AH4">
+        <v>16</v>
+      </c>
+      <c r="AI4">
+        <v>28</v>
+      </c>
+      <c r="AJ4">
+        <v>70</v>
+      </c>
+      <c r="AK4">
+        <v>42</v>
+      </c>
+      <c r="AL4">
+        <v>44</v>
+      </c>
+      <c r="AM4">
+        <v>60</v>
+      </c>
+      <c r="AN4">
+        <v>30</v>
+      </c>
+      <c r="AO4">
+        <v>13.5</v>
+      </c>
+      <c r="AP4">
+        <v>17.5</v>
+      </c>
+      <c r="AQ4">
         <v>11</v>
       </c>
-      <c r="I4">
-        <v>870</v>
-      </c>
-      <c r="J4">
-        <v>4.4</v>
-      </c>
-      <c r="K4">
-        <v>8.4</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>1.7</v>
-      </c>
-      <c r="Q4">
-        <v>1.81</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <v>0</v>
-      </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0</v>
-      </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>0</v>
-      </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
-      <c r="AI4">
-        <v>0</v>
-      </c>
-      <c r="AJ4">
-        <v>0</v>
-      </c>
-      <c r="AK4">
-        <v>0</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>0</v>
-      </c>
-      <c r="AO4">
-        <v>0</v>
-      </c>
-      <c r="AP4">
-        <v>0</v>
-      </c>
-      <c r="AQ4">
-        <v>0</v>
-      </c>
       <c r="AR4">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AU4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AV4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AW4">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AX4">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AY4">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AZ4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BA4">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BB4">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BC4">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BD4">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BE4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BF4">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BG4">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BH4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1636,483 +1648,483 @@
         <v>81</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F5">
-        <v>3.45</v>
+        <v>1.23</v>
       </c>
       <c r="G5">
+        <v>1.42</v>
+      </c>
+      <c r="H5">
+        <v>11</v>
+      </c>
+      <c r="I5">
+        <v>870</v>
+      </c>
+      <c r="J5">
         <v>4.4</v>
       </c>
-      <c r="H5">
-        <v>2.38</v>
-      </c>
-      <c r="I5">
-        <v>2.66</v>
-      </c>
-      <c r="J5">
-        <v>2.84</v>
-      </c>
       <c r="K5">
+        <v>10</v>
+      </c>
+      <c r="L5">
+        <v>1.33</v>
+      </c>
+      <c r="M5">
+        <v>1.01</v>
+      </c>
+      <c r="N5">
         <v>3.15</v>
       </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
       <c r="O5">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P5">
-        <v>1.41</v>
+        <v>1.7</v>
       </c>
       <c r="Q5">
-        <v>2.72</v>
+        <v>1.81</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F6">
-        <v>2.04</v>
+        <v>3.55</v>
       </c>
       <c r="G6">
-        <v>2.06</v>
+        <v>4.3</v>
       </c>
       <c r="H6">
-        <v>4.3</v>
+        <v>2.38</v>
       </c>
       <c r="I6">
-        <v>4.5</v>
+        <v>2.72</v>
       </c>
       <c r="J6">
-        <v>3.5</v>
+        <v>2.74</v>
       </c>
       <c r="K6">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M6">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N6">
-        <v>3.15</v>
+        <v>2.36</v>
       </c>
       <c r="O6">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="P6">
-        <v>1.73</v>
+        <v>1.46</v>
       </c>
       <c r="Q6">
-        <v>2.28</v>
+        <v>2.8</v>
       </c>
       <c r="R6">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="S6">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="T6">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="U6">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X6">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="Y6">
-        <v>13</v>
+        <v>8.6</v>
       </c>
       <c r="Z6">
-        <v>32</v>
+        <v>17.5</v>
       </c>
       <c r="AA6">
-        <v>130</v>
+        <v>48</v>
       </c>
       <c r="AB6">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="AC6">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AD6">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AE6">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="AF6">
-        <v>11.5</v>
+        <v>30</v>
       </c>
       <c r="AG6">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="AH6">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AI6">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AJ6">
-        <v>25</v>
+        <v>110</v>
       </c>
       <c r="AK6">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="AL6">
+        <v>120</v>
+      </c>
+      <c r="AM6">
+        <v>260</v>
+      </c>
+      <c r="AN6">
+        <v>120</v>
+      </c>
+      <c r="AO6">
         <v>55</v>
       </c>
-      <c r="AM6">
-        <v>180</v>
-      </c>
-      <c r="AN6">
-        <v>19.5</v>
-      </c>
-      <c r="AO6">
-        <v>110</v>
-      </c>
       <c r="AP6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AQ6">
-        <v>11.5</v>
+        <v>5.4</v>
       </c>
       <c r="AR6">
-        <v>29</v>
+        <v>10.5</v>
       </c>
       <c r="AS6">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="AT6">
         <v>7.2</v>
       </c>
       <c r="AU6">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="AV6">
-        <v>16.5</v>
+        <v>10</v>
       </c>
       <c r="AW6">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="AX6">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AY6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ6">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA6">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="BB6">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="BC6">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="BD6">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="BE6">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BF6">
-        <v>17.5</v>
+        <v>65</v>
       </c>
       <c r="BG6">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="BH6">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>2.52</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BL6">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BP6">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR6">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BV6">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BX6">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2120,64 +2132,64 @@
         <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E7" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F7">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="G7">
-        <v>600</v>
+        <v>2.04</v>
       </c>
       <c r="H7">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="I7">
-        <v>870</v>
+        <v>4.5</v>
       </c>
       <c r="J7">
-        <v>1.09</v>
+        <v>3.5</v>
       </c>
       <c r="K7">
-        <v>950</v>
+        <v>3.55</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P7">
-        <v>1.24</v>
+        <v>1.74</v>
       </c>
       <c r="Q7">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="V7">
         <v>0</v>
@@ -2186,417 +2198,659 @@
         <v>0</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AO7">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AP7">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AU7">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV7">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AW7">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AX7">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AY7">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ7">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BA7">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BB7">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BC7">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD7">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BE7">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BF7">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BG7">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BH7">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BI7">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BJ7">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BK7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BL7">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="BM7">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BN7">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BO7">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BP7">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BQ7">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BR7">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BS7">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BT7">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BU7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BV7">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BW7">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BX7">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="BY7">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BZ7">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="CA7">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="CB7" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E8" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F8">
+        <v>1.04</v>
+      </c>
+      <c r="G8">
+        <v>600</v>
+      </c>
+      <c r="H8">
+        <v>1.04</v>
+      </c>
+      <c r="I8">
+        <v>870</v>
+      </c>
+      <c r="J8">
+        <v>1.09</v>
+      </c>
+      <c r="K8">
+        <v>950</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>1.24</v>
+      </c>
+      <c r="Q8">
+        <v>1.01</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <v>0</v>
+      </c>
+      <c r="BC8">
+        <v>0</v>
+      </c>
+      <c r="BD8">
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <v>0</v>
+      </c>
+      <c r="BF8">
+        <v>0</v>
+      </c>
+      <c r="BG8">
+        <v>0</v>
+      </c>
+      <c r="BH8">
+        <v>0</v>
+      </c>
+      <c r="BI8">
+        <v>0</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
+      </c>
+      <c r="BK8">
+        <v>0</v>
+      </c>
+      <c r="BL8">
+        <v>0</v>
+      </c>
+      <c r="BM8">
+        <v>0</v>
+      </c>
+      <c r="BN8">
+        <v>0</v>
+      </c>
+      <c r="BO8">
+        <v>0</v>
+      </c>
+      <c r="BP8">
+        <v>0</v>
+      </c>
+      <c r="BQ8">
+        <v>0</v>
+      </c>
+      <c r="BR8">
+        <v>0</v>
+      </c>
+      <c r="BS8">
+        <v>0</v>
+      </c>
+      <c r="BT8">
+        <v>0</v>
+      </c>
+      <c r="BU8">
+        <v>0</v>
+      </c>
+      <c r="BV8">
+        <v>0</v>
+      </c>
+      <c r="BW8">
+        <v>0</v>
+      </c>
+      <c r="BX8">
+        <v>0</v>
+      </c>
+      <c r="BY8">
+        <v>0</v>
+      </c>
+      <c r="BZ8">
+        <v>0</v>
+      </c>
+      <c r="CA8">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D9" t="s">
+        <v>99</v>
+      </c>
+      <c r="E9" t="s">
+        <v>107</v>
+      </c>
+      <c r="F9">
         <v>1.33</v>
       </c>
-      <c r="G8">
+      <c r="G9">
         <v>1.34</v>
       </c>
-      <c r="H8">
-        <v>10</v>
-      </c>
-      <c r="I8">
+      <c r="H9">
+        <v>10.5</v>
+      </c>
+      <c r="I9">
         <v>11</v>
       </c>
-      <c r="J8">
+      <c r="J9">
         <v>6.2</v>
       </c>
-      <c r="K8">
+      <c r="K9">
         <v>6.6</v>
       </c>
-      <c r="L8">
+      <c r="L9">
         <v>1.22</v>
       </c>
-      <c r="M8">
+      <c r="M9">
         <v>1.03</v>
       </c>
-      <c r="N8">
+      <c r="N9">
         <v>6.6</v>
       </c>
-      <c r="O8">
+      <c r="O9">
         <v>1.16</v>
       </c>
-      <c r="P8">
+      <c r="P9">
         <v>2.98</v>
       </c>
-      <c r="Q8">
+      <c r="Q9">
         <v>1.49</v>
       </c>
-      <c r="R8">
+      <c r="R9">
         <v>1.77</v>
       </c>
-      <c r="S8">
+      <c r="S9">
         <v>2.2</v>
       </c>
-      <c r="T8">
+      <c r="T9">
         <v>1.83</v>
       </c>
-      <c r="U8">
+      <c r="U9">
         <v>2.14</v>
       </c>
-      <c r="V8">
+      <c r="V9">
         <v>1.1</v>
       </c>
-      <c r="W8">
+      <c r="W9">
         <v>3.9</v>
       </c>
-      <c r="X8">
+      <c r="X9">
         <v>32</v>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <v>42</v>
       </c>
-      <c r="Z8">
+      <c r="Z9">
         <v>120</v>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <v>410</v>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <v>12</v>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <v>14.5</v>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <v>38</v>
       </c>
-      <c r="AE8">
+      <c r="AE9">
         <v>170</v>
       </c>
-      <c r="AF8">
+      <c r="AF9">
         <v>9.6</v>
       </c>
-      <c r="AG8">
+      <c r="AG9">
         <v>10.5</v>
       </c>
-      <c r="AH8">
+      <c r="AH9">
         <v>26</v>
       </c>
-      <c r="AI8">
+      <c r="AI9">
         <v>120</v>
       </c>
-      <c r="AJ8">
+      <c r="AJ9">
         <v>12</v>
       </c>
-      <c r="AK8">
+      <c r="AK9">
         <v>13</v>
       </c>
-      <c r="AL8">
+      <c r="AL9">
         <v>28</v>
       </c>
-      <c r="AM8">
+      <c r="AM9">
         <v>130</v>
       </c>
-      <c r="AN8">
+      <c r="AN9">
         <v>4.2</v>
       </c>
-      <c r="AO8">
+      <c r="AO9">
         <v>160</v>
       </c>
-      <c r="AP8">
-        <v>27</v>
-      </c>
-      <c r="AQ8">
+      <c r="AP9">
+        <v>28</v>
+      </c>
+      <c r="AQ9">
         <v>36</v>
       </c>
-      <c r="AR8">
+      <c r="AR9">
         <v>38</v>
       </c>
-      <c r="AS8">
+      <c r="AS9">
         <v>60</v>
       </c>
-      <c r="AT8">
+      <c r="AT9">
         <v>11</v>
       </c>
-      <c r="AU8">
+      <c r="AU9">
         <v>13</v>
       </c>
-      <c r="AV8">
+      <c r="AV9">
         <v>32</v>
       </c>
-      <c r="AW8">
-        <v>40</v>
-      </c>
-      <c r="AX8">
+      <c r="AW9">
+        <v>42</v>
+      </c>
+      <c r="AX9">
+        <v>9</v>
+      </c>
+      <c r="AY9">
+        <v>9.6</v>
+      </c>
+      <c r="AZ9">
+        <v>23</v>
+      </c>
+      <c r="BA9">
+        <v>50</v>
+      </c>
+      <c r="BB9">
+        <v>10.5</v>
+      </c>
+      <c r="BC9">
+        <v>12</v>
+      </c>
+      <c r="BD9">
+        <v>26</v>
+      </c>
+      <c r="BE9">
+        <v>50</v>
+      </c>
+      <c r="BF9">
+        <v>4</v>
+      </c>
+      <c r="BG9">
+        <v>42</v>
+      </c>
+      <c r="BH9">
+        <v>5.7</v>
+      </c>
+      <c r="BI9">
+        <v>3.8</v>
+      </c>
+      <c r="BJ9">
+        <v>13</v>
+      </c>
+      <c r="BK9">
+        <v>3.5</v>
+      </c>
+      <c r="BL9">
+        <v>130</v>
+      </c>
+      <c r="BM9">
+        <v>4.6</v>
+      </c>
+      <c r="BN9">
+        <v>4.9</v>
+      </c>
+      <c r="BO9">
+        <v>3.25</v>
+      </c>
+      <c r="BP9">
         <v>9.199999999999999</v>
       </c>
-      <c r="AY8">
-        <v>9.6</v>
-      </c>
-      <c r="AZ8">
-        <v>23</v>
-      </c>
-      <c r="BA8">
-        <v>50</v>
-      </c>
-      <c r="BB8">
-        <v>10.5</v>
-      </c>
-      <c r="BC8">
-        <v>12</v>
-      </c>
-      <c r="BD8">
-        <v>25</v>
-      </c>
-      <c r="BE8">
-        <v>50</v>
-      </c>
-      <c r="BF8">
+      <c r="BQ9">
+        <v>3.15</v>
+      </c>
+      <c r="BR9">
+        <v>24</v>
+      </c>
+      <c r="BS9">
         <v>4</v>
       </c>
-      <c r="BG8">
-        <v>42</v>
-      </c>
-      <c r="BH8">
-        <v>5.7</v>
-      </c>
-      <c r="BI8">
-        <v>3.8</v>
-      </c>
-      <c r="BJ8">
-        <v>13</v>
-      </c>
-      <c r="BK8">
-        <v>3.5</v>
-      </c>
-      <c r="BL8">
-        <v>130</v>
-      </c>
-      <c r="BM8">
-        <v>4.6</v>
-      </c>
-      <c r="BN8">
-        <v>4.9</v>
-      </c>
-      <c r="BO8">
-        <v>3.25</v>
-      </c>
-      <c r="BP8">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BQ8">
-        <v>3.15</v>
-      </c>
-      <c r="BR8">
-        <v>24</v>
-      </c>
-      <c r="BS8">
-        <v>4</v>
-      </c>
-      <c r="BT8">
+      <c r="BT9">
         <v>15</v>
       </c>
-      <c r="BU8">
+      <c r="BU9">
         <v>3.65</v>
       </c>
-      <c r="BV8">
+      <c r="BV9">
         <v>85</v>
       </c>
-      <c r="BW8">
+      <c r="BW9">
         <v>4.5</v>
       </c>
-      <c r="BX8">
+      <c r="BX9">
         <v>70</v>
       </c>
-      <c r="BY8">
+      <c r="BY9">
         <v>4.5</v>
       </c>
-      <c r="BZ8">
+      <c r="BZ9">
         <v>11.5</v>
       </c>
-      <c r="CA8">
+      <c r="CA9">
         <v>3.4</v>
       </c>
-      <c r="CB8" t="s">
-        <v>104</v>
+      <c r="CB9" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="113">
   <si>
     <t>League</t>
   </si>
@@ -268,6 +268,9 @@
     <t>Spanish La Liga</t>
   </si>
   <si>
+    <t>English National League</t>
+  </si>
+  <si>
     <t>Bolivian Liga de Futbol Profesional</t>
   </si>
   <si>
@@ -289,6 +292,9 @@
     <t>18:30:00</t>
   </si>
   <si>
+    <t>18:45:00</t>
+  </si>
+  <si>
     <t>19:00:00</t>
   </si>
   <si>
@@ -310,6 +316,9 @@
     <t>Celta Vigo</t>
   </si>
   <si>
+    <t>Boreham Wood</t>
+  </si>
+  <si>
     <t>Always Ready</t>
   </si>
   <si>
@@ -334,13 +343,16 @@
     <t>Osasuna</t>
   </si>
   <si>
+    <t>Boston Utd</t>
+  </si>
+  <si>
     <t>Aurora</t>
   </si>
   <si>
     <t>Athletic Bilbao</t>
   </si>
   <si>
-    <t>2026-08-25 15:31:23</t>
+    <t>2026-08-25 17:41:34</t>
   </si>
 </sst>
 </file>
@@ -672,7 +684,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB9"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -922,25 +934,25 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F2">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="G2">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="H2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I2">
         <v>7.2</v>
@@ -952,7 +964,7 @@
         <v>4.3</v>
       </c>
       <c r="L2">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="M2">
         <v>1.07</v>
@@ -985,7 +997,7 @@
         <v>1.16</v>
       </c>
       <c r="W2">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="X2">
         <v>15</v>
@@ -1024,7 +1036,7 @@
         <v>120</v>
       </c>
       <c r="AJ2">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AK2">
         <v>23</v>
@@ -1048,10 +1060,10 @@
         <v>14</v>
       </c>
       <c r="AR2">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS2">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT2">
         <v>5.8</v>
@@ -1063,7 +1075,7 @@
         <v>19</v>
       </c>
       <c r="AW2">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX2">
         <v>8</v>
@@ -1072,28 +1084,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA2">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB2">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BC2">
         <v>16</v>
       </c>
       <c r="BD2">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE2">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BF2">
         <v>9.199999999999999</v>
       </c>
       <c r="BG2">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BH2">
         <v>3.35</v>
@@ -1105,13 +1117,13 @@
         <v>12</v>
       </c>
       <c r="BK2">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN2">
         <v>4.2</v>
@@ -1123,16 +1135,16 @@
         <v>12</v>
       </c>
       <c r="BQ2">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BR2">
         <v>32</v>
       </c>
       <c r="BS2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BT2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BU2">
         <v>5.2</v>
@@ -1141,22 +1153,22 @@
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX2">
         <v>75</v>
       </c>
       <c r="BY2">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BZ2">
         <v>25</v>
       </c>
       <c r="CA2">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="CB2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1164,49 +1176,49 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F3">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="G3">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I3">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="J3">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="K3">
         <v>3.05</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="N3">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="O3">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P3">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Q3">
         <v>3.05</v>
@@ -1215,10 +1227,10 @@
         <v>1.08</v>
       </c>
       <c r="S3">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="T3">
-        <v>1.11</v>
+        <v>2.16</v>
       </c>
       <c r="U3">
         <v>1.48</v>
@@ -1227,10 +1239,10 @@
         <v>1.21</v>
       </c>
       <c r="W3">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X3">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
         <v>1000</v>
@@ -1284,121 +1296,121 @@
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AR3">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AS3">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AT3">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AU3">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AV3">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AW3">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AX3">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AY3">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BA3">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BB3">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BC3">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BD3">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BE3">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BF3">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BG3">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BH3">
-        <v>2.64</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>1.92</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>1.63</v>
+        <v>1.04</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.63</v>
+        <v>1.04</v>
       </c>
       <c r="BN3">
         <v>1000</v>
       </c>
       <c r="BO3">
-        <v>1.63</v>
+        <v>1.04</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.63</v>
+        <v>1.04</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.63</v>
+        <v>1.04</v>
       </c>
       <c r="BT3">
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>1.63</v>
+        <v>1.04</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.63</v>
+        <v>1.04</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.63</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.63</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1406,31 +1418,31 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F4">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="G4">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="H4">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="I4">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="J4">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K4">
         <v>4.4</v>
@@ -1448,13 +1460,13 @@
         <v>1.2</v>
       </c>
       <c r="P4">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q4">
         <v>1.59</v>
       </c>
       <c r="R4">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S4">
         <v>2.46</v>
@@ -1466,25 +1478,25 @@
         <v>2.48</v>
       </c>
       <c r="V4">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="W4">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="X4">
         <v>28</v>
       </c>
       <c r="Y4">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z4">
         <v>19</v>
       </c>
       <c r="AA4">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AB4">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AC4">
         <v>9.800000000000001</v>
@@ -1493,10 +1505,10 @@
         <v>13</v>
       </c>
       <c r="AE4">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF4">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AG4">
         <v>19.5</v>
@@ -1520,10 +1532,10 @@
         <v>60</v>
       </c>
       <c r="AN4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO4">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AP4">
         <v>17.5</v>
@@ -1535,7 +1547,7 @@
         <v>12.5</v>
       </c>
       <c r="AS4">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AT4">
         <v>17</v>
@@ -1544,13 +1556,13 @@
         <v>8</v>
       </c>
       <c r="AV4">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW4">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AX4">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="AY4">
         <v>12.5</v>
@@ -1562,22 +1574,22 @@
         <v>16.5</v>
       </c>
       <c r="BB4">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BC4">
         <v>27</v>
       </c>
       <c r="BD4">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BE4">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BF4">
         <v>21</v>
       </c>
       <c r="BG4">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1640,7 +1652,7 @@
         <v>1.04</v>
       </c>
       <c r="CB4" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1648,16 +1660,16 @@
         <v>81</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F5">
         <v>1.23</v>
@@ -1666,49 +1678,49 @@
         <v>1.42</v>
       </c>
       <c r="H5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="I5">
-        <v>870</v>
+        <v>27</v>
       </c>
       <c r="J5">
         <v>4.4</v>
       </c>
       <c r="K5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L5">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M5">
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="O5">
         <v>1.33</v>
       </c>
       <c r="P5">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q5">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R5">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S5">
         <v>3</v>
       </c>
       <c r="T5">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U5">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V5">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W5">
         <v>3.35</v>
@@ -1768,52 +1780,52 @@
         <v>1000</v>
       </c>
       <c r="AP5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF5">
         <v>1.01</v>
@@ -1825,64 +1837,64 @@
         <v>1000</v>
       </c>
       <c r="BI5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5">
         <v>1000</v>
       </c>
       <c r="BK5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN5">
         <v>1000</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP5">
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT5">
         <v>1000</v>
       </c>
       <c r="BU5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1890,52 +1902,52 @@
         <v>81</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E6" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F6">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="G6">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H6">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="I6">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="J6">
         <v>2.74</v>
       </c>
       <c r="K6">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="L6">
         <v>1.51</v>
       </c>
       <c r="M6">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="N6">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="O6">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="P6">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q6">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="R6">
         <v>1.16</v>
@@ -1947,13 +1959,13 @@
         <v>2.14</v>
       </c>
       <c r="U6">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="V6">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W6">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="X6">
         <v>9.6</v>
@@ -1965,13 +1977,13 @@
         <v>17.5</v>
       </c>
       <c r="AA6">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB6">
         <v>12</v>
       </c>
       <c r="AC6">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD6">
         <v>15.5</v>
@@ -1980,7 +1992,7 @@
         <v>46</v>
       </c>
       <c r="AF6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AG6">
         <v>21</v>
@@ -1995,7 +2007,7 @@
         <v>110</v>
       </c>
       <c r="AK6">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AL6">
         <v>120</v>
@@ -2004,10 +2016,10 @@
         <v>260</v>
       </c>
       <c r="AN6">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AO6">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP6">
         <v>6</v>
@@ -2016,115 +2028,115 @@
         <v>5.4</v>
       </c>
       <c r="AR6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AS6">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AT6">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU6">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AV6">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW6">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AX6">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AY6">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ6">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA6">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB6">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC6">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BD6">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BE6">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF6">
-        <v>65</v>
+        <v>4.2</v>
       </c>
       <c r="BG6">
-        <v>30</v>
+        <v>3.95</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>2.98</v>
       </c>
       <c r="BI6">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK6">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="CB6" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2132,19 +2144,19 @@
         <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E7" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F7">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G7">
         <v>2.04</v>
@@ -2162,10 +2174,10 @@
         <v>3.55</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M7">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N7">
         <v>3.15</v>
@@ -2192,10 +2204,10 @@
         <v>1.92</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="X7">
         <v>11</v>
@@ -2207,7 +2219,7 @@
         <v>32</v>
       </c>
       <c r="AA7">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB7">
         <v>7.8</v>
@@ -2231,10 +2243,10 @@
         <v>22</v>
       </c>
       <c r="AI7">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AJ7">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK7">
         <v>24</v>
@@ -2249,31 +2261,31 @@
         <v>19</v>
       </c>
       <c r="AO7">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AP7">
         <v>10</v>
       </c>
       <c r="AQ7">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR7">
         <v>29</v>
       </c>
       <c r="AS7">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="AT7">
         <v>7.2</v>
       </c>
       <c r="AU7">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV7">
         <v>16</v>
       </c>
       <c r="AW7">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AX7">
         <v>10.5</v>
@@ -2282,40 +2294,40 @@
         <v>10</v>
       </c>
       <c r="AZ7">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA7">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="BB7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC7">
         <v>21</v>
       </c>
       <c r="BD7">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="BE7">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="BF7">
         <v>17</v>
       </c>
       <c r="BG7">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="BH7">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BI7">
-        <v>2.52</v>
+        <v>2.76</v>
       </c>
       <c r="BJ7">
         <v>12.5</v>
       </c>
       <c r="BK7">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BL7">
         <v>200</v>
@@ -2327,7 +2339,7 @@
         <v>5.1</v>
       </c>
       <c r="BO7">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="BP7">
         <v>17.5</v>
@@ -2345,7 +2357,7 @@
         <v>9</v>
       </c>
       <c r="BU7">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BV7">
         <v>50</v>
@@ -2366,7 +2378,7 @@
         <v>5.1</v>
       </c>
       <c r="CB7" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2374,483 +2386,725 @@
         <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F8">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G8">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H8">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="I8">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J8">
+        <v>1.11</v>
+      </c>
+      <c r="K8">
+        <v>500</v>
+      </c>
+      <c r="L8">
+        <v>1.01</v>
+      </c>
+      <c r="M8">
+        <v>1.03</v>
+      </c>
+      <c r="N8">
+        <v>1.12</v>
+      </c>
+      <c r="O8">
+        <v>1.18</v>
+      </c>
+      <c r="P8">
+        <v>1.12</v>
+      </c>
+      <c r="Q8">
+        <v>1.17</v>
+      </c>
+      <c r="R8">
         <v>1.09</v>
       </c>
-      <c r="K8">
-        <v>950</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>1.24</v>
-      </c>
-      <c r="Q8">
-        <v>1.01</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" t="s">
+        <v>110</v>
+      </c>
+      <c r="F9">
+        <v>1.04</v>
+      </c>
+      <c r="G9">
+        <v>990</v>
+      </c>
+      <c r="H9">
+        <v>1.04</v>
+      </c>
+      <c r="I9">
+        <v>990</v>
+      </c>
+      <c r="J9">
+        <v>1.09</v>
+      </c>
+      <c r="K9">
+        <v>950</v>
+      </c>
+      <c r="L9">
+        <v>1.01</v>
+      </c>
+      <c r="M9">
+        <v>1.01</v>
+      </c>
+      <c r="N9">
+        <v>1.25</v>
+      </c>
+      <c r="O9">
+        <v>1.08</v>
+      </c>
+      <c r="P9">
+        <v>1.24</v>
+      </c>
+      <c r="Q9">
+        <v>1.08</v>
+      </c>
+      <c r="R9">
+        <v>1.18</v>
+      </c>
+      <c r="S9">
+        <v>1.08</v>
+      </c>
+      <c r="T9">
+        <v>1.11</v>
+      </c>
+      <c r="U9">
+        <v>1.11</v>
+      </c>
+      <c r="V9">
+        <v>1.01</v>
+      </c>
+      <c r="W9">
+        <v>1.01</v>
+      </c>
+      <c r="X9">
+        <v>1000</v>
+      </c>
+      <c r="Y9">
+        <v>1000</v>
+      </c>
+      <c r="Z9">
+        <v>1000</v>
+      </c>
+      <c r="AA9">
+        <v>1000</v>
+      </c>
+      <c r="AB9">
+        <v>1000</v>
+      </c>
+      <c r="AC9">
+        <v>1000</v>
+      </c>
+      <c r="AD9">
+        <v>1000</v>
+      </c>
+      <c r="AE9">
+        <v>1000</v>
+      </c>
+      <c r="AF9">
+        <v>1000</v>
+      </c>
+      <c r="AG9">
+        <v>1000</v>
+      </c>
+      <c r="AH9">
+        <v>1000</v>
+      </c>
+      <c r="AI9">
+        <v>1000</v>
+      </c>
+      <c r="AJ9">
+        <v>1000</v>
+      </c>
+      <c r="AK9">
+        <v>1000</v>
+      </c>
+      <c r="AL9">
+        <v>1000</v>
+      </c>
+      <c r="AM9">
+        <v>1000</v>
+      </c>
+      <c r="AN9">
+        <v>1000</v>
+      </c>
+      <c r="AO9">
+        <v>1000</v>
+      </c>
+      <c r="AP9">
+        <v>1.01</v>
+      </c>
+      <c r="AQ9">
+        <v>1.01</v>
+      </c>
+      <c r="AR9">
+        <v>1.01</v>
+      </c>
+      <c r="AS9">
+        <v>1.01</v>
+      </c>
+      <c r="AT9">
+        <v>1.01</v>
+      </c>
+      <c r="AU9">
+        <v>1.01</v>
+      </c>
+      <c r="AV9">
+        <v>1.01</v>
+      </c>
+      <c r="AW9">
+        <v>1.01</v>
+      </c>
+      <c r="AX9">
+        <v>1.01</v>
+      </c>
+      <c r="AY9">
+        <v>1.01</v>
+      </c>
+      <c r="AZ9">
+        <v>1.01</v>
+      </c>
+      <c r="BA9">
+        <v>1.01</v>
+      </c>
+      <c r="BB9">
+        <v>1.01</v>
+      </c>
+      <c r="BC9">
+        <v>1.01</v>
+      </c>
+      <c r="BD9">
+        <v>1.01</v>
+      </c>
+      <c r="BE9">
+        <v>1.01</v>
+      </c>
+      <c r="BF9">
+        <v>1.01</v>
+      </c>
+      <c r="BG9">
+        <v>1.01</v>
+      </c>
+      <c r="BH9">
+        <v>1000</v>
+      </c>
+      <c r="BI9">
+        <v>1.04</v>
+      </c>
+      <c r="BJ9">
+        <v>1000</v>
+      </c>
+      <c r="BK9">
+        <v>1.04</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>1.04</v>
+      </c>
+      <c r="BN9">
+        <v>1000</v>
+      </c>
+      <c r="BO9">
+        <v>1.04</v>
+      </c>
+      <c r="BP9">
+        <v>1000</v>
+      </c>
+      <c r="BQ9">
+        <v>1.04</v>
+      </c>
+      <c r="BR9">
+        <v>1000</v>
+      </c>
+      <c r="BS9">
+        <v>1.04</v>
+      </c>
+      <c r="BT9">
+        <v>1000</v>
+      </c>
+      <c r="BU9">
+        <v>1.04</v>
+      </c>
+      <c r="BV9">
+        <v>1000</v>
+      </c>
+      <c r="BW9">
+        <v>1.04</v>
+      </c>
+      <c r="BX9">
+        <v>1000</v>
+      </c>
+      <c r="BY9">
+        <v>1.04</v>
+      </c>
+      <c r="BZ9">
+        <v>0</v>
+      </c>
+      <c r="CA9">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
         <v>83</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D10" t="s">
+        <v>102</v>
+      </c>
+      <c r="E10" t="s">
+        <v>111</v>
+      </c>
+      <c r="F10">
+        <v>1.34</v>
+      </c>
+      <c r="G10">
+        <v>1.35</v>
+      </c>
+      <c r="H10">
+        <v>10.5</v>
+      </c>
+      <c r="I10">
+        <v>11</v>
+      </c>
+      <c r="J10">
+        <v>6.2</v>
+      </c>
+      <c r="K10">
+        <v>6.4</v>
+      </c>
+      <c r="L10">
+        <v>1.23</v>
+      </c>
+      <c r="M10">
+        <v>1.03</v>
+      </c>
+      <c r="N10">
+        <v>6.6</v>
+      </c>
+      <c r="O10">
+        <v>1.16</v>
+      </c>
+      <c r="P10">
+        <v>3</v>
+      </c>
+      <c r="Q10">
+        <v>1.48</v>
+      </c>
+      <c r="R10">
+        <v>1.78</v>
+      </c>
+      <c r="S10">
+        <v>2.2</v>
+      </c>
+      <c r="T10">
+        <v>1.83</v>
+      </c>
+      <c r="U10">
+        <v>2.14</v>
+      </c>
+      <c r="V10">
+        <v>1.1</v>
+      </c>
+      <c r="W10">
+        <v>3.85</v>
+      </c>
+      <c r="X10">
+        <v>30</v>
+      </c>
+      <c r="Y10">
+        <v>46</v>
+      </c>
+      <c r="Z10">
+        <v>110</v>
+      </c>
+      <c r="AA10">
+        <v>360</v>
+      </c>
+      <c r="AB10">
+        <v>12</v>
+      </c>
+      <c r="AC10">
+        <v>14.5</v>
+      </c>
+      <c r="AD10">
+        <v>38</v>
+      </c>
+      <c r="AE10">
+        <v>150</v>
+      </c>
+      <c r="AF10">
+        <v>9.6</v>
+      </c>
+      <c r="AG10">
+        <v>10.5</v>
+      </c>
+      <c r="AH10">
+        <v>25</v>
+      </c>
+      <c r="AI10">
+        <v>100</v>
+      </c>
+      <c r="AJ10">
+        <v>11.5</v>
+      </c>
+      <c r="AK10">
+        <v>12.5</v>
+      </c>
+      <c r="AL10">
+        <v>28</v>
+      </c>
+      <c r="AM10">
+        <v>110</v>
+      </c>
+      <c r="AN10">
+        <v>4.2</v>
+      </c>
+      <c r="AO10">
+        <v>120</v>
+      </c>
+      <c r="AP10">
+        <v>28</v>
+      </c>
+      <c r="AQ10">
+        <v>38</v>
+      </c>
+      <c r="AR10">
+        <v>70</v>
+      </c>
+      <c r="AS10">
+        <v>26</v>
+      </c>
+      <c r="AT10">
+        <v>11.5</v>
+      </c>
+      <c r="AU10">
+        <v>13</v>
+      </c>
+      <c r="AV10">
+        <v>34</v>
+      </c>
+      <c r="AW10">
+        <v>42</v>
+      </c>
+      <c r="AX10">
+        <v>9</v>
+      </c>
+      <c r="AY10">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ10">
+        <v>23</v>
+      </c>
+      <c r="BA10">
+        <v>55</v>
+      </c>
+      <c r="BB10">
+        <v>10.5</v>
+      </c>
+      <c r="BC10">
+        <v>12</v>
+      </c>
+      <c r="BD10">
+        <v>25</v>
+      </c>
+      <c r="BE10">
+        <v>60</v>
+      </c>
+      <c r="BF10">
+        <v>4</v>
+      </c>
+      <c r="BG10">
+        <v>42</v>
+      </c>
+      <c r="BH10">
+        <v>5.7</v>
+      </c>
+      <c r="BI10">
+        <v>3.8</v>
+      </c>
+      <c r="BJ10">
+        <v>13</v>
+      </c>
+      <c r="BK10">
+        <v>3.5</v>
+      </c>
+      <c r="BL10">
+        <v>130</v>
+      </c>
+      <c r="BM10">
+        <v>4.6</v>
+      </c>
+      <c r="BN10">
+        <v>4.9</v>
+      </c>
+      <c r="BO10">
+        <v>3.65</v>
+      </c>
+      <c r="BP10">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BQ10">
+        <v>6.4</v>
+      </c>
+      <c r="BR10">
+        <v>24</v>
+      </c>
+      <c r="BS10">
+        <v>4</v>
+      </c>
+      <c r="BT10">
+        <v>15</v>
+      </c>
+      <c r="BU10">
+        <v>9.6</v>
+      </c>
+      <c r="BV10">
         <v>85</v>
       </c>
-      <c r="C9" t="s">
-        <v>91</v>
-      </c>
-      <c r="D9" t="s">
-        <v>99</v>
-      </c>
-      <c r="E9" t="s">
-        <v>107</v>
-      </c>
-      <c r="F9">
-        <v>1.33</v>
-      </c>
-      <c r="G9">
-        <v>1.34</v>
-      </c>
-      <c r="H9">
-        <v>10.5</v>
-      </c>
-      <c r="I9">
-        <v>11</v>
-      </c>
-      <c r="J9">
-        <v>6.2</v>
-      </c>
-      <c r="K9">
-        <v>6.6</v>
-      </c>
-      <c r="L9">
-        <v>1.22</v>
-      </c>
-      <c r="M9">
-        <v>1.03</v>
-      </c>
-      <c r="N9">
-        <v>6.6</v>
-      </c>
-      <c r="O9">
-        <v>1.16</v>
-      </c>
-      <c r="P9">
-        <v>2.98</v>
-      </c>
-      <c r="Q9">
-        <v>1.49</v>
-      </c>
-      <c r="R9">
-        <v>1.77</v>
-      </c>
-      <c r="S9">
-        <v>2.2</v>
-      </c>
-      <c r="T9">
-        <v>1.83</v>
-      </c>
-      <c r="U9">
-        <v>2.14</v>
-      </c>
-      <c r="V9">
-        <v>1.1</v>
-      </c>
-      <c r="W9">
-        <v>3.9</v>
-      </c>
-      <c r="X9">
-        <v>32</v>
-      </c>
-      <c r="Y9">
-        <v>42</v>
-      </c>
-      <c r="Z9">
-        <v>120</v>
-      </c>
-      <c r="AA9">
-        <v>410</v>
-      </c>
-      <c r="AB9">
-        <v>12</v>
-      </c>
-      <c r="AC9">
-        <v>14.5</v>
-      </c>
-      <c r="AD9">
-        <v>38</v>
-      </c>
-      <c r="AE9">
-        <v>170</v>
-      </c>
-      <c r="AF9">
-        <v>9.6</v>
-      </c>
-      <c r="AG9">
-        <v>10.5</v>
-      </c>
-      <c r="AH9">
-        <v>26</v>
-      </c>
-      <c r="AI9">
-        <v>120</v>
-      </c>
-      <c r="AJ9">
-        <v>12</v>
-      </c>
-      <c r="AK9">
-        <v>13</v>
-      </c>
-      <c r="AL9">
-        <v>28</v>
-      </c>
-      <c r="AM9">
-        <v>130</v>
-      </c>
-      <c r="AN9">
-        <v>4.2</v>
-      </c>
-      <c r="AO9">
-        <v>160</v>
-      </c>
-      <c r="AP9">
-        <v>28</v>
-      </c>
-      <c r="AQ9">
-        <v>36</v>
-      </c>
-      <c r="AR9">
-        <v>38</v>
-      </c>
-      <c r="AS9">
-        <v>60</v>
-      </c>
-      <c r="AT9">
-        <v>11</v>
-      </c>
-      <c r="AU9">
-        <v>13</v>
-      </c>
-      <c r="AV9">
-        <v>32</v>
-      </c>
-      <c r="AW9">
-        <v>42</v>
-      </c>
-      <c r="AX9">
-        <v>9</v>
-      </c>
-      <c r="AY9">
-        <v>9.6</v>
-      </c>
-      <c r="AZ9">
-        <v>23</v>
-      </c>
-      <c r="BA9">
-        <v>50</v>
-      </c>
-      <c r="BB9">
-        <v>10.5</v>
-      </c>
-      <c r="BC9">
-        <v>12</v>
-      </c>
-      <c r="BD9">
-        <v>26</v>
-      </c>
-      <c r="BE9">
-        <v>50</v>
-      </c>
-      <c r="BF9">
-        <v>4</v>
-      </c>
-      <c r="BG9">
-        <v>42</v>
-      </c>
-      <c r="BH9">
-        <v>5.7</v>
-      </c>
-      <c r="BI9">
-        <v>3.8</v>
-      </c>
-      <c r="BJ9">
-        <v>13</v>
-      </c>
-      <c r="BK9">
-        <v>3.5</v>
-      </c>
-      <c r="BL9">
-        <v>130</v>
-      </c>
-      <c r="BM9">
-        <v>4.6</v>
-      </c>
-      <c r="BN9">
-        <v>4.9</v>
-      </c>
-      <c r="BO9">
-        <v>3.25</v>
-      </c>
-      <c r="BP9">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BQ9">
-        <v>3.15</v>
-      </c>
-      <c r="BR9">
-        <v>24</v>
-      </c>
-      <c r="BS9">
-        <v>4</v>
-      </c>
-      <c r="BT9">
-        <v>15</v>
-      </c>
-      <c r="BU9">
-        <v>3.65</v>
-      </c>
-      <c r="BV9">
-        <v>85</v>
-      </c>
-      <c r="BW9">
+      <c r="BW10">
         <v>4.5</v>
       </c>
-      <c r="BX9">
+      <c r="BX10">
         <v>70</v>
       </c>
-      <c r="BY9">
+      <c r="BY10">
         <v>4.5</v>
       </c>
-      <c r="BZ9">
+      <c r="BZ10">
         <v>11.5</v>
       </c>
-      <c r="CA9">
+      <c r="CA10">
         <v>3.4</v>
       </c>
-      <c r="CB9" t="s">
-        <v>108</v>
+      <c r="CB10" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
@@ -352,7 +352,7 @@
     <t>Athletic Bilbao</t>
   </si>
   <si>
-    <t>2026-08-25 17:41:34</t>
+    <t>2026-08-25 19:51:41</t>
   </si>
 </sst>
 </file>
@@ -964,7 +964,7 @@
         <v>4.3</v>
       </c>
       <c r="L2">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M2">
         <v>1.07</v>
@@ -988,7 +988,7 @@
         <v>3.75</v>
       </c>
       <c r="T2">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U2">
         <v>1.82</v>
@@ -1006,25 +1006,25 @@
         <v>22</v>
       </c>
       <c r="Z2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA2">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AB2">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC2">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE2">
         <v>130</v>
       </c>
       <c r="AF2">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AG2">
         <v>12</v>
@@ -1033,10 +1033,10 @@
         <v>28</v>
       </c>
       <c r="AI2">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AJ2">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AK2">
         <v>23</v>
@@ -1045,49 +1045,49 @@
         <v>50</v>
       </c>
       <c r="AM2">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AN2">
         <v>14</v>
       </c>
       <c r="AO2">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AP2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AR2">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="AS2">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AT2">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AU2">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AV2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AW2">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="AX2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AY2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ2">
         <v>20</v>
       </c>
       <c r="BA2">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BB2">
         <v>14</v>
@@ -1096,76 +1096,76 @@
         <v>16</v>
       </c>
       <c r="BD2">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BE2">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BF2">
         <v>9.199999999999999</v>
       </c>
       <c r="BG2">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BH2">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>2.7</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BN2">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP2">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR2">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BT2">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BX2">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="s">
         <v>112</v>
@@ -1194,7 +1194,7 @@
         <v>3</v>
       </c>
       <c r="H3">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I3">
         <v>5.8</v>
@@ -1203,7 +1203,7 @@
         <v>2.4</v>
       </c>
       <c r="K3">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="L3">
         <v>1.61</v>
@@ -1442,7 +1442,7 @@
         <v>2.14</v>
       </c>
       <c r="J4">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K4">
         <v>4.4</v>
@@ -1511,7 +1511,7 @@
         <v>38</v>
       </c>
       <c r="AG4">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AH4">
         <v>16</v>
@@ -1535,7 +1535,7 @@
         <v>29</v>
       </c>
       <c r="AO4">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AP4">
         <v>17.5</v>
@@ -1562,28 +1562,28 @@
         <v>16</v>
       </c>
       <c r="AX4">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AY4">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AZ4">
         <v>11</v>
       </c>
       <c r="BA4">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="BB4">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BC4">
-        <v>27</v>
+        <v>5.9</v>
       </c>
       <c r="BD4">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BE4">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BF4">
         <v>21</v>
@@ -1681,7 +1681,7 @@
         <v>11.5</v>
       </c>
       <c r="I5">
-        <v>27</v>
+        <v>990</v>
       </c>
       <c r="J5">
         <v>4.4</v>
@@ -1711,7 +1711,7 @@
         <v>1.26</v>
       </c>
       <c r="S5">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T5">
         <v>1.11</v>
@@ -1720,7 +1720,7 @@
         <v>1.11</v>
       </c>
       <c r="V5">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W5">
         <v>3.35</v>
@@ -1917,31 +1917,31 @@
         <v>3.6</v>
       </c>
       <c r="G6">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H6">
         <v>2.32</v>
       </c>
       <c r="I6">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="J6">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="K6">
         <v>3.2</v>
       </c>
       <c r="L6">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="M6">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N6">
         <v>2.42</v>
       </c>
       <c r="O6">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="P6">
         <v>1.47</v>
@@ -1950,22 +1950,22 @@
         <v>2.78</v>
       </c>
       <c r="R6">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="S6">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="T6">
         <v>2.14</v>
       </c>
       <c r="U6">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="V6">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="W6">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X6">
         <v>9.6</v>
@@ -1974,7 +1974,7 @@
         <v>8.6</v>
       </c>
       <c r="Z6">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AA6">
         <v>46</v>
@@ -2034,10 +2034,10 @@
         <v>3.95</v>
       </c>
       <c r="AT6">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AU6">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV6">
         <v>9.199999999999999</v>
@@ -2058,22 +2058,22 @@
         <v>4.1</v>
       </c>
       <c r="BB6">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BC6">
         <v>4.1</v>
       </c>
       <c r="BD6">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE6">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF6">
         <v>4.2</v>
       </c>
       <c r="BG6">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BH6">
         <v>2.98</v>
@@ -2156,16 +2156,16 @@
         <v>108</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="G7">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H7">
+        <v>4.3</v>
+      </c>
+      <c r="I7">
         <v>4.4</v>
-      </c>
-      <c r="I7">
-        <v>4.5</v>
       </c>
       <c r="J7">
         <v>3.5</v>
@@ -2174,28 +2174,28 @@
         <v>3.55</v>
       </c>
       <c r="L7">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="M7">
         <v>1.09</v>
       </c>
       <c r="N7">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O7">
         <v>1.43</v>
       </c>
       <c r="P7">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q7">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R7">
         <v>1.28</v>
       </c>
       <c r="S7">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T7">
         <v>2.04</v>
@@ -2204,10 +2204,10 @@
         <v>1.92</v>
       </c>
       <c r="V7">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W7">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="X7">
         <v>11</v>
@@ -2219,7 +2219,7 @@
         <v>32</v>
       </c>
       <c r="AA7">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB7">
         <v>7.8</v>
@@ -2231,7 +2231,7 @@
         <v>18</v>
       </c>
       <c r="AE7">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF7">
         <v>11.5</v>
@@ -2261,7 +2261,7 @@
         <v>19</v>
       </c>
       <c r="AO7">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AP7">
         <v>10</v>
@@ -2270,10 +2270,10 @@
         <v>12</v>
       </c>
       <c r="AR7">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS7">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="AT7">
         <v>7.2</v>
@@ -2282,7 +2282,7 @@
         <v>7.4</v>
       </c>
       <c r="AV7">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW7">
         <v>55</v>
@@ -2294,13 +2294,13 @@
         <v>10</v>
       </c>
       <c r="AZ7">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA7">
         <v>65</v>
       </c>
       <c r="BB7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC7">
         <v>21</v>
@@ -2315,28 +2315,28 @@
         <v>17</v>
       </c>
       <c r="BG7">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="BH7">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="BI7">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="BJ7">
         <v>12.5</v>
       </c>
       <c r="BK7">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="BL7">
         <v>200</v>
       </c>
       <c r="BM7">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="BN7">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BO7">
         <v>4.1</v>
@@ -2345,37 +2345,37 @@
         <v>17.5</v>
       </c>
       <c r="BQ7">
-        <v>4.4</v>
+        <v>11.5</v>
       </c>
       <c r="BR7">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BS7">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="BT7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU7">
+        <v>7</v>
+      </c>
+      <c r="BV7">
+        <v>44</v>
+      </c>
+      <c r="BW7">
         <v>9</v>
-      </c>
-      <c r="BU7">
-        <v>6.8</v>
-      </c>
-      <c r="BV7">
-        <v>50</v>
-      </c>
-      <c r="BW7">
-        <v>5.3</v>
       </c>
       <c r="BX7">
         <v>70</v>
       </c>
       <c r="BY7">
-        <v>5.4</v>
+        <v>9.6</v>
       </c>
       <c r="BZ7">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="CA7">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="CB7" t="s">
         <v>112</v>
@@ -2398,22 +2398,22 @@
         <v>109</v>
       </c>
       <c r="F8">
-        <v>1.09</v>
+        <v>1.65</v>
       </c>
       <c r="G8">
-        <v>990</v>
+        <v>1.77</v>
       </c>
       <c r="H8">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="I8">
-        <v>990</v>
+        <v>5.6</v>
       </c>
       <c r="J8">
-        <v>1.11</v>
+        <v>4.2</v>
       </c>
       <c r="K8">
-        <v>500</v>
+        <v>4.8</v>
       </c>
       <c r="L8">
         <v>1.01</v>
@@ -2422,22 +2422,22 @@
         <v>1.03</v>
       </c>
       <c r="N8">
-        <v>1.12</v>
+        <v>2.14</v>
       </c>
       <c r="O8">
         <v>1.18</v>
       </c>
       <c r="P8">
-        <v>1.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q8">
-        <v>1.17</v>
+        <v>1.49</v>
       </c>
       <c r="R8">
-        <v>1.09</v>
+        <v>1.46</v>
       </c>
       <c r="S8">
-        <v>1.18</v>
+        <v>2.22</v>
       </c>
       <c r="T8">
         <v>1.11</v>
@@ -2446,10 +2446,10 @@
         <v>1.11</v>
       </c>
       <c r="V8">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W8">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2640,13 +2640,13 @@
         <v>110</v>
       </c>
       <c r="F9">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="G9">
         <v>990</v>
       </c>
       <c r="H9">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="I9">
         <v>990</v>
@@ -2664,13 +2664,13 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O9">
         <v>1.08</v>
       </c>
       <c r="P9">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q9">
         <v>1.08</v>
@@ -2679,7 +2679,7 @@
         <v>1.18</v>
       </c>
       <c r="S9">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="T9">
         <v>1.11</v>
@@ -2888,10 +2888,10 @@
         <v>1.35</v>
       </c>
       <c r="H10">
+        <v>10</v>
+      </c>
+      <c r="I10">
         <v>10.5</v>
-      </c>
-      <c r="I10">
-        <v>11</v>
       </c>
       <c r="J10">
         <v>6.2</v>
@@ -2900,28 +2900,28 @@
         <v>6.4</v>
       </c>
       <c r="L10">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="M10">
         <v>1.03</v>
       </c>
       <c r="N10">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O10">
         <v>1.16</v>
       </c>
       <c r="P10">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="Q10">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R10">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="S10">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T10">
         <v>1.83</v>
@@ -2936,16 +2936,16 @@
         <v>3.85</v>
       </c>
       <c r="X10">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y10">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Z10">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AA10">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="AB10">
         <v>12</v>
@@ -2957,7 +2957,7 @@
         <v>38</v>
       </c>
       <c r="AE10">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AF10">
         <v>9.6</v>
@@ -2969,7 +2969,7 @@
         <v>25</v>
       </c>
       <c r="AI10">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AJ10">
         <v>11.5</v>
@@ -2996,25 +2996,25 @@
         <v>38</v>
       </c>
       <c r="AR10">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="AS10">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="AT10">
         <v>11.5</v>
       </c>
       <c r="AU10">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AV10">
         <v>34</v>
       </c>
       <c r="AW10">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AX10">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY10">
         <v>9.800000000000001</v>
@@ -3026,13 +3026,13 @@
         <v>55</v>
       </c>
       <c r="BB10">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC10">
         <v>12</v>
       </c>
       <c r="BD10">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE10">
         <v>60</v>
@@ -3041,67 +3041,67 @@
         <v>4</v>
       </c>
       <c r="BG10">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BH10">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>3.8</v>
+        <v>2.38</v>
       </c>
       <c r="BJ10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BK10">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="BL10">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="BM10">
-        <v>4.6</v>
+        <v>2.18</v>
       </c>
       <c r="BN10">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BO10">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="BP10">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BQ10">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BR10">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BS10">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="BT10">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BU10">
-        <v>9.6</v>
+        <v>3.4</v>
       </c>
       <c r="BV10">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>4.5</v>
+        <v>2.14</v>
       </c>
       <c r="BX10">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="BZ10">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="CA10">
-        <v>3.4</v>
+        <v>6.2</v>
       </c>
       <c r="CB10" t="s">
         <v>112</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="120">
   <si>
     <t>League</t>
   </si>
@@ -265,6 +265,9 @@
     <t>Qatari Stars League</t>
   </si>
   <si>
+    <t>Algerian Ligue 1</t>
+  </si>
+  <si>
     <t>Spanish La Liga</t>
   </si>
   <si>
@@ -289,6 +292,9 @@
     <t>17:00:00</t>
   </si>
   <si>
+    <t>18:00:00</t>
+  </si>
+  <si>
     <t>18:30:00</t>
   </si>
   <si>
@@ -298,6 +304,9 @@
     <t>19:00:00</t>
   </si>
   <si>
+    <t>20:00:00</t>
+  </si>
+  <si>
     <t>Atletico Nacional Medellin</t>
   </si>
   <si>
@@ -313,6 +322,9 @@
     <t>Al Mokawloon</t>
   </si>
   <si>
+    <t>ES Setif</t>
+  </si>
+  <si>
     <t>Celta Vigo</t>
   </si>
   <si>
@@ -325,6 +337,9 @@
     <t>Barcelona</t>
   </si>
   <si>
+    <t>MC Alger</t>
+  </si>
+  <si>
     <t>Deportivo Cali</t>
   </si>
   <si>
@@ -340,6 +355,9 @@
     <t>Al-Masry</t>
   </si>
   <si>
+    <t>ES Ben Aknoun</t>
+  </si>
+  <si>
     <t>Osasuna</t>
   </si>
   <si>
@@ -352,7 +370,10 @@
     <t>Athletic Bilbao</t>
   </si>
   <si>
-    <t>2026-08-25 19:51:41</t>
+    <t>MC Oran</t>
+  </si>
+  <si>
+    <t>2026-08-25 22:00:28</t>
   </si>
 </sst>
 </file>
@@ -684,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CB12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -934,31 +955,31 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E2" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F2">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G2">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I2">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="J2">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K2">
         <v>4.3</v>
@@ -970,22 +991,22 @@
         <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O2">
         <v>1.36</v>
       </c>
       <c r="P2">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="Q2">
         <v>2.02</v>
       </c>
       <c r="R2">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S2">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="T2">
         <v>2.02</v>
@@ -994,10 +1015,10 @@
         <v>1.82</v>
       </c>
       <c r="V2">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W2">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="X2">
         <v>15</v>
@@ -1027,7 +1048,7 @@
         <v>9.6</v>
       </c>
       <c r="AG2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH2">
         <v>28</v>
@@ -1036,19 +1057,19 @@
         <v>130</v>
       </c>
       <c r="AJ2">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AK2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL2">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM2">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN2">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AO2">
         <v>190</v>
@@ -1060,10 +1081,10 @@
         <v>16</v>
       </c>
       <c r="AR2">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AS2">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AT2">
         <v>6.2</v>
@@ -1075,7 +1096,7 @@
         <v>21</v>
       </c>
       <c r="AW2">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AX2">
         <v>7.8</v>
@@ -1087,7 +1108,7 @@
         <v>20</v>
       </c>
       <c r="BA2">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BB2">
         <v>14</v>
@@ -1096,16 +1117,16 @@
         <v>16</v>
       </c>
       <c r="BD2">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BE2">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BF2">
         <v>9.199999999999999</v>
       </c>
       <c r="BG2">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1168,7 +1189,7 @@
         <v>1.04</v>
       </c>
       <c r="CB2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1176,19 +1197,19 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="F3">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="G3">
         <v>3</v>
@@ -1197,7 +1218,7 @@
         <v>3.7</v>
       </c>
       <c r="I3">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="J3">
         <v>2.4</v>
@@ -1233,10 +1254,10 @@
         <v>2.16</v>
       </c>
       <c r="U3">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="V3">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="W3">
         <v>1.5</v>
@@ -1410,7 +1431,7 @@
         <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1418,31 +1439,31 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E4" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F4">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="G4">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="H4">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="I4">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="J4">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K4">
         <v>4.4</v>
@@ -1478,10 +1499,10 @@
         <v>2.48</v>
       </c>
       <c r="V4">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="W4">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X4">
         <v>28</v>
@@ -1490,19 +1511,19 @@
         <v>15.5</v>
       </c>
       <c r="Z4">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AA4">
         <v>27</v>
       </c>
       <c r="AB4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AC4">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AD4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE4">
         <v>20</v>
@@ -1535,7 +1556,7 @@
         <v>29</v>
       </c>
       <c r="AO4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AP4">
         <v>17.5</v>
@@ -1562,10 +1583,10 @@
         <v>16</v>
       </c>
       <c r="AX4">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="AY4">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ4">
         <v>11</v>
@@ -1574,22 +1595,22 @@
         <v>21</v>
       </c>
       <c r="BB4">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BC4">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="BD4">
-        <v>5.9</v>
+        <v>32</v>
       </c>
       <c r="BE4">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BF4">
         <v>21</v>
       </c>
       <c r="BG4">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1652,7 +1673,7 @@
         <v>1.04</v>
       </c>
       <c r="CB4" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1660,16 +1681,16 @@
         <v>81</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E5" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F5">
         <v>1.23</v>
@@ -1894,7 +1915,7 @@
         <v>1.04</v>
       </c>
       <c r="CB5" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1902,31 +1923,31 @@
         <v>81</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E6" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F6">
         <v>3.6</v>
       </c>
       <c r="G6">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H6">
         <v>2.32</v>
       </c>
       <c r="I6">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="J6">
-        <v>2.84</v>
+        <v>2.56</v>
       </c>
       <c r="K6">
         <v>3.2</v>
@@ -1935,10 +1956,10 @@
         <v>1.59</v>
       </c>
       <c r="M6">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N6">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="O6">
         <v>1.57</v>
@@ -1950,19 +1971,19 @@
         <v>2.78</v>
       </c>
       <c r="R6">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S6">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="T6">
         <v>2.14</v>
       </c>
       <c r="U6">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="V6">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W6">
         <v>1.31</v>
@@ -2037,7 +2058,7 @@
         <v>7.4</v>
       </c>
       <c r="AU6">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="AV6">
         <v>9.199999999999999</v>
@@ -2136,7 +2157,7 @@
         <v>4.7</v>
       </c>
       <c r="CB6" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2144,241 +2165,241 @@
         <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E7" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="F7">
-        <v>2.04</v>
+        <v>1.59</v>
       </c>
       <c r="G7">
         <v>2.06</v>
       </c>
       <c r="H7">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I7">
-        <v>4.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J7">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="K7">
-        <v>3.55</v>
+        <v>6.8</v>
       </c>
       <c r="L7">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="M7">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N7">
-        <v>3.2</v>
+        <v>2.24</v>
       </c>
       <c r="O7">
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="P7">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="Q7">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="R7">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="S7">
-        <v>4.5</v>
+        <v>2.46</v>
       </c>
       <c r="T7">
-        <v>2.04</v>
+        <v>1.11</v>
       </c>
       <c r="U7">
-        <v>1.92</v>
+        <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="W7">
         <v>1.94</v>
       </c>
       <c r="X7">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y7">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z7">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA7">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC7">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD7">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AE7">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF7">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG7">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH7">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI7">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ7">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AK7">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL7">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM7">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN7">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AO7">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP7">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AR7">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="AS7">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="AT7">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU7">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV7">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW7">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="AX7">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY7">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA7">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BB7">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BC7">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BD7">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BE7">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BF7">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BH7">
-        <v>2.96</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>2.8</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="BM7">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BP7">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2386,241 +2407,241 @@
         <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E8" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F8">
-        <v>1.65</v>
+        <v>2.04</v>
       </c>
       <c r="G8">
-        <v>1.77</v>
+        <v>2.06</v>
       </c>
       <c r="H8">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="I8">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="J8">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="K8">
-        <v>4.8</v>
+        <v>3.55</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M8">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="N8">
-        <v>2.14</v>
+        <v>3.2</v>
       </c>
       <c r="O8">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="P8">
-        <v>2.14</v>
+        <v>1.73</v>
       </c>
       <c r="Q8">
-        <v>1.49</v>
+        <v>2.3</v>
       </c>
       <c r="R8">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="S8">
-        <v>2.22</v>
+        <v>4.5</v>
       </c>
       <c r="T8">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="U8">
-        <v>1.11</v>
+        <v>1.91</v>
       </c>
       <c r="V8">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="W8">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP8">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ8">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR8">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="AS8">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AT8">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU8">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV8">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AW8">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="AX8">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY8">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ8">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BA8">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD8">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="BI8">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK8">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BL8">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="BM8">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO8">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ8">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS8">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU8">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW8">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY8">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA8">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="CB8" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2628,58 +2649,58 @@
         <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E9" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F9">
-        <v>1.06</v>
+        <v>1.65</v>
       </c>
       <c r="G9">
-        <v>990</v>
+        <v>1.76</v>
       </c>
       <c r="H9">
-        <v>1.06</v>
+        <v>4.8</v>
       </c>
       <c r="I9">
-        <v>990</v>
+        <v>5.6</v>
       </c>
       <c r="J9">
-        <v>1.09</v>
+        <v>4.2</v>
       </c>
       <c r="K9">
-        <v>950</v>
+        <v>4.8</v>
       </c>
       <c r="L9">
         <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N9">
-        <v>1.26</v>
+        <v>2.14</v>
       </c>
       <c r="O9">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="P9">
-        <v>1.25</v>
+        <v>2.14</v>
       </c>
       <c r="Q9">
-        <v>1.08</v>
+        <v>1.49</v>
       </c>
       <c r="R9">
-        <v>1.18</v>
+        <v>1.46</v>
       </c>
       <c r="S9">
-        <v>1.09</v>
+        <v>2.22</v>
       </c>
       <c r="T9">
         <v>1.11</v>
@@ -2856,255 +2877,739 @@
         <v>1.04</v>
       </c>
       <c r="BZ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" t="s">
+        <v>116</v>
+      </c>
+      <c r="F10">
+        <v>1.08</v>
+      </c>
+      <c r="G10">
+        <v>990</v>
+      </c>
+      <c r="H10">
+        <v>1.08</v>
+      </c>
+      <c r="I10">
+        <v>990</v>
+      </c>
+      <c r="J10">
+        <v>3.95</v>
+      </c>
+      <c r="K10">
+        <v>950</v>
+      </c>
+      <c r="L10">
+        <v>1.01</v>
+      </c>
+      <c r="M10">
+        <v>1.01</v>
+      </c>
+      <c r="N10">
+        <v>1.1</v>
+      </c>
+      <c r="O10">
+        <v>1.08</v>
+      </c>
+      <c r="P10">
+        <v>1.25</v>
+      </c>
+      <c r="Q10">
+        <v>1.07</v>
+      </c>
+      <c r="R10">
+        <v>1.18</v>
+      </c>
+      <c r="S10">
+        <v>1.08</v>
+      </c>
+      <c r="T10">
+        <v>1.11</v>
+      </c>
+      <c r="U10">
+        <v>1.11</v>
+      </c>
+      <c r="V10">
+        <v>1.01</v>
+      </c>
+      <c r="W10">
+        <v>1.01</v>
+      </c>
+      <c r="X10">
+        <v>1000</v>
+      </c>
+      <c r="Y10">
+        <v>1000</v>
+      </c>
+      <c r="Z10">
+        <v>1000</v>
+      </c>
+      <c r="AA10">
+        <v>1000</v>
+      </c>
+      <c r="AB10">
+        <v>1000</v>
+      </c>
+      <c r="AC10">
+        <v>1000</v>
+      </c>
+      <c r="AD10">
+        <v>1000</v>
+      </c>
+      <c r="AE10">
+        <v>1000</v>
+      </c>
+      <c r="AF10">
+        <v>1000</v>
+      </c>
+      <c r="AG10">
+        <v>1000</v>
+      </c>
+      <c r="AH10">
+        <v>1000</v>
+      </c>
+      <c r="AI10">
+        <v>1000</v>
+      </c>
+      <c r="AJ10">
+        <v>1000</v>
+      </c>
+      <c r="AK10">
+        <v>1000</v>
+      </c>
+      <c r="AL10">
+        <v>1000</v>
+      </c>
+      <c r="AM10">
+        <v>1000</v>
+      </c>
+      <c r="AN10">
+        <v>1000</v>
+      </c>
+      <c r="AO10">
+        <v>1000</v>
+      </c>
+      <c r="AP10">
+        <v>1.01</v>
+      </c>
+      <c r="AQ10">
+        <v>1.01</v>
+      </c>
+      <c r="AR10">
+        <v>1.01</v>
+      </c>
+      <c r="AS10">
+        <v>1.01</v>
+      </c>
+      <c r="AT10">
+        <v>1.01</v>
+      </c>
+      <c r="AU10">
+        <v>1.01</v>
+      </c>
+      <c r="AV10">
+        <v>1.01</v>
+      </c>
+      <c r="AW10">
+        <v>1.01</v>
+      </c>
+      <c r="AX10">
+        <v>1.01</v>
+      </c>
+      <c r="AY10">
+        <v>1.01</v>
+      </c>
+      <c r="AZ10">
+        <v>1.01</v>
+      </c>
+      <c r="BA10">
+        <v>1.01</v>
+      </c>
+      <c r="BB10">
+        <v>1.01</v>
+      </c>
+      <c r="BC10">
+        <v>1.01</v>
+      </c>
+      <c r="BD10">
+        <v>1.01</v>
+      </c>
+      <c r="BE10">
+        <v>1.01</v>
+      </c>
+      <c r="BF10">
+        <v>1.01</v>
+      </c>
+      <c r="BG10">
+        <v>1.01</v>
+      </c>
+      <c r="BH10">
+        <v>1000</v>
+      </c>
+      <c r="BI10">
+        <v>1.04</v>
+      </c>
+      <c r="BJ10">
+        <v>1000</v>
+      </c>
+      <c r="BK10">
+        <v>1.04</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>1.04</v>
+      </c>
+      <c r="BN10">
+        <v>1000</v>
+      </c>
+      <c r="BO10">
+        <v>1.04</v>
+      </c>
+      <c r="BP10">
+        <v>1000</v>
+      </c>
+      <c r="BQ10">
+        <v>1.04</v>
+      </c>
+      <c r="BR10">
+        <v>1000</v>
+      </c>
+      <c r="BS10">
+        <v>1.04</v>
+      </c>
+      <c r="BT10">
+        <v>1000</v>
+      </c>
+      <c r="BU10">
+        <v>1.04</v>
+      </c>
+      <c r="BV10">
+        <v>1000</v>
+      </c>
+      <c r="BW10">
+        <v>1.04</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
+        <v>1.04</v>
+      </c>
+      <c r="BZ10">
+        <v>0</v>
+      </c>
+      <c r="CA10">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" t="s">
+        <v>106</v>
+      </c>
+      <c r="E11" t="s">
+        <v>117</v>
+      </c>
+      <c r="F11">
+        <v>1.33</v>
+      </c>
+      <c r="G11">
+        <v>1.35</v>
+      </c>
+      <c r="H11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="I11">
+        <v>10.5</v>
+      </c>
+      <c r="J11">
+        <v>6.2</v>
+      </c>
+      <c r="K11">
+        <v>6.4</v>
+      </c>
+      <c r="L11">
+        <v>1.26</v>
+      </c>
+      <c r="M11">
+        <v>1.03</v>
+      </c>
+      <c r="N11">
+        <v>6.8</v>
+      </c>
+      <c r="O11">
+        <v>1.16</v>
+      </c>
+      <c r="P11">
+        <v>2.98</v>
+      </c>
+      <c r="Q11">
+        <v>1.49</v>
+      </c>
+      <c r="R11">
+        <v>1.77</v>
+      </c>
+      <c r="S11">
+        <v>2.22</v>
+      </c>
+      <c r="T11">
+        <v>1.84</v>
+      </c>
+      <c r="U11">
+        <v>2.14</v>
+      </c>
+      <c r="V11">
+        <v>1.1</v>
+      </c>
+      <c r="W11">
+        <v>3.85</v>
+      </c>
+      <c r="X11">
+        <v>32</v>
+      </c>
+      <c r="Y11">
+        <v>44</v>
+      </c>
+      <c r="Z11">
+        <v>95</v>
+      </c>
+      <c r="AA11">
+        <v>350</v>
+      </c>
+      <c r="AB11">
+        <v>12</v>
+      </c>
+      <c r="AC11">
+        <v>14.5</v>
+      </c>
+      <c r="AD11">
+        <v>38</v>
+      </c>
+      <c r="AE11">
+        <v>120</v>
+      </c>
+      <c r="AF11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG11">
+        <v>10.5</v>
+      </c>
+      <c r="AH11">
+        <v>25</v>
+      </c>
+      <c r="AI11">
+        <v>120</v>
+      </c>
+      <c r="AJ11">
+        <v>11.5</v>
+      </c>
+      <c r="AK11">
+        <v>12.5</v>
+      </c>
+      <c r="AL11">
+        <v>28</v>
+      </c>
+      <c r="AM11">
+        <v>110</v>
+      </c>
+      <c r="AN11">
+        <v>4.2</v>
+      </c>
+      <c r="AO11">
+        <v>120</v>
+      </c>
+      <c r="AP11">
+        <v>28</v>
+      </c>
+      <c r="AQ11">
+        <v>38</v>
+      </c>
+      <c r="AR11">
+        <v>50</v>
+      </c>
+      <c r="AS11">
+        <v>60</v>
+      </c>
+      <c r="AT11">
+        <v>11.5</v>
+      </c>
+      <c r="AU11">
+        <v>13</v>
+      </c>
+      <c r="AV11">
+        <v>34</v>
+      </c>
+      <c r="AW11">
+        <v>65</v>
+      </c>
+      <c r="AX11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ11">
+        <v>23</v>
+      </c>
+      <c r="BA11">
+        <v>55</v>
+      </c>
+      <c r="BB11">
+        <v>10.5</v>
+      </c>
+      <c r="BC11">
+        <v>12</v>
+      </c>
+      <c r="BD11">
+        <v>26</v>
+      </c>
+      <c r="BE11">
+        <v>65</v>
+      </c>
+      <c r="BF11">
+        <v>4</v>
+      </c>
+      <c r="BG11">
+        <v>46</v>
+      </c>
+      <c r="BH11">
+        <v>1000</v>
+      </c>
+      <c r="BI11">
+        <v>2.38</v>
+      </c>
+      <c r="BJ11">
+        <v>15</v>
+      </c>
+      <c r="BK11">
+        <v>3.3</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>2.18</v>
+      </c>
+      <c r="BN11">
+        <v>5.2</v>
+      </c>
+      <c r="BO11">
+        <v>3</v>
+      </c>
+      <c r="BP11">
+        <v>10.5</v>
+      </c>
+      <c r="BQ11">
+        <v>5.5</v>
+      </c>
+      <c r="BR11">
+        <v>28</v>
+      </c>
+      <c r="BS11">
+        <v>3.6</v>
+      </c>
+      <c r="BT11">
+        <v>17.5</v>
+      </c>
+      <c r="BU11">
+        <v>3.4</v>
+      </c>
+      <c r="BV11">
+        <v>1000</v>
+      </c>
+      <c r="BW11">
+        <v>2.14</v>
+      </c>
+      <c r="BX11">
+        <v>1000</v>
+      </c>
+      <c r="BY11">
+        <v>2.12</v>
+      </c>
+      <c r="BZ11">
+        <v>14</v>
+      </c>
+      <c r="CA11">
+        <v>6.2</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
         <v>83</v>
       </c>
-      <c r="B10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10" t="s">
-        <v>93</v>
-      </c>
-      <c r="D10" t="s">
-        <v>102</v>
-      </c>
-      <c r="E10" t="s">
-        <v>111</v>
-      </c>
-      <c r="F10">
-        <v>1.34</v>
-      </c>
-      <c r="G10">
-        <v>1.35</v>
-      </c>
-      <c r="H10">
-        <v>10</v>
-      </c>
-      <c r="I10">
-        <v>10.5</v>
-      </c>
-      <c r="J10">
-        <v>6.2</v>
-      </c>
-      <c r="K10">
-        <v>6.4</v>
-      </c>
-      <c r="L10">
-        <v>1.26</v>
-      </c>
-      <c r="M10">
-        <v>1.03</v>
-      </c>
-      <c r="N10">
-        <v>6.8</v>
-      </c>
-      <c r="O10">
-        <v>1.16</v>
-      </c>
-      <c r="P10">
-        <v>2.98</v>
-      </c>
-      <c r="Q10">
-        <v>1.49</v>
-      </c>
-      <c r="R10">
-        <v>1.77</v>
-      </c>
-      <c r="S10">
-        <v>2.22</v>
-      </c>
-      <c r="T10">
-        <v>1.83</v>
-      </c>
-      <c r="U10">
-        <v>2.14</v>
-      </c>
-      <c r="V10">
-        <v>1.1</v>
-      </c>
-      <c r="W10">
-        <v>3.85</v>
-      </c>
-      <c r="X10">
-        <v>32</v>
-      </c>
-      <c r="Y10">
-        <v>44</v>
-      </c>
-      <c r="Z10">
-        <v>95</v>
-      </c>
-      <c r="AA10">
-        <v>350</v>
-      </c>
-      <c r="AB10">
-        <v>12</v>
-      </c>
-      <c r="AC10">
-        <v>14.5</v>
-      </c>
-      <c r="AD10">
-        <v>38</v>
-      </c>
-      <c r="AE10">
-        <v>120</v>
-      </c>
-      <c r="AF10">
-        <v>9.6</v>
-      </c>
-      <c r="AG10">
-        <v>10.5</v>
-      </c>
-      <c r="AH10">
-        <v>25</v>
-      </c>
-      <c r="AI10">
-        <v>120</v>
-      </c>
-      <c r="AJ10">
-        <v>11.5</v>
-      </c>
-      <c r="AK10">
-        <v>12.5</v>
-      </c>
-      <c r="AL10">
-        <v>28</v>
-      </c>
-      <c r="AM10">
-        <v>110</v>
-      </c>
-      <c r="AN10">
-        <v>4.2</v>
-      </c>
-      <c r="AO10">
-        <v>120</v>
-      </c>
-      <c r="AP10">
-        <v>28</v>
-      </c>
-      <c r="AQ10">
-        <v>38</v>
-      </c>
-      <c r="AR10">
-        <v>42</v>
-      </c>
-      <c r="AS10">
-        <v>60</v>
-      </c>
-      <c r="AT10">
-        <v>11.5</v>
-      </c>
-      <c r="AU10">
-        <v>13.5</v>
-      </c>
-      <c r="AV10">
-        <v>34</v>
-      </c>
-      <c r="AW10">
-        <v>60</v>
-      </c>
-      <c r="AX10">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY10">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ10">
-        <v>23</v>
-      </c>
-      <c r="BA10">
-        <v>55</v>
-      </c>
-      <c r="BB10">
-        <v>11</v>
-      </c>
-      <c r="BC10">
-        <v>12</v>
-      </c>
-      <c r="BD10">
-        <v>26</v>
-      </c>
-      <c r="BE10">
-        <v>60</v>
-      </c>
-      <c r="BF10">
-        <v>4</v>
-      </c>
-      <c r="BG10">
-        <v>46</v>
-      </c>
-      <c r="BH10">
-        <v>1000</v>
-      </c>
-      <c r="BI10">
-        <v>2.38</v>
-      </c>
-      <c r="BJ10">
-        <v>15</v>
-      </c>
-      <c r="BK10">
+      <c r="B12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" t="s">
+        <v>107</v>
+      </c>
+      <c r="E12" t="s">
+        <v>118</v>
+      </c>
+      <c r="F12">
+        <v>1.48</v>
+      </c>
+      <c r="G12">
+        <v>1.68</v>
+      </c>
+      <c r="H12">
         <v>3.35</v>
       </c>
-      <c r="BL10">
-        <v>1000</v>
-      </c>
-      <c r="BM10">
-        <v>2.18</v>
-      </c>
-      <c r="BN10">
-        <v>5.2</v>
-      </c>
-      <c r="BO10">
-        <v>3</v>
-      </c>
-      <c r="BP10">
-        <v>10.5</v>
-      </c>
-      <c r="BQ10">
-        <v>5.5</v>
-      </c>
-      <c r="BR10">
-        <v>28</v>
-      </c>
-      <c r="BS10">
-        <v>3.6</v>
-      </c>
-      <c r="BT10">
-        <v>17.5</v>
-      </c>
-      <c r="BU10">
-        <v>3.4</v>
-      </c>
-      <c r="BV10">
-        <v>1000</v>
-      </c>
-      <c r="BW10">
-        <v>2.14</v>
-      </c>
-      <c r="BX10">
-        <v>1000</v>
-      </c>
-      <c r="BY10">
-        <v>3.85</v>
-      </c>
-      <c r="BZ10">
-        <v>14</v>
-      </c>
-      <c r="CA10">
-        <v>6.2</v>
-      </c>
-      <c r="CB10" t="s">
-        <v>112</v>
+      <c r="I12">
+        <v>16</v>
+      </c>
+      <c r="J12">
+        <v>3.55</v>
+      </c>
+      <c r="K12">
+        <v>950</v>
+      </c>
+      <c r="L12">
+        <v>1.01</v>
+      </c>
+      <c r="M12">
+        <v>1.01</v>
+      </c>
+      <c r="N12">
+        <v>2.74</v>
+      </c>
+      <c r="O12">
+        <v>1.44</v>
+      </c>
+      <c r="P12">
+        <v>1.52</v>
+      </c>
+      <c r="Q12">
+        <v>2.3</v>
+      </c>
+      <c r="R12">
+        <v>1.12</v>
+      </c>
+      <c r="S12">
+        <v>2.74</v>
+      </c>
+      <c r="T12">
+        <v>1.11</v>
+      </c>
+      <c r="U12">
+        <v>1.11</v>
+      </c>
+      <c r="V12">
+        <v>1.06</v>
+      </c>
+      <c r="W12">
+        <v>2.46</v>
+      </c>
+      <c r="X12">
+        <v>1000</v>
+      </c>
+      <c r="Y12">
+        <v>1000</v>
+      </c>
+      <c r="Z12">
+        <v>1000</v>
+      </c>
+      <c r="AA12">
+        <v>1000</v>
+      </c>
+      <c r="AB12">
+        <v>1000</v>
+      </c>
+      <c r="AC12">
+        <v>1000</v>
+      </c>
+      <c r="AD12">
+        <v>1000</v>
+      </c>
+      <c r="AE12">
+        <v>1000</v>
+      </c>
+      <c r="AF12">
+        <v>1000</v>
+      </c>
+      <c r="AG12">
+        <v>1000</v>
+      </c>
+      <c r="AH12">
+        <v>1000</v>
+      </c>
+      <c r="AI12">
+        <v>1000</v>
+      </c>
+      <c r="AJ12">
+        <v>1000</v>
+      </c>
+      <c r="AK12">
+        <v>1000</v>
+      </c>
+      <c r="AL12">
+        <v>1000</v>
+      </c>
+      <c r="AM12">
+        <v>1000</v>
+      </c>
+      <c r="AN12">
+        <v>1000</v>
+      </c>
+      <c r="AO12">
+        <v>1000</v>
+      </c>
+      <c r="AP12">
+        <v>1.01</v>
+      </c>
+      <c r="AQ12">
+        <v>1.01</v>
+      </c>
+      <c r="AR12">
+        <v>1.01</v>
+      </c>
+      <c r="AS12">
+        <v>1.01</v>
+      </c>
+      <c r="AT12">
+        <v>1.01</v>
+      </c>
+      <c r="AU12">
+        <v>1.01</v>
+      </c>
+      <c r="AV12">
+        <v>1.01</v>
+      </c>
+      <c r="AW12">
+        <v>1.01</v>
+      </c>
+      <c r="AX12">
+        <v>1.01</v>
+      </c>
+      <c r="AY12">
+        <v>1.01</v>
+      </c>
+      <c r="AZ12">
+        <v>1.01</v>
+      </c>
+      <c r="BA12">
+        <v>1.01</v>
+      </c>
+      <c r="BB12">
+        <v>1.01</v>
+      </c>
+      <c r="BC12">
+        <v>1.01</v>
+      </c>
+      <c r="BD12">
+        <v>1.01</v>
+      </c>
+      <c r="BE12">
+        <v>1.01</v>
+      </c>
+      <c r="BF12">
+        <v>1.01</v>
+      </c>
+      <c r="BG12">
+        <v>1.01</v>
+      </c>
+      <c r="BH12">
+        <v>1000</v>
+      </c>
+      <c r="BI12">
+        <v>1.04</v>
+      </c>
+      <c r="BJ12">
+        <v>1000</v>
+      </c>
+      <c r="BK12">
+        <v>1.04</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>1.04</v>
+      </c>
+      <c r="BN12">
+        <v>1000</v>
+      </c>
+      <c r="BO12">
+        <v>1.04</v>
+      </c>
+      <c r="BP12">
+        <v>1000</v>
+      </c>
+      <c r="BQ12">
+        <v>1.04</v>
+      </c>
+      <c r="BR12">
+        <v>1000</v>
+      </c>
+      <c r="BS12">
+        <v>1.04</v>
+      </c>
+      <c r="BT12">
+        <v>1000</v>
+      </c>
+      <c r="BU12">
+        <v>1.04</v>
+      </c>
+      <c r="BV12">
+        <v>1000</v>
+      </c>
+      <c r="BW12">
+        <v>1.04</v>
+      </c>
+      <c r="BX12">
+        <v>1000</v>
+      </c>
+      <c r="BY12">
+        <v>1.04</v>
+      </c>
+      <c r="BZ12">
+        <v>1000</v>
+      </c>
+      <c r="CA12">
+        <v>1.04</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="126">
   <si>
     <t>League</t>
   </si>
@@ -286,6 +286,9 @@
     <t>14:00:00</t>
   </si>
   <si>
+    <t>14:15:00</t>
+  </si>
+  <si>
     <t>16:30:00</t>
   </si>
   <si>
@@ -307,12 +310,18 @@
     <t>20:00:00</t>
   </si>
   <si>
+    <t>23:10:00</t>
+  </si>
+  <si>
     <t>Atletico Nacional Medellin</t>
   </si>
   <si>
     <t>Modern Sport FC</t>
   </si>
   <si>
+    <t>Al Gharafa</t>
+  </si>
+  <si>
     <t>Al-Wakra</t>
   </si>
   <si>
@@ -340,12 +349,18 @@
     <t>MC Alger</t>
   </si>
   <si>
+    <t>Llaneros FC</t>
+  </si>
+  <si>
     <t>Deportivo Cali</t>
   </si>
   <si>
     <t>Ghazl El Mahallah</t>
   </si>
   <si>
+    <t>Al Shamal</t>
+  </si>
+  <si>
     <t>Al Rayyan</t>
   </si>
   <si>
@@ -373,7 +388,10 @@
     <t>MC Oran</t>
   </si>
   <si>
-    <t>2026-08-25 22:00:28</t>
+    <t>Millonarios</t>
+  </si>
+  <si>
+    <t>2026-08-26 00:09:27</t>
   </si>
 </sst>
 </file>
@@ -705,7 +723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB12"/>
+  <dimension ref="A1:CB14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -961,16 +979,16 @@
         <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F2">
         <v>1.64</v>
       </c>
       <c r="G2">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="H2">
         <v>6.2</v>
@@ -982,7 +1000,7 @@
         <v>3.85</v>
       </c>
       <c r="K2">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L2">
         <v>1.01</v>
@@ -1018,7 +1036,7 @@
         <v>1.15</v>
       </c>
       <c r="W2">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="X2">
         <v>15</v>
@@ -1027,10 +1045,10 @@
         <v>22</v>
       </c>
       <c r="Z2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA2">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AB2">
         <v>7.6</v>
@@ -1039,25 +1057,25 @@
         <v>9.4</v>
       </c>
       <c r="AD2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG2">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ2">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AK2">
         <v>22</v>
@@ -1072,7 +1090,7 @@
         <v>12.5</v>
       </c>
       <c r="AO2">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AP2">
         <v>11</v>
@@ -1081,34 +1099,34 @@
         <v>16</v>
       </c>
       <c r="AR2">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AS2">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AT2">
         <v>6.2</v>
       </c>
       <c r="AU2">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV2">
         <v>21</v>
       </c>
       <c r="AW2">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX2">
         <v>7.8</v>
       </c>
       <c r="AY2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ2">
         <v>20</v>
       </c>
       <c r="BA2">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB2">
         <v>14</v>
@@ -1117,16 +1135,16 @@
         <v>16</v>
       </c>
       <c r="BD2">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BE2">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BF2">
         <v>9.199999999999999</v>
       </c>
       <c r="BG2">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1189,7 +1207,7 @@
         <v>1.04</v>
       </c>
       <c r="CB2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1203,10 +1221,10 @@
         <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F3">
         <v>2.42</v>
@@ -1431,7 +1449,7 @@
         <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1445,28 +1463,28 @@
         <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E4" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F4">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="G4">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="H4">
-        <v>1.96</v>
+        <v>1.04</v>
       </c>
       <c r="I4">
-        <v>2.1</v>
+        <v>1000</v>
       </c>
       <c r="J4">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="K4">
-        <v>4.4</v>
+        <v>950</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1475,210 +1493,210 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>5</v>
+        <v>1.25</v>
       </c>
       <c r="O4">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="P4">
-        <v>2.38</v>
+        <v>1.24</v>
       </c>
       <c r="Q4">
-        <v>1.59</v>
+        <v>1.17</v>
       </c>
       <c r="R4">
-        <v>1.56</v>
+        <v>1.18</v>
       </c>
       <c r="S4">
-        <v>2.46</v>
+        <v>1.16</v>
       </c>
       <c r="T4">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="U4">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="W4">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="X4">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AC4">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD4">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE4">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AG4">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AH4">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AI4">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK4">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AL4">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM4">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AO4">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AR4">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS4">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AT4">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AU4">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AV4">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AW4">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AX4">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="AY4">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="BA4">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BB4">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="BC4">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="BD4">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BE4">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="BF4">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BG4">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH4">
         <v>1000</v>
       </c>
       <c r="BI4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4">
         <v>1000</v>
       </c>
       <c r="BK4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN4">
         <v>1000</v>
       </c>
       <c r="BO4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT4">
         <v>1000</v>
       </c>
       <c r="BU4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B5" t="s">
         <v>87</v>
@@ -1687,172 +1705,172 @@
         <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E5" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F5">
-        <v>1.23</v>
+        <v>3.65</v>
       </c>
       <c r="G5">
-        <v>1.42</v>
+        <v>4.4</v>
       </c>
       <c r="H5">
-        <v>11.5</v>
+        <v>1.96</v>
       </c>
       <c r="I5">
-        <v>990</v>
+        <v>2.1</v>
       </c>
       <c r="J5">
+        <v>3.75</v>
+      </c>
+      <c r="K5">
         <v>4.4</v>
       </c>
-      <c r="K5">
-        <v>9.800000000000001</v>
-      </c>
       <c r="L5">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M5">
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="O5">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="P5">
-        <v>1.71</v>
+        <v>2.38</v>
       </c>
       <c r="Q5">
-        <v>1.83</v>
+        <v>1.59</v>
       </c>
       <c r="R5">
-        <v>1.26</v>
+        <v>1.56</v>
       </c>
       <c r="S5">
-        <v>3.05</v>
+        <v>2.46</v>
       </c>
       <c r="T5">
-        <v>1.11</v>
+        <v>1.54</v>
       </c>
       <c r="U5">
-        <v>1.11</v>
+        <v>2.48</v>
       </c>
       <c r="V5">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="W5">
-        <v>3.35</v>
+        <v>1.3</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y5">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z5">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AB5">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AC5">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD5">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE5">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AF5">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AG5">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH5">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AJ5">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK5">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL5">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN5">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AP5">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AQ5">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR5">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AS5">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AT5">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AU5">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AV5">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW5">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AX5">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AY5">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AZ5">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BA5">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BB5">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BC5">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BD5">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BE5">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BF5">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BG5">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -1915,7 +1933,7 @@
         <v>1.04</v>
       </c>
       <c r="CB5" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1926,243 +1944,243 @@
         <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E6" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F6">
-        <v>3.6</v>
+        <v>1.23</v>
       </c>
       <c r="G6">
+        <v>1.42</v>
+      </c>
+      <c r="H6">
+        <v>11.5</v>
+      </c>
+      <c r="I6">
+        <v>990</v>
+      </c>
+      <c r="J6">
         <v>4.4</v>
       </c>
-      <c r="H6">
-        <v>2.32</v>
-      </c>
-      <c r="I6">
-        <v>2.72</v>
-      </c>
-      <c r="J6">
-        <v>2.56</v>
-      </c>
       <c r="K6">
-        <v>3.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L6">
-        <v>1.59</v>
+        <v>1.32</v>
       </c>
       <c r="M6">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N6">
-        <v>2.38</v>
+        <v>3.3</v>
       </c>
       <c r="O6">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="P6">
-        <v>1.47</v>
+        <v>1.71</v>
       </c>
       <c r="Q6">
-        <v>2.78</v>
+        <v>1.83</v>
       </c>
       <c r="R6">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="S6">
-        <v>5.1</v>
+        <v>3.05</v>
       </c>
       <c r="T6">
-        <v>2.14</v>
+        <v>1.11</v>
       </c>
       <c r="U6">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="V6">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="W6">
-        <v>1.31</v>
+        <v>3.35</v>
       </c>
       <c r="X6">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="Y6">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="Z6">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC6">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD6">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE6">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AG6">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AH6">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR6">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU6">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV6">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW6">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY6">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA6">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC6">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BD6">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE6">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BF6">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG6">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BH6">
-        <v>2.98</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>2.16</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BN6">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BP6">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BT6">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="BV6">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX6">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B7" t="s">
         <v>87</v>
@@ -2171,240 +2189,240 @@
         <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E7" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="F7">
-        <v>1.59</v>
+        <v>3.6</v>
       </c>
       <c r="G7">
-        <v>2.06</v>
+        <v>4.3</v>
       </c>
       <c r="H7">
-        <v>4.5</v>
+        <v>2.32</v>
       </c>
       <c r="I7">
-        <v>8.800000000000001</v>
+        <v>2.58</v>
       </c>
       <c r="J7">
+        <v>2.84</v>
+      </c>
+      <c r="K7">
         <v>3.2</v>
       </c>
-      <c r="K7">
-        <v>6.8</v>
-      </c>
       <c r="L7">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="M7">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N7">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="O7">
-        <v>1.23</v>
+        <v>1.58</v>
       </c>
       <c r="P7">
         <v>1.47</v>
       </c>
       <c r="Q7">
-        <v>2.1</v>
+        <v>2.78</v>
       </c>
       <c r="R7">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="S7">
-        <v>2.46</v>
+        <v>5.8</v>
       </c>
       <c r="T7">
-        <v>1.11</v>
+        <v>2.14</v>
       </c>
       <c r="U7">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="V7">
-        <v>1.12</v>
+        <v>1.63</v>
       </c>
       <c r="W7">
-        <v>1.94</v>
+        <v>1.3</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Y7">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB7">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC7">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF7">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG7">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH7">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI7">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ7">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK7">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AL7">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP7">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AQ7">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AR7">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AS7">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AT7">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AU7">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AV7">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW7">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AX7">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AY7">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AZ7">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BA7">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB7">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC7">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD7">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE7">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF7">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG7">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>2.98</v>
       </c>
       <c r="BI7">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK7">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO7">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BQ7">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU7">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW7">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY7">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="CB7" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B8" t="s">
         <v>87</v>
@@ -2413,240 +2431,240 @@
         <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E8" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F8">
-        <v>2.04</v>
+        <v>1.64</v>
       </c>
       <c r="G8">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="H8">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I8">
-        <v>4.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J8">
-        <v>3.5</v>
+        <v>2.92</v>
       </c>
       <c r="K8">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="L8">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="M8">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>3.2</v>
+        <v>2.24</v>
       </c>
       <c r="O8">
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="P8">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="Q8">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="R8">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="S8">
-        <v>4.5</v>
+        <v>2.46</v>
       </c>
       <c r="T8">
-        <v>2.04</v>
+        <v>1.11</v>
       </c>
       <c r="U8">
-        <v>1.91</v>
+        <v>1.11</v>
       </c>
       <c r="V8">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="W8">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="X8">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>2.96</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>2.8</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL8">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN8">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BP8">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR8">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT8">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BV8">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BX8">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B9" t="s">
         <v>87</v>
@@ -2655,240 +2673,240 @@
         <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E9" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F9">
-        <v>1.65</v>
+        <v>2.04</v>
       </c>
       <c r="G9">
-        <v>1.76</v>
+        <v>2.06</v>
       </c>
       <c r="H9">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="I9">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="J9">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="K9">
-        <v>4.8</v>
+        <v>3.55</v>
       </c>
       <c r="L9">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M9">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="N9">
-        <v>2.14</v>
+        <v>3.2</v>
       </c>
       <c r="O9">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="P9">
-        <v>2.14</v>
+        <v>1.73</v>
       </c>
       <c r="Q9">
-        <v>1.49</v>
+        <v>2.3</v>
       </c>
       <c r="R9">
-        <v>1.46</v>
+        <v>1.27</v>
       </c>
       <c r="S9">
-        <v>2.22</v>
+        <v>4.5</v>
       </c>
       <c r="T9">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="U9">
-        <v>1.11</v>
+        <v>1.91</v>
       </c>
       <c r="V9">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="X9">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y9">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z9">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB9">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC9">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD9">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF9">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG9">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH9">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ9">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK9">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP9">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ9">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR9">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="AS9">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AT9">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU9">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV9">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="AX9">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY9">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ9">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BE9">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BG9">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BH9">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="BI9">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK9">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BL9">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="BM9">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO9">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ9">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS9">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU9">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW9">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY9">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA9">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="CB9" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B10" t="s">
         <v>87</v>
@@ -2897,52 +2915,52 @@
         <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E10" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F10">
-        <v>1.08</v>
+        <v>1.65</v>
       </c>
       <c r="G10">
-        <v>990</v>
+        <v>1.76</v>
       </c>
       <c r="H10">
-        <v>1.08</v>
+        <v>4.8</v>
       </c>
       <c r="I10">
-        <v>990</v>
+        <v>5.6</v>
       </c>
       <c r="J10">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="K10">
-        <v>950</v>
+        <v>4.8</v>
       </c>
       <c r="L10">
         <v>1.01</v>
       </c>
       <c r="M10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N10">
-        <v>1.1</v>
+        <v>2.14</v>
       </c>
       <c r="O10">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="P10">
-        <v>1.25</v>
+        <v>2.14</v>
       </c>
       <c r="Q10">
-        <v>1.07</v>
+        <v>1.49</v>
       </c>
       <c r="R10">
-        <v>1.18</v>
+        <v>1.46</v>
       </c>
       <c r="S10">
-        <v>1.08</v>
+        <v>2.22</v>
       </c>
       <c r="T10">
         <v>1.11</v>
@@ -3119,260 +3137,260 @@
         <v>1.04</v>
       </c>
       <c r="BZ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B11" t="s">
         <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E11" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F11">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="G11">
-        <v>1.35</v>
+        <v>990</v>
       </c>
       <c r="H11">
-        <v>9.800000000000001</v>
+        <v>1.08</v>
       </c>
       <c r="I11">
-        <v>10.5</v>
+        <v>990</v>
       </c>
       <c r="J11">
-        <v>6.2</v>
+        <v>1.1</v>
       </c>
       <c r="K11">
-        <v>6.4</v>
+        <v>950</v>
       </c>
       <c r="L11">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="M11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N11">
-        <v>6.8</v>
+        <v>1.1</v>
       </c>
       <c r="O11">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="P11">
-        <v>2.98</v>
+        <v>1.25</v>
       </c>
       <c r="Q11">
-        <v>1.49</v>
+        <v>1.07</v>
       </c>
       <c r="R11">
-        <v>1.77</v>
+        <v>1.18</v>
       </c>
       <c r="S11">
-        <v>2.22</v>
+        <v>1.08</v>
       </c>
       <c r="T11">
-        <v>1.84</v>
+        <v>1.11</v>
       </c>
       <c r="U11">
-        <v>2.14</v>
+        <v>1.11</v>
       </c>
       <c r="V11">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="W11">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="X11">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y11">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="Z11">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AA11">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC11">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AD11">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AE11">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF11">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AG11">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH11">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI11">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ11">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AK11">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AL11">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AM11">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="AO11">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP11">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="AR11">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="AS11">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="AT11">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU11">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AV11">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AW11">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="AX11">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY11">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BA11">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BB11">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC11">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BD11">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BE11">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BF11">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BG11">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BH11">
         <v>1000</v>
       </c>
       <c r="BI11">
-        <v>2.38</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>2.18</v>
+        <v>1.04</v>
       </c>
       <c r="BN11">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="BP11">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR11">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT11">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>2.14</v>
+        <v>1.04</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>2.12</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="CA11">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B12" t="s">
         <v>87</v>
@@ -3381,235 +3399,719 @@
         <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E12" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F12">
+        <v>1.33</v>
+      </c>
+      <c r="G12">
+        <v>1.35</v>
+      </c>
+      <c r="H12">
+        <v>10</v>
+      </c>
+      <c r="I12">
+        <v>10.5</v>
+      </c>
+      <c r="J12">
+        <v>6.2</v>
+      </c>
+      <c r="K12">
+        <v>6.6</v>
+      </c>
+      <c r="L12">
+        <v>1.26</v>
+      </c>
+      <c r="M12">
+        <v>1.03</v>
+      </c>
+      <c r="N12">
+        <v>6.8</v>
+      </c>
+      <c r="O12">
+        <v>1.16</v>
+      </c>
+      <c r="P12">
+        <v>2.98</v>
+      </c>
+      <c r="Q12">
+        <v>1.49</v>
+      </c>
+      <c r="R12">
+        <v>1.77</v>
+      </c>
+      <c r="S12">
+        <v>2.22</v>
+      </c>
+      <c r="T12">
+        <v>1.84</v>
+      </c>
+      <c r="U12">
+        <v>2.14</v>
+      </c>
+      <c r="V12">
+        <v>1.1</v>
+      </c>
+      <c r="W12">
+        <v>3.85</v>
+      </c>
+      <c r="X12">
+        <v>32</v>
+      </c>
+      <c r="Y12">
+        <v>44</v>
+      </c>
+      <c r="Z12">
+        <v>95</v>
+      </c>
+      <c r="AA12">
+        <v>370</v>
+      </c>
+      <c r="AB12">
+        <v>12</v>
+      </c>
+      <c r="AC12">
+        <v>14.5</v>
+      </c>
+      <c r="AD12">
+        <v>38</v>
+      </c>
+      <c r="AE12">
+        <v>120</v>
+      </c>
+      <c r="AF12">
+        <v>9.6</v>
+      </c>
+      <c r="AG12">
+        <v>10.5</v>
+      </c>
+      <c r="AH12">
+        <v>25</v>
+      </c>
+      <c r="AI12">
+        <v>120</v>
+      </c>
+      <c r="AJ12">
+        <v>11.5</v>
+      </c>
+      <c r="AK12">
+        <v>12.5</v>
+      </c>
+      <c r="AL12">
+        <v>28</v>
+      </c>
+      <c r="AM12">
+        <v>110</v>
+      </c>
+      <c r="AN12">
+        <v>4.2</v>
+      </c>
+      <c r="AO12">
+        <v>120</v>
+      </c>
+      <c r="AP12">
+        <v>28</v>
+      </c>
+      <c r="AQ12">
+        <v>38</v>
+      </c>
+      <c r="AR12">
+        <v>48</v>
+      </c>
+      <c r="AS12">
+        <v>60</v>
+      </c>
+      <c r="AT12">
+        <v>11.5</v>
+      </c>
+      <c r="AU12">
+        <v>13.5</v>
+      </c>
+      <c r="AV12">
+        <v>34</v>
+      </c>
+      <c r="AW12">
+        <v>40</v>
+      </c>
+      <c r="AX12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY12">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ12">
+        <v>24</v>
+      </c>
+      <c r="BA12">
+        <v>85</v>
+      </c>
+      <c r="BB12">
+        <v>10.5</v>
+      </c>
+      <c r="BC12">
+        <v>12</v>
+      </c>
+      <c r="BD12">
+        <v>26</v>
+      </c>
+      <c r="BE12">
+        <v>65</v>
+      </c>
+      <c r="BF12">
+        <v>4</v>
+      </c>
+      <c r="BG12">
+        <v>46</v>
+      </c>
+      <c r="BH12">
+        <v>1000</v>
+      </c>
+      <c r="BI12">
+        <v>2.38</v>
+      </c>
+      <c r="BJ12">
+        <v>15</v>
+      </c>
+      <c r="BK12">
+        <v>3.3</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>2.18</v>
+      </c>
+      <c r="BN12">
+        <v>5.2</v>
+      </c>
+      <c r="BO12">
+        <v>3</v>
+      </c>
+      <c r="BP12">
+        <v>10.5</v>
+      </c>
+      <c r="BQ12">
+        <v>5.5</v>
+      </c>
+      <c r="BR12">
+        <v>28</v>
+      </c>
+      <c r="BS12">
+        <v>3.6</v>
+      </c>
+      <c r="BT12">
+        <v>17.5</v>
+      </c>
+      <c r="BU12">
+        <v>3.4</v>
+      </c>
+      <c r="BV12">
+        <v>1000</v>
+      </c>
+      <c r="BW12">
+        <v>2.14</v>
+      </c>
+      <c r="BX12">
+        <v>1000</v>
+      </c>
+      <c r="BY12">
+        <v>2.12</v>
+      </c>
+      <c r="BZ12">
+        <v>14</v>
+      </c>
+      <c r="CA12">
+        <v>6.2</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" t="s">
+        <v>97</v>
+      </c>
+      <c r="D13" t="s">
+        <v>110</v>
+      </c>
+      <c r="E13" t="s">
+        <v>123</v>
+      </c>
+      <c r="F13">
         <v>1.48</v>
       </c>
-      <c r="G12">
+      <c r="G13">
         <v>1.68</v>
       </c>
-      <c r="H12">
+      <c r="H13">
         <v>3.35</v>
       </c>
-      <c r="I12">
+      <c r="I13">
         <v>16</v>
       </c>
-      <c r="J12">
+      <c r="J13">
         <v>3.55</v>
       </c>
-      <c r="K12">
+      <c r="K13">
         <v>950</v>
       </c>
-      <c r="L12">
-        <v>1.01</v>
-      </c>
-      <c r="M12">
-        <v>1.01</v>
-      </c>
-      <c r="N12">
+      <c r="L13">
+        <v>1.42</v>
+      </c>
+      <c r="M13">
+        <v>1.01</v>
+      </c>
+      <c r="N13">
+        <v>2.46</v>
+      </c>
+      <c r="O13">
+        <v>1.44</v>
+      </c>
+      <c r="P13">
+        <v>1.52</v>
+      </c>
+      <c r="Q13">
+        <v>2.3</v>
+      </c>
+      <c r="R13">
+        <v>1.12</v>
+      </c>
+      <c r="S13">
         <v>2.74</v>
       </c>
-      <c r="O12">
-        <v>1.44</v>
-      </c>
-      <c r="P12">
-        <v>1.52</v>
-      </c>
-      <c r="Q12">
-        <v>2.3</v>
-      </c>
-      <c r="R12">
-        <v>1.12</v>
-      </c>
-      <c r="S12">
-        <v>2.74</v>
-      </c>
-      <c r="T12">
+      <c r="T13">
         <v>1.11</v>
       </c>
-      <c r="U12">
+      <c r="U13">
         <v>1.11</v>
       </c>
-      <c r="V12">
+      <c r="V13">
         <v>1.06</v>
       </c>
-      <c r="W12">
+      <c r="W13">
         <v>2.46</v>
       </c>
-      <c r="X12">
-        <v>1000</v>
-      </c>
-      <c r="Y12">
-        <v>1000</v>
-      </c>
-      <c r="Z12">
-        <v>1000</v>
-      </c>
-      <c r="AA12">
-        <v>1000</v>
-      </c>
-      <c r="AB12">
-        <v>1000</v>
-      </c>
-      <c r="AC12">
-        <v>1000</v>
-      </c>
-      <c r="AD12">
-        <v>1000</v>
-      </c>
-      <c r="AE12">
-        <v>1000</v>
-      </c>
-      <c r="AF12">
-        <v>1000</v>
-      </c>
-      <c r="AG12">
-        <v>1000</v>
-      </c>
-      <c r="AH12">
-        <v>1000</v>
-      </c>
-      <c r="AI12">
-        <v>1000</v>
-      </c>
-      <c r="AJ12">
-        <v>1000</v>
-      </c>
-      <c r="AK12">
-        <v>1000</v>
-      </c>
-      <c r="AL12">
-        <v>1000</v>
-      </c>
-      <c r="AM12">
-        <v>1000</v>
-      </c>
-      <c r="AN12">
-        <v>1000</v>
-      </c>
-      <c r="AO12">
-        <v>1000</v>
-      </c>
-      <c r="AP12">
-        <v>1.01</v>
-      </c>
-      <c r="AQ12">
-        <v>1.01</v>
-      </c>
-      <c r="AR12">
-        <v>1.01</v>
-      </c>
-      <c r="AS12">
-        <v>1.01</v>
-      </c>
-      <c r="AT12">
-        <v>1.01</v>
-      </c>
-      <c r="AU12">
-        <v>1.01</v>
-      </c>
-      <c r="AV12">
-        <v>1.01</v>
-      </c>
-      <c r="AW12">
-        <v>1.01</v>
-      </c>
-      <c r="AX12">
-        <v>1.01</v>
-      </c>
-      <c r="AY12">
-        <v>1.01</v>
-      </c>
-      <c r="AZ12">
-        <v>1.01</v>
-      </c>
-      <c r="BA12">
-        <v>1.01</v>
-      </c>
-      <c r="BB12">
-        <v>1.01</v>
-      </c>
-      <c r="BC12">
-        <v>1.01</v>
-      </c>
-      <c r="BD12">
-        <v>1.01</v>
-      </c>
-      <c r="BE12">
-        <v>1.01</v>
-      </c>
-      <c r="BF12">
-        <v>1.01</v>
-      </c>
-      <c r="BG12">
-        <v>1.01</v>
-      </c>
-      <c r="BH12">
-        <v>1000</v>
-      </c>
-      <c r="BI12">
-        <v>1.04</v>
-      </c>
-      <c r="BJ12">
-        <v>1000</v>
-      </c>
-      <c r="BK12">
-        <v>1.04</v>
-      </c>
-      <c r="BL12">
-        <v>1000</v>
-      </c>
-      <c r="BM12">
-        <v>1.04</v>
-      </c>
-      <c r="BN12">
-        <v>1000</v>
-      </c>
-      <c r="BO12">
-        <v>1.04</v>
-      </c>
-      <c r="BP12">
-        <v>1000</v>
-      </c>
-      <c r="BQ12">
-        <v>1.04</v>
-      </c>
-      <c r="BR12">
-        <v>1000</v>
-      </c>
-      <c r="BS12">
-        <v>1.04</v>
-      </c>
-      <c r="BT12">
-        <v>1000</v>
-      </c>
-      <c r="BU12">
-        <v>1.04</v>
-      </c>
-      <c r="BV12">
-        <v>1000</v>
-      </c>
-      <c r="BW12">
-        <v>1.04</v>
-      </c>
-      <c r="BX12">
-        <v>1000</v>
-      </c>
-      <c r="BY12">
-        <v>1.04</v>
-      </c>
-      <c r="BZ12">
-        <v>1000</v>
-      </c>
-      <c r="CA12">
-        <v>1.04</v>
-      </c>
-      <c r="CB12" t="s">
-        <v>119</v>
+      <c r="X13">
+        <v>1000</v>
+      </c>
+      <c r="Y13">
+        <v>1000</v>
+      </c>
+      <c r="Z13">
+        <v>1000</v>
+      </c>
+      <c r="AA13">
+        <v>1000</v>
+      </c>
+      <c r="AB13">
+        <v>1000</v>
+      </c>
+      <c r="AC13">
+        <v>1000</v>
+      </c>
+      <c r="AD13">
+        <v>1000</v>
+      </c>
+      <c r="AE13">
+        <v>1000</v>
+      </c>
+      <c r="AF13">
+        <v>1000</v>
+      </c>
+      <c r="AG13">
+        <v>1000</v>
+      </c>
+      <c r="AH13">
+        <v>1000</v>
+      </c>
+      <c r="AI13">
+        <v>1000</v>
+      </c>
+      <c r="AJ13">
+        <v>1000</v>
+      </c>
+      <c r="AK13">
+        <v>1000</v>
+      </c>
+      <c r="AL13">
+        <v>1000</v>
+      </c>
+      <c r="AM13">
+        <v>1000</v>
+      </c>
+      <c r="AN13">
+        <v>1000</v>
+      </c>
+      <c r="AO13">
+        <v>1000</v>
+      </c>
+      <c r="AP13">
+        <v>1.01</v>
+      </c>
+      <c r="AQ13">
+        <v>1.01</v>
+      </c>
+      <c r="AR13">
+        <v>1.01</v>
+      </c>
+      <c r="AS13">
+        <v>1.01</v>
+      </c>
+      <c r="AT13">
+        <v>1.01</v>
+      </c>
+      <c r="AU13">
+        <v>1.01</v>
+      </c>
+      <c r="AV13">
+        <v>1.01</v>
+      </c>
+      <c r="AW13">
+        <v>1.01</v>
+      </c>
+      <c r="AX13">
+        <v>1.01</v>
+      </c>
+      <c r="AY13">
+        <v>1.01</v>
+      </c>
+      <c r="AZ13">
+        <v>1.01</v>
+      </c>
+      <c r="BA13">
+        <v>1.01</v>
+      </c>
+      <c r="BB13">
+        <v>1.01</v>
+      </c>
+      <c r="BC13">
+        <v>1.01</v>
+      </c>
+      <c r="BD13">
+        <v>1.01</v>
+      </c>
+      <c r="BE13">
+        <v>1.01</v>
+      </c>
+      <c r="BF13">
+        <v>1.01</v>
+      </c>
+      <c r="BG13">
+        <v>1.01</v>
+      </c>
+      <c r="BH13">
+        <v>1000</v>
+      </c>
+      <c r="BI13">
+        <v>1.04</v>
+      </c>
+      <c r="BJ13">
+        <v>1000</v>
+      </c>
+      <c r="BK13">
+        <v>1.04</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>1.04</v>
+      </c>
+      <c r="BN13">
+        <v>1000</v>
+      </c>
+      <c r="BO13">
+        <v>1.04</v>
+      </c>
+      <c r="BP13">
+        <v>1000</v>
+      </c>
+      <c r="BQ13">
+        <v>1.04</v>
+      </c>
+      <c r="BR13">
+        <v>1000</v>
+      </c>
+      <c r="BS13">
+        <v>1.04</v>
+      </c>
+      <c r="BT13">
+        <v>1000</v>
+      </c>
+      <c r="BU13">
+        <v>1.04</v>
+      </c>
+      <c r="BV13">
+        <v>1000</v>
+      </c>
+      <c r="BW13">
+        <v>1.04</v>
+      </c>
+      <c r="BX13">
+        <v>1000</v>
+      </c>
+      <c r="BY13">
+        <v>1.04</v>
+      </c>
+      <c r="BZ13">
+        <v>1000</v>
+      </c>
+      <c r="CA13">
+        <v>1.04</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" t="s">
+        <v>98</v>
+      </c>
+      <c r="D14" t="s">
+        <v>111</v>
+      </c>
+      <c r="E14" t="s">
+        <v>124</v>
+      </c>
+      <c r="F14">
+        <v>3.75</v>
+      </c>
+      <c r="G14">
+        <v>4.7</v>
+      </c>
+      <c r="H14">
+        <v>2.12</v>
+      </c>
+      <c r="I14">
+        <v>2.44</v>
+      </c>
+      <c r="J14">
+        <v>2.98</v>
+      </c>
+      <c r="K14">
+        <v>3.4</v>
+      </c>
+      <c r="L14">
+        <v>1.01</v>
+      </c>
+      <c r="M14">
+        <v>1.1</v>
+      </c>
+      <c r="N14">
+        <v>2.86</v>
+      </c>
+      <c r="O14">
+        <v>1.43</v>
+      </c>
+      <c r="P14">
+        <v>1.6</v>
+      </c>
+      <c r="Q14">
+        <v>2.2</v>
+      </c>
+      <c r="R14">
+        <v>1.21</v>
+      </c>
+      <c r="S14">
+        <v>4.1</v>
+      </c>
+      <c r="T14">
+        <v>1.11</v>
+      </c>
+      <c r="U14">
+        <v>1.11</v>
+      </c>
+      <c r="V14">
+        <v>1.7</v>
+      </c>
+      <c r="W14">
+        <v>1.27</v>
+      </c>
+      <c r="X14">
+        <v>1000</v>
+      </c>
+      <c r="Y14">
+        <v>1000</v>
+      </c>
+      <c r="Z14">
+        <v>1000</v>
+      </c>
+      <c r="AA14">
+        <v>1000</v>
+      </c>
+      <c r="AB14">
+        <v>1000</v>
+      </c>
+      <c r="AC14">
+        <v>1000</v>
+      </c>
+      <c r="AD14">
+        <v>1000</v>
+      </c>
+      <c r="AE14">
+        <v>1000</v>
+      </c>
+      <c r="AF14">
+        <v>1000</v>
+      </c>
+      <c r="AG14">
+        <v>1000</v>
+      </c>
+      <c r="AH14">
+        <v>1000</v>
+      </c>
+      <c r="AI14">
+        <v>1000</v>
+      </c>
+      <c r="AJ14">
+        <v>1000</v>
+      </c>
+      <c r="AK14">
+        <v>1000</v>
+      </c>
+      <c r="AL14">
+        <v>1000</v>
+      </c>
+      <c r="AM14">
+        <v>1000</v>
+      </c>
+      <c r="AN14">
+        <v>1000</v>
+      </c>
+      <c r="AO14">
+        <v>1000</v>
+      </c>
+      <c r="AP14">
+        <v>1.01</v>
+      </c>
+      <c r="AQ14">
+        <v>1.01</v>
+      </c>
+      <c r="AR14">
+        <v>1.01</v>
+      </c>
+      <c r="AS14">
+        <v>1.01</v>
+      </c>
+      <c r="AT14">
+        <v>1.01</v>
+      </c>
+      <c r="AU14">
+        <v>1.01</v>
+      </c>
+      <c r="AV14">
+        <v>1.01</v>
+      </c>
+      <c r="AW14">
+        <v>1.01</v>
+      </c>
+      <c r="AX14">
+        <v>1.01</v>
+      </c>
+      <c r="AY14">
+        <v>1.01</v>
+      </c>
+      <c r="AZ14">
+        <v>1.01</v>
+      </c>
+      <c r="BA14">
+        <v>1.01</v>
+      </c>
+      <c r="BB14">
+        <v>1.01</v>
+      </c>
+      <c r="BC14">
+        <v>1.01</v>
+      </c>
+      <c r="BD14">
+        <v>1.01</v>
+      </c>
+      <c r="BE14">
+        <v>1.01</v>
+      </c>
+      <c r="BF14">
+        <v>1.01</v>
+      </c>
+      <c r="BG14">
+        <v>1.01</v>
+      </c>
+      <c r="BH14">
+        <v>1000</v>
+      </c>
+      <c r="BI14">
+        <v>1.04</v>
+      </c>
+      <c r="BJ14">
+        <v>1000</v>
+      </c>
+      <c r="BK14">
+        <v>1.04</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>1.04</v>
+      </c>
+      <c r="BN14">
+        <v>1000</v>
+      </c>
+      <c r="BO14">
+        <v>1.04</v>
+      </c>
+      <c r="BP14">
+        <v>1000</v>
+      </c>
+      <c r="BQ14">
+        <v>1.04</v>
+      </c>
+      <c r="BR14">
+        <v>1000</v>
+      </c>
+      <c r="BS14">
+        <v>1.04</v>
+      </c>
+      <c r="BT14">
+        <v>1000</v>
+      </c>
+      <c r="BU14">
+        <v>1.04</v>
+      </c>
+      <c r="BV14">
+        <v>1000</v>
+      </c>
+      <c r="BW14">
+        <v>1.04</v>
+      </c>
+      <c r="BX14">
+        <v>1000</v>
+      </c>
+      <c r="BY14">
+        <v>1.04</v>
+      </c>
+      <c r="BZ14">
+        <v>1000</v>
+      </c>
+      <c r="CA14">
+        <v>1.04</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="132">
   <si>
     <t>League</t>
   </si>
@@ -265,6 +265,9 @@
     <t>Qatari Stars League</t>
   </si>
   <si>
+    <t>Saudi 1st Division</t>
+  </si>
+  <si>
     <t>Algerian Ligue 1</t>
   </si>
   <si>
@@ -289,6 +292,9 @@
     <t>14:15:00</t>
   </si>
   <si>
+    <t>16:20:00</t>
+  </si>
+  <si>
     <t>16:30:00</t>
   </si>
   <si>
@@ -322,6 +328,12 @@
     <t>Al Gharafa</t>
   </si>
   <si>
+    <t>Al Jabalain</t>
+  </si>
+  <si>
+    <t>Jeddah Club</t>
+  </si>
+  <si>
     <t>Al-Wakra</t>
   </si>
   <si>
@@ -361,6 +373,12 @@
     <t>Al Shamal</t>
   </si>
   <si>
+    <t>Al Jeel</t>
+  </si>
+  <si>
+    <t>Al Najma Club</t>
+  </si>
+  <si>
     <t>Al Rayyan</t>
   </si>
   <si>
@@ -391,7 +409,7 @@
     <t>Millonarios</t>
   </si>
   <si>
-    <t>2026-08-26 00:09:27</t>
+    <t>2026-08-26 02:18:24</t>
   </si>
 </sst>
 </file>
@@ -723,7 +741,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB14"/>
+  <dimension ref="A1:CB16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -973,58 +991,58 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F2">
         <v>1.64</v>
       </c>
       <c r="G2">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="H2">
         <v>6.2</v>
       </c>
       <c r="I2">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J2">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K2">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M2">
         <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O2">
         <v>1.36</v>
       </c>
       <c r="P2">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="Q2">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="R2">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S2">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="T2">
         <v>2.02</v>
@@ -1033,7 +1051,7 @@
         <v>1.82</v>
       </c>
       <c r="V2">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W2">
         <v>2.46</v>
@@ -1069,7 +1087,7 @@
         <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI2">
         <v>120</v>
@@ -1102,7 +1120,7 @@
         <v>7</v>
       </c>
       <c r="AS2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT2">
         <v>6.2</v>
@@ -1114,7 +1132,7 @@
         <v>21</v>
       </c>
       <c r="AW2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX2">
         <v>7.8</v>
@@ -1126,7 +1144,7 @@
         <v>20</v>
       </c>
       <c r="BA2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB2">
         <v>14</v>
@@ -1207,7 +1225,7 @@
         <v>1.04</v>
       </c>
       <c r="CB2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1215,19 +1233,19 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="F3">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="G3">
         <v>3</v>
@@ -1236,13 +1254,13 @@
         <v>3.7</v>
       </c>
       <c r="I3">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="J3">
         <v>2.4</v>
       </c>
       <c r="K3">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="L3">
         <v>1.61</v>
@@ -1275,7 +1293,7 @@
         <v>1.49</v>
       </c>
       <c r="V3">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="W3">
         <v>1.5</v>
@@ -1449,7 +1467,7 @@
         <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1457,34 +1475,34 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F4">
-        <v>1.04</v>
+        <v>2.48</v>
       </c>
       <c r="G4">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="H4">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="I4">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="J4">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="K4">
-        <v>950</v>
+        <v>5.8</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1493,22 +1511,22 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O4">
         <v>1.17</v>
       </c>
       <c r="P4">
-        <v>1.24</v>
+        <v>2.34</v>
       </c>
       <c r="Q4">
-        <v>1.17</v>
+        <v>1.58</v>
       </c>
       <c r="R4">
-        <v>1.18</v>
+        <v>1.51</v>
       </c>
       <c r="S4">
-        <v>1.16</v>
+        <v>2.38</v>
       </c>
       <c r="T4">
         <v>1.01</v>
@@ -1517,10 +1535,10 @@
         <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="W4">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -1691,320 +1709,320 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E5" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F5">
-        <v>3.65</v>
+        <v>1.47</v>
       </c>
       <c r="G5">
-        <v>4.4</v>
+        <v>1.77</v>
       </c>
       <c r="H5">
-        <v>1.96</v>
+        <v>5.5</v>
       </c>
       <c r="I5">
-        <v>2.1</v>
+        <v>12</v>
       </c>
       <c r="J5">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="K5">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M5">
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>5</v>
+        <v>2.94</v>
       </c>
       <c r="O5">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="P5">
-        <v>2.38</v>
+        <v>1.79</v>
       </c>
       <c r="Q5">
-        <v>1.59</v>
+        <v>1.74</v>
       </c>
       <c r="R5">
-        <v>1.56</v>
+        <v>1.26</v>
       </c>
       <c r="S5">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="T5">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="U5">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="V5">
-        <v>1.91</v>
+        <v>1.09</v>
       </c>
       <c r="W5">
-        <v>1.3</v>
+        <v>2.28</v>
       </c>
       <c r="X5">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Y5">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Z5">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AA5">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AC5">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD5">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE5">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AF5">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AG5">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AH5">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AI5">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AJ5">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK5">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AL5">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM5">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AN5">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AO5">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AP5">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AR5">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS5">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AT5">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AU5">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AV5">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AW5">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AX5">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="AY5">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="BA5">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BB5">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="BC5">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="BD5">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BE5">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="BF5">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BG5">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH5">
         <v>1000</v>
       </c>
       <c r="BI5">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5">
         <v>1000</v>
       </c>
       <c r="BK5">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN5">
         <v>1000</v>
       </c>
       <c r="BO5">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP5">
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT5">
         <v>1000</v>
       </c>
       <c r="BU5">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA5">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
         <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E6" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F6">
-        <v>1.23</v>
+        <v>4.3</v>
       </c>
       <c r="G6">
-        <v>1.42</v>
+        <v>5.9</v>
       </c>
       <c r="H6">
-        <v>11.5</v>
+        <v>1.76</v>
       </c>
       <c r="I6">
-        <v>990</v>
+        <v>1.99</v>
       </c>
       <c r="J6">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="K6">
-        <v>9.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="L6">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M6">
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O6">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="P6">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="Q6">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="R6">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="S6">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T6">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U6">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="W6">
-        <v>3.35</v>
+        <v>1.2</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2061,52 +2079,52 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF6">
         <v>1.01</v>
@@ -2118,485 +2136,485 @@
         <v>1000</v>
       </c>
       <c r="BI6">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6">
         <v>1000</v>
       </c>
       <c r="BK6">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN6">
         <v>1000</v>
       </c>
       <c r="BO6">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT6">
         <v>1000</v>
       </c>
       <c r="BU6">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA6">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E7" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F7">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="G7">
+        <v>4.1</v>
+      </c>
+      <c r="H7">
+        <v>1.96</v>
+      </c>
+      <c r="I7">
+        <v>2.1</v>
+      </c>
+      <c r="J7">
+        <v>3.75</v>
+      </c>
+      <c r="K7">
         <v>4.3</v>
       </c>
-      <c r="H7">
-        <v>2.32</v>
-      </c>
-      <c r="I7">
-        <v>2.58</v>
-      </c>
-      <c r="J7">
-        <v>2.84</v>
-      </c>
-      <c r="K7">
-        <v>3.2</v>
-      </c>
       <c r="L7">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N7">
-        <v>2.36</v>
+        <v>5.1</v>
       </c>
       <c r="O7">
-        <v>1.58</v>
+        <v>1.2</v>
       </c>
       <c r="P7">
-        <v>1.47</v>
+        <v>2.4</v>
       </c>
       <c r="Q7">
-        <v>2.78</v>
+        <v>1.59</v>
       </c>
       <c r="R7">
-        <v>1.16</v>
+        <v>1.57</v>
       </c>
       <c r="S7">
+        <v>2.46</v>
+      </c>
+      <c r="T7">
+        <v>1.55</v>
+      </c>
+      <c r="U7">
+        <v>2.48</v>
+      </c>
+      <c r="V7">
+        <v>1.92</v>
+      </c>
+      <c r="W7">
+        <v>1.32</v>
+      </c>
+      <c r="X7">
+        <v>28</v>
+      </c>
+      <c r="Y7">
+        <v>15.5</v>
+      </c>
+      <c r="Z7">
+        <v>16</v>
+      </c>
+      <c r="AA7">
+        <v>25</v>
+      </c>
+      <c r="AB7">
+        <v>26</v>
+      </c>
+      <c r="AC7">
+        <v>12</v>
+      </c>
+      <c r="AD7">
+        <v>12.5</v>
+      </c>
+      <c r="AE7">
+        <v>19.5</v>
+      </c>
+      <c r="AF7">
+        <v>38</v>
+      </c>
+      <c r="AG7">
+        <v>18.5</v>
+      </c>
+      <c r="AH7">
+        <v>16</v>
+      </c>
+      <c r="AI7">
+        <v>28</v>
+      </c>
+      <c r="AJ7">
+        <v>70</v>
+      </c>
+      <c r="AK7">
+        <v>42</v>
+      </c>
+      <c r="AL7">
+        <v>44</v>
+      </c>
+      <c r="AM7">
+        <v>60</v>
+      </c>
+      <c r="AN7">
+        <v>29</v>
+      </c>
+      <c r="AO7">
+        <v>10.5</v>
+      </c>
+      <c r="AP7">
+        <v>17.5</v>
+      </c>
+      <c r="AQ7">
+        <v>11</v>
+      </c>
+      <c r="AR7">
+        <v>12.5</v>
+      </c>
+      <c r="AS7">
+        <v>21</v>
+      </c>
+      <c r="AT7">
+        <v>18</v>
+      </c>
+      <c r="AU7">
+        <v>8</v>
+      </c>
+      <c r="AV7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW7">
+        <v>16</v>
+      </c>
+      <c r="AX7">
+        <v>5.4</v>
+      </c>
+      <c r="AY7">
+        <v>14.5</v>
+      </c>
+      <c r="AZ7">
+        <v>11</v>
+      </c>
+      <c r="BA7">
+        <v>21</v>
+      </c>
+      <c r="BB7">
         <v>5.8</v>
       </c>
-      <c r="T7">
-        <v>2.14</v>
-      </c>
-      <c r="U7">
-        <v>1.6</v>
-      </c>
-      <c r="V7">
-        <v>1.63</v>
-      </c>
-      <c r="W7">
-        <v>1.3</v>
-      </c>
-      <c r="X7">
-        <v>9.6</v>
-      </c>
-      <c r="Y7">
-        <v>8.6</v>
-      </c>
-      <c r="Z7">
-        <v>17</v>
-      </c>
-      <c r="AA7">
-        <v>46</v>
-      </c>
-      <c r="AB7">
-        <v>12</v>
-      </c>
-      <c r="AC7">
-        <v>8.6</v>
-      </c>
-      <c r="AD7">
-        <v>15.5</v>
-      </c>
-      <c r="AE7">
-        <v>46</v>
-      </c>
-      <c r="AF7">
+      <c r="BC7">
+        <v>5.5</v>
+      </c>
+      <c r="BD7">
         <v>32</v>
       </c>
-      <c r="AG7">
+      <c r="BE7">
+        <v>5.7</v>
+      </c>
+      <c r="BF7">
         <v>21</v>
       </c>
-      <c r="AH7">
-        <v>30</v>
-      </c>
-      <c r="AI7">
-        <v>85</v>
-      </c>
-      <c r="AJ7">
-        <v>110</v>
-      </c>
-      <c r="AK7">
-        <v>85</v>
-      </c>
-      <c r="AL7">
-        <v>120</v>
-      </c>
-      <c r="AM7">
-        <v>260</v>
-      </c>
-      <c r="AN7">
-        <v>130</v>
-      </c>
-      <c r="AO7">
-        <v>50</v>
-      </c>
-      <c r="AP7">
-        <v>6</v>
-      </c>
-      <c r="AQ7">
-        <v>5.4</v>
-      </c>
-      <c r="AR7">
-        <v>10</v>
-      </c>
-      <c r="AS7">
-        <v>3.95</v>
-      </c>
-      <c r="AT7">
-        <v>7.4</v>
-      </c>
-      <c r="AU7">
-        <v>5.4</v>
-      </c>
-      <c r="AV7">
-        <v>10.5</v>
-      </c>
-      <c r="AW7">
-        <v>3.95</v>
-      </c>
-      <c r="AX7">
-        <v>18.5</v>
-      </c>
-      <c r="AY7">
-        <v>12.5</v>
-      </c>
-      <c r="AZ7">
-        <v>18</v>
-      </c>
-      <c r="BA7">
-        <v>4.1</v>
-      </c>
-      <c r="BB7">
-        <v>4.2</v>
-      </c>
-      <c r="BC7">
-        <v>4.1</v>
-      </c>
-      <c r="BD7">
-        <v>4.2</v>
-      </c>
-      <c r="BE7">
-        <v>4.3</v>
-      </c>
-      <c r="BF7">
-        <v>4.2</v>
-      </c>
       <c r="BG7">
-        <v>4</v>
+        <v>8.4</v>
       </c>
       <c r="BH7">
-        <v>2.98</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>2.16</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BP7">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E8" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F8">
-        <v>1.64</v>
+        <v>1.27</v>
       </c>
       <c r="G8">
-        <v>2.1</v>
+        <v>1.34</v>
       </c>
       <c r="H8">
+        <v>15.5</v>
+      </c>
+      <c r="I8">
+        <v>23</v>
+      </c>
+      <c r="J8">
+        <v>5.2</v>
+      </c>
+      <c r="K8">
+        <v>6.2</v>
+      </c>
+      <c r="L8">
+        <v>1.32</v>
+      </c>
+      <c r="M8">
+        <v>1.07</v>
+      </c>
+      <c r="N8">
+        <v>3.5</v>
+      </c>
+      <c r="O8">
+        <v>1.34</v>
+      </c>
+      <c r="P8">
+        <v>1.84</v>
+      </c>
+      <c r="Q8">
+        <v>2</v>
+      </c>
+      <c r="R8">
+        <v>1.31</v>
+      </c>
+      <c r="S8">
+        <v>3.6</v>
+      </c>
+      <c r="T8">
+        <v>2.68</v>
+      </c>
+      <c r="U8">
+        <v>1.47</v>
+      </c>
+      <c r="V8">
+        <v>1.05</v>
+      </c>
+      <c r="W8">
+        <v>3.9</v>
+      </c>
+      <c r="X8">
+        <v>17.5</v>
+      </c>
+      <c r="Y8">
+        <v>46</v>
+      </c>
+      <c r="Z8">
+        <v>230</v>
+      </c>
+      <c r="AA8">
+        <v>1000</v>
+      </c>
+      <c r="AB8">
+        <v>7.4</v>
+      </c>
+      <c r="AC8">
+        <v>16.5</v>
+      </c>
+      <c r="AD8">
+        <v>950</v>
+      </c>
+      <c r="AE8">
+        <v>620</v>
+      </c>
+      <c r="AF8">
+        <v>7.6</v>
+      </c>
+      <c r="AG8">
+        <v>14.5</v>
+      </c>
+      <c r="AH8">
+        <v>60</v>
+      </c>
+      <c r="AI8">
+        <v>460</v>
+      </c>
+      <c r="AJ8">
+        <v>11</v>
+      </c>
+      <c r="AK8">
+        <v>22</v>
+      </c>
+      <c r="AL8">
+        <v>85</v>
+      </c>
+      <c r="AM8">
+        <v>530</v>
+      </c>
+      <c r="AN8">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO8">
+        <v>1000</v>
+      </c>
+      <c r="AP8">
+        <v>10.5</v>
+      </c>
+      <c r="AQ8">
+        <v>4.2</v>
+      </c>
+      <c r="AR8">
         <v>4.5</v>
       </c>
-      <c r="I8">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J8">
-        <v>2.92</v>
-      </c>
-      <c r="K8">
-        <v>3.75</v>
-      </c>
-      <c r="L8">
-        <v>1.42</v>
-      </c>
-      <c r="M8">
-        <v>1.01</v>
-      </c>
-      <c r="N8">
-        <v>2.24</v>
-      </c>
-      <c r="O8">
-        <v>1.23</v>
-      </c>
-      <c r="P8">
-        <v>1.47</v>
-      </c>
-      <c r="Q8">
-        <v>2.1</v>
-      </c>
-      <c r="R8">
-        <v>1.13</v>
-      </c>
-      <c r="S8">
-        <v>2.46</v>
-      </c>
-      <c r="T8">
-        <v>1.11</v>
-      </c>
-      <c r="U8">
-        <v>1.11</v>
-      </c>
-      <c r="V8">
-        <v>1.12</v>
-      </c>
-      <c r="W8">
-        <v>1.92</v>
-      </c>
-      <c r="X8">
-        <v>1000</v>
-      </c>
-      <c r="Y8">
-        <v>1000</v>
-      </c>
-      <c r="Z8">
-        <v>1000</v>
-      </c>
-      <c r="AA8">
-        <v>1000</v>
-      </c>
-      <c r="AB8">
-        <v>1000</v>
-      </c>
-      <c r="AC8">
-        <v>1000</v>
-      </c>
-      <c r="AD8">
-        <v>1000</v>
-      </c>
-      <c r="AE8">
-        <v>1000</v>
-      </c>
-      <c r="AF8">
-        <v>1000</v>
-      </c>
-      <c r="AG8">
-        <v>1000</v>
-      </c>
-      <c r="AH8">
-        <v>1000</v>
-      </c>
-      <c r="AI8">
-        <v>1000</v>
-      </c>
-      <c r="AJ8">
-        <v>1000</v>
-      </c>
-      <c r="AK8">
-        <v>1000</v>
-      </c>
-      <c r="AL8">
-        <v>1000</v>
-      </c>
-      <c r="AM8">
-        <v>1000</v>
-      </c>
-      <c r="AN8">
-        <v>1000</v>
-      </c>
-      <c r="AO8">
-        <v>1000</v>
-      </c>
-      <c r="AP8">
-        <v>1.01</v>
-      </c>
-      <c r="AQ8">
-        <v>1.01</v>
-      </c>
-      <c r="AR8">
-        <v>1.01</v>
-      </c>
       <c r="AS8">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT8">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AU8">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV8">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AW8">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX8">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AY8">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ8">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA8">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BD8">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2659,308 +2677,308 @@
         <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
         <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E9" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F9">
-        <v>2.04</v>
+        <v>3.7</v>
       </c>
       <c r="G9">
-        <v>2.06</v>
+        <v>4.2</v>
       </c>
       <c r="H9">
+        <v>2.3</v>
+      </c>
+      <c r="I9">
+        <v>2.54</v>
+      </c>
+      <c r="J9">
+        <v>2.84</v>
+      </c>
+      <c r="K9">
+        <v>3.2</v>
+      </c>
+      <c r="L9">
+        <v>1.6</v>
+      </c>
+      <c r="M9">
+        <v>1.13</v>
+      </c>
+      <c r="N9">
+        <v>2.3</v>
+      </c>
+      <c r="O9">
+        <v>1.58</v>
+      </c>
+      <c r="P9">
+        <v>1.47</v>
+      </c>
+      <c r="Q9">
+        <v>2.78</v>
+      </c>
+      <c r="R9">
+        <v>1.17</v>
+      </c>
+      <c r="S9">
+        <v>5.9</v>
+      </c>
+      <c r="T9">
+        <v>2.16</v>
+      </c>
+      <c r="U9">
+        <v>1.6</v>
+      </c>
+      <c r="V9">
+        <v>1.64</v>
+      </c>
+      <c r="W9">
+        <v>1.3</v>
+      </c>
+      <c r="X9">
+        <v>9.6</v>
+      </c>
+      <c r="Y9">
+        <v>8.6</v>
+      </c>
+      <c r="Z9">
+        <v>17</v>
+      </c>
+      <c r="AA9">
+        <v>46</v>
+      </c>
+      <c r="AB9">
+        <v>12</v>
+      </c>
+      <c r="AC9">
+        <v>8.6</v>
+      </c>
+      <c r="AD9">
+        <v>15.5</v>
+      </c>
+      <c r="AE9">
+        <v>46</v>
+      </c>
+      <c r="AF9">
+        <v>32</v>
+      </c>
+      <c r="AG9">
+        <v>21</v>
+      </c>
+      <c r="AH9">
+        <v>30</v>
+      </c>
+      <c r="AI9">
+        <v>85</v>
+      </c>
+      <c r="AJ9">
+        <v>110</v>
+      </c>
+      <c r="AK9">
+        <v>85</v>
+      </c>
+      <c r="AL9">
+        <v>120</v>
+      </c>
+      <c r="AM9">
+        <v>260</v>
+      </c>
+      <c r="AN9">
+        <v>130</v>
+      </c>
+      <c r="AO9">
+        <v>50</v>
+      </c>
+      <c r="AP9">
+        <v>6</v>
+      </c>
+      <c r="AQ9">
+        <v>5.3</v>
+      </c>
+      <c r="AR9">
+        <v>10</v>
+      </c>
+      <c r="AS9">
+        <v>3.95</v>
+      </c>
+      <c r="AT9">
+        <v>7.4</v>
+      </c>
+      <c r="AU9">
+        <v>5.4</v>
+      </c>
+      <c r="AV9">
+        <v>10</v>
+      </c>
+      <c r="AW9">
+        <v>3.95</v>
+      </c>
+      <c r="AX9">
+        <v>18.5</v>
+      </c>
+      <c r="AY9">
+        <v>12.5</v>
+      </c>
+      <c r="AZ9">
+        <v>18</v>
+      </c>
+      <c r="BA9">
+        <v>4.1</v>
+      </c>
+      <c r="BB9">
+        <v>4.2</v>
+      </c>
+      <c r="BC9">
+        <v>4.1</v>
+      </c>
+      <c r="BD9">
+        <v>4.2</v>
+      </c>
+      <c r="BE9">
         <v>4.3</v>
       </c>
-      <c r="I9">
-        <v>4.5</v>
-      </c>
-      <c r="J9">
-        <v>3.5</v>
-      </c>
-      <c r="K9">
-        <v>3.55</v>
-      </c>
-      <c r="L9">
-        <v>1.5</v>
-      </c>
-      <c r="M9">
-        <v>1.09</v>
-      </c>
-      <c r="N9">
-        <v>3.2</v>
-      </c>
-      <c r="O9">
-        <v>1.43</v>
-      </c>
-      <c r="P9">
-        <v>1.73</v>
-      </c>
-      <c r="Q9">
-        <v>2.3</v>
-      </c>
-      <c r="R9">
-        <v>1.27</v>
-      </c>
-      <c r="S9">
-        <v>4.5</v>
-      </c>
-      <c r="T9">
-        <v>2.04</v>
-      </c>
-      <c r="U9">
-        <v>1.91</v>
-      </c>
-      <c r="V9">
-        <v>1.29</v>
-      </c>
-      <c r="W9">
-        <v>1.94</v>
-      </c>
-      <c r="X9">
-        <v>11</v>
-      </c>
-      <c r="Y9">
-        <v>13</v>
-      </c>
-      <c r="Z9">
-        <v>32</v>
-      </c>
-      <c r="AA9">
-        <v>110</v>
-      </c>
-      <c r="AB9">
-        <v>7.8</v>
-      </c>
-      <c r="AC9">
-        <v>7.8</v>
-      </c>
-      <c r="AD9">
-        <v>18</v>
-      </c>
-      <c r="AE9">
-        <v>65</v>
-      </c>
-      <c r="AF9">
-        <v>11.5</v>
-      </c>
-      <c r="AG9">
-        <v>11</v>
-      </c>
-      <c r="AH9">
-        <v>22</v>
-      </c>
-      <c r="AI9">
-        <v>80</v>
-      </c>
-      <c r="AJ9">
-        <v>24</v>
-      </c>
-      <c r="AK9">
-        <v>24</v>
-      </c>
-      <c r="AL9">
-        <v>46</v>
-      </c>
-      <c r="AM9">
-        <v>170</v>
-      </c>
-      <c r="AN9">
-        <v>19</v>
-      </c>
-      <c r="AO9">
-        <v>80</v>
-      </c>
-      <c r="AP9">
-        <v>10</v>
-      </c>
-      <c r="AQ9">
-        <v>12</v>
-      </c>
-      <c r="AR9">
-        <v>28</v>
-      </c>
-      <c r="AS9">
-        <v>38</v>
-      </c>
-      <c r="AT9">
-        <v>7.2</v>
-      </c>
-      <c r="AU9">
-        <v>7.4</v>
-      </c>
-      <c r="AV9">
-        <v>16.5</v>
-      </c>
-      <c r="AW9">
-        <v>55</v>
-      </c>
-      <c r="AX9">
-        <v>10.5</v>
-      </c>
-      <c r="AY9">
-        <v>10</v>
-      </c>
-      <c r="AZ9">
-        <v>19.5</v>
-      </c>
-      <c r="BA9">
-        <v>65</v>
-      </c>
-      <c r="BB9">
-        <v>22</v>
-      </c>
-      <c r="BC9">
-        <v>21</v>
-      </c>
-      <c r="BD9">
-        <v>42</v>
-      </c>
-      <c r="BE9">
-        <v>44</v>
-      </c>
       <c r="BF9">
-        <v>17.5</v>
+        <v>4.2</v>
       </c>
       <c r="BG9">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="BH9">
         <v>2.96</v>
       </c>
       <c r="BI9">
-        <v>2.8</v>
+        <v>2.16</v>
       </c>
       <c r="BJ9">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BK9">
-        <v>6.2</v>
+        <v>3.75</v>
       </c>
       <c r="BL9">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="BM9">
-        <v>10.5</v>
+        <v>5.1</v>
       </c>
       <c r="BN9">
-        <v>4.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO9">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="BP9">
-        <v>17.5</v>
+        <v>48</v>
       </c>
       <c r="BQ9">
-        <v>11.5</v>
+        <v>4.7</v>
       </c>
       <c r="BR9">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>8.4</v>
+        <v>4.8</v>
       </c>
       <c r="BT9">
-        <v>8.800000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="BU9">
-        <v>7</v>
+        <v>3.85</v>
       </c>
       <c r="BV9">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="BW9">
-        <v>9</v>
+        <v>4.3</v>
       </c>
       <c r="BX9">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BY9">
-        <v>9.6</v>
+        <v>4.7</v>
       </c>
       <c r="BZ9">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>8.4</v>
+        <v>4.8</v>
       </c>
       <c r="CB9" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
         <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F10">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="G10">
-        <v>1.76</v>
+        <v>2.14</v>
       </c>
       <c r="H10">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="I10">
-        <v>5.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J10">
-        <v>4.2</v>
+        <v>2.92</v>
       </c>
       <c r="K10">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="L10">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N10">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="O10">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="P10">
-        <v>2.14</v>
+        <v>1.47</v>
       </c>
       <c r="Q10">
-        <v>1.49</v>
+        <v>2.1</v>
       </c>
       <c r="R10">
-        <v>1.46</v>
+        <v>1.13</v>
       </c>
       <c r="S10">
-        <v>2.22</v>
+        <v>2.46</v>
       </c>
       <c r="T10">
         <v>1.11</v>
@@ -2969,10 +2987,10 @@
         <v>1.11</v>
       </c>
       <c r="V10">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="W10">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3143,550 +3161,550 @@
         <v>1.04</v>
       </c>
       <c r="CB10" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
         <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E11" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F11">
-        <v>1.08</v>
+        <v>2.04</v>
       </c>
       <c r="G11">
-        <v>990</v>
+        <v>2.06</v>
       </c>
       <c r="H11">
-        <v>1.08</v>
+        <v>4.3</v>
       </c>
       <c r="I11">
-        <v>990</v>
+        <v>4.5</v>
       </c>
       <c r="J11">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="K11">
-        <v>950</v>
+        <v>3.55</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M11">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N11">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="O11">
-        <v>1.08</v>
+        <v>1.43</v>
       </c>
       <c r="P11">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="Q11">
-        <v>1.07</v>
+        <v>2.3</v>
       </c>
       <c r="R11">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="S11">
-        <v>1.08</v>
+        <v>4.5</v>
       </c>
       <c r="T11">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="U11">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="V11">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="W11">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="X11">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y11">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z11">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA11">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB11">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC11">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD11">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE11">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF11">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG11">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH11">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ11">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK11">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL11">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AO11">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP11">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ11">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR11">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="AS11">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AT11">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU11">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV11">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AW11">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="AX11">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY11">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ11">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BA11">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BB11">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BC11">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD11">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BE11">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BF11">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BG11">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="BI11">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="BJ11">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK11">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL11">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="BM11">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO11">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ11">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS11">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU11">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW11">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY11">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BZ11">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="CA11">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="CB11" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D12" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E12" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F12">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="G12">
-        <v>1.35</v>
+        <v>1.71</v>
       </c>
       <c r="H12">
+        <v>4.9</v>
+      </c>
+      <c r="I12">
+        <v>6</v>
+      </c>
+      <c r="J12">
+        <v>4.3</v>
+      </c>
+      <c r="K12">
+        <v>5</v>
+      </c>
+      <c r="L12">
+        <v>1.01</v>
+      </c>
+      <c r="M12">
+        <v>1.03</v>
+      </c>
+      <c r="N12">
+        <v>5.2</v>
+      </c>
+      <c r="O12">
+        <v>1.19</v>
+      </c>
+      <c r="P12">
+        <v>2.46</v>
+      </c>
+      <c r="Q12">
+        <v>1.58</v>
+      </c>
+      <c r="R12">
+        <v>1.57</v>
+      </c>
+      <c r="S12">
+        <v>2.46</v>
+      </c>
+      <c r="T12">
+        <v>1.56</v>
+      </c>
+      <c r="U12">
+        <v>2.04</v>
+      </c>
+      <c r="V12">
+        <v>1.01</v>
+      </c>
+      <c r="W12">
+        <v>1.01</v>
+      </c>
+      <c r="X12">
+        <v>30</v>
+      </c>
+      <c r="Y12">
+        <v>30</v>
+      </c>
+      <c r="Z12">
+        <v>60</v>
+      </c>
+      <c r="AA12">
+        <v>150</v>
+      </c>
+      <c r="AB12">
+        <v>14</v>
+      </c>
+      <c r="AC12">
+        <v>13</v>
+      </c>
+      <c r="AD12">
+        <v>26</v>
+      </c>
+      <c r="AE12">
+        <v>75</v>
+      </c>
+      <c r="AF12">
+        <v>14.5</v>
+      </c>
+      <c r="AG12">
+        <v>12.5</v>
+      </c>
+      <c r="AH12">
+        <v>23</v>
+      </c>
+      <c r="AI12">
+        <v>70</v>
+      </c>
+      <c r="AJ12">
+        <v>21</v>
+      </c>
+      <c r="AK12">
+        <v>19</v>
+      </c>
+      <c r="AL12">
+        <v>34</v>
+      </c>
+      <c r="AM12">
+        <v>95</v>
+      </c>
+      <c r="AN12">
+        <v>8.4</v>
+      </c>
+      <c r="AO12">
+        <v>70</v>
+      </c>
+      <c r="AP12">
+        <v>17.5</v>
+      </c>
+      <c r="AQ12">
+        <v>3.8</v>
+      </c>
+      <c r="AR12">
+        <v>4</v>
+      </c>
+      <c r="AS12">
+        <v>4.2</v>
+      </c>
+      <c r="AT12">
         <v>10</v>
       </c>
-      <c r="I12">
-        <v>10.5</v>
-      </c>
-      <c r="J12">
-        <v>6.2</v>
-      </c>
-      <c r="K12">
-        <v>6.6</v>
-      </c>
-      <c r="L12">
-        <v>1.26</v>
-      </c>
-      <c r="M12">
-        <v>1.03</v>
-      </c>
-      <c r="N12">
-        <v>6.8</v>
-      </c>
-      <c r="O12">
-        <v>1.16</v>
-      </c>
-      <c r="P12">
-        <v>2.98</v>
-      </c>
-      <c r="Q12">
-        <v>1.49</v>
-      </c>
-      <c r="R12">
-        <v>1.77</v>
-      </c>
-      <c r="S12">
-        <v>2.22</v>
-      </c>
-      <c r="T12">
-        <v>1.84</v>
-      </c>
-      <c r="U12">
-        <v>2.14</v>
-      </c>
-      <c r="V12">
-        <v>1.1</v>
-      </c>
-      <c r="W12">
+      <c r="AU12">
+        <v>8</v>
+      </c>
+      <c r="AV12">
+        <v>3.7</v>
+      </c>
+      <c r="AW12">
+        <v>4.1</v>
+      </c>
+      <c r="AX12">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY12">
+        <v>7.6</v>
+      </c>
+      <c r="AZ12">
+        <v>3.65</v>
+      </c>
+      <c r="BA12">
+        <v>4.1</v>
+      </c>
+      <c r="BB12">
+        <v>12</v>
+      </c>
+      <c r="BC12">
+        <v>11.5</v>
+      </c>
+      <c r="BD12">
         <v>3.85</v>
       </c>
-      <c r="X12">
-        <v>32</v>
-      </c>
-      <c r="Y12">
-        <v>44</v>
-      </c>
-      <c r="Z12">
-        <v>95</v>
-      </c>
-      <c r="AA12">
-        <v>370</v>
-      </c>
-      <c r="AB12">
-        <v>12</v>
-      </c>
-      <c r="AC12">
-        <v>14.5</v>
-      </c>
-      <c r="AD12">
-        <v>38</v>
-      </c>
-      <c r="AE12">
-        <v>120</v>
-      </c>
-      <c r="AF12">
-        <v>9.6</v>
-      </c>
-      <c r="AG12">
-        <v>10.5</v>
-      </c>
-      <c r="AH12">
-        <v>25</v>
-      </c>
-      <c r="AI12">
-        <v>120</v>
-      </c>
-      <c r="AJ12">
-        <v>11.5</v>
-      </c>
-      <c r="AK12">
-        <v>12.5</v>
-      </c>
-      <c r="AL12">
-        <v>28</v>
-      </c>
-      <c r="AM12">
-        <v>110</v>
-      </c>
-      <c r="AN12">
-        <v>4.2</v>
-      </c>
-      <c r="AO12">
-        <v>120</v>
-      </c>
-      <c r="AP12">
-        <v>28</v>
-      </c>
-      <c r="AQ12">
-        <v>38</v>
-      </c>
-      <c r="AR12">
-        <v>48</v>
-      </c>
-      <c r="AS12">
-        <v>60</v>
-      </c>
-      <c r="AT12">
-        <v>11.5</v>
-      </c>
-      <c r="AU12">
-        <v>13.5</v>
-      </c>
-      <c r="AV12">
-        <v>34</v>
-      </c>
-      <c r="AW12">
-        <v>40</v>
-      </c>
-      <c r="AX12">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY12">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ12">
-        <v>24</v>
-      </c>
-      <c r="BA12">
-        <v>85</v>
-      </c>
-      <c r="BB12">
-        <v>10.5</v>
-      </c>
-      <c r="BC12">
-        <v>12</v>
-      </c>
-      <c r="BD12">
-        <v>26</v>
-      </c>
       <c r="BE12">
-        <v>65</v>
+        <v>4.1</v>
       </c>
       <c r="BF12">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BG12">
-        <v>46</v>
+        <v>4.1</v>
       </c>
       <c r="BH12">
         <v>1000</v>
       </c>
       <c r="BI12">
-        <v>2.38</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>2.18</v>
+        <v>1.04</v>
       </c>
       <c r="BN12">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="BP12">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR12">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT12">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>2.14</v>
+        <v>1.04</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>2.12</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E13" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F13">
-        <v>1.48</v>
+        <v>1.08</v>
       </c>
       <c r="G13">
-        <v>1.68</v>
+        <v>990</v>
       </c>
       <c r="H13">
-        <v>3.35</v>
+        <v>1.08</v>
       </c>
       <c r="I13">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="J13">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="K13">
         <v>950</v>
       </c>
       <c r="L13">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M13">
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>2.46</v>
+        <v>1.26</v>
       </c>
       <c r="O13">
-        <v>1.44</v>
+        <v>1.08</v>
       </c>
       <c r="P13">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="Q13">
-        <v>2.3</v>
+        <v>1.08</v>
       </c>
       <c r="R13">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="S13">
-        <v>2.74</v>
+        <v>1.09</v>
       </c>
       <c r="T13">
         <v>1.11</v>
@@ -3695,10 +3713,10 @@
         <v>1.11</v>
       </c>
       <c r="V13">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W13">
-        <v>2.46</v>
+        <v>1.03</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -3863,255 +3881,739 @@
         <v>1.04</v>
       </c>
       <c r="BZ13">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA13">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C14" t="s">
         <v>98</v>
       </c>
       <c r="D14" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E14" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F14">
+        <v>1.34</v>
+      </c>
+      <c r="G14">
+        <v>1.35</v>
+      </c>
+      <c r="H14">
+        <v>10</v>
+      </c>
+      <c r="I14">
+        <v>10.5</v>
+      </c>
+      <c r="J14">
+        <v>6.2</v>
+      </c>
+      <c r="K14">
+        <v>6.4</v>
+      </c>
+      <c r="L14">
+        <v>1.26</v>
+      </c>
+      <c r="M14">
+        <v>1.03</v>
+      </c>
+      <c r="N14">
+        <v>6.8</v>
+      </c>
+      <c r="O14">
+        <v>1.16</v>
+      </c>
+      <c r="P14">
+        <v>2.98</v>
+      </c>
+      <c r="Q14">
+        <v>1.49</v>
+      </c>
+      <c r="R14">
+        <v>1.77</v>
+      </c>
+      <c r="S14">
+        <v>2.22</v>
+      </c>
+      <c r="T14">
+        <v>1.84</v>
+      </c>
+      <c r="U14">
+        <v>2.14</v>
+      </c>
+      <c r="V14">
+        <v>1.1</v>
+      </c>
+      <c r="W14">
+        <v>3.85</v>
+      </c>
+      <c r="X14">
+        <v>30</v>
+      </c>
+      <c r="Y14">
+        <v>44</v>
+      </c>
+      <c r="Z14">
+        <v>95</v>
+      </c>
+      <c r="AA14">
+        <v>370</v>
+      </c>
+      <c r="AB14">
+        <v>12</v>
+      </c>
+      <c r="AC14">
+        <v>14.5</v>
+      </c>
+      <c r="AD14">
+        <v>38</v>
+      </c>
+      <c r="AE14">
+        <v>120</v>
+      </c>
+      <c r="AF14">
+        <v>9.6</v>
+      </c>
+      <c r="AG14">
+        <v>10.5</v>
+      </c>
+      <c r="AH14">
+        <v>25</v>
+      </c>
+      <c r="AI14">
+        <v>120</v>
+      </c>
+      <c r="AJ14">
+        <v>11.5</v>
+      </c>
+      <c r="AK14">
+        <v>12.5</v>
+      </c>
+      <c r="AL14">
+        <v>28</v>
+      </c>
+      <c r="AM14">
+        <v>110</v>
+      </c>
+      <c r="AN14">
+        <v>4.2</v>
+      </c>
+      <c r="AO14">
+        <v>140</v>
+      </c>
+      <c r="AP14">
+        <v>28</v>
+      </c>
+      <c r="AQ14">
+        <v>38</v>
+      </c>
+      <c r="AR14">
+        <v>48</v>
+      </c>
+      <c r="AS14">
+        <v>60</v>
+      </c>
+      <c r="AT14">
+        <v>11.5</v>
+      </c>
+      <c r="AU14">
+        <v>13.5</v>
+      </c>
+      <c r="AV14">
+        <v>34</v>
+      </c>
+      <c r="AW14">
+        <v>40</v>
+      </c>
+      <c r="AX14">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY14">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ14">
+        <v>24</v>
+      </c>
+      <c r="BA14">
+        <v>85</v>
+      </c>
+      <c r="BB14">
+        <v>10.5</v>
+      </c>
+      <c r="BC14">
+        <v>12</v>
+      </c>
+      <c r="BD14">
+        <v>26</v>
+      </c>
+      <c r="BE14">
+        <v>90</v>
+      </c>
+      <c r="BF14">
+        <v>4</v>
+      </c>
+      <c r="BG14">
+        <v>46</v>
+      </c>
+      <c r="BH14">
+        <v>1000</v>
+      </c>
+      <c r="BI14">
+        <v>2.36</v>
+      </c>
+      <c r="BJ14">
+        <v>15</v>
+      </c>
+      <c r="BK14">
+        <v>3.15</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>2.2</v>
+      </c>
+      <c r="BN14">
+        <v>5.2</v>
+      </c>
+      <c r="BO14">
+        <v>3</v>
+      </c>
+      <c r="BP14">
+        <v>10.5</v>
+      </c>
+      <c r="BQ14">
+        <v>5.5</v>
+      </c>
+      <c r="BR14">
+        <v>28</v>
+      </c>
+      <c r="BS14">
+        <v>3.45</v>
+      </c>
+      <c r="BT14">
+        <v>17.5</v>
+      </c>
+      <c r="BU14">
+        <v>3.2</v>
+      </c>
+      <c r="BV14">
+        <v>1000</v>
+      </c>
+      <c r="BW14">
+        <v>2.16</v>
+      </c>
+      <c r="BX14">
+        <v>1000</v>
+      </c>
+      <c r="BY14">
+        <v>2.14</v>
+      </c>
+      <c r="BZ14">
+        <v>14</v>
+      </c>
+      <c r="CA14">
+        <v>6.2</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" t="s">
+        <v>99</v>
+      </c>
+      <c r="D15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F15">
+        <v>1.48</v>
+      </c>
+      <c r="G15">
+        <v>1.67</v>
+      </c>
+      <c r="H15">
+        <v>7</v>
+      </c>
+      <c r="I15">
+        <v>16</v>
+      </c>
+      <c r="J15">
+        <v>3.55</v>
+      </c>
+      <c r="K15">
+        <v>5.5</v>
+      </c>
+      <c r="L15">
+        <v>1.42</v>
+      </c>
+      <c r="M15">
+        <v>1.01</v>
+      </c>
+      <c r="N15">
+        <v>2.46</v>
+      </c>
+      <c r="O15">
+        <v>1.44</v>
+      </c>
+      <c r="P15">
+        <v>1.52</v>
+      </c>
+      <c r="Q15">
+        <v>2.3</v>
+      </c>
+      <c r="R15">
+        <v>1.12</v>
+      </c>
+      <c r="S15">
+        <v>2.74</v>
+      </c>
+      <c r="T15">
+        <v>1.11</v>
+      </c>
+      <c r="U15">
+        <v>1.11</v>
+      </c>
+      <c r="V15">
+        <v>1.06</v>
+      </c>
+      <c r="W15">
+        <v>2.5</v>
+      </c>
+      <c r="X15">
+        <v>1000</v>
+      </c>
+      <c r="Y15">
+        <v>1000</v>
+      </c>
+      <c r="Z15">
+        <v>1000</v>
+      </c>
+      <c r="AA15">
+        <v>1000</v>
+      </c>
+      <c r="AB15">
+        <v>1000</v>
+      </c>
+      <c r="AC15">
+        <v>1000</v>
+      </c>
+      <c r="AD15">
+        <v>1000</v>
+      </c>
+      <c r="AE15">
+        <v>1000</v>
+      </c>
+      <c r="AF15">
+        <v>1000</v>
+      </c>
+      <c r="AG15">
+        <v>1000</v>
+      </c>
+      <c r="AH15">
+        <v>1000</v>
+      </c>
+      <c r="AI15">
+        <v>1000</v>
+      </c>
+      <c r="AJ15">
+        <v>1000</v>
+      </c>
+      <c r="AK15">
+        <v>1000</v>
+      </c>
+      <c r="AL15">
+        <v>1000</v>
+      </c>
+      <c r="AM15">
+        <v>1000</v>
+      </c>
+      <c r="AN15">
+        <v>1000</v>
+      </c>
+      <c r="AO15">
+        <v>1000</v>
+      </c>
+      <c r="AP15">
+        <v>1.01</v>
+      </c>
+      <c r="AQ15">
+        <v>1.01</v>
+      </c>
+      <c r="AR15">
+        <v>1.01</v>
+      </c>
+      <c r="AS15">
+        <v>1.01</v>
+      </c>
+      <c r="AT15">
+        <v>1.01</v>
+      </c>
+      <c r="AU15">
+        <v>1.01</v>
+      </c>
+      <c r="AV15">
+        <v>1.01</v>
+      </c>
+      <c r="AW15">
+        <v>1.01</v>
+      </c>
+      <c r="AX15">
+        <v>1.01</v>
+      </c>
+      <c r="AY15">
+        <v>1.01</v>
+      </c>
+      <c r="AZ15">
+        <v>1.01</v>
+      </c>
+      <c r="BA15">
+        <v>1.01</v>
+      </c>
+      <c r="BB15">
+        <v>1.01</v>
+      </c>
+      <c r="BC15">
+        <v>1.01</v>
+      </c>
+      <c r="BD15">
+        <v>1.01</v>
+      </c>
+      <c r="BE15">
+        <v>1.01</v>
+      </c>
+      <c r="BF15">
+        <v>1.01</v>
+      </c>
+      <c r="BG15">
+        <v>1.01</v>
+      </c>
+      <c r="BH15">
+        <v>1000</v>
+      </c>
+      <c r="BI15">
+        <v>1.04</v>
+      </c>
+      <c r="BJ15">
+        <v>1000</v>
+      </c>
+      <c r="BK15">
+        <v>1.04</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>1.04</v>
+      </c>
+      <c r="BN15">
+        <v>1000</v>
+      </c>
+      <c r="BO15">
+        <v>1.04</v>
+      </c>
+      <c r="BP15">
+        <v>1000</v>
+      </c>
+      <c r="BQ15">
+        <v>1.04</v>
+      </c>
+      <c r="BR15">
+        <v>1000</v>
+      </c>
+      <c r="BS15">
+        <v>1.04</v>
+      </c>
+      <c r="BT15">
+        <v>1000</v>
+      </c>
+      <c r="BU15">
+        <v>1.04</v>
+      </c>
+      <c r="BV15">
+        <v>1000</v>
+      </c>
+      <c r="BW15">
+        <v>1.04</v>
+      </c>
+      <c r="BX15">
+        <v>1000</v>
+      </c>
+      <c r="BY15">
+        <v>1.04</v>
+      </c>
+      <c r="BZ15">
+        <v>1000</v>
+      </c>
+      <c r="CA15">
+        <v>1.04</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" t="s">
+        <v>100</v>
+      </c>
+      <c r="D16" t="s">
+        <v>115</v>
+      </c>
+      <c r="E16" t="s">
+        <v>130</v>
+      </c>
+      <c r="F16">
         <v>3.75</v>
       </c>
-      <c r="G14">
+      <c r="G16">
         <v>4.7</v>
       </c>
-      <c r="H14">
+      <c r="H16">
         <v>2.12</v>
       </c>
-      <c r="I14">
+      <c r="I16">
         <v>2.44</v>
       </c>
-      <c r="J14">
+      <c r="J16">
         <v>2.98</v>
       </c>
-      <c r="K14">
+      <c r="K16">
         <v>3.4</v>
       </c>
-      <c r="L14">
-        <v>1.01</v>
-      </c>
-      <c r="M14">
+      <c r="L16">
+        <v>1.01</v>
+      </c>
+      <c r="M16">
         <v>1.1</v>
       </c>
-      <c r="N14">
+      <c r="N16">
         <v>2.86</v>
       </c>
-      <c r="O14">
+      <c r="O16">
         <v>1.43</v>
       </c>
-      <c r="P14">
+      <c r="P16">
         <v>1.6</v>
       </c>
-      <c r="Q14">
+      <c r="Q16">
         <v>2.2</v>
       </c>
-      <c r="R14">
+      <c r="R16">
         <v>1.21</v>
       </c>
-      <c r="S14">
+      <c r="S16">
         <v>4.1</v>
       </c>
-      <c r="T14">
+      <c r="T16">
         <v>1.11</v>
       </c>
-      <c r="U14">
+      <c r="U16">
         <v>1.11</v>
       </c>
-      <c r="V14">
-        <v>1.7</v>
-      </c>
-      <c r="W14">
-        <v>1.27</v>
-      </c>
-      <c r="X14">
-        <v>1000</v>
-      </c>
-      <c r="Y14">
-        <v>1000</v>
-      </c>
-      <c r="Z14">
-        <v>1000</v>
-      </c>
-      <c r="AA14">
-        <v>1000</v>
-      </c>
-      <c r="AB14">
-        <v>1000</v>
-      </c>
-      <c r="AC14">
-        <v>1000</v>
-      </c>
-      <c r="AD14">
-        <v>1000</v>
-      </c>
-      <c r="AE14">
-        <v>1000</v>
-      </c>
-      <c r="AF14">
-        <v>1000</v>
-      </c>
-      <c r="AG14">
-        <v>1000</v>
-      </c>
-      <c r="AH14">
-        <v>1000</v>
-      </c>
-      <c r="AI14">
-        <v>1000</v>
-      </c>
-      <c r="AJ14">
-        <v>1000</v>
-      </c>
-      <c r="AK14">
-        <v>1000</v>
-      </c>
-      <c r="AL14">
-        <v>1000</v>
-      </c>
-      <c r="AM14">
-        <v>1000</v>
-      </c>
-      <c r="AN14">
-        <v>1000</v>
-      </c>
-      <c r="AO14">
-        <v>1000</v>
-      </c>
-      <c r="AP14">
-        <v>1.01</v>
-      </c>
-      <c r="AQ14">
-        <v>1.01</v>
-      </c>
-      <c r="AR14">
-        <v>1.01</v>
-      </c>
-      <c r="AS14">
-        <v>1.01</v>
-      </c>
-      <c r="AT14">
-        <v>1.01</v>
-      </c>
-      <c r="AU14">
-        <v>1.01</v>
-      </c>
-      <c r="AV14">
-        <v>1.01</v>
-      </c>
-      <c r="AW14">
-        <v>1.01</v>
-      </c>
-      <c r="AX14">
-        <v>1.01</v>
-      </c>
-      <c r="AY14">
-        <v>1.01</v>
-      </c>
-      <c r="AZ14">
-        <v>1.01</v>
-      </c>
-      <c r="BA14">
-        <v>1.01</v>
-      </c>
-      <c r="BB14">
-        <v>1.01</v>
-      </c>
-      <c r="BC14">
-        <v>1.01</v>
-      </c>
-      <c r="BD14">
-        <v>1.01</v>
-      </c>
-      <c r="BE14">
-        <v>1.01</v>
-      </c>
-      <c r="BF14">
-        <v>1.01</v>
-      </c>
-      <c r="BG14">
-        <v>1.01</v>
-      </c>
-      <c r="BH14">
-        <v>1000</v>
-      </c>
-      <c r="BI14">
-        <v>1.04</v>
-      </c>
-      <c r="BJ14">
-        <v>1000</v>
-      </c>
-      <c r="BK14">
-        <v>1.04</v>
-      </c>
-      <c r="BL14">
-        <v>1000</v>
-      </c>
-      <c r="BM14">
-        <v>1.04</v>
-      </c>
-      <c r="BN14">
-        <v>1000</v>
-      </c>
-      <c r="BO14">
-        <v>1.04</v>
-      </c>
-      <c r="BP14">
-        <v>1000</v>
-      </c>
-      <c r="BQ14">
-        <v>1.04</v>
-      </c>
-      <c r="BR14">
-        <v>1000</v>
-      </c>
-      <c r="BS14">
-        <v>1.04</v>
-      </c>
-      <c r="BT14">
-        <v>1000</v>
-      </c>
-      <c r="BU14">
-        <v>1.04</v>
-      </c>
-      <c r="BV14">
-        <v>1000</v>
-      </c>
-      <c r="BW14">
-        <v>1.04</v>
-      </c>
-      <c r="BX14">
-        <v>1000</v>
-      </c>
-      <c r="BY14">
-        <v>1.04</v>
-      </c>
-      <c r="BZ14">
-        <v>1000</v>
-      </c>
-      <c r="CA14">
-        <v>1.04</v>
-      </c>
-      <c r="CB14" t="s">
-        <v>125</v>
+      <c r="V16">
+        <v>1.72</v>
+      </c>
+      <c r="W16">
+        <v>1.28</v>
+      </c>
+      <c r="X16">
+        <v>1000</v>
+      </c>
+      <c r="Y16">
+        <v>1000</v>
+      </c>
+      <c r="Z16">
+        <v>1000</v>
+      </c>
+      <c r="AA16">
+        <v>1000</v>
+      </c>
+      <c r="AB16">
+        <v>1000</v>
+      </c>
+      <c r="AC16">
+        <v>1000</v>
+      </c>
+      <c r="AD16">
+        <v>1000</v>
+      </c>
+      <c r="AE16">
+        <v>1000</v>
+      </c>
+      <c r="AF16">
+        <v>1000</v>
+      </c>
+      <c r="AG16">
+        <v>1000</v>
+      </c>
+      <c r="AH16">
+        <v>1000</v>
+      </c>
+      <c r="AI16">
+        <v>1000</v>
+      </c>
+      <c r="AJ16">
+        <v>1000</v>
+      </c>
+      <c r="AK16">
+        <v>1000</v>
+      </c>
+      <c r="AL16">
+        <v>1000</v>
+      </c>
+      <c r="AM16">
+        <v>1000</v>
+      </c>
+      <c r="AN16">
+        <v>1000</v>
+      </c>
+      <c r="AO16">
+        <v>1000</v>
+      </c>
+      <c r="AP16">
+        <v>1.01</v>
+      </c>
+      <c r="AQ16">
+        <v>1.01</v>
+      </c>
+      <c r="AR16">
+        <v>1.01</v>
+      </c>
+      <c r="AS16">
+        <v>1.01</v>
+      </c>
+      <c r="AT16">
+        <v>1.01</v>
+      </c>
+      <c r="AU16">
+        <v>1.01</v>
+      </c>
+      <c r="AV16">
+        <v>1.01</v>
+      </c>
+      <c r="AW16">
+        <v>1.01</v>
+      </c>
+      <c r="AX16">
+        <v>1.01</v>
+      </c>
+      <c r="AY16">
+        <v>1.01</v>
+      </c>
+      <c r="AZ16">
+        <v>1.01</v>
+      </c>
+      <c r="BA16">
+        <v>1.01</v>
+      </c>
+      <c r="BB16">
+        <v>1.01</v>
+      </c>
+      <c r="BC16">
+        <v>1.01</v>
+      </c>
+      <c r="BD16">
+        <v>1.01</v>
+      </c>
+      <c r="BE16">
+        <v>1.01</v>
+      </c>
+      <c r="BF16">
+        <v>1.01</v>
+      </c>
+      <c r="BG16">
+        <v>1.01</v>
+      </c>
+      <c r="BH16">
+        <v>1000</v>
+      </c>
+      <c r="BI16">
+        <v>1.04</v>
+      </c>
+      <c r="BJ16">
+        <v>1000</v>
+      </c>
+      <c r="BK16">
+        <v>1.04</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>1.04</v>
+      </c>
+      <c r="BN16">
+        <v>1000</v>
+      </c>
+      <c r="BO16">
+        <v>1.04</v>
+      </c>
+      <c r="BP16">
+        <v>1000</v>
+      </c>
+      <c r="BQ16">
+        <v>1.04</v>
+      </c>
+      <c r="BR16">
+        <v>1000</v>
+      </c>
+      <c r="BS16">
+        <v>1.04</v>
+      </c>
+      <c r="BT16">
+        <v>1000</v>
+      </c>
+      <c r="BU16">
+        <v>1.04</v>
+      </c>
+      <c r="BV16">
+        <v>1000</v>
+      </c>
+      <c r="BW16">
+        <v>1.04</v>
+      </c>
+      <c r="BX16">
+        <v>1000</v>
+      </c>
+      <c r="BY16">
+        <v>1.04</v>
+      </c>
+      <c r="BZ16">
+        <v>1000</v>
+      </c>
+      <c r="CA16">
+        <v>1.04</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
@@ -409,7 +409,7 @@
     <t>Millonarios</t>
   </si>
   <si>
-    <t>2026-08-26 02:18:24</t>
+    <t>2026-08-26 03:53:56</t>
   </si>
 </sst>
 </file>
@@ -1006,13 +1006,13 @@
         <v>1.64</v>
       </c>
       <c r="G2">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J2">
         <v>3.9</v>
@@ -1030,7 +1030,7 @@
         <v>3.55</v>
       </c>
       <c r="O2">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P2">
         <v>1.86</v>
@@ -1054,7 +1054,7 @@
         <v>1.17</v>
       </c>
       <c r="W2">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="X2">
         <v>15</v>
@@ -1066,7 +1066,7 @@
         <v>60</v>
       </c>
       <c r="AA2">
-        <v>230</v>
+        <v>280</v>
       </c>
       <c r="AB2">
         <v>7.6</v>
@@ -1093,7 +1093,7 @@
         <v>120</v>
       </c>
       <c r="AJ2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK2">
         <v>22</v>
@@ -1147,7 +1147,7 @@
         <v>7.6</v>
       </c>
       <c r="BB2">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BC2">
         <v>16</v>
@@ -1156,73 +1156,73 @@
         <v>6.8</v>
       </c>
       <c r="BE2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF2">
         <v>9.199999999999999</v>
       </c>
       <c r="BG2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI2">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK2">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BO2">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ2">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS2">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU2">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BY2">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA2">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="CB2" t="s">
         <v>131</v>
@@ -1290,7 +1290,7 @@
         <v>2.16</v>
       </c>
       <c r="U3">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="V3">
         <v>1.22</v>
@@ -1487,7 +1487,7 @@
         <v>118</v>
       </c>
       <c r="F4">
-        <v>2.48</v>
+        <v>2.22</v>
       </c>
       <c r="G4">
         <v>3.35</v>
@@ -1502,7 +1502,7 @@
         <v>3.25</v>
       </c>
       <c r="K4">
-        <v>5.8</v>
+        <v>8.6</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1511,13 +1511,13 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="O4">
         <v>1.17</v>
       </c>
       <c r="P4">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="Q4">
         <v>1.58</v>
@@ -1526,7 +1526,7 @@
         <v>1.51</v>
       </c>
       <c r="S4">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="T4">
         <v>1.01</v>
@@ -1535,7 +1535,7 @@
         <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W4">
         <v>1.43</v>
@@ -1729,163 +1729,163 @@
         <v>119</v>
       </c>
       <c r="F5">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="G5">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="H5">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="I5">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="J5">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="L5">
         <v>1.31</v>
       </c>
       <c r="M5">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N5">
-        <v>2.94</v>
+        <v>3.7</v>
       </c>
       <c r="O5">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="P5">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="Q5">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="R5">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="S5">
-        <v>2.56</v>
+        <v>3.25</v>
       </c>
       <c r="T5">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="U5">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="V5">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="W5">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y5">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z5">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AB5">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC5">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD5">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AE5">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF5">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG5">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH5">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ5">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AK5">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL5">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN5">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP5">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AQ5">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AR5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT5">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AU5">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AV5">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AW5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX5">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AY5">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AZ5">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BA5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB5">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BC5">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BD5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF5">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BG5">
         <v>1.01</v>
@@ -2219,19 +2219,19 @@
         <v>4.1</v>
       </c>
       <c r="H7">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="I7">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="J7">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K7">
         <v>4.3</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M7">
         <v>1.01</v>
@@ -2375,64 +2375,64 @@
         <v>8.4</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI7">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK7">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO7">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ7">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS7">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BU7">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BW7">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BY7">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="CA7">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="CB7" t="s">
         <v>131</v>
@@ -2458,7 +2458,7 @@
         <v>1.27</v>
       </c>
       <c r="G8">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="H8">
         <v>15.5</v>
@@ -2473,7 +2473,7 @@
         <v>6.2</v>
       </c>
       <c r="L8">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="M8">
         <v>1.07</v>
@@ -2497,7 +2497,7 @@
         <v>3.6</v>
       </c>
       <c r="T8">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="U8">
         <v>1.47</v>
@@ -2506,7 +2506,7 @@
         <v>1.05</v>
       </c>
       <c r="W8">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="X8">
         <v>17.5</v>
@@ -2530,7 +2530,7 @@
         <v>950</v>
       </c>
       <c r="AE8">
-        <v>620</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
         <v>7.6</v>
@@ -2566,19 +2566,19 @@
         <v>10.5</v>
       </c>
       <c r="AQ8">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AR8">
+        <v>4.4</v>
+      </c>
+      <c r="AS8">
         <v>4.5</v>
-      </c>
-      <c r="AS8">
-        <v>4.6</v>
       </c>
       <c r="AT8">
         <v>4.7</v>
       </c>
       <c r="AU8">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV8">
         <v>4.3</v>
@@ -2590,7 +2590,7 @@
         <v>4.8</v>
       </c>
       <c r="AY8">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ8">
         <v>4.2</v>
@@ -2614,67 +2614,67 @@
         <v>5.3</v>
       </c>
       <c r="BG8">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI8">
-        <v>1.04</v>
+        <v>2.76</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BK8">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BO8">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BQ8">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BU8">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="CA8">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="CB8" t="s">
         <v>131</v>
@@ -2700,7 +2700,7 @@
         <v>3.7</v>
       </c>
       <c r="G9">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H9">
         <v>2.3</v>
@@ -2715,13 +2715,13 @@
         <v>3.2</v>
       </c>
       <c r="L9">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="M9">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="N9">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="O9">
         <v>1.58</v>
@@ -2736,19 +2736,19 @@
         <v>1.17</v>
       </c>
       <c r="S9">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="T9">
         <v>2.16</v>
       </c>
       <c r="U9">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="V9">
         <v>1.64</v>
       </c>
       <c r="W9">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="X9">
         <v>9.6</v>
@@ -2823,7 +2823,7 @@
         <v>5.4</v>
       </c>
       <c r="AV9">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW9">
         <v>3.95</v>
@@ -2939,112 +2939,112 @@
         <v>124</v>
       </c>
       <c r="F10">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="G10">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="H10">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I10">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="J10">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K10">
         <v>3.7</v>
       </c>
       <c r="L10">
+        <v>1.53</v>
+      </c>
+      <c r="M10">
+        <v>1.11</v>
+      </c>
+      <c r="N10">
+        <v>2.46</v>
+      </c>
+      <c r="O10">
         <v>1.42</v>
       </c>
-      <c r="M10">
-        <v>1.01</v>
-      </c>
-      <c r="N10">
-        <v>2.24</v>
-      </c>
-      <c r="O10">
-        <v>1.23</v>
-      </c>
       <c r="P10">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="Q10">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="R10">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="S10">
-        <v>2.46</v>
+        <v>3.9</v>
       </c>
       <c r="T10">
-        <v>1.11</v>
+        <v>2.18</v>
       </c>
       <c r="U10">
-        <v>1.11</v>
+        <v>1.71</v>
       </c>
       <c r="V10">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="W10">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="X10">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y10">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z10">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA10">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AB10">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AC10">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD10">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE10">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF10">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AG10">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH10">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI10">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ10">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AK10">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL10">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM10">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN10">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AO10">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AP10">
         <v>1.01</v>
@@ -3101,13 +3101,13 @@
         <v>1.01</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="BI10">
-        <v>1.04</v>
+        <v>2.34</v>
       </c>
       <c r="BJ10">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK10">
         <v>1.04</v>
@@ -3119,25 +3119,25 @@
         <v>1.04</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO10">
         <v>1.04</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BQ10">
         <v>1.04</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS10">
         <v>1.04</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU10">
         <v>1.04</v>
@@ -3155,7 +3155,7 @@
         <v>1.04</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA10">
         <v>1.04</v>
@@ -3181,7 +3181,7 @@
         <v>125</v>
       </c>
       <c r="F11">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G11">
         <v>2.06</v>
@@ -3217,7 +3217,7 @@
         <v>2.3</v>
       </c>
       <c r="R11">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S11">
         <v>4.5</v>
@@ -3229,7 +3229,7 @@
         <v>1.92</v>
       </c>
       <c r="V11">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W11">
         <v>1.94</v>
@@ -3280,13 +3280,13 @@
         <v>46</v>
       </c>
       <c r="AM11">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AN11">
         <v>19</v>
       </c>
       <c r="AO11">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AP11">
         <v>10</v>
@@ -3346,7 +3346,7 @@
         <v>2.96</v>
       </c>
       <c r="BI11">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BJ11">
         <v>12.5</v>
@@ -3358,7 +3358,7 @@
         <v>200</v>
       </c>
       <c r="BM11">
-        <v>10.5</v>
+        <v>34</v>
       </c>
       <c r="BN11">
         <v>4.5</v>
@@ -3423,7 +3423,7 @@
         <v>126</v>
       </c>
       <c r="F12">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G12">
         <v>1.71</v>
@@ -3432,16 +3432,16 @@
         <v>4.9</v>
       </c>
       <c r="I12">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J12">
         <v>4.3</v>
       </c>
       <c r="K12">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L12">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M12">
         <v>1.03</v>
@@ -3450,25 +3450,25 @@
         <v>5.2</v>
       </c>
       <c r="O12">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P12">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="Q12">
+        <v>1.48</v>
+      </c>
+      <c r="R12">
         <v>1.58</v>
       </c>
-      <c r="R12">
+      <c r="S12">
+        <v>2.28</v>
+      </c>
+      <c r="T12">
         <v>1.57</v>
       </c>
-      <c r="S12">
-        <v>2.46</v>
-      </c>
-      <c r="T12">
-        <v>1.56</v>
-      </c>
       <c r="U12">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="V12">
         <v>1.01</v>
@@ -3534,7 +3534,7 @@
         <v>17.5</v>
       </c>
       <c r="AQ12">
-        <v>3.8</v>
+        <v>17.5</v>
       </c>
       <c r="AR12">
         <v>4</v>
@@ -3543,13 +3543,13 @@
         <v>4.2</v>
       </c>
       <c r="AT12">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AU12">
         <v>8</v>
       </c>
       <c r="AV12">
-        <v>3.7</v>
+        <v>15.5</v>
       </c>
       <c r="AW12">
         <v>4.1</v>
@@ -3561,7 +3561,7 @@
         <v>7.6</v>
       </c>
       <c r="AZ12">
-        <v>3.65</v>
+        <v>13.5</v>
       </c>
       <c r="BA12">
         <v>4.1</v>
@@ -3573,76 +3573,76 @@
         <v>11.5</v>
       </c>
       <c r="BD12">
-        <v>3.85</v>
+        <v>20</v>
       </c>
       <c r="BE12">
         <v>4.1</v>
       </c>
       <c r="BF12">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BG12">
         <v>4.1</v>
       </c>
       <c r="BH12">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BI12">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BJ12">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK12">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BN12">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO12">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BP12">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ12">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BR12">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS12">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BT12">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU12">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BV12">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW12">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BX12">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY12">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BZ12">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="CA12">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="CB12" t="s">
         <v>131</v>
@@ -3665,13 +3665,13 @@
         <v>127</v>
       </c>
       <c r="F13">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="G13">
         <v>990</v>
       </c>
       <c r="H13">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="I13">
         <v>990</v>
@@ -3698,7 +3698,7 @@
         <v>1.25</v>
       </c>
       <c r="Q13">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="R13">
         <v>1.18</v>
@@ -3713,10 +3713,10 @@
         <v>1.11</v>
       </c>
       <c r="V13">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W13">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -3907,7 +3907,7 @@
         <v>128</v>
       </c>
       <c r="F14">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="G14">
         <v>1.35</v>
@@ -3916,7 +3916,7 @@
         <v>10</v>
       </c>
       <c r="I14">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="J14">
         <v>6.2</v>
@@ -3952,7 +3952,7 @@
         <v>1.84</v>
       </c>
       <c r="U14">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V14">
         <v>1.1</v>
@@ -3994,7 +3994,7 @@
         <v>25</v>
       </c>
       <c r="AI14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AJ14">
         <v>11.5</v>
@@ -4021,7 +4021,7 @@
         <v>38</v>
       </c>
       <c r="AR14">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AS14">
         <v>60</v>
@@ -4045,7 +4045,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA14">
         <v>85</v>
@@ -4060,73 +4060,73 @@
         <v>26</v>
       </c>
       <c r="BE14">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="BF14">
         <v>4</v>
       </c>
       <c r="BG14">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="BH14">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BI14">
-        <v>2.36</v>
+        <v>4.4</v>
       </c>
       <c r="BJ14">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="BK14">
-        <v>3.15</v>
+        <v>9.6</v>
       </c>
       <c r="BL14">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM14">
-        <v>2.2</v>
+        <v>26</v>
       </c>
       <c r="BN14">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO14">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="BP14">
+        <v>8</v>
+      </c>
+      <c r="BQ14">
+        <v>6.8</v>
+      </c>
+      <c r="BR14">
+        <v>21</v>
+      </c>
+      <c r="BS14">
+        <v>10</v>
+      </c>
+      <c r="BT14">
+        <v>13.5</v>
+      </c>
+      <c r="BU14">
+        <v>11</v>
+      </c>
+      <c r="BV14">
+        <v>75</v>
+      </c>
+      <c r="BW14">
+        <v>11</v>
+      </c>
+      <c r="BX14">
+        <v>65</v>
+      </c>
+      <c r="BY14">
         <v>10.5</v>
       </c>
-      <c r="BQ14">
-        <v>5.5</v>
-      </c>
-      <c r="BR14">
-        <v>28</v>
-      </c>
-      <c r="BS14">
-        <v>3.45</v>
-      </c>
-      <c r="BT14">
-        <v>17.5</v>
-      </c>
-      <c r="BU14">
-        <v>3.2</v>
-      </c>
-      <c r="BV14">
-        <v>1000</v>
-      </c>
-      <c r="BW14">
-        <v>2.16</v>
-      </c>
-      <c r="BX14">
-        <v>1000</v>
-      </c>
-      <c r="BY14">
-        <v>2.14</v>
-      </c>
       <c r="BZ14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="CA14">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="CB14" t="s">
         <v>131</v>
@@ -4149,10 +4149,10 @@
         <v>129</v>
       </c>
       <c r="F15">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="G15">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="H15">
         <v>7</v>
@@ -4164,7 +4164,7 @@
         <v>3.55</v>
       </c>
       <c r="K15">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="L15">
         <v>1.42</v>
@@ -4394,223 +4394,223 @@
         <v>3.75</v>
       </c>
       <c r="G16">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="H16">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="I16">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="J16">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="K16">
         <v>3.4</v>
       </c>
       <c r="L16">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M16">
         <v>1.1</v>
       </c>
       <c r="N16">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O16">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P16">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Q16">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="R16">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="S16">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="T16">
-        <v>1.11</v>
+        <v>1.98</v>
       </c>
       <c r="U16">
-        <v>1.11</v>
+        <v>1.89</v>
       </c>
       <c r="V16">
         <v>1.72</v>
       </c>
       <c r="W16">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="X16">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y16">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC16">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD16">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF16">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG16">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH16">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ16">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL16">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP16">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AQ16">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AR16">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AS16">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT16">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU16">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AV16">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW16">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AX16">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AY16">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AZ16">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA16">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB16">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BC16">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BD16">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE16">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BH16">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI16">
-        <v>1.04</v>
+        <v>2.44</v>
       </c>
       <c r="BJ16">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK16">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BN16">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO16">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BP16">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BQ16">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS16">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BU16">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW16">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY16">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA16">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="CB16" t="s">
         <v>131</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
@@ -409,7 +409,7 @@
     <t>Millonarios</t>
   </si>
   <si>
-    <t>2026-08-26 03:53:56</t>
+    <t>2026-08-26 06:03:53</t>
   </si>
 </sst>
 </file>
@@ -1003,7 +1003,7 @@
         <v>116</v>
       </c>
       <c r="F2">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="G2">
         <v>1.67</v>
@@ -1012,7 +1012,7 @@
         <v>6.4</v>
       </c>
       <c r="I2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J2">
         <v>3.9</v>
@@ -1033,7 +1033,7 @@
         <v>1.35</v>
       </c>
       <c r="P2">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q2">
         <v>2.08</v>
@@ -1045,124 +1045,124 @@
         <v>3.85</v>
       </c>
       <c r="T2">
-        <v>2.02</v>
+        <v>1.11</v>
       </c>
       <c r="U2">
         <v>1.82</v>
       </c>
       <c r="V2">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W2">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="X2">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AC2">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD2">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AE2">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AG2">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH2">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI2">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AK2">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL2">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM2">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AO2">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AR2">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AS2">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT2">
         <v>6.2</v>
       </c>
       <c r="AU2">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AV2">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AW2">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX2">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AY2">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BA2">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB2">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC2">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BD2">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE2">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF2">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG2">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH2">
         <v>3.45</v>
@@ -1245,16 +1245,16 @@
         <v>117</v>
       </c>
       <c r="F3">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>990</v>
       </c>
       <c r="H3">
-        <v>3.7</v>
+        <v>1.06</v>
       </c>
       <c r="I3">
-        <v>5.6</v>
+        <v>870</v>
       </c>
       <c r="J3">
         <v>2.4</v>
@@ -1263,7 +1263,7 @@
         <v>2.82</v>
       </c>
       <c r="L3">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="M3">
         <v>1.16</v>
@@ -1284,7 +1284,7 @@
         <v>1.08</v>
       </c>
       <c r="S3">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="T3">
         <v>2.16</v>
@@ -1293,10 +1293,10 @@
         <v>1.48</v>
       </c>
       <c r="V3">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W3">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -1487,22 +1487,22 @@
         <v>118</v>
       </c>
       <c r="F4">
-        <v>2.22</v>
+        <v>1.11</v>
       </c>
       <c r="G4">
-        <v>3.35</v>
+        <v>990</v>
       </c>
       <c r="H4">
-        <v>2.36</v>
+        <v>1.11</v>
       </c>
       <c r="I4">
-        <v>3.2</v>
+        <v>990</v>
       </c>
       <c r="J4">
-        <v>3.25</v>
+        <v>1.11</v>
       </c>
       <c r="K4">
-        <v>8.6</v>
+        <v>950</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1511,13 +1511,13 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>2.14</v>
+        <v>4.7</v>
       </c>
       <c r="O4">
         <v>1.17</v>
       </c>
       <c r="P4">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="Q4">
         <v>1.58</v>
@@ -1526,20 +1526,20 @@
         <v>1.51</v>
       </c>
       <c r="S4">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="T4">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="U4">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="V4">
+        <v>1.54</v>
+      </c>
+      <c r="W4">
         <v>1.46</v>
       </c>
-      <c r="W4">
-        <v>1.43</v>
-      </c>
       <c r="X4">
         <v>1000</v>
       </c>
@@ -1595,52 +1595,52 @@
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF4">
         <v>1.01</v>
@@ -1652,61 +1652,61 @@
         <v>1000</v>
       </c>
       <c r="BI4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
         <v>1000</v>
       </c>
       <c r="BK4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
         <v>1000</v>
       </c>
       <c r="BO4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
         <v>1000</v>
       </c>
       <c r="BU4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="s">
         <v>131</v>
@@ -1729,118 +1729,118 @@
         <v>119</v>
       </c>
       <c r="F5">
-        <v>1.54</v>
+        <v>1.09</v>
       </c>
       <c r="G5">
-        <v>1.67</v>
+        <v>990</v>
       </c>
       <c r="H5">
-        <v>6.4</v>
+        <v>1.1</v>
       </c>
       <c r="I5">
-        <v>8.4</v>
+        <v>990</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>1.08</v>
       </c>
       <c r="K5">
-        <v>5.1</v>
+        <v>950</v>
       </c>
       <c r="L5">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N5">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="O5">
         <v>1.26</v>
       </c>
       <c r="P5">
-        <v>1.92</v>
+        <v>1.25</v>
       </c>
       <c r="Q5">
-        <v>1.87</v>
+        <v>1.28</v>
       </c>
       <c r="R5">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="S5">
-        <v>3.25</v>
+        <v>1.28</v>
       </c>
       <c r="T5">
-        <v>1.94</v>
+        <v>1.11</v>
       </c>
       <c r="U5">
-        <v>1.78</v>
+        <v>1.11</v>
       </c>
       <c r="V5">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="W5">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="X5">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Y5">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Z5">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA5">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC5">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD5">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AE5">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AF5">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG5">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH5">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI5">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ5">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AK5">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AL5">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM5">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN5">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AO5">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AP5">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR5">
         <v>1.01</v>
@@ -1849,34 +1849,34 @@
         <v>1.01</v>
       </c>
       <c r="AT5">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU5">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV5">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW5">
         <v>1.01</v>
       </c>
       <c r="AX5">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY5">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA5">
         <v>1.01</v>
       </c>
       <c r="BB5">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC5">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BD5">
         <v>1.01</v>
@@ -1885,7 +1885,7 @@
         <v>1.01</v>
       </c>
       <c r="BF5">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG5">
         <v>1.01</v>
@@ -1894,55 +1894,55 @@
         <v>1000</v>
       </c>
       <c r="BI5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5">
         <v>1000</v>
       </c>
       <c r="BK5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN5">
         <v>1000</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP5">
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT5">
         <v>1000</v>
       </c>
       <c r="BU5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5">
         <v>0</v>
@@ -1971,7 +1971,7 @@
         <v>120</v>
       </c>
       <c r="F6">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G6">
         <v>5.9</v>
@@ -1980,7 +1980,7 @@
         <v>1.76</v>
       </c>
       <c r="I6">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="J6">
         <v>3.5</v>
@@ -1989,40 +1989,40 @@
         <v>4.1</v>
       </c>
       <c r="L6">
+        <v>1.01</v>
+      </c>
+      <c r="M6">
+        <v>1.07</v>
+      </c>
+      <c r="N6">
+        <v>3.5</v>
+      </c>
+      <c r="O6">
+        <v>1.27</v>
+      </c>
+      <c r="P6">
+        <v>1.81</v>
+      </c>
+      <c r="Q6">
+        <v>1.07</v>
+      </c>
+      <c r="R6">
+        <v>1.18</v>
+      </c>
+      <c r="S6">
         <v>1.33</v>
       </c>
-      <c r="M6">
-        <v>1.01</v>
-      </c>
-      <c r="N6">
-        <v>3.4</v>
-      </c>
-      <c r="O6">
-        <v>1.01</v>
-      </c>
-      <c r="P6">
-        <v>1.83</v>
-      </c>
-      <c r="Q6">
-        <v>1.94</v>
-      </c>
-      <c r="R6">
-        <v>1.29</v>
-      </c>
-      <c r="S6">
-        <v>3.1</v>
-      </c>
       <c r="T6">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="U6">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="V6">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="W6">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2136,55 +2136,55 @@
         <v>1000</v>
       </c>
       <c r="BI6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6">
         <v>1000</v>
       </c>
       <c r="BK6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN6">
         <v>1000</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT6">
         <v>1000</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6">
         <v>0</v>
@@ -2213,226 +2213,226 @@
         <v>121</v>
       </c>
       <c r="F7">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="G7">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="H7">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="I7">
-        <v>2.08</v>
+        <v>1000</v>
       </c>
       <c r="J7">
-        <v>3.8</v>
+        <v>1.22</v>
       </c>
       <c r="K7">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="L7">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="O7">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P7">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q7">
-        <v>1.59</v>
+        <v>1.49</v>
       </c>
       <c r="R7">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="S7">
-        <v>2.46</v>
+        <v>1.16</v>
       </c>
       <c r="T7">
-        <v>1.55</v>
+        <v>1.11</v>
       </c>
       <c r="U7">
-        <v>2.48</v>
+        <v>1.11</v>
       </c>
       <c r="V7">
         <v>1.92</v>
       </c>
       <c r="W7">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="X7">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Y7">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Z7">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AA7">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AC7">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD7">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE7">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AF7">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AG7">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AH7">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AI7">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AJ7">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK7">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AL7">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM7">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AN7">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AO7">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AP7">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AR7">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS7">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AT7">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AU7">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AV7">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW7">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AX7">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY7">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BA7">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BB7">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC7">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD7">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BE7">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BF7">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH7">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP7">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="s">
         <v>131</v>
@@ -2461,61 +2461,61 @@
         <v>1.33</v>
       </c>
       <c r="H8">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="I8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J8">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="K8">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="L8">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
         <v>1.07</v>
       </c>
       <c r="N8">
-        <v>3.5</v>
+        <v>1.25</v>
       </c>
       <c r="O8">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P8">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="Q8">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R8">
         <v>1.31</v>
       </c>
       <c r="S8">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="T8">
-        <v>2.72</v>
+        <v>1.11</v>
       </c>
       <c r="U8">
-        <v>1.47</v>
+        <v>1.11</v>
       </c>
       <c r="V8">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W8">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="X8">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y8">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Z8">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AA8">
         <v>1000</v>
@@ -2524,7 +2524,7 @@
         <v>7.4</v>
       </c>
       <c r="AC8">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AD8">
         <v>950</v>
@@ -2539,10 +2539,10 @@
         <v>14.5</v>
       </c>
       <c r="AH8">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AI8">
-        <v>460</v>
+        <v>490</v>
       </c>
       <c r="AJ8">
         <v>11</v>
@@ -2554,7 +2554,7 @@
         <v>85</v>
       </c>
       <c r="AM8">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="AN8">
         <v>8.199999999999999</v>
@@ -2566,13 +2566,13 @@
         <v>10.5</v>
       </c>
       <c r="AQ8">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AR8">
+        <v>4.3</v>
+      </c>
+      <c r="AS8">
         <v>4.4</v>
-      </c>
-      <c r="AS8">
-        <v>4.5</v>
       </c>
       <c r="AT8">
         <v>4.7</v>
@@ -2581,10 +2581,10 @@
         <v>10</v>
       </c>
       <c r="AV8">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AW8">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AX8">
         <v>4.8</v>
@@ -2593,10 +2593,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ8">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BA8">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BB8">
         <v>6.8</v>
@@ -2605,76 +2605,76 @@
         <v>13</v>
       </c>
       <c r="BD8">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BE8">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BF8">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BG8">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BH8">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="BI8">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="BJ8">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>6.6</v>
+        <v>1.34</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>10.5</v>
+        <v>1.34</v>
       </c>
       <c r="BN8">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>2.66</v>
+        <v>1.34</v>
       </c>
       <c r="BP8">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>5.6</v>
+        <v>1.34</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>8.4</v>
+        <v>1.34</v>
       </c>
       <c r="BT8">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>7</v>
+        <v>1.34</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>10.5</v>
+        <v>1.34</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>10.5</v>
+        <v>1.34</v>
       </c>
       <c r="BZ8">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>6.6</v>
+        <v>1.34</v>
       </c>
       <c r="CB8" t="s">
         <v>131</v>
@@ -2700,52 +2700,52 @@
         <v>3.7</v>
       </c>
       <c r="G9">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H9">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="I9">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="J9">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="K9">
         <v>3.2</v>
       </c>
       <c r="L9">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="N9">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="O9">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="P9">
         <v>1.47</v>
       </c>
       <c r="Q9">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="R9">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="S9">
-        <v>5.8</v>
+        <v>1.05</v>
       </c>
       <c r="T9">
-        <v>2.16</v>
+        <v>1.11</v>
       </c>
       <c r="U9">
-        <v>1.66</v>
+        <v>1.11</v>
       </c>
       <c r="V9">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="W9">
         <v>1.32</v>
@@ -2754,7 +2754,7 @@
         <v>9.6</v>
       </c>
       <c r="Y9">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z9">
         <v>17</v>
@@ -2814,7 +2814,7 @@
         <v>10</v>
       </c>
       <c r="AS9">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="AT9">
         <v>7.4</v>
@@ -2826,7 +2826,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW9">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="AX9">
         <v>18.5</v>
@@ -2838,85 +2838,85 @@
         <v>18</v>
       </c>
       <c r="BA9">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BB9">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BC9">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BD9">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BE9">
+        <v>4.6</v>
+      </c>
+      <c r="BF9">
+        <v>4.6</v>
+      </c>
+      <c r="BG9">
         <v>4.3</v>
       </c>
-      <c r="BF9">
-        <v>4.2</v>
-      </c>
-      <c r="BG9">
-        <v>4</v>
-      </c>
       <c r="BH9">
-        <v>2.96</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>2.16</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BN9">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BP9">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BT9">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="BV9">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BX9">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="s">
         <v>131</v>
@@ -2939,112 +2939,112 @@
         <v>124</v>
       </c>
       <c r="F10">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="G10">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="H10">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="I10">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="J10">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K10">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L10">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="M10">
         <v>1.11</v>
       </c>
       <c r="N10">
-        <v>2.46</v>
+        <v>1.59</v>
       </c>
       <c r="O10">
-        <v>1.42</v>
+        <v>1.11</v>
       </c>
       <c r="P10">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="Q10">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="R10">
         <v>1.21</v>
       </c>
       <c r="S10">
-        <v>3.9</v>
+        <v>2.32</v>
       </c>
       <c r="T10">
-        <v>2.18</v>
+        <v>1.11</v>
       </c>
       <c r="U10">
-        <v>1.71</v>
+        <v>1.11</v>
       </c>
       <c r="V10">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="W10">
-        <v>1.97</v>
+        <v>2.12</v>
       </c>
       <c r="X10">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y10">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Z10">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA10">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AB10">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AC10">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD10">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE10">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF10">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AG10">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH10">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI10">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AK10">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL10">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM10">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AN10">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AO10">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AP10">
         <v>1.01</v>
@@ -3101,13 +3101,13 @@
         <v>1.01</v>
       </c>
       <c r="BH10">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>2.34</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
         <v>1.04</v>
@@ -3119,25 +3119,25 @@
         <v>1.04</v>
       </c>
       <c r="BN10">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
         <v>1.04</v>
       </c>
       <c r="BP10">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
         <v>1.04</v>
       </c>
       <c r="BR10">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
         <v>1.04</v>
       </c>
       <c r="BT10">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
         <v>1.04</v>
@@ -3155,7 +3155,7 @@
         <v>1.04</v>
       </c>
       <c r="BZ10">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
         <v>1.04</v>
@@ -3181,16 +3181,16 @@
         <v>125</v>
       </c>
       <c r="F11">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G11">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H11">
         <v>4.3</v>
       </c>
       <c r="I11">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J11">
         <v>3.5</v>
@@ -3199,7 +3199,7 @@
         <v>3.55</v>
       </c>
       <c r="L11">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="M11">
         <v>1.09</v>
@@ -3217,10 +3217,10 @@
         <v>2.3</v>
       </c>
       <c r="R11">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S11">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T11">
         <v>2.04</v>
@@ -3229,10 +3229,10 @@
         <v>1.92</v>
       </c>
       <c r="V11">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W11">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="X11">
         <v>11</v>
@@ -3280,13 +3280,13 @@
         <v>46</v>
       </c>
       <c r="AM11">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AO11">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP11">
         <v>10</v>
@@ -3298,7 +3298,7 @@
         <v>27</v>
       </c>
       <c r="AS11">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="AT11">
         <v>7.2</v>
@@ -3310,7 +3310,7 @@
         <v>16.5</v>
       </c>
       <c r="AW11">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AX11">
         <v>10.5</v>
@@ -3322,85 +3322,85 @@
         <v>19.5</v>
       </c>
       <c r="BA11">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="BB11">
         <v>22</v>
       </c>
       <c r="BC11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD11">
         <v>42</v>
       </c>
       <c r="BE11">
-        <v>44</v>
+        <v>18.5</v>
       </c>
       <c r="BF11">
         <v>17.5</v>
       </c>
       <c r="BG11">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="BH11">
-        <v>2.96</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>2.82</v>
+        <v>1.46</v>
       </c>
       <c r="BJ11">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>6</v>
+        <v>2.58</v>
       </c>
       <c r="BL11">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="BM11">
-        <v>34</v>
+        <v>1.45</v>
       </c>
       <c r="BN11">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>4.1</v>
+        <v>1.74</v>
       </c>
       <c r="BP11">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>11.5</v>
+        <v>2.58</v>
       </c>
       <c r="BR11">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>8.4</v>
+        <v>1.45</v>
       </c>
       <c r="BT11">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>7</v>
+        <v>1.99</v>
       </c>
       <c r="BV11">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>9</v>
+        <v>1.45</v>
       </c>
       <c r="BX11">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>9.6</v>
+        <v>1.45</v>
       </c>
       <c r="BZ11">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>8.4</v>
+        <v>1.45</v>
       </c>
       <c r="CB11" t="s">
         <v>131</v>
@@ -3429,7 +3429,7 @@
         <v>1.71</v>
       </c>
       <c r="H12">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="I12">
         <v>5.9</v>
@@ -3438,7 +3438,7 @@
         <v>4.3</v>
       </c>
       <c r="K12">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L12">
         <v>1.24</v>
@@ -3447,22 +3447,22 @@
         <v>1.03</v>
       </c>
       <c r="N12">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="O12">
         <v>1.18</v>
       </c>
       <c r="P12">
-        <v>2.44</v>
+        <v>1.12</v>
       </c>
       <c r="Q12">
-        <v>1.48</v>
+        <v>1.18</v>
       </c>
       <c r="R12">
-        <v>1.58</v>
+        <v>1.09</v>
       </c>
       <c r="S12">
-        <v>2.28</v>
+        <v>1.18</v>
       </c>
       <c r="T12">
         <v>1.57</v>
@@ -3477,172 +3477,172 @@
         <v>1.01</v>
       </c>
       <c r="X12">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="Y12">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="Z12">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA12">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB12">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC12">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AD12">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AE12">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF12">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AG12">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH12">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI12">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AK12">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AL12">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM12">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN12">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AO12">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP12">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR12">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AS12">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT12">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU12">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AV12">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW12">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX12">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY12">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA12">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BB12">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BC12">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD12">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BE12">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF12">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BG12">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH12">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN12">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="BP12">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR12">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="BT12">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="BV12">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX12">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="s">
         <v>131</v>
@@ -3677,7 +3677,7 @@
         <v>990</v>
       </c>
       <c r="J13">
-        <v>3.9</v>
+        <v>1.17</v>
       </c>
       <c r="K13">
         <v>950</v>
@@ -3916,13 +3916,13 @@
         <v>10</v>
       </c>
       <c r="I14">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="J14">
         <v>6.2</v>
       </c>
       <c r="K14">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="L14">
         <v>1.26</v>
@@ -3949,7 +3949,7 @@
         <v>2.22</v>
       </c>
       <c r="T14">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="U14">
         <v>2.12</v>
@@ -3961,16 +3961,16 @@
         <v>3.85</v>
       </c>
       <c r="X14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y14">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="Z14">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AA14">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="AB14">
         <v>12</v>
@@ -3982,10 +3982,10 @@
         <v>38</v>
       </c>
       <c r="AE14">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF14">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG14">
         <v>10.5</v>
@@ -3994,7 +3994,7 @@
         <v>25</v>
       </c>
       <c r="AI14">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ14">
         <v>11.5</v>
@@ -4012,19 +4012,19 @@
         <v>4.2</v>
       </c>
       <c r="AO14">
-        <v>140</v>
+        <v>980</v>
       </c>
       <c r="AP14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ14">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AR14">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AS14">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AT14">
         <v>11.5</v>
@@ -4033,10 +4033,10 @@
         <v>13.5</v>
       </c>
       <c r="AV14">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AW14">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="AX14">
         <v>9.199999999999999</v>
@@ -4048,7 +4048,7 @@
         <v>23</v>
       </c>
       <c r="BA14">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="BB14">
         <v>10.5</v>
@@ -4060,7 +4060,7 @@
         <v>26</v>
       </c>
       <c r="BE14">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BF14">
         <v>4</v>
@@ -4069,64 +4069,64 @@
         <v>95</v>
       </c>
       <c r="BH14">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BI14">
-        <v>4.4</v>
+        <v>1.47</v>
       </c>
       <c r="BJ14">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
-        <v>9.6</v>
+        <v>1.97</v>
       </c>
       <c r="BL14">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="BM14">
-        <v>26</v>
+        <v>1.97</v>
       </c>
       <c r="BN14">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BO14">
-        <v>3.85</v>
+        <v>1.4</v>
       </c>
       <c r="BP14">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>6.8</v>
+        <v>1.65</v>
       </c>
       <c r="BR14">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>10</v>
+        <v>1.97</v>
       </c>
       <c r="BT14">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
-        <v>11</v>
+        <v>1.97</v>
       </c>
       <c r="BV14">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
-        <v>11</v>
+        <v>1.97</v>
       </c>
       <c r="BX14">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY14">
-        <v>10.5</v>
+        <v>1.97</v>
       </c>
       <c r="BZ14">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
-        <v>8</v>
+        <v>1.97</v>
       </c>
       <c r="CB14" t="s">
         <v>131</v>
@@ -4149,46 +4149,46 @@
         <v>129</v>
       </c>
       <c r="F15">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="G15">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="H15">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I15">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="J15">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K15">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="L15">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M15">
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="O15">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="P15">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="Q15">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R15">
         <v>1.12</v>
       </c>
       <c r="S15">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="T15">
         <v>1.11</v>
@@ -4197,10 +4197,10 @@
         <v>1.11</v>
       </c>
       <c r="V15">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="W15">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4209,7 +4209,7 @@
         <v>1000</v>
       </c>
       <c r="Z15">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AA15">
         <v>1000</v>
@@ -4218,7 +4218,7 @@
         <v>1000</v>
       </c>
       <c r="AC15">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD15">
         <v>1000</v>
@@ -4227,31 +4227,31 @@
         <v>1000</v>
       </c>
       <c r="AF15">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG15">
         <v>1000</v>
       </c>
       <c r="AH15">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI15">
         <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AK15">
         <v>1000</v>
       </c>
       <c r="AL15">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM15">
         <v>1000</v>
       </c>
       <c r="AN15">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO15">
         <v>1000</v>
@@ -4311,10 +4311,10 @@
         <v>1.01</v>
       </c>
       <c r="BH15">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI15">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="BJ15">
         <v>1000</v>
@@ -4394,223 +4394,223 @@
         <v>3.75</v>
       </c>
       <c r="G16">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="H16">
         <v>2.22</v>
       </c>
       <c r="I16">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="J16">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="K16">
         <v>3.4</v>
       </c>
       <c r="L16">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M16">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N16">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O16">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="P16">
         <v>1.63</v>
       </c>
       <c r="Q16">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="R16">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="S16">
-        <v>4.6</v>
+        <v>1.43</v>
       </c>
       <c r="T16">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="U16">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="V16">
-        <v>1.72</v>
+        <v>1.29</v>
       </c>
       <c r="W16">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="X16">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y16">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Z16">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AA16">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AB16">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC16">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD16">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE16">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF16">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AG16">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AH16">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI16">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ16">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AK16">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AL16">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM16">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN16">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AO16">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AP16">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR16">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS16">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT16">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU16">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV16">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW16">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX16">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY16">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA16">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB16">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC16">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BD16">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE16">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BF16">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG16">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BH16">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>2.44</v>
+        <v>1.04</v>
       </c>
       <c r="BJ16">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BN16">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP16">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BR16">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BT16">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="BV16">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX16">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="CB16" t="s">
         <v>131</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
@@ -409,7 +409,7 @@
     <t>Millonarios</t>
   </si>
   <si>
-    <t>2026-08-26 06:03:53</t>
+    <t>2026-08-26 08:13:39</t>
   </si>
 </sst>
 </file>
@@ -1003,13 +1003,13 @@
         <v>116</v>
       </c>
       <c r="F2">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="G2">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I2">
         <v>7.6</v>
@@ -1033,7 +1033,7 @@
         <v>1.35</v>
       </c>
       <c r="P2">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q2">
         <v>2.08</v>
@@ -1045,10 +1045,10 @@
         <v>3.85</v>
       </c>
       <c r="T2">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="U2">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="V2">
         <v>1.16</v>
@@ -1057,139 +1057,139 @@
         <v>2.5</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AB2">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AP2">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AQ2">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AR2">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AS2">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AT2">
         <v>6.2</v>
       </c>
       <c r="AU2">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AV2">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AW2">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AX2">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AY2">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ2">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BA2">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BB2">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BC2">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BD2">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BE2">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BF2">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG2">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BH2">
         <v>3.45</v>
       </c>
       <c r="BI2">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BJ2">
         <v>12</v>
       </c>
       <c r="BK2">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BN2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BO2">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BP2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BQ2">
         <v>5.4</v>
@@ -1198,31 +1198,31 @@
         <v>30</v>
       </c>
       <c r="BS2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BU2">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BX2">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BZ2">
         <v>23</v>
       </c>
       <c r="CA2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="CB2" t="s">
         <v>131</v>
@@ -1245,46 +1245,46 @@
         <v>117</v>
       </c>
       <c r="F3">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="G3">
-        <v>990</v>
+        <v>2.54</v>
       </c>
       <c r="H3">
-        <v>1.06</v>
+        <v>3.95</v>
       </c>
       <c r="I3">
-        <v>870</v>
+        <v>5.7</v>
       </c>
       <c r="J3">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="K3">
         <v>2.82</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="M3">
         <v>1.16</v>
       </c>
       <c r="N3">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="O3">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P3">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q3">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="R3">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S3">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="T3">
         <v>2.16</v>
@@ -1293,10 +1293,10 @@
         <v>1.48</v>
       </c>
       <c r="V3">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W3">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -1487,46 +1487,46 @@
         <v>118</v>
       </c>
       <c r="F4">
-        <v>1.11</v>
+        <v>2.6</v>
       </c>
       <c r="G4">
-        <v>990</v>
+        <v>3</v>
       </c>
       <c r="H4">
-        <v>1.11</v>
+        <v>2.44</v>
       </c>
       <c r="I4">
-        <v>990</v>
+        <v>2.74</v>
       </c>
       <c r="J4">
-        <v>1.11</v>
+        <v>3.4</v>
       </c>
       <c r="K4">
-        <v>950</v>
+        <v>4.8</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M4">
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="O4">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="P4">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="Q4">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R4">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S4">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="T4">
         <v>1.48</v>
@@ -1535,118 +1535,118 @@
         <v>2.34</v>
       </c>
       <c r="V4">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="W4">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB4">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AC4">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD4">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF4">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG4">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH4">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AP4">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AQ4">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR4">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AS4">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AT4">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AU4">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV4">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AW4">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AX4">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AY4">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ4">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BA4">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB4">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC4">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD4">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE4">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF4">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1729,220 +1729,220 @@
         <v>119</v>
       </c>
       <c r="F5">
-        <v>1.09</v>
+        <v>1.54</v>
       </c>
       <c r="G5">
-        <v>990</v>
+        <v>1.67</v>
       </c>
       <c r="H5">
-        <v>1.1</v>
+        <v>5.7</v>
       </c>
       <c r="I5">
-        <v>990</v>
+        <v>8.4</v>
       </c>
       <c r="J5">
-        <v>1.08</v>
+        <v>3.8</v>
       </c>
       <c r="K5">
-        <v>950</v>
+        <v>5.1</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M5">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N5">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="O5">
         <v>1.26</v>
       </c>
       <c r="P5">
-        <v>1.25</v>
+        <v>1.92</v>
       </c>
       <c r="Q5">
-        <v>1.28</v>
+        <v>1.87</v>
       </c>
       <c r="R5">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="S5">
-        <v>1.28</v>
+        <v>3</v>
       </c>
       <c r="T5">
-        <v>1.11</v>
+        <v>1.94</v>
       </c>
       <c r="U5">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="V5">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="W5">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y5">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z5">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AB5">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC5">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD5">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AE5">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF5">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG5">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH5">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ5">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AK5">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL5">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN5">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP5">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AQ5">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR5">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AS5">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT5">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AU5">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AV5">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AW5">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX5">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AY5">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AZ5">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA5">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB5">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BC5">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD5">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE5">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF5">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BG5">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI5">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK5">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO5">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ5">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS5">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU5">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BZ5">
         <v>0</v>
@@ -1971,7 +1971,7 @@
         <v>120</v>
       </c>
       <c r="F6">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="G6">
         <v>5.9</v>
@@ -1980,16 +1980,16 @@
         <v>1.76</v>
       </c>
       <c r="I6">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="J6">
         <v>3.5</v>
       </c>
       <c r="K6">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M6">
         <v>1.07</v>
@@ -1998,139 +1998,139 @@
         <v>3.5</v>
       </c>
       <c r="O6">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="P6">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q6">
-        <v>1.07</v>
+        <v>1.96</v>
       </c>
       <c r="R6">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="S6">
-        <v>1.33</v>
+        <v>3.1</v>
       </c>
       <c r="T6">
         <v>1.73</v>
       </c>
       <c r="U6">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="V6">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="W6">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AB6">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AP6">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AQ6">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="AR6">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AS6">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AT6">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AU6">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="AV6">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AW6">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AX6">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AY6">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AZ6">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="BA6">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BB6">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC6">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BD6">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE6">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2213,52 +2213,52 @@
         <v>121</v>
       </c>
       <c r="F7">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="G7">
-        <v>6</v>
+        <v>3.95</v>
       </c>
       <c r="H7">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="I7">
-        <v>1000</v>
+        <v>2.08</v>
       </c>
       <c r="J7">
-        <v>1.22</v>
+        <v>3.75</v>
       </c>
       <c r="K7">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M7">
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="O7">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P7">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q7">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="R7">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="S7">
-        <v>1.16</v>
+        <v>2.44</v>
       </c>
       <c r="T7">
-        <v>1.11</v>
+        <v>1.55</v>
       </c>
       <c r="U7">
-        <v>1.11</v>
+        <v>2.46</v>
       </c>
       <c r="V7">
         <v>1.92</v>
@@ -2267,172 +2267,172 @@
         <v>1.34</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y7">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AB7">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AC7">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AF7">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG7">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH7">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI7">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ7">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AK7">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL7">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AP7">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AQ7">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AR7">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AS7">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AT7">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AU7">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV7">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AW7">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AX7">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AY7">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AZ7">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BA7">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BB7">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC7">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD7">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE7">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF7">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BG7">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI7">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK7">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO7">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ7">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS7">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BU7">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BW7">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BY7">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="CA7">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="CB7" t="s">
         <v>131</v>
@@ -2458,7 +2458,7 @@
         <v>1.27</v>
       </c>
       <c r="G8">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="H8">
         <v>16.5</v>
@@ -2467,46 +2467,46 @@
         <v>24</v>
       </c>
       <c r="J8">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="K8">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M8">
         <v>1.07</v>
       </c>
       <c r="N8">
-        <v>1.25</v>
+        <v>3.5</v>
       </c>
       <c r="O8">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P8">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="Q8">
         <v>1.98</v>
       </c>
       <c r="R8">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S8">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="T8">
-        <v>1.11</v>
+        <v>2.68</v>
       </c>
       <c r="U8">
-        <v>1.11</v>
+        <v>1.47</v>
       </c>
       <c r="V8">
         <v>1.04</v>
       </c>
       <c r="W8">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="X8">
         <v>18</v>
@@ -2617,64 +2617,64 @@
         <v>4.4</v>
       </c>
       <c r="BH8">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>2.66</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8">
         <v>1000</v>
       </c>
       <c r="BK8">
-        <v>1.34</v>
+        <v>1.04</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.34</v>
+        <v>1.04</v>
       </c>
       <c r="BN8">
         <v>1000</v>
       </c>
       <c r="BO8">
-        <v>1.34</v>
+        <v>1.04</v>
       </c>
       <c r="BP8">
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>1.34</v>
+        <v>1.04</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>1.34</v>
+        <v>1.04</v>
       </c>
       <c r="BT8">
         <v>1000</v>
       </c>
       <c r="BU8">
-        <v>1.34</v>
+        <v>1.04</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>1.34</v>
+        <v>1.04</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.34</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>1.34</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="s">
         <v>131</v>
@@ -2697,34 +2697,34 @@
         <v>123</v>
       </c>
       <c r="F9">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G9">
         <v>4.4</v>
       </c>
       <c r="H9">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I9">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J9">
-        <v>2.68</v>
+        <v>2.84</v>
       </c>
       <c r="K9">
         <v>3.2</v>
       </c>
       <c r="L9">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M9">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="N9">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="O9">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="P9">
         <v>1.47</v>
@@ -2733,28 +2733,28 @@
         <v>2.8</v>
       </c>
       <c r="R9">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="S9">
-        <v>1.05</v>
+        <v>5.5</v>
       </c>
       <c r="T9">
-        <v>1.11</v>
+        <v>2.16</v>
       </c>
       <c r="U9">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="V9">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="W9">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="X9">
         <v>9.6</v>
       </c>
       <c r="Y9">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="Z9">
         <v>17</v>
@@ -2814,7 +2814,7 @@
         <v>10</v>
       </c>
       <c r="AS9">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="AT9">
         <v>7.4</v>
@@ -2826,7 +2826,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW9">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="AX9">
         <v>18.5</v>
@@ -2838,85 +2838,85 @@
         <v>18</v>
       </c>
       <c r="BA9">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BB9">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BC9">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BD9">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BE9">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BF9">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BG9">
+        <v>4</v>
+      </c>
+      <c r="BH9">
+        <v>2.96</v>
+      </c>
+      <c r="BI9">
+        <v>2.16</v>
+      </c>
+      <c r="BJ9">
+        <v>14</v>
+      </c>
+      <c r="BK9">
+        <v>3.75</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>5.1</v>
+      </c>
+      <c r="BN9">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BO9">
+        <v>5.1</v>
+      </c>
+      <c r="BP9">
+        <v>48</v>
+      </c>
+      <c r="BQ9">
+        <v>4.7</v>
+      </c>
+      <c r="BR9">
+        <v>1000</v>
+      </c>
+      <c r="BS9">
+        <v>4.8</v>
+      </c>
+      <c r="BT9">
+        <v>5.9</v>
+      </c>
+      <c r="BU9">
+        <v>3.85</v>
+      </c>
+      <c r="BV9">
+        <v>26</v>
+      </c>
+      <c r="BW9">
         <v>4.3</v>
       </c>
-      <c r="BH9">
-        <v>1000</v>
-      </c>
-      <c r="BI9">
-        <v>1.04</v>
-      </c>
-      <c r="BJ9">
-        <v>1000</v>
-      </c>
-      <c r="BK9">
-        <v>1.04</v>
-      </c>
-      <c r="BL9">
-        <v>1000</v>
-      </c>
-      <c r="BM9">
-        <v>1.04</v>
-      </c>
-      <c r="BN9">
-        <v>1000</v>
-      </c>
-      <c r="BO9">
-        <v>1.04</v>
-      </c>
-      <c r="BP9">
-        <v>1000</v>
-      </c>
-      <c r="BQ9">
-        <v>1.04</v>
-      </c>
-      <c r="BR9">
-        <v>1000</v>
-      </c>
-      <c r="BS9">
-        <v>1.04</v>
-      </c>
-      <c r="BT9">
-        <v>1000</v>
-      </c>
-      <c r="BU9">
-        <v>1.04</v>
-      </c>
-      <c r="BV9">
-        <v>1000</v>
-      </c>
-      <c r="BW9">
-        <v>1.04</v>
-      </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY9">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="CB9" t="s">
         <v>131</v>
@@ -2942,10 +2942,10 @@
         <v>1.75</v>
       </c>
       <c r="G10">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="H10">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="I10">
         <v>7.6</v>
@@ -2954,37 +2954,37 @@
         <v>2.96</v>
       </c>
       <c r="K10">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L10">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="M10">
         <v>1.11</v>
       </c>
       <c r="N10">
-        <v>1.59</v>
+        <v>2.46</v>
       </c>
       <c r="O10">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="P10">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Q10">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="R10">
         <v>1.21</v>
       </c>
       <c r="S10">
-        <v>2.32</v>
+        <v>1.05</v>
       </c>
       <c r="T10">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="U10">
-        <v>1.11</v>
+        <v>1.59</v>
       </c>
       <c r="V10">
         <v>1.15</v>
@@ -2993,172 +2993,172 @@
         <v>2.12</v>
       </c>
       <c r="X10">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y10">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z10">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA10">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AB10">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC10">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD10">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AE10">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF10">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG10">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH10">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI10">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ10">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK10">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL10">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM10">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN10">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO10">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AP10">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AQ10">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AR10">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS10">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT10">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="AU10">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AV10">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AW10">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AX10">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AY10">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AZ10">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BA10">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB10">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BC10">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BD10">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE10">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF10">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BG10">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="BI10">
-        <v>1.04</v>
+        <v>2.34</v>
       </c>
       <c r="BJ10">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK10">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO10">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BQ10">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS10">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU10">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA10">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="CB10" t="s">
         <v>131</v>
@@ -3181,16 +3181,16 @@
         <v>125</v>
       </c>
       <c r="F11">
+        <v>2.02</v>
+      </c>
+      <c r="G11">
         <v>2.04</v>
       </c>
-      <c r="G11">
-        <v>2.08</v>
-      </c>
       <c r="H11">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I11">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J11">
         <v>3.5</v>
@@ -3199,40 +3199,40 @@
         <v>3.55</v>
       </c>
       <c r="L11">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="M11">
         <v>1.09</v>
       </c>
       <c r="N11">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O11">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P11">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Q11">
         <v>2.3</v>
       </c>
       <c r="R11">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S11">
         <v>4.4</v>
       </c>
       <c r="T11">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U11">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V11">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W11">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="X11">
         <v>11</v>
@@ -3253,7 +3253,7 @@
         <v>7.8</v>
       </c>
       <c r="AD11">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE11">
         <v>65</v>
@@ -3280,13 +3280,13 @@
         <v>46</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN11">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="AO11">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP11">
         <v>10</v>
@@ -3298,7 +3298,7 @@
         <v>27</v>
       </c>
       <c r="AS11">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="AT11">
         <v>7.2</v>
@@ -3310,7 +3310,7 @@
         <v>16.5</v>
       </c>
       <c r="AW11">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX11">
         <v>10.5</v>
@@ -3322,7 +3322,7 @@
         <v>19.5</v>
       </c>
       <c r="BA11">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="BB11">
         <v>22</v>
@@ -3334,73 +3334,73 @@
         <v>42</v>
       </c>
       <c r="BE11">
-        <v>18.5</v>
+        <v>44</v>
       </c>
       <c r="BF11">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG11">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI11">
-        <v>1.46</v>
+        <v>2.8</v>
       </c>
       <c r="BJ11">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK11">
-        <v>2.58</v>
+        <v>9.6</v>
       </c>
       <c r="BL11">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="BM11">
-        <v>1.45</v>
+        <v>36</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO11">
-        <v>1.74</v>
+        <v>4.1</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ11">
-        <v>2.58</v>
+        <v>6.2</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS11">
-        <v>1.45</v>
+        <v>8</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU11">
-        <v>1.99</v>
+        <v>7</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW11">
-        <v>1.45</v>
+        <v>7.8</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY11">
-        <v>1.45</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA11">
-        <v>1.45</v>
+        <v>7.4</v>
       </c>
       <c r="CB11" t="s">
         <v>131</v>
@@ -3423,10 +3423,10 @@
         <v>126</v>
       </c>
       <c r="F12">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="G12">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="H12">
         <v>5.2</v>
@@ -3435,7 +3435,7 @@
         <v>5.9</v>
       </c>
       <c r="J12">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K12">
         <v>5</v>
@@ -3447,25 +3447,25 @@
         <v>1.03</v>
       </c>
       <c r="N12">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="O12">
         <v>1.18</v>
       </c>
       <c r="P12">
-        <v>1.12</v>
+        <v>2.44</v>
       </c>
       <c r="Q12">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="R12">
-        <v>1.09</v>
+        <v>1.58</v>
       </c>
       <c r="S12">
-        <v>1.18</v>
+        <v>2.46</v>
       </c>
       <c r="T12">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="U12">
         <v>2.26</v>
@@ -3477,112 +3477,112 @@
         <v>1.01</v>
       </c>
       <c r="X12">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Y12">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Z12">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA12">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB12">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC12">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD12">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AE12">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF12">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG12">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH12">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI12">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ12">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK12">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AL12">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM12">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN12">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AO12">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP12">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AQ12">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AR12">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS12">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT12">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AU12">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AV12">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AW12">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX12">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY12">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AZ12">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA12">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB12">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BC12">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BD12">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BE12">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF12">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BG12">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3677,7 +3677,7 @@
         <v>990</v>
       </c>
       <c r="J13">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="K13">
         <v>950</v>
@@ -3713,10 +3713,10 @@
         <v>1.11</v>
       </c>
       <c r="V13">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W13">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -3910,13 +3910,13 @@
         <v>1.33</v>
       </c>
       <c r="G14">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="H14">
         <v>10</v>
       </c>
       <c r="I14">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="J14">
         <v>6.2</v>
@@ -3943,13 +3943,13 @@
         <v>1.49</v>
       </c>
       <c r="R14">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="S14">
         <v>2.22</v>
       </c>
       <c r="T14">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="U14">
         <v>2.12</v>
@@ -3958,16 +3958,16 @@
         <v>1.1</v>
       </c>
       <c r="W14">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="X14">
         <v>32</v>
       </c>
       <c r="Y14">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="Z14">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AA14">
         <v>360</v>
@@ -3982,10 +3982,10 @@
         <v>38</v>
       </c>
       <c r="AE14">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF14">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AG14">
         <v>10.5</v>
@@ -3994,13 +3994,13 @@
         <v>25</v>
       </c>
       <c r="AI14">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ14">
         <v>11.5</v>
       </c>
       <c r="AK14">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AL14">
         <v>28</v>
@@ -4012,16 +4012,16 @@
         <v>4.2</v>
       </c>
       <c r="AO14">
-        <v>980</v>
+        <v>130</v>
       </c>
       <c r="AP14">
         <v>29</v>
       </c>
       <c r="AQ14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AR14">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AS14">
         <v>70</v>
@@ -4033,10 +4033,10 @@
         <v>13.5</v>
       </c>
       <c r="AV14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AW14">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="AX14">
         <v>9.199999999999999</v>
@@ -4048,7 +4048,7 @@
         <v>23</v>
       </c>
       <c r="BA14">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="BB14">
         <v>10.5</v>
@@ -4060,7 +4060,7 @@
         <v>26</v>
       </c>
       <c r="BE14">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="BF14">
         <v>4</v>
@@ -4069,64 +4069,64 @@
         <v>95</v>
       </c>
       <c r="BH14">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BI14">
-        <v>1.47</v>
+        <v>4.4</v>
       </c>
       <c r="BJ14">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK14">
-        <v>1.97</v>
+        <v>9.6</v>
       </c>
       <c r="BL14">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM14">
-        <v>1.97</v>
+        <v>5.9</v>
       </c>
       <c r="BN14">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BO14">
-        <v>1.4</v>
+        <v>3.85</v>
       </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ14">
-        <v>1.65</v>
+        <v>6.8</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS14">
-        <v>1.97</v>
+        <v>14.5</v>
       </c>
       <c r="BT14">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BU14">
-        <v>1.97</v>
+        <v>11</v>
       </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BW14">
-        <v>1.97</v>
+        <v>5.8</v>
       </c>
       <c r="BX14">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY14">
-        <v>1.97</v>
+        <v>6</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="CA14">
-        <v>1.97</v>
+        <v>8</v>
       </c>
       <c r="CB14" t="s">
         <v>131</v>
@@ -4149,37 +4149,37 @@
         <v>129</v>
       </c>
       <c r="F15">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="G15">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="H15">
         <v>6.8</v>
       </c>
       <c r="I15">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="J15">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K15">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="L15">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M15">
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>2.68</v>
+        <v>2.52</v>
       </c>
       <c r="O15">
         <v>1.28</v>
       </c>
       <c r="P15">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="Q15">
         <v>2.38</v>
@@ -4197,64 +4197,64 @@
         <v>1.11</v>
       </c>
       <c r="V15">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="W15">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="X15">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y15">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z15">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AA15">
-        <v>1000</v>
+        <v>510</v>
       </c>
       <c r="AB15">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AC15">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD15">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AE15">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AF15">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG15">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH15">
-        <v>950</v>
+        <v>42</v>
       </c>
       <c r="AI15">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AJ15">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK15">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL15">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM15">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AN15">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO15">
-        <v>1000</v>
+        <v>590</v>
       </c>
       <c r="AP15">
         <v>1.01</v>
@@ -4311,10 +4311,10 @@
         <v>1.01</v>
       </c>
       <c r="BH15">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15">
         <v>1000</v>
@@ -4394,223 +4394,223 @@
         <v>3.75</v>
       </c>
       <c r="G16">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="H16">
         <v>2.22</v>
       </c>
       <c r="I16">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J16">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="K16">
         <v>3.4</v>
       </c>
       <c r="L16">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M16">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N16">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="O16">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="P16">
         <v>1.63</v>
       </c>
       <c r="Q16">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R16">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="S16">
-        <v>1.43</v>
+        <v>4.5</v>
       </c>
       <c r="T16">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="U16">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V16">
-        <v>1.29</v>
+        <v>1.72</v>
       </c>
       <c r="W16">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="X16">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y16">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC16">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD16">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF16">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG16">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH16">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ16">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL16">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP16">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AQ16">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AR16">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AS16">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AT16">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU16">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AV16">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW16">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX16">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AY16">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AZ16">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BA16">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BB16">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BC16">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BD16">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BE16">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BH16">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI16">
-        <v>1.04</v>
+        <v>2.44</v>
       </c>
       <c r="BJ16">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK16">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BN16">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO16">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BP16">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BQ16">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS16">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BU16">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW16">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY16">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA16">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="CB16" t="s">
         <v>131</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
@@ -409,7 +409,7 @@
     <t>Millonarios</t>
   </si>
   <si>
-    <t>2026-08-26 08:13:39</t>
+    <t>2026-08-26 10:23:20</t>
   </si>
 </sst>
 </file>
@@ -1003,16 +1003,16 @@
         <v>116</v>
       </c>
       <c r="F2">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="G2">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="I2">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="J2">
         <v>3.9</v>
@@ -1024,205 +1024,205 @@
         <v>1.43</v>
       </c>
       <c r="M2">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N2">
         <v>3.55</v>
       </c>
       <c r="O2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P2">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q2">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R2">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S2">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="T2">
-        <v>2.04</v>
+        <v>1.11</v>
       </c>
       <c r="U2">
         <v>1.83</v>
       </c>
       <c r="V2">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W2">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="X2">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
+        <v>26</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>8.6</v>
+      </c>
+      <c r="AC2">
+        <v>1000</v>
+      </c>
+      <c r="AD2">
+        <v>1000</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>970</v>
+      </c>
+      <c r="AG2">
+        <v>13</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
         <v>22</v>
       </c>
-      <c r="Z2">
-        <v>70</v>
-      </c>
-      <c r="AA2">
-        <v>260</v>
-      </c>
-      <c r="AB2">
-        <v>7.6</v>
-      </c>
-      <c r="AC2">
-        <v>11</v>
-      </c>
-      <c r="AD2">
-        <v>29</v>
-      </c>
-      <c r="AE2">
-        <v>140</v>
-      </c>
-      <c r="AF2">
-        <v>9.4</v>
-      </c>
-      <c r="AG2">
-        <v>10.5</v>
-      </c>
-      <c r="AH2">
-        <v>26</v>
-      </c>
-      <c r="AI2">
-        <v>130</v>
-      </c>
-      <c r="AJ2">
-        <v>16</v>
-      </c>
-      <c r="AK2">
-        <v>19.5</v>
-      </c>
       <c r="AL2">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM2">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AO2">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
-        <v>11.5</v>
+        <v>1.63</v>
       </c>
       <c r="AQ2">
-        <v>17</v>
+        <v>1.54</v>
       </c>
       <c r="AR2">
-        <v>6.4</v>
+        <v>1.63</v>
       </c>
       <c r="AS2">
-        <v>7</v>
+        <v>1.63</v>
       </c>
       <c r="AT2">
-        <v>6.2</v>
+        <v>1.37</v>
       </c>
       <c r="AU2">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AV2">
-        <v>5.7</v>
+        <v>19</v>
       </c>
       <c r="AW2">
-        <v>6.8</v>
+        <v>1.63</v>
       </c>
       <c r="AX2">
-        <v>7.6</v>
+        <v>1.39</v>
       </c>
       <c r="AY2">
-        <v>8.800000000000001</v>
+        <v>1.72</v>
       </c>
       <c r="AZ2">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BA2">
-        <v>6.8</v>
+        <v>1.63</v>
       </c>
       <c r="BB2">
-        <v>12.5</v>
+        <v>1.63</v>
       </c>
       <c r="BC2">
-        <v>15.5</v>
+        <v>1.52</v>
       </c>
       <c r="BD2">
-        <v>6.2</v>
+        <v>1.63</v>
       </c>
       <c r="BE2">
-        <v>6.8</v>
+        <v>1.63</v>
       </c>
       <c r="BF2">
-        <v>8.199999999999999</v>
+        <v>1.63</v>
       </c>
       <c r="BG2">
-        <v>6.8</v>
+        <v>1.63</v>
       </c>
       <c r="BH2">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>2.76</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN2">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="BP2">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR2">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT2">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="s">
         <v>131</v>
@@ -1254,7 +1254,7 @@
         <v>3.95</v>
       </c>
       <c r="I3">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="J3">
         <v>2.42</v>
@@ -1272,7 +1272,7 @@
         <v>1.87</v>
       </c>
       <c r="O3">
-        <v>1.42</v>
+        <v>1.72</v>
       </c>
       <c r="P3">
         <v>1.3</v>
@@ -1293,7 +1293,7 @@
         <v>1.48</v>
       </c>
       <c r="V3">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W3">
         <v>1.64</v>
@@ -1487,166 +1487,166 @@
         <v>118</v>
       </c>
       <c r="F4">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="H4">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="I4">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="J4">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K4">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="L4">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N4">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="O4">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="P4">
+        <v>2.02</v>
+      </c>
+      <c r="Q4">
+        <v>1.5</v>
+      </c>
+      <c r="R4">
+        <v>1.47</v>
+      </c>
+      <c r="S4">
         <v>2.36</v>
       </c>
-      <c r="Q4">
-        <v>1.59</v>
-      </c>
-      <c r="R4">
-        <v>1.5</v>
-      </c>
-      <c r="S4">
-        <v>2.48</v>
-      </c>
       <c r="T4">
+        <v>1.11</v>
+      </c>
+      <c r="U4">
+        <v>1.11</v>
+      </c>
+      <c r="V4">
         <v>1.48</v>
       </c>
-      <c r="U4">
-        <v>2.34</v>
-      </c>
-      <c r="V4">
-        <v>1.57</v>
-      </c>
       <c r="W4">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="X4">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AC4">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD4">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE4">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AG4">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH4">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI4">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AK4">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL4">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM4">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AO4">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR4">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AS4">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT4">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AU4">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV4">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW4">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX4">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY4">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA4">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB4">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC4">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD4">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE4">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BF4">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BG4">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1729,220 +1729,220 @@
         <v>119</v>
       </c>
       <c r="F5">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="G5">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="H5">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I5">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
       <c r="J5">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K5">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="L5">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="M5">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N5">
-        <v>3.7</v>
+        <v>2.98</v>
       </c>
       <c r="O5">
-        <v>1.26</v>
+        <v>1.04</v>
       </c>
       <c r="P5">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="Q5">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="R5">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="S5">
-        <v>3</v>
+        <v>2.52</v>
       </c>
       <c r="T5">
-        <v>1.94</v>
+        <v>1.11</v>
       </c>
       <c r="U5">
-        <v>1.78</v>
+        <v>1.11</v>
       </c>
       <c r="V5">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="W5">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="X5">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Y5">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Z5">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA5">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC5">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD5">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AE5">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AF5">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG5">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH5">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI5">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ5">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AK5">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AL5">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM5">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN5">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AO5">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AP5">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR5">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS5">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AT5">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="AU5">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AV5">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW5">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AX5">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY5">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BA5">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BB5">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BC5">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BD5">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE5">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BF5">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG5">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BH5">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>2.66</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN5">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>2.74</v>
+        <v>1.04</v>
       </c>
       <c r="BP5">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BR5">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT5">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5">
         <v>0</v>
@@ -1974,217 +1974,217 @@
         <v>4.3</v>
       </c>
       <c r="G6">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="H6">
         <v>1.76</v>
       </c>
       <c r="I6">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="J6">
         <v>3.5</v>
       </c>
       <c r="K6">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="L6">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N6">
         <v>3.5</v>
       </c>
       <c r="O6">
-        <v>1.32</v>
+        <v>1.05</v>
       </c>
       <c r="P6">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q6">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R6">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="S6">
         <v>3.1</v>
       </c>
       <c r="T6">
-        <v>1.73</v>
+        <v>1.11</v>
       </c>
       <c r="U6">
-        <v>1.95</v>
+        <v>1.11</v>
       </c>
       <c r="V6">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="W6">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X6">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Y6">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Z6">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AC6">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD6">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE6">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AG6">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AH6">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="AR6">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AU6">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="AV6">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="AW6">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AY6">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BA6">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BC6">
+        <v>1.01</v>
+      </c>
+      <c r="BD6">
+        <v>1.01</v>
+      </c>
+      <c r="BE6">
+        <v>1.01</v>
+      </c>
+      <c r="BF6">
+        <v>1.01</v>
+      </c>
+      <c r="BG6">
+        <v>1.01</v>
+      </c>
+      <c r="BH6">
         <v>4</v>
       </c>
-      <c r="BD6">
-        <v>4</v>
-      </c>
-      <c r="BE6">
-        <v>4.1</v>
-      </c>
-      <c r="BF6">
-        <v>4.1</v>
-      </c>
-      <c r="BG6">
-        <v>3.35</v>
-      </c>
-      <c r="BH6">
-        <v>1000</v>
-      </c>
       <c r="BI6">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="BJ6">
         <v>1000</v>
       </c>
       <c r="BK6">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="BN6">
         <v>1000</v>
       </c>
       <c r="BO6">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="BT6">
         <v>1000</v>
       </c>
       <c r="BU6">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="BZ6">
         <v>0</v>
@@ -2213,37 +2213,37 @@
         <v>121</v>
       </c>
       <c r="F7">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="G7">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="H7">
         <v>1.97</v>
       </c>
       <c r="I7">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="J7">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="K7">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="L7">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="O7">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="P7">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="Q7">
         <v>1.58</v>
@@ -2252,187 +2252,187 @@
         <v>1.57</v>
       </c>
       <c r="S7">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="T7">
-        <v>1.55</v>
+        <v>1.12</v>
       </c>
       <c r="U7">
-        <v>2.46</v>
+        <v>1.12</v>
       </c>
       <c r="V7">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="W7">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="X7">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="Y7">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Z7">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AA7">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AC7">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD7">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE7">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AF7">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AG7">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AH7">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI7">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AJ7">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AK7">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AL7">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM7">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AN7">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AO7">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AP7">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR7">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AS7">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT7">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AU7">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV7">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AW7">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX7">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY7">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BA7">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB7">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BC7">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD7">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BE7">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BF7">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH7">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP7">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="s">
         <v>131</v>
@@ -2455,166 +2455,166 @@
         <v>122</v>
       </c>
       <c r="F8">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="G8">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="H8">
-        <v>16.5</v>
+        <v>10</v>
       </c>
       <c r="I8">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="J8">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="K8">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="L8">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="M8">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N8">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="O8">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P8">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="Q8">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="R8">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="S8">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="T8">
-        <v>2.68</v>
+        <v>1.12</v>
       </c>
       <c r="U8">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="V8">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W8">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="X8">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
         <v>1000</v>
       </c>
       <c r="AB8">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
         <v>1000</v>
       </c>
       <c r="AF8">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>490</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>550</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2697,226 +2697,226 @@
         <v>123</v>
       </c>
       <c r="F9">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="G9">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H9">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="I9">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="J9">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="K9">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="L9">
         <v>1.51</v>
       </c>
       <c r="M9">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N9">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="O9">
         <v>1.57</v>
       </c>
       <c r="P9">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="Q9">
         <v>2.8</v>
       </c>
       <c r="R9">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="S9">
         <v>5.5</v>
       </c>
       <c r="T9">
-        <v>2.16</v>
+        <v>1.11</v>
       </c>
       <c r="U9">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="V9">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W9">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X9">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="Y9">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="Z9">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AA9">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC9">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD9">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE9">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF9">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AG9">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AH9">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI9">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AK9">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AL9">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AM9">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AO9">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AP9">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BH9">
-        <v>2.96</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>2.16</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BN9">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BP9">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BT9">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="BV9">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BX9">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="s">
         <v>131</v>
@@ -2939,226 +2939,226 @@
         <v>124</v>
       </c>
       <c r="F10">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="G10">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H10">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="I10">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J10">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="K10">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="L10">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="M10">
+        <v>1.09</v>
+      </c>
+      <c r="N10">
+        <v>2.5</v>
+      </c>
+      <c r="O10">
+        <v>1.37</v>
+      </c>
+      <c r="P10">
+        <v>1.47</v>
+      </c>
+      <c r="Q10">
+        <v>2.14</v>
+      </c>
+      <c r="R10">
+        <v>1.12</v>
+      </c>
+      <c r="S10">
+        <v>2.14</v>
+      </c>
+      <c r="T10">
         <v>1.11</v>
       </c>
-      <c r="N10">
-        <v>2.46</v>
-      </c>
-      <c r="O10">
-        <v>1.4</v>
-      </c>
-      <c r="P10">
-        <v>1.5</v>
-      </c>
-      <c r="Q10">
-        <v>2.28</v>
-      </c>
-      <c r="R10">
-        <v>1.21</v>
-      </c>
-      <c r="S10">
-        <v>1.05</v>
-      </c>
-      <c r="T10">
-        <v>2.2</v>
-      </c>
       <c r="U10">
-        <v>1.59</v>
+        <v>1.11</v>
       </c>
       <c r="V10">
         <v>1.15</v>
       </c>
       <c r="W10">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="X10">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y10">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Z10">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA10">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AB10">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AC10">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD10">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AE10">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF10">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG10">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH10">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI10">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AK10">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL10">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM10">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AN10">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AO10">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AP10">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AR10">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AS10">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>2.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU10">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="AV10">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AW10">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AX10">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY10">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BA10">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BB10">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BC10">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BD10">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE10">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BF10">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BG10">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH10">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>2.34</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BN10">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>2.46</v>
+        <v>1.04</v>
       </c>
       <c r="BP10">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="BR10">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT10">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="s">
         <v>131</v>
@@ -3181,22 +3181,22 @@
         <v>125</v>
       </c>
       <c r="F11">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G11">
         <v>2.04</v>
       </c>
       <c r="H11">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I11">
         <v>4.5</v>
       </c>
       <c r="J11">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K11">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L11">
         <v>1.51</v>
@@ -3217,7 +3217,7 @@
         <v>2.3</v>
       </c>
       <c r="R11">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S11">
         <v>4.4</v>
@@ -3226,7 +3226,7 @@
         <v>2.02</v>
       </c>
       <c r="U11">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V11">
         <v>1.28</v>
@@ -3268,7 +3268,7 @@
         <v>22</v>
       </c>
       <c r="AI11">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ11">
         <v>24</v>
@@ -3277,16 +3277,16 @@
         <v>24</v>
       </c>
       <c r="AL11">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM11">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
         <v>18.5</v>
       </c>
       <c r="AO11">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP11">
         <v>10</v>
@@ -3298,19 +3298,19 @@
         <v>27</v>
       </c>
       <c r="AS11">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="AT11">
         <v>7.2</v>
       </c>
       <c r="AU11">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV11">
         <v>16.5</v>
       </c>
       <c r="AW11">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AX11">
         <v>10.5</v>
@@ -3322,10 +3322,10 @@
         <v>19.5</v>
       </c>
       <c r="BA11">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="BB11">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC11">
         <v>22</v>
@@ -3334,73 +3334,73 @@
         <v>42</v>
       </c>
       <c r="BE11">
-        <v>44</v>
+        <v>18.5</v>
       </c>
       <c r="BF11">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BG11">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="BH11">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>2.8</v>
+        <v>1.46</v>
       </c>
       <c r="BJ11">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>9.6</v>
+        <v>2.64</v>
       </c>
       <c r="BL11">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="BM11">
         <v>36</v>
       </c>
       <c r="BN11">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="BP11">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>6.2</v>
+        <v>2.64</v>
       </c>
       <c r="BR11">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>8</v>
+        <v>13.5</v>
       </c>
       <c r="BT11">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>7</v>
+        <v>2.02</v>
       </c>
       <c r="BV11">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>7.8</v>
+        <v>14.5</v>
       </c>
       <c r="BX11">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>8.199999999999999</v>
+        <v>15.5</v>
       </c>
       <c r="BZ11">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>7.4</v>
+        <v>12</v>
       </c>
       <c r="CB11" t="s">
         <v>131</v>
@@ -3423,52 +3423,52 @@
         <v>126</v>
       </c>
       <c r="F12">
-        <v>1.6</v>
+        <v>1.09</v>
       </c>
       <c r="G12">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="H12">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="I12">
-        <v>5.9</v>
+        <v>870</v>
       </c>
       <c r="J12">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="K12">
-        <v>5</v>
+        <v>950</v>
       </c>
       <c r="L12">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="M12">
         <v>1.03</v>
       </c>
       <c r="N12">
-        <v>5.2</v>
+        <v>2.18</v>
       </c>
       <c r="O12">
         <v>1.18</v>
       </c>
       <c r="P12">
-        <v>2.44</v>
+        <v>2.18</v>
       </c>
       <c r="Q12">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="R12">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="S12">
-        <v>2.46</v>
+        <v>2.12</v>
       </c>
       <c r="T12">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="U12">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="V12">
         <v>1.01</v>
@@ -3477,112 +3477,112 @@
         <v>1.01</v>
       </c>
       <c r="X12">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="Y12">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="Z12">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA12">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB12">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC12">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AD12">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AE12">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF12">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AG12">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH12">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI12">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AK12">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AL12">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM12">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN12">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AO12">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP12">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AR12">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AS12">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT12">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU12">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AV12">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW12">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AX12">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY12">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA12">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BB12">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BC12">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD12">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BE12">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF12">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG12">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3665,19 +3665,19 @@
         <v>127</v>
       </c>
       <c r="F13">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="G13">
-        <v>990</v>
+        <v>1.56</v>
       </c>
       <c r="H13">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="I13">
         <v>990</v>
       </c>
       <c r="J13">
-        <v>1.19</v>
+        <v>4.3</v>
       </c>
       <c r="K13">
         <v>950</v>
@@ -3689,22 +3689,22 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>1.26</v>
+        <v>2.36</v>
       </c>
       <c r="O13">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="P13">
-        <v>1.25</v>
+        <v>2.36</v>
       </c>
       <c r="Q13">
-        <v>1.09</v>
+        <v>1.35</v>
       </c>
       <c r="R13">
-        <v>1.18</v>
+        <v>1.65</v>
       </c>
       <c r="S13">
-        <v>1.09</v>
+        <v>1.81</v>
       </c>
       <c r="T13">
         <v>1.11</v>
@@ -3716,7 +3716,7 @@
         <v>1.01</v>
       </c>
       <c r="W13">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -3907,19 +3907,19 @@
         <v>128</v>
       </c>
       <c r="F14">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="G14">
         <v>1.34</v>
       </c>
       <c r="H14">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="I14">
         <v>11</v>
       </c>
       <c r="J14">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="K14">
         <v>6.6</v>
@@ -3931,49 +3931,49 @@
         <v>1.03</v>
       </c>
       <c r="N14">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O14">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P14">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="Q14">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="R14">
         <v>1.79</v>
       </c>
       <c r="S14">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T14">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U14">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V14">
         <v>1.1</v>
       </c>
       <c r="W14">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="X14">
         <v>32</v>
       </c>
       <c r="Y14">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="Z14">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AA14">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="AB14">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC14">
         <v>14.5</v>
@@ -3982,7 +3982,7 @@
         <v>38</v>
       </c>
       <c r="AE14">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AF14">
         <v>9.6</v>
@@ -3991,28 +3991,28 @@
         <v>10.5</v>
       </c>
       <c r="AH14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI14">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ14">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AK14">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AL14">
         <v>28</v>
       </c>
       <c r="AM14">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN14">
         <v>4.2</v>
       </c>
       <c r="AO14">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AP14">
         <v>29</v>
@@ -4021,10 +4021,10 @@
         <v>38</v>
       </c>
       <c r="AR14">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AS14">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="AT14">
         <v>11.5</v>
@@ -4036,7 +4036,7 @@
         <v>34</v>
       </c>
       <c r="AW14">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="AX14">
         <v>9.199999999999999</v>
@@ -4048,85 +4048,85 @@
         <v>23</v>
       </c>
       <c r="BA14">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="BB14">
         <v>10.5</v>
       </c>
       <c r="BC14">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BD14">
         <v>26</v>
       </c>
       <c r="BE14">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="BF14">
         <v>4</v>
       </c>
       <c r="BG14">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BH14">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BI14">
-        <v>4.4</v>
+        <v>1.54</v>
       </c>
       <c r="BJ14">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
-        <v>9.6</v>
+        <v>2.08</v>
       </c>
       <c r="BL14">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="BM14">
-        <v>5.9</v>
+        <v>24</v>
       </c>
       <c r="BN14">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BO14">
-        <v>3.85</v>
+        <v>1.46</v>
       </c>
       <c r="BP14">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>6.8</v>
+        <v>1.65</v>
       </c>
       <c r="BR14">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>14.5</v>
+        <v>2.08</v>
       </c>
       <c r="BT14">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
-        <v>11</v>
+        <v>2.08</v>
       </c>
       <c r="BV14">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
-        <v>5.8</v>
+        <v>18</v>
       </c>
       <c r="BX14">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BY14">
-        <v>6</v>
+        <v>17.5</v>
       </c>
       <c r="BZ14">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="CB14" t="s">
         <v>131</v>
@@ -4149,22 +4149,22 @@
         <v>129</v>
       </c>
       <c r="F15">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="G15">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H15">
         <v>6.8</v>
       </c>
       <c r="I15">
-        <v>11.5</v>
+        <v>19.5</v>
       </c>
       <c r="J15">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K15">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="L15">
         <v>1.44</v>
@@ -4173,22 +4173,22 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="O15">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="P15">
         <v>1.52</v>
       </c>
       <c r="Q15">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="R15">
         <v>1.12</v>
       </c>
       <c r="S15">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="T15">
         <v>1.11</v>
@@ -4197,64 +4197,64 @@
         <v>1.11</v>
       </c>
       <c r="V15">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="W15">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="X15">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y15">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Z15">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AA15">
-        <v>510</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="AC15">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD15">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AE15">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AG15">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH15">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AI15">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AK15">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL15">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM15">
-        <v>390</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AO15">
-        <v>590</v>
+        <v>1000</v>
       </c>
       <c r="AP15">
         <v>1.01</v>
@@ -4391,226 +4391,226 @@
         <v>130</v>
       </c>
       <c r="F16">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="G16">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="H16">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="I16">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="J16">
-        <v>3</v>
+        <v>2.64</v>
       </c>
       <c r="K16">
         <v>3.4</v>
       </c>
       <c r="L16">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M16">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N16">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="O16">
         <v>1.43</v>
       </c>
       <c r="P16">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Q16">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="R16">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S16">
-        <v>4.5</v>
+        <v>2.68</v>
       </c>
       <c r="T16">
-        <v>1.98</v>
+        <v>1.11</v>
       </c>
       <c r="U16">
         <v>1.89</v>
       </c>
       <c r="V16">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="W16">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="X16">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="Z16">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AA16">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AB16">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC16">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD16">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE16">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AF16">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AG16">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AH16">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI16">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ16">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AK16">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AL16">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM16">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN16">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AO16">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AP16">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR16">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS16">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT16">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU16">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV16">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW16">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AX16">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY16">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA16">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB16">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC16">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD16">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE16">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BF16">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG16">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BH16">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>2.44</v>
+        <v>1.04</v>
       </c>
       <c r="BJ16">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BN16">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP16">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BR16">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BT16">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="BV16">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX16">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="CB16" t="s">
         <v>131</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="147">
   <si>
     <t>League</t>
   </si>
@@ -280,6 +280,12 @@
     <t>Bolivian Liga de Futbol Profesional</t>
   </si>
   <si>
+    <t>Icelandic 2 Deild</t>
+  </si>
+  <si>
+    <t>Ecuadorian Serie B</t>
+  </si>
+  <si>
     <t>2026-08-27</t>
   </si>
   <si>
@@ -301,6 +307,9 @@
     <t>17:00:00</t>
   </si>
   <si>
+    <t>17:50:00</t>
+  </si>
+  <si>
     <t>18:00:00</t>
   </si>
   <si>
@@ -316,6 +325,12 @@
     <t>20:00:00</t>
   </si>
   <si>
+    <t>20:30:00</t>
+  </si>
+  <si>
+    <t>22:30:00</t>
+  </si>
+  <si>
     <t>23:10:00</t>
   </si>
   <si>
@@ -343,6 +358,9 @@
     <t>Al Mokawloon</t>
   </si>
   <si>
+    <t>Al-Jndal</t>
+  </si>
+  <si>
     <t>ES Setif</t>
   </si>
   <si>
@@ -361,6 +379,18 @@
     <t>MC Alger</t>
   </si>
   <si>
+    <t>Hviti Riddarinn</t>
+  </si>
+  <si>
+    <t>Vinotinto Ecuador</t>
+  </si>
+  <si>
+    <t>22 de Julio FC</t>
+  </si>
+  <si>
+    <t>Club Independiente Petrolero</t>
+  </si>
+  <si>
     <t>Llaneros FC</t>
   </si>
   <si>
@@ -388,6 +418,9 @@
     <t>Al-Masry</t>
   </si>
   <si>
+    <t>Al-Saqer FC</t>
+  </si>
+  <si>
     <t>ES Ben Aknoun</t>
   </si>
   <si>
@@ -406,10 +439,22 @@
     <t>MC Oran</t>
   </si>
   <si>
+    <t>Fjolnir</t>
+  </si>
+  <si>
+    <t>Atletico Rojiblanco</t>
+  </si>
+  <si>
+    <t>Deportivo Santo Domingo</t>
+  </si>
+  <si>
+    <t>Guabira</t>
+  </si>
+  <si>
     <t>Millonarios</t>
   </si>
   <si>
-    <t>2026-08-26 10:23:20</t>
+    <t>2026-08-26 12:32:50</t>
   </si>
 </sst>
 </file>
@@ -741,7 +786,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB16"/>
+  <dimension ref="A1:CB21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -991,31 +1036,31 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E2" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="F2">
         <v>1.63</v>
       </c>
       <c r="G2">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="H2">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="I2">
         <v>6.8</v>
       </c>
       <c r="J2">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K2">
         <v>4.3</v>
@@ -1045,7 +1090,7 @@
         <v>3.95</v>
       </c>
       <c r="T2">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="U2">
         <v>1.83</v>
@@ -1054,178 +1099,178 @@
         <v>1.17</v>
       </c>
       <c r="W2">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y2">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AB2">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF2">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AG2">
+        <v>10.5</v>
+      </c>
+      <c r="AH2">
+        <v>25</v>
+      </c>
+      <c r="AI2">
+        <v>130</v>
+      </c>
+      <c r="AJ2">
+        <v>16</v>
+      </c>
+      <c r="AK2">
+        <v>19.5</v>
+      </c>
+      <c r="AL2">
+        <v>46</v>
+      </c>
+      <c r="AM2">
+        <v>190</v>
+      </c>
+      <c r="AN2">
+        <v>11.5</v>
+      </c>
+      <c r="AO2">
+        <v>210</v>
+      </c>
+      <c r="AP2">
+        <v>11</v>
+      </c>
+      <c r="AQ2">
+        <v>17.5</v>
+      </c>
+      <c r="AR2">
+        <v>40</v>
+      </c>
+      <c r="AS2">
+        <v>10</v>
+      </c>
+      <c r="AT2">
+        <v>6.2</v>
+      </c>
+      <c r="AU2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV2">
+        <v>19.5</v>
+      </c>
+      <c r="AW2">
+        <v>9.6</v>
+      </c>
+      <c r="AX2">
+        <v>7.8</v>
+      </c>
+      <c r="AY2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ2">
+        <v>21</v>
+      </c>
+      <c r="BA2">
+        <v>9.6</v>
+      </c>
+      <c r="BB2">
         <v>13</v>
       </c>
-      <c r="AH2">
-        <v>1000</v>
-      </c>
-      <c r="AI2">
-        <v>1000</v>
-      </c>
-      <c r="AJ2">
-        <v>1000</v>
-      </c>
-      <c r="AK2">
-        <v>22</v>
-      </c>
-      <c r="AL2">
-        <v>1000</v>
-      </c>
-      <c r="AM2">
-        <v>1000</v>
-      </c>
-      <c r="AN2">
-        <v>1000</v>
-      </c>
-      <c r="AO2">
-        <v>1000</v>
-      </c>
-      <c r="AP2">
-        <v>1.63</v>
-      </c>
-      <c r="AQ2">
-        <v>1.54</v>
-      </c>
-      <c r="AR2">
-        <v>1.63</v>
-      </c>
-      <c r="AS2">
-        <v>1.63</v>
-      </c>
-      <c r="AT2">
-        <v>1.37</v>
-      </c>
-      <c r="AU2">
+      <c r="BC2">
+        <v>16</v>
+      </c>
+      <c r="BD2">
+        <v>27</v>
+      </c>
+      <c r="BE2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF2">
+        <v>9.4</v>
+      </c>
+      <c r="BG2">
+        <v>10</v>
+      </c>
+      <c r="BH2">
+        <v>3.4</v>
+      </c>
+      <c r="BI2">
+        <v>2.74</v>
+      </c>
+      <c r="BJ2">
+        <v>12</v>
+      </c>
+      <c r="BK2">
+        <v>5.6</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>10</v>
+      </c>
+      <c r="BN2">
+        <v>4.1</v>
+      </c>
+      <c r="BO2">
+        <v>3.25</v>
+      </c>
+      <c r="BP2">
+        <v>11.5</v>
+      </c>
+      <c r="BQ2">
+        <v>5.5</v>
+      </c>
+      <c r="BR2">
+        <v>30</v>
+      </c>
+      <c r="BS2">
+        <v>7.8</v>
+      </c>
+      <c r="BT2">
+        <v>11</v>
+      </c>
+      <c r="BU2">
+        <v>5.4</v>
+      </c>
+      <c r="BV2">
+        <v>70</v>
+      </c>
+      <c r="BW2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BX2">
+        <v>75</v>
+      </c>
+      <c r="BY2">
+        <v>9.4</v>
+      </c>
+      <c r="BZ2">
+        <v>24</v>
+      </c>
+      <c r="CA2">
         <v>7.4</v>
       </c>
-      <c r="AV2">
-        <v>19</v>
-      </c>
-      <c r="AW2">
-        <v>1.63</v>
-      </c>
-      <c r="AX2">
-        <v>1.39</v>
-      </c>
-      <c r="AY2">
-        <v>1.72</v>
-      </c>
-      <c r="AZ2">
-        <v>18.5</v>
-      </c>
-      <c r="BA2">
-        <v>1.63</v>
-      </c>
-      <c r="BB2">
-        <v>1.63</v>
-      </c>
-      <c r="BC2">
-        <v>1.52</v>
-      </c>
-      <c r="BD2">
-        <v>1.63</v>
-      </c>
-      <c r="BE2">
-        <v>1.63</v>
-      </c>
-      <c r="BF2">
-        <v>1.63</v>
-      </c>
-      <c r="BG2">
-        <v>1.63</v>
-      </c>
-      <c r="BH2">
-        <v>1000</v>
-      </c>
-      <c r="BI2">
-        <v>1.04</v>
-      </c>
-      <c r="BJ2">
-        <v>1000</v>
-      </c>
-      <c r="BK2">
-        <v>1.04</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>1.04</v>
-      </c>
-      <c r="BN2">
-        <v>1000</v>
-      </c>
-      <c r="BO2">
-        <v>1.04</v>
-      </c>
-      <c r="BP2">
-        <v>1000</v>
-      </c>
-      <c r="BQ2">
-        <v>1.04</v>
-      </c>
-      <c r="BR2">
-        <v>1000</v>
-      </c>
-      <c r="BS2">
-        <v>1.04</v>
-      </c>
-      <c r="BT2">
-        <v>1000</v>
-      </c>
-      <c r="BU2">
-        <v>1.04</v>
-      </c>
-      <c r="BV2">
-        <v>1000</v>
-      </c>
-      <c r="BW2">
-        <v>1.04</v>
-      </c>
-      <c r="BX2">
-        <v>1000</v>
-      </c>
-      <c r="BY2">
-        <v>1.04</v>
-      </c>
-      <c r="BZ2">
-        <v>1000</v>
-      </c>
-      <c r="CA2">
-        <v>1.04</v>
-      </c>
       <c r="CB2" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1233,76 +1278,76 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E3" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="F3">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="G3">
-        <v>2.54</v>
+        <v>2.8</v>
       </c>
       <c r="H3">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I3">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="J3">
         <v>2.42</v>
       </c>
       <c r="K3">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="L3">
         <v>1.6</v>
       </c>
       <c r="M3">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="N3">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="O3">
-        <v>1.72</v>
+        <v>1.42</v>
       </c>
       <c r="P3">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Q3">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="R3">
         <v>1.09</v>
       </c>
       <c r="S3">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="T3">
         <v>2.16</v>
       </c>
       <c r="U3">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V3">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W3">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="X3">
         <v>1000</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z3">
         <v>1000</v>
@@ -1311,22 +1356,22 @@
         <v>1000</v>
       </c>
       <c r="AB3">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC3">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE3">
         <v>1000</v>
       </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG3">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH3">
         <v>1000</v>
@@ -1353,58 +1398,58 @@
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="AQ3">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AR3">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="AS3">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="AT3">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AU3">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AV3">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="AW3">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="AX3">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AY3">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ3">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="BA3">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="BB3">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="BC3">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="BD3">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="BE3">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BF3">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="BG3">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1467,7 +1512,7 @@
         <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1475,241 +1520,241 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E4" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F4">
-        <v>2.38</v>
+        <v>2.64</v>
       </c>
       <c r="G4">
+        <v>2.98</v>
+      </c>
+      <c r="H4">
+        <v>2.42</v>
+      </c>
+      <c r="I4">
+        <v>2.72</v>
+      </c>
+      <c r="J4">
+        <v>3.8</v>
+      </c>
+      <c r="K4">
+        <v>4.4</v>
+      </c>
+      <c r="L4">
+        <v>1.26</v>
+      </c>
+      <c r="M4">
+        <v>1.01</v>
+      </c>
+      <c r="N4">
+        <v>4.7</v>
+      </c>
+      <c r="O4">
+        <v>1.19</v>
+      </c>
+      <c r="P4">
+        <v>2.36</v>
+      </c>
+      <c r="Q4">
+        <v>1.58</v>
+      </c>
+      <c r="R4">
+        <v>1.55</v>
+      </c>
+      <c r="S4">
+        <v>2.44</v>
+      </c>
+      <c r="T4">
+        <v>1.53</v>
+      </c>
+      <c r="U4">
+        <v>2.48</v>
+      </c>
+      <c r="V4">
+        <v>1.58</v>
+      </c>
+      <c r="W4">
+        <v>1.5</v>
+      </c>
+      <c r="X4">
+        <v>24</v>
+      </c>
+      <c r="Y4">
+        <v>16</v>
+      </c>
+      <c r="Z4">
+        <v>23</v>
+      </c>
+      <c r="AA4">
+        <v>42</v>
+      </c>
+      <c r="AB4">
+        <v>17</v>
+      </c>
+      <c r="AC4">
+        <v>10</v>
+      </c>
+      <c r="AD4">
+        <v>14.5</v>
+      </c>
+      <c r="AE4">
+        <v>28</v>
+      </c>
+      <c r="AF4">
+        <v>25</v>
+      </c>
+      <c r="AG4">
+        <v>14</v>
+      </c>
+      <c r="AH4">
+        <v>17</v>
+      </c>
+      <c r="AI4">
+        <v>36</v>
+      </c>
+      <c r="AJ4">
+        <v>44</v>
+      </c>
+      <c r="AK4">
+        <v>32</v>
+      </c>
+      <c r="AL4">
+        <v>34</v>
+      </c>
+      <c r="AM4">
+        <v>70</v>
+      </c>
+      <c r="AN4">
+        <v>19</v>
+      </c>
+      <c r="AO4">
+        <v>17</v>
+      </c>
+      <c r="AP4">
+        <v>19.5</v>
+      </c>
+      <c r="AQ4">
+        <v>12</v>
+      </c>
+      <c r="AR4">
+        <v>16.5</v>
+      </c>
+      <c r="AS4">
+        <v>5.5</v>
+      </c>
+      <c r="AT4">
+        <v>13.5</v>
+      </c>
+      <c r="AU4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV4">
+        <v>10.5</v>
+      </c>
+      <c r="AW4">
+        <v>20</v>
+      </c>
+      <c r="AX4">
+        <v>16.5</v>
+      </c>
+      <c r="AY4">
+        <v>11</v>
+      </c>
+      <c r="AZ4">
+        <v>12.5</v>
+      </c>
+      <c r="BA4">
+        <v>25</v>
+      </c>
+      <c r="BB4">
+        <v>34</v>
+      </c>
+      <c r="BC4">
+        <v>20</v>
+      </c>
+      <c r="BD4">
+        <v>27</v>
+      </c>
+      <c r="BE4">
+        <v>5.8</v>
+      </c>
+      <c r="BF4">
+        <v>14</v>
+      </c>
+      <c r="BG4">
+        <v>11</v>
+      </c>
+      <c r="BH4">
+        <v>4.8</v>
+      </c>
+      <c r="BI4">
         <v>3.45</v>
       </c>
-      <c r="H4">
-        <v>2.3</v>
-      </c>
-      <c r="I4">
-        <v>3.1</v>
-      </c>
-      <c r="J4">
-        <v>3.35</v>
-      </c>
-      <c r="K4">
-        <v>7</v>
-      </c>
-      <c r="L4">
-        <v>1.01</v>
-      </c>
-      <c r="M4">
-        <v>1.03</v>
-      </c>
-      <c r="N4">
-        <v>4.1</v>
-      </c>
-      <c r="O4">
-        <v>1.17</v>
-      </c>
-      <c r="P4">
-        <v>2.02</v>
-      </c>
-      <c r="Q4">
-        <v>1.5</v>
-      </c>
-      <c r="R4">
-        <v>1.47</v>
-      </c>
-      <c r="S4">
-        <v>2.36</v>
-      </c>
-      <c r="T4">
-        <v>1.11</v>
-      </c>
-      <c r="U4">
-        <v>1.11</v>
-      </c>
-      <c r="V4">
-        <v>1.48</v>
-      </c>
-      <c r="W4">
-        <v>1.41</v>
-      </c>
-      <c r="X4">
-        <v>1000</v>
-      </c>
-      <c r="Y4">
-        <v>1000</v>
-      </c>
-      <c r="Z4">
-        <v>1000</v>
-      </c>
-      <c r="AA4">
-        <v>1000</v>
-      </c>
-      <c r="AB4">
-        <v>1000</v>
-      </c>
-      <c r="AC4">
-        <v>1000</v>
-      </c>
-      <c r="AD4">
-        <v>1000</v>
-      </c>
-      <c r="AE4">
-        <v>1000</v>
-      </c>
-      <c r="AF4">
-        <v>1000</v>
-      </c>
-      <c r="AG4">
-        <v>1000</v>
-      </c>
-      <c r="AH4">
-        <v>1000</v>
-      </c>
-      <c r="AI4">
-        <v>1000</v>
-      </c>
-      <c r="AJ4">
-        <v>1000</v>
-      </c>
-      <c r="AK4">
-        <v>1000</v>
-      </c>
-      <c r="AL4">
-        <v>1000</v>
-      </c>
-      <c r="AM4">
-        <v>1000</v>
-      </c>
-      <c r="AN4">
-        <v>1000</v>
-      </c>
-      <c r="AO4">
-        <v>1000</v>
-      </c>
-      <c r="AP4">
-        <v>1.01</v>
-      </c>
-      <c r="AQ4">
-        <v>1.01</v>
-      </c>
-      <c r="AR4">
-        <v>1.01</v>
-      </c>
-      <c r="AS4">
-        <v>1.01</v>
-      </c>
-      <c r="AT4">
-        <v>1.01</v>
-      </c>
-      <c r="AU4">
-        <v>1.01</v>
-      </c>
-      <c r="AV4">
-        <v>1.01</v>
-      </c>
-      <c r="AW4">
-        <v>1.01</v>
-      </c>
-      <c r="AX4">
-        <v>1.01</v>
-      </c>
-      <c r="AY4">
-        <v>1.01</v>
-      </c>
-      <c r="AZ4">
-        <v>1.01</v>
-      </c>
-      <c r="BA4">
-        <v>1.01</v>
-      </c>
-      <c r="BB4">
-        <v>1.01</v>
-      </c>
-      <c r="BC4">
-        <v>1.01</v>
-      </c>
-      <c r="BD4">
-        <v>1.01</v>
-      </c>
-      <c r="BE4">
-        <v>1.01</v>
-      </c>
-      <c r="BF4">
-        <v>1.01</v>
-      </c>
-      <c r="BG4">
-        <v>1.01</v>
-      </c>
-      <c r="BH4">
-        <v>1000</v>
-      </c>
-      <c r="BI4">
-        <v>1.04</v>
-      </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK4">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM4">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO4">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ4">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS4">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU4">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="CA4">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="CB4" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1717,232 +1762,232 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="F5">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="G5">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="H5">
         <v>5.8</v>
       </c>
       <c r="I5">
-        <v>14.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J5">
         <v>3.85</v>
       </c>
       <c r="K5">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="L5">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="M5">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N5">
-        <v>2.98</v>
+        <v>3.4</v>
       </c>
       <c r="O5">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="P5">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="Q5">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="R5">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="S5">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="T5">
-        <v>1.11</v>
+        <v>1.95</v>
       </c>
       <c r="U5">
-        <v>1.11</v>
+        <v>1.77</v>
       </c>
       <c r="V5">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="W5">
-        <v>2.32</v>
+        <v>2.54</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y5">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z5">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AB5">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC5">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD5">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE5">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF5">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG5">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH5">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ5">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AK5">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL5">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN5">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AP5">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AQ5">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR5">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AS5">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT5">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AU5">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AV5">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AW5">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX5">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AY5">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AZ5">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA5">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB5">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BC5">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD5">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE5">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF5">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BG5">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BI5">
-        <v>1.04</v>
+        <v>2.9</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK5">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO5">
-        <v>1.04</v>
+        <v>2.5</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ5">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS5">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU5">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BZ5">
         <v>0</v>
@@ -1951,7 +1996,7 @@
         <v>0</v>
       </c>
       <c r="CB5" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1959,232 +2004,232 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="F6">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="G6">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="H6">
         <v>1.76</v>
       </c>
       <c r="I6">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="J6">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K6">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M6">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N6">
         <v>3.5</v>
       </c>
       <c r="O6">
-        <v>1.05</v>
+        <v>1.27</v>
       </c>
       <c r="P6">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="Q6">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R6">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S6">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="T6">
-        <v>1.11</v>
+        <v>1.73</v>
       </c>
       <c r="U6">
-        <v>1.11</v>
+        <v>1.81</v>
       </c>
       <c r="V6">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="W6">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AB6">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AP6">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ6">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AR6">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AS6">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AT6">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AU6">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV6">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AW6">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AX6">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AY6">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AZ6">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA6">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BB6">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC6">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD6">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE6">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BH6">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="BI6">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK6">
-        <v>1.34</v>
+        <v>3.95</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.34</v>
+        <v>5.5</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BO6">
-        <v>1.34</v>
+        <v>3.65</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BQ6">
-        <v>1.34</v>
+        <v>5.2</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS6">
-        <v>1.34</v>
+        <v>5.3</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BU6">
-        <v>1.34</v>
+        <v>3.4</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BW6">
-        <v>1.34</v>
+        <v>4.2</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY6">
-        <v>1.34</v>
+        <v>4.9</v>
       </c>
       <c r="BZ6">
         <v>0</v>
@@ -2193,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2201,49 +2246,49 @@
         <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D7" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E7" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="F7">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="G7">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="H7">
         <v>1.97</v>
       </c>
       <c r="I7">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="J7">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K7">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N7">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="O7">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="P7">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="Q7">
         <v>1.58</v>
@@ -2252,190 +2297,190 @@
         <v>1.57</v>
       </c>
       <c r="S7">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="T7">
-        <v>1.12</v>
+        <v>1.55</v>
       </c>
       <c r="U7">
-        <v>1.12</v>
+        <v>2.46</v>
       </c>
       <c r="V7">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="W7">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y7">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AB7">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AC7">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF7">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG7">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH7">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI7">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ7">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AK7">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL7">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AP7">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AQ7">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR7">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AS7">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AT7">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AU7">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV7">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AW7">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AX7">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AY7">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AZ7">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BA7">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BB7">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BC7">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BD7">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BE7">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BF7">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BG7">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI7">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK7">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO7">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ7">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS7">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BU7">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BW7">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BY7">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="CA7">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="CB7" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2443,241 +2488,241 @@
         <v>81</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E8" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="F8">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="G8">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="H8">
-        <v>10</v>
+        <v>16.5</v>
       </c>
       <c r="I8">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="J8">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="K8">
-        <v>11</v>
+        <v>6.2</v>
       </c>
       <c r="L8">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="M8">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N8">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="O8">
         <v>1.33</v>
       </c>
       <c r="P8">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="Q8">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="R8">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="S8">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="T8">
-        <v>1.12</v>
+        <v>2.72</v>
       </c>
       <c r="U8">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="V8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W8">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AA8">
         <v>1000</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE8">
         <v>1000</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>530</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO8">
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ8">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AR8">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AS8">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AT8">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AU8">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AV8">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AW8">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX8">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AY8">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ8">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BA8">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BD8">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI8">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BK8">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BO8">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BQ8">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS8">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BU8">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="CA8">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="CB8" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2685,1935 +2730,3145 @@
         <v>81</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E9" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="F9">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="G9">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H9">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I9">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J9">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="K9">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="L9">
         <v>1.51</v>
       </c>
       <c r="M9">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N9">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="O9">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P9">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="Q9">
         <v>2.8</v>
       </c>
       <c r="R9">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="S9">
+        <v>5.7</v>
+      </c>
+      <c r="T9">
+        <v>2.18</v>
+      </c>
+      <c r="U9">
+        <v>1.71</v>
+      </c>
+      <c r="V9">
+        <v>1.64</v>
+      </c>
+      <c r="W9">
+        <v>1.32</v>
+      </c>
+      <c r="X9">
+        <v>9.4</v>
+      </c>
+      <c r="Y9">
+        <v>7.2</v>
+      </c>
+      <c r="Z9">
+        <v>16.5</v>
+      </c>
+      <c r="AA9">
+        <v>46</v>
+      </c>
+      <c r="AB9">
+        <v>12</v>
+      </c>
+      <c r="AC9">
+        <v>7.4</v>
+      </c>
+      <c r="AD9">
+        <v>15.5</v>
+      </c>
+      <c r="AE9">
+        <v>46</v>
+      </c>
+      <c r="AF9">
+        <v>27</v>
+      </c>
+      <c r="AG9">
+        <v>21</v>
+      </c>
+      <c r="AH9">
+        <v>30</v>
+      </c>
+      <c r="AI9">
+        <v>85</v>
+      </c>
+      <c r="AJ9">
+        <v>110</v>
+      </c>
+      <c r="AK9">
+        <v>85</v>
+      </c>
+      <c r="AL9">
+        <v>120</v>
+      </c>
+      <c r="AM9">
+        <v>260</v>
+      </c>
+      <c r="AN9">
+        <v>130</v>
+      </c>
+      <c r="AO9">
+        <v>50</v>
+      </c>
+      <c r="AP9">
+        <v>6</v>
+      </c>
+      <c r="AQ9">
+        <v>5.3</v>
+      </c>
+      <c r="AR9">
+        <v>10</v>
+      </c>
+      <c r="AS9">
+        <v>5</v>
+      </c>
+      <c r="AT9">
+        <v>7.4</v>
+      </c>
+      <c r="AU9">
+        <v>5.4</v>
+      </c>
+      <c r="AV9">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW9">
+        <v>5</v>
+      </c>
+      <c r="AX9">
+        <v>18.5</v>
+      </c>
+      <c r="AY9">
+        <v>12.5</v>
+      </c>
+      <c r="AZ9">
+        <v>18</v>
+      </c>
+      <c r="BA9">
+        <v>5.2</v>
+      </c>
+      <c r="BB9">
+        <v>5.3</v>
+      </c>
+      <c r="BC9">
+        <v>5.2</v>
+      </c>
+      <c r="BD9">
+        <v>5.3</v>
+      </c>
+      <c r="BE9">
         <v>5.5</v>
       </c>
-      <c r="T9">
-        <v>1.11</v>
-      </c>
-      <c r="U9">
-        <v>1.66</v>
-      </c>
-      <c r="V9">
-        <v>1.63</v>
-      </c>
-      <c r="W9">
-        <v>1.3</v>
-      </c>
-      <c r="X9">
-        <v>1000</v>
-      </c>
-      <c r="Y9">
-        <v>1000</v>
-      </c>
-      <c r="Z9">
-        <v>1000</v>
-      </c>
-      <c r="AA9">
-        <v>1000</v>
-      </c>
-      <c r="AB9">
-        <v>1000</v>
-      </c>
-      <c r="AC9">
-        <v>1000</v>
-      </c>
-      <c r="AD9">
-        <v>1000</v>
-      </c>
-      <c r="AE9">
-        <v>1000</v>
-      </c>
-      <c r="AF9">
-        <v>1000</v>
-      </c>
-      <c r="AG9">
-        <v>1000</v>
-      </c>
-      <c r="AH9">
-        <v>1000</v>
-      </c>
-      <c r="AI9">
-        <v>1000</v>
-      </c>
-      <c r="AJ9">
-        <v>1000</v>
-      </c>
-      <c r="AK9">
-        <v>1000</v>
-      </c>
-      <c r="AL9">
-        <v>1000</v>
-      </c>
-      <c r="AM9">
-        <v>1000</v>
-      </c>
-      <c r="AN9">
-        <v>1000</v>
-      </c>
-      <c r="AO9">
-        <v>1000</v>
-      </c>
-      <c r="AP9">
-        <v>1.01</v>
-      </c>
-      <c r="AQ9">
-        <v>1.01</v>
-      </c>
-      <c r="AR9">
-        <v>1.01</v>
-      </c>
-      <c r="AS9">
-        <v>1.01</v>
-      </c>
-      <c r="AT9">
-        <v>1.01</v>
-      </c>
-      <c r="AU9">
-        <v>1.01</v>
-      </c>
-      <c r="AV9">
-        <v>1.01</v>
-      </c>
-      <c r="AW9">
-        <v>1.01</v>
-      </c>
-      <c r="AX9">
-        <v>1.01</v>
-      </c>
-      <c r="AY9">
-        <v>1.01</v>
-      </c>
-      <c r="AZ9">
-        <v>1.01</v>
-      </c>
-      <c r="BA9">
-        <v>1.01</v>
-      </c>
-      <c r="BB9">
-        <v>1.01</v>
-      </c>
-      <c r="BC9">
-        <v>1.01</v>
-      </c>
-      <c r="BD9">
-        <v>1.01</v>
-      </c>
-      <c r="BE9">
-        <v>1.01</v>
-      </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BG9">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH9">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="BI9">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK9">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO9">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BQ9">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU9">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW9">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY9">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="CB9" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E10" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="F10">
-        <v>1.64</v>
+        <v>2.72</v>
       </c>
       <c r="G10">
-        <v>2.06</v>
+        <v>3.1</v>
       </c>
       <c r="H10">
-        <v>5.1</v>
+        <v>2.56</v>
       </c>
       <c r="I10">
-        <v>8.199999999999999</v>
+        <v>2.92</v>
       </c>
       <c r="J10">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="K10">
-        <v>5.2</v>
+        <v>3.7</v>
       </c>
       <c r="L10">
         <v>1.43</v>
       </c>
       <c r="M10">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N10">
+        <v>3.35</v>
+      </c>
+      <c r="O10">
+        <v>1.35</v>
+      </c>
+      <c r="P10">
+        <v>1.74</v>
+      </c>
+      <c r="Q10">
+        <v>1.94</v>
+      </c>
+      <c r="R10">
+        <v>1.3</v>
+      </c>
+      <c r="S10">
+        <v>3.25</v>
+      </c>
+      <c r="T10">
+        <v>1.77</v>
+      </c>
+      <c r="U10">
+        <v>2.04</v>
+      </c>
+      <c r="V10">
+        <v>1.52</v>
+      </c>
+      <c r="W10">
+        <v>1.47</v>
+      </c>
+      <c r="X10">
+        <v>14.5</v>
+      </c>
+      <c r="Y10">
+        <v>12</v>
+      </c>
+      <c r="Z10">
+        <v>21</v>
+      </c>
+      <c r="AA10">
+        <v>50</v>
+      </c>
+      <c r="AB10">
+        <v>12.5</v>
+      </c>
+      <c r="AC10">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD10">
+        <v>14.5</v>
+      </c>
+      <c r="AE10">
+        <v>38</v>
+      </c>
+      <c r="AF10">
+        <v>23</v>
+      </c>
+      <c r="AG10">
+        <v>15</v>
+      </c>
+      <c r="AH10">
+        <v>21</v>
+      </c>
+      <c r="AI10">
+        <v>55</v>
+      </c>
+      <c r="AJ10">
+        <v>55</v>
+      </c>
+      <c r="AK10">
+        <v>40</v>
+      </c>
+      <c r="AL10">
+        <v>55</v>
+      </c>
+      <c r="AM10">
+        <v>120</v>
+      </c>
+      <c r="AN10">
+        <v>38</v>
+      </c>
+      <c r="AO10">
+        <v>34</v>
+      </c>
+      <c r="AP10">
+        <v>1.01</v>
+      </c>
+      <c r="AQ10">
+        <v>1.01</v>
+      </c>
+      <c r="AR10">
+        <v>1.01</v>
+      </c>
+      <c r="AS10">
+        <v>1.01</v>
+      </c>
+      <c r="AT10">
+        <v>1.01</v>
+      </c>
+      <c r="AU10">
+        <v>1.01</v>
+      </c>
+      <c r="AV10">
+        <v>1.01</v>
+      </c>
+      <c r="AW10">
+        <v>1.01</v>
+      </c>
+      <c r="AX10">
+        <v>1.01</v>
+      </c>
+      <c r="AY10">
+        <v>1.01</v>
+      </c>
+      <c r="AZ10">
+        <v>1.01</v>
+      </c>
+      <c r="BA10">
+        <v>1.01</v>
+      </c>
+      <c r="BB10">
+        <v>1.01</v>
+      </c>
+      <c r="BC10">
+        <v>1.01</v>
+      </c>
+      <c r="BD10">
+        <v>1.01</v>
+      </c>
+      <c r="BE10">
+        <v>1.03</v>
+      </c>
+      <c r="BF10">
+        <v>1.01</v>
+      </c>
+      <c r="BG10">
+        <v>1.01</v>
+      </c>
+      <c r="BH10">
+        <v>3.35</v>
+      </c>
+      <c r="BI10">
+        <v>2.86</v>
+      </c>
+      <c r="BJ10">
+        <v>10</v>
+      </c>
+      <c r="BK10">
+        <v>5.1</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
         <v>2.5</v>
       </c>
-      <c r="O10">
-        <v>1.37</v>
-      </c>
-      <c r="P10">
-        <v>1.47</v>
-      </c>
-      <c r="Q10">
-        <v>2.14</v>
-      </c>
-      <c r="R10">
-        <v>1.12</v>
-      </c>
-      <c r="S10">
-        <v>2.14</v>
-      </c>
-      <c r="T10">
-        <v>1.11</v>
-      </c>
-      <c r="U10">
-        <v>1.11</v>
-      </c>
-      <c r="V10">
-        <v>1.15</v>
-      </c>
-      <c r="W10">
-        <v>1.93</v>
-      </c>
-      <c r="X10">
-        <v>1000</v>
-      </c>
-      <c r="Y10">
-        <v>1000</v>
-      </c>
-      <c r="Z10">
-        <v>1000</v>
-      </c>
-      <c r="AA10">
-        <v>1000</v>
-      </c>
-      <c r="AB10">
-        <v>1000</v>
-      </c>
-      <c r="AC10">
-        <v>1000</v>
-      </c>
-      <c r="AD10">
-        <v>1000</v>
-      </c>
-      <c r="AE10">
-        <v>1000</v>
-      </c>
-      <c r="AF10">
-        <v>1000</v>
-      </c>
-      <c r="AG10">
-        <v>1000</v>
-      </c>
-      <c r="AH10">
-        <v>1000</v>
-      </c>
-      <c r="AI10">
-        <v>1000</v>
-      </c>
-      <c r="AJ10">
-        <v>1000</v>
-      </c>
-      <c r="AK10">
-        <v>1000</v>
-      </c>
-      <c r="AL10">
-        <v>1000</v>
-      </c>
-      <c r="AM10">
-        <v>1000</v>
-      </c>
-      <c r="AN10">
-        <v>1000</v>
-      </c>
-      <c r="AO10">
-        <v>1000</v>
-      </c>
-      <c r="AP10">
-        <v>1.01</v>
-      </c>
-      <c r="AQ10">
-        <v>1.01</v>
-      </c>
-      <c r="AR10">
-        <v>1.01</v>
-      </c>
-      <c r="AS10">
-        <v>1.01</v>
-      </c>
-      <c r="AT10">
-        <v>1.01</v>
-      </c>
-      <c r="AU10">
-        <v>1.01</v>
-      </c>
-      <c r="AV10">
-        <v>1.01</v>
-      </c>
-      <c r="AW10">
-        <v>1.01</v>
-      </c>
-      <c r="AX10">
-        <v>1.01</v>
-      </c>
-      <c r="AY10">
-        <v>1.01</v>
-      </c>
-      <c r="AZ10">
-        <v>1.01</v>
-      </c>
-      <c r="BA10">
-        <v>1.01</v>
-      </c>
-      <c r="BB10">
-        <v>1.01</v>
-      </c>
-      <c r="BC10">
-        <v>1.01</v>
-      </c>
-      <c r="BD10">
-        <v>1.01</v>
-      </c>
-      <c r="BE10">
-        <v>1.01</v>
-      </c>
-      <c r="BF10">
-        <v>1.01</v>
-      </c>
-      <c r="BG10">
-        <v>1.01</v>
-      </c>
-      <c r="BH10">
-        <v>1000</v>
-      </c>
-      <c r="BI10">
-        <v>1.04</v>
-      </c>
-      <c r="BJ10">
-        <v>1000</v>
-      </c>
-      <c r="BK10">
-        <v>1.04</v>
-      </c>
-      <c r="BL10">
-        <v>1000</v>
-      </c>
-      <c r="BM10">
-        <v>1.04</v>
-      </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO10">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ10">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU10">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW10">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="CB10" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E11" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="G11">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="H11">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="I11">
+        <v>7.6</v>
+      </c>
+      <c r="J11">
+        <v>3.1</v>
+      </c>
+      <c r="K11">
+        <v>3.7</v>
+      </c>
+      <c r="L11">
+        <v>1.52</v>
+      </c>
+      <c r="M11">
+        <v>1.11</v>
+      </c>
+      <c r="N11">
+        <v>2.48</v>
+      </c>
+      <c r="O11">
+        <v>1.47</v>
+      </c>
+      <c r="P11">
+        <v>1.59</v>
+      </c>
+      <c r="Q11">
+        <v>2.38</v>
+      </c>
+      <c r="R11">
+        <v>1.21</v>
+      </c>
+      <c r="S11">
+        <v>3.9</v>
+      </c>
+      <c r="T11">
+        <v>1.99</v>
+      </c>
+      <c r="U11">
+        <v>1.71</v>
+      </c>
+      <c r="V11">
+        <v>1.15</v>
+      </c>
+      <c r="W11">
+        <v>2.12</v>
+      </c>
+      <c r="X11">
+        <v>12</v>
+      </c>
+      <c r="Y11">
+        <v>15.5</v>
+      </c>
+      <c r="Z11">
+        <v>60</v>
+      </c>
+      <c r="AA11">
+        <v>250</v>
+      </c>
+      <c r="AB11">
+        <v>6.6</v>
+      </c>
+      <c r="AC11">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD11">
+        <v>950</v>
+      </c>
+      <c r="AE11">
+        <v>140</v>
+      </c>
+      <c r="AF11">
+        <v>9.6</v>
+      </c>
+      <c r="AG11">
+        <v>13</v>
+      </c>
+      <c r="AH11">
+        <v>950</v>
+      </c>
+      <c r="AI11">
+        <v>160</v>
+      </c>
+      <c r="AJ11">
+        <v>20</v>
+      </c>
+      <c r="AK11">
+        <v>29</v>
+      </c>
+      <c r="AL11">
+        <v>70</v>
+      </c>
+      <c r="AM11">
+        <v>260</v>
+      </c>
+      <c r="AN11">
+        <v>23</v>
+      </c>
+      <c r="AO11">
+        <v>250</v>
+      </c>
+      <c r="AP11">
         <v>4.5</v>
       </c>
-      <c r="J11">
-        <v>3.55</v>
-      </c>
-      <c r="K11">
-        <v>3.6</v>
-      </c>
-      <c r="L11">
-        <v>1.51</v>
-      </c>
-      <c r="M11">
-        <v>1.09</v>
-      </c>
-      <c r="N11">
-        <v>3.25</v>
-      </c>
-      <c r="O11">
-        <v>1.42</v>
-      </c>
-      <c r="P11">
-        <v>1.75</v>
-      </c>
-      <c r="Q11">
-        <v>2.3</v>
-      </c>
-      <c r="R11">
-        <v>1.27</v>
-      </c>
-      <c r="S11">
-        <v>4.4</v>
-      </c>
-      <c r="T11">
-        <v>2.02</v>
-      </c>
-      <c r="U11">
-        <v>1.92</v>
-      </c>
-      <c r="V11">
-        <v>1.28</v>
-      </c>
-      <c r="W11">
-        <v>1.96</v>
-      </c>
-      <c r="X11">
+      <c r="AQ11">
+        <v>4.9</v>
+      </c>
+      <c r="AR11">
+        <v>6.4</v>
+      </c>
+      <c r="AS11">
+        <v>7</v>
+      </c>
+      <c r="AT11">
+        <v>3.45</v>
+      </c>
+      <c r="AU11">
+        <v>3.85</v>
+      </c>
+      <c r="AV11">
+        <v>5.6</v>
+      </c>
+      <c r="AW11">
+        <v>6.8</v>
+      </c>
+      <c r="AX11">
+        <v>4.1</v>
+      </c>
+      <c r="AY11">
+        <v>4.6</v>
+      </c>
+      <c r="AZ11">
+        <v>5.7</v>
+      </c>
+      <c r="BA11">
+        <v>7</v>
+      </c>
+      <c r="BB11">
+        <v>5.3</v>
+      </c>
+      <c r="BC11">
+        <v>5.8</v>
+      </c>
+      <c r="BD11">
+        <v>6.6</v>
+      </c>
+      <c r="BE11">
+        <v>7</v>
+      </c>
+      <c r="BF11">
+        <v>5.5</v>
+      </c>
+      <c r="BG11">
+        <v>7</v>
+      </c>
+      <c r="BH11">
+        <v>3.3</v>
+      </c>
+      <c r="BI11">
+        <v>2.34</v>
+      </c>
+      <c r="BJ11">
+        <v>14.5</v>
+      </c>
+      <c r="BK11">
+        <v>3.75</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>5</v>
+      </c>
+      <c r="BN11">
+        <v>4.8</v>
+      </c>
+      <c r="BO11">
+        <v>2.46</v>
+      </c>
+      <c r="BP11">
+        <v>16.5</v>
+      </c>
+      <c r="BQ11">
+        <v>3.9</v>
+      </c>
+      <c r="BR11">
+        <v>44</v>
+      </c>
+      <c r="BS11">
+        <v>4.5</v>
+      </c>
+      <c r="BT11">
         <v>11</v>
       </c>
-      <c r="Y11">
-        <v>13</v>
-      </c>
-      <c r="Z11">
-        <v>32</v>
-      </c>
-      <c r="AA11">
-        <v>110</v>
-      </c>
-      <c r="AB11">
-        <v>7.8</v>
-      </c>
-      <c r="AC11">
-        <v>7.8</v>
-      </c>
-      <c r="AD11">
-        <v>18</v>
-      </c>
-      <c r="AE11">
-        <v>65</v>
-      </c>
-      <c r="AF11">
-        <v>11.5</v>
-      </c>
-      <c r="AG11">
-        <v>11</v>
-      </c>
-      <c r="AH11">
-        <v>22</v>
-      </c>
-      <c r="AI11">
-        <v>1000</v>
-      </c>
-      <c r="AJ11">
-        <v>24</v>
-      </c>
-      <c r="AK11">
-        <v>24</v>
-      </c>
-      <c r="AL11">
-        <v>48</v>
-      </c>
-      <c r="AM11">
-        <v>1000</v>
-      </c>
-      <c r="AN11">
-        <v>18.5</v>
-      </c>
-      <c r="AO11">
-        <v>1000</v>
-      </c>
-      <c r="AP11">
-        <v>10</v>
-      </c>
-      <c r="AQ11">
-        <v>12</v>
-      </c>
-      <c r="AR11">
-        <v>27</v>
-      </c>
-      <c r="AS11">
-        <v>18</v>
-      </c>
-      <c r="AT11">
-        <v>7.2</v>
-      </c>
-      <c r="AU11">
-        <v>7.6</v>
-      </c>
-      <c r="AV11">
-        <v>16.5</v>
-      </c>
-      <c r="AW11">
-        <v>50</v>
-      </c>
-      <c r="AX11">
-        <v>10.5</v>
-      </c>
-      <c r="AY11">
-        <v>10</v>
-      </c>
-      <c r="AZ11">
-        <v>19.5</v>
-      </c>
-      <c r="BA11">
-        <v>50</v>
-      </c>
-      <c r="BB11">
-        <v>21</v>
-      </c>
-      <c r="BC11">
-        <v>22</v>
-      </c>
-      <c r="BD11">
+      <c r="BU11">
+        <v>3.45</v>
+      </c>
+      <c r="BV11">
+        <v>1000</v>
+      </c>
+      <c r="BW11">
+        <v>4.8</v>
+      </c>
+      <c r="BX11">
+        <v>1000</v>
+      </c>
+      <c r="BY11">
+        <v>4.8</v>
+      </c>
+      <c r="BZ11">
         <v>42</v>
       </c>
-      <c r="BE11">
-        <v>18.5</v>
-      </c>
-      <c r="BF11">
-        <v>16</v>
-      </c>
-      <c r="BG11">
-        <v>34</v>
-      </c>
-      <c r="BH11">
-        <v>1000</v>
-      </c>
-      <c r="BI11">
-        <v>1.46</v>
-      </c>
-      <c r="BJ11">
-        <v>1000</v>
-      </c>
-      <c r="BK11">
-        <v>2.64</v>
-      </c>
-      <c r="BL11">
-        <v>1000</v>
-      </c>
-      <c r="BM11">
-        <v>36</v>
-      </c>
-      <c r="BN11">
-        <v>1000</v>
-      </c>
-      <c r="BO11">
-        <v>3.75</v>
-      </c>
-      <c r="BP11">
-        <v>1000</v>
-      </c>
-      <c r="BQ11">
-        <v>2.64</v>
-      </c>
-      <c r="BR11">
-        <v>1000</v>
-      </c>
-      <c r="BS11">
-        <v>13.5</v>
-      </c>
-      <c r="BT11">
-        <v>1000</v>
-      </c>
-      <c r="BU11">
-        <v>2.02</v>
-      </c>
-      <c r="BV11">
-        <v>1000</v>
-      </c>
-      <c r="BW11">
-        <v>14.5</v>
-      </c>
-      <c r="BX11">
-        <v>1000</v>
-      </c>
-      <c r="BY11">
-        <v>15.5</v>
-      </c>
-      <c r="BZ11">
-        <v>1000</v>
-      </c>
       <c r="CA11">
-        <v>12</v>
+        <v>4.5</v>
       </c>
       <c r="CB11" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E12" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12">
+        <v>2.02</v>
+      </c>
+      <c r="H12">
+        <v>4.4</v>
+      </c>
+      <c r="I12">
+        <v>4.5</v>
+      </c>
+      <c r="J12">
+        <v>3.55</v>
+      </c>
+      <c r="K12">
+        <v>3.6</v>
+      </c>
+      <c r="L12">
+        <v>1.51</v>
+      </c>
+      <c r="M12">
         <v>1.09</v>
       </c>
-      <c r="G12">
-        <v>1.76</v>
-      </c>
-      <c r="H12">
-        <v>4.6</v>
-      </c>
-      <c r="I12">
-        <v>870</v>
-      </c>
-      <c r="J12">
-        <v>4</v>
-      </c>
-      <c r="K12">
-        <v>950</v>
-      </c>
-      <c r="L12">
-        <v>1.01</v>
-      </c>
-      <c r="M12">
-        <v>1.03</v>
-      </c>
       <c r="N12">
-        <v>2.18</v>
+        <v>3.3</v>
       </c>
       <c r="O12">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="P12">
-        <v>2.18</v>
+        <v>1.75</v>
       </c>
       <c r="Q12">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="R12">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="S12">
-        <v>2.12</v>
+        <v>4.4</v>
       </c>
       <c r="T12">
-        <v>1.55</v>
+        <v>2.02</v>
       </c>
       <c r="U12">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="V12">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="W12">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="X12">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y12">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z12">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA12">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB12">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC12">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD12">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE12">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF12">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG12">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH12">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI12">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ12">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK12">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL12">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM12">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN12">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO12">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP12">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ12">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR12">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="AS12">
-        <v>1.01</v>
+        <v>95</v>
       </c>
       <c r="AT12">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AU12">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV12">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AW12">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="AX12">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY12">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ12">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BA12">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BB12">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BC12">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BD12">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BE12">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BF12">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BG12">
-        <v>1.01</v>
+        <v>70</v>
       </c>
       <c r="BH12">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="BI12">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="BJ12">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK12">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BL12">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="BM12">
-        <v>1.04</v>
+        <v>15</v>
       </c>
       <c r="BN12">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO12">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BP12">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ12">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BR12">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS12">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BT12">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU12">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BV12">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW12">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BX12">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY12">
-        <v>1.04</v>
+        <v>13</v>
       </c>
       <c r="BZ12">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA12">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="CB12" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E13" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="F13">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="G13">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="H13">
+        <v>5.2</v>
+      </c>
+      <c r="I13">
+        <v>5.9</v>
+      </c>
+      <c r="J13">
+        <v>4.4</v>
+      </c>
+      <c r="K13">
         <v>5</v>
       </c>
-      <c r="I13">
-        <v>990</v>
-      </c>
-      <c r="J13">
-        <v>4.3</v>
-      </c>
-      <c r="K13">
+      <c r="L13">
+        <v>1.24</v>
+      </c>
+      <c r="M13">
+        <v>1.03</v>
+      </c>
+      <c r="N13">
+        <v>5.2</v>
+      </c>
+      <c r="O13">
+        <v>1.2</v>
+      </c>
+      <c r="P13">
+        <v>2.46</v>
+      </c>
+      <c r="Q13">
+        <v>1.59</v>
+      </c>
+      <c r="R13">
+        <v>1.58</v>
+      </c>
+      <c r="S13">
+        <v>2.46</v>
+      </c>
+      <c r="T13">
+        <v>1.67</v>
+      </c>
+      <c r="U13">
+        <v>2.26</v>
+      </c>
+      <c r="V13">
+        <v>1.01</v>
+      </c>
+      <c r="W13">
+        <v>1.01</v>
+      </c>
+      <c r="X13">
+        <v>30</v>
+      </c>
+      <c r="Y13">
         <v>950</v>
       </c>
-      <c r="L13">
-        <v>1.01</v>
-      </c>
-      <c r="M13">
-        <v>1.01</v>
-      </c>
-      <c r="N13">
-        <v>2.36</v>
-      </c>
-      <c r="O13">
-        <v>1.1</v>
-      </c>
-      <c r="P13">
-        <v>2.36</v>
-      </c>
-      <c r="Q13">
-        <v>1.35</v>
-      </c>
-      <c r="R13">
-        <v>1.65</v>
-      </c>
-      <c r="S13">
-        <v>1.81</v>
-      </c>
-      <c r="T13">
-        <v>1.11</v>
-      </c>
-      <c r="U13">
-        <v>1.11</v>
-      </c>
-      <c r="V13">
-        <v>1.01</v>
-      </c>
-      <c r="W13">
-        <v>2.8</v>
-      </c>
-      <c r="X13">
-        <v>1000</v>
-      </c>
-      <c r="Y13">
-        <v>1000</v>
-      </c>
       <c r="Z13">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA13">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB13">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC13">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD13">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE13">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF13">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG13">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH13">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI13">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ13">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AK13">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AL13">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AM13">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN13">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AO13">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP13">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AQ13">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AR13">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AS13">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AT13">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AU13">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AV13">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AW13">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AX13">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY13">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AZ13">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA13">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BB13">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BC13">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BD13">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BE13">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BF13">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BG13">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BI13">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK13">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BN13">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO13">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BP13">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ13">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BR13">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS13">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU13">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BV13">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW13">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BX13">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY13">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BZ13">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="CA13">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="CB13" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E14" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F14">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="G14">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="H14">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="I14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J14">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="K14">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="L14">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="M14">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N14">
-        <v>7</v>
+        <v>1.1</v>
       </c>
       <c r="O14">
         <v>1.15</v>
       </c>
       <c r="P14">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="Q14">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="R14">
+        <v>1.66</v>
+      </c>
+      <c r="S14">
+        <v>2.08</v>
+      </c>
+      <c r="T14">
         <v>1.79</v>
       </c>
-      <c r="S14">
-        <v>2.2</v>
-      </c>
-      <c r="T14">
-        <v>1.84</v>
-      </c>
       <c r="U14">
-        <v>2.14</v>
+        <v>1.96</v>
       </c>
       <c r="V14">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="W14">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="X14">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="Y14">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="Z14">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA14">
-        <v>370</v>
+        <v>400</v>
       </c>
       <c r="AB14">
+        <v>13</v>
+      </c>
+      <c r="AC14">
+        <v>16</v>
+      </c>
+      <c r="AD14">
+        <v>55</v>
+      </c>
+      <c r="AE14">
+        <v>170</v>
+      </c>
+      <c r="AF14">
+        <v>11</v>
+      </c>
+      <c r="AG14">
+        <v>12</v>
+      </c>
+      <c r="AH14">
+        <v>28</v>
+      </c>
+      <c r="AI14">
+        <v>130</v>
+      </c>
+      <c r="AJ14">
         <v>12.5</v>
       </c>
-      <c r="AC14">
-        <v>14.5</v>
-      </c>
-      <c r="AD14">
-        <v>38</v>
-      </c>
-      <c r="AE14">
+      <c r="AK14">
+        <v>15</v>
+      </c>
+      <c r="AL14">
+        <v>34</v>
+      </c>
+      <c r="AM14">
         <v>140</v>
       </c>
-      <c r="AF14">
-        <v>9.6</v>
-      </c>
-      <c r="AG14">
-        <v>10.5</v>
-      </c>
-      <c r="AH14">
-        <v>26</v>
-      </c>
-      <c r="AI14">
-        <v>110</v>
-      </c>
-      <c r="AJ14">
-        <v>11</v>
-      </c>
-      <c r="AK14">
-        <v>12.5</v>
-      </c>
-      <c r="AL14">
-        <v>28</v>
-      </c>
-      <c r="AM14">
-        <v>1000</v>
-      </c>
       <c r="AN14">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AO14">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP14">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="AQ14">
-        <v>38</v>
+        <v>6.2</v>
       </c>
       <c r="AR14">
-        <v>50</v>
+        <v>6.6</v>
       </c>
       <c r="AS14">
+        <v>7</v>
+      </c>
+      <c r="AT14">
+        <v>4.6</v>
+      </c>
+      <c r="AU14">
+        <v>4.9</v>
+      </c>
+      <c r="AV14">
+        <v>6</v>
+      </c>
+      <c r="AW14">
+        <v>6.8</v>
+      </c>
+      <c r="AX14">
+        <v>4.3</v>
+      </c>
+      <c r="AY14">
+        <v>4.4</v>
+      </c>
+      <c r="AZ14">
+        <v>5.7</v>
+      </c>
+      <c r="BA14">
+        <v>6.8</v>
+      </c>
+      <c r="BB14">
+        <v>4.5</v>
+      </c>
+      <c r="BC14">
+        <v>4.8</v>
+      </c>
+      <c r="BD14">
+        <v>5.9</v>
+      </c>
+      <c r="BE14">
+        <v>6.8</v>
+      </c>
+      <c r="BF14">
+        <v>2.8</v>
+      </c>
+      <c r="BG14">
+        <v>6.8</v>
+      </c>
+      <c r="BH14">
+        <v>5.8</v>
+      </c>
+      <c r="BI14">
+        <v>2.64</v>
+      </c>
+      <c r="BJ14">
+        <v>13.5</v>
+      </c>
+      <c r="BK14">
+        <v>3.55</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>4.6</v>
+      </c>
+      <c r="BN14">
+        <v>4.8</v>
+      </c>
+      <c r="BO14">
+        <v>2.4</v>
+      </c>
+      <c r="BP14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BQ14">
+        <v>3.1</v>
+      </c>
+      <c r="BR14">
         <v>24</v>
       </c>
-      <c r="AT14">
-        <v>11.5</v>
-      </c>
-      <c r="AU14">
-        <v>13.5</v>
-      </c>
-      <c r="AV14">
-        <v>34</v>
-      </c>
-      <c r="AW14">
-        <v>40</v>
-      </c>
-      <c r="AX14">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY14">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ14">
-        <v>23</v>
-      </c>
-      <c r="BA14">
-        <v>65</v>
-      </c>
-      <c r="BB14">
-        <v>10.5</v>
-      </c>
-      <c r="BC14">
-        <v>11.5</v>
-      </c>
-      <c r="BD14">
-        <v>26</v>
-      </c>
-      <c r="BE14">
-        <v>65</v>
-      </c>
-      <c r="BF14">
+      <c r="BS14">
         <v>4</v>
       </c>
-      <c r="BG14">
-        <v>100</v>
-      </c>
-      <c r="BH14">
-        <v>1000</v>
-      </c>
-      <c r="BI14">
-        <v>1.54</v>
-      </c>
-      <c r="BJ14">
-        <v>1000</v>
-      </c>
-      <c r="BK14">
-        <v>2.08</v>
-      </c>
-      <c r="BL14">
-        <v>1000</v>
-      </c>
-      <c r="BM14">
-        <v>24</v>
-      </c>
-      <c r="BN14">
-        <v>4.7</v>
-      </c>
-      <c r="BO14">
-        <v>1.46</v>
-      </c>
-      <c r="BP14">
-        <v>1000</v>
-      </c>
-      <c r="BQ14">
-        <v>1.65</v>
-      </c>
-      <c r="BR14">
-        <v>1000</v>
-      </c>
-      <c r="BS14">
-        <v>2.08</v>
-      </c>
       <c r="BT14">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BU14">
-        <v>2.08</v>
+        <v>3.7</v>
       </c>
       <c r="BV14">
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>18</v>
+        <v>4.6</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>17.5</v>
+        <v>4.5</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA14">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D15" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E15" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="F15">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="G15">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="H15">
+        <v>10.5</v>
+      </c>
+      <c r="I15">
+        <v>11</v>
+      </c>
+      <c r="J15">
+        <v>6.6</v>
+      </c>
+      <c r="K15">
         <v>6.8</v>
       </c>
-      <c r="I15">
-        <v>19.5</v>
-      </c>
-      <c r="J15">
-        <v>3.65</v>
-      </c>
-      <c r="K15">
+      <c r="L15">
+        <v>1.26</v>
+      </c>
+      <c r="M15">
+        <v>1.03</v>
+      </c>
+      <c r="N15">
+        <v>7</v>
+      </c>
+      <c r="O15">
+        <v>1.15</v>
+      </c>
+      <c r="P15">
+        <v>3</v>
+      </c>
+      <c r="Q15">
+        <v>1.48</v>
+      </c>
+      <c r="R15">
+        <v>1.8</v>
+      </c>
+      <c r="S15">
+        <v>2.2</v>
+      </c>
+      <c r="T15">
+        <v>1.86</v>
+      </c>
+      <c r="U15">
+        <v>2.14</v>
+      </c>
+      <c r="V15">
+        <v>1.1</v>
+      </c>
+      <c r="W15">
+        <v>4</v>
+      </c>
+      <c r="X15">
+        <v>32</v>
+      </c>
+      <c r="Y15">
+        <v>46</v>
+      </c>
+      <c r="Z15">
+        <v>120</v>
+      </c>
+      <c r="AA15">
+        <v>390</v>
+      </c>
+      <c r="AB15">
+        <v>12.5</v>
+      </c>
+      <c r="AC15">
+        <v>14.5</v>
+      </c>
+      <c r="AD15">
+        <v>38</v>
+      </c>
+      <c r="AE15">
+        <v>130</v>
+      </c>
+      <c r="AF15">
+        <v>9.4</v>
+      </c>
+      <c r="AG15">
+        <v>10.5</v>
+      </c>
+      <c r="AH15">
+        <v>26</v>
+      </c>
+      <c r="AI15">
+        <v>110</v>
+      </c>
+      <c r="AJ15">
+        <v>11</v>
+      </c>
+      <c r="AK15">
+        <v>12.5</v>
+      </c>
+      <c r="AL15">
+        <v>28</v>
+      </c>
+      <c r="AM15">
+        <v>110</v>
+      </c>
+      <c r="AN15">
+        <v>4.1</v>
+      </c>
+      <c r="AO15">
+        <v>140</v>
+      </c>
+      <c r="AP15">
+        <v>29</v>
+      </c>
+      <c r="AQ15">
+        <v>40</v>
+      </c>
+      <c r="AR15">
+        <v>60</v>
+      </c>
+      <c r="AS15">
+        <v>65</v>
+      </c>
+      <c r="AT15">
+        <v>11.5</v>
+      </c>
+      <c r="AU15">
+        <v>13.5</v>
+      </c>
+      <c r="AV15">
+        <v>34</v>
+      </c>
+      <c r="AW15">
+        <v>42</v>
+      </c>
+      <c r="AX15">
+        <v>9</v>
+      </c>
+      <c r="AY15">
+        <v>10</v>
+      </c>
+      <c r="AZ15">
+        <v>24</v>
+      </c>
+      <c r="BA15">
+        <v>90</v>
+      </c>
+      <c r="BB15">
+        <v>10.5</v>
+      </c>
+      <c r="BC15">
+        <v>11.5</v>
+      </c>
+      <c r="BD15">
+        <v>26</v>
+      </c>
+      <c r="BE15">
+        <v>85</v>
+      </c>
+      <c r="BF15">
+        <v>3.85</v>
+      </c>
+      <c r="BG15">
+        <v>100</v>
+      </c>
+      <c r="BH15">
+        <v>5.8</v>
+      </c>
+      <c r="BI15">
         <v>4.4</v>
       </c>
-      <c r="L15">
-        <v>1.44</v>
-      </c>
-      <c r="M15">
-        <v>1.01</v>
-      </c>
-      <c r="N15">
-        <v>2.58</v>
-      </c>
-      <c r="O15">
-        <v>1.42</v>
-      </c>
-      <c r="P15">
-        <v>1.52</v>
-      </c>
-      <c r="Q15">
-        <v>2.28</v>
-      </c>
-      <c r="R15">
-        <v>1.12</v>
-      </c>
-      <c r="S15">
-        <v>2.74</v>
-      </c>
-      <c r="T15">
-        <v>1.11</v>
-      </c>
-      <c r="U15">
-        <v>1.11</v>
-      </c>
-      <c r="V15">
-        <v>1.05</v>
-      </c>
-      <c r="W15">
-        <v>2.62</v>
-      </c>
-      <c r="X15">
-        <v>1000</v>
-      </c>
-      <c r="Y15">
-        <v>1000</v>
-      </c>
-      <c r="Z15">
-        <v>1000</v>
-      </c>
-      <c r="AA15">
-        <v>1000</v>
-      </c>
-      <c r="AB15">
-        <v>1000</v>
-      </c>
-      <c r="AC15">
-        <v>1000</v>
-      </c>
-      <c r="AD15">
-        <v>1000</v>
-      </c>
-      <c r="AE15">
-        <v>1000</v>
-      </c>
-      <c r="AF15">
-        <v>1000</v>
-      </c>
-      <c r="AG15">
-        <v>1000</v>
-      </c>
-      <c r="AH15">
-        <v>1000</v>
-      </c>
-      <c r="AI15">
-        <v>1000</v>
-      </c>
-      <c r="AJ15">
-        <v>1000</v>
-      </c>
-      <c r="AK15">
-        <v>1000</v>
-      </c>
-      <c r="AL15">
-        <v>1000</v>
-      </c>
-      <c r="AM15">
-        <v>1000</v>
-      </c>
-      <c r="AN15">
-        <v>1000</v>
-      </c>
-      <c r="AO15">
-        <v>1000</v>
-      </c>
-      <c r="AP15">
-        <v>1.01</v>
-      </c>
-      <c r="AQ15">
-        <v>1.01</v>
-      </c>
-      <c r="AR15">
-        <v>1.01</v>
-      </c>
-      <c r="AS15">
-        <v>1.01</v>
-      </c>
-      <c r="AT15">
-        <v>1.01</v>
-      </c>
-      <c r="AU15">
-        <v>1.01</v>
-      </c>
-      <c r="AV15">
-        <v>1.01</v>
-      </c>
-      <c r="AW15">
-        <v>1.01</v>
-      </c>
-      <c r="AX15">
-        <v>1.01</v>
-      </c>
-      <c r="AY15">
-        <v>1.01</v>
-      </c>
-      <c r="AZ15">
-        <v>1.01</v>
-      </c>
-      <c r="BA15">
-        <v>1.01</v>
-      </c>
-      <c r="BB15">
-        <v>1.01</v>
-      </c>
-      <c r="BC15">
-        <v>1.01</v>
-      </c>
-      <c r="BD15">
-        <v>1.01</v>
-      </c>
-      <c r="BE15">
-        <v>1.01</v>
-      </c>
-      <c r="BF15">
-        <v>1.01</v>
-      </c>
-      <c r="BG15">
-        <v>1.01</v>
-      </c>
-      <c r="BH15">
-        <v>1000</v>
-      </c>
-      <c r="BI15">
-        <v>1.04</v>
-      </c>
       <c r="BJ15">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK15">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BL15">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM15">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BN15">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BO15">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BP15">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BQ15">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BR15">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BS15">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BT15">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BU15">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BV15">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BW15">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BX15">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY15">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BZ15">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="CA15">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="CB15" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D16" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E16" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="F16">
-        <v>3.7</v>
+        <v>1.48</v>
       </c>
       <c r="G16">
-        <v>4.8</v>
+        <v>1.56</v>
       </c>
       <c r="H16">
-        <v>2.08</v>
+        <v>6.8</v>
       </c>
       <c r="I16">
-        <v>2.42</v>
+        <v>12.5</v>
       </c>
       <c r="J16">
-        <v>2.64</v>
+        <v>3.6</v>
       </c>
       <c r="K16">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="L16">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M16">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N16">
         <v>2.8</v>
       </c>
       <c r="O16">
+        <v>1.44</v>
+      </c>
+      <c r="P16">
+        <v>1.56</v>
+      </c>
+      <c r="Q16">
+        <v>2.3</v>
+      </c>
+      <c r="R16">
+        <v>1.12</v>
+      </c>
+      <c r="S16">
+        <v>2.74</v>
+      </c>
+      <c r="T16">
+        <v>2.34</v>
+      </c>
+      <c r="U16">
+        <v>1.48</v>
+      </c>
+      <c r="V16">
+        <v>1.08</v>
+      </c>
+      <c r="W16">
+        <v>2.78</v>
+      </c>
+      <c r="X16">
+        <v>12</v>
+      </c>
+      <c r="Y16">
+        <v>26</v>
+      </c>
+      <c r="Z16">
+        <v>110</v>
+      </c>
+      <c r="AA16">
+        <v>620</v>
+      </c>
+      <c r="AB16">
+        <v>6.4</v>
+      </c>
+      <c r="AC16">
+        <v>11.5</v>
+      </c>
+      <c r="AD16">
+        <v>48</v>
+      </c>
+      <c r="AE16">
+        <v>310</v>
+      </c>
+      <c r="AF16">
+        <v>8.4</v>
+      </c>
+      <c r="AG16">
+        <v>13</v>
+      </c>
+      <c r="AH16">
+        <v>44</v>
+      </c>
+      <c r="AI16">
+        <v>290</v>
+      </c>
+      <c r="AJ16">
+        <v>15.5</v>
+      </c>
+      <c r="AK16">
+        <v>25</v>
+      </c>
+      <c r="AL16">
+        <v>80</v>
+      </c>
+      <c r="AM16">
+        <v>410</v>
+      </c>
+      <c r="AN16">
+        <v>14.5</v>
+      </c>
+      <c r="AO16">
+        <v>1000</v>
+      </c>
+      <c r="AP16">
+        <v>1.01</v>
+      </c>
+      <c r="AQ16">
+        <v>1.01</v>
+      </c>
+      <c r="AR16">
+        <v>1.01</v>
+      </c>
+      <c r="AS16">
+        <v>1.01</v>
+      </c>
+      <c r="AT16">
+        <v>1.01</v>
+      </c>
+      <c r="AU16">
+        <v>1.01</v>
+      </c>
+      <c r="AV16">
+        <v>1.01</v>
+      </c>
+      <c r="AW16">
+        <v>1.01</v>
+      </c>
+      <c r="AX16">
+        <v>1.01</v>
+      </c>
+      <c r="AY16">
+        <v>1.01</v>
+      </c>
+      <c r="AZ16">
+        <v>1.01</v>
+      </c>
+      <c r="BA16">
+        <v>1.01</v>
+      </c>
+      <c r="BB16">
+        <v>1.01</v>
+      </c>
+      <c r="BC16">
+        <v>1.01</v>
+      </c>
+      <c r="BD16">
+        <v>1.01</v>
+      </c>
+      <c r="BE16">
+        <v>1.01</v>
+      </c>
+      <c r="BF16">
+        <v>1.01</v>
+      </c>
+      <c r="BG16">
+        <v>1.01</v>
+      </c>
+      <c r="BH16">
+        <v>3.25</v>
+      </c>
+      <c r="BI16">
+        <v>2.44</v>
+      </c>
+      <c r="BJ16">
+        <v>16.5</v>
+      </c>
+      <c r="BK16">
+        <v>4.5</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>6</v>
+      </c>
+      <c r="BN16">
+        <v>4</v>
+      </c>
+      <c r="BO16">
+        <v>2.96</v>
+      </c>
+      <c r="BP16">
+        <v>12</v>
+      </c>
+      <c r="BQ16">
+        <v>4</v>
+      </c>
+      <c r="BR16">
+        <v>44</v>
+      </c>
+      <c r="BS16">
+        <v>5.4</v>
+      </c>
+      <c r="BT16">
+        <v>15</v>
+      </c>
+      <c r="BU16">
+        <v>4.3</v>
+      </c>
+      <c r="BV16">
+        <v>1000</v>
+      </c>
+      <c r="BW16">
+        <v>5.9</v>
+      </c>
+      <c r="BX16">
+        <v>1000</v>
+      </c>
+      <c r="BY16">
+        <v>5.9</v>
+      </c>
+      <c r="BZ16">
+        <v>32</v>
+      </c>
+      <c r="CA16">
+        <v>5.1</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" t="s">
+        <v>121</v>
+      </c>
+      <c r="E17" t="s">
+        <v>141</v>
+      </c>
+      <c r="F17">
+        <v>3.4</v>
+      </c>
+      <c r="G17">
+        <v>4.4</v>
+      </c>
+      <c r="H17">
+        <v>1.68</v>
+      </c>
+      <c r="I17">
+        <v>1.91</v>
+      </c>
+      <c r="J17">
+        <v>4.8</v>
+      </c>
+      <c r="K17">
+        <v>5.7</v>
+      </c>
+      <c r="L17">
+        <v>1.15</v>
+      </c>
+      <c r="M17">
+        <v>1.01</v>
+      </c>
+      <c r="N17">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="O17">
+        <v>1.07</v>
+      </c>
+      <c r="P17">
+        <v>3.65</v>
+      </c>
+      <c r="Q17">
+        <v>1.23</v>
+      </c>
+      <c r="R17">
+        <v>2.16</v>
+      </c>
+      <c r="S17">
+        <v>1.57</v>
+      </c>
+      <c r="T17">
+        <v>1.3</v>
+      </c>
+      <c r="U17">
+        <v>3.1</v>
+      </c>
+      <c r="V17">
+        <v>2.08</v>
+      </c>
+      <c r="W17">
+        <v>1.29</v>
+      </c>
+      <c r="X17">
+        <v>70</v>
+      </c>
+      <c r="Y17">
+        <v>30</v>
+      </c>
+      <c r="Z17">
+        <v>26</v>
+      </c>
+      <c r="AA17">
+        <v>29</v>
+      </c>
+      <c r="AB17">
+        <v>46</v>
+      </c>
+      <c r="AC17">
+        <v>18.5</v>
+      </c>
+      <c r="AD17">
+        <v>15.5</v>
+      </c>
+      <c r="AE17">
+        <v>19.5</v>
+      </c>
+      <c r="AF17">
+        <v>55</v>
+      </c>
+      <c r="AG17">
+        <v>23</v>
+      </c>
+      <c r="AH17">
+        <v>17.5</v>
+      </c>
+      <c r="AI17">
+        <v>23</v>
+      </c>
+      <c r="AJ17">
+        <v>90</v>
+      </c>
+      <c r="AK17">
+        <v>42</v>
+      </c>
+      <c r="AL17">
+        <v>34</v>
+      </c>
+      <c r="AM17">
+        <v>42</v>
+      </c>
+      <c r="AN17">
+        <v>17.5</v>
+      </c>
+      <c r="AO17">
+        <v>5.4</v>
+      </c>
+      <c r="AP17">
+        <v>1.03</v>
+      </c>
+      <c r="AQ17">
+        <v>1.01</v>
+      </c>
+      <c r="AR17">
+        <v>1.01</v>
+      </c>
+      <c r="AS17">
+        <v>1.01</v>
+      </c>
+      <c r="AT17">
+        <v>1.01</v>
+      </c>
+      <c r="AU17">
+        <v>1.01</v>
+      </c>
+      <c r="AV17">
+        <v>1.01</v>
+      </c>
+      <c r="AW17">
+        <v>1.01</v>
+      </c>
+      <c r="AX17">
+        <v>1.01</v>
+      </c>
+      <c r="AY17">
+        <v>1.01</v>
+      </c>
+      <c r="AZ17">
+        <v>1.01</v>
+      </c>
+      <c r="BA17">
+        <v>1.01</v>
+      </c>
+      <c r="BB17">
+        <v>1.03</v>
+      </c>
+      <c r="BC17">
+        <v>1.01</v>
+      </c>
+      <c r="BD17">
+        <v>1.01</v>
+      </c>
+      <c r="BE17">
+        <v>1.01</v>
+      </c>
+      <c r="BF17">
+        <v>1.01</v>
+      </c>
+      <c r="BG17">
+        <v>1.01</v>
+      </c>
+      <c r="BH17">
+        <v>7.6</v>
+      </c>
+      <c r="BI17">
+        <v>3.15</v>
+      </c>
+      <c r="BJ17">
+        <v>9.4</v>
+      </c>
+      <c r="BK17">
+        <v>3.45</v>
+      </c>
+      <c r="BL17">
+        <v>50</v>
+      </c>
+      <c r="BM17">
+        <v>4.9</v>
+      </c>
+      <c r="BN17">
+        <v>10.5</v>
+      </c>
+      <c r="BO17">
+        <v>3.55</v>
+      </c>
+      <c r="BP17">
+        <v>28</v>
+      </c>
+      <c r="BQ17">
+        <v>4.5</v>
+      </c>
+      <c r="BR17">
+        <v>26</v>
+      </c>
+      <c r="BS17">
+        <v>4.5</v>
+      </c>
+      <c r="BT17">
+        <v>6.8</v>
+      </c>
+      <c r="BU17">
+        <v>3</v>
+      </c>
+      <c r="BV17">
+        <v>13</v>
+      </c>
+      <c r="BW17">
+        <v>3.85</v>
+      </c>
+      <c r="BX17">
+        <v>17.5</v>
+      </c>
+      <c r="BY17">
+        <v>4.1</v>
+      </c>
+      <c r="BZ17">
+        <v>0</v>
+      </c>
+      <c r="CA17">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D18" t="s">
+        <v>122</v>
+      </c>
+      <c r="E18" t="s">
+        <v>142</v>
+      </c>
+      <c r="F18">
+        <v>1.04</v>
+      </c>
+      <c r="G18">
+        <v>1000</v>
+      </c>
+      <c r="H18">
+        <v>1.04</v>
+      </c>
+      <c r="I18">
+        <v>1000</v>
+      </c>
+      <c r="J18">
+        <v>1.02</v>
+      </c>
+      <c r="K18">
+        <v>1000</v>
+      </c>
+      <c r="L18">
+        <v>1.01</v>
+      </c>
+      <c r="M18">
+        <v>1.01</v>
+      </c>
+      <c r="N18">
+        <v>1.08</v>
+      </c>
+      <c r="O18">
+        <v>1.01</v>
+      </c>
+      <c r="P18">
+        <v>1.06</v>
+      </c>
+      <c r="Q18">
+        <v>1.01</v>
+      </c>
+      <c r="R18">
+        <v>1.06</v>
+      </c>
+      <c r="S18">
+        <v>1.01</v>
+      </c>
+      <c r="T18">
+        <v>1.01</v>
+      </c>
+      <c r="U18">
+        <v>1.01</v>
+      </c>
+      <c r="V18">
+        <v>1.01</v>
+      </c>
+      <c r="W18">
+        <v>1.01</v>
+      </c>
+      <c r="X18">
+        <v>1000</v>
+      </c>
+      <c r="Y18">
+        <v>1000</v>
+      </c>
+      <c r="Z18">
+        <v>1000</v>
+      </c>
+      <c r="AA18">
+        <v>1000</v>
+      </c>
+      <c r="AB18">
+        <v>1000</v>
+      </c>
+      <c r="AC18">
+        <v>1000</v>
+      </c>
+      <c r="AD18">
+        <v>1000</v>
+      </c>
+      <c r="AE18">
+        <v>1000</v>
+      </c>
+      <c r="AF18">
+        <v>1000</v>
+      </c>
+      <c r="AG18">
+        <v>1000</v>
+      </c>
+      <c r="AH18">
+        <v>1000</v>
+      </c>
+      <c r="AI18">
+        <v>1000</v>
+      </c>
+      <c r="AJ18">
+        <v>1000</v>
+      </c>
+      <c r="AK18">
+        <v>1000</v>
+      </c>
+      <c r="AL18">
+        <v>1000</v>
+      </c>
+      <c r="AM18">
+        <v>1000</v>
+      </c>
+      <c r="AN18">
+        <v>1000</v>
+      </c>
+      <c r="AO18">
+        <v>1000</v>
+      </c>
+      <c r="AP18">
+        <v>1.01</v>
+      </c>
+      <c r="AQ18">
+        <v>1.01</v>
+      </c>
+      <c r="AR18">
+        <v>1.01</v>
+      </c>
+      <c r="AS18">
+        <v>1.01</v>
+      </c>
+      <c r="AT18">
+        <v>1.01</v>
+      </c>
+      <c r="AU18">
+        <v>1.01</v>
+      </c>
+      <c r="AV18">
+        <v>1.01</v>
+      </c>
+      <c r="AW18">
+        <v>1.01</v>
+      </c>
+      <c r="AX18">
+        <v>1.01</v>
+      </c>
+      <c r="AY18">
+        <v>1.01</v>
+      </c>
+      <c r="AZ18">
+        <v>1.01</v>
+      </c>
+      <c r="BA18">
+        <v>1.01</v>
+      </c>
+      <c r="BB18">
+        <v>1.01</v>
+      </c>
+      <c r="BC18">
+        <v>1.01</v>
+      </c>
+      <c r="BD18">
+        <v>1.01</v>
+      </c>
+      <c r="BE18">
+        <v>1.01</v>
+      </c>
+      <c r="BF18">
+        <v>1.01</v>
+      </c>
+      <c r="BG18">
+        <v>1.01</v>
+      </c>
+      <c r="BH18">
+        <v>1000</v>
+      </c>
+      <c r="BI18">
+        <v>1.01</v>
+      </c>
+      <c r="BJ18">
+        <v>1000</v>
+      </c>
+      <c r="BK18">
+        <v>1.01</v>
+      </c>
+      <c r="BL18">
+        <v>1000</v>
+      </c>
+      <c r="BM18">
+        <v>1.01</v>
+      </c>
+      <c r="BN18">
+        <v>1000</v>
+      </c>
+      <c r="BO18">
+        <v>1.01</v>
+      </c>
+      <c r="BP18">
+        <v>1000</v>
+      </c>
+      <c r="BQ18">
+        <v>1.01</v>
+      </c>
+      <c r="BR18">
+        <v>1000</v>
+      </c>
+      <c r="BS18">
+        <v>1.01</v>
+      </c>
+      <c r="BT18">
+        <v>1000</v>
+      </c>
+      <c r="BU18">
+        <v>1.01</v>
+      </c>
+      <c r="BV18">
+        <v>1000</v>
+      </c>
+      <c r="BW18">
+        <v>1.01</v>
+      </c>
+      <c r="BX18">
+        <v>1000</v>
+      </c>
+      <c r="BY18">
+        <v>1.01</v>
+      </c>
+      <c r="BZ18">
+        <v>1000</v>
+      </c>
+      <c r="CA18">
+        <v>1.01</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80">
+      <c r="A19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D19" t="s">
+        <v>123</v>
+      </c>
+      <c r="E19" t="s">
+        <v>143</v>
+      </c>
+      <c r="F19">
+        <v>1.04</v>
+      </c>
+      <c r="G19">
+        <v>1000</v>
+      </c>
+      <c r="H19">
+        <v>1.04</v>
+      </c>
+      <c r="I19">
+        <v>1000</v>
+      </c>
+      <c r="J19">
+        <v>1.04</v>
+      </c>
+      <c r="K19">
+        <v>950</v>
+      </c>
+      <c r="L19">
+        <v>1.01</v>
+      </c>
+      <c r="M19">
+        <v>1.01</v>
+      </c>
+      <c r="N19">
+        <v>1.25</v>
+      </c>
+      <c r="O19">
+        <v>1.01</v>
+      </c>
+      <c r="P19">
+        <v>1.24</v>
+      </c>
+      <c r="Q19">
+        <v>1.01</v>
+      </c>
+      <c r="R19">
+        <v>1.18</v>
+      </c>
+      <c r="S19">
+        <v>1.01</v>
+      </c>
+      <c r="T19">
+        <v>1.01</v>
+      </c>
+      <c r="U19">
+        <v>1.01</v>
+      </c>
+      <c r="V19">
+        <v>1.01</v>
+      </c>
+      <c r="W19">
+        <v>1.01</v>
+      </c>
+      <c r="X19">
+        <v>1000</v>
+      </c>
+      <c r="Y19">
+        <v>1000</v>
+      </c>
+      <c r="Z19">
+        <v>1000</v>
+      </c>
+      <c r="AA19">
+        <v>1000</v>
+      </c>
+      <c r="AB19">
+        <v>1000</v>
+      </c>
+      <c r="AC19">
+        <v>1000</v>
+      </c>
+      <c r="AD19">
+        <v>1000</v>
+      </c>
+      <c r="AE19">
+        <v>1000</v>
+      </c>
+      <c r="AF19">
+        <v>1000</v>
+      </c>
+      <c r="AG19">
+        <v>1000</v>
+      </c>
+      <c r="AH19">
+        <v>1000</v>
+      </c>
+      <c r="AI19">
+        <v>1000</v>
+      </c>
+      <c r="AJ19">
+        <v>1000</v>
+      </c>
+      <c r="AK19">
+        <v>1000</v>
+      </c>
+      <c r="AL19">
+        <v>1000</v>
+      </c>
+      <c r="AM19">
+        <v>1000</v>
+      </c>
+      <c r="AN19">
+        <v>1000</v>
+      </c>
+      <c r="AO19">
+        <v>1000</v>
+      </c>
+      <c r="AP19">
+        <v>1.03</v>
+      </c>
+      <c r="AQ19">
+        <v>1.03</v>
+      </c>
+      <c r="AR19">
+        <v>1.03</v>
+      </c>
+      <c r="AS19">
+        <v>1.03</v>
+      </c>
+      <c r="AT19">
+        <v>1.03</v>
+      </c>
+      <c r="AU19">
+        <v>1.03</v>
+      </c>
+      <c r="AV19">
+        <v>1.03</v>
+      </c>
+      <c r="AW19">
+        <v>1.03</v>
+      </c>
+      <c r="AX19">
+        <v>1.03</v>
+      </c>
+      <c r="AY19">
+        <v>1.03</v>
+      </c>
+      <c r="AZ19">
+        <v>1.03</v>
+      </c>
+      <c r="BA19">
+        <v>1.03</v>
+      </c>
+      <c r="BB19">
+        <v>1.03</v>
+      </c>
+      <c r="BC19">
+        <v>1.03</v>
+      </c>
+      <c r="BD19">
+        <v>1.03</v>
+      </c>
+      <c r="BE19">
+        <v>1.03</v>
+      </c>
+      <c r="BF19">
+        <v>1.01</v>
+      </c>
+      <c r="BG19">
+        <v>1.01</v>
+      </c>
+      <c r="BH19">
+        <v>1000</v>
+      </c>
+      <c r="BI19">
+        <v>1.01</v>
+      </c>
+      <c r="BJ19">
+        <v>1000</v>
+      </c>
+      <c r="BK19">
+        <v>1.01</v>
+      </c>
+      <c r="BL19">
+        <v>1000</v>
+      </c>
+      <c r="BM19">
+        <v>1.01</v>
+      </c>
+      <c r="BN19">
+        <v>1000</v>
+      </c>
+      <c r="BO19">
+        <v>1.01</v>
+      </c>
+      <c r="BP19">
+        <v>1000</v>
+      </c>
+      <c r="BQ19">
+        <v>1.01</v>
+      </c>
+      <c r="BR19">
+        <v>1000</v>
+      </c>
+      <c r="BS19">
+        <v>1.01</v>
+      </c>
+      <c r="BT19">
+        <v>1000</v>
+      </c>
+      <c r="BU19">
+        <v>1.01</v>
+      </c>
+      <c r="BV19">
+        <v>1000</v>
+      </c>
+      <c r="BW19">
+        <v>1.01</v>
+      </c>
+      <c r="BX19">
+        <v>1000</v>
+      </c>
+      <c r="BY19">
+        <v>1.01</v>
+      </c>
+      <c r="BZ19">
+        <v>1000</v>
+      </c>
+      <c r="CA19">
+        <v>1.01</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" t="s">
+        <v>90</v>
+      </c>
+      <c r="C20" t="s">
+        <v>104</v>
+      </c>
+      <c r="D20" t="s">
+        <v>124</v>
+      </c>
+      <c r="E20" t="s">
+        <v>144</v>
+      </c>
+      <c r="F20">
+        <v>1.93</v>
+      </c>
+      <c r="G20">
+        <v>2.22</v>
+      </c>
+      <c r="H20">
+        <v>3.05</v>
+      </c>
+      <c r="I20">
+        <v>4</v>
+      </c>
+      <c r="J20">
+        <v>3.3</v>
+      </c>
+      <c r="K20">
+        <v>4.7</v>
+      </c>
+      <c r="L20">
+        <v>1.25</v>
+      </c>
+      <c r="M20">
+        <v>1.01</v>
+      </c>
+      <c r="N20">
+        <v>5</v>
+      </c>
+      <c r="O20">
+        <v>1.18</v>
+      </c>
+      <c r="P20">
+        <v>2.4</v>
+      </c>
+      <c r="Q20">
+        <v>1.54</v>
+      </c>
+      <c r="R20">
+        <v>1.56</v>
+      </c>
+      <c r="S20">
+        <v>2.34</v>
+      </c>
+      <c r="T20">
+        <v>1.53</v>
+      </c>
+      <c r="U20">
+        <v>2.42</v>
+      </c>
+      <c r="V20">
+        <v>1.33</v>
+      </c>
+      <c r="W20">
+        <v>1.81</v>
+      </c>
+      <c r="X20">
+        <v>29</v>
+      </c>
+      <c r="Y20">
+        <v>23</v>
+      </c>
+      <c r="Z20">
+        <v>36</v>
+      </c>
+      <c r="AA20">
+        <v>75</v>
+      </c>
+      <c r="AB20">
+        <v>16</v>
+      </c>
+      <c r="AC20">
+        <v>11.5</v>
+      </c>
+      <c r="AD20">
+        <v>18</v>
+      </c>
+      <c r="AE20">
+        <v>42</v>
+      </c>
+      <c r="AF20">
+        <v>18.5</v>
+      </c>
+      <c r="AG20">
+        <v>13</v>
+      </c>
+      <c r="AH20">
+        <v>18</v>
+      </c>
+      <c r="AI20">
+        <v>44</v>
+      </c>
+      <c r="AJ20">
+        <v>29</v>
+      </c>
+      <c r="AK20">
+        <v>22</v>
+      </c>
+      <c r="AL20">
+        <v>32</v>
+      </c>
+      <c r="AM20">
+        <v>70</v>
+      </c>
+      <c r="AN20">
+        <v>11.5</v>
+      </c>
+      <c r="AO20">
+        <v>29</v>
+      </c>
+      <c r="AP20">
+        <v>1.01</v>
+      </c>
+      <c r="AQ20">
+        <v>1.01</v>
+      </c>
+      <c r="AR20">
+        <v>1.01</v>
+      </c>
+      <c r="AS20">
+        <v>1.03</v>
+      </c>
+      <c r="AT20">
+        <v>1.01</v>
+      </c>
+      <c r="AU20">
+        <v>1.01</v>
+      </c>
+      <c r="AV20">
+        <v>1.01</v>
+      </c>
+      <c r="AW20">
+        <v>1.01</v>
+      </c>
+      <c r="AX20">
+        <v>1.01</v>
+      </c>
+      <c r="AY20">
+        <v>1.01</v>
+      </c>
+      <c r="AZ20">
+        <v>1.01</v>
+      </c>
+      <c r="BA20">
+        <v>1.01</v>
+      </c>
+      <c r="BB20">
+        <v>1.01</v>
+      </c>
+      <c r="BC20">
+        <v>1.01</v>
+      </c>
+      <c r="BD20">
+        <v>1.01</v>
+      </c>
+      <c r="BE20">
+        <v>1.03</v>
+      </c>
+      <c r="BF20">
+        <v>1.01</v>
+      </c>
+      <c r="BG20">
+        <v>1.01</v>
+      </c>
+      <c r="BH20">
+        <v>1000</v>
+      </c>
+      <c r="BI20">
+        <v>1.01</v>
+      </c>
+      <c r="BJ20">
+        <v>1000</v>
+      </c>
+      <c r="BK20">
+        <v>1.01</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>1.01</v>
+      </c>
+      <c r="BN20">
+        <v>1000</v>
+      </c>
+      <c r="BO20">
+        <v>1.01</v>
+      </c>
+      <c r="BP20">
+        <v>1000</v>
+      </c>
+      <c r="BQ20">
+        <v>1.01</v>
+      </c>
+      <c r="BR20">
+        <v>1000</v>
+      </c>
+      <c r="BS20">
+        <v>1.01</v>
+      </c>
+      <c r="BT20">
+        <v>1000</v>
+      </c>
+      <c r="BU20">
+        <v>1.01</v>
+      </c>
+      <c r="BV20">
+        <v>1000</v>
+      </c>
+      <c r="BW20">
+        <v>1.01</v>
+      </c>
+      <c r="BX20">
+        <v>1000</v>
+      </c>
+      <c r="BY20">
+        <v>1.01</v>
+      </c>
+      <c r="BZ20">
+        <v>1000</v>
+      </c>
+      <c r="CA20">
+        <v>1.01</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21" spans="1:80">
+      <c r="A21" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" t="s">
+        <v>105</v>
+      </c>
+      <c r="D21" t="s">
+        <v>125</v>
+      </c>
+      <c r="E21" t="s">
+        <v>145</v>
+      </c>
+      <c r="F21">
+        <v>3.75</v>
+      </c>
+      <c r="G21">
+        <v>4.1</v>
+      </c>
+      <c r="H21">
+        <v>2.22</v>
+      </c>
+      <c r="I21">
+        <v>2.4</v>
+      </c>
+      <c r="J21">
+        <v>2.94</v>
+      </c>
+      <c r="K21">
+        <v>3.4</v>
+      </c>
+      <c r="L21">
+        <v>1.44</v>
+      </c>
+      <c r="M21">
+        <v>1.1</v>
+      </c>
+      <c r="N21">
+        <v>2.9</v>
+      </c>
+      <c r="O21">
         <v>1.43</v>
       </c>
-      <c r="P16">
-        <v>1.6</v>
-      </c>
-      <c r="Q16">
-        <v>2.18</v>
-      </c>
-      <c r="R16">
-        <v>1.22</v>
-      </c>
-      <c r="S16">
-        <v>2.68</v>
-      </c>
-      <c r="T16">
-        <v>1.11</v>
-      </c>
-      <c r="U16">
+      <c r="P21">
+        <v>1.64</v>
+      </c>
+      <c r="Q21">
+        <v>2.28</v>
+      </c>
+      <c r="R21">
+        <v>1.24</v>
+      </c>
+      <c r="S21">
+        <v>4.4</v>
+      </c>
+      <c r="T21">
+        <v>1.84</v>
+      </c>
+      <c r="U21">
         <v>1.89</v>
       </c>
-      <c r="V16">
-        <v>1.7</v>
-      </c>
-      <c r="W16">
-        <v>1.26</v>
-      </c>
-      <c r="X16">
-        <v>1000</v>
-      </c>
-      <c r="Y16">
-        <v>1000</v>
-      </c>
-      <c r="Z16">
-        <v>1000</v>
-      </c>
-      <c r="AA16">
-        <v>1000</v>
-      </c>
-      <c r="AB16">
-        <v>1000</v>
-      </c>
-      <c r="AC16">
-        <v>1000</v>
-      </c>
-      <c r="AD16">
-        <v>1000</v>
-      </c>
-      <c r="AE16">
-        <v>1000</v>
-      </c>
-      <c r="AF16">
-        <v>1000</v>
-      </c>
-      <c r="AG16">
-        <v>1000</v>
-      </c>
-      <c r="AH16">
-        <v>1000</v>
-      </c>
-      <c r="AI16">
-        <v>1000</v>
-      </c>
-      <c r="AJ16">
-        <v>1000</v>
-      </c>
-      <c r="AK16">
-        <v>1000</v>
-      </c>
-      <c r="AL16">
-        <v>1000</v>
-      </c>
-      <c r="AM16">
-        <v>1000</v>
-      </c>
-      <c r="AN16">
-        <v>1000</v>
-      </c>
-      <c r="AO16">
-        <v>1000</v>
-      </c>
-      <c r="AP16">
-        <v>1.01</v>
-      </c>
-      <c r="AQ16">
-        <v>1.01</v>
-      </c>
-      <c r="AR16">
-        <v>1.01</v>
-      </c>
-      <c r="AS16">
-        <v>1.01</v>
-      </c>
-      <c r="AT16">
-        <v>1.01</v>
-      </c>
-      <c r="AU16">
-        <v>1.01</v>
-      </c>
-      <c r="AV16">
-        <v>1.01</v>
-      </c>
-      <c r="AW16">
-        <v>1.01</v>
-      </c>
-      <c r="AX16">
-        <v>1.01</v>
-      </c>
-      <c r="AY16">
-        <v>1.01</v>
-      </c>
-      <c r="AZ16">
-        <v>1.01</v>
-      </c>
-      <c r="BA16">
-        <v>1.01</v>
-      </c>
-      <c r="BB16">
-        <v>1.01</v>
-      </c>
-      <c r="BC16">
-        <v>1.01</v>
-      </c>
-      <c r="BD16">
-        <v>1.01</v>
-      </c>
-      <c r="BE16">
-        <v>1.01</v>
-      </c>
-      <c r="BF16">
-        <v>1.01</v>
-      </c>
-      <c r="BG16">
-        <v>1.01</v>
-      </c>
-      <c r="BH16">
-        <v>1000</v>
-      </c>
-      <c r="BI16">
-        <v>1.04</v>
-      </c>
-      <c r="BJ16">
-        <v>1000</v>
-      </c>
-      <c r="BK16">
-        <v>1.04</v>
-      </c>
-      <c r="BL16">
-        <v>1000</v>
-      </c>
-      <c r="BM16">
-        <v>1.04</v>
-      </c>
-      <c r="BN16">
-        <v>1000</v>
-      </c>
-      <c r="BO16">
-        <v>1.04</v>
-      </c>
-      <c r="BP16">
-        <v>1000</v>
-      </c>
-      <c r="BQ16">
-        <v>1.04</v>
-      </c>
-      <c r="BR16">
-        <v>1000</v>
-      </c>
-      <c r="BS16">
-        <v>1.04</v>
-      </c>
-      <c r="BT16">
-        <v>1000</v>
-      </c>
-      <c r="BU16">
-        <v>1.04</v>
-      </c>
-      <c r="BV16">
-        <v>1000</v>
-      </c>
-      <c r="BW16">
-        <v>1.04</v>
-      </c>
-      <c r="BX16">
-        <v>1000</v>
-      </c>
-      <c r="BY16">
-        <v>1.04</v>
-      </c>
-      <c r="BZ16">
-        <v>1000</v>
-      </c>
-      <c r="CA16">
-        <v>1.04</v>
-      </c>
-      <c r="CB16" t="s">
-        <v>131</v>
+      <c r="V21">
+        <v>1.73</v>
+      </c>
+      <c r="W21">
+        <v>1.33</v>
+      </c>
+      <c r="X21">
+        <v>12</v>
+      </c>
+      <c r="Y21">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z21">
+        <v>16</v>
+      </c>
+      <c r="AA21">
+        <v>38</v>
+      </c>
+      <c r="AB21">
+        <v>13.5</v>
+      </c>
+      <c r="AC21">
+        <v>8.6</v>
+      </c>
+      <c r="AD21">
+        <v>13.5</v>
+      </c>
+      <c r="AE21">
+        <v>34</v>
+      </c>
+      <c r="AF21">
+        <v>30</v>
+      </c>
+      <c r="AG21">
+        <v>17.5</v>
+      </c>
+      <c r="AH21">
+        <v>24</v>
+      </c>
+      <c r="AI21">
+        <v>60</v>
+      </c>
+      <c r="AJ21">
+        <v>95</v>
+      </c>
+      <c r="AK21">
+        <v>65</v>
+      </c>
+      <c r="AL21">
+        <v>85</v>
+      </c>
+      <c r="AM21">
+        <v>170</v>
+      </c>
+      <c r="AN21">
+        <v>85</v>
+      </c>
+      <c r="AO21">
+        <v>32</v>
+      </c>
+      <c r="AP21">
+        <v>8</v>
+      </c>
+      <c r="AQ21">
+        <v>6.2</v>
+      </c>
+      <c r="AR21">
+        <v>10.5</v>
+      </c>
+      <c r="AS21">
+        <v>5</v>
+      </c>
+      <c r="AT21">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU21">
+        <v>5.8</v>
+      </c>
+      <c r="AV21">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW21">
+        <v>4.9</v>
+      </c>
+      <c r="AX21">
+        <v>19</v>
+      </c>
+      <c r="AY21">
+        <v>12.5</v>
+      </c>
+      <c r="AZ21">
+        <v>17</v>
+      </c>
+      <c r="BA21">
+        <v>38</v>
+      </c>
+      <c r="BB21">
+        <v>5.4</v>
+      </c>
+      <c r="BC21">
+        <v>5.3</v>
+      </c>
+      <c r="BD21">
+        <v>5.4</v>
+      </c>
+      <c r="BE21">
+        <v>5.5</v>
+      </c>
+      <c r="BF21">
+        <v>5.4</v>
+      </c>
+      <c r="BG21">
+        <v>20</v>
+      </c>
+      <c r="BH21">
+        <v>3.25</v>
+      </c>
+      <c r="BI21">
+        <v>2.46</v>
+      </c>
+      <c r="BJ21">
+        <v>12</v>
+      </c>
+      <c r="BK21">
+        <v>4</v>
+      </c>
+      <c r="BL21">
+        <v>1000</v>
+      </c>
+      <c r="BM21">
+        <v>5.8</v>
+      </c>
+      <c r="BN21">
+        <v>7.8</v>
+      </c>
+      <c r="BO21">
+        <v>5.4</v>
+      </c>
+      <c r="BP21">
+        <v>40</v>
+      </c>
+      <c r="BQ21">
+        <v>5.2</v>
+      </c>
+      <c r="BR21">
+        <v>60</v>
+      </c>
+      <c r="BS21">
+        <v>5.5</v>
+      </c>
+      <c r="BT21">
+        <v>5.6</v>
+      </c>
+      <c r="BU21">
+        <v>3.95</v>
+      </c>
+      <c r="BV21">
+        <v>22</v>
+      </c>
+      <c r="BW21">
+        <v>4.7</v>
+      </c>
+      <c r="BX21">
+        <v>44</v>
+      </c>
+      <c r="BY21">
+        <v>5.3</v>
+      </c>
+      <c r="BZ21">
+        <v>44</v>
+      </c>
+      <c r="CA21">
+        <v>5.3</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
@@ -454,7 +454,7 @@
     <t>Millonarios</t>
   </si>
   <si>
-    <t>2026-08-26 12:32:50</t>
+    <t>2026-08-26 14:44:27</t>
   </si>
 </sst>
 </file>
@@ -1048,16 +1048,16 @@
         <v>126</v>
       </c>
       <c r="F2">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="G2">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I2">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="J2">
         <v>3.95</v>
@@ -1078,37 +1078,37 @@
         <v>1.36</v>
       </c>
       <c r="P2">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q2">
         <v>2.1</v>
       </c>
       <c r="R2">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S2">
         <v>3.95</v>
       </c>
       <c r="T2">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U2">
         <v>1.83</v>
       </c>
       <c r="V2">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W2">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="X2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z2">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AA2">
         <v>270</v>
@@ -1117,22 +1117,22 @@
         <v>7.6</v>
       </c>
       <c r="AC2">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AE2">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF2">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AG2">
         <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI2">
         <v>130</v>
@@ -1141,7 +1141,7 @@
         <v>16</v>
       </c>
       <c r="AK2">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AL2">
         <v>46</v>
@@ -1156,118 +1156,118 @@
         <v>210</v>
       </c>
       <c r="AP2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AR2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AS2">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT2">
         <v>6.2</v>
       </c>
       <c r="AU2">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AV2">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW2">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="AX2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BA2">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="BB2">
         <v>13</v>
       </c>
       <c r="BC2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BD2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE2">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BF2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG2">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH2">
         <v>3.4</v>
       </c>
       <c r="BI2">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BJ2">
         <v>12</v>
       </c>
       <c r="BK2">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN2">
         <v>4.1</v>
       </c>
       <c r="BO2">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="BP2">
         <v>11.5</v>
       </c>
       <c r="BQ2">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BR2">
         <v>30</v>
       </c>
       <c r="BS2">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BU2">
         <v>5.4</v>
       </c>
       <c r="BV2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BW2">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BX2">
         <v>75</v>
       </c>
       <c r="BY2">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ2">
         <v>24</v>
       </c>
       <c r="CA2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB2" t="s">
         <v>146</v>
@@ -1299,13 +1299,13 @@
         <v>3.9</v>
       </c>
       <c r="I3">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="J3">
         <v>2.42</v>
       </c>
       <c r="K3">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="L3">
         <v>1.6</v>
@@ -1320,7 +1320,7 @@
         <v>1.42</v>
       </c>
       <c r="P3">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="Q3">
         <v>3.35</v>
@@ -1338,7 +1338,7 @@
         <v>1.5</v>
       </c>
       <c r="V3">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W3">
         <v>1.56</v>
@@ -1359,7 +1359,7 @@
         <v>970</v>
       </c>
       <c r="AC3">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AD3">
         <v>950</v>
@@ -1368,10 +1368,10 @@
         <v>1000</v>
       </c>
       <c r="AF3">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AG3">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AH3">
         <v>1000</v>
@@ -1398,28 +1398,28 @@
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AQ3">
         <v>7.2</v>
       </c>
       <c r="AR3">
-        <v>1.69</v>
+        <v>15.5</v>
       </c>
       <c r="AS3">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AT3">
         <v>4.8</v>
       </c>
       <c r="AU3">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AV3">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AW3">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AX3">
         <v>8.6</v>
@@ -1428,28 +1428,28 @@
         <v>9.4</v>
       </c>
       <c r="AZ3">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="BA3">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="BB3">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="BC3">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="BD3">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="BE3">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="BF3">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="BG3">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1535,10 +1535,10 @@
         <v>2.64</v>
       </c>
       <c r="G4">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H4">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="I4">
         <v>2.72</v>
@@ -1550,28 +1550,28 @@
         <v>4.4</v>
       </c>
       <c r="L4">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N4">
-        <v>4.7</v>
+        <v>2.16</v>
       </c>
       <c r="O4">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="P4">
-        <v>2.36</v>
+        <v>2.16</v>
       </c>
       <c r="Q4">
         <v>1.58</v>
       </c>
       <c r="R4">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="S4">
-        <v>2.44</v>
+        <v>2.24</v>
       </c>
       <c r="T4">
         <v>1.53</v>
@@ -1583,13 +1583,13 @@
         <v>1.58</v>
       </c>
       <c r="W4">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X4">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Y4">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="Z4">
         <v>23</v>
@@ -1598,7 +1598,7 @@
         <v>42</v>
       </c>
       <c r="AB4">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AC4">
         <v>10</v>
@@ -1610,85 +1610,85 @@
         <v>28</v>
       </c>
       <c r="AF4">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AG4">
         <v>14</v>
       </c>
       <c r="AH4">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AI4">
         <v>36</v>
       </c>
       <c r="AJ4">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AK4">
         <v>32</v>
       </c>
       <c r="AL4">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AM4">
         <v>70</v>
       </c>
       <c r="AN4">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AO4">
         <v>17</v>
       </c>
       <c r="AP4">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ4">
+        <v>13</v>
+      </c>
+      <c r="AR4">
+        <v>15</v>
+      </c>
+      <c r="AS4">
+        <v>5.2</v>
+      </c>
+      <c r="AT4">
         <v>12</v>
-      </c>
-      <c r="AR4">
-        <v>16.5</v>
-      </c>
-      <c r="AS4">
-        <v>5.5</v>
-      </c>
-      <c r="AT4">
-        <v>13.5</v>
       </c>
       <c r="AU4">
         <v>8.199999999999999</v>
       </c>
       <c r="AV4">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AW4">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AX4">
         <v>16.5</v>
       </c>
       <c r="AY4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ4">
         <v>12.5</v>
       </c>
       <c r="BA4">
-        <v>25</v>
+        <v>5.1</v>
       </c>
       <c r="BB4">
-        <v>34</v>
+        <v>5.3</v>
       </c>
       <c r="BC4">
         <v>20</v>
       </c>
       <c r="BD4">
-        <v>27</v>
+        <v>5.1</v>
       </c>
       <c r="BE4">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="BF4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BG4">
         <v>11</v>
@@ -1786,10 +1786,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="J5">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K5">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L5">
         <v>1.38</v>
@@ -1822,7 +1822,7 @@
         <v>1.77</v>
       </c>
       <c r="V5">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W5">
         <v>2.54</v>
@@ -2028,10 +2028,10 @@
         <v>1.93</v>
       </c>
       <c r="J6">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K6">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="L6">
         <v>1.34</v>
@@ -2046,10 +2046,10 @@
         <v>1.27</v>
       </c>
       <c r="P6">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="Q6">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="R6">
         <v>1.32</v>
@@ -2085,7 +2085,7 @@
         <v>21</v>
       </c>
       <c r="AC6">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AD6">
         <v>12.5</v>
@@ -2124,58 +2124,58 @@
         <v>16</v>
       </c>
       <c r="AP6">
-        <v>10</v>
+        <v>3.6</v>
       </c>
       <c r="AQ6">
-        <v>6.2</v>
+        <v>3.15</v>
       </c>
       <c r="AR6">
-        <v>8</v>
+        <v>3.4</v>
       </c>
       <c r="AS6">
-        <v>14.5</v>
+        <v>3.85</v>
       </c>
       <c r="AT6">
-        <v>12</v>
+        <v>3.75</v>
       </c>
       <c r="AU6">
-        <v>6.4</v>
+        <v>3</v>
       </c>
       <c r="AV6">
-        <v>7.6</v>
+        <v>3.35</v>
       </c>
       <c r="AW6">
-        <v>14.5</v>
+        <v>3.85</v>
       </c>
       <c r="AX6">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AY6">
-        <v>14.5</v>
+        <v>3.85</v>
       </c>
       <c r="AZ6">
-        <v>14.5</v>
+        <v>3.85</v>
       </c>
       <c r="BA6">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BB6">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BC6">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BD6">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BE6">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BF6">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BG6">
-        <v>9.6</v>
+        <v>3.55</v>
       </c>
       <c r="BH6">
         <v>3.45</v>
@@ -2264,19 +2264,19 @@
         <v>3.95</v>
       </c>
       <c r="H7">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="I7">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="J7">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K7">
         <v>4.3</v>
       </c>
       <c r="L7">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="M7">
         <v>1.03</v>
@@ -2294,19 +2294,19 @@
         <v>1.58</v>
       </c>
       <c r="R7">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S7">
         <v>2.44</v>
       </c>
       <c r="T7">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="U7">
         <v>2.46</v>
       </c>
       <c r="V7">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="W7">
         <v>1.34</v>
@@ -2327,13 +2327,13 @@
         <v>26</v>
       </c>
       <c r="AC7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD7">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE7">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AF7">
         <v>34</v>
@@ -2348,10 +2348,10 @@
         <v>32</v>
       </c>
       <c r="AJ7">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AK7">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AL7">
         <v>55</v>
@@ -2360,7 +2360,7 @@
         <v>65</v>
       </c>
       <c r="AN7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO7">
         <v>10.5</v>
@@ -2372,46 +2372,46 @@
         <v>10.5</v>
       </c>
       <c r="AR7">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AS7">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AT7">
         <v>18</v>
       </c>
       <c r="AU7">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AV7">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AW7">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AX7">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="AY7">
         <v>12.5</v>
       </c>
       <c r="AZ7">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA7">
         <v>18.5</v>
       </c>
       <c r="BB7">
-        <v>5.4</v>
+        <v>30</v>
       </c>
       <c r="BC7">
-        <v>5.2</v>
+        <v>32</v>
       </c>
       <c r="BD7">
-        <v>32</v>
+        <v>6.2</v>
       </c>
       <c r="BE7">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BF7">
         <v>19</v>
@@ -2420,64 +2420,64 @@
         <v>8.4</v>
       </c>
       <c r="BH7">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BI7">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BJ7">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BK7">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="BL7">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM7">
-        <v>9.4</v>
+        <v>4.4</v>
       </c>
       <c r="BN7">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BO7">
         <v>5.4</v>
       </c>
       <c r="BP7">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BQ7">
-        <v>7.6</v>
+        <v>4</v>
       </c>
       <c r="BR7">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BS7">
-        <v>8</v>
+        <v>4.1</v>
       </c>
       <c r="BT7">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU7">
         <v>4</v>
       </c>
       <c r="BV7">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BW7">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="BX7">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BY7">
-        <v>7.2</v>
+        <v>4</v>
       </c>
       <c r="BZ7">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="CA7">
-        <v>6.4</v>
+        <v>3.75</v>
       </c>
       <c r="CB7" t="s">
         <v>146</v>
@@ -2503,22 +2503,22 @@
         <v>1.27</v>
       </c>
       <c r="G8">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="H8">
         <v>16.5</v>
       </c>
       <c r="I8">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J8">
         <v>5.2</v>
       </c>
       <c r="K8">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L8">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M8">
         <v>1.07</v>
@@ -2530,7 +2530,7 @@
         <v>1.33</v>
       </c>
       <c r="P8">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="Q8">
         <v>1.99</v>
@@ -2548,16 +2548,16 @@
         <v>1.49</v>
       </c>
       <c r="V8">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W8">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="X8">
         <v>18</v>
       </c>
       <c r="Y8">
-        <v>48</v>
+        <v>950</v>
       </c>
       <c r="Z8">
         <v>230</v>
@@ -2566,22 +2566,22 @@
         <v>1000</v>
       </c>
       <c r="AB8">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="AC8">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AD8">
         <v>950</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>640</v>
       </c>
       <c r="AF8">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AG8">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH8">
         <v>60</v>
@@ -2590,19 +2590,19 @@
         <v>460</v>
       </c>
       <c r="AJ8">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AK8">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AL8">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM8">
         <v>530</v>
       </c>
       <c r="AN8">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AO8">
         <v>1000</v>
@@ -2611,25 +2611,25 @@
         <v>10.5</v>
       </c>
       <c r="AQ8">
-        <v>4.1</v>
+        <v>28</v>
       </c>
       <c r="AR8">
-        <v>4.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS8">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="AT8">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AU8">
         <v>10</v>
       </c>
       <c r="AV8">
-        <v>4.3</v>
+        <v>8</v>
       </c>
       <c r="AW8">
-        <v>4.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX8">
         <v>5.4</v>
@@ -2641,7 +2641,7 @@
         <v>36</v>
       </c>
       <c r="BA8">
-        <v>4.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB8">
         <v>6.8</v>
@@ -2650,22 +2650,22 @@
         <v>13</v>
       </c>
       <c r="BD8">
-        <v>4.3</v>
+        <v>8</v>
       </c>
       <c r="BE8">
-        <v>4.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF8">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BG8">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="BH8">
         <v>4</v>
       </c>
       <c r="BI8">
-        <v>3.05</v>
+        <v>2.76</v>
       </c>
       <c r="BJ8">
         <v>19.5</v>
@@ -2683,7 +2683,7 @@
         <v>3.85</v>
       </c>
       <c r="BO8">
-        <v>2.94</v>
+        <v>2.66</v>
       </c>
       <c r="BP8">
         <v>9</v>
@@ -2742,19 +2742,19 @@
         <v>133</v>
       </c>
       <c r="F9">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="G9">
         <v>4.2</v>
       </c>
       <c r="H9">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I9">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="J9">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="K9">
         <v>3.2</v>
@@ -2766,7 +2766,7 @@
         <v>1.13</v>
       </c>
       <c r="N9">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="O9">
         <v>1.58</v>
@@ -2778,7 +2778,7 @@
         <v>2.8</v>
       </c>
       <c r="R9">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S9">
         <v>5.7</v>
@@ -2787,10 +2787,10 @@
         <v>2.18</v>
       </c>
       <c r="U9">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V9">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W9">
         <v>1.32</v>
@@ -2817,7 +2817,7 @@
         <v>15.5</v>
       </c>
       <c r="AE9">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF9">
         <v>27</v>
@@ -2853,13 +2853,13 @@
         <v>6</v>
       </c>
       <c r="AQ9">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AR9">
         <v>10</v>
       </c>
       <c r="AS9">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AT9">
         <v>7.4</v>
@@ -2871,7 +2871,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW9">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AX9">
         <v>18.5</v>
@@ -2880,34 +2880,34 @@
         <v>12.5</v>
       </c>
       <c r="AZ9">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="BA9">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BB9">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BC9">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BD9">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BE9">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BF9">
+        <v>5.8</v>
+      </c>
+      <c r="BG9">
         <v>5.4</v>
-      </c>
-      <c r="BG9">
-        <v>5</v>
       </c>
       <c r="BH9">
         <v>2.96</v>
       </c>
       <c r="BI9">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="BJ9">
         <v>14</v>
@@ -2919,7 +2919,7 @@
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BN9">
         <v>8.199999999999999</v>
@@ -2931,7 +2931,7 @@
         <v>48</v>
       </c>
       <c r="BQ9">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BR9">
         <v>1000</v>
@@ -2958,7 +2958,7 @@
         <v>4.7</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="CA9">
         <v>4.8</v>
@@ -2993,19 +2993,19 @@
         <v>2.56</v>
       </c>
       <c r="I10">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="J10">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K10">
         <v>3.7</v>
       </c>
       <c r="L10">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M10">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N10">
         <v>3.35</v>
@@ -3014,7 +3014,7 @@
         <v>1.35</v>
       </c>
       <c r="P10">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="Q10">
         <v>1.94</v>
@@ -3023,16 +3023,16 @@
         <v>1.3</v>
       </c>
       <c r="S10">
-        <v>3.25</v>
+        <v>2.58</v>
       </c>
       <c r="T10">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="U10">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V10">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W10">
         <v>1.47</v>
@@ -3092,58 +3092,58 @@
         <v>34</v>
       </c>
       <c r="AP10">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AQ10">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AR10">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS10">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT10">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AU10">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AV10">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AW10">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX10">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AY10">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AZ10">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA10">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB10">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BC10">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD10">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE10">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF10">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG10">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH10">
         <v>3.35</v>
@@ -3232,25 +3232,25 @@
         <v>1.88</v>
       </c>
       <c r="H11">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="I11">
         <v>7.6</v>
       </c>
       <c r="J11">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="K11">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L11">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="M11">
         <v>1.11</v>
       </c>
       <c r="N11">
-        <v>2.48</v>
+        <v>2.72</v>
       </c>
       <c r="O11">
         <v>1.47</v>
@@ -3259,13 +3259,13 @@
         <v>1.59</v>
       </c>
       <c r="Q11">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="R11">
         <v>1.21</v>
       </c>
       <c r="S11">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="T11">
         <v>1.99</v>
@@ -3274,7 +3274,7 @@
         <v>1.71</v>
       </c>
       <c r="V11">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W11">
         <v>2.12</v>
@@ -3307,7 +3307,7 @@
         <v>9.6</v>
       </c>
       <c r="AG11">
-        <v>13</v>
+        <v>950</v>
       </c>
       <c r="AH11">
         <v>950</v>
@@ -3334,58 +3334,58 @@
         <v>250</v>
       </c>
       <c r="AP11">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="AQ11">
-        <v>4.9</v>
+        <v>11</v>
       </c>
       <c r="AR11">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS11">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="AT11">
-        <v>3.45</v>
+        <v>5.7</v>
       </c>
       <c r="AU11">
-        <v>3.85</v>
+        <v>6</v>
       </c>
       <c r="AV11">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AW11">
-        <v>6.8</v>
+        <v>4.6</v>
       </c>
       <c r="AX11">
-        <v>4.1</v>
+        <v>8.4</v>
       </c>
       <c r="AY11">
-        <v>4.6</v>
+        <v>7.8</v>
       </c>
       <c r="AZ11">
-        <v>5.7</v>
+        <v>19</v>
       </c>
       <c r="BA11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB11">
-        <v>5.3</v>
+        <v>17</v>
       </c>
       <c r="BC11">
-        <v>5.8</v>
+        <v>20</v>
       </c>
       <c r="BD11">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE11">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="BF11">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BG11">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="BH11">
         <v>3.3</v>
@@ -3409,7 +3409,7 @@
         <v>4.8</v>
       </c>
       <c r="BO11">
-        <v>2.46</v>
+        <v>3.2</v>
       </c>
       <c r="BP11">
         <v>16.5</v>
@@ -3468,31 +3468,31 @@
         <v>136</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="G12">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="H12">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I12">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J12">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K12">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L12">
         <v>1.51</v>
       </c>
       <c r="M12">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N12">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O12">
         <v>1.42</v>
@@ -3516,16 +3516,16 @@
         <v>1.92</v>
       </c>
       <c r="V12">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W12">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="X12">
         <v>11</v>
       </c>
       <c r="Y12">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z12">
         <v>32</v>
@@ -3534,16 +3534,16 @@
         <v>110</v>
       </c>
       <c r="AB12">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC12">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD12">
         <v>18</v>
       </c>
       <c r="AE12">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AF12">
         <v>11</v>
@@ -3555,13 +3555,13 @@
         <v>22</v>
       </c>
       <c r="AI12">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ12">
         <v>24</v>
       </c>
       <c r="AK12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL12">
         <v>44</v>
@@ -3579,10 +3579,10 @@
         <v>10.5</v>
       </c>
       <c r="AQ12">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR12">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS12">
         <v>95</v>
@@ -3606,19 +3606,19 @@
         <v>10</v>
       </c>
       <c r="AZ12">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA12">
         <v>65</v>
       </c>
       <c r="BB12">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC12">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD12">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BE12">
         <v>44</v>
@@ -3627,7 +3627,7 @@
         <v>16.5</v>
       </c>
       <c r="BG12">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BH12">
         <v>3</v>
@@ -3719,28 +3719,28 @@
         <v>5.2</v>
       </c>
       <c r="I13">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="J13">
         <v>4.4</v>
       </c>
       <c r="K13">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L13">
         <v>1.24</v>
       </c>
       <c r="M13">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N13">
         <v>5.2</v>
       </c>
       <c r="O13">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="P13">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="Q13">
         <v>1.59</v>
@@ -3752,7 +3752,7 @@
         <v>2.46</v>
       </c>
       <c r="T13">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U13">
         <v>2.26</v>
@@ -3809,7 +3809,7 @@
         <v>28</v>
       </c>
       <c r="AM13">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN13">
         <v>7</v>
@@ -3824,7 +3824,7 @@
         <v>18</v>
       </c>
       <c r="AR13">
-        <v>6.8</v>
+        <v>28</v>
       </c>
       <c r="AS13">
         <v>7.4</v>
@@ -3958,16 +3958,16 @@
         <v>1.39</v>
       </c>
       <c r="H14">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="I14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J14">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="K14">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="L14">
         <v>1.2</v>
@@ -3976,19 +3976,19 @@
         <v>1.02</v>
       </c>
       <c r="N14">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="O14">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P14">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="Q14">
         <v>1.43</v>
       </c>
       <c r="R14">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="S14">
         <v>2.08</v>
@@ -4000,7 +4000,7 @@
         <v>1.96</v>
       </c>
       <c r="V14">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W14">
         <v>3.55</v>
@@ -4108,7 +4108,7 @@
         <v>6.8</v>
       </c>
       <c r="BF14">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="BG14">
         <v>6.8</v>
@@ -4194,22 +4194,22 @@
         <v>139</v>
       </c>
       <c r="F15">
+        <v>1.3</v>
+      </c>
+      <c r="G15">
         <v>1.31</v>
       </c>
-      <c r="G15">
-        <v>1.33</v>
-      </c>
       <c r="H15">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="I15">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="J15">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="K15">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="L15">
         <v>1.26</v>
@@ -4233,43 +4233,43 @@
         <v>1.8</v>
       </c>
       <c r="S15">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="T15">
         <v>1.86</v>
       </c>
       <c r="U15">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V15">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W15">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="X15">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Y15">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Z15">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AA15">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="AB15">
         <v>12.5</v>
       </c>
       <c r="AC15">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AD15">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AE15">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="AF15">
         <v>9.4</v>
@@ -4278,7 +4278,7 @@
         <v>10.5</v>
       </c>
       <c r="AH15">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI15">
         <v>110</v>
@@ -4296,13 +4296,13 @@
         <v>110</v>
       </c>
       <c r="AN15">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AO15">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AP15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ15">
         <v>40</v>
@@ -4317,13 +4317,13 @@
         <v>11.5</v>
       </c>
       <c r="AU15">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AV15">
         <v>34</v>
       </c>
       <c r="AW15">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="AX15">
         <v>9</v>
@@ -4332,13 +4332,13 @@
         <v>10</v>
       </c>
       <c r="AZ15">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA15">
         <v>90</v>
       </c>
       <c r="BB15">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BC15">
         <v>11.5</v>
@@ -4347,13 +4347,13 @@
         <v>26</v>
       </c>
       <c r="BE15">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BF15">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BG15">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BH15">
         <v>5.8</v>
@@ -4362,7 +4362,7 @@
         <v>4.4</v>
       </c>
       <c r="BJ15">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK15">
         <v>9.6</v>
@@ -4377,7 +4377,7 @@
         <v>4.1</v>
       </c>
       <c r="BO15">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="BP15">
         <v>9</v>
@@ -4389,7 +4389,7 @@
         <v>20</v>
       </c>
       <c r="BS15">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BT15">
         <v>16</v>
@@ -4410,7 +4410,7 @@
         <v>6.2</v>
       </c>
       <c r="BZ15">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="CA15">
         <v>8</v>
@@ -4439,55 +4439,55 @@
         <v>1.48</v>
       </c>
       <c r="G16">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="H16">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="I16">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="J16">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="K16">
         <v>4.4</v>
       </c>
       <c r="L16">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="M16">
         <v>1.1</v>
       </c>
       <c r="N16">
+        <v>2.76</v>
+      </c>
+      <c r="O16">
+        <v>1.46</v>
+      </c>
+      <c r="P16">
+        <v>1.6</v>
+      </c>
+      <c r="Q16">
+        <v>2.4</v>
+      </c>
+      <c r="R16">
+        <v>1.21</v>
+      </c>
+      <c r="S16">
+        <v>4.8</v>
+      </c>
+      <c r="T16">
+        <v>2.52</v>
+      </c>
+      <c r="U16">
+        <v>1.55</v>
+      </c>
+      <c r="V16">
+        <v>1.09</v>
+      </c>
+      <c r="W16">
         <v>2.8</v>
-      </c>
-      <c r="O16">
-        <v>1.44</v>
-      </c>
-      <c r="P16">
-        <v>1.56</v>
-      </c>
-      <c r="Q16">
-        <v>2.3</v>
-      </c>
-      <c r="R16">
-        <v>1.12</v>
-      </c>
-      <c r="S16">
-        <v>2.74</v>
-      </c>
-      <c r="T16">
-        <v>2.34</v>
-      </c>
-      <c r="U16">
-        <v>1.48</v>
-      </c>
-      <c r="V16">
-        <v>1.08</v>
-      </c>
-      <c r="W16">
-        <v>2.78</v>
       </c>
       <c r="X16">
         <v>12</v>
@@ -4502,10 +4502,10 @@
         <v>620</v>
       </c>
       <c r="AB16">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AC16">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD16">
         <v>48</v>
@@ -4514,7 +4514,7 @@
         <v>310</v>
       </c>
       <c r="AF16">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AG16">
         <v>13</v>
@@ -4544,61 +4544,61 @@
         <v>1000</v>
       </c>
       <c r="AP16">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AQ16">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AR16">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AS16">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AT16">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AU16">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV16">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AW16">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AX16">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AY16">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ16">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BA16">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BB16">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BC16">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BD16">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BE16">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH16">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="BI16">
         <v>2.44</v>
@@ -4607,13 +4607,13 @@
         <v>16.5</v>
       </c>
       <c r="BK16">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BN16">
         <v>4</v>
@@ -4625,37 +4625,37 @@
         <v>12</v>
       </c>
       <c r="BQ16">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BR16">
         <v>44</v>
       </c>
       <c r="BS16">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT16">
         <v>15</v>
       </c>
       <c r="BU16">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BZ16">
         <v>32</v>
       </c>
       <c r="CA16">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="CB16" t="s">
         <v>146</v>
@@ -4684,7 +4684,7 @@
         <v>4.4</v>
       </c>
       <c r="H17">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="I17">
         <v>1.91</v>
@@ -4702,7 +4702,7 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="O17">
         <v>1.07</v>
@@ -4717,7 +4717,7 @@
         <v>2.16</v>
       </c>
       <c r="S17">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="T17">
         <v>1.3</v>
@@ -4732,7 +4732,7 @@
         <v>1.29</v>
       </c>
       <c r="X17">
-        <v>70</v>
+        <v>950</v>
       </c>
       <c r="Y17">
         <v>30</v>
@@ -4786,58 +4786,58 @@
         <v>5.4</v>
       </c>
       <c r="AP17">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AQ17">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AR17">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AS17">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT17">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AU17">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AV17">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AW17">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX17">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AY17">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AZ17">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA17">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB17">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BC17">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD17">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE17">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BF17">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG17">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BH17">
         <v>7.6</v>
@@ -4920,58 +4920,58 @@
         <v>142</v>
       </c>
       <c r="F18">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="G18">
-        <v>1000</v>
+        <v>2.2</v>
       </c>
       <c r="H18">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="I18">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J18">
-        <v>1.02</v>
+        <v>1.86</v>
       </c>
       <c r="K18">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L18">
         <v>1.01</v>
       </c>
       <c r="M18">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N18">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="O18">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="P18">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="Q18">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="R18">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="S18">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="T18">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U18">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V18">
         <v>1.01</v>
       </c>
       <c r="W18">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="X18">
         <v>1000</v>
@@ -5085,61 +5085,61 @@
         <v>1000</v>
       </c>
       <c r="BI18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ18">
         <v>1000</v>
       </c>
       <c r="BK18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN18">
         <v>1000</v>
       </c>
       <c r="BO18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP18">
         <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR18">
         <v>1000</v>
       </c>
       <c r="BS18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT18">
         <v>1000</v>
       </c>
       <c r="BU18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV18">
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ18">
         <v>1000</v>
       </c>
       <c r="CA18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB18" t="s">
         <v>146</v>
@@ -5162,19 +5162,19 @@
         <v>143</v>
       </c>
       <c r="F19">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="G19">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H19">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="I19">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J19">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K19">
         <v>950</v>
@@ -5183,31 +5183,31 @@
         <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N19">
+        <v>1.26</v>
+      </c>
+      <c r="O19">
+        <v>1.44</v>
+      </c>
+      <c r="P19">
         <v>1.25</v>
       </c>
-      <c r="O19">
-        <v>1.01</v>
-      </c>
-      <c r="P19">
-        <v>1.24</v>
-      </c>
       <c r="Q19">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="R19">
         <v>1.18</v>
       </c>
       <c r="S19">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="T19">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U19">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V19">
         <v>1.01</v>
@@ -5270,52 +5270,52 @@
         <v>1000</v>
       </c>
       <c r="AP19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF19">
         <v>1.01</v>
@@ -5327,61 +5327,61 @@
         <v>1000</v>
       </c>
       <c r="BI19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ19">
         <v>1000</v>
       </c>
       <c r="BK19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN19">
         <v>1000</v>
       </c>
       <c r="BO19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP19">
         <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT19">
         <v>1000</v>
       </c>
       <c r="BU19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV19">
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19">
         <v>1000</v>
       </c>
       <c r="CA19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB19" t="s">
         <v>146</v>
@@ -5407,19 +5407,19 @@
         <v>1.93</v>
       </c>
       <c r="G20">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H20">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="I20">
         <v>4</v>
       </c>
       <c r="J20">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="K20">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L20">
         <v>1.25</v>
@@ -5428,34 +5428,34 @@
         <v>1.01</v>
       </c>
       <c r="N20">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O20">
         <v>1.18</v>
       </c>
       <c r="P20">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q20">
         <v>1.54</v>
       </c>
       <c r="R20">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S20">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T20">
         <v>1.53</v>
       </c>
       <c r="U20">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V20">
         <v>1.33</v>
       </c>
       <c r="W20">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X20">
         <v>29</v>
@@ -5464,166 +5464,166 @@
         <v>23</v>
       </c>
       <c r="Z20">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA20">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB20">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC20">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD20">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE20">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF20">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AG20">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH20">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AI20">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AJ20">
+        <v>26</v>
+      </c>
+      <c r="AK20">
+        <v>21</v>
+      </c>
+      <c r="AL20">
         <v>29</v>
       </c>
-      <c r="AK20">
-        <v>22</v>
-      </c>
-      <c r="AL20">
+      <c r="AM20">
+        <v>65</v>
+      </c>
+      <c r="AN20">
+        <v>10.5</v>
+      </c>
+      <c r="AO20">
+        <v>27</v>
+      </c>
+      <c r="AP20">
+        <v>5.8</v>
+      </c>
+      <c r="AQ20">
+        <v>16.5</v>
+      </c>
+      <c r="AR20">
+        <v>5.9</v>
+      </c>
+      <c r="AS20">
+        <v>6.6</v>
+      </c>
+      <c r="AT20">
+        <v>10.5</v>
+      </c>
+      <c r="AU20">
+        <v>8.4</v>
+      </c>
+      <c r="AV20">
+        <v>12</v>
+      </c>
+      <c r="AW20">
+        <v>6</v>
+      </c>
+      <c r="AX20">
+        <v>12</v>
+      </c>
+      <c r="AY20">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ20">
+        <v>12</v>
+      </c>
+      <c r="BA20">
+        <v>6</v>
+      </c>
+      <c r="BB20">
+        <v>5.7</v>
+      </c>
+      <c r="BC20">
+        <v>14.5</v>
+      </c>
+      <c r="BD20">
+        <v>20</v>
+      </c>
+      <c r="BE20">
+        <v>6.4</v>
+      </c>
+      <c r="BF20">
+        <v>4.3</v>
+      </c>
+      <c r="BG20">
+        <v>19</v>
+      </c>
+      <c r="BH20">
+        <v>4.7</v>
+      </c>
+      <c r="BI20">
+        <v>3.55</v>
+      </c>
+      <c r="BJ20">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK20">
+        <v>4.4</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>7.8</v>
+      </c>
+      <c r="BN20">
+        <v>5.6</v>
+      </c>
+      <c r="BO20">
+        <v>4.2</v>
+      </c>
+      <c r="BP20">
+        <v>14</v>
+      </c>
+      <c r="BQ20">
+        <v>5.3</v>
+      </c>
+      <c r="BR20">
+        <v>23</v>
+      </c>
+      <c r="BS20">
+        <v>6.2</v>
+      </c>
+      <c r="BT20">
+        <v>7.8</v>
+      </c>
+      <c r="BU20">
+        <v>5.8</v>
+      </c>
+      <c r="BV20">
+        <v>27</v>
+      </c>
+      <c r="BW20">
+        <v>6.4</v>
+      </c>
+      <c r="BX20">
         <v>32</v>
       </c>
-      <c r="AM20">
-        <v>70</v>
-      </c>
-      <c r="AN20">
-        <v>11.5</v>
-      </c>
-      <c r="AO20">
-        <v>29</v>
-      </c>
-      <c r="AP20">
-        <v>1.01</v>
-      </c>
-      <c r="AQ20">
-        <v>1.01</v>
-      </c>
-      <c r="AR20">
-        <v>1.01</v>
-      </c>
-      <c r="AS20">
-        <v>1.03</v>
-      </c>
-      <c r="AT20">
-        <v>1.01</v>
-      </c>
-      <c r="AU20">
-        <v>1.01</v>
-      </c>
-      <c r="AV20">
-        <v>1.01</v>
-      </c>
-      <c r="AW20">
-        <v>1.01</v>
-      </c>
-      <c r="AX20">
-        <v>1.01</v>
-      </c>
-      <c r="AY20">
-        <v>1.01</v>
-      </c>
-      <c r="AZ20">
-        <v>1.01</v>
-      </c>
-      <c r="BA20">
-        <v>1.01</v>
-      </c>
-      <c r="BB20">
-        <v>1.01</v>
-      </c>
-      <c r="BC20">
-        <v>1.01</v>
-      </c>
-      <c r="BD20">
-        <v>1.01</v>
-      </c>
-      <c r="BE20">
-        <v>1.03</v>
-      </c>
-      <c r="BF20">
-        <v>1.01</v>
-      </c>
-      <c r="BG20">
-        <v>1.01</v>
-      </c>
-      <c r="BH20">
-        <v>1000</v>
-      </c>
-      <c r="BI20">
-        <v>1.01</v>
-      </c>
-      <c r="BJ20">
-        <v>1000</v>
-      </c>
-      <c r="BK20">
-        <v>1.01</v>
-      </c>
-      <c r="BL20">
-        <v>1000</v>
-      </c>
-      <c r="BM20">
-        <v>1.01</v>
-      </c>
-      <c r="BN20">
-        <v>1000</v>
-      </c>
-      <c r="BO20">
-        <v>1.01</v>
-      </c>
-      <c r="BP20">
-        <v>1000</v>
-      </c>
-      <c r="BQ20">
-        <v>1.01</v>
-      </c>
-      <c r="BR20">
-        <v>1000</v>
-      </c>
-      <c r="BS20">
-        <v>1.01</v>
-      </c>
-      <c r="BT20">
-        <v>1000</v>
-      </c>
-      <c r="BU20">
-        <v>1.01</v>
-      </c>
-      <c r="BV20">
-        <v>1000</v>
-      </c>
-      <c r="BW20">
-        <v>1.01</v>
-      </c>
-      <c r="BX20">
-        <v>1000</v>
-      </c>
       <c r="BY20">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BZ20">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="CA20">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="CB20" t="s">
         <v>146</v>
@@ -5658,7 +5658,7 @@
         <v>2.4</v>
       </c>
       <c r="J21">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="K21">
         <v>3.4</v>
@@ -5670,25 +5670,25 @@
         <v>1.1</v>
       </c>
       <c r="N21">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O21">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P21">
         <v>1.64</v>
       </c>
       <c r="Q21">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R21">
         <v>1.24</v>
       </c>
       <c r="S21">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="T21">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="U21">
         <v>1.89</v>
@@ -5697,16 +5697,16 @@
         <v>1.73</v>
       </c>
       <c r="W21">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X21">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Y21">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z21">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA21">
         <v>38</v>
@@ -5715,7 +5715,7 @@
         <v>13.5</v>
       </c>
       <c r="AC21">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD21">
         <v>13.5</v>
@@ -5727,7 +5727,7 @@
         <v>30</v>
       </c>
       <c r="AG21">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH21">
         <v>24</v>
@@ -5754,58 +5754,58 @@
         <v>32</v>
       </c>
       <c r="AP21">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ21">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AR21">
         <v>10.5</v>
       </c>
       <c r="AS21">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AT21">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU21">
         <v>5.8</v>
       </c>
       <c r="AV21">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW21">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AX21">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AY21">
         <v>12.5</v>
       </c>
       <c r="AZ21">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA21">
-        <v>38</v>
+        <v>5.9</v>
       </c>
       <c r="BB21">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BC21">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BD21">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BE21">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BF21">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BG21">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BH21">
         <v>3.25</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="149">
   <si>
     <t>League</t>
   </si>
@@ -388,6 +388,9 @@
     <t>22 de Julio FC</t>
   </si>
   <si>
+    <t>San Antonio FC</t>
+  </si>
+  <si>
     <t>Club Independiente Petrolero</t>
   </si>
   <si>
@@ -448,13 +451,16 @@
     <t>Deportivo Santo Domingo</t>
   </si>
   <si>
+    <t>Independiente Juniors</t>
+  </si>
+  <si>
     <t>Guabira</t>
   </si>
   <si>
     <t>Millonarios</t>
   </si>
   <si>
-    <t>2026-08-26 14:44:27</t>
+    <t>2026-08-26 17:01:58</t>
   </si>
 </sst>
 </file>
@@ -786,7 +792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB21"/>
+  <dimension ref="A1:CB22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1045,70 +1051,70 @@
         <v>106</v>
       </c>
       <c r="E2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F2">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="G2">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I2">
         <v>7.6</v>
       </c>
       <c r="J2">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K2">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L2">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M2">
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O2">
         <v>1.36</v>
       </c>
       <c r="P2">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="Q2">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R2">
         <v>1.32</v>
       </c>
       <c r="S2">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="T2">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U2">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V2">
         <v>1.16</v>
       </c>
       <c r="W2">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="X2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y2">
         <v>22</v>
       </c>
       <c r="Z2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA2">
         <v>270</v>
@@ -1117,16 +1123,16 @@
         <v>7.6</v>
       </c>
       <c r="AC2">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AE2">
         <v>130</v>
       </c>
       <c r="AF2">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AG2">
         <v>10.5</v>
@@ -1135,22 +1141,22 @@
         <v>26</v>
       </c>
       <c r="AI2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AK2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM2">
         <v>190</v>
       </c>
       <c r="AN2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO2">
         <v>210</v>
@@ -1165,52 +1171,52 @@
         <v>42</v>
       </c>
       <c r="AS2">
+        <v>10</v>
+      </c>
+      <c r="AT2">
+        <v>6.4</v>
+      </c>
+      <c r="AU2">
         <v>8.199999999999999</v>
       </c>
-      <c r="AT2">
-        <v>6.2</v>
-      </c>
-      <c r="AU2">
-        <v>7.2</v>
-      </c>
       <c r="AV2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX2">
         <v>7.6</v>
       </c>
       <c r="AY2">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AZ2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BB2">
         <v>13</v>
       </c>
       <c r="BC2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BF2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG2">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BH2">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="BI2">
         <v>2.76</v>
@@ -1219,13 +1225,13 @@
         <v>12</v>
       </c>
       <c r="BK2">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="BM2">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="BN2">
         <v>4.1</v>
@@ -1237,40 +1243,40 @@
         <v>11.5</v>
       </c>
       <c r="BQ2">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="BR2">
         <v>30</v>
       </c>
       <c r="BS2">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BT2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BU2">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="BV2">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BW2">
-        <v>9.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BY2">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BZ2">
         <v>24</v>
       </c>
       <c r="CA2">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="CB2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1287,16 +1293,16 @@
         <v>107</v>
       </c>
       <c r="E3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F3">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="G3">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="H3">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I3">
         <v>5.8</v>
@@ -1314,16 +1320,16 @@
         <v>1.18</v>
       </c>
       <c r="N3">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="O3">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="P3">
         <v>1.27</v>
       </c>
       <c r="Q3">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="R3">
         <v>1.09</v>
@@ -1332,16 +1338,16 @@
         <v>6.6</v>
       </c>
       <c r="T3">
-        <v>2.16</v>
+        <v>1.11</v>
       </c>
       <c r="U3">
-        <v>1.5</v>
+        <v>1.11</v>
       </c>
       <c r="V3">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W3">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -1356,7 +1362,7 @@
         <v>1000</v>
       </c>
       <c r="AB3">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AC3">
         <v>8.4</v>
@@ -1392,34 +1398,34 @@
         <v>1000</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP3">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AQ3">
         <v>7.2</v>
       </c>
       <c r="AR3">
-        <v>15.5</v>
+        <v>1.8</v>
       </c>
       <c r="AS3">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AT3">
         <v>4.8</v>
       </c>
       <c r="AU3">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="AV3">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AW3">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AX3">
         <v>8.6</v>
@@ -1428,28 +1434,28 @@
         <v>9.4</v>
       </c>
       <c r="AZ3">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="BA3">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="BB3">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="BC3">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="BD3">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="BE3">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="BF3">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="BG3">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1512,7 +1518,7 @@
         <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1529,7 +1535,7 @@
         <v>108</v>
       </c>
       <c r="E4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F4">
         <v>2.64</v>
@@ -1547,7 +1553,7 @@
         <v>3.8</v>
       </c>
       <c r="K4">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1556,13 +1562,13 @@
         <v>1.03</v>
       </c>
       <c r="N4">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="O4">
         <v>1.17</v>
       </c>
       <c r="P4">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q4">
         <v>1.58</v>
@@ -1574,7 +1580,7 @@
         <v>2.24</v>
       </c>
       <c r="T4">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="U4">
         <v>2.48</v>
@@ -1622,7 +1628,7 @@
         <v>36</v>
       </c>
       <c r="AJ4">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK4">
         <v>32</v>
@@ -1634,7 +1640,7 @@
         <v>70</v>
       </c>
       <c r="AN4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AO4">
         <v>17</v>
@@ -1682,10 +1688,10 @@
         <v>20</v>
       </c>
       <c r="BD4">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE4">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF4">
         <v>13</v>
@@ -1754,7 +1760,7 @@
         <v>4.3</v>
       </c>
       <c r="CB4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1771,25 +1777,25 @@
         <v>109</v>
       </c>
       <c r="E5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F5">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="G5">
         <v>1.65</v>
       </c>
       <c r="H5">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="I5">
         <v>8.800000000000001</v>
       </c>
       <c r="J5">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="L5">
         <v>1.38</v>
@@ -1798,7 +1804,7 @@
         <v>1.06</v>
       </c>
       <c r="N5">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="O5">
         <v>1.27</v>
@@ -1807,13 +1813,13 @@
         <v>1.92</v>
       </c>
       <c r="Q5">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="R5">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="S5">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="T5">
         <v>1.95</v>
@@ -1825,7 +1831,7 @@
         <v>1.13</v>
       </c>
       <c r="W5">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="X5">
         <v>18</v>
@@ -1882,10 +1888,10 @@
         <v>180</v>
       </c>
       <c r="AP5">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AQ5">
-        <v>4.2</v>
+        <v>16.5</v>
       </c>
       <c r="AR5">
         <v>4.7</v>
@@ -1894,34 +1900,34 @@
         <v>5</v>
       </c>
       <c r="AT5">
-        <v>3.3</v>
+        <v>6.2</v>
       </c>
       <c r="AU5">
-        <v>3.55</v>
+        <v>7.6</v>
       </c>
       <c r="AV5">
-        <v>4.4</v>
+        <v>20</v>
       </c>
       <c r="AW5">
         <v>4.9</v>
       </c>
       <c r="AX5">
-        <v>3.45</v>
+        <v>7.2</v>
       </c>
       <c r="AY5">
-        <v>3.55</v>
+        <v>7.8</v>
       </c>
       <c r="AZ5">
-        <v>4.3</v>
+        <v>18</v>
       </c>
       <c r="BA5">
         <v>4.9</v>
       </c>
       <c r="BB5">
-        <v>3.95</v>
+        <v>11</v>
       </c>
       <c r="BC5">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="BD5">
         <v>4.6</v>
@@ -1930,7 +1936,7 @@
         <v>5</v>
       </c>
       <c r="BF5">
-        <v>3.5</v>
+        <v>7.2</v>
       </c>
       <c r="BG5">
         <v>5</v>
@@ -1957,7 +1963,7 @@
         <v>4.5</v>
       </c>
       <c r="BO5">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="BP5">
         <v>12</v>
@@ -1996,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="CB5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2013,13 +2019,13 @@
         <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F6">
         <v>4.7</v>
       </c>
       <c r="G6">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="H6">
         <v>1.76</v>
@@ -2028,7 +2034,7 @@
         <v>1.93</v>
       </c>
       <c r="J6">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K6">
         <v>4.1</v>
@@ -2040,7 +2046,7 @@
         <v>1.07</v>
       </c>
       <c r="N6">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O6">
         <v>1.27</v>
@@ -2061,10 +2067,10 @@
         <v>1.73</v>
       </c>
       <c r="U6">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="V6">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="W6">
         <v>1.21</v>
@@ -2124,37 +2130,37 @@
         <v>16</v>
       </c>
       <c r="AP6">
-        <v>3.6</v>
+        <v>10</v>
       </c>
       <c r="AQ6">
-        <v>3.15</v>
+        <v>6.2</v>
       </c>
       <c r="AR6">
         <v>3.4</v>
       </c>
       <c r="AS6">
-        <v>3.85</v>
+        <v>14.5</v>
       </c>
       <c r="AT6">
-        <v>3.75</v>
+        <v>12</v>
       </c>
       <c r="AU6">
-        <v>3</v>
+        <v>6.4</v>
       </c>
       <c r="AV6">
-        <v>3.35</v>
+        <v>7.6</v>
       </c>
       <c r="AW6">
-        <v>3.85</v>
+        <v>14.5</v>
       </c>
       <c r="AX6">
         <v>4.1</v>
       </c>
       <c r="AY6">
-        <v>3.85</v>
+        <v>14.5</v>
       </c>
       <c r="AZ6">
-        <v>3.85</v>
+        <v>14.5</v>
       </c>
       <c r="BA6">
         <v>4.1</v>
@@ -2175,7 +2181,7 @@
         <v>4.4</v>
       </c>
       <c r="BG6">
-        <v>3.55</v>
+        <v>9.6</v>
       </c>
       <c r="BH6">
         <v>3.45</v>
@@ -2238,7 +2244,7 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2255,13 +2261,13 @@
         <v>111</v>
       </c>
       <c r="E7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F7">
         <v>3.65</v>
       </c>
       <c r="G7">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="H7">
         <v>1.98</v>
@@ -2309,7 +2315,7 @@
         <v>1.94</v>
       </c>
       <c r="W7">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X7">
         <v>29</v>
@@ -2480,7 +2486,7 @@
         <v>3.75</v>
       </c>
       <c r="CB7" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2497,7 +2503,7 @@
         <v>112</v>
       </c>
       <c r="E8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F8">
         <v>1.27</v>
@@ -2524,10 +2530,10 @@
         <v>1.07</v>
       </c>
       <c r="N8">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O8">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="P8">
         <v>1.82</v>
@@ -2542,7 +2548,7 @@
         <v>3.55</v>
       </c>
       <c r="T8">
-        <v>2.72</v>
+        <v>2.44</v>
       </c>
       <c r="U8">
         <v>1.49</v>
@@ -2575,7 +2581,7 @@
         <v>950</v>
       </c>
       <c r="AE8">
-        <v>640</v>
+        <v>620</v>
       </c>
       <c r="AF8">
         <v>6.6</v>
@@ -2722,7 +2728,7 @@
         <v>4</v>
       </c>
       <c r="CB8" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2739,7 +2745,7 @@
         <v>113</v>
       </c>
       <c r="E9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F9">
         <v>3.75</v>
@@ -2748,7 +2754,7 @@
         <v>4.2</v>
       </c>
       <c r="H9">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I9">
         <v>2.54</v>
@@ -2757,13 +2763,13 @@
         <v>2.88</v>
       </c>
       <c r="K9">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="L9">
         <v>1.51</v>
       </c>
       <c r="M9">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N9">
         <v>2.44</v>
@@ -2772,7 +2778,7 @@
         <v>1.58</v>
       </c>
       <c r="P9">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q9">
         <v>2.8</v>
@@ -2787,7 +2793,7 @@
         <v>2.18</v>
       </c>
       <c r="U9">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="V9">
         <v>1.65</v>
@@ -2859,7 +2865,7 @@
         <v>10</v>
       </c>
       <c r="AS9">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AT9">
         <v>7.4</v>
@@ -2871,7 +2877,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW9">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX9">
         <v>18.5</v>
@@ -2880,22 +2886,22 @@
         <v>12.5</v>
       </c>
       <c r="AZ9">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BA9">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BB9">
+        <v>5.8</v>
+      </c>
+      <c r="BC9">
         <v>5.7</v>
-      </c>
-      <c r="BC9">
-        <v>5.6</v>
       </c>
       <c r="BD9">
         <v>5.8</v>
       </c>
       <c r="BE9">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF9">
         <v>5.8</v>
@@ -2964,7 +2970,7 @@
         <v>4.8</v>
       </c>
       <c r="CB9" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2981,10 +2987,10 @@
         <v>114</v>
       </c>
       <c r="E10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F10">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="G10">
         <v>3.1</v>
@@ -2993,19 +2999,19 @@
         <v>2.56</v>
       </c>
       <c r="I10">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J10">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K10">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L10">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M10">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N10">
         <v>3.35</v>
@@ -3014,16 +3020,16 @@
         <v>1.35</v>
       </c>
       <c r="P10">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="Q10">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="R10">
         <v>1.3</v>
       </c>
       <c r="S10">
-        <v>2.58</v>
+        <v>3.65</v>
       </c>
       <c r="T10">
         <v>1.79</v>
@@ -3047,7 +3053,7 @@
         <v>21</v>
       </c>
       <c r="AA10">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB10">
         <v>12.5</v>
@@ -3104,10 +3110,10 @@
         <v>4.7</v>
       </c>
       <c r="AT10">
-        <v>3.7</v>
+        <v>8.4</v>
       </c>
       <c r="AU10">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="AV10">
         <v>3.85</v>
@@ -3116,10 +3122,10 @@
         <v>4.6</v>
       </c>
       <c r="AX10">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AY10">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AZ10">
         <v>4.2</v>
@@ -3155,58 +3161,58 @@
         <v>10</v>
       </c>
       <c r="BK10">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>2.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN10">
         <v>6.2</v>
       </c>
       <c r="BO10">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="BP10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BQ10">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>2.38</v>
+        <v>8</v>
       </c>
       <c r="BT10">
         <v>5.9</v>
       </c>
       <c r="BU10">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="BV10">
         <v>23</v>
       </c>
       <c r="BW10">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>2.38</v>
+        <v>7.8</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA10">
-        <v>2.36</v>
+        <v>7.6</v>
       </c>
       <c r="CB10" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3223,7 +3229,7 @@
         <v>115</v>
       </c>
       <c r="E11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F11">
         <v>1.75</v>
@@ -3235,7 +3241,7 @@
         <v>5.7</v>
       </c>
       <c r="I11">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="J11">
         <v>3.35</v>
@@ -3244,16 +3250,16 @@
         <v>3.75</v>
       </c>
       <c r="L11">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M11">
         <v>1.11</v>
       </c>
       <c r="N11">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O11">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P11">
         <v>1.59</v>
@@ -3274,7 +3280,7 @@
         <v>1.71</v>
       </c>
       <c r="V11">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W11">
         <v>2.12</v>
@@ -3343,37 +3349,37 @@
         <v>7.2</v>
       </c>
       <c r="AS11">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AT11">
         <v>5.7</v>
       </c>
       <c r="AU11">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AV11">
-        <v>6.2</v>
+        <v>18</v>
       </c>
       <c r="AW11">
-        <v>4.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX11">
         <v>8.4</v>
       </c>
       <c r="AY11">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="AZ11">
         <v>19</v>
       </c>
       <c r="BA11">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BB11">
+        <v>14.5</v>
+      </c>
+      <c r="BC11">
         <v>17</v>
-      </c>
-      <c r="BC11">
-        <v>20</v>
       </c>
       <c r="BD11">
         <v>7.4</v>
@@ -3382,10 +3388,10 @@
         <v>4.7</v>
       </c>
       <c r="BF11">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="BG11">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BH11">
         <v>3.3</v>
@@ -3448,7 +3454,7 @@
         <v>4.5</v>
       </c>
       <c r="CB11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3465,67 +3471,67 @@
         <v>116</v>
       </c>
       <c r="E12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F12">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="G12">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="H12">
+        <v>4.4</v>
+      </c>
+      <c r="I12">
         <v>4.5</v>
       </c>
-      <c r="I12">
-        <v>4.7</v>
-      </c>
       <c r="J12">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="K12">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L12">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M12">
         <v>1.1</v>
       </c>
       <c r="N12">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="O12">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="P12">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="Q12">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R12">
         <v>1.27</v>
       </c>
       <c r="S12">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="T12">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U12">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V12">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W12">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="X12">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y12">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z12">
         <v>32</v>
@@ -3537,13 +3543,13 @@
         <v>7.6</v>
       </c>
       <c r="AC12">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD12">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE12">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AF12">
         <v>11</v>
@@ -3561,34 +3567,34 @@
         <v>24</v>
       </c>
       <c r="AK12">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL12">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM12">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AN12">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AO12">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AP12">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ12">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR12">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS12">
         <v>95</v>
       </c>
       <c r="AT12">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU12">
         <v>7.4</v>
@@ -3597,7 +3603,7 @@
         <v>17</v>
       </c>
       <c r="AW12">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX12">
         <v>10</v>
@@ -3606,16 +3612,16 @@
         <v>10</v>
       </c>
       <c r="AZ12">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA12">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BB12">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC12">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD12">
         <v>40</v>
@@ -3624,13 +3630,13 @@
         <v>44</v>
       </c>
       <c r="BF12">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BG12">
         <v>75</v>
       </c>
       <c r="BH12">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BI12">
         <v>2.8</v>
@@ -3645,7 +3651,7 @@
         <v>190</v>
       </c>
       <c r="BM12">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BN12">
         <v>4.5</v>
@@ -3657,13 +3663,13 @@
         <v>15</v>
       </c>
       <c r="BQ12">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="BR12">
         <v>34</v>
       </c>
       <c r="BS12">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT12">
         <v>7.6</v>
@@ -3681,16 +3687,16 @@
         <v>60</v>
       </c>
       <c r="BY12">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BZ12">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="CA12">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CB12" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3707,10 +3713,10 @@
         <v>117</v>
       </c>
       <c r="E13" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F13">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G13">
         <v>1.69</v>
@@ -3740,7 +3746,7 @@
         <v>1.18</v>
       </c>
       <c r="P13">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q13">
         <v>1.59</v>
@@ -3755,7 +3761,7 @@
         <v>1.68</v>
       </c>
       <c r="U13">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V13">
         <v>1.01</v>
@@ -3767,7 +3773,7 @@
         <v>30</v>
       </c>
       <c r="Y13">
-        <v>950</v>
+        <v>34</v>
       </c>
       <c r="Z13">
         <v>60</v>
@@ -3782,7 +3788,7 @@
         <v>13</v>
       </c>
       <c r="AD13">
-        <v>950</v>
+        <v>30</v>
       </c>
       <c r="AE13">
         <v>75</v>
@@ -3794,10 +3800,10 @@
         <v>10.5</v>
       </c>
       <c r="AH13">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AI13">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AJ13">
         <v>17</v>
@@ -3806,7 +3812,7 @@
         <v>16</v>
       </c>
       <c r="AL13">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AM13">
         <v>100</v>
@@ -3839,7 +3845,7 @@
         <v>15.5</v>
       </c>
       <c r="AW13">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="AX13">
         <v>8.800000000000001</v>
@@ -3851,7 +3857,7 @@
         <v>13.5</v>
       </c>
       <c r="BA13">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="BB13">
         <v>14.5</v>
@@ -3863,19 +3869,19 @@
         <v>20</v>
       </c>
       <c r="BE13">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF13">
         <v>5.3</v>
       </c>
       <c r="BG13">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="BH13">
         <v>5.1</v>
       </c>
       <c r="BI13">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BJ13">
         <v>11.5</v>
@@ -3887,7 +3893,7 @@
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BN13">
         <v>5.4</v>
@@ -3902,7 +3908,7 @@
         <v>3.4</v>
       </c>
       <c r="BR13">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BS13">
         <v>3.95</v>
@@ -3914,7 +3920,7 @@
         <v>3.25</v>
       </c>
       <c r="BV13">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BW13">
         <v>4.2</v>
@@ -3932,7 +3938,7 @@
         <v>3.65</v>
       </c>
       <c r="CB13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3949,7 +3955,7 @@
         <v>118</v>
       </c>
       <c r="E14" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F14">
         <v>1.29</v>
@@ -3964,10 +3970,10 @@
         <v>12</v>
       </c>
       <c r="J14">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="K14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L14">
         <v>1.2</v>
@@ -3997,7 +4003,7 @@
         <v>1.79</v>
       </c>
       <c r="U14">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V14">
         <v>1.09</v>
@@ -4009,7 +4015,7 @@
         <v>40</v>
       </c>
       <c r="Y14">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Z14">
         <v>120</v>
@@ -4075,10 +4081,10 @@
         <v>4.6</v>
       </c>
       <c r="AU14">
-        <v>4.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV14">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AW14">
         <v>6.8</v>
@@ -4090,7 +4096,7 @@
         <v>4.4</v>
       </c>
       <c r="AZ14">
-        <v>5.7</v>
+        <v>18</v>
       </c>
       <c r="BA14">
         <v>6.8</v>
@@ -4174,7 +4180,7 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4191,13 +4197,13 @@
         <v>119</v>
       </c>
       <c r="E15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F15">
+        <v>1.29</v>
+      </c>
+      <c r="G15">
         <v>1.3</v>
-      </c>
-      <c r="G15">
-        <v>1.31</v>
       </c>
       <c r="H15">
         <v>11</v>
@@ -4206,46 +4212,46 @@
         <v>11.5</v>
       </c>
       <c r="J15">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="K15">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="L15">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M15">
         <v>1.03</v>
       </c>
       <c r="N15">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="O15">
         <v>1.15</v>
       </c>
       <c r="P15">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q15">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="R15">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="S15">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="T15">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U15">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V15">
         <v>1.09</v>
       </c>
       <c r="W15">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="X15">
         <v>34</v>
@@ -4254,10 +4260,10 @@
         <v>48</v>
       </c>
       <c r="Z15">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AA15">
-        <v>410</v>
+        <v>440</v>
       </c>
       <c r="AB15">
         <v>12.5</v>
@@ -4269,7 +4275,7 @@
         <v>42</v>
       </c>
       <c r="AE15">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AF15">
         <v>9.4</v>
@@ -4278,10 +4284,10 @@
         <v>10.5</v>
       </c>
       <c r="AH15">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI15">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AJ15">
         <v>11</v>
@@ -4290,13 +4296,13 @@
         <v>12.5</v>
       </c>
       <c r="AL15">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AM15">
         <v>110</v>
       </c>
       <c r="AN15">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AO15">
         <v>160</v>
@@ -4308,10 +4314,10 @@
         <v>40</v>
       </c>
       <c r="AR15">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="AS15">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AT15">
         <v>11.5</v>
@@ -4323,7 +4329,7 @@
         <v>34</v>
       </c>
       <c r="AW15">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AX15">
         <v>9</v>
@@ -4350,10 +4356,10 @@
         <v>90</v>
       </c>
       <c r="BF15">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="BG15">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BH15">
         <v>5.8</v>
@@ -4371,25 +4377,25 @@
         <v>130</v>
       </c>
       <c r="BM15">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BN15">
         <v>4.1</v>
       </c>
       <c r="BO15">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="BP15">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ15">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR15">
         <v>20</v>
       </c>
       <c r="BS15">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BT15">
         <v>16</v>
@@ -4401,22 +4407,22 @@
         <v>85</v>
       </c>
       <c r="BW15">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BX15">
         <v>75</v>
       </c>
       <c r="BY15">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BZ15">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="CA15">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="CB15" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4433,7 +4439,7 @@
         <v>120</v>
       </c>
       <c r="E16" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F16">
         <v>1.48</v>
@@ -4445,7 +4451,7 @@
         <v>9.6</v>
       </c>
       <c r="I16">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="J16">
         <v>3.9</v>
@@ -4454,16 +4460,16 @@
         <v>4.4</v>
       </c>
       <c r="L16">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M16">
         <v>1.1</v>
       </c>
       <c r="N16">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="O16">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P16">
         <v>1.6</v>
@@ -4493,7 +4499,7 @@
         <v>12</v>
       </c>
       <c r="Y16">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Z16">
         <v>110</v>
@@ -4502,10 +4508,10 @@
         <v>620</v>
       </c>
       <c r="AB16">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AC16">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD16">
         <v>48</v>
@@ -4514,7 +4520,7 @@
         <v>310</v>
       </c>
       <c r="AF16">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AG16">
         <v>13</v>
@@ -4538,7 +4544,7 @@
         <v>410</v>
       </c>
       <c r="AN16">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AO16">
         <v>1000</v>
@@ -4547,58 +4553,58 @@
         <v>8</v>
       </c>
       <c r="AQ16">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR16">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AS16">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AT16">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AU16">
         <v>8.800000000000001</v>
       </c>
       <c r="AV16">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AW16">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AX16">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AY16">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ16">
         <v>5.4</v>
       </c>
       <c r="BA16">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BB16">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC16">
         <v>18.5</v>
       </c>
       <c r="BD16">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BE16">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BF16">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG16">
         <v>6.2</v>
       </c>
       <c r="BH16">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="BI16">
         <v>2.44</v>
@@ -4607,13 +4613,13 @@
         <v>16.5</v>
       </c>
       <c r="BK16">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="BN16">
         <v>4</v>
@@ -4625,40 +4631,40 @@
         <v>12</v>
       </c>
       <c r="BQ16">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="BR16">
         <v>44</v>
       </c>
       <c r="BS16">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="BT16">
         <v>15</v>
       </c>
       <c r="BU16">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="BZ16">
         <v>32</v>
       </c>
       <c r="CA16">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="CB16" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4675,7 +4681,7 @@
         <v>121</v>
       </c>
       <c r="E17" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F17">
         <v>3.4</v>
@@ -4702,7 +4708,7 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O17">
         <v>1.07</v>
@@ -4711,13 +4717,13 @@
         <v>3.65</v>
       </c>
       <c r="Q17">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="R17">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="S17">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="T17">
         <v>1.3</v>
@@ -4900,7 +4906,7 @@
         <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4917,7 +4923,7 @@
         <v>122</v>
       </c>
       <c r="E18" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F18">
         <v>1.5</v>
@@ -4932,7 +4938,7 @@
         <v>990</v>
       </c>
       <c r="J18">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="K18">
         <v>950</v>
@@ -4953,13 +4959,13 @@
         <v>1.25</v>
       </c>
       <c r="Q18">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R18">
         <v>1.18</v>
       </c>
       <c r="S18">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="T18">
         <v>1.11</v>
@@ -4968,7 +4974,7 @@
         <v>1.11</v>
       </c>
       <c r="V18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W18">
         <v>1.83</v>
@@ -5142,7 +5148,7 @@
         <v>1.04</v>
       </c>
       <c r="CB18" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5159,7 +5165,7 @@
         <v>123</v>
       </c>
       <c r="E19" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F19">
         <v>2.2</v>
@@ -5183,7 +5189,7 @@
         <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N19">
         <v>1.26</v>
@@ -5192,16 +5198,16 @@
         <v>1.44</v>
       </c>
       <c r="P19">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q19">
-        <v>1.48</v>
+        <v>2.26</v>
       </c>
       <c r="R19">
         <v>1.18</v>
       </c>
       <c r="S19">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="T19">
         <v>1.11</v>
@@ -5210,10 +5216,10 @@
         <v>1.11</v>
       </c>
       <c r="V19">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W19">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X19">
         <v>1000</v>
@@ -5384,491 +5390,733 @@
         <v>1.04</v>
       </c>
       <c r="CB19" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B20" t="s">
         <v>90</v>
       </c>
       <c r="C20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D20" t="s">
         <v>124</v>
       </c>
       <c r="E20" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F20">
-        <v>1.93</v>
+        <v>1.04</v>
       </c>
       <c r="G20">
-        <v>2.2</v>
+        <v>1000</v>
       </c>
       <c r="H20">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="I20">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="J20">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="K20">
-        <v>4.5</v>
+        <v>950</v>
       </c>
       <c r="L20">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="M20">
         <v>1.01</v>
       </c>
       <c r="N20">
-        <v>5.2</v>
+        <v>1.24</v>
       </c>
       <c r="O20">
+        <v>1.01</v>
+      </c>
+      <c r="P20">
+        <v>1.24</v>
+      </c>
+      <c r="Q20">
+        <v>1.02</v>
+      </c>
+      <c r="R20">
         <v>1.18</v>
       </c>
-      <c r="P20">
-        <v>2.42</v>
-      </c>
-      <c r="Q20">
-        <v>1.54</v>
-      </c>
-      <c r="R20">
-        <v>1.57</v>
-      </c>
       <c r="S20">
-        <v>2.36</v>
+        <v>1.02</v>
       </c>
       <c r="T20">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="U20">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="V20">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="W20">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="X20">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="Y20">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Z20">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA20">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB20">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AC20">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD20">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE20">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF20">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AG20">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH20">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AI20">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ20">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AK20">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL20">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AM20">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AN20">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AO20">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AP20">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR20">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AS20">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT20">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU20">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV20">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AW20">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AX20">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AY20">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BA20">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BB20">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BC20">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD20">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BE20">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF20">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BG20">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BH20">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BI20">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BJ20">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK20">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BN20">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BO20">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP20">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BR20">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BS20">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BT20">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU20">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV20">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BW20">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX20">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY20">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BZ20">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="CA20">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="CB20" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B21" t="s">
         <v>90</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D21" t="s">
         <v>125</v>
       </c>
       <c r="E21" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F21">
-        <v>3.75</v>
+        <v>1.93</v>
       </c>
       <c r="G21">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="H21">
-        <v>2.22</v>
+        <v>3.3</v>
       </c>
       <c r="I21">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="J21">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="K21">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="L21">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="M21">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N21">
-        <v>2.92</v>
+        <v>5.2</v>
       </c>
       <c r="O21">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="P21">
-        <v>1.64</v>
+        <v>2.42</v>
       </c>
       <c r="Q21">
-        <v>2.32</v>
+        <v>1.54</v>
       </c>
       <c r="R21">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="S21">
-        <v>4.1</v>
+        <v>2.34</v>
       </c>
       <c r="T21">
-        <v>1.96</v>
+        <v>1.53</v>
       </c>
       <c r="U21">
-        <v>1.89</v>
+        <v>2.44</v>
       </c>
       <c r="V21">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="W21">
-        <v>1.32</v>
+        <v>1.83</v>
       </c>
       <c r="X21">
+        <v>29</v>
+      </c>
+      <c r="Y21">
+        <v>23</v>
+      </c>
+      <c r="Z21">
+        <v>32</v>
+      </c>
+      <c r="AA21">
+        <v>70</v>
+      </c>
+      <c r="AB21">
+        <v>15</v>
+      </c>
+      <c r="AC21">
+        <v>11</v>
+      </c>
+      <c r="AD21">
+        <v>17</v>
+      </c>
+      <c r="AE21">
+        <v>40</v>
+      </c>
+      <c r="AF21">
+        <v>17</v>
+      </c>
+      <c r="AG21">
+        <v>12</v>
+      </c>
+      <c r="AH21">
+        <v>16.5</v>
+      </c>
+      <c r="AI21">
+        <v>40</v>
+      </c>
+      <c r="AJ21">
+        <v>26</v>
+      </c>
+      <c r="AK21">
+        <v>21</v>
+      </c>
+      <c r="AL21">
+        <v>29</v>
+      </c>
+      <c r="AM21">
+        <v>65</v>
+      </c>
+      <c r="AN21">
         <v>10.5</v>
       </c>
-      <c r="Y21">
+      <c r="AO21">
+        <v>27</v>
+      </c>
+      <c r="AP21">
+        <v>5.8</v>
+      </c>
+      <c r="AQ21">
+        <v>15</v>
+      </c>
+      <c r="AR21">
+        <v>5.9</v>
+      </c>
+      <c r="AS21">
+        <v>6.6</v>
+      </c>
+      <c r="AT21">
+        <v>10.5</v>
+      </c>
+      <c r="AU21">
+        <v>8.4</v>
+      </c>
+      <c r="AV21">
+        <v>12</v>
+      </c>
+      <c r="AW21">
+        <v>6</v>
+      </c>
+      <c r="AX21">
+        <v>12</v>
+      </c>
+      <c r="AY21">
         <v>9.199999999999999</v>
       </c>
-      <c r="Z21">
-        <v>14</v>
-      </c>
-      <c r="AA21">
-        <v>38</v>
-      </c>
-      <c r="AB21">
-        <v>13.5</v>
-      </c>
-      <c r="AC21">
-        <v>7.6</v>
-      </c>
-      <c r="AD21">
-        <v>13.5</v>
-      </c>
-      <c r="AE21">
-        <v>34</v>
-      </c>
-      <c r="AF21">
-        <v>30</v>
-      </c>
-      <c r="AG21">
-        <v>16.5</v>
-      </c>
-      <c r="AH21">
-        <v>24</v>
-      </c>
-      <c r="AI21">
-        <v>60</v>
-      </c>
-      <c r="AJ21">
-        <v>95</v>
-      </c>
-      <c r="AK21">
-        <v>65</v>
-      </c>
-      <c r="AL21">
-        <v>85</v>
-      </c>
-      <c r="AM21">
-        <v>170</v>
-      </c>
-      <c r="AN21">
-        <v>85</v>
-      </c>
-      <c r="AO21">
-        <v>32</v>
-      </c>
-      <c r="AP21">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ21">
-        <v>7.2</v>
-      </c>
-      <c r="AR21">
-        <v>10.5</v>
-      </c>
-      <c r="AS21">
-        <v>5.6</v>
-      </c>
-      <c r="AT21">
-        <v>10</v>
-      </c>
-      <c r="AU21">
-        <v>5.8</v>
-      </c>
-      <c r="AV21">
-        <v>10</v>
-      </c>
-      <c r="AW21">
-        <v>5.5</v>
-      </c>
-      <c r="AX21">
-        <v>19.5</v>
-      </c>
-      <c r="AY21">
-        <v>12.5</v>
-      </c>
       <c r="AZ21">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="BA21">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BB21">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BC21">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="BD21">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="BE21">
         <v>6.4</v>
       </c>
       <c r="BF21">
+        <v>4.3</v>
+      </c>
+      <c r="BG21">
+        <v>19</v>
+      </c>
+      <c r="BH21">
+        <v>4.7</v>
+      </c>
+      <c r="BI21">
+        <v>3.55</v>
+      </c>
+      <c r="BJ21">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK21">
+        <v>4.4</v>
+      </c>
+      <c r="BL21">
+        <v>1000</v>
+      </c>
+      <c r="BM21">
+        <v>7.8</v>
+      </c>
+      <c r="BN21">
+        <v>5.6</v>
+      </c>
+      <c r="BO21">
+        <v>4.2</v>
+      </c>
+      <c r="BP21">
+        <v>14</v>
+      </c>
+      <c r="BQ21">
+        <v>5.3</v>
+      </c>
+      <c r="BR21">
+        <v>23</v>
+      </c>
+      <c r="BS21">
+        <v>6.2</v>
+      </c>
+      <c r="BT21">
+        <v>7.8</v>
+      </c>
+      <c r="BU21">
+        <v>5.8</v>
+      </c>
+      <c r="BV21">
+        <v>27</v>
+      </c>
+      <c r="BW21">
+        <v>6.4</v>
+      </c>
+      <c r="BX21">
+        <v>32</v>
+      </c>
+      <c r="BY21">
+        <v>6.8</v>
+      </c>
+      <c r="BZ21">
+        <v>16.5</v>
+      </c>
+      <c r="CA21">
+        <v>5.6</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="22" spans="1:80">
+      <c r="A22" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" t="s">
+        <v>90</v>
+      </c>
+      <c r="C22" t="s">
+        <v>105</v>
+      </c>
+      <c r="D22" t="s">
+        <v>126</v>
+      </c>
+      <c r="E22" t="s">
+        <v>147</v>
+      </c>
+      <c r="F22">
+        <v>3.75</v>
+      </c>
+      <c r="G22">
+        <v>4.1</v>
+      </c>
+      <c r="H22">
+        <v>2.22</v>
+      </c>
+      <c r="I22">
+        <v>2.4</v>
+      </c>
+      <c r="J22">
+        <v>3.1</v>
+      </c>
+      <c r="K22">
+        <v>3.4</v>
+      </c>
+      <c r="L22">
+        <v>1.44</v>
+      </c>
+      <c r="M22">
+        <v>1.1</v>
+      </c>
+      <c r="N22">
+        <v>2.92</v>
+      </c>
+      <c r="O22">
+        <v>1.43</v>
+      </c>
+      <c r="P22">
+        <v>1.64</v>
+      </c>
+      <c r="Q22">
+        <v>2.32</v>
+      </c>
+      <c r="R22">
+        <v>1.24</v>
+      </c>
+      <c r="S22">
+        <v>4.4</v>
+      </c>
+      <c r="T22">
+        <v>1.96</v>
+      </c>
+      <c r="U22">
+        <v>1.89</v>
+      </c>
+      <c r="V22">
+        <v>1.73</v>
+      </c>
+      <c r="W22">
+        <v>1.32</v>
+      </c>
+      <c r="X22">
+        <v>10.5</v>
+      </c>
+      <c r="Y22">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z22">
+        <v>14</v>
+      </c>
+      <c r="AA22">
+        <v>38</v>
+      </c>
+      <c r="AB22">
+        <v>13.5</v>
+      </c>
+      <c r="AC22">
+        <v>7.6</v>
+      </c>
+      <c r="AD22">
+        <v>13.5</v>
+      </c>
+      <c r="AE22">
+        <v>34</v>
+      </c>
+      <c r="AF22">
+        <v>30</v>
+      </c>
+      <c r="AG22">
+        <v>16.5</v>
+      </c>
+      <c r="AH22">
+        <v>24</v>
+      </c>
+      <c r="AI22">
+        <v>60</v>
+      </c>
+      <c r="AJ22">
+        <v>95</v>
+      </c>
+      <c r="AK22">
+        <v>65</v>
+      </c>
+      <c r="AL22">
+        <v>85</v>
+      </c>
+      <c r="AM22">
+        <v>170</v>
+      </c>
+      <c r="AN22">
+        <v>85</v>
+      </c>
+      <c r="AO22">
+        <v>32</v>
+      </c>
+      <c r="AP22">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ22">
+        <v>7.2</v>
+      </c>
+      <c r="AR22">
+        <v>10.5</v>
+      </c>
+      <c r="AS22">
+        <v>5.6</v>
+      </c>
+      <c r="AT22">
+        <v>10</v>
+      </c>
+      <c r="AU22">
+        <v>5.8</v>
+      </c>
+      <c r="AV22">
+        <v>10</v>
+      </c>
+      <c r="AW22">
+        <v>5.5</v>
+      </c>
+      <c r="AX22">
+        <v>19.5</v>
+      </c>
+      <c r="AY22">
+        <v>12.5</v>
+      </c>
+      <c r="AZ22">
+        <v>18</v>
+      </c>
+      <c r="BA22">
+        <v>5.9</v>
+      </c>
+      <c r="BB22">
+        <v>6.2</v>
+      </c>
+      <c r="BC22">
         <v>6</v>
       </c>
-      <c r="BG21">
+      <c r="BD22">
+        <v>6</v>
+      </c>
+      <c r="BE22">
+        <v>6.4</v>
+      </c>
+      <c r="BF22">
+        <v>6</v>
+      </c>
+      <c r="BG22">
         <v>19.5</v>
       </c>
-      <c r="BH21">
+      <c r="BH22">
         <v>3.25</v>
       </c>
-      <c r="BI21">
+      <c r="BI22">
         <v>2.46</v>
       </c>
-      <c r="BJ21">
+      <c r="BJ22">
         <v>12</v>
       </c>
-      <c r="BK21">
+      <c r="BK22">
         <v>4</v>
       </c>
-      <c r="BL21">
-        <v>1000</v>
-      </c>
-      <c r="BM21">
+      <c r="BL22">
+        <v>1000</v>
+      </c>
+      <c r="BM22">
         <v>5.8</v>
       </c>
-      <c r="BN21">
+      <c r="BN22">
         <v>7.8</v>
       </c>
-      <c r="BO21">
+      <c r="BO22">
         <v>5.4</v>
       </c>
-      <c r="BP21">
+      <c r="BP22">
         <v>40</v>
       </c>
-      <c r="BQ21">
+      <c r="BQ22">
         <v>5.2</v>
       </c>
-      <c r="BR21">
+      <c r="BR22">
         <v>60</v>
       </c>
-      <c r="BS21">
+      <c r="BS22">
         <v>5.5</v>
       </c>
-      <c r="BT21">
+      <c r="BT22">
         <v>5.6</v>
       </c>
-      <c r="BU21">
+      <c r="BU22">
         <v>3.95</v>
       </c>
-      <c r="BV21">
+      <c r="BV22">
         <v>22</v>
       </c>
-      <c r="BW21">
+      <c r="BW22">
         <v>4.7</v>
       </c>
-      <c r="BX21">
+      <c r="BX22">
         <v>44</v>
       </c>
-      <c r="BY21">
+      <c r="BY22">
         <v>5.3</v>
       </c>
-      <c r="BZ21">
+      <c r="BZ22">
         <v>44</v>
       </c>
-      <c r="CA21">
+      <c r="CA22">
         <v>5.3</v>
       </c>
-      <c r="CB21" t="s">
-        <v>146</v>
+      <c r="CB22" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
@@ -469,7 +469,7 @@
     <t>Millonarios</t>
   </si>
   <si>
-    <t>2026-08-26 19:16:27</t>
+    <t>2026-08-26 21:29:22</t>
   </si>
 </sst>
 </file>
@@ -1063,25 +1063,25 @@
         <v>129</v>
       </c>
       <c r="F2">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="G2">
         <v>1.39</v>
       </c>
       <c r="H2">
+        <v>7.6</v>
+      </c>
+      <c r="I2">
+        <v>8.6</v>
+      </c>
+      <c r="J2">
+        <v>6.4</v>
+      </c>
+      <c r="K2">
         <v>6.8</v>
       </c>
-      <c r="I2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="J2">
-        <v>6.2</v>
-      </c>
-      <c r="K2">
-        <v>7.4</v>
-      </c>
       <c r="L2">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="M2">
         <v>1.01</v>
@@ -1090,193 +1090,193 @@
         <v>10</v>
       </c>
       <c r="O2">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="P2">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="Q2">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="R2">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="S2">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="T2">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="U2">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="V2">
         <v>1.13</v>
       </c>
       <c r="W2">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="X2">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="Y2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="Z2">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AA2">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="AB2">
+        <v>20</v>
+      </c>
+      <c r="AC2">
+        <v>18</v>
+      </c>
+      <c r="AD2">
+        <v>38</v>
+      </c>
+      <c r="AE2">
+        <v>90</v>
+      </c>
+      <c r="AF2">
+        <v>15</v>
+      </c>
+      <c r="AG2">
+        <v>13</v>
+      </c>
+      <c r="AH2">
+        <v>21</v>
+      </c>
+      <c r="AI2">
+        <v>70</v>
+      </c>
+      <c r="AJ2">
+        <v>16</v>
+      </c>
+      <c r="AK2">
+        <v>13</v>
+      </c>
+      <c r="AL2">
         <v>24</v>
       </c>
-      <c r="AC2">
-        <v>22</v>
-      </c>
-      <c r="AD2">
-        <v>40</v>
-      </c>
-      <c r="AE2">
-        <v>85</v>
-      </c>
-      <c r="AF2">
-        <v>19.5</v>
-      </c>
-      <c r="AG2">
-        <v>15.5</v>
-      </c>
-      <c r="AH2">
-        <v>24</v>
-      </c>
-      <c r="AI2">
-        <v>60</v>
-      </c>
-      <c r="AJ2">
-        <v>19.5</v>
-      </c>
-      <c r="AK2">
-        <v>16.5</v>
-      </c>
-      <c r="AL2">
-        <v>25</v>
-      </c>
       <c r="AM2">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AN2">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AO2">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AP2">
+        <v>44</v>
+      </c>
+      <c r="AQ2">
         <v>46</v>
       </c>
-      <c r="AQ2">
-        <v>38</v>
-      </c>
       <c r="AR2">
+        <v>55</v>
+      </c>
+      <c r="AS2">
+        <v>14.5</v>
+      </c>
+      <c r="AT2">
+        <v>17</v>
+      </c>
+      <c r="AU2">
+        <v>16</v>
+      </c>
+      <c r="AV2">
+        <v>30</v>
+      </c>
+      <c r="AW2">
         <v>65</v>
-      </c>
-      <c r="AS2">
-        <v>140</v>
-      </c>
-      <c r="AT2">
-        <v>15.5</v>
-      </c>
-      <c r="AU2">
-        <v>14.5</v>
-      </c>
-      <c r="AV2">
-        <v>26</v>
-      </c>
-      <c r="AW2">
-        <v>55</v>
       </c>
       <c r="AX2">
         <v>13</v>
       </c>
       <c r="AY2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ2">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BA2">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BB2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BD2">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BE2">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="BF2">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="BG2">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="BH2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BI2">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="BJ2">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BK2">
-        <v>8.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="BL2">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BM2">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BN2">
         <v>5.4</v>
       </c>
       <c r="BO2">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BP2">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BQ2">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BS2">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BU2">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="BV2">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>34</v>
+        <v>9.4</v>
       </c>
       <c r="BX2">
         <v>38</v>
       </c>
       <c r="BY2">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1305,19 +1305,19 @@
         <v>130</v>
       </c>
       <c r="F3">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="G3">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J3">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K3">
         <v>4.3</v>
@@ -1329,25 +1329,25 @@
         <v>1.07</v>
       </c>
       <c r="N3">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O3">
         <v>1.34</v>
       </c>
       <c r="P3">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="Q3">
         <v>2.02</v>
       </c>
       <c r="R3">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S3">
         <v>3.65</v>
       </c>
       <c r="T3">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U3">
         <v>1.88</v>
@@ -1356,7 +1356,7 @@
         <v>1.15</v>
       </c>
       <c r="W3">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="X3">
         <v>14.5</v>
@@ -1368,7 +1368,7 @@
         <v>60</v>
       </c>
       <c r="AA3">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AB3">
         <v>7.8</v>
@@ -1380,151 +1380,151 @@
         <v>27</v>
       </c>
       <c r="AE3">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF3">
         <v>9</v>
       </c>
       <c r="AG3">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AH3">
         <v>25</v>
       </c>
       <c r="AI3">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK3">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL3">
         <v>42</v>
       </c>
       <c r="AM3">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AO3">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AP3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ3">
         <v>20</v>
       </c>
       <c r="AR3">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AS3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AT3">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AU3">
         <v>8.6</v>
       </c>
       <c r="AV3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AW3">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="AX3">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AY3">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA3">
-        <v>55</v>
+        <v>15.5</v>
       </c>
       <c r="BB3">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC3">
+        <v>15.5</v>
+      </c>
+      <c r="BD3">
+        <v>34</v>
+      </c>
+      <c r="BE3">
+        <v>14.5</v>
+      </c>
+      <c r="BF3">
+        <v>9</v>
+      </c>
+      <c r="BG3">
         <v>15</v>
       </c>
-      <c r="BD3">
-        <v>26</v>
-      </c>
-      <c r="BE3">
-        <v>11.5</v>
-      </c>
-      <c r="BF3">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BG3">
-        <v>12</v>
-      </c>
       <c r="BH3">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="BI3">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="BJ3">
         <v>12</v>
       </c>
       <c r="BK3">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BL3">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="BM3">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BN3">
         <v>4.1</v>
       </c>
       <c r="BO3">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BP3">
         <v>11.5</v>
       </c>
       <c r="BQ3">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BR3">
         <v>30</v>
       </c>
       <c r="BS3">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BT3">
         <v>11</v>
       </c>
       <c r="BU3">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BV3">
         <v>70</v>
       </c>
       <c r="BW3">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX3">
         <v>75</v>
       </c>
       <c r="BY3">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BZ3">
         <v>24</v>
       </c>
       <c r="CA3">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="CB3" t="s">
         <v>151</v>
@@ -1559,7 +1559,7 @@
         <v>5.9</v>
       </c>
       <c r="J4">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="K4">
         <v>2.76</v>
@@ -1568,16 +1568,16 @@
         <v>1.6</v>
       </c>
       <c r="M4">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="N4">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="O4">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="P4">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1601,10 +1601,10 @@
         <v>1.59</v>
       </c>
       <c r="X4">
+        <v>7.2</v>
+      </c>
+      <c r="Y4">
         <v>970</v>
-      </c>
-      <c r="Y4">
-        <v>500</v>
       </c>
       <c r="Z4">
         <v>500</v>
@@ -1613,7 +1613,7 @@
         <v>900</v>
       </c>
       <c r="AB4">
-        <v>9.800000000000001</v>
+        <v>48</v>
       </c>
       <c r="AC4">
         <v>500</v>
@@ -1661,52 +1661,52 @@
         <v>7.2</v>
       </c>
       <c r="AR4">
-        <v>15.5</v>
+        <v>2.54</v>
       </c>
       <c r="AS4">
-        <v>1.9</v>
+        <v>2.58</v>
       </c>
       <c r="AT4">
         <v>4.8</v>
       </c>
       <c r="AU4">
-        <v>5.1</v>
+        <v>1.94</v>
       </c>
       <c r="AV4">
-        <v>1.81</v>
+        <v>14</v>
       </c>
       <c r="AW4">
-        <v>1.9</v>
+        <v>2.58</v>
       </c>
       <c r="AX4">
         <v>7.8</v>
       </c>
       <c r="AY4">
-        <v>9.4</v>
+        <v>2.48</v>
       </c>
       <c r="AZ4">
-        <v>1.9</v>
+        <v>2.58</v>
       </c>
       <c r="BA4">
-        <v>1.9</v>
+        <v>2.58</v>
       </c>
       <c r="BB4">
-        <v>1.89</v>
+        <v>2.58</v>
       </c>
       <c r="BC4">
-        <v>1.89</v>
+        <v>2.56</v>
       </c>
       <c r="BD4">
-        <v>1.89</v>
+        <v>2.56</v>
       </c>
       <c r="BE4">
-        <v>1.9</v>
+        <v>2.58</v>
       </c>
       <c r="BF4">
-        <v>1.86</v>
+        <v>2.5</v>
       </c>
       <c r="BG4">
-        <v>1.88</v>
+        <v>2.54</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1789,19 +1789,19 @@
         <v>132</v>
       </c>
       <c r="F5">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="G5">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="H5">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I5">
         <v>2.7</v>
       </c>
       <c r="J5">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K5">
         <v>4.3</v>
@@ -1813,7 +1813,7 @@
         <v>1.03</v>
       </c>
       <c r="N5">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="O5">
         <v>1.17</v>
@@ -1834,13 +1834,13 @@
         <v>1.55</v>
       </c>
       <c r="U5">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="V5">
         <v>1.58</v>
       </c>
       <c r="W5">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X5">
         <v>27</v>
@@ -1882,16 +1882,16 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM5">
         <v>65</v>
       </c>
       <c r="AN5">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AO5">
         <v>14.5</v>
@@ -1900,13 +1900,13 @@
         <v>17.5</v>
       </c>
       <c r="AQ5">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR5">
         <v>15</v>
       </c>
       <c r="AS5">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AT5">
         <v>12</v>
@@ -1930,19 +1930,19 @@
         <v>12.5</v>
       </c>
       <c r="BA5">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BB5">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BC5">
         <v>20</v>
       </c>
       <c r="BD5">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BE5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF5">
         <v>13</v>
@@ -1966,7 +1966,7 @@
         <v>85</v>
       </c>
       <c r="BM5">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BN5">
         <v>7.2</v>
@@ -1978,7 +1978,7 @@
         <v>22</v>
       </c>
       <c r="BQ5">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BR5">
         <v>30</v>
@@ -2002,10 +2002,10 @@
         <v>28</v>
       </c>
       <c r="BY5">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BZ5">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="CA5">
         <v>4.3</v>
@@ -2381,10 +2381,10 @@
         <v>15.5</v>
       </c>
       <c r="AP7">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AQ7">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AR7">
         <v>9.4</v>
@@ -2399,7 +2399,7 @@
         <v>7.4</v>
       </c>
       <c r="AV7">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AW7">
         <v>3.9</v>
@@ -2408,10 +2408,10 @@
         <v>4.2</v>
       </c>
       <c r="AY7">
-        <v>14.5</v>
+        <v>3.95</v>
       </c>
       <c r="AZ7">
-        <v>14.5</v>
+        <v>3.95</v>
       </c>
       <c r="BA7">
         <v>4.2</v>
@@ -2515,19 +2515,19 @@
         <v>135</v>
       </c>
       <c r="F8">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="G8">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H8">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="I8">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="J8">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K8">
         <v>4.3</v>
@@ -2536,16 +2536,16 @@
         <v>1.28</v>
       </c>
       <c r="M8">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N8">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O8">
         <v>1.2</v>
       </c>
       <c r="P8">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q8">
         <v>1.58</v>
@@ -2563,7 +2563,7 @@
         <v>2.48</v>
       </c>
       <c r="V8">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="W8">
         <v>1.33</v>
@@ -2575,7 +2575,7 @@
         <v>15.5</v>
       </c>
       <c r="Z8">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA8">
         <v>30</v>
@@ -2620,7 +2620,7 @@
         <v>29</v>
       </c>
       <c r="AO8">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP8">
         <v>17</v>
@@ -2635,7 +2635,7 @@
         <v>20</v>
       </c>
       <c r="AT8">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AU8">
         <v>8.4</v>
@@ -2647,10 +2647,10 @@
         <v>16</v>
       </c>
       <c r="AX8">
-        <v>24</v>
+        <v>14.5</v>
       </c>
       <c r="AY8">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AZ8">
         <v>13</v>
@@ -2665,10 +2665,10 @@
         <v>32</v>
       </c>
       <c r="BD8">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BE8">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF8">
         <v>19</v>
@@ -2686,7 +2686,7 @@
         <v>10.5</v>
       </c>
       <c r="BK8">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BL8">
         <v>95</v>
@@ -2695,13 +2695,13 @@
         <v>4.4</v>
       </c>
       <c r="BN8">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO8">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BP8">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BQ8">
         <v>4</v>
@@ -2719,19 +2719,19 @@
         <v>4</v>
       </c>
       <c r="BV8">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BW8">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BX8">
         <v>27</v>
       </c>
       <c r="BY8">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BZ8">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="CA8">
         <v>3.75</v>
@@ -2781,16 +2781,16 @@
         <v>1.07</v>
       </c>
       <c r="N9">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O9">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P9">
         <v>1.82</v>
       </c>
       <c r="Q9">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R9">
         <v>1.31</v>
@@ -2799,10 +2799,10 @@
         <v>3.55</v>
       </c>
       <c r="T9">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="U9">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="V9">
         <v>1.05</v>
@@ -2832,7 +2832,7 @@
         <v>160</v>
       </c>
       <c r="AE9">
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="AF9">
         <v>6.6</v>
@@ -2841,7 +2841,7 @@
         <v>12.5</v>
       </c>
       <c r="AH9">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AI9">
         <v>460</v>
@@ -2871,10 +2871,10 @@
         <v>28</v>
       </c>
       <c r="AR9">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AS9">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT9">
         <v>5.5</v>
@@ -2886,7 +2886,7 @@
         <v>23</v>
       </c>
       <c r="AW9">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX9">
         <v>5.4</v>
@@ -2898,7 +2898,7 @@
         <v>36</v>
       </c>
       <c r="BA9">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB9">
         <v>6.8</v>
@@ -2907,16 +2907,16 @@
         <v>13</v>
       </c>
       <c r="BD9">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE9">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF9">
         <v>5.9</v>
       </c>
       <c r="BG9">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH9">
         <v>4</v>
@@ -3002,7 +3002,7 @@
         <v>4.1</v>
       </c>
       <c r="G10">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H10">
         <v>2.2</v>
@@ -3017,13 +3017,13 @@
         <v>3.05</v>
       </c>
       <c r="L10">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="M10">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N10">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="O10">
         <v>1.58</v>
@@ -3053,7 +3053,7 @@
         <v>1.27</v>
       </c>
       <c r="X10">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Y10">
         <v>8</v>
@@ -3065,13 +3065,13 @@
         <v>40</v>
       </c>
       <c r="AB10">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC10">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD10">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AE10">
         <v>140</v>
@@ -3086,7 +3086,7 @@
         <v>32</v>
       </c>
       <c r="AI10">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AJ10">
         <v>900</v>
@@ -3128,7 +3128,7 @@
         <v>10</v>
       </c>
       <c r="AW10">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AX10">
         <v>10.5</v>
@@ -3140,28 +3140,28 @@
         <v>18.5</v>
       </c>
       <c r="BA10">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB10">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BC10">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BD10">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE10">
+        <v>4.9</v>
+      </c>
+      <c r="BF10">
         <v>4.8</v>
-      </c>
-      <c r="BF10">
-        <v>4.7</v>
       </c>
       <c r="BG10">
         <v>7.2</v>
       </c>
       <c r="BH10">
-        <v>2.98</v>
+        <v>2.64</v>
       </c>
       <c r="BI10">
         <v>2.16</v>
@@ -3170,13 +3170,13 @@
         <v>14.5</v>
       </c>
       <c r="BK10">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BN10">
         <v>8.6</v>
@@ -3188,13 +3188,13 @@
         <v>55</v>
       </c>
       <c r="BQ10">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BT10">
         <v>5.6</v>
@@ -3206,19 +3206,19 @@
         <v>24</v>
       </c>
       <c r="BW10">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="BX10">
         <v>55</v>
       </c>
       <c r="BY10">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="BZ10">
         <v>65</v>
       </c>
       <c r="CA10">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="CB10" t="s">
         <v>151</v>
@@ -3259,28 +3259,28 @@
         <v>3.6</v>
       </c>
       <c r="L11">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M11">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N11">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O11">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="P11">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="Q11">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="R11">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="S11">
-        <v>3.65</v>
+        <v>2.64</v>
       </c>
       <c r="T11">
         <v>1.79</v>
@@ -3501,13 +3501,13 @@
         <v>3.75</v>
       </c>
       <c r="L12">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="M12">
         <v>1.11</v>
       </c>
       <c r="N12">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="O12">
         <v>1.46</v>
@@ -3519,7 +3519,7 @@
         <v>2.42</v>
       </c>
       <c r="R12">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S12">
         <v>4.8</v>
@@ -3546,7 +3546,7 @@
         <v>60</v>
       </c>
       <c r="AA12">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB12">
         <v>6.6</v>
@@ -3555,7 +3555,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD12">
-        <v>950</v>
+        <v>55</v>
       </c>
       <c r="AE12">
         <v>700</v>
@@ -3564,16 +3564,16 @@
         <v>9.6</v>
       </c>
       <c r="AG12">
-        <v>950</v>
+        <v>36</v>
       </c>
       <c r="AH12">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AI12">
         <v>700</v>
       </c>
       <c r="AJ12">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AK12">
         <v>29</v>
@@ -3582,7 +3582,7 @@
         <v>70</v>
       </c>
       <c r="AM12">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN12">
         <v>23</v>
@@ -3591,16 +3591,16 @@
         <v>700</v>
       </c>
       <c r="AP12">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ12">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AR12">
         <v>7.2</v>
       </c>
       <c r="AS12">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="AT12">
         <v>5.7</v>
@@ -3621,28 +3621,28 @@
         <v>9.4</v>
       </c>
       <c r="AZ12">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="BA12">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB12">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BC12">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BD12">
         <v>7.4</v>
       </c>
       <c r="BE12">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="BF12">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="BG12">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="BH12">
         <v>3.3</v>
@@ -3725,10 +3725,10 @@
         <v>140</v>
       </c>
       <c r="F13">
+        <v>2.02</v>
+      </c>
+      <c r="G13">
         <v>2.04</v>
-      </c>
-      <c r="G13">
-        <v>2.06</v>
       </c>
       <c r="H13">
         <v>4.4</v>
@@ -3737,10 +3737,10 @@
         <v>4.5</v>
       </c>
       <c r="J13">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K13">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L13">
         <v>1.53</v>
@@ -3755,7 +3755,7 @@
         <v>1.46</v>
       </c>
       <c r="P13">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q13">
         <v>2.4</v>
@@ -3770,13 +3770,13 @@
         <v>2.06</v>
       </c>
       <c r="U13">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V13">
         <v>1.28</v>
       </c>
       <c r="W13">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X13">
         <v>10.5</v>
@@ -3824,13 +3824,13 @@
         <v>48</v>
       </c>
       <c r="AM13">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AN13">
         <v>20</v>
       </c>
       <c r="AO13">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP13">
         <v>9.800000000000001</v>
@@ -3869,7 +3869,7 @@
         <v>70</v>
       </c>
       <c r="BB13">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC13">
         <v>22</v>
@@ -3881,7 +3881,7 @@
         <v>90</v>
       </c>
       <c r="BF13">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BG13">
         <v>75</v>
@@ -3902,7 +3902,7 @@
         <v>200</v>
       </c>
       <c r="BM13">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BN13">
         <v>4.5</v>
@@ -3932,13 +3932,13 @@
         <v>42</v>
       </c>
       <c r="BW13">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX13">
         <v>60</v>
       </c>
       <c r="BY13">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BZ13">
         <v>34</v>
@@ -3967,10 +3967,10 @@
         <v>141</v>
       </c>
       <c r="F14">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G14">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="H14">
         <v>5.3</v>
@@ -3985,7 +3985,7 @@
         <v>4.8</v>
       </c>
       <c r="L14">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="M14">
         <v>1.04</v>
@@ -4009,7 +4009,7 @@
         <v>2.46</v>
       </c>
       <c r="T14">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U14">
         <v>2.28</v>
@@ -4054,7 +4054,7 @@
         <v>500</v>
       </c>
       <c r="AI14">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="AJ14">
         <v>17</v>
@@ -4066,7 +4066,7 @@
         <v>500</v>
       </c>
       <c r="AM14">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="AN14">
         <v>7</v>
@@ -4081,7 +4081,7 @@
         <v>18</v>
       </c>
       <c r="AR14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS14">
         <v>7.4</v>
@@ -4096,7 +4096,7 @@
         <v>15.5</v>
       </c>
       <c r="AW14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AX14">
         <v>8.800000000000001</v>
@@ -4212,10 +4212,10 @@
         <v>1.3</v>
       </c>
       <c r="G15">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="H15">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I15">
         <v>12</v>
@@ -4230,7 +4230,7 @@
         <v>1.2</v>
       </c>
       <c r="M15">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N15">
         <v>6</v>
@@ -4254,13 +4254,13 @@
         <v>1.8</v>
       </c>
       <c r="U15">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V15">
         <v>1.09</v>
       </c>
       <c r="W15">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="X15">
         <v>75</v>
@@ -4320,7 +4320,7 @@
         <v>6.2</v>
       </c>
       <c r="AQ15">
-        <v>26</v>
+        <v>6.6</v>
       </c>
       <c r="AR15">
         <v>7.2</v>
@@ -4335,7 +4335,7 @@
         <v>12</v>
       </c>
       <c r="AV15">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW15">
         <v>7.4</v>
@@ -4347,7 +4347,7 @@
         <v>6.4</v>
       </c>
       <c r="AZ15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA15">
         <v>7.2</v>
@@ -4356,10 +4356,10 @@
         <v>7</v>
       </c>
       <c r="BC15">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="BD15">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BE15">
         <v>7.2</v>
@@ -4451,16 +4451,16 @@
         <v>143</v>
       </c>
       <c r="F16">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="G16">
         <v>1.29</v>
       </c>
       <c r="H16">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="I16">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="J16">
         <v>7</v>
@@ -4481,7 +4481,7 @@
         <v>1.14</v>
       </c>
       <c r="P16">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q16">
         <v>1.46</v>
@@ -4490,43 +4490,43 @@
         <v>1.86</v>
       </c>
       <c r="S16">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="T16">
         <v>1.89</v>
       </c>
       <c r="U16">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V16">
         <v>1.08</v>
       </c>
       <c r="W16">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="X16">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Y16">
         <v>55</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AA16">
-        <v>440</v>
+        <v>520</v>
       </c>
       <c r="AB16">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC16">
         <v>16</v>
       </c>
       <c r="AD16">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AF16">
         <v>9</v>
@@ -4535,13 +4535,13 @@
         <v>11</v>
       </c>
       <c r="AH16">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ16">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AK16">
         <v>12</v>
@@ -4553,37 +4553,37 @@
         <v>120</v>
       </c>
       <c r="AN16">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AO16">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="AP16">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AQ16">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AR16">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AS16">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="AT16">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU16">
         <v>15</v>
       </c>
       <c r="AV16">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AW16">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AX16">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AY16">
         <v>10.5</v>
@@ -4592,7 +4592,7 @@
         <v>27</v>
       </c>
       <c r="BA16">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="BB16">
         <v>10</v>
@@ -4601,76 +4601,76 @@
         <v>11.5</v>
       </c>
       <c r="BD16">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BE16">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="BF16">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BG16">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="BH16">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="BI16">
+        <v>4.6</v>
+      </c>
+      <c r="BJ16">
+        <v>12</v>
+      </c>
+      <c r="BK16">
+        <v>10</v>
+      </c>
+      <c r="BL16">
+        <v>140</v>
+      </c>
+      <c r="BM16">
+        <v>12.5</v>
+      </c>
+      <c r="BN16">
         <v>4</v>
       </c>
-      <c r="BJ16">
-        <v>1000</v>
-      </c>
-      <c r="BK16">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BL16">
-        <v>1000</v>
-      </c>
-      <c r="BM16">
-        <v>2.34</v>
-      </c>
-      <c r="BN16">
-        <v>4.6</v>
-      </c>
       <c r="BO16">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="BP16">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BQ16">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS16">
-        <v>2.34</v>
+        <v>16.5</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BU16">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BW16">
-        <v>2.38</v>
+        <v>12</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY16">
-        <v>2.34</v>
+        <v>11.5</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="CA16">
-        <v>2.8</v>
+        <v>7.2</v>
       </c>
       <c r="CB16" t="s">
         <v>151</v>
@@ -4693,19 +4693,19 @@
         <v>144</v>
       </c>
       <c r="F17">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="G17">
         <v>1.55</v>
       </c>
       <c r="H17">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="I17">
         <v>11.5</v>
       </c>
       <c r="J17">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K17">
         <v>4.4</v>
@@ -4717,10 +4717,10 @@
         <v>1.1</v>
       </c>
       <c r="N17">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O17">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="P17">
         <v>1.6</v>
@@ -4729,16 +4729,16 @@
         <v>2.4</v>
       </c>
       <c r="R17">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S17">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="T17">
         <v>2.54</v>
       </c>
       <c r="U17">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="V17">
         <v>1.09</v>
@@ -4756,10 +4756,10 @@
         <v>110</v>
       </c>
       <c r="AA17">
-        <v>620</v>
+        <v>600</v>
       </c>
       <c r="AB17">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="AC17">
         <v>11.5</v>
@@ -4768,7 +4768,7 @@
         <v>48</v>
       </c>
       <c r="AE17">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AF17">
         <v>7.4</v>
@@ -4780,7 +4780,7 @@
         <v>44</v>
       </c>
       <c r="AI17">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AJ17">
         <v>15.5</v>
@@ -4792,7 +4792,7 @@
         <v>80</v>
       </c>
       <c r="AM17">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="AN17">
         <v>14.5</v>
@@ -4807,10 +4807,10 @@
         <v>19</v>
       </c>
       <c r="AR17">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AS17">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AT17">
         <v>5</v>
@@ -4819,10 +4819,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV17">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AW17">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AX17">
         <v>6.4</v>
@@ -4831,28 +4831,28 @@
         <v>9.6</v>
       </c>
       <c r="AZ17">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BA17">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BB17">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BC17">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BD17">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BE17">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BF17">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BG17">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BH17">
         <v>3.25</v>
@@ -4935,10 +4935,10 @@
         <v>145</v>
       </c>
       <c r="F18">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="G18">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="H18">
         <v>1.73</v>
@@ -4959,34 +4959,34 @@
         <v>1.01</v>
       </c>
       <c r="N18">
-        <v>3.45</v>
+        <v>10.5</v>
       </c>
       <c r="O18">
         <v>1.07</v>
       </c>
       <c r="P18">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="Q18">
         <v>1.23</v>
       </c>
       <c r="R18">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="S18">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="T18">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="U18">
         <v>3.1</v>
       </c>
       <c r="V18">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="W18">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="X18">
         <v>160</v>
@@ -5004,13 +5004,13 @@
         <v>46</v>
       </c>
       <c r="AC18">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AD18">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE18">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AF18">
         <v>120</v>
@@ -5025,13 +5025,13 @@
         <v>23</v>
       </c>
       <c r="AJ18">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK18">
         <v>42</v>
       </c>
       <c r="AL18">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM18">
         <v>42</v>
@@ -5043,64 +5043,64 @@
         <v>5</v>
       </c>
       <c r="AP18">
+        <v>5.3</v>
+      </c>
+      <c r="AQ18">
+        <v>21</v>
+      </c>
+      <c r="AR18">
+        <v>18.5</v>
+      </c>
+      <c r="AS18">
+        <v>21</v>
+      </c>
+      <c r="AT18">
+        <v>5.1</v>
+      </c>
+      <c r="AU18">
+        <v>12</v>
+      </c>
+      <c r="AV18">
+        <v>10</v>
+      </c>
+      <c r="AW18">
+        <v>14</v>
+      </c>
+      <c r="AX18">
+        <v>5.2</v>
+      </c>
+      <c r="AY18">
+        <v>16.5</v>
+      </c>
+      <c r="AZ18">
+        <v>12.5</v>
+      </c>
+      <c r="BA18">
+        <v>16.5</v>
+      </c>
+      <c r="BB18">
         <v>5.4</v>
       </c>
-      <c r="AQ18">
-        <v>4.9</v>
-      </c>
-      <c r="AR18">
-        <v>4.8</v>
-      </c>
-      <c r="AS18">
-        <v>4.9</v>
-      </c>
-      <c r="AT18">
-        <v>5.2</v>
-      </c>
-      <c r="AU18">
-        <v>4.3</v>
-      </c>
-      <c r="AV18">
-        <v>4.3</v>
-      </c>
-      <c r="AW18">
-        <v>4.5</v>
-      </c>
-      <c r="AX18">
-        <v>5.3</v>
-      </c>
-      <c r="AY18">
-        <v>4.7</v>
-      </c>
-      <c r="AZ18">
-        <v>4.4</v>
-      </c>
-      <c r="BA18">
-        <v>4.7</v>
-      </c>
-      <c r="BB18">
-        <v>5.5</v>
-      </c>
       <c r="BC18">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BD18">
         <v>5</v>
       </c>
       <c r="BE18">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF18">
-        <v>4.4</v>
+        <v>12.5</v>
       </c>
       <c r="BG18">
-        <v>2.7</v>
+        <v>3.85</v>
       </c>
       <c r="BH18">
         <v>7.6</v>
       </c>
       <c r="BI18">
-        <v>3.15</v>
+        <v>5.2</v>
       </c>
       <c r="BJ18">
         <v>9.4</v>
@@ -5177,28 +5177,28 @@
         <v>146</v>
       </c>
       <c r="F19">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="G19">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="H19">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="I19">
         <v>990</v>
       </c>
       <c r="J19">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="K19">
-        <v>950</v>
+        <v>3.95</v>
       </c>
       <c r="L19">
         <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N19">
         <v>1.27</v>
@@ -5225,34 +5225,34 @@
         <v>1.11</v>
       </c>
       <c r="V19">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="W19">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="X19">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y19">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z19">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA19">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB19">
         <v>950</v>
       </c>
       <c r="AC19">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD19">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE19">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF19">
         <v>500</v>
@@ -5261,10 +5261,10 @@
         <v>950</v>
       </c>
       <c r="AH19">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI19">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ19">
         <v>900</v>
@@ -5276,67 +5276,67 @@
         <v>500</v>
       </c>
       <c r="AM19">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN19">
         <v>500</v>
       </c>
       <c r="AO19">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP19">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AQ19">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AR19">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AS19">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AT19">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AU19">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AV19">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AW19">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AX19">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AY19">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AZ19">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BA19">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BB19">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BC19">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BD19">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BE19">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BF19">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG19">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5428,7 +5428,7 @@
         <v>1.58</v>
       </c>
       <c r="I20">
-        <v>870</v>
+        <v>2.44</v>
       </c>
       <c r="J20">
         <v>2.84</v>
@@ -5467,7 +5467,7 @@
         <v>1.11</v>
       </c>
       <c r="V20">
-        <v>1.52</v>
+        <v>1.69</v>
       </c>
       <c r="W20">
         <v>1.17</v>
@@ -5527,7 +5527,7 @@
         <v>500</v>
       </c>
       <c r="AP20">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="AQ20">
         <v>3.85</v>
@@ -5536,43 +5536,43 @@
         <v>5.1</v>
       </c>
       <c r="AS20">
-        <v>1.28</v>
+        <v>1.04</v>
       </c>
       <c r="AT20">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="AU20">
         <v>5.1</v>
       </c>
       <c r="AV20">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="AW20">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="AX20">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="AY20">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="AZ20">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="BA20">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="BB20">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="BC20">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="BD20">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="BE20">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="BF20">
         <v>1.55</v>
@@ -5709,10 +5709,10 @@
         <v>1.11</v>
       </c>
       <c r="V21">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W21">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X21">
         <v>1000</v>
@@ -5826,61 +5826,61 @@
         <v>1000</v>
       </c>
       <c r="BI21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ21">
         <v>1000</v>
       </c>
       <c r="BK21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN21">
         <v>1000</v>
       </c>
       <c r="BO21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP21">
         <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR21">
         <v>1000</v>
       </c>
       <c r="BS21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT21">
         <v>1000</v>
       </c>
       <c r="BU21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV21">
         <v>1000</v>
       </c>
       <c r="BW21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ21">
         <v>1000</v>
       </c>
       <c r="CA21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB21" t="s">
         <v>151</v>
@@ -5906,7 +5906,7 @@
         <v>1.98</v>
       </c>
       <c r="G22">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H22">
         <v>3.4</v>
@@ -5927,7 +5927,7 @@
         <v>1.01</v>
       </c>
       <c r="N22">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O22">
         <v>1.18</v>
@@ -5945,7 +5945,7 @@
         <v>2.34</v>
       </c>
       <c r="T22">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U22">
         <v>2.44</v>
@@ -5954,7 +5954,7 @@
         <v>1.31</v>
       </c>
       <c r="W22">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X22">
         <v>27</v>
@@ -5975,7 +5975,7 @@
         <v>11</v>
       </c>
       <c r="AD22">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE22">
         <v>40</v>
@@ -5987,7 +5987,7 @@
         <v>12</v>
       </c>
       <c r="AH22">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI22">
         <v>40</v>
@@ -5996,7 +5996,7 @@
         <v>26</v>
       </c>
       <c r="AK22">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL22">
         <v>29</v>
@@ -6011,16 +6011,16 @@
         <v>29</v>
       </c>
       <c r="AP22">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="AQ22">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AR22">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS22">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT22">
         <v>10.5</v>
@@ -6029,13 +6029,13 @@
         <v>8.4</v>
       </c>
       <c r="AV22">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW22">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX22">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY22">
         <v>9.199999999999999</v>
@@ -6044,19 +6044,19 @@
         <v>12</v>
       </c>
       <c r="BA22">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB22">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BC22">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD22">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BF22">
         <v>7.6</v>
@@ -6148,13 +6148,13 @@
         <v>3.75</v>
       </c>
       <c r="G23">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="H23">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="I23">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="J23">
         <v>3.1</v>
@@ -6163,13 +6163,13 @@
         <v>3.4</v>
       </c>
       <c r="L23">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="M23">
         <v>1.1</v>
       </c>
       <c r="N23">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="O23">
         <v>1.44</v>
@@ -6178,7 +6178,7 @@
         <v>1.64</v>
       </c>
       <c r="Q23">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R23">
         <v>1.24</v>
@@ -6190,13 +6190,13 @@
         <v>1.84</v>
       </c>
       <c r="U23">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V23">
         <v>1.73</v>
       </c>
       <c r="W23">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="X23">
         <v>10.5</v>
@@ -6205,7 +6205,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z23">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA23">
         <v>38</v>
@@ -6223,10 +6223,10 @@
         <v>34</v>
       </c>
       <c r="AF23">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AG23">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AH23">
         <v>24</v>
@@ -6235,7 +6235,7 @@
         <v>60</v>
       </c>
       <c r="AJ23">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AK23">
         <v>65</v>
@@ -6256,13 +6256,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ23">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AR23">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AS23">
-        <v>5.6</v>
+        <v>26</v>
       </c>
       <c r="AT23">
         <v>10</v>
@@ -6289,19 +6289,19 @@
         <v>5.9</v>
       </c>
       <c r="BB23">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BC23">
+        <v>5.7</v>
+      </c>
+      <c r="BD23">
+        <v>5.8</v>
+      </c>
+      <c r="BE23">
         <v>6</v>
       </c>
-      <c r="BD23">
-        <v>6</v>
-      </c>
-      <c r="BE23">
-        <v>6.4</v>
-      </c>
       <c r="BF23">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BG23">
         <v>19.5</v>
@@ -6322,7 +6322,7 @@
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BN23">
         <v>7.8</v>
@@ -6334,7 +6334,7 @@
         <v>40</v>
       </c>
       <c r="BQ23">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BR23">
         <v>60</v>
@@ -6349,7 +6349,7 @@
         <v>3.95</v>
       </c>
       <c r="BV23">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BW23">
         <v>4.7</v>
@@ -6358,13 +6358,13 @@
         <v>44</v>
       </c>
       <c r="BY23">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BZ23">
         <v>44</v>
       </c>
       <c r="CA23">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="CB23" t="s">
         <v>151</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="149">
   <si>
     <t>League</t>
   </si>
@@ -256,30 +256,30 @@
     <t>SnapshotTS</t>
   </si>
   <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
+    <t>Egyptian Premier</t>
+  </si>
+  <si>
+    <t>Qatari Stars League</t>
+  </si>
+  <si>
+    <t>Saudi 1st Division</t>
+  </si>
+  <si>
+    <t>Algerian Ligue 1</t>
+  </si>
+  <si>
+    <t>Spanish La Liga</t>
+  </si>
+  <si>
+    <t>English National League</t>
+  </si>
+  <si>
     <t>Bolivian Liga de Futbol Profesional</t>
   </si>
   <si>
-    <t>Colombian Primera A</t>
-  </si>
-  <si>
-    <t>Egyptian Premier</t>
-  </si>
-  <si>
-    <t>Qatari Stars League</t>
-  </si>
-  <si>
-    <t>Saudi 1st Division</t>
-  </si>
-  <si>
-    <t>Algerian Ligue 1</t>
-  </si>
-  <si>
-    <t>Spanish La Liga</t>
-  </si>
-  <si>
-    <t>English National League</t>
-  </si>
-  <si>
     <t>Icelandic 2 Deild</t>
   </si>
   <si>
@@ -289,9 +289,6 @@
     <t>2026-08-27</t>
   </si>
   <si>
-    <t>00:30:00</t>
-  </si>
-  <si>
     <t>01:30:00</t>
   </si>
   <si>
@@ -337,9 +334,6 @@
     <t>23:10:00</t>
   </si>
   <si>
-    <t>Blooming Santa Cruz</t>
-  </si>
-  <si>
     <t>Atletico Nacional Medellin</t>
   </si>
   <si>
@@ -403,9 +397,6 @@
     <t>Llaneros FC</t>
   </si>
   <si>
-    <t>CDT Real Oruro</t>
-  </si>
-  <si>
     <t>Deportivo Cali</t>
   </si>
   <si>
@@ -469,7 +460,7 @@
     <t>Millonarios</t>
   </si>
   <si>
-    <t>2026-08-26 21:29:22</t>
+    <t>2026-08-26 23:42:08</t>
   </si>
 </sst>
 </file>
@@ -801,7 +792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CB22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1057,226 +1048,226 @@
         <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F2">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="G2">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="H2">
+        <v>28</v>
+      </c>
+      <c r="I2">
+        <v>34</v>
+      </c>
+      <c r="J2">
+        <v>7</v>
+      </c>
+      <c r="K2">
         <v>7.6</v>
       </c>
-      <c r="I2">
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>4.5</v>
+      </c>
+      <c r="O2">
+        <v>1.27</v>
+      </c>
+      <c r="P2">
+        <v>1.83</v>
+      </c>
+      <c r="Q2">
+        <v>2.18</v>
+      </c>
+      <c r="R2">
+        <v>1.21</v>
+      </c>
+      <c r="S2">
+        <v>5.6</v>
+      </c>
+      <c r="T2">
+        <v>2.54</v>
+      </c>
+      <c r="U2">
+        <v>1.57</v>
+      </c>
+      <c r="V2">
+        <v>1.03</v>
+      </c>
+      <c r="W2">
+        <v>5.5</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>1000</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>4.8</v>
+      </c>
+      <c r="AC2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD2">
+        <v>48</v>
+      </c>
+      <c r="AE2">
+        <v>370</v>
+      </c>
+      <c r="AF2">
+        <v>4.5</v>
+      </c>
+      <c r="AG2">
+        <v>9.4</v>
+      </c>
+      <c r="AH2">
+        <v>44</v>
+      </c>
+      <c r="AI2">
+        <v>340</v>
+      </c>
+      <c r="AJ2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AK2">
+        <v>19.5</v>
+      </c>
+      <c r="AL2">
+        <v>100</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>14</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>15</v>
+      </c>
+      <c r="AQ2">
+        <v>15.5</v>
+      </c>
+      <c r="AR2">
+        <v>15</v>
+      </c>
+      <c r="AS2">
+        <v>15</v>
+      </c>
+      <c r="AT2">
+        <v>4.5</v>
+      </c>
+      <c r="AU2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV2">
+        <v>38</v>
+      </c>
+      <c r="AW2">
+        <v>210</v>
+      </c>
+      <c r="AX2">
+        <v>4.2</v>
+      </c>
+      <c r="AY2">
         <v>8.6</v>
       </c>
-      <c r="J2">
-        <v>6.4</v>
-      </c>
-      <c r="K2">
-        <v>6.8</v>
-      </c>
-      <c r="L2">
-        <v>1.16</v>
-      </c>
-      <c r="M2">
-        <v>1.01</v>
-      </c>
-      <c r="N2">
-        <v>10</v>
-      </c>
-      <c r="O2">
-        <v>1.09</v>
-      </c>
-      <c r="P2">
-        <v>4</v>
-      </c>
-      <c r="Q2">
-        <v>1.3</v>
-      </c>
-      <c r="R2">
-        <v>2.28</v>
-      </c>
-      <c r="S2">
-        <v>1.72</v>
-      </c>
-      <c r="T2">
-        <v>1.58</v>
-      </c>
-      <c r="U2">
-        <v>2.48</v>
-      </c>
-      <c r="V2">
-        <v>1.13</v>
-      </c>
-      <c r="W2">
-        <v>3.55</v>
-      </c>
-      <c r="X2">
-        <v>55</v>
-      </c>
-      <c r="Y2">
-        <v>55</v>
-      </c>
-      <c r="Z2">
-        <v>110</v>
-      </c>
-      <c r="AA2">
-        <v>250</v>
-      </c>
-      <c r="AB2">
-        <v>20</v>
-      </c>
-      <c r="AC2">
-        <v>18</v>
-      </c>
-      <c r="AD2">
-        <v>38</v>
-      </c>
-      <c r="AE2">
-        <v>90</v>
-      </c>
-      <c r="AF2">
-        <v>15</v>
-      </c>
-      <c r="AG2">
-        <v>13</v>
-      </c>
-      <c r="AH2">
-        <v>21</v>
-      </c>
-      <c r="AI2">
+      <c r="AZ2">
+        <v>28</v>
+      </c>
+      <c r="BA2">
+        <v>180</v>
+      </c>
+      <c r="BB2">
+        <v>8</v>
+      </c>
+      <c r="BC2">
+        <v>17</v>
+      </c>
+      <c r="BD2">
         <v>70</v>
       </c>
-      <c r="AJ2">
-        <v>16</v>
-      </c>
-      <c r="AK2">
-        <v>13</v>
-      </c>
-      <c r="AL2">
-        <v>24</v>
-      </c>
-      <c r="AM2">
+      <c r="BE2">
         <v>70</v>
       </c>
-      <c r="AN2">
-        <v>3.25</v>
-      </c>
-      <c r="AO2">
-        <v>55</v>
-      </c>
-      <c r="AP2">
-        <v>44</v>
-      </c>
-      <c r="AQ2">
-        <v>46</v>
-      </c>
-      <c r="AR2">
-        <v>55</v>
-      </c>
-      <c r="AS2">
-        <v>14.5</v>
-      </c>
-      <c r="AT2">
-        <v>17</v>
-      </c>
-      <c r="AU2">
-        <v>16</v>
-      </c>
-      <c r="AV2">
-        <v>30</v>
-      </c>
-      <c r="AW2">
-        <v>65</v>
-      </c>
-      <c r="AX2">
-        <v>13</v>
-      </c>
-      <c r="AY2">
-        <v>12</v>
-      </c>
-      <c r="AZ2">
-        <v>18</v>
-      </c>
-      <c r="BA2">
-        <v>50</v>
-      </c>
-      <c r="BB2">
-        <v>14</v>
-      </c>
-      <c r="BC2">
-        <v>11.5</v>
-      </c>
-      <c r="BD2">
-        <v>20</v>
-      </c>
-      <c r="BE2">
-        <v>46</v>
-      </c>
       <c r="BF2">
-        <v>3.1</v>
+        <v>12.5</v>
       </c>
       <c r="BG2">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="BH2">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1285,7 +1276,7 @@
         <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1299,235 +1290,235 @@
         <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F3">
+        <v>2.3</v>
+      </c>
+      <c r="G3">
+        <v>2.62</v>
+      </c>
+      <c r="H3">
+        <v>4</v>
+      </c>
+      <c r="I3">
+        <v>5.8</v>
+      </c>
+      <c r="J3">
+        <v>2.44</v>
+      </c>
+      <c r="K3">
+        <v>2.82</v>
+      </c>
+      <c r="L3">
         <v>1.6</v>
       </c>
-      <c r="G3">
-        <v>1.63</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
-      </c>
-      <c r="I3">
-        <v>7.6</v>
-      </c>
-      <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>4.3</v>
-      </c>
-      <c r="L3">
-        <v>1.41</v>
-      </c>
       <c r="M3">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N3">
-        <v>3.8</v>
+        <v>2.02</v>
       </c>
       <c r="O3">
-        <v>1.34</v>
+        <v>1.69</v>
       </c>
       <c r="P3">
-        <v>1.93</v>
+        <v>1.29</v>
       </c>
       <c r="Q3">
-        <v>2.02</v>
+        <v>3.3</v>
       </c>
       <c r="R3">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="S3">
-        <v>3.65</v>
+        <v>6.6</v>
       </c>
       <c r="T3">
-        <v>2.02</v>
+        <v>1.11</v>
       </c>
       <c r="U3">
-        <v>1.88</v>
+        <v>1.11</v>
       </c>
       <c r="V3">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="W3">
-        <v>2.58</v>
+        <v>1.61</v>
       </c>
       <c r="X3">
-        <v>14.5</v>
+        <v>7.2</v>
       </c>
       <c r="Y3">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="Z3">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AA3">
-        <v>230</v>
+        <v>900</v>
       </c>
       <c r="AB3">
+        <v>14</v>
+      </c>
+      <c r="AC3">
+        <v>8.4</v>
+      </c>
+      <c r="AD3">
+        <v>950</v>
+      </c>
+      <c r="AE3">
+        <v>500</v>
+      </c>
+      <c r="AF3">
+        <v>500</v>
+      </c>
+      <c r="AG3">
+        <v>970</v>
+      </c>
+      <c r="AH3">
+        <v>950</v>
+      </c>
+      <c r="AI3">
+        <v>500</v>
+      </c>
+      <c r="AJ3">
+        <v>900</v>
+      </c>
+      <c r="AK3">
+        <v>500</v>
+      </c>
+      <c r="AL3">
+        <v>500</v>
+      </c>
+      <c r="AM3">
+        <v>500</v>
+      </c>
+      <c r="AN3">
+        <v>600</v>
+      </c>
+      <c r="AO3">
+        <v>600</v>
+      </c>
+      <c r="AP3">
+        <v>4.4</v>
+      </c>
+      <c r="AQ3">
         <v>7.8</v>
       </c>
-      <c r="AC3">
-        <v>9.4</v>
-      </c>
-      <c r="AD3">
-        <v>27</v>
-      </c>
-      <c r="AE3">
-        <v>120</v>
-      </c>
-      <c r="AF3">
-        <v>9</v>
-      </c>
-      <c r="AG3">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AH3">
-        <v>25</v>
-      </c>
-      <c r="AI3">
-        <v>110</v>
-      </c>
-      <c r="AJ3">
-        <v>15</v>
-      </c>
-      <c r="AK3">
-        <v>18</v>
-      </c>
-      <c r="AL3">
-        <v>42</v>
-      </c>
-      <c r="AM3">
-        <v>160</v>
-      </c>
-      <c r="AN3">
-        <v>10.5</v>
-      </c>
-      <c r="AO3">
-        <v>160</v>
-      </c>
-      <c r="AP3">
-        <v>12.5</v>
-      </c>
-      <c r="AQ3">
-        <v>20</v>
-      </c>
       <c r="AR3">
-        <v>38</v>
+        <v>2.3</v>
       </c>
       <c r="AS3">
-        <v>15</v>
+        <v>2.38</v>
       </c>
       <c r="AT3">
-        <v>7</v>
+        <v>1.85</v>
       </c>
       <c r="AU3">
-        <v>8.6</v>
+        <v>1.85</v>
       </c>
       <c r="AV3">
-        <v>23</v>
+        <v>2.3</v>
       </c>
       <c r="AW3">
-        <v>17</v>
+        <v>2.38</v>
       </c>
       <c r="AX3">
-        <v>8</v>
+        <v>2.14</v>
       </c>
       <c r="AY3">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AZ3">
-        <v>21</v>
+        <v>2.38</v>
       </c>
       <c r="BA3">
-        <v>15.5</v>
+        <v>2.38</v>
       </c>
       <c r="BB3">
-        <v>13.5</v>
+        <v>2.38</v>
       </c>
       <c r="BC3">
-        <v>15.5</v>
+        <v>2.36</v>
       </c>
       <c r="BD3">
-        <v>34</v>
+        <v>2.36</v>
       </c>
       <c r="BE3">
-        <v>14.5</v>
+        <v>2.38</v>
       </c>
       <c r="BF3">
-        <v>9</v>
+        <v>2.22</v>
       </c>
       <c r="BG3">
-        <v>15</v>
+        <v>2.32</v>
       </c>
       <c r="BH3">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BL3">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="BM3">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN3">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="BP3">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR3">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT3">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV3">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BX3">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1541,52 +1532,52 @@
         <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F4">
-        <v>2.34</v>
+        <v>2.64</v>
       </c>
       <c r="G4">
-        <v>2.68</v>
+        <v>3.3</v>
       </c>
       <c r="H4">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="I4">
-        <v>5.9</v>
+        <v>2.62</v>
       </c>
       <c r="J4">
-        <v>2.42</v>
+        <v>3.85</v>
       </c>
       <c r="K4">
-        <v>2.76</v>
+        <v>4.4</v>
       </c>
       <c r="L4">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N4">
-        <v>1.86</v>
+        <v>4.7</v>
       </c>
       <c r="O4">
-        <v>1.69</v>
+        <v>1.18</v>
       </c>
       <c r="P4">
-        <v>1.28</v>
+        <v>2.16</v>
       </c>
       <c r="Q4">
-        <v>3</v>
+        <v>1.45</v>
       </c>
       <c r="R4">
-        <v>1.09</v>
+        <v>1.36</v>
       </c>
       <c r="S4">
-        <v>6.6</v>
+        <v>2.4</v>
       </c>
       <c r="T4">
         <v>1.11</v>
@@ -1595,118 +1586,118 @@
         <v>1.11</v>
       </c>
       <c r="V4">
-        <v>1.22</v>
+        <v>1.61</v>
       </c>
       <c r="W4">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="X4">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
         <v>970</v>
       </c>
       <c r="Z4">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AA4">
         <v>900</v>
       </c>
       <c r="AB4">
-        <v>48</v>
+        <v>970</v>
       </c>
       <c r="AC4">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AD4">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE4">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AF4">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AG4">
         <v>970</v>
       </c>
       <c r="AH4">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="AI4">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AJ4">
         <v>900</v>
       </c>
       <c r="AK4">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AL4">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AM4">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN4">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AO4">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AP4">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="AQ4">
-        <v>7.2</v>
+        <v>1.6</v>
       </c>
       <c r="AR4">
-        <v>2.54</v>
+        <v>1.62</v>
       </c>
       <c r="AS4">
-        <v>2.58</v>
+        <v>1.66</v>
       </c>
       <c r="AT4">
-        <v>4.8</v>
+        <v>1.64</v>
       </c>
       <c r="AU4">
-        <v>1.94</v>
+        <v>1.45</v>
       </c>
       <c r="AV4">
-        <v>14</v>
+        <v>1.58</v>
       </c>
       <c r="AW4">
-        <v>2.58</v>
+        <v>1.68</v>
       </c>
       <c r="AX4">
-        <v>7.8</v>
+        <v>1.62</v>
       </c>
       <c r="AY4">
-        <v>2.48</v>
+        <v>6.6</v>
       </c>
       <c r="AZ4">
-        <v>2.58</v>
+        <v>1.58</v>
       </c>
       <c r="BA4">
-        <v>2.58</v>
+        <v>1.66</v>
       </c>
       <c r="BB4">
-        <v>2.58</v>
+        <v>1.67</v>
       </c>
       <c r="BC4">
-        <v>2.56</v>
+        <v>1.66</v>
       </c>
       <c r="BD4">
-        <v>2.56</v>
+        <v>1.66</v>
       </c>
       <c r="BE4">
-        <v>2.58</v>
+        <v>1.68</v>
       </c>
       <c r="BF4">
-        <v>2.5</v>
+        <v>1.69</v>
       </c>
       <c r="BG4">
-        <v>2.54</v>
+        <v>1.64</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1769,7 +1760,7 @@
         <v>1.04</v>
       </c>
       <c r="CB4" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1783,426 +1774,426 @@
         <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F5">
-        <v>2.64</v>
+        <v>1.47</v>
       </c>
       <c r="G5">
-        <v>2.9</v>
+        <v>1.74</v>
       </c>
       <c r="H5">
-        <v>2.46</v>
+        <v>3.6</v>
       </c>
       <c r="I5">
-        <v>2.7</v>
+        <v>990</v>
       </c>
       <c r="J5">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="K5">
-        <v>4.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L5">
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N5">
-        <v>4.8</v>
+        <v>2.04</v>
       </c>
       <c r="O5">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="P5">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="Q5">
-        <v>1.56</v>
+        <v>1.85</v>
       </c>
       <c r="R5">
-        <v>1.54</v>
+        <v>1.26</v>
       </c>
       <c r="S5">
-        <v>2.24</v>
+        <v>2.56</v>
       </c>
       <c r="T5">
-        <v>1.55</v>
+        <v>1.11</v>
       </c>
       <c r="U5">
-        <v>2.58</v>
+        <v>1.11</v>
       </c>
       <c r="V5">
-        <v>1.58</v>
+        <v>1.14</v>
       </c>
       <c r="W5">
+        <v>2.34</v>
+      </c>
+      <c r="X5">
+        <v>970</v>
+      </c>
+      <c r="Y5">
+        <v>950</v>
+      </c>
+      <c r="Z5">
+        <v>160</v>
+      </c>
+      <c r="AA5">
+        <v>1000</v>
+      </c>
+      <c r="AB5">
+        <v>970</v>
+      </c>
+      <c r="AC5">
+        <v>970</v>
+      </c>
+      <c r="AD5">
+        <v>950</v>
+      </c>
+      <c r="AE5">
+        <v>1000</v>
+      </c>
+      <c r="AF5">
+        <v>970</v>
+      </c>
+      <c r="AG5">
+        <v>970</v>
+      </c>
+      <c r="AH5">
+        <v>1000</v>
+      </c>
+      <c r="AI5">
+        <v>260</v>
+      </c>
+      <c r="AJ5">
+        <v>970</v>
+      </c>
+      <c r="AK5">
+        <v>65</v>
+      </c>
+      <c r="AL5">
+        <v>100</v>
+      </c>
+      <c r="AM5">
+        <v>1000</v>
+      </c>
+      <c r="AN5">
+        <v>29</v>
+      </c>
+      <c r="AO5">
+        <v>1000</v>
+      </c>
+      <c r="AP5">
+        <v>1.45</v>
+      </c>
+      <c r="AQ5">
+        <v>1.5</v>
+      </c>
+      <c r="AR5">
+        <v>1.51</v>
+      </c>
+      <c r="AS5">
         <v>1.52</v>
       </c>
-      <c r="X5">
-        <v>27</v>
-      </c>
-      <c r="Y5">
-        <v>17.5</v>
-      </c>
-      <c r="Z5">
-        <v>23</v>
-      </c>
-      <c r="AA5">
-        <v>40</v>
-      </c>
-      <c r="AB5">
-        <v>18.5</v>
-      </c>
-      <c r="AC5">
-        <v>10</v>
-      </c>
-      <c r="AD5">
-        <v>14.5</v>
-      </c>
-      <c r="AE5">
-        <v>28</v>
-      </c>
-      <c r="AF5">
-        <v>23</v>
-      </c>
-      <c r="AG5">
-        <v>14</v>
-      </c>
-      <c r="AH5">
-        <v>15.5</v>
-      </c>
-      <c r="AI5">
-        <v>36</v>
-      </c>
-      <c r="AJ5">
-        <v>46</v>
-      </c>
-      <c r="AK5">
-        <v>30</v>
-      </c>
-      <c r="AL5">
-        <v>36</v>
-      </c>
-      <c r="AM5">
-        <v>65</v>
-      </c>
-      <c r="AN5">
-        <v>16.5</v>
-      </c>
-      <c r="AO5">
-        <v>14.5</v>
-      </c>
-      <c r="AP5">
-        <v>17.5</v>
-      </c>
-      <c r="AQ5">
-        <v>13.5</v>
-      </c>
-      <c r="AR5">
-        <v>15</v>
-      </c>
-      <c r="AS5">
-        <v>6</v>
-      </c>
       <c r="AT5">
-        <v>12</v>
+        <v>1.45</v>
       </c>
       <c r="AU5">
-        <v>8.199999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="AV5">
-        <v>9.6</v>
+        <v>1.49</v>
       </c>
       <c r="AW5">
-        <v>18.5</v>
+        <v>4.2</v>
       </c>
       <c r="AX5">
-        <v>16.5</v>
+        <v>1.4</v>
       </c>
       <c r="AY5">
-        <v>10</v>
+        <v>1.41</v>
       </c>
       <c r="AZ5">
-        <v>12.5</v>
+        <v>1.52</v>
       </c>
       <c r="BA5">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="BB5">
-        <v>6</v>
+        <v>1.51</v>
       </c>
       <c r="BC5">
-        <v>20</v>
+        <v>1.46</v>
       </c>
       <c r="BD5">
-        <v>5.9</v>
+        <v>1.5</v>
       </c>
       <c r="BE5">
-        <v>6.2</v>
+        <v>1.52</v>
       </c>
       <c r="BF5">
-        <v>13</v>
+        <v>1.44</v>
       </c>
       <c r="BG5">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="BH5">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="BL5">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BM5">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BN5">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BP5">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR5">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BT5">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV5">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BX5">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="CA5">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B6" t="s">
         <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F6">
-        <v>1.53</v>
+        <v>4.7</v>
       </c>
       <c r="G6">
-        <v>1.65</v>
+        <v>5.6</v>
       </c>
       <c r="H6">
-        <v>6.6</v>
+        <v>1.76</v>
       </c>
       <c r="I6">
-        <v>7.8</v>
+        <v>1.92</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="K6">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="L6">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="M6">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N6">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="O6">
         <v>1.27</v>
       </c>
       <c r="P6">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="Q6">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="R6">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S6">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="T6">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="U6">
-        <v>1.77</v>
+        <v>1.97</v>
       </c>
       <c r="V6">
-        <v>1.14</v>
+        <v>2.08</v>
       </c>
       <c r="W6">
-        <v>2.52</v>
+        <v>1.21</v>
       </c>
       <c r="X6">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y6">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="Z6">
-        <v>160</v>
+        <v>13.5</v>
       </c>
       <c r="AA6">
-        <v>260</v>
+        <v>24</v>
       </c>
       <c r="AB6">
-        <v>9.199999999999999</v>
+        <v>21</v>
       </c>
       <c r="AC6">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AD6">
-        <v>32</v>
+        <v>12.5</v>
       </c>
       <c r="AE6">
-        <v>130</v>
+        <v>24</v>
       </c>
       <c r="AF6">
-        <v>10.5</v>
+        <v>48</v>
       </c>
       <c r="AG6">
-        <v>11.5</v>
+        <v>25</v>
       </c>
       <c r="AH6">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI6">
-        <v>260</v>
+        <v>46</v>
       </c>
       <c r="AJ6">
-        <v>17</v>
+        <v>470</v>
       </c>
       <c r="AK6">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="AL6">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="AM6">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="AN6">
-        <v>9.6</v>
+        <v>110</v>
       </c>
       <c r="AO6">
-        <v>180</v>
+        <v>15.5</v>
       </c>
       <c r="AP6">
         <v>12</v>
       </c>
       <c r="AQ6">
-        <v>18.5</v>
+        <v>7.4</v>
       </c>
       <c r="AR6">
-        <v>5.3</v>
+        <v>9.4</v>
       </c>
       <c r="AS6">
-        <v>5.6</v>
+        <v>3.9</v>
       </c>
       <c r="AT6">
-        <v>6.2</v>
+        <v>3.8</v>
       </c>
       <c r="AU6">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV6">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="AW6">
-        <v>5.5</v>
+        <v>3.9</v>
       </c>
       <c r="AX6">
-        <v>7.2</v>
+        <v>4.2</v>
       </c>
       <c r="AY6">
-        <v>7.8</v>
+        <v>3.95</v>
       </c>
       <c r="AZ6">
-        <v>18</v>
+        <v>3.95</v>
       </c>
       <c r="BA6">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="BB6">
-        <v>11</v>
+        <v>4.5</v>
       </c>
       <c r="BC6">
-        <v>13</v>
+        <v>4.4</v>
       </c>
       <c r="BD6">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="BE6">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="BF6">
-        <v>7.2</v>
+        <v>4.5</v>
       </c>
       <c r="BG6">
-        <v>5.6</v>
+        <v>3.8</v>
       </c>
       <c r="BH6">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="BI6">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="BJ6">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK6">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BL6">
         <v>1000</v>
@@ -2211,40 +2202,40 @@
         <v>5.5</v>
       </c>
       <c r="BN6">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="BO6">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="BP6">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="BQ6">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="BR6">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="BS6">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BT6">
-        <v>12</v>
+        <v>5.2</v>
       </c>
       <c r="BU6">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BW6">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY6">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BZ6">
         <v>0</v>
@@ -2253,12 +2244,12 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B7" t="s">
         <v>90</v>
@@ -2267,240 +2258,240 @@
         <v>95</v>
       </c>
       <c r="D7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F7">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="G7">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="H7">
-        <v>1.76</v>
+        <v>1.94</v>
       </c>
       <c r="I7">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="J7">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="K7">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L7">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="N7">
-        <v>3.55</v>
+        <v>5</v>
       </c>
       <c r="O7">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="P7">
-        <v>1.94</v>
+        <v>2.28</v>
       </c>
       <c r="Q7">
+        <v>1.58</v>
+      </c>
+      <c r="R7">
+        <v>1.18</v>
+      </c>
+      <c r="S7">
+        <v>1.16</v>
+      </c>
+      <c r="T7">
+        <v>1.56</v>
+      </c>
+      <c r="U7">
+        <v>1.11</v>
+      </c>
+      <c r="V7">
         <v>1.96</v>
       </c>
-      <c r="R7">
-        <v>1.33</v>
-      </c>
-      <c r="S7">
-        <v>3.45</v>
-      </c>
-      <c r="T7">
-        <v>1.83</v>
-      </c>
-      <c r="U7">
-        <v>1.97</v>
-      </c>
-      <c r="V7">
-        <v>2.08</v>
-      </c>
       <c r="W7">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="X7">
-        <v>17</v>
+        <v>950</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="Z7">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AA7">
-        <v>24</v>
+        <v>130</v>
       </c>
       <c r="AB7">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="AC7">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="AD7">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AE7">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="AF7">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="AG7">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="AH7">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="AI7">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="AJ7">
-        <v>470</v>
+        <v>900</v>
       </c>
       <c r="AK7">
         <v>85</v>
       </c>
       <c r="AL7">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="AM7">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN7">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="AO7">
-        <v>15.5</v>
+        <v>85</v>
       </c>
       <c r="AP7">
+        <v>1.87</v>
+      </c>
+      <c r="AQ7">
+        <v>1.81</v>
+      </c>
+      <c r="AR7">
+        <v>1.83</v>
+      </c>
+      <c r="AS7">
+        <v>1.82</v>
+      </c>
+      <c r="AT7">
+        <v>16</v>
+      </c>
+      <c r="AU7">
+        <v>1.7</v>
+      </c>
+      <c r="AV7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW7">
         <v>12</v>
       </c>
-      <c r="AQ7">
-        <v>7.4</v>
-      </c>
-      <c r="AR7">
-        <v>9.4</v>
-      </c>
-      <c r="AS7">
-        <v>3.9</v>
-      </c>
-      <c r="AT7">
-        <v>3.8</v>
-      </c>
-      <c r="AU7">
-        <v>7.4</v>
-      </c>
-      <c r="AV7">
-        <v>7</v>
-      </c>
-      <c r="AW7">
-        <v>3.9</v>
-      </c>
       <c r="AX7">
-        <v>4.2</v>
+        <v>17.5</v>
       </c>
       <c r="AY7">
-        <v>3.95</v>
+        <v>1.78</v>
       </c>
       <c r="AZ7">
-        <v>3.95</v>
+        <v>12</v>
       </c>
       <c r="BA7">
-        <v>4.2</v>
+        <v>1.82</v>
       </c>
       <c r="BB7">
-        <v>4.5</v>
+        <v>23</v>
       </c>
       <c r="BC7">
-        <v>4.4</v>
+        <v>20</v>
       </c>
       <c r="BD7">
-        <v>4.4</v>
+        <v>1.9</v>
       </c>
       <c r="BE7">
-        <v>4.5</v>
+        <v>1.92</v>
       </c>
       <c r="BF7">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BG7">
-        <v>3.8</v>
+        <v>2.48</v>
       </c>
       <c r="BH7">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP7">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B8" t="s">
         <v>90</v>
@@ -2509,482 +2500,482 @@
         <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F8">
-        <v>3.8</v>
+        <v>1.19</v>
       </c>
       <c r="G8">
-        <v>4.1</v>
+        <v>1.47</v>
       </c>
       <c r="H8">
-        <v>1.97</v>
+        <v>7.8</v>
       </c>
       <c r="I8">
-        <v>2.04</v>
+        <v>990</v>
       </c>
       <c r="J8">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="K8">
-        <v>4.3</v>
+        <v>9.6</v>
       </c>
       <c r="L8">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="M8">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="N8">
-        <v>5.2</v>
+        <v>1.25</v>
       </c>
       <c r="O8">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="P8">
-        <v>2.42</v>
+        <v>1.24</v>
       </c>
       <c r="Q8">
-        <v>1.58</v>
+        <v>1.31</v>
       </c>
       <c r="R8">
-        <v>1.58</v>
+        <v>1.14</v>
       </c>
       <c r="S8">
-        <v>2.44</v>
+        <v>1.31</v>
       </c>
       <c r="T8">
-        <v>1.56</v>
+        <v>1.11</v>
       </c>
       <c r="U8">
-        <v>2.48</v>
+        <v>1.11</v>
       </c>
       <c r="V8">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="W8">
-        <v>1.33</v>
+        <v>3.2</v>
       </c>
       <c r="X8">
-        <v>29</v>
+        <v>970</v>
       </c>
       <c r="Y8">
-        <v>15.5</v>
+        <v>950</v>
       </c>
       <c r="Z8">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>26</v>
+        <v>970</v>
       </c>
       <c r="AC8">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AD8">
-        <v>11.5</v>
+        <v>950</v>
       </c>
       <c r="AE8">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>34</v>
+        <v>970</v>
       </c>
       <c r="AG8">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AH8">
-        <v>16</v>
+        <v>950</v>
       </c>
       <c r="AI8">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>440</v>
+        <v>970</v>
       </c>
       <c r="AK8">
-        <v>44</v>
+        <v>970</v>
       </c>
       <c r="AL8">
-        <v>55</v>
+        <v>330</v>
       </c>
       <c r="AM8">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
         <v>29</v>
       </c>
       <c r="AO8">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>17</v>
+        <v>1.92</v>
       </c>
       <c r="AQ8">
-        <v>10.5</v>
+        <v>4.2</v>
       </c>
       <c r="AR8">
-        <v>13</v>
+        <v>2.14</v>
       </c>
       <c r="AS8">
-        <v>20</v>
+        <v>4.2</v>
       </c>
       <c r="AT8">
-        <v>18.5</v>
+        <v>1.77</v>
       </c>
       <c r="AU8">
-        <v>8.4</v>
+        <v>1.92</v>
       </c>
       <c r="AV8">
-        <v>9</v>
+        <v>4.2</v>
       </c>
       <c r="AW8">
-        <v>16</v>
+        <v>2.14</v>
       </c>
       <c r="AX8">
-        <v>14.5</v>
+        <v>1.79</v>
       </c>
       <c r="AY8">
-        <v>15</v>
+        <v>1.92</v>
       </c>
       <c r="AZ8">
-        <v>13</v>
+        <v>2.1</v>
       </c>
       <c r="BA8">
-        <v>18.5</v>
+        <v>2.14</v>
       </c>
       <c r="BB8">
-        <v>30</v>
+        <v>1.88</v>
       </c>
       <c r="BC8">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="BD8">
-        <v>6.6</v>
+        <v>2.1</v>
       </c>
       <c r="BE8">
-        <v>6.8</v>
+        <v>2.14</v>
       </c>
       <c r="BF8">
-        <v>19</v>
+        <v>1.87</v>
       </c>
       <c r="BG8">
-        <v>8.4</v>
+        <v>4.2</v>
       </c>
       <c r="BH8">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL8">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN8">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP8">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BR8">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BT8">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BV8">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX8">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B9" t="s">
         <v>90</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F9">
-        <v>1.27</v>
+        <v>2.42</v>
       </c>
       <c r="G9">
-        <v>1.32</v>
+        <v>13.5</v>
       </c>
       <c r="H9">
-        <v>16.5</v>
+        <v>1.74</v>
       </c>
       <c r="I9">
-        <v>19.5</v>
+        <v>5.3</v>
       </c>
       <c r="J9">
-        <v>5.2</v>
+        <v>2.52</v>
       </c>
       <c r="K9">
-        <v>6</v>
+        <v>3.05</v>
       </c>
       <c r="L9">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N9">
-        <v>3.5</v>
+        <v>1.25</v>
       </c>
       <c r="O9">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="P9">
-        <v>1.82</v>
+        <v>1.43</v>
       </c>
       <c r="Q9">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="R9">
+        <v>1.14</v>
+      </c>
+      <c r="S9">
+        <v>1.05</v>
+      </c>
+      <c r="T9">
+        <v>1.11</v>
+      </c>
+      <c r="U9">
+        <v>1.11</v>
+      </c>
+      <c r="V9">
         <v>1.31</v>
       </c>
-      <c r="S9">
-        <v>3.55</v>
-      </c>
-      <c r="T9">
-        <v>2.66</v>
-      </c>
-      <c r="U9">
-        <v>1.51</v>
-      </c>
-      <c r="V9">
-        <v>1.05</v>
-      </c>
       <c r="W9">
-        <v>4.1</v>
+        <v>1.24</v>
       </c>
       <c r="X9">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="Y9">
-        <v>85</v>
+        <v>7.4</v>
       </c>
       <c r="Z9">
-        <v>230</v>
+        <v>970</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB9">
-        <v>6.4</v>
+        <v>970</v>
       </c>
       <c r="AC9">
-        <v>14</v>
+        <v>8.6</v>
       </c>
       <c r="AD9">
-        <v>160</v>
+        <v>970</v>
       </c>
       <c r="AE9">
-        <v>610</v>
+        <v>500</v>
       </c>
       <c r="AF9">
-        <v>6.6</v>
+        <v>90</v>
       </c>
       <c r="AG9">
-        <v>12.5</v>
+        <v>950</v>
       </c>
       <c r="AH9">
-        <v>55</v>
+        <v>950</v>
       </c>
       <c r="AI9">
         <v>460</v>
       </c>
       <c r="AJ9">
-        <v>9.6</v>
+        <v>900</v>
       </c>
       <c r="AK9">
-        <v>19</v>
+        <v>500</v>
       </c>
       <c r="AL9">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AM9">
-        <v>530</v>
+        <v>500</v>
       </c>
       <c r="AN9">
-        <v>7.2</v>
+        <v>500</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP9">
-        <v>10.5</v>
+        <v>2</v>
       </c>
       <c r="AQ9">
-        <v>28</v>
+        <v>1.75</v>
       </c>
       <c r="AR9">
-        <v>9.6</v>
+        <v>2.1</v>
       </c>
       <c r="AS9">
-        <v>10</v>
+        <v>2.24</v>
       </c>
       <c r="AT9">
-        <v>5.5</v>
+        <v>2.24</v>
       </c>
       <c r="AU9">
-        <v>10</v>
+        <v>1.81</v>
       </c>
       <c r="AV9">
-        <v>23</v>
+        <v>1.95</v>
       </c>
       <c r="AW9">
-        <v>9.800000000000001</v>
+        <v>2.22</v>
       </c>
       <c r="AX9">
-        <v>5.4</v>
+        <v>2.22</v>
       </c>
       <c r="AY9">
-        <v>10</v>
+        <v>2.16</v>
       </c>
       <c r="AZ9">
-        <v>36</v>
+        <v>2.22</v>
       </c>
       <c r="BA9">
-        <v>9.800000000000001</v>
+        <v>2.26</v>
       </c>
       <c r="BB9">
-        <v>6.8</v>
+        <v>2.28</v>
       </c>
       <c r="BC9">
-        <v>13</v>
+        <v>2.28</v>
       </c>
       <c r="BD9">
-        <v>8.800000000000001</v>
+        <v>2.28</v>
       </c>
       <c r="BE9">
-        <v>9.800000000000001</v>
+        <v>2.28</v>
       </c>
       <c r="BF9">
-        <v>5.9</v>
+        <v>2.26</v>
       </c>
       <c r="BG9">
-        <v>10</v>
+        <v>2.18</v>
       </c>
       <c r="BH9">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>2.76</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BN9">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>2.96</v>
+        <v>1.04</v>
       </c>
       <c r="BP9">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR9">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT9">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B10" t="s">
         <v>90</v>
@@ -2993,235 +2984,235 @@
         <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E10" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F10">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="G10">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="H10">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="I10">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="J10">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="K10">
-        <v>3.05</v>
+        <v>6.6</v>
       </c>
       <c r="L10">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="M10">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="N10">
-        <v>2.44</v>
+        <v>3.25</v>
       </c>
       <c r="O10">
-        <v>1.58</v>
+        <v>1.27</v>
       </c>
       <c r="P10">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="Q10">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="R10">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="S10">
-        <v>5.7</v>
+        <v>2.64</v>
       </c>
       <c r="T10">
-        <v>2.2</v>
+        <v>1.11</v>
       </c>
       <c r="U10">
-        <v>1.7</v>
+        <v>1.11</v>
       </c>
       <c r="V10">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="X10">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="Z10">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="AA10">
-        <v>40</v>
+        <v>900</v>
       </c>
       <c r="AB10">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AC10">
-        <v>7.6</v>
+        <v>42</v>
       </c>
       <c r="AD10">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AE10">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AF10">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AG10">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="AH10">
-        <v>32</v>
+        <v>970</v>
       </c>
       <c r="AI10">
-        <v>190</v>
+        <v>290</v>
       </c>
       <c r="AJ10">
         <v>900</v>
       </c>
       <c r="AK10">
-        <v>230</v>
+        <v>90</v>
       </c>
       <c r="AL10">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AM10">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN10">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AO10">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AP10">
-        <v>6</v>
+        <v>1.68</v>
       </c>
       <c r="AQ10">
-        <v>5.9</v>
+        <v>1.68</v>
       </c>
       <c r="AR10">
-        <v>10.5</v>
+        <v>1.79</v>
       </c>
       <c r="AS10">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="AT10">
-        <v>9.6</v>
+        <v>1.67</v>
       </c>
       <c r="AU10">
+        <v>1.62</v>
+      </c>
+      <c r="AV10">
+        <v>1.72</v>
+      </c>
+      <c r="AW10">
+        <v>1.79</v>
+      </c>
+      <c r="AX10">
+        <v>1.75</v>
+      </c>
+      <c r="AY10">
+        <v>1.7</v>
+      </c>
+      <c r="AZ10">
+        <v>1.77</v>
+      </c>
+      <c r="BA10">
+        <v>1.8</v>
+      </c>
+      <c r="BB10">
+        <v>1.8</v>
+      </c>
+      <c r="BC10">
+        <v>1.79</v>
+      </c>
+      <c r="BD10">
+        <v>1.8</v>
+      </c>
+      <c r="BE10">
+        <v>1.82</v>
+      </c>
+      <c r="BF10">
+        <v>1.78</v>
+      </c>
+      <c r="BG10">
         <v>6.2</v>
       </c>
-      <c r="AV10">
-        <v>10</v>
-      </c>
-      <c r="AW10">
-        <v>16</v>
-      </c>
-      <c r="AX10">
-        <v>10.5</v>
-      </c>
-      <c r="AY10">
-        <v>16.5</v>
-      </c>
-      <c r="AZ10">
-        <v>18.5</v>
-      </c>
-      <c r="BA10">
-        <v>4.7</v>
-      </c>
-      <c r="BB10">
-        <v>4.8</v>
-      </c>
-      <c r="BC10">
-        <v>4.8</v>
-      </c>
-      <c r="BD10">
-        <v>4.8</v>
-      </c>
-      <c r="BE10">
-        <v>4.9</v>
-      </c>
-      <c r="BF10">
-        <v>4.8</v>
-      </c>
-      <c r="BG10">
-        <v>7.2</v>
-      </c>
       <c r="BH10">
-        <v>2.64</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>2.16</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN10">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP10">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT10">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV10">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX10">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3235,235 +3226,235 @@
         <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E11" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F11">
-        <v>2.76</v>
+        <v>1.75</v>
       </c>
       <c r="G11">
-        <v>3.1</v>
+        <v>1.88</v>
       </c>
       <c r="H11">
-        <v>2.56</v>
+        <v>5.7</v>
       </c>
       <c r="I11">
-        <v>2.86</v>
+        <v>6.6</v>
       </c>
       <c r="J11">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="K11">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M11">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="N11">
-        <v>3.4</v>
+        <v>2.78</v>
       </c>
       <c r="O11">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="P11">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="Q11">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="R11">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S11">
-        <v>2.64</v>
+        <v>4.8</v>
       </c>
       <c r="T11">
-        <v>1.79</v>
+        <v>2.2</v>
       </c>
       <c r="U11">
-        <v>2.06</v>
+        <v>1.71</v>
       </c>
       <c r="V11">
-        <v>1.53</v>
+        <v>1.18</v>
       </c>
       <c r="W11">
-        <v>1.47</v>
+        <v>2.12</v>
       </c>
       <c r="X11">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Y11">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="Z11">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="AA11">
-        <v>150</v>
+        <v>900</v>
       </c>
       <c r="AB11">
-        <v>11.5</v>
+        <v>6.6</v>
       </c>
       <c r="AC11">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD11">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="AE11">
-        <v>75</v>
+        <v>700</v>
       </c>
       <c r="AF11">
-        <v>21</v>
+        <v>9.6</v>
       </c>
       <c r="AG11">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="AH11">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AI11">
-        <v>290</v>
+        <v>700</v>
       </c>
       <c r="AJ11">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="AK11">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="AL11">
-        <v>290</v>
+        <v>70</v>
       </c>
       <c r="AM11">
         <v>580</v>
       </c>
       <c r="AN11">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="AO11">
-        <v>60</v>
+        <v>700</v>
       </c>
       <c r="AP11">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ11">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="AR11">
+        <v>7.4</v>
+      </c>
+      <c r="AS11">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT11">
+        <v>5.7</v>
+      </c>
+      <c r="AU11">
+        <v>7.2</v>
+      </c>
+      <c r="AV11">
+        <v>18</v>
+      </c>
+      <c r="AW11">
+        <v>8</v>
+      </c>
+      <c r="AX11">
+        <v>8.4</v>
+      </c>
+      <c r="AY11">
+        <v>9.4</v>
+      </c>
+      <c r="AZ11">
+        <v>13</v>
+      </c>
+      <c r="BA11">
+        <v>5.9</v>
+      </c>
+      <c r="BB11">
+        <v>17</v>
+      </c>
+      <c r="BC11">
+        <v>20</v>
+      </c>
+      <c r="BD11">
+        <v>7.6</v>
+      </c>
+      <c r="BE11">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF11">
         <v>6</v>
       </c>
-      <c r="AS11">
-        <v>7</v>
-      </c>
-      <c r="AT11">
-        <v>8.4</v>
-      </c>
-      <c r="AU11">
-        <v>6</v>
-      </c>
-      <c r="AV11">
-        <v>5.1</v>
-      </c>
-      <c r="AW11">
-        <v>6.6</v>
-      </c>
-      <c r="AX11">
-        <v>6</v>
-      </c>
-      <c r="AY11">
-        <v>5.2</v>
-      </c>
-      <c r="AZ11">
-        <v>5.8</v>
-      </c>
-      <c r="BA11">
-        <v>7.2</v>
-      </c>
-      <c r="BB11">
-        <v>7.2</v>
-      </c>
-      <c r="BC11">
-        <v>6.8</v>
-      </c>
-      <c r="BD11">
-        <v>7.2</v>
-      </c>
-      <c r="BE11">
-        <v>7.8</v>
-      </c>
-      <c r="BF11">
-        <v>6.8</v>
-      </c>
       <c r="BG11">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH11">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BI11">
-        <v>2.86</v>
+        <v>2.34</v>
       </c>
       <c r="BJ11">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="BK11">
+        <v>3.75</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
         <v>5</v>
       </c>
-      <c r="BL11">
-        <v>1000</v>
-      </c>
-      <c r="BM11">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BN11">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="BO11">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="BP11">
-        <v>25</v>
+        <v>16.5</v>
       </c>
       <c r="BQ11">
-        <v>7</v>
+        <v>3.9</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS11">
-        <v>8</v>
+        <v>4.5</v>
       </c>
       <c r="BT11">
-        <v>5.9</v>
+        <v>11</v>
       </c>
       <c r="BU11">
+        <v>3.45</v>
+      </c>
+      <c r="BV11">
+        <v>1000</v>
+      </c>
+      <c r="BW11">
+        <v>4.8</v>
+      </c>
+      <c r="BX11">
+        <v>1000</v>
+      </c>
+      <c r="BY11">
+        <v>4.8</v>
+      </c>
+      <c r="BZ11">
+        <v>42</v>
+      </c>
+      <c r="CA11">
         <v>4.5</v>
       </c>
-      <c r="BV11">
-        <v>23</v>
-      </c>
-      <c r="BW11">
-        <v>7</v>
-      </c>
-      <c r="BX11">
-        <v>1000</v>
-      </c>
-      <c r="BY11">
-        <v>7.8</v>
-      </c>
-      <c r="BZ11">
-        <v>34</v>
-      </c>
-      <c r="CA11">
-        <v>7.6</v>
-      </c>
       <c r="CB11" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3477,235 +3468,235 @@
         <v>99</v>
       </c>
       <c r="D12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E12" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F12">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="G12">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="H12">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="I12">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="J12">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K12">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="L12">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M12">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N12">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="O12">
         <v>1.46</v>
       </c>
       <c r="P12">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="Q12">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R12">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S12">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T12">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U12">
-        <v>1.71</v>
+        <v>1.89</v>
       </c>
       <c r="V12">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="W12">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="X12">
+        <v>10.5</v>
+      </c>
+      <c r="Y12">
+        <v>12.5</v>
+      </c>
+      <c r="Z12">
+        <v>32</v>
+      </c>
+      <c r="AA12">
+        <v>110</v>
+      </c>
+      <c r="AB12">
+        <v>7.4</v>
+      </c>
+      <c r="AC12">
+        <v>7.8</v>
+      </c>
+      <c r="AD12">
+        <v>17.5</v>
+      </c>
+      <c r="AE12">
+        <v>70</v>
+      </c>
+      <c r="AF12">
+        <v>11</v>
+      </c>
+      <c r="AG12">
+        <v>11</v>
+      </c>
+      <c r="AH12">
+        <v>22</v>
+      </c>
+      <c r="AI12">
+        <v>95</v>
+      </c>
+      <c r="AJ12">
+        <v>24</v>
+      </c>
+      <c r="AK12">
+        <v>24</v>
+      </c>
+      <c r="AL12">
+        <v>50</v>
+      </c>
+      <c r="AM12">
+        <v>180</v>
+      </c>
+      <c r="AN12">
+        <v>20</v>
+      </c>
+      <c r="AO12">
+        <v>130</v>
+      </c>
+      <c r="AP12">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ12">
+        <v>11.5</v>
+      </c>
+      <c r="AR12">
+        <v>28</v>
+      </c>
+      <c r="AS12">
+        <v>38</v>
+      </c>
+      <c r="AT12">
+        <v>7</v>
+      </c>
+      <c r="AU12">
+        <v>7.4</v>
+      </c>
+      <c r="AV12">
+        <v>16.5</v>
+      </c>
+      <c r="AW12">
+        <v>60</v>
+      </c>
+      <c r="AX12">
+        <v>10</v>
+      </c>
+      <c r="AY12">
+        <v>10</v>
+      </c>
+      <c r="AZ12">
+        <v>21</v>
+      </c>
+      <c r="BA12">
+        <v>65</v>
+      </c>
+      <c r="BB12">
+        <v>22</v>
+      </c>
+      <c r="BC12">
+        <v>22</v>
+      </c>
+      <c r="BD12">
+        <v>46</v>
+      </c>
+      <c r="BE12">
+        <v>100</v>
+      </c>
+      <c r="BF12">
+        <v>19.5</v>
+      </c>
+      <c r="BG12">
+        <v>75</v>
+      </c>
+      <c r="BH12">
+        <v>2.94</v>
+      </c>
+      <c r="BI12">
+        <v>2.8</v>
+      </c>
+      <c r="BJ12">
+        <v>12.5</v>
+      </c>
+      <c r="BK12">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BL12">
+        <v>200</v>
+      </c>
+      <c r="BM12">
+        <v>16</v>
+      </c>
+      <c r="BN12">
+        <v>4.5</v>
+      </c>
+      <c r="BO12">
+        <v>4.1</v>
+      </c>
+      <c r="BP12">
+        <v>15</v>
+      </c>
+      <c r="BQ12">
+        <v>13</v>
+      </c>
+      <c r="BR12">
+        <v>34</v>
+      </c>
+      <c r="BS12">
+        <v>11.5</v>
+      </c>
+      <c r="BT12">
+        <v>7.6</v>
+      </c>
+      <c r="BU12">
+        <v>7</v>
+      </c>
+      <c r="BV12">
+        <v>42</v>
+      </c>
+      <c r="BW12">
         <v>12</v>
       </c>
-      <c r="Y12">
-        <v>15.5</v>
-      </c>
-      <c r="Z12">
+      <c r="BX12">
         <v>60</v>
       </c>
-      <c r="AA12">
-        <v>900</v>
-      </c>
-      <c r="AB12">
-        <v>6.6</v>
-      </c>
-      <c r="AC12">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD12">
-        <v>55</v>
-      </c>
-      <c r="AE12">
-        <v>700</v>
-      </c>
-      <c r="AF12">
-        <v>9.6</v>
-      </c>
-      <c r="AG12">
-        <v>36</v>
-      </c>
-      <c r="AH12">
-        <v>65</v>
-      </c>
-      <c r="AI12">
-        <v>700</v>
-      </c>
-      <c r="AJ12">
+      <c r="BY12">
+        <v>13.5</v>
+      </c>
+      <c r="BZ12">
         <v>34</v>
       </c>
-      <c r="AK12">
-        <v>29</v>
-      </c>
-      <c r="AL12">
-        <v>70</v>
-      </c>
-      <c r="AM12">
-        <v>580</v>
-      </c>
-      <c r="AN12">
-        <v>23</v>
-      </c>
-      <c r="AO12">
-        <v>700</v>
-      </c>
-      <c r="AP12">
-        <v>7.4</v>
-      </c>
-      <c r="AQ12">
-        <v>13</v>
-      </c>
-      <c r="AR12">
-        <v>7.2</v>
-      </c>
-      <c r="AS12">
-        <v>8</v>
-      </c>
-      <c r="AT12">
-        <v>5.7</v>
-      </c>
-      <c r="AU12">
-        <v>7.2</v>
-      </c>
-      <c r="AV12">
-        <v>18</v>
-      </c>
-      <c r="AW12">
-        <v>7.8</v>
-      </c>
-      <c r="AX12">
-        <v>8.4</v>
-      </c>
-      <c r="AY12">
-        <v>9.4</v>
-      </c>
-      <c r="AZ12">
-        <v>13</v>
-      </c>
-      <c r="BA12">
-        <v>8</v>
-      </c>
-      <c r="BB12">
-        <v>17</v>
-      </c>
-      <c r="BC12">
-        <v>20</v>
-      </c>
-      <c r="BD12">
-        <v>7.4</v>
-      </c>
-      <c r="BE12">
-        <v>8</v>
-      </c>
-      <c r="BF12">
-        <v>6</v>
-      </c>
-      <c r="BG12">
-        <v>8</v>
-      </c>
-      <c r="BH12">
-        <v>3.3</v>
-      </c>
-      <c r="BI12">
-        <v>2.34</v>
-      </c>
-      <c r="BJ12">
-        <v>14.5</v>
-      </c>
-      <c r="BK12">
-        <v>3.75</v>
-      </c>
-      <c r="BL12">
-        <v>1000</v>
-      </c>
-      <c r="BM12">
-        <v>5</v>
-      </c>
-      <c r="BN12">
-        <v>4.8</v>
-      </c>
-      <c r="BO12">
-        <v>3.2</v>
-      </c>
-      <c r="BP12">
-        <v>16.5</v>
-      </c>
-      <c r="BQ12">
-        <v>3.9</v>
-      </c>
-      <c r="BR12">
-        <v>44</v>
-      </c>
-      <c r="BS12">
-        <v>4.5</v>
-      </c>
-      <c r="BT12">
-        <v>11</v>
-      </c>
-      <c r="BU12">
-        <v>3.45</v>
-      </c>
-      <c r="BV12">
-        <v>1000</v>
-      </c>
-      <c r="BW12">
-        <v>4.8</v>
-      </c>
-      <c r="BX12">
-        <v>1000</v>
-      </c>
-      <c r="BY12">
-        <v>4.8</v>
-      </c>
-      <c r="BZ12">
-        <v>42</v>
-      </c>
       <c r="CA12">
-        <v>4.5</v>
+        <v>11.5</v>
       </c>
       <c r="CB12" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3719,235 +3710,235 @@
         <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E13" t="s">
+        <v>138</v>
+      </c>
+      <c r="F13">
+        <v>1.57</v>
+      </c>
+      <c r="G13">
+        <v>1.66</v>
+      </c>
+      <c r="H13">
+        <v>4.8</v>
+      </c>
+      <c r="I13">
+        <v>7.2</v>
+      </c>
+      <c r="J13">
+        <v>3.95</v>
+      </c>
+      <c r="K13">
+        <v>4.8</v>
+      </c>
+      <c r="L13">
+        <v>1.01</v>
+      </c>
+      <c r="M13">
+        <v>1.04</v>
+      </c>
+      <c r="N13">
+        <v>1.98</v>
+      </c>
+      <c r="O13">
+        <v>1.18</v>
+      </c>
+      <c r="P13">
+        <v>1.98</v>
+      </c>
+      <c r="Q13">
+        <v>1.62</v>
+      </c>
+      <c r="R13">
+        <v>1.46</v>
+      </c>
+      <c r="S13">
+        <v>2</v>
+      </c>
+      <c r="T13">
+        <v>1.11</v>
+      </c>
+      <c r="U13">
+        <v>1.11</v>
+      </c>
+      <c r="V13">
+        <v>1.01</v>
+      </c>
+      <c r="W13">
+        <v>1.01</v>
+      </c>
+      <c r="X13">
+        <v>950</v>
+      </c>
+      <c r="Y13">
+        <v>950</v>
+      </c>
+      <c r="Z13">
+        <v>220</v>
+      </c>
+      <c r="AA13">
+        <v>700</v>
+      </c>
+      <c r="AB13">
+        <v>970</v>
+      </c>
+      <c r="AC13">
+        <v>42</v>
+      </c>
+      <c r="AD13">
+        <v>950</v>
+      </c>
+      <c r="AE13">
+        <v>400</v>
+      </c>
+      <c r="AF13">
+        <v>970</v>
+      </c>
+      <c r="AG13">
+        <v>970</v>
+      </c>
+      <c r="AH13">
+        <v>970</v>
+      </c>
+      <c r="AI13">
+        <v>320</v>
+      </c>
+      <c r="AJ13">
+        <v>970</v>
+      </c>
+      <c r="AK13">
+        <v>970</v>
+      </c>
+      <c r="AL13">
+        <v>500</v>
+      </c>
+      <c r="AM13">
+        <v>580</v>
+      </c>
+      <c r="AN13">
+        <v>29</v>
+      </c>
+      <c r="AO13">
         <v>140</v>
       </c>
-      <c r="F13">
-        <v>2.02</v>
-      </c>
-      <c r="G13">
-        <v>2.04</v>
-      </c>
-      <c r="H13">
-        <v>4.4</v>
-      </c>
-      <c r="I13">
-        <v>4.5</v>
-      </c>
-      <c r="J13">
-        <v>3.5</v>
-      </c>
-      <c r="K13">
-        <v>3.55</v>
-      </c>
-      <c r="L13">
-        <v>1.53</v>
-      </c>
-      <c r="M13">
-        <v>1.1</v>
-      </c>
-      <c r="N13">
-        <v>3.1</v>
-      </c>
-      <c r="O13">
-        <v>1.46</v>
-      </c>
-      <c r="P13">
-        <v>1.69</v>
-      </c>
-      <c r="Q13">
-        <v>2.4</v>
-      </c>
-      <c r="R13">
-        <v>1.25</v>
-      </c>
-      <c r="S13">
-        <v>4.7</v>
-      </c>
-      <c r="T13">
-        <v>2.06</v>
-      </c>
-      <c r="U13">
-        <v>1.89</v>
-      </c>
-      <c r="V13">
-        <v>1.28</v>
-      </c>
-      <c r="W13">
-        <v>1.96</v>
-      </c>
-      <c r="X13">
-        <v>10.5</v>
-      </c>
-      <c r="Y13">
-        <v>12.5</v>
-      </c>
-      <c r="Z13">
-        <v>30</v>
-      </c>
-      <c r="AA13">
-        <v>110</v>
-      </c>
-      <c r="AB13">
-        <v>7.4</v>
-      </c>
-      <c r="AC13">
-        <v>7.8</v>
-      </c>
-      <c r="AD13">
-        <v>17.5</v>
-      </c>
-      <c r="AE13">
-        <v>70</v>
-      </c>
-      <c r="AF13">
-        <v>11</v>
-      </c>
-      <c r="AG13">
-        <v>11</v>
-      </c>
-      <c r="AH13">
-        <v>22</v>
-      </c>
-      <c r="AI13">
-        <v>85</v>
-      </c>
-      <c r="AJ13">
-        <v>25</v>
-      </c>
-      <c r="AK13">
-        <v>24</v>
-      </c>
-      <c r="AL13">
-        <v>48</v>
-      </c>
-      <c r="AM13">
-        <v>190</v>
-      </c>
-      <c r="AN13">
-        <v>20</v>
-      </c>
-      <c r="AO13">
-        <v>120</v>
-      </c>
       <c r="AP13">
-        <v>9.800000000000001</v>
+        <v>1.93</v>
       </c>
       <c r="AQ13">
-        <v>11.5</v>
+        <v>1.91</v>
       </c>
       <c r="AR13">
-        <v>28</v>
+        <v>1.97</v>
       </c>
       <c r="AS13">
-        <v>95</v>
+        <v>2</v>
       </c>
       <c r="AT13">
-        <v>7</v>
+        <v>1.8</v>
       </c>
       <c r="AU13">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="AV13">
-        <v>16.5</v>
+        <v>1.92</v>
       </c>
       <c r="AW13">
-        <v>60</v>
+        <v>1.98</v>
       </c>
       <c r="AX13">
-        <v>10</v>
+        <v>1.85</v>
       </c>
       <c r="AY13">
-        <v>10</v>
+        <v>1.77</v>
       </c>
       <c r="AZ13">
-        <v>21</v>
+        <v>1.9</v>
       </c>
       <c r="BA13">
-        <v>70</v>
+        <v>1.98</v>
       </c>
       <c r="BB13">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="BC13">
-        <v>22</v>
+        <v>1.87</v>
       </c>
       <c r="BD13">
-        <v>44</v>
+        <v>1.94</v>
       </c>
       <c r="BE13">
-        <v>90</v>
+        <v>1.99</v>
       </c>
       <c r="BF13">
-        <v>19</v>
+        <v>1.93</v>
       </c>
       <c r="BG13">
-        <v>75</v>
+        <v>1.97</v>
       </c>
       <c r="BH13">
-        <v>2.94</v>
+        <v>1000</v>
       </c>
       <c r="BI13">
-        <v>2.8</v>
+        <v>1.04</v>
       </c>
       <c r="BJ13">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BL13">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="BM13">
-        <v>16.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN13">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BP13">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>13</v>
+        <v>1.04</v>
       </c>
       <c r="BR13">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS13">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT13">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BV13">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BW13">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX13">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY13">
-        <v>14</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB13" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3961,482 +3952,482 @@
         <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E14" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F14">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="G14">
-        <v>1.67</v>
+        <v>1.37</v>
       </c>
       <c r="H14">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I14">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="J14">
+        <v>5.6</v>
+      </c>
+      <c r="K14">
+        <v>7</v>
+      </c>
+      <c r="L14">
+        <v>1.2</v>
+      </c>
+      <c r="M14">
+        <v>1.03</v>
+      </c>
+      <c r="N14">
+        <v>6</v>
+      </c>
+      <c r="O14">
+        <v>1.15</v>
+      </c>
+      <c r="P14">
+        <v>2.74</v>
+      </c>
+      <c r="Q14">
+        <v>1.43</v>
+      </c>
+      <c r="R14">
+        <v>1.71</v>
+      </c>
+      <c r="S14">
+        <v>2.08</v>
+      </c>
+      <c r="T14">
+        <v>1.8</v>
+      </c>
+      <c r="U14">
+        <v>1.96</v>
+      </c>
+      <c r="V14">
+        <v>1.09</v>
+      </c>
+      <c r="W14">
+        <v>3.55</v>
+      </c>
+      <c r="X14">
+        <v>75</v>
+      </c>
+      <c r="Y14">
+        <v>100</v>
+      </c>
+      <c r="Z14">
+        <v>450</v>
+      </c>
+      <c r="AA14">
+        <v>390</v>
+      </c>
+      <c r="AB14">
+        <v>13</v>
+      </c>
+      <c r="AC14">
+        <v>16</v>
+      </c>
+      <c r="AD14">
+        <v>55</v>
+      </c>
+      <c r="AE14">
+        <v>170</v>
+      </c>
+      <c r="AF14">
+        <v>11</v>
+      </c>
+      <c r="AG14">
+        <v>12</v>
+      </c>
+      <c r="AH14">
+        <v>28</v>
+      </c>
+      <c r="AI14">
+        <v>320</v>
+      </c>
+      <c r="AJ14">
+        <v>12.5</v>
+      </c>
+      <c r="AK14">
+        <v>15</v>
+      </c>
+      <c r="AL14">
+        <v>34</v>
+      </c>
+      <c r="AM14">
+        <v>260</v>
+      </c>
+      <c r="AN14">
         <v>4.4</v>
       </c>
-      <c r="K14">
-        <v>4.8</v>
-      </c>
-      <c r="L14">
-        <v>1.01</v>
-      </c>
-      <c r="M14">
-        <v>1.04</v>
-      </c>
-      <c r="N14">
-        <v>5.2</v>
-      </c>
-      <c r="O14">
-        <v>1.18</v>
-      </c>
-      <c r="P14">
-        <v>2.46</v>
-      </c>
-      <c r="Q14">
-        <v>1.62</v>
-      </c>
-      <c r="R14">
-        <v>1.58</v>
-      </c>
-      <c r="S14">
-        <v>2.46</v>
-      </c>
-      <c r="T14">
-        <v>1.68</v>
-      </c>
-      <c r="U14">
-        <v>2.28</v>
-      </c>
-      <c r="V14">
-        <v>1.01</v>
-      </c>
-      <c r="W14">
-        <v>1.01</v>
-      </c>
-      <c r="X14">
-        <v>30</v>
-      </c>
-      <c r="Y14">
-        <v>55</v>
-      </c>
-      <c r="Z14">
-        <v>60</v>
-      </c>
-      <c r="AA14">
-        <v>700</v>
-      </c>
-      <c r="AB14">
+      <c r="AO14">
+        <v>170</v>
+      </c>
+      <c r="AP14">
+        <v>6.2</v>
+      </c>
+      <c r="AQ14">
+        <v>20</v>
+      </c>
+      <c r="AR14">
+        <v>7.2</v>
+      </c>
+      <c r="AS14">
+        <v>7.6</v>
+      </c>
+      <c r="AT14">
+        <v>7.6</v>
+      </c>
+      <c r="AU14">
         <v>12</v>
       </c>
-      <c r="AC14">
-        <v>13</v>
-      </c>
-      <c r="AD14">
-        <v>44</v>
-      </c>
-      <c r="AE14">
-        <v>160</v>
-      </c>
-      <c r="AF14">
-        <v>14.5</v>
-      </c>
-      <c r="AG14">
-        <v>10.5</v>
-      </c>
-      <c r="AH14">
-        <v>500</v>
-      </c>
-      <c r="AI14">
-        <v>160</v>
-      </c>
-      <c r="AJ14">
+      <c r="AV14">
+        <v>23</v>
+      </c>
+      <c r="AW14">
+        <v>7.4</v>
+      </c>
+      <c r="AX14">
+        <v>6.2</v>
+      </c>
+      <c r="AY14">
+        <v>6.4</v>
+      </c>
+      <c r="AZ14">
         <v>17</v>
       </c>
-      <c r="AK14">
-        <v>16</v>
-      </c>
-      <c r="AL14">
-        <v>500</v>
-      </c>
-      <c r="AM14">
-        <v>500</v>
-      </c>
-      <c r="AN14">
+      <c r="BA14">
+        <v>7.2</v>
+      </c>
+      <c r="BB14">
         <v>7</v>
-      </c>
-      <c r="AO14">
-        <v>70</v>
-      </c>
-      <c r="AP14">
-        <v>17.5</v>
-      </c>
-      <c r="AQ14">
-        <v>18</v>
-      </c>
-      <c r="AR14">
-        <v>29</v>
-      </c>
-      <c r="AS14">
-        <v>7.4</v>
-      </c>
-      <c r="AT14">
-        <v>8.6</v>
-      </c>
-      <c r="AU14">
-        <v>8</v>
-      </c>
-      <c r="AV14">
-        <v>15.5</v>
-      </c>
-      <c r="AW14">
-        <v>38</v>
-      </c>
-      <c r="AX14">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY14">
-        <v>7.6</v>
-      </c>
-      <c r="AZ14">
-        <v>13.5</v>
-      </c>
-      <c r="BA14">
-        <v>7</v>
-      </c>
-      <c r="BB14">
-        <v>14.5</v>
       </c>
       <c r="BC14">
         <v>11.5</v>
       </c>
       <c r="BD14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BE14">
-        <v>28</v>
+        <v>7.2</v>
       </c>
       <c r="BF14">
-        <v>5.3</v>
+        <v>3.55</v>
       </c>
       <c r="BG14">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="BH14">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BI14">
-        <v>3.4</v>
+        <v>2.64</v>
       </c>
       <c r="BJ14">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BK14">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
+        <v>4.6</v>
+      </c>
+      <c r="BN14">
+        <v>4.8</v>
+      </c>
+      <c r="BO14">
+        <v>2.4</v>
+      </c>
+      <c r="BP14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BQ14">
+        <v>3.1</v>
+      </c>
+      <c r="BR14">
+        <v>24</v>
+      </c>
+      <c r="BS14">
+        <v>4</v>
+      </c>
+      <c r="BT14">
+        <v>16.5</v>
+      </c>
+      <c r="BU14">
+        <v>3.7</v>
+      </c>
+      <c r="BV14">
+        <v>1000</v>
+      </c>
+      <c r="BW14">
+        <v>4.6</v>
+      </c>
+      <c r="BX14">
+        <v>1000</v>
+      </c>
+      <c r="BY14">
         <v>4.5</v>
       </c>
-      <c r="BN14">
-        <v>5.4</v>
-      </c>
-      <c r="BO14">
-        <v>3.55</v>
-      </c>
-      <c r="BP14">
-        <v>12.5</v>
-      </c>
-      <c r="BQ14">
-        <v>3.4</v>
-      </c>
-      <c r="BR14">
-        <v>25</v>
-      </c>
-      <c r="BS14">
-        <v>3.95</v>
-      </c>
-      <c r="BT14">
-        <v>11</v>
-      </c>
-      <c r="BU14">
-        <v>3.25</v>
-      </c>
-      <c r="BV14">
-        <v>50</v>
-      </c>
-      <c r="BW14">
-        <v>4.2</v>
-      </c>
-      <c r="BX14">
-        <v>50</v>
-      </c>
-      <c r="BY14">
-        <v>4.2</v>
-      </c>
       <c r="BZ14">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="CA14">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B15" t="s">
         <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F15">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="G15">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="H15">
-        <v>8.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="I15">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="J15">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="K15">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="L15">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="M15">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="N15">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="O15">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P15">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="Q15">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="R15">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="S15">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="T15">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="U15">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="V15">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W15">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="X15">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="Y15">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="Z15">
-        <v>450</v>
+        <v>1000</v>
       </c>
       <c r="AA15">
-        <v>390</v>
+        <v>490</v>
       </c>
       <c r="AB15">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC15">
         <v>16</v>
       </c>
       <c r="AD15">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AE15">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AF15">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG15">
         <v>11</v>
       </c>
-      <c r="AG15">
+      <c r="AH15">
+        <v>29</v>
+      </c>
+      <c r="AI15">
+        <v>130</v>
+      </c>
+      <c r="AJ15">
+        <v>10.5</v>
+      </c>
+      <c r="AK15">
         <v>12</v>
-      </c>
-      <c r="AH15">
-        <v>28</v>
-      </c>
-      <c r="AI15">
-        <v>320</v>
-      </c>
-      <c r="AJ15">
-        <v>12.5</v>
-      </c>
-      <c r="AK15">
-        <v>15</v>
       </c>
       <c r="AL15">
         <v>34</v>
       </c>
       <c r="AM15">
-        <v>260</v>
+        <v>130</v>
       </c>
       <c r="AN15">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="AO15">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AP15">
+        <v>34</v>
+      </c>
+      <c r="AQ15">
+        <v>48</v>
+      </c>
+      <c r="AR15">
+        <v>110</v>
+      </c>
+      <c r="AS15">
+        <v>100</v>
+      </c>
+      <c r="AT15">
+        <v>11.5</v>
+      </c>
+      <c r="AU15">
+        <v>15</v>
+      </c>
+      <c r="AV15">
+        <v>42</v>
+      </c>
+      <c r="AW15">
+        <v>140</v>
+      </c>
+      <c r="AX15">
+        <v>8.6</v>
+      </c>
+      <c r="AY15">
+        <v>10</v>
+      </c>
+      <c r="AZ15">
+        <v>28</v>
+      </c>
+      <c r="BA15">
+        <v>100</v>
+      </c>
+      <c r="BB15">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC15">
+        <v>11</v>
+      </c>
+      <c r="BD15">
+        <v>30</v>
+      </c>
+      <c r="BE15">
+        <v>100</v>
+      </c>
+      <c r="BF15">
+        <v>3.5</v>
+      </c>
+      <c r="BG15">
+        <v>140</v>
+      </c>
+      <c r="BH15">
+        <v>5.2</v>
+      </c>
+      <c r="BI15">
+        <v>4.5</v>
+      </c>
+      <c r="BJ15">
+        <v>12.5</v>
+      </c>
+      <c r="BK15">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BL15">
+        <v>140</v>
+      </c>
+      <c r="BM15">
+        <v>8.4</v>
+      </c>
+      <c r="BN15">
+        <v>4.1</v>
+      </c>
+      <c r="BO15">
+        <v>3.6</v>
+      </c>
+      <c r="BP15">
+        <v>7.2</v>
+      </c>
+      <c r="BQ15">
         <v>6.2</v>
-      </c>
-      <c r="AQ15">
-        <v>6.6</v>
-      </c>
-      <c r="AR15">
-        <v>7.2</v>
-      </c>
-      <c r="AS15">
-        <v>7.6</v>
-      </c>
-      <c r="AT15">
-        <v>7.6</v>
-      </c>
-      <c r="AU15">
-        <v>12</v>
-      </c>
-      <c r="AV15">
-        <v>23</v>
-      </c>
-      <c r="AW15">
-        <v>7.4</v>
-      </c>
-      <c r="AX15">
-        <v>6.2</v>
-      </c>
-      <c r="AY15">
-        <v>6.4</v>
-      </c>
-      <c r="AZ15">
-        <v>17</v>
-      </c>
-      <c r="BA15">
-        <v>7.2</v>
-      </c>
-      <c r="BB15">
-        <v>7</v>
-      </c>
-      <c r="BC15">
-        <v>11.5</v>
-      </c>
-      <c r="BD15">
-        <v>18</v>
-      </c>
-      <c r="BE15">
-        <v>7.2</v>
-      </c>
-      <c r="BF15">
-        <v>3.55</v>
-      </c>
-      <c r="BG15">
-        <v>13.5</v>
-      </c>
-      <c r="BH15">
-        <v>5.8</v>
-      </c>
-      <c r="BI15">
-        <v>2.64</v>
-      </c>
-      <c r="BJ15">
-        <v>13.5</v>
-      </c>
-      <c r="BK15">
-        <v>3.55</v>
-      </c>
-      <c r="BL15">
-        <v>1000</v>
-      </c>
-      <c r="BM15">
-        <v>4.6</v>
-      </c>
-      <c r="BN15">
-        <v>4.8</v>
-      </c>
-      <c r="BO15">
-        <v>2.4</v>
-      </c>
-      <c r="BP15">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BQ15">
-        <v>3.1</v>
       </c>
       <c r="BR15">
         <v>24</v>
       </c>
       <c r="BS15">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="BT15">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BU15">
-        <v>3.7</v>
+        <v>12</v>
       </c>
       <c r="BV15">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BW15">
-        <v>4.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX15">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BY15">
-        <v>4.5</v>
+        <v>11</v>
       </c>
       <c r="BZ15">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="CA15">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="CB15" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B16" t="s">
         <v>90</v>
@@ -4445,482 +4436,482 @@
         <v>102</v>
       </c>
       <c r="D16" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E16" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F16">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="G16">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="H16">
+        <v>7.6</v>
+      </c>
+      <c r="I16">
+        <v>990</v>
+      </c>
+      <c r="J16">
+        <v>3.05</v>
+      </c>
+      <c r="K16">
+        <v>8</v>
+      </c>
+      <c r="L16">
+        <v>1.01</v>
+      </c>
+      <c r="M16">
+        <v>1.1</v>
+      </c>
+      <c r="N16">
+        <v>2.8</v>
+      </c>
+      <c r="O16">
+        <v>1.47</v>
+      </c>
+      <c r="P16">
+        <v>1.6</v>
+      </c>
+      <c r="Q16">
+        <v>2.4</v>
+      </c>
+      <c r="R16">
+        <v>1.22</v>
+      </c>
+      <c r="S16">
+        <v>4.8</v>
+      </c>
+      <c r="T16">
+        <v>1.11</v>
+      </c>
+      <c r="U16">
+        <v>1.11</v>
+      </c>
+      <c r="V16">
+        <v>1.02</v>
+      </c>
+      <c r="W16">
+        <v>2.8</v>
+      </c>
+      <c r="X16">
+        <v>12</v>
+      </c>
+      <c r="Y16">
+        <v>26</v>
+      </c>
+      <c r="Z16">
+        <v>110</v>
+      </c>
+      <c r="AA16">
+        <v>600</v>
+      </c>
+      <c r="AB16">
+        <v>5.7</v>
+      </c>
+      <c r="AC16">
+        <v>11.5</v>
+      </c>
+      <c r="AD16">
+        <v>48</v>
+      </c>
+      <c r="AE16">
+        <v>300</v>
+      </c>
+      <c r="AF16">
+        <v>7.4</v>
+      </c>
+      <c r="AG16">
         <v>13</v>
       </c>
-      <c r="I16">
-        <v>13.5</v>
-      </c>
-      <c r="J16">
-        <v>7</v>
-      </c>
-      <c r="K16">
-        <v>7.2</v>
-      </c>
-      <c r="L16">
-        <v>1.25</v>
-      </c>
-      <c r="M16">
-        <v>1.02</v>
-      </c>
-      <c r="N16">
-        <v>7.4</v>
-      </c>
-      <c r="O16">
-        <v>1.14</v>
-      </c>
-      <c r="P16">
-        <v>3.15</v>
-      </c>
-      <c r="Q16">
-        <v>1.46</v>
-      </c>
-      <c r="R16">
-        <v>1.86</v>
-      </c>
-      <c r="S16">
-        <v>2.12</v>
-      </c>
-      <c r="T16">
-        <v>1.89</v>
-      </c>
-      <c r="U16">
-        <v>2.08</v>
-      </c>
-      <c r="V16">
-        <v>1.08</v>
-      </c>
-      <c r="W16">
-        <v>4.5</v>
-      </c>
-      <c r="X16">
-        <v>38</v>
-      </c>
-      <c r="Y16">
-        <v>55</v>
-      </c>
-      <c r="Z16">
-        <v>130</v>
-      </c>
-      <c r="AA16">
-        <v>520</v>
-      </c>
-      <c r="AB16">
-        <v>12.5</v>
-      </c>
-      <c r="AC16">
-        <v>16</v>
-      </c>
-      <c r="AD16">
+      <c r="AH16">
         <v>44</v>
       </c>
-      <c r="AE16">
-        <v>180</v>
-      </c>
-      <c r="AF16">
-        <v>9</v>
-      </c>
-      <c r="AG16">
+      <c r="AI16">
+        <v>280</v>
+      </c>
+      <c r="AJ16">
+        <v>15.5</v>
+      </c>
+      <c r="AK16">
+        <v>25</v>
+      </c>
+      <c r="AL16">
+        <v>80</v>
+      </c>
+      <c r="AM16">
+        <v>400</v>
+      </c>
+      <c r="AN16">
+        <v>14.5</v>
+      </c>
+      <c r="AO16">
+        <v>1000</v>
+      </c>
+      <c r="AP16">
+        <v>8</v>
+      </c>
+      <c r="AQ16">
+        <v>19</v>
+      </c>
+      <c r="AR16">
+        <v>6</v>
+      </c>
+      <c r="AS16">
+        <v>6.4</v>
+      </c>
+      <c r="AT16">
+        <v>5</v>
+      </c>
+      <c r="AU16">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV16">
+        <v>5.7</v>
+      </c>
+      <c r="AW16">
+        <v>6.2</v>
+      </c>
+      <c r="AX16">
+        <v>6.4</v>
+      </c>
+      <c r="AY16">
+        <v>9.6</v>
+      </c>
+      <c r="AZ16">
+        <v>5.6</v>
+      </c>
+      <c r="BA16">
+        <v>6.2</v>
+      </c>
+      <c r="BB16">
+        <v>11.5</v>
+      </c>
+      <c r="BC16">
+        <v>18.5</v>
+      </c>
+      <c r="BD16">
+        <v>6</v>
+      </c>
+      <c r="BE16">
+        <v>6.2</v>
+      </c>
+      <c r="BF16">
         <v>11</v>
       </c>
-      <c r="AH16">
-        <v>28</v>
-      </c>
-      <c r="AI16">
-        <v>130</v>
-      </c>
-      <c r="AJ16">
-        <v>10.5</v>
-      </c>
-      <c r="AK16">
-        <v>12</v>
-      </c>
-      <c r="AL16">
-        <v>32</v>
-      </c>
-      <c r="AM16">
-        <v>120</v>
-      </c>
-      <c r="AN16">
-        <v>3.65</v>
-      </c>
-      <c r="AO16">
-        <v>200</v>
-      </c>
-      <c r="AP16">
-        <v>34</v>
-      </c>
-      <c r="AQ16">
-        <v>48</v>
-      </c>
-      <c r="AR16">
-        <v>110</v>
-      </c>
-      <c r="AS16">
-        <v>70</v>
-      </c>
-      <c r="AT16">
-        <v>11.5</v>
-      </c>
-      <c r="AU16">
-        <v>15</v>
-      </c>
-      <c r="AV16">
-        <v>42</v>
-      </c>
-      <c r="AW16">
-        <v>140</v>
-      </c>
-      <c r="AX16">
-        <v>8.6</v>
-      </c>
-      <c r="AY16">
-        <v>10.5</v>
-      </c>
-      <c r="AZ16">
-        <v>27</v>
-      </c>
-      <c r="BA16">
-        <v>110</v>
-      </c>
-      <c r="BB16">
-        <v>10</v>
-      </c>
-      <c r="BC16">
-        <v>11.5</v>
-      </c>
-      <c r="BD16">
-        <v>29</v>
-      </c>
-      <c r="BE16">
-        <v>100</v>
-      </c>
-      <c r="BF16">
-        <v>3.55</v>
-      </c>
       <c r="BG16">
-        <v>130</v>
+        <v>6.4</v>
       </c>
       <c r="BH16">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BJ16">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BL16">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="BM16">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN16">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="BP16">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR16">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>16.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT16">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV16">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BX16">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="CB16" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B17" t="s">
         <v>90</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E17" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F17">
+        <v>2.66</v>
+      </c>
+      <c r="G17">
+        <v>990</v>
+      </c>
+      <c r="H17">
+        <v>1.29</v>
+      </c>
+      <c r="I17">
+        <v>2.46</v>
+      </c>
+      <c r="J17">
+        <v>4.6</v>
+      </c>
+      <c r="K17">
+        <v>11</v>
+      </c>
+      <c r="L17">
+        <v>1.01</v>
+      </c>
+      <c r="M17">
+        <v>1.01</v>
+      </c>
+      <c r="N17">
+        <v>1.93</v>
+      </c>
+      <c r="O17">
+        <v>1.06</v>
+      </c>
+      <c r="P17">
+        <v>1.93</v>
+      </c>
+      <c r="Q17">
+        <v>1.06</v>
+      </c>
+      <c r="R17">
+        <v>1.93</v>
+      </c>
+      <c r="S17">
+        <v>1.06</v>
+      </c>
+      <c r="T17">
+        <v>1.11</v>
+      </c>
+      <c r="U17">
+        <v>1.11</v>
+      </c>
+      <c r="V17">
+        <v>1.95</v>
+      </c>
+      <c r="W17">
+        <v>1.22</v>
+      </c>
+      <c r="X17">
+        <v>950</v>
+      </c>
+      <c r="Y17">
+        <v>950</v>
+      </c>
+      <c r="Z17">
+        <v>500</v>
+      </c>
+      <c r="AA17">
+        <v>900</v>
+      </c>
+      <c r="AB17">
+        <v>950</v>
+      </c>
+      <c r="AC17">
+        <v>970</v>
+      </c>
+      <c r="AD17">
+        <v>970</v>
+      </c>
+      <c r="AE17">
+        <v>970</v>
+      </c>
+      <c r="AF17">
+        <v>500</v>
+      </c>
+      <c r="AG17">
+        <v>950</v>
+      </c>
+      <c r="AH17">
+        <v>970</v>
+      </c>
+      <c r="AI17">
+        <v>500</v>
+      </c>
+      <c r="AJ17">
+        <v>500</v>
+      </c>
+      <c r="AK17">
+        <v>500</v>
+      </c>
+      <c r="AL17">
+        <v>500</v>
+      </c>
+      <c r="AM17">
+        <v>580</v>
+      </c>
+      <c r="AN17">
+        <v>970</v>
+      </c>
+      <c r="AO17">
+        <v>29</v>
+      </c>
+      <c r="AP17">
+        <v>1.47</v>
+      </c>
+      <c r="AQ17">
+        <v>1.45</v>
+      </c>
+      <c r="AR17">
         <v>1.48</v>
       </c>
-      <c r="G17">
+      <c r="AS17">
+        <v>1.44</v>
+      </c>
+      <c r="AT17">
+        <v>1.46</v>
+      </c>
+      <c r="AU17">
+        <v>1.43</v>
+      </c>
+      <c r="AV17">
+        <v>1.4</v>
+      </c>
+      <c r="AW17">
+        <v>1.45</v>
+      </c>
+      <c r="AX17">
+        <v>1.46</v>
+      </c>
+      <c r="AY17">
+        <v>1.42</v>
+      </c>
+      <c r="AZ17">
+        <v>1.41</v>
+      </c>
+      <c r="BA17">
+        <v>1.42</v>
+      </c>
+      <c r="BB17">
+        <v>1.48</v>
+      </c>
+      <c r="BC17">
+        <v>1.46</v>
+      </c>
+      <c r="BD17">
+        <v>1.45</v>
+      </c>
+      <c r="BE17">
+        <v>1.48</v>
+      </c>
+      <c r="BF17">
         <v>1.55</v>
       </c>
-      <c r="H17">
-        <v>9.4</v>
-      </c>
-      <c r="I17">
-        <v>11.5</v>
-      </c>
-      <c r="J17">
-        <v>3.85</v>
-      </c>
-      <c r="K17">
-        <v>4.4</v>
-      </c>
-      <c r="L17">
-        <v>1.51</v>
-      </c>
-      <c r="M17">
-        <v>1.1</v>
-      </c>
-      <c r="N17">
-        <v>2.8</v>
-      </c>
-      <c r="O17">
-        <v>1.47</v>
-      </c>
-      <c r="P17">
-        <v>1.6</v>
-      </c>
-      <c r="Q17">
-        <v>2.4</v>
-      </c>
-      <c r="R17">
-        <v>1.22</v>
-      </c>
-      <c r="S17">
-        <v>4.8</v>
-      </c>
-      <c r="T17">
-        <v>2.54</v>
-      </c>
-      <c r="U17">
-        <v>1.56</v>
-      </c>
-      <c r="V17">
-        <v>1.09</v>
-      </c>
-      <c r="W17">
-        <v>2.8</v>
-      </c>
-      <c r="X17">
-        <v>12</v>
-      </c>
-      <c r="Y17">
-        <v>26</v>
-      </c>
-      <c r="Z17">
-        <v>110</v>
-      </c>
-      <c r="AA17">
-        <v>600</v>
-      </c>
-      <c r="AB17">
-        <v>5.7</v>
-      </c>
-      <c r="AC17">
-        <v>11.5</v>
-      </c>
-      <c r="AD17">
-        <v>48</v>
-      </c>
-      <c r="AE17">
-        <v>300</v>
-      </c>
-      <c r="AF17">
-        <v>7.4</v>
-      </c>
-      <c r="AG17">
-        <v>13</v>
-      </c>
-      <c r="AH17">
-        <v>44</v>
-      </c>
-      <c r="AI17">
-        <v>280</v>
-      </c>
-      <c r="AJ17">
-        <v>15.5</v>
-      </c>
-      <c r="AK17">
-        <v>25</v>
-      </c>
-      <c r="AL17">
-        <v>80</v>
-      </c>
-      <c r="AM17">
-        <v>400</v>
-      </c>
-      <c r="AN17">
-        <v>14.5</v>
-      </c>
-      <c r="AO17">
-        <v>1000</v>
-      </c>
-      <c r="AP17">
-        <v>8</v>
-      </c>
-      <c r="AQ17">
-        <v>19</v>
-      </c>
-      <c r="AR17">
-        <v>6</v>
-      </c>
-      <c r="AS17">
-        <v>6.4</v>
-      </c>
-      <c r="AT17">
-        <v>5</v>
-      </c>
-      <c r="AU17">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV17">
-        <v>5.7</v>
-      </c>
-      <c r="AW17">
-        <v>6.2</v>
-      </c>
-      <c r="AX17">
-        <v>6.4</v>
-      </c>
-      <c r="AY17">
-        <v>9.6</v>
-      </c>
-      <c r="AZ17">
-        <v>5.6</v>
-      </c>
-      <c r="BA17">
-        <v>6.2</v>
-      </c>
-      <c r="BB17">
-        <v>11.5</v>
-      </c>
-      <c r="BC17">
-        <v>18.5</v>
-      </c>
-      <c r="BD17">
-        <v>6</v>
-      </c>
-      <c r="BE17">
-        <v>6.2</v>
-      </c>
-      <c r="BF17">
-        <v>11</v>
-      </c>
       <c r="BG17">
-        <v>6.4</v>
+        <v>1.35</v>
       </c>
       <c r="BH17">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="BI17">
-        <v>2.44</v>
+        <v>1.04</v>
       </c>
       <c r="BJ17">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BK17">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BN17">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BO17">
-        <v>2.96</v>
+        <v>1.04</v>
       </c>
       <c r="BP17">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BR17">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS17">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT17">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BU17">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV17">
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BZ17">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="CA17">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B18" t="s">
         <v>90</v>
@@ -4929,235 +4920,235 @@
         <v>103</v>
       </c>
       <c r="D18" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E18" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F18">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="G18">
-        <v>4.3</v>
+        <v>2.28</v>
       </c>
       <c r="H18">
-        <v>1.73</v>
+        <v>3.45</v>
       </c>
       <c r="I18">
-        <v>1.91</v>
+        <v>38</v>
       </c>
       <c r="J18">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="K18">
-        <v>5.7</v>
+        <v>3.7</v>
       </c>
       <c r="L18">
+        <v>1.01</v>
+      </c>
+      <c r="M18">
+        <v>1.08</v>
+      </c>
+      <c r="N18">
+        <v>1.28</v>
+      </c>
+      <c r="O18">
+        <v>1.13</v>
+      </c>
+      <c r="P18">
+        <v>1.28</v>
+      </c>
+      <c r="Q18">
+        <v>1.5</v>
+      </c>
+      <c r="R18">
+        <v>1.18</v>
+      </c>
+      <c r="S18">
+        <v>1.5</v>
+      </c>
+      <c r="T18">
+        <v>1.11</v>
+      </c>
+      <c r="U18">
+        <v>1.11</v>
+      </c>
+      <c r="V18">
+        <v>1.17</v>
+      </c>
+      <c r="W18">
+        <v>1.78</v>
+      </c>
+      <c r="X18">
+        <v>950</v>
+      </c>
+      <c r="Y18">
+        <v>950</v>
+      </c>
+      <c r="Z18">
+        <v>500</v>
+      </c>
+      <c r="AA18">
+        <v>500</v>
+      </c>
+      <c r="AB18">
+        <v>950</v>
+      </c>
+      <c r="AC18">
+        <v>500</v>
+      </c>
+      <c r="AD18">
+        <v>950</v>
+      </c>
+      <c r="AE18">
+        <v>500</v>
+      </c>
+      <c r="AF18">
+        <v>500</v>
+      </c>
+      <c r="AG18">
+        <v>950</v>
+      </c>
+      <c r="AH18">
+        <v>950</v>
+      </c>
+      <c r="AI18">
+        <v>500</v>
+      </c>
+      <c r="AJ18">
+        <v>900</v>
+      </c>
+      <c r="AK18">
+        <v>500</v>
+      </c>
+      <c r="AL18">
+        <v>500</v>
+      </c>
+      <c r="AM18">
+        <v>500</v>
+      </c>
+      <c r="AN18">
+        <v>500</v>
+      </c>
+      <c r="AO18">
+        <v>500</v>
+      </c>
+      <c r="AP18">
+        <v>1.17</v>
+      </c>
+      <c r="AQ18">
+        <v>1.17</v>
+      </c>
+      <c r="AR18">
+        <v>1.16</v>
+      </c>
+      <c r="AS18">
+        <v>1.16</v>
+      </c>
+      <c r="AT18">
+        <v>1.14</v>
+      </c>
+      <c r="AU18">
+        <v>1.14</v>
+      </c>
+      <c r="AV18">
         <v>1.15</v>
       </c>
-      <c r="M18">
-        <v>1.01</v>
-      </c>
-      <c r="N18">
-        <v>10.5</v>
-      </c>
-      <c r="O18">
-        <v>1.07</v>
-      </c>
-      <c r="P18">
-        <v>4</v>
-      </c>
-      <c r="Q18">
-        <v>1.23</v>
-      </c>
-      <c r="R18">
-        <v>2.24</v>
-      </c>
-      <c r="S18">
-        <v>1.64</v>
-      </c>
-      <c r="T18">
-        <v>1.31</v>
-      </c>
-      <c r="U18">
-        <v>3.1</v>
-      </c>
-      <c r="V18">
-        <v>2.1</v>
-      </c>
-      <c r="W18">
-        <v>1.3</v>
-      </c>
-      <c r="X18">
-        <v>160</v>
-      </c>
-      <c r="Y18">
-        <v>30</v>
-      </c>
-      <c r="Z18">
-        <v>26</v>
-      </c>
-      <c r="AA18">
-        <v>29</v>
-      </c>
-      <c r="AB18">
-        <v>46</v>
-      </c>
-      <c r="AC18">
-        <v>18</v>
-      </c>
-      <c r="AD18">
-        <v>15</v>
-      </c>
-      <c r="AE18">
-        <v>19</v>
-      </c>
-      <c r="AF18">
-        <v>120</v>
-      </c>
-      <c r="AG18">
-        <v>23</v>
-      </c>
-      <c r="AH18">
-        <v>17.5</v>
-      </c>
-      <c r="AI18">
-        <v>23</v>
-      </c>
-      <c r="AJ18">
-        <v>500</v>
-      </c>
-      <c r="AK18">
-        <v>42</v>
-      </c>
-      <c r="AL18">
-        <v>36</v>
-      </c>
-      <c r="AM18">
-        <v>42</v>
-      </c>
-      <c r="AN18">
-        <v>17.5</v>
-      </c>
-      <c r="AO18">
-        <v>5</v>
-      </c>
-      <c r="AP18">
-        <v>5.3</v>
-      </c>
-      <c r="AQ18">
-        <v>21</v>
-      </c>
-      <c r="AR18">
-        <v>18.5</v>
-      </c>
-      <c r="AS18">
-        <v>21</v>
-      </c>
-      <c r="AT18">
-        <v>5.1</v>
-      </c>
-      <c r="AU18">
-        <v>12</v>
-      </c>
-      <c r="AV18">
-        <v>10</v>
-      </c>
       <c r="AW18">
-        <v>14</v>
+        <v>1.16</v>
       </c>
       <c r="AX18">
-        <v>5.2</v>
+        <v>1.17</v>
       </c>
       <c r="AY18">
-        <v>16.5</v>
+        <v>1.13</v>
       </c>
       <c r="AZ18">
-        <v>12.5</v>
+        <v>1.17</v>
       </c>
       <c r="BA18">
-        <v>16.5</v>
+        <v>1.17</v>
       </c>
       <c r="BB18">
-        <v>5.4</v>
+        <v>1.16</v>
       </c>
       <c r="BC18">
-        <v>5.1</v>
+        <v>1.15</v>
       </c>
       <c r="BD18">
-        <v>5</v>
+        <v>1.16</v>
       </c>
       <c r="BE18">
-        <v>5.3</v>
+        <v>1.17</v>
       </c>
       <c r="BF18">
-        <v>12.5</v>
+        <v>1.55</v>
       </c>
       <c r="BG18">
-        <v>3.85</v>
+        <v>1.17</v>
       </c>
       <c r="BH18">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BI18">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BJ18">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK18">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BL18">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BM18">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BN18">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BO18">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="BP18">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR18">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS18">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT18">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU18">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="BV18">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BW18">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="BX18">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BY18">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BZ18">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA18">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB18" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5168,55 +5159,55 @@
         <v>90</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E19" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F19">
-        <v>2.2</v>
+        <v>3.05</v>
       </c>
       <c r="G19">
-        <v>2.28</v>
+        <v>110</v>
       </c>
       <c r="H19">
-        <v>3.4</v>
+        <v>1.59</v>
       </c>
       <c r="I19">
-        <v>990</v>
+        <v>2.44</v>
       </c>
       <c r="J19">
-        <v>2.1</v>
+        <v>2.84</v>
       </c>
       <c r="K19">
-        <v>3.95</v>
+        <v>8.6</v>
       </c>
       <c r="L19">
         <v>1.01</v>
       </c>
       <c r="M19">
+        <v>1.07</v>
+      </c>
+      <c r="N19">
+        <v>1.3</v>
+      </c>
+      <c r="O19">
         <v>1.08</v>
       </c>
-      <c r="N19">
-        <v>1.27</v>
-      </c>
-      <c r="O19">
-        <v>1.13</v>
-      </c>
       <c r="P19">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q19">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="R19">
         <v>1.18</v>
       </c>
       <c r="S19">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="T19">
         <v>1.11</v>
@@ -5225,28 +5216,28 @@
         <v>1.11</v>
       </c>
       <c r="V19">
+        <v>1.69</v>
+      </c>
+      <c r="W19">
         <v>1.17</v>
-      </c>
-      <c r="W19">
-        <v>1.78</v>
       </c>
       <c r="X19">
         <v>950</v>
       </c>
       <c r="Y19">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z19">
         <v>500</v>
       </c>
       <c r="AA19">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB19">
         <v>950</v>
       </c>
       <c r="AC19">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AD19">
         <v>950</v>
@@ -5267,7 +5258,7 @@
         <v>500</v>
       </c>
       <c r="AJ19">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK19">
         <v>500</v>
@@ -5285,58 +5276,58 @@
         <v>500</v>
       </c>
       <c r="AP19">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AQ19">
-        <v>1.17</v>
+        <v>3.85</v>
       </c>
       <c r="AR19">
-        <v>1.16</v>
+        <v>5.1</v>
       </c>
       <c r="AS19">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="AT19">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AU19">
-        <v>1.14</v>
+        <v>5.1</v>
       </c>
       <c r="AV19">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AW19">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="AX19">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AY19">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AZ19">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="BA19">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="BB19">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="BC19">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="BD19">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="BE19">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="BF19">
         <v>1.55</v>
       </c>
       <c r="BG19">
-        <v>1.17</v>
+        <v>5.5</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5399,7 +5390,7 @@
         <v>1.04</v>
       </c>
       <c r="CB19" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5410,28 +5401,28 @@
         <v>90</v>
       </c>
       <c r="C20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E20" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F20">
-        <v>2.86</v>
+        <v>1.07</v>
       </c>
       <c r="G20">
         <v>990</v>
       </c>
       <c r="H20">
-        <v>1.58</v>
+        <v>1.07</v>
       </c>
       <c r="I20">
-        <v>2.44</v>
+        <v>990</v>
       </c>
       <c r="J20">
-        <v>2.84</v>
+        <v>1.09</v>
       </c>
       <c r="K20">
         <v>950</v>
@@ -5440,25 +5431,25 @@
         <v>1.01</v>
       </c>
       <c r="M20">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N20">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="O20">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="P20">
         <v>1.25</v>
       </c>
       <c r="Q20">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="R20">
         <v>1.18</v>
       </c>
       <c r="S20">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="T20">
         <v>1.11</v>
@@ -5467,34 +5458,34 @@
         <v>1.11</v>
       </c>
       <c r="V20">
-        <v>1.69</v>
+        <v>1.02</v>
       </c>
       <c r="W20">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="X20">
         <v>1000</v>
       </c>
       <c r="Y20">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z20">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AA20">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB20">
         <v>1000</v>
       </c>
       <c r="AC20">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD20">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE20">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AF20">
         <v>1000</v>
@@ -5506,7 +5497,7 @@
         <v>1000</v>
       </c>
       <c r="AI20">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ20">
         <v>1000</v>
@@ -5524,61 +5515,61 @@
         <v>1000</v>
       </c>
       <c r="AO20">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AP20">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AR20">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AS20">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AT20">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AU20">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AV20">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AW20">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AX20">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AY20">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BA20">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BB20">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BC20">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BD20">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BE20">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BF20">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="BG20">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5641,12 +5632,12 @@
         <v>1.04</v>
       </c>
       <c r="CB20" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B21" t="s">
         <v>90</v>
@@ -5655,172 +5646,172 @@
         <v>104</v>
       </c>
       <c r="D21" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E21" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F21">
-        <v>1.04</v>
+        <v>1.98</v>
       </c>
       <c r="G21">
-        <v>990</v>
+        <v>2.12</v>
       </c>
       <c r="H21">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="I21">
-        <v>990</v>
+        <v>4.2</v>
       </c>
       <c r="J21">
-        <v>1.06</v>
+        <v>3.85</v>
       </c>
       <c r="K21">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L21">
         <v>1.01</v>
       </c>
       <c r="M21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N21">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="O21">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="P21">
-        <v>1.25</v>
+        <v>2.42</v>
       </c>
       <c r="Q21">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="R21">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="S21">
-        <v>1.4</v>
+        <v>2.34</v>
       </c>
       <c r="T21">
-        <v>1.11</v>
+        <v>1.49</v>
       </c>
       <c r="U21">
         <v>1.11</v>
       </c>
       <c r="V21">
-        <v>1.02</v>
+        <v>1.31</v>
       </c>
       <c r="W21">
-        <v>1.02</v>
+        <v>1.89</v>
       </c>
       <c r="X21">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y21">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z21">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA21">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB21">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC21">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD21">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE21">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF21">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG21">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH21">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI21">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ21">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK21">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL21">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AM21">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN21">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO21">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP21">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AQ21">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AR21">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AS21">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AT21">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU21">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AV21">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AW21">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AX21">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY21">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ21">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA21">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BB21">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BC21">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BD21">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BE21">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BF21">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG21">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BH21">
         <v>1000</v>
@@ -5883,7 +5874,7 @@
         <v>1.04</v>
       </c>
       <c r="CB21" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -5897,477 +5888,235 @@
         <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E22" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F22">
-        <v>1.98</v>
+        <v>3.75</v>
       </c>
       <c r="G22">
-        <v>2.12</v>
+        <v>4.1</v>
       </c>
       <c r="H22">
+        <v>2.2</v>
+      </c>
+      <c r="I22">
+        <v>2.38</v>
+      </c>
+      <c r="J22">
+        <v>3.1</v>
+      </c>
+      <c r="K22">
         <v>3.4</v>
       </c>
-      <c r="I22">
-        <v>4.2</v>
-      </c>
-      <c r="J22">
-        <v>3.85</v>
-      </c>
-      <c r="K22">
-        <v>4.5</v>
-      </c>
       <c r="L22">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="M22">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N22">
-        <v>5.2</v>
+        <v>2.9</v>
       </c>
       <c r="O22">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="P22">
-        <v>2.42</v>
+        <v>1.64</v>
       </c>
       <c r="Q22">
-        <v>1.54</v>
+        <v>2.2</v>
       </c>
       <c r="R22">
-        <v>1.57</v>
+        <v>1.24</v>
       </c>
       <c r="S22">
-        <v>2.34</v>
+        <v>4.4</v>
       </c>
       <c r="T22">
-        <v>1.54</v>
+        <v>1.84</v>
       </c>
       <c r="U22">
-        <v>2.44</v>
+        <v>1.89</v>
       </c>
       <c r="V22">
-        <v>1.31</v>
+        <v>1.73</v>
       </c>
       <c r="W22">
-        <v>1.89</v>
+        <v>1.32</v>
       </c>
       <c r="X22">
-        <v>27</v>
+        <v>10.5</v>
       </c>
       <c r="Y22">
-        <v>22</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z22">
+        <v>13.5</v>
+      </c>
+      <c r="AA22">
+        <v>38</v>
+      </c>
+      <c r="AB22">
+        <v>13.5</v>
+      </c>
+      <c r="AC22">
+        <v>7.6</v>
+      </c>
+      <c r="AD22">
+        <v>13.5</v>
+      </c>
+      <c r="AE22">
+        <v>34</v>
+      </c>
+      <c r="AF22">
         <v>32</v>
       </c>
-      <c r="AA22">
-        <v>70</v>
-      </c>
-      <c r="AB22">
-        <v>15</v>
-      </c>
-      <c r="AC22">
-        <v>11</v>
-      </c>
-      <c r="AD22">
-        <v>17.5</v>
-      </c>
-      <c r="AE22">
+      <c r="AG22">
+        <v>19</v>
+      </c>
+      <c r="AH22">
+        <v>24</v>
+      </c>
+      <c r="AI22">
+        <v>60</v>
+      </c>
+      <c r="AJ22">
+        <v>100</v>
+      </c>
+      <c r="AK22">
+        <v>65</v>
+      </c>
+      <c r="AL22">
+        <v>85</v>
+      </c>
+      <c r="AM22">
+        <v>170</v>
+      </c>
+      <c r="AN22">
+        <v>85</v>
+      </c>
+      <c r="AO22">
+        <v>32</v>
+      </c>
+      <c r="AP22">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ22">
+        <v>6.2</v>
+      </c>
+      <c r="AR22">
+        <v>12</v>
+      </c>
+      <c r="AS22">
+        <v>26</v>
+      </c>
+      <c r="AT22">
+        <v>10</v>
+      </c>
+      <c r="AU22">
+        <v>5.8</v>
+      </c>
+      <c r="AV22">
+        <v>10</v>
+      </c>
+      <c r="AW22">
+        <v>5.3</v>
+      </c>
+      <c r="AX22">
+        <v>19.5</v>
+      </c>
+      <c r="AY22">
+        <v>12.5</v>
+      </c>
+      <c r="AZ22">
+        <v>18</v>
+      </c>
+      <c r="BA22">
+        <v>5.7</v>
+      </c>
+      <c r="BB22">
+        <v>5.9</v>
+      </c>
+      <c r="BC22">
+        <v>5.7</v>
+      </c>
+      <c r="BD22">
+        <v>5.8</v>
+      </c>
+      <c r="BE22">
+        <v>6</v>
+      </c>
+      <c r="BF22">
+        <v>5.8</v>
+      </c>
+      <c r="BG22">
+        <v>19.5</v>
+      </c>
+      <c r="BH22">
+        <v>3.25</v>
+      </c>
+      <c r="BI22">
+        <v>2.46</v>
+      </c>
+      <c r="BJ22">
+        <v>12</v>
+      </c>
+      <c r="BK22">
+        <v>4</v>
+      </c>
+      <c r="BL22">
+        <v>1000</v>
+      </c>
+      <c r="BM22">
+        <v>5.9</v>
+      </c>
+      <c r="BN22">
+        <v>7.8</v>
+      </c>
+      <c r="BO22">
+        <v>5.4</v>
+      </c>
+      <c r="BP22">
         <v>40</v>
-      </c>
-      <c r="AF22">
-        <v>16.5</v>
-      </c>
-      <c r="AG22">
-        <v>12</v>
-      </c>
-      <c r="AH22">
-        <v>17</v>
-      </c>
-      <c r="AI22">
-        <v>40</v>
-      </c>
-      <c r="AJ22">
-        <v>26</v>
-      </c>
-      <c r="AK22">
-        <v>19.5</v>
-      </c>
-      <c r="AL22">
-        <v>29</v>
-      </c>
-      <c r="AM22">
-        <v>65</v>
-      </c>
-      <c r="AN22">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AO22">
-        <v>29</v>
-      </c>
-      <c r="AP22">
-        <v>20</v>
-      </c>
-      <c r="AQ22">
-        <v>16.5</v>
-      </c>
-      <c r="AR22">
-        <v>7.2</v>
-      </c>
-      <c r="AS22">
-        <v>7.4</v>
-      </c>
-      <c r="AT22">
-        <v>10.5</v>
-      </c>
-      <c r="AU22">
-        <v>8.4</v>
-      </c>
-      <c r="AV22">
-        <v>13</v>
-      </c>
-      <c r="AW22">
-        <v>7.4</v>
-      </c>
-      <c r="AX22">
-        <v>12.5</v>
-      </c>
-      <c r="AY22">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ22">
-        <v>12</v>
-      </c>
-      <c r="BA22">
-        <v>7.4</v>
-      </c>
-      <c r="BB22">
-        <v>6.8</v>
-      </c>
-      <c r="BC22">
-        <v>15</v>
-      </c>
-      <c r="BD22">
-        <v>21</v>
-      </c>
-      <c r="BE22">
-        <v>8</v>
-      </c>
-      <c r="BF22">
-        <v>7.6</v>
-      </c>
-      <c r="BG22">
-        <v>19</v>
-      </c>
-      <c r="BH22">
-        <v>4.7</v>
-      </c>
-      <c r="BI22">
-        <v>3.55</v>
-      </c>
-      <c r="BJ22">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK22">
-        <v>4.4</v>
-      </c>
-      <c r="BL22">
-        <v>1000</v>
-      </c>
-      <c r="BM22">
-        <v>7.6</v>
-      </c>
-      <c r="BN22">
-        <v>5.5</v>
-      </c>
-      <c r="BO22">
-        <v>4.1</v>
-      </c>
-      <c r="BP22">
-        <v>14</v>
       </c>
       <c r="BQ22">
         <v>5.3</v>
       </c>
       <c r="BR22">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="BS22">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="BT22">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="BU22">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BV22">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="BW22">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="BX22">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="BY22">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="BZ22">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="CA22">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="CB22" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="23" spans="1:80">
-      <c r="A23" t="s">
-        <v>81</v>
-      </c>
-      <c r="B23" t="s">
-        <v>90</v>
-      </c>
-      <c r="C23" t="s">
-        <v>106</v>
-      </c>
-      <c r="D23" t="s">
-        <v>128</v>
-      </c>
-      <c r="E23" t="s">
-        <v>150</v>
-      </c>
-      <c r="F23">
-        <v>3.75</v>
-      </c>
-      <c r="G23">
-        <v>4.1</v>
-      </c>
-      <c r="H23">
-        <v>2.2</v>
-      </c>
-      <c r="I23">
-        <v>2.38</v>
-      </c>
-      <c r="J23">
-        <v>3.1</v>
-      </c>
-      <c r="K23">
-        <v>3.4</v>
-      </c>
-      <c r="L23">
-        <v>1.5</v>
-      </c>
-      <c r="M23">
-        <v>1.1</v>
-      </c>
-      <c r="N23">
-        <v>2.9</v>
-      </c>
-      <c r="O23">
-        <v>1.44</v>
-      </c>
-      <c r="P23">
-        <v>1.64</v>
-      </c>
-      <c r="Q23">
-        <v>2.3</v>
-      </c>
-      <c r="R23">
-        <v>1.24</v>
-      </c>
-      <c r="S23">
-        <v>4.4</v>
-      </c>
-      <c r="T23">
-        <v>1.84</v>
-      </c>
-      <c r="U23">
-        <v>1.89</v>
-      </c>
-      <c r="V23">
-        <v>1.73</v>
-      </c>
-      <c r="W23">
-        <v>1.32</v>
-      </c>
-      <c r="X23">
-        <v>10.5</v>
-      </c>
-      <c r="Y23">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Z23">
-        <v>13.5</v>
-      </c>
-      <c r="AA23">
-        <v>38</v>
-      </c>
-      <c r="AB23">
-        <v>13.5</v>
-      </c>
-      <c r="AC23">
-        <v>7.6</v>
-      </c>
-      <c r="AD23">
-        <v>13.5</v>
-      </c>
-      <c r="AE23">
-        <v>34</v>
-      </c>
-      <c r="AF23">
-        <v>32</v>
-      </c>
-      <c r="AG23">
-        <v>19</v>
-      </c>
-      <c r="AH23">
-        <v>24</v>
-      </c>
-      <c r="AI23">
-        <v>60</v>
-      </c>
-      <c r="AJ23">
-        <v>100</v>
-      </c>
-      <c r="AK23">
-        <v>65</v>
-      </c>
-      <c r="AL23">
-        <v>85</v>
-      </c>
-      <c r="AM23">
-        <v>170</v>
-      </c>
-      <c r="AN23">
-        <v>85</v>
-      </c>
-      <c r="AO23">
-        <v>32</v>
-      </c>
-      <c r="AP23">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ23">
-        <v>6.2</v>
-      </c>
-      <c r="AR23">
-        <v>12</v>
-      </c>
-      <c r="AS23">
-        <v>26</v>
-      </c>
-      <c r="AT23">
-        <v>10</v>
-      </c>
-      <c r="AU23">
-        <v>5.8</v>
-      </c>
-      <c r="AV23">
-        <v>10</v>
-      </c>
-      <c r="AW23">
-        <v>5.5</v>
-      </c>
-      <c r="AX23">
-        <v>19.5</v>
-      </c>
-      <c r="AY23">
-        <v>12.5</v>
-      </c>
-      <c r="AZ23">
-        <v>18</v>
-      </c>
-      <c r="BA23">
-        <v>5.9</v>
-      </c>
-      <c r="BB23">
-        <v>5.9</v>
-      </c>
-      <c r="BC23">
-        <v>5.7</v>
-      </c>
-      <c r="BD23">
-        <v>5.8</v>
-      </c>
-      <c r="BE23">
-        <v>6</v>
-      </c>
-      <c r="BF23">
-        <v>5.8</v>
-      </c>
-      <c r="BG23">
-        <v>19.5</v>
-      </c>
-      <c r="BH23">
-        <v>3.25</v>
-      </c>
-      <c r="BI23">
-        <v>2.46</v>
-      </c>
-      <c r="BJ23">
-        <v>12</v>
-      </c>
-      <c r="BK23">
-        <v>4</v>
-      </c>
-      <c r="BL23">
-        <v>1000</v>
-      </c>
-      <c r="BM23">
-        <v>5.9</v>
-      </c>
-      <c r="BN23">
-        <v>7.8</v>
-      </c>
-      <c r="BO23">
-        <v>5.4</v>
-      </c>
-      <c r="BP23">
-        <v>40</v>
-      </c>
-      <c r="BQ23">
-        <v>5.3</v>
-      </c>
-      <c r="BR23">
-        <v>60</v>
-      </c>
-      <c r="BS23">
-        <v>5.5</v>
-      </c>
-      <c r="BT23">
-        <v>5.6</v>
-      </c>
-      <c r="BU23">
-        <v>3.95</v>
-      </c>
-      <c r="BV23">
-        <v>21</v>
-      </c>
-      <c r="BW23">
-        <v>4.7</v>
-      </c>
-      <c r="BX23">
-        <v>44</v>
-      </c>
-      <c r="BY23">
-        <v>5.4</v>
-      </c>
-      <c r="BZ23">
-        <v>44</v>
-      </c>
-      <c r="CA23">
-        <v>5.4</v>
-      </c>
-      <c r="CB23" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="146">
   <si>
     <t>League</t>
   </si>
@@ -256,42 +256,39 @@
     <t>SnapshotTS</t>
   </si>
   <si>
+    <t>Egyptian Premier</t>
+  </si>
+  <si>
+    <t>Qatari Stars League</t>
+  </si>
+  <si>
+    <t>Saudi 1st Division</t>
+  </si>
+  <si>
+    <t>Algerian Ligue 1</t>
+  </si>
+  <si>
+    <t>Spanish La Liga</t>
+  </si>
+  <si>
+    <t>English National League</t>
+  </si>
+  <si>
+    <t>Bolivian Liga de Futbol Profesional</t>
+  </si>
+  <si>
+    <t>Icelandic 2 Deild</t>
+  </si>
+  <si>
+    <t>Ecuadorian Serie B</t>
+  </si>
+  <si>
     <t>Colombian Primera A</t>
   </si>
   <si>
-    <t>Egyptian Premier</t>
-  </si>
-  <si>
-    <t>Qatari Stars League</t>
-  </si>
-  <si>
-    <t>Saudi 1st Division</t>
-  </si>
-  <si>
-    <t>Algerian Ligue 1</t>
-  </si>
-  <si>
-    <t>Spanish La Liga</t>
-  </si>
-  <si>
-    <t>English National League</t>
-  </si>
-  <si>
-    <t>Bolivian Liga de Futbol Profesional</t>
-  </si>
-  <si>
-    <t>Icelandic 2 Deild</t>
-  </si>
-  <si>
-    <t>Ecuadorian Serie B</t>
-  </si>
-  <si>
     <t>2026-08-27</t>
   </si>
   <si>
-    <t>01:30:00</t>
-  </si>
-  <si>
     <t>14:00:00</t>
   </si>
   <si>
@@ -334,9 +331,6 @@
     <t>23:10:00</t>
   </si>
   <si>
-    <t>Atletico Nacional Medellin</t>
-  </si>
-  <si>
     <t>Modern Sport FC</t>
   </si>
   <si>
@@ -397,9 +391,6 @@
     <t>Llaneros FC</t>
   </si>
   <si>
-    <t>Deportivo Cali</t>
-  </si>
-  <si>
     <t>Ghazl El Mahallah</t>
   </si>
   <si>
@@ -460,7 +451,7 @@
     <t>Millonarios</t>
   </si>
   <si>
-    <t>2026-08-26 23:42:08</t>
+    <t>2026-08-27 01:57:44</t>
   </si>
 </sst>
 </file>
@@ -792,7 +783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB22"/>
+  <dimension ref="A1:CB21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1048,235 +1039,235 @@
         <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F2">
-        <v>1.2</v>
+        <v>2.32</v>
       </c>
       <c r="G2">
-        <v>1.22</v>
+        <v>2.42</v>
       </c>
       <c r="H2">
-        <v>28</v>
+        <v>4.8</v>
       </c>
       <c r="I2">
-        <v>34</v>
+        <v>5.4</v>
       </c>
       <c r="J2">
-        <v>7</v>
+        <v>2.6</v>
       </c>
       <c r="K2">
-        <v>7.6</v>
+        <v>2.74</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="N2">
-        <v>4.5</v>
+        <v>2.22</v>
       </c>
       <c r="O2">
-        <v>1.27</v>
+        <v>1.76</v>
       </c>
       <c r="P2">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="Q2">
-        <v>2.18</v>
+        <v>3.5</v>
       </c>
       <c r="R2">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="S2">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="T2">
-        <v>2.54</v>
+        <v>1.11</v>
       </c>
       <c r="U2">
-        <v>1.57</v>
+        <v>1.11</v>
       </c>
       <c r="V2">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="W2">
-        <v>5.5</v>
+        <v>1.71</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB2">
-        <v>4.8</v>
+        <v>14</v>
       </c>
       <c r="AC2">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD2">
-        <v>48</v>
+        <v>950</v>
       </c>
       <c r="AE2">
-        <v>370</v>
+        <v>500</v>
       </c>
       <c r="AF2">
-        <v>4.5</v>
+        <v>500</v>
       </c>
       <c r="AG2">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="AH2">
-        <v>44</v>
+        <v>950</v>
       </c>
       <c r="AI2">
-        <v>340</v>
+        <v>500</v>
       </c>
       <c r="AJ2">
-        <v>8.800000000000001</v>
+        <v>900</v>
       </c>
       <c r="AK2">
-        <v>19.5</v>
+        <v>500</v>
       </c>
       <c r="AL2">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN2">
-        <v>14</v>
+        <v>600</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP2">
-        <v>15</v>
+        <v>1.92</v>
       </c>
       <c r="AQ2">
-        <v>15.5</v>
+        <v>2.04</v>
       </c>
       <c r="AR2">
-        <v>15</v>
+        <v>2.24</v>
       </c>
       <c r="AS2">
-        <v>15</v>
+        <v>2.3</v>
       </c>
       <c r="AT2">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="AU2">
-        <v>8.800000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="AV2">
-        <v>38</v>
+        <v>14.5</v>
       </c>
       <c r="AW2">
-        <v>210</v>
+        <v>2.3</v>
       </c>
       <c r="AX2">
-        <v>4.2</v>
+        <v>2.08</v>
       </c>
       <c r="AY2">
-        <v>8.6</v>
+        <v>2.14</v>
       </c>
       <c r="AZ2">
-        <v>28</v>
+        <v>2.3</v>
       </c>
       <c r="BA2">
-        <v>180</v>
+        <v>2.3</v>
       </c>
       <c r="BB2">
-        <v>8</v>
+        <v>2.3</v>
       </c>
       <c r="BC2">
-        <v>17</v>
+        <v>2.22</v>
       </c>
       <c r="BD2">
-        <v>70</v>
+        <v>2.28</v>
       </c>
       <c r="BE2">
-        <v>70</v>
+        <v>2.3</v>
       </c>
       <c r="BF2">
-        <v>12.5</v>
+        <v>2.2</v>
       </c>
       <c r="BG2">
-        <v>29</v>
+        <v>2.24</v>
       </c>
       <c r="BH2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1290,235 +1281,235 @@
         <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F3">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="G3">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>2.36</v>
       </c>
       <c r="I3">
-        <v>5.8</v>
+        <v>2.54</v>
       </c>
       <c r="J3">
-        <v>2.44</v>
+        <v>3.85</v>
       </c>
       <c r="K3">
-        <v>2.82</v>
+        <v>4.3</v>
       </c>
       <c r="L3">
+        <v>1.3</v>
+      </c>
+      <c r="M3">
+        <v>1.04</v>
+      </c>
+      <c r="N3">
+        <v>5.4</v>
+      </c>
+      <c r="O3">
+        <v>1.2</v>
+      </c>
+      <c r="P3">
+        <v>2.5</v>
+      </c>
+      <c r="Q3">
         <v>1.6</v>
       </c>
-      <c r="M3">
-        <v>1.01</v>
-      </c>
-      <c r="N3">
-        <v>2.02</v>
-      </c>
-      <c r="O3">
-        <v>1.69</v>
-      </c>
-      <c r="P3">
-        <v>1.29</v>
-      </c>
-      <c r="Q3">
-        <v>3.3</v>
-      </c>
       <c r="R3">
-        <v>1.09</v>
+        <v>1.6</v>
       </c>
       <c r="S3">
-        <v>6.6</v>
+        <v>2.5</v>
       </c>
       <c r="T3">
-        <v>1.11</v>
+        <v>1.55</v>
       </c>
       <c r="U3">
-        <v>1.11</v>
+        <v>2.6</v>
       </c>
       <c r="V3">
-        <v>1.26</v>
+        <v>1.64</v>
       </c>
       <c r="W3">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="X3">
-        <v>7.2</v>
+        <v>25</v>
       </c>
       <c r="Y3">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="Z3">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="AA3">
-        <v>900</v>
+        <v>36</v>
       </c>
       <c r="AB3">
+        <v>18</v>
+      </c>
+      <c r="AC3">
+        <v>10</v>
+      </c>
+      <c r="AD3">
+        <v>13</v>
+      </c>
+      <c r="AE3">
+        <v>24</v>
+      </c>
+      <c r="AF3">
+        <v>24</v>
+      </c>
+      <c r="AG3">
         <v>14</v>
       </c>
-      <c r="AC3">
-        <v>8.4</v>
-      </c>
-      <c r="AD3">
-        <v>950</v>
-      </c>
-      <c r="AE3">
-        <v>500</v>
-      </c>
-      <c r="AF3">
-        <v>500</v>
-      </c>
-      <c r="AG3">
-        <v>970</v>
-      </c>
       <c r="AH3">
-        <v>950</v>
+        <v>15.5</v>
       </c>
       <c r="AI3">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AJ3">
-        <v>900</v>
+        <v>50</v>
       </c>
       <c r="AK3">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AL3">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AM3">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AN3">
-        <v>600</v>
+        <v>18</v>
       </c>
       <c r="AO3">
-        <v>600</v>
+        <v>14</v>
       </c>
       <c r="AP3">
-        <v>4.4</v>
+        <v>20</v>
       </c>
       <c r="AQ3">
-        <v>7.8</v>
+        <v>13.5</v>
       </c>
       <c r="AR3">
-        <v>2.3</v>
+        <v>17</v>
       </c>
       <c r="AS3">
-        <v>2.38</v>
+        <v>16</v>
       </c>
       <c r="AT3">
-        <v>1.85</v>
+        <v>15</v>
       </c>
       <c r="AU3">
-        <v>1.85</v>
+        <v>8.6</v>
       </c>
       <c r="AV3">
-        <v>2.3</v>
+        <v>10</v>
       </c>
       <c r="AW3">
-        <v>2.38</v>
+        <v>19.5</v>
       </c>
       <c r="AX3">
-        <v>2.14</v>
+        <v>19.5</v>
       </c>
       <c r="AY3">
         <v>11</v>
       </c>
       <c r="AZ3">
-        <v>2.38</v>
+        <v>12.5</v>
       </c>
       <c r="BA3">
-        <v>2.38</v>
+        <v>24</v>
       </c>
       <c r="BB3">
-        <v>2.38</v>
+        <v>19.5</v>
       </c>
       <c r="BC3">
-        <v>2.36</v>
+        <v>13</v>
       </c>
       <c r="BD3">
-        <v>2.36</v>
+        <v>15</v>
       </c>
       <c r="BE3">
-        <v>2.38</v>
+        <v>20</v>
       </c>
       <c r="BF3">
-        <v>2.22</v>
+        <v>14.5</v>
       </c>
       <c r="BG3">
-        <v>2.32</v>
+        <v>11.5</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI3">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK3">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BM3">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO3">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ3">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS3">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU3">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BW3">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY3">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="CA3">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="CB3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1532,468 +1523,468 @@
         <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F4">
-        <v>2.64</v>
+        <v>1.54</v>
       </c>
       <c r="G4">
-        <v>3.3</v>
+        <v>1.65</v>
       </c>
       <c r="H4">
-        <v>2.3</v>
+        <v>6.6</v>
       </c>
       <c r="I4">
-        <v>2.62</v>
+        <v>8</v>
       </c>
       <c r="J4">
+        <v>4</v>
+      </c>
+      <c r="K4">
+        <v>4.7</v>
+      </c>
+      <c r="L4">
+        <v>1.39</v>
+      </c>
+      <c r="M4">
+        <v>1.06</v>
+      </c>
+      <c r="N4">
         <v>3.85</v>
       </c>
-      <c r="K4">
-        <v>4.4</v>
-      </c>
-      <c r="L4">
-        <v>1.01</v>
-      </c>
-      <c r="M4">
-        <v>1.03</v>
-      </c>
-      <c r="N4">
-        <v>4.7</v>
-      </c>
       <c r="O4">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="P4">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="Q4">
-        <v>1.45</v>
+        <v>1.89</v>
       </c>
       <c r="R4">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="S4">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="T4">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="U4">
-        <v>1.11</v>
+        <v>1.85</v>
       </c>
       <c r="V4">
-        <v>1.61</v>
+        <v>1.14</v>
       </c>
       <c r="W4">
-        <v>1.48</v>
+        <v>2.52</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y4">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="Z4">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="AA4">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="AB4">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC4">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="AD4">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AE4">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AF4">
-        <v>38</v>
+        <v>10.5</v>
       </c>
       <c r="AG4">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AH4">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="AI4">
-        <v>80</v>
+        <v>700</v>
       </c>
       <c r="AJ4">
-        <v>900</v>
+        <v>17</v>
       </c>
       <c r="AK4">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="AL4">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="AM4">
-        <v>580</v>
+        <v>700</v>
       </c>
       <c r="AN4">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AO4">
-        <v>970</v>
+        <v>700</v>
       </c>
       <c r="AP4">
-        <v>1.69</v>
+        <v>13</v>
       </c>
       <c r="AQ4">
-        <v>1.6</v>
+        <v>18.5</v>
       </c>
       <c r="AR4">
-        <v>1.62</v>
+        <v>7.6</v>
       </c>
       <c r="AS4">
-        <v>1.66</v>
+        <v>7.2</v>
       </c>
       <c r="AT4">
-        <v>1.64</v>
+        <v>6.8</v>
       </c>
       <c r="AU4">
-        <v>1.45</v>
+        <v>8.4</v>
       </c>
       <c r="AV4">
-        <v>1.58</v>
+        <v>12.5</v>
       </c>
       <c r="AW4">
-        <v>1.68</v>
+        <v>7</v>
       </c>
       <c r="AX4">
-        <v>1.62</v>
+        <v>7.8</v>
       </c>
       <c r="AY4">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="AZ4">
-        <v>1.58</v>
+        <v>20</v>
       </c>
       <c r="BA4">
-        <v>1.66</v>
+        <v>7</v>
       </c>
       <c r="BB4">
-        <v>1.67</v>
+        <v>12.5</v>
       </c>
       <c r="BC4">
-        <v>1.66</v>
+        <v>14.5</v>
       </c>
       <c r="BD4">
-        <v>1.66</v>
+        <v>14.5</v>
       </c>
       <c r="BE4">
-        <v>1.68</v>
+        <v>7</v>
       </c>
       <c r="BF4">
-        <v>1.69</v>
+        <v>8</v>
       </c>
       <c r="BG4">
-        <v>1.64</v>
+        <v>7</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI4">
-        <v>1.04</v>
+        <v>2.9</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK4">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO4">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ4">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS4">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU4">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA4">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B5" t="s">
         <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F5">
-        <v>1.47</v>
+        <v>4.7</v>
       </c>
       <c r="G5">
-        <v>1.74</v>
+        <v>5.6</v>
       </c>
       <c r="H5">
+        <v>1.77</v>
+      </c>
+      <c r="I5">
+        <v>1.91</v>
+      </c>
+      <c r="J5">
+        <v>3.55</v>
+      </c>
+      <c r="K5">
+        <v>4.1</v>
+      </c>
+      <c r="L5">
+        <v>1.41</v>
+      </c>
+      <c r="M5">
+        <v>1.07</v>
+      </c>
+      <c r="N5">
+        <v>3.7</v>
+      </c>
+      <c r="O5">
+        <v>1.3</v>
+      </c>
+      <c r="P5">
+        <v>1.94</v>
+      </c>
+      <c r="Q5">
+        <v>1.92</v>
+      </c>
+      <c r="R5">
+        <v>1.35</v>
+      </c>
+      <c r="S5">
+        <v>3.35</v>
+      </c>
+      <c r="T5">
+        <v>1.83</v>
+      </c>
+      <c r="U5">
+        <v>1.97</v>
+      </c>
+      <c r="V5">
+        <v>2.1</v>
+      </c>
+      <c r="W5">
+        <v>1.21</v>
+      </c>
+      <c r="X5">
+        <v>17</v>
+      </c>
+      <c r="Y5">
+        <v>10</v>
+      </c>
+      <c r="Z5">
+        <v>13.5</v>
+      </c>
+      <c r="AA5">
+        <v>24</v>
+      </c>
+      <c r="AB5">
+        <v>21</v>
+      </c>
+      <c r="AC5">
+        <v>9</v>
+      </c>
+      <c r="AD5">
+        <v>12.5</v>
+      </c>
+      <c r="AE5">
+        <v>24</v>
+      </c>
+      <c r="AF5">
+        <v>48</v>
+      </c>
+      <c r="AG5">
+        <v>24</v>
+      </c>
+      <c r="AH5">
+        <v>24</v>
+      </c>
+      <c r="AI5">
+        <v>46</v>
+      </c>
+      <c r="AJ5">
+        <v>470</v>
+      </c>
+      <c r="AK5">
+        <v>85</v>
+      </c>
+      <c r="AL5">
+        <v>90</v>
+      </c>
+      <c r="AM5">
+        <v>200</v>
+      </c>
+      <c r="AN5">
+        <v>100</v>
+      </c>
+      <c r="AO5">
+        <v>15.5</v>
+      </c>
+      <c r="AP5">
+        <v>12</v>
+      </c>
+      <c r="AQ5">
+        <v>7.4</v>
+      </c>
+      <c r="AR5">
+        <v>9.4</v>
+      </c>
+      <c r="AS5">
+        <v>4</v>
+      </c>
+      <c r="AT5">
+        <v>3.9</v>
+      </c>
+      <c r="AU5">
+        <v>7.4</v>
+      </c>
+      <c r="AV5">
+        <v>8.6</v>
+      </c>
+      <c r="AW5">
+        <v>4</v>
+      </c>
+      <c r="AX5">
+        <v>4.3</v>
+      </c>
+      <c r="AY5">
+        <v>4</v>
+      </c>
+      <c r="AZ5">
+        <v>4</v>
+      </c>
+      <c r="BA5">
+        <v>4.3</v>
+      </c>
+      <c r="BB5">
+        <v>4.6</v>
+      </c>
+      <c r="BC5">
+        <v>4.5</v>
+      </c>
+      <c r="BD5">
+        <v>4.5</v>
+      </c>
+      <c r="BE5">
+        <v>4.6</v>
+      </c>
+      <c r="BF5">
+        <v>4.5</v>
+      </c>
+      <c r="BG5">
+        <v>3.8</v>
+      </c>
+      <c r="BH5">
+        <v>3.5</v>
+      </c>
+      <c r="BI5">
+        <v>3</v>
+      </c>
+      <c r="BJ5">
+        <v>12.5</v>
+      </c>
+      <c r="BK5">
+        <v>3.9</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>5.5</v>
+      </c>
+      <c r="BN5">
+        <v>10</v>
+      </c>
+      <c r="BO5">
         <v>3.6</v>
       </c>
-      <c r="I5">
-        <v>990</v>
-      </c>
-      <c r="J5">
-        <v>3.6</v>
-      </c>
-      <c r="K5">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="L5">
-        <v>1.01</v>
-      </c>
-      <c r="M5">
-        <v>1.06</v>
-      </c>
-      <c r="N5">
-        <v>2.04</v>
-      </c>
-      <c r="O5">
-        <v>1.06</v>
-      </c>
-      <c r="P5">
-        <v>2.04</v>
-      </c>
-      <c r="Q5">
-        <v>1.85</v>
-      </c>
-      <c r="R5">
-        <v>1.26</v>
-      </c>
-      <c r="S5">
-        <v>2.56</v>
-      </c>
-      <c r="T5">
-        <v>1.11</v>
-      </c>
-      <c r="U5">
-        <v>1.11</v>
-      </c>
-      <c r="V5">
-        <v>1.14</v>
-      </c>
-      <c r="W5">
-        <v>2.34</v>
-      </c>
-      <c r="X5">
-        <v>970</v>
-      </c>
-      <c r="Y5">
-        <v>950</v>
-      </c>
-      <c r="Z5">
-        <v>160</v>
-      </c>
-      <c r="AA5">
-        <v>1000</v>
-      </c>
-      <c r="AB5">
-        <v>970</v>
-      </c>
-      <c r="AC5">
-        <v>970</v>
-      </c>
-      <c r="AD5">
-        <v>950</v>
-      </c>
-      <c r="AE5">
-        <v>1000</v>
-      </c>
-      <c r="AF5">
-        <v>970</v>
-      </c>
-      <c r="AG5">
-        <v>970</v>
-      </c>
-      <c r="AH5">
-        <v>1000</v>
-      </c>
-      <c r="AI5">
-        <v>260</v>
-      </c>
-      <c r="AJ5">
-        <v>970</v>
-      </c>
-      <c r="AK5">
+      <c r="BP5">
+        <v>55</v>
+      </c>
+      <c r="BQ5">
+        <v>5.2</v>
+      </c>
+      <c r="BR5">
         <v>65</v>
       </c>
-      <c r="AL5">
-        <v>100</v>
-      </c>
-      <c r="AM5">
-        <v>1000</v>
-      </c>
-      <c r="AN5">
-        <v>29</v>
-      </c>
-      <c r="AO5">
-        <v>1000</v>
-      </c>
-      <c r="AP5">
-        <v>1.45</v>
-      </c>
-      <c r="AQ5">
-        <v>1.5</v>
-      </c>
-      <c r="AR5">
-        <v>1.51</v>
-      </c>
-      <c r="AS5">
-        <v>1.52</v>
-      </c>
-      <c r="AT5">
-        <v>1.45</v>
-      </c>
-      <c r="AU5">
-        <v>1.4</v>
-      </c>
-      <c r="AV5">
-        <v>1.49</v>
-      </c>
-      <c r="AW5">
-        <v>4.2</v>
-      </c>
-      <c r="AX5">
-        <v>1.4</v>
-      </c>
-      <c r="AY5">
-        <v>1.41</v>
-      </c>
-      <c r="AZ5">
-        <v>1.52</v>
-      </c>
-      <c r="BA5">
-        <v>4.2</v>
-      </c>
-      <c r="BB5">
-        <v>1.51</v>
-      </c>
-      <c r="BC5">
-        <v>1.46</v>
-      </c>
-      <c r="BD5">
-        <v>1.5</v>
-      </c>
-      <c r="BE5">
-        <v>1.52</v>
-      </c>
-      <c r="BF5">
-        <v>1.44</v>
-      </c>
-      <c r="BG5">
-        <v>4.2</v>
-      </c>
-      <c r="BH5">
-        <v>1000</v>
-      </c>
-      <c r="BI5">
-        <v>1.04</v>
-      </c>
-      <c r="BJ5">
-        <v>1000</v>
-      </c>
-      <c r="BK5">
-        <v>1.04</v>
-      </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
-        <v>1.04</v>
-      </c>
-      <c r="BN5">
-        <v>1000</v>
-      </c>
-      <c r="BO5">
-        <v>1.04</v>
-      </c>
-      <c r="BP5">
-        <v>1000</v>
-      </c>
-      <c r="BQ5">
-        <v>1.04</v>
-      </c>
-      <c r="BR5">
-        <v>1000</v>
-      </c>
       <c r="BS5">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BU5">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BW5">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY5">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BZ5">
         <v>0</v>
@@ -2002,12 +1993,12 @@
         <v>0</v>
       </c>
       <c r="CB5" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B6" t="s">
         <v>90</v>
@@ -2016,240 +2007,240 @@
         <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F6">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="G6">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>1.76</v>
+        <v>1.97</v>
       </c>
       <c r="I6">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="J6">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="K6">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L6">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="M6">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="N6">
-        <v>3.55</v>
+        <v>5.4</v>
       </c>
       <c r="O6">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="P6">
-        <v>1.94</v>
+        <v>2.52</v>
       </c>
       <c r="Q6">
-        <v>1.96</v>
+        <v>1.59</v>
       </c>
       <c r="R6">
+        <v>1.6</v>
+      </c>
+      <c r="S6">
+        <v>2.48</v>
+      </c>
+      <c r="T6">
+        <v>1.57</v>
+      </c>
+      <c r="U6">
+        <v>2.48</v>
+      </c>
+      <c r="V6">
+        <v>1.98</v>
+      </c>
+      <c r="W6">
         <v>1.33</v>
       </c>
-      <c r="S6">
-        <v>3.45</v>
-      </c>
-      <c r="T6">
-        <v>1.83</v>
-      </c>
-      <c r="U6">
-        <v>1.97</v>
-      </c>
-      <c r="V6">
-        <v>2.08</v>
-      </c>
-      <c r="W6">
-        <v>1.21</v>
-      </c>
       <c r="X6">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="Y6">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z6">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA6">
         <v>24</v>
       </c>
       <c r="AB6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD6">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE6">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AF6">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="AG6">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AH6">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="AI6">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="AJ6">
-        <v>470</v>
+        <v>75</v>
       </c>
       <c r="AK6">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="AL6">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="AM6">
         <v>200</v>
       </c>
       <c r="AN6">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="AO6">
-        <v>15.5</v>
+        <v>9.6</v>
       </c>
       <c r="AP6">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AQ6">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="AR6">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="AS6">
-        <v>3.9</v>
+        <v>20</v>
       </c>
       <c r="AT6">
-        <v>3.8</v>
+        <v>18.5</v>
       </c>
       <c r="AU6">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AV6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AW6">
-        <v>3.9</v>
+        <v>16</v>
       </c>
       <c r="AX6">
-        <v>4.2</v>
+        <v>27</v>
       </c>
       <c r="AY6">
-        <v>3.95</v>
+        <v>15</v>
       </c>
       <c r="AZ6">
-        <v>3.95</v>
+        <v>13</v>
       </c>
       <c r="BA6">
-        <v>4.2</v>
+        <v>22</v>
       </c>
       <c r="BB6">
-        <v>4.5</v>
+        <v>46</v>
       </c>
       <c r="BC6">
-        <v>4.4</v>
+        <v>29</v>
       </c>
       <c r="BD6">
-        <v>4.4</v>
+        <v>29</v>
       </c>
       <c r="BE6">
-        <v>4.5</v>
+        <v>46</v>
       </c>
       <c r="BF6">
-        <v>4.5</v>
+        <v>19</v>
       </c>
       <c r="BG6">
-        <v>3.8</v>
+        <v>8</v>
       </c>
       <c r="BH6">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="BI6">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ6">
-        <v>12.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK6">
-        <v>3.9</v>
+        <v>6.8</v>
       </c>
       <c r="BL6">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM6">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BN6">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="BO6">
-        <v>3.6</v>
+        <v>5.7</v>
       </c>
       <c r="BP6">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="BQ6">
         <v>5.2</v>
       </c>
       <c r="BR6">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="BS6">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BT6">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BU6">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="BV6">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BW6">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BX6">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="BY6">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BZ6">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="CA6">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="CB6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B7" t="s">
         <v>90</v>
@@ -2258,172 +2249,172 @@
         <v>95</v>
       </c>
       <c r="D7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F7">
-        <v>3.6</v>
+        <v>1.29</v>
       </c>
       <c r="G7">
-        <v>4.2</v>
+        <v>1.32</v>
       </c>
       <c r="H7">
-        <v>1.94</v>
+        <v>14.5</v>
       </c>
       <c r="I7">
+        <v>17.5</v>
+      </c>
+      <c r="J7">
+        <v>5.7</v>
+      </c>
+      <c r="K7">
+        <v>6.2</v>
+      </c>
+      <c r="L7">
+        <v>1.4</v>
+      </c>
+      <c r="M7">
+        <v>1.07</v>
+      </c>
+      <c r="N7">
+        <v>4</v>
+      </c>
+      <c r="O7">
+        <v>1.31</v>
+      </c>
+      <c r="P7">
         <v>2.04</v>
       </c>
-      <c r="J7">
-        <v>3.85</v>
-      </c>
-      <c r="K7">
-        <v>4.3</v>
-      </c>
-      <c r="L7">
-        <v>1.01</v>
-      </c>
-      <c r="M7">
-        <v>1.04</v>
-      </c>
-      <c r="N7">
-        <v>5</v>
-      </c>
-      <c r="O7">
-        <v>1.16</v>
-      </c>
-      <c r="P7">
-        <v>2.28</v>
-      </c>
       <c r="Q7">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="R7">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="S7">
-        <v>1.16</v>
+        <v>3.45</v>
       </c>
       <c r="T7">
-        <v>1.56</v>
+        <v>2.56</v>
       </c>
       <c r="U7">
-        <v>1.11</v>
+        <v>1.53</v>
       </c>
       <c r="V7">
-        <v>1.96</v>
+        <v>1.06</v>
       </c>
       <c r="W7">
-        <v>1.32</v>
+        <v>4.1</v>
       </c>
       <c r="X7">
-        <v>950</v>
+        <v>16</v>
       </c>
       <c r="Y7">
-        <v>970</v>
+        <v>85</v>
       </c>
       <c r="Z7">
-        <v>970</v>
+        <v>200</v>
       </c>
       <c r="AA7">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
-        <v>950</v>
+        <v>6.8</v>
       </c>
       <c r="AC7">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD7">
-        <v>970</v>
+        <v>160</v>
       </c>
       <c r="AE7">
-        <v>970</v>
+        <v>490</v>
       </c>
       <c r="AF7">
-        <v>90</v>
+        <v>6.6</v>
       </c>
       <c r="AG7">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AH7">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AI7">
-        <v>75</v>
+        <v>360</v>
       </c>
       <c r="AJ7">
-        <v>900</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AK7">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="AL7">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="AM7">
-        <v>580</v>
+        <v>430</v>
       </c>
       <c r="AN7">
-        <v>970</v>
+        <v>6.6</v>
       </c>
       <c r="AO7">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP7">
-        <v>1.87</v>
+        <v>10.5</v>
       </c>
       <c r="AQ7">
-        <v>1.81</v>
+        <v>14.5</v>
       </c>
       <c r="AR7">
-        <v>1.83</v>
+        <v>11.5</v>
       </c>
       <c r="AS7">
-        <v>1.82</v>
+        <v>12.5</v>
       </c>
       <c r="AT7">
-        <v>16</v>
+        <v>5.9</v>
       </c>
       <c r="AU7">
-        <v>1.7</v>
+        <v>11.5</v>
       </c>
       <c r="AV7">
-        <v>8.800000000000001</v>
+        <v>24</v>
       </c>
       <c r="AW7">
         <v>12</v>
       </c>
       <c r="AX7">
-        <v>17.5</v>
+        <v>5.8</v>
       </c>
       <c r="AY7">
-        <v>1.78</v>
+        <v>10</v>
       </c>
       <c r="AZ7">
+        <v>10</v>
+      </c>
+      <c r="BA7">
         <v>12</v>
       </c>
-      <c r="BA7">
-        <v>1.82</v>
-      </c>
       <c r="BB7">
-        <v>23</v>
+        <v>8.4</v>
       </c>
       <c r="BC7">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="BD7">
-        <v>1.9</v>
+        <v>10.5</v>
       </c>
       <c r="BE7">
-        <v>1.92</v>
+        <v>12</v>
       </c>
       <c r="BF7">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="BG7">
-        <v>2.48</v>
+        <v>13.5</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2486,186 +2477,186 @@
         <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B8" t="s">
         <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F8">
-        <v>1.19</v>
+        <v>4.2</v>
       </c>
       <c r="G8">
+        <v>4.6</v>
+      </c>
+      <c r="H8">
+        <v>2.24</v>
+      </c>
+      <c r="I8">
+        <v>2.32</v>
+      </c>
+      <c r="J8">
+        <v>2.88</v>
+      </c>
+      <c r="K8">
+        <v>3.05</v>
+      </c>
+      <c r="L8">
+        <v>1.64</v>
+      </c>
+      <c r="M8">
+        <v>1.15</v>
+      </c>
+      <c r="N8">
+        <v>2.52</v>
+      </c>
+      <c r="O8">
+        <v>1.62</v>
+      </c>
+      <c r="P8">
         <v>1.47</v>
       </c>
-      <c r="H8">
-        <v>7.8</v>
-      </c>
-      <c r="I8">
-        <v>990</v>
-      </c>
-      <c r="J8">
-        <v>3.35</v>
-      </c>
-      <c r="K8">
-        <v>9.6</v>
-      </c>
-      <c r="L8">
-        <v>1.34</v>
-      </c>
-      <c r="M8">
-        <v>1.07</v>
-      </c>
-      <c r="N8">
-        <v>1.25</v>
-      </c>
-      <c r="O8">
-        <v>1.32</v>
-      </c>
-      <c r="P8">
-        <v>1.24</v>
-      </c>
       <c r="Q8">
-        <v>1.31</v>
+        <v>3</v>
       </c>
       <c r="R8">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="S8">
-        <v>1.31</v>
+        <v>6.2</v>
       </c>
       <c r="T8">
-        <v>1.11</v>
+        <v>2.24</v>
       </c>
       <c r="U8">
-        <v>1.11</v>
+        <v>1.7</v>
       </c>
       <c r="V8">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="W8">
-        <v>3.2</v>
+        <v>1.28</v>
       </c>
       <c r="X8">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="Y8">
-        <v>950</v>
+        <v>6.8</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB8">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AC8">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="AD8">
-        <v>950</v>
+        <v>12.5</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF8">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AG8">
-        <v>970</v>
+        <v>40</v>
       </c>
       <c r="AH8">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AJ8">
-        <v>970</v>
+        <v>900</v>
       </c>
       <c r="AK8">
-        <v>970</v>
+        <v>440</v>
       </c>
       <c r="AL8">
-        <v>330</v>
+        <v>500</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN8">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP8">
-        <v>1.92</v>
+        <v>5.9</v>
       </c>
       <c r="AQ8">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="AR8">
-        <v>2.14</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS8">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="AT8">
-        <v>1.77</v>
+        <v>9.4</v>
       </c>
       <c r="AU8">
-        <v>1.92</v>
+        <v>6.2</v>
       </c>
       <c r="AV8">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="AW8">
-        <v>2.14</v>
+        <v>5.9</v>
       </c>
       <c r="AX8">
-        <v>1.79</v>
+        <v>5.8</v>
       </c>
       <c r="AY8">
-        <v>1.92</v>
+        <v>16.5</v>
       </c>
       <c r="AZ8">
-        <v>2.1</v>
+        <v>21</v>
       </c>
       <c r="BA8">
-        <v>2.14</v>
+        <v>6.4</v>
       </c>
       <c r="BB8">
-        <v>1.88</v>
+        <v>6.6</v>
       </c>
       <c r="BC8">
-        <v>2</v>
+        <v>6.4</v>
       </c>
       <c r="BD8">
-        <v>2.1</v>
+        <v>6.4</v>
       </c>
       <c r="BE8">
-        <v>2.14</v>
+        <v>6.6</v>
       </c>
       <c r="BF8">
-        <v>1.87</v>
+        <v>6.4</v>
       </c>
       <c r="BG8">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2728,12 +2719,12 @@
         <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B9" t="s">
         <v>90</v>
@@ -2742,52 +2733,52 @@
         <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E9" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F9">
-        <v>2.42</v>
+        <v>2.68</v>
       </c>
       <c r="G9">
-        <v>13.5</v>
+        <v>3.15</v>
       </c>
       <c r="H9">
-        <v>1.74</v>
+        <v>2.48</v>
       </c>
       <c r="I9">
-        <v>5.3</v>
+        <v>2.84</v>
       </c>
       <c r="J9">
-        <v>2.52</v>
+        <v>3.25</v>
       </c>
       <c r="K9">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="L9">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M9">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N9">
-        <v>1.25</v>
+        <v>3.35</v>
       </c>
       <c r="O9">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="P9">
-        <v>1.43</v>
+        <v>1.79</v>
       </c>
       <c r="Q9">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="R9">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="S9">
-        <v>1.05</v>
+        <v>3.75</v>
       </c>
       <c r="T9">
         <v>1.11</v>
@@ -2796,19 +2787,19 @@
         <v>1.11</v>
       </c>
       <c r="V9">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="W9">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="X9">
         <v>970</v>
       </c>
       <c r="Y9">
-        <v>7.4</v>
+        <v>970</v>
       </c>
       <c r="Z9">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AA9">
         <v>900</v>
@@ -2817,7 +2808,7 @@
         <v>970</v>
       </c>
       <c r="AC9">
-        <v>8.6</v>
+        <v>42</v>
       </c>
       <c r="AD9">
         <v>970</v>
@@ -2826,16 +2817,16 @@
         <v>500</v>
       </c>
       <c r="AF9">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AG9">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AH9">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AI9">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="AJ9">
         <v>900</v>
@@ -2847,67 +2838,67 @@
         <v>500</v>
       </c>
       <c r="AM9">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN9">
         <v>500</v>
       </c>
       <c r="AO9">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AP9">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AQ9">
+        <v>1.68</v>
+      </c>
+      <c r="AR9">
+        <v>1.79</v>
+      </c>
+      <c r="AS9">
+        <v>1.8</v>
+      </c>
+      <c r="AT9">
+        <v>1.67</v>
+      </c>
+      <c r="AU9">
+        <v>1.62</v>
+      </c>
+      <c r="AV9">
+        <v>1.72</v>
+      </c>
+      <c r="AW9">
+        <v>1.79</v>
+      </c>
+      <c r="AX9">
         <v>1.75</v>
       </c>
-      <c r="AR9">
-        <v>2.1</v>
-      </c>
-      <c r="AS9">
-        <v>2.24</v>
-      </c>
-      <c r="AT9">
-        <v>2.24</v>
-      </c>
-      <c r="AU9">
-        <v>1.81</v>
-      </c>
-      <c r="AV9">
-        <v>1.95</v>
-      </c>
-      <c r="AW9">
-        <v>2.22</v>
-      </c>
-      <c r="AX9">
-        <v>2.22</v>
-      </c>
       <c r="AY9">
-        <v>2.16</v>
+        <v>1.7</v>
       </c>
       <c r="AZ9">
-        <v>2.22</v>
+        <v>1.77</v>
       </c>
       <c r="BA9">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="BB9">
-        <v>2.28</v>
+        <v>1.8</v>
       </c>
       <c r="BC9">
-        <v>2.28</v>
+        <v>1.79</v>
       </c>
       <c r="BD9">
-        <v>2.28</v>
+        <v>1.8</v>
       </c>
       <c r="BE9">
-        <v>2.28</v>
+        <v>1.82</v>
       </c>
       <c r="BF9">
-        <v>2.26</v>
+        <v>1.78</v>
       </c>
       <c r="BG9">
-        <v>2.18</v>
+        <v>6.2</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -2970,7 +2961,7 @@
         <v>1.04</v>
       </c>
       <c r="CB9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2984,235 +2975,235 @@
         <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E10" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F10">
-        <v>2.4</v>
+        <v>1.77</v>
       </c>
       <c r="G10">
+        <v>1.86</v>
+      </c>
+      <c r="H10">
+        <v>5.7</v>
+      </c>
+      <c r="I10">
+        <v>6.6</v>
+      </c>
+      <c r="J10">
         <v>3.3</v>
       </c>
-      <c r="H10">
-        <v>2.26</v>
-      </c>
-      <c r="I10">
-        <v>3.25</v>
-      </c>
-      <c r="J10">
-        <v>3.1</v>
-      </c>
       <c r="K10">
-        <v>6.6</v>
+        <v>3.7</v>
       </c>
       <c r="L10">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="M10">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="N10">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="O10">
-        <v>1.27</v>
+        <v>1.49</v>
       </c>
       <c r="P10">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="Q10">
-        <v>2</v>
+        <v>2.52</v>
       </c>
       <c r="R10">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S10">
-        <v>2.64</v>
+        <v>5</v>
       </c>
       <c r="T10">
-        <v>1.11</v>
+        <v>2.22</v>
       </c>
       <c r="U10">
-        <v>1.11</v>
+        <v>1.71</v>
       </c>
       <c r="V10">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="W10">
-        <v>1.44</v>
+        <v>2.16</v>
       </c>
       <c r="X10">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="Y10">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="Z10">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA10">
         <v>900</v>
       </c>
       <c r="AB10">
-        <v>970</v>
+        <v>6.4</v>
       </c>
       <c r="AC10">
-        <v>42</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD10">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AE10">
-        <v>110</v>
+        <v>700</v>
       </c>
       <c r="AF10">
-        <v>38</v>
+        <v>9.6</v>
       </c>
       <c r="AG10">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AH10">
-        <v>970</v>
+        <v>65</v>
       </c>
       <c r="AI10">
-        <v>290</v>
+        <v>700</v>
       </c>
       <c r="AJ10">
-        <v>900</v>
+        <v>34</v>
       </c>
       <c r="AK10">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AL10">
-        <v>290</v>
+        <v>70</v>
       </c>
       <c r="AM10">
         <v>580</v>
       </c>
       <c r="AN10">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="AO10">
-        <v>60</v>
+        <v>700</v>
       </c>
       <c r="AP10">
-        <v>1.68</v>
+        <v>7.4</v>
       </c>
       <c r="AQ10">
-        <v>1.68</v>
+        <v>13</v>
       </c>
       <c r="AR10">
-        <v>1.79</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS10">
-        <v>1.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT10">
-        <v>1.67</v>
+        <v>5.7</v>
       </c>
       <c r="AU10">
-        <v>1.62</v>
+        <v>7.2</v>
       </c>
       <c r="AV10">
-        <v>1.72</v>
+        <v>18</v>
       </c>
       <c r="AW10">
-        <v>1.79</v>
+        <v>9</v>
       </c>
       <c r="AX10">
-        <v>1.75</v>
+        <v>8.4</v>
       </c>
       <c r="AY10">
-        <v>1.7</v>
+        <v>9.4</v>
       </c>
       <c r="AZ10">
-        <v>1.77</v>
+        <v>13</v>
       </c>
       <c r="BA10">
-        <v>1.8</v>
+        <v>9</v>
       </c>
       <c r="BB10">
-        <v>1.8</v>
+        <v>17</v>
       </c>
       <c r="BC10">
-        <v>1.79</v>
+        <v>20</v>
       </c>
       <c r="BD10">
-        <v>1.8</v>
+        <v>8.4</v>
       </c>
       <c r="BE10">
-        <v>1.82</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF10">
-        <v>1.78</v>
+        <v>16</v>
       </c>
       <c r="BG10">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="BI10">
-        <v>1.04</v>
+        <v>2.34</v>
       </c>
       <c r="BJ10">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK10">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO10">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BQ10">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS10">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU10">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA10">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="CB10" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3226,235 +3217,235 @@
         <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F11">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="G11">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="H11">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="I11">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="J11">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K11">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="L11">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M11">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N11">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="O11">
         <v>1.46</v>
       </c>
       <c r="P11">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="Q11">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R11">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="S11">
         <v>4.8</v>
       </c>
       <c r="T11">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="U11">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="V11">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="W11">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="X11">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Y11">
+        <v>12.5</v>
+      </c>
+      <c r="Z11">
+        <v>32</v>
+      </c>
+      <c r="AA11">
+        <v>110</v>
+      </c>
+      <c r="AB11">
+        <v>7.4</v>
+      </c>
+      <c r="AC11">
+        <v>7.8</v>
+      </c>
+      <c r="AD11">
+        <v>17.5</v>
+      </c>
+      <c r="AE11">
+        <v>70</v>
+      </c>
+      <c r="AF11">
+        <v>11</v>
+      </c>
+      <c r="AG11">
+        <v>11</v>
+      </c>
+      <c r="AH11">
+        <v>22</v>
+      </c>
+      <c r="AI11">
+        <v>110</v>
+      </c>
+      <c r="AJ11">
+        <v>25</v>
+      </c>
+      <c r="AK11">
+        <v>24</v>
+      </c>
+      <c r="AL11">
+        <v>50</v>
+      </c>
+      <c r="AM11">
+        <v>180</v>
+      </c>
+      <c r="AN11">
+        <v>20</v>
+      </c>
+      <c r="AO11">
+        <v>490</v>
+      </c>
+      <c r="AP11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ11">
+        <v>11.5</v>
+      </c>
+      <c r="AR11">
+        <v>28</v>
+      </c>
+      <c r="AS11">
+        <v>90</v>
+      </c>
+      <c r="AT11">
+        <v>7</v>
+      </c>
+      <c r="AU11">
+        <v>7.4</v>
+      </c>
+      <c r="AV11">
+        <v>16.5</v>
+      </c>
+      <c r="AW11">
+        <v>60</v>
+      </c>
+      <c r="AX11">
+        <v>10</v>
+      </c>
+      <c r="AY11">
+        <v>10</v>
+      </c>
+      <c r="AZ11">
+        <v>20</v>
+      </c>
+      <c r="BA11">
+        <v>75</v>
+      </c>
+      <c r="BB11">
+        <v>22</v>
+      </c>
+      <c r="BC11">
+        <v>22</v>
+      </c>
+      <c r="BD11">
+        <v>46</v>
+      </c>
+      <c r="BE11">
+        <v>100</v>
+      </c>
+      <c r="BF11">
+        <v>19.5</v>
+      </c>
+      <c r="BG11">
+        <v>75</v>
+      </c>
+      <c r="BH11">
+        <v>2.94</v>
+      </c>
+      <c r="BI11">
+        <v>2.72</v>
+      </c>
+      <c r="BJ11">
+        <v>11</v>
+      </c>
+      <c r="BK11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BL11">
+        <v>210</v>
+      </c>
+      <c r="BM11">
+        <v>18.5</v>
+      </c>
+      <c r="BN11">
+        <v>4.5</v>
+      </c>
+      <c r="BO11">
+        <v>4.2</v>
+      </c>
+      <c r="BP11">
+        <v>16</v>
+      </c>
+      <c r="BQ11">
+        <v>13.5</v>
+      </c>
+      <c r="BR11">
+        <v>34</v>
+      </c>
+      <c r="BS11">
+        <v>12.5</v>
+      </c>
+      <c r="BT11">
+        <v>7.6</v>
+      </c>
+      <c r="BU11">
+        <v>6.8</v>
+      </c>
+      <c r="BV11">
+        <v>42</v>
+      </c>
+      <c r="BW11">
+        <v>13.5</v>
+      </c>
+      <c r="BX11">
+        <v>60</v>
+      </c>
+      <c r="BY11">
         <v>15.5</v>
       </c>
-      <c r="Z11">
-        <v>60</v>
-      </c>
-      <c r="AA11">
-        <v>900</v>
-      </c>
-      <c r="AB11">
-        <v>6.6</v>
-      </c>
-      <c r="AC11">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD11">
-        <v>55</v>
-      </c>
-      <c r="AE11">
-        <v>700</v>
-      </c>
-      <c r="AF11">
-        <v>9.6</v>
-      </c>
-      <c r="AG11">
-        <v>36</v>
-      </c>
-      <c r="AH11">
-        <v>65</v>
-      </c>
-      <c r="AI11">
-        <v>700</v>
-      </c>
-      <c r="AJ11">
+      <c r="BZ11">
         <v>34</v>
       </c>
-      <c r="AK11">
-        <v>29</v>
-      </c>
-      <c r="AL11">
-        <v>70</v>
-      </c>
-      <c r="AM11">
-        <v>580</v>
-      </c>
-      <c r="AN11">
-        <v>23</v>
-      </c>
-      <c r="AO11">
-        <v>700</v>
-      </c>
-      <c r="AP11">
-        <v>7.4</v>
-      </c>
-      <c r="AQ11">
-        <v>13</v>
-      </c>
-      <c r="AR11">
-        <v>7.4</v>
-      </c>
-      <c r="AS11">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT11">
-        <v>5.7</v>
-      </c>
-      <c r="AU11">
-        <v>7.2</v>
-      </c>
-      <c r="AV11">
-        <v>18</v>
-      </c>
-      <c r="AW11">
-        <v>8</v>
-      </c>
-      <c r="AX11">
-        <v>8.4</v>
-      </c>
-      <c r="AY11">
-        <v>9.4</v>
-      </c>
-      <c r="AZ11">
-        <v>13</v>
-      </c>
-      <c r="BA11">
-        <v>5.9</v>
-      </c>
-      <c r="BB11">
-        <v>17</v>
-      </c>
-      <c r="BC11">
-        <v>20</v>
-      </c>
-      <c r="BD11">
-        <v>7.6</v>
-      </c>
-      <c r="BE11">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF11">
-        <v>6</v>
-      </c>
-      <c r="BG11">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BH11">
-        <v>3.3</v>
-      </c>
-      <c r="BI11">
-        <v>2.34</v>
-      </c>
-      <c r="BJ11">
-        <v>14.5</v>
-      </c>
-      <c r="BK11">
-        <v>3.75</v>
-      </c>
-      <c r="BL11">
-        <v>1000</v>
-      </c>
-      <c r="BM11">
-        <v>5</v>
-      </c>
-      <c r="BN11">
-        <v>4.8</v>
-      </c>
-      <c r="BO11">
-        <v>3.2</v>
-      </c>
-      <c r="BP11">
-        <v>16.5</v>
-      </c>
-      <c r="BQ11">
-        <v>3.9</v>
-      </c>
-      <c r="BR11">
-        <v>44</v>
-      </c>
-      <c r="BS11">
-        <v>4.5</v>
-      </c>
-      <c r="BT11">
-        <v>11</v>
-      </c>
-      <c r="BU11">
-        <v>3.45</v>
-      </c>
-      <c r="BV11">
-        <v>1000</v>
-      </c>
-      <c r="BW11">
-        <v>4.8</v>
-      </c>
-      <c r="BX11">
-        <v>1000</v>
-      </c>
-      <c r="BY11">
-        <v>4.8</v>
-      </c>
-      <c r="BZ11">
-        <v>42</v>
-      </c>
       <c r="CA11">
-        <v>4.5</v>
+        <v>12.5</v>
       </c>
       <c r="CB11" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3468,235 +3459,235 @@
         <v>99</v>
       </c>
       <c r="D12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E12" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F12">
-        <v>2.02</v>
+        <v>1.62</v>
       </c>
       <c r="G12">
-        <v>2.04</v>
+        <v>1.66</v>
       </c>
       <c r="H12">
+        <v>5.2</v>
+      </c>
+      <c r="I12">
+        <v>5.9</v>
+      </c>
+      <c r="J12">
         <v>4.4</v>
       </c>
-      <c r="I12">
-        <v>4.5</v>
-      </c>
-      <c r="J12">
-        <v>3.5</v>
-      </c>
       <c r="K12">
-        <v>3.55</v>
+        <v>4.8</v>
       </c>
       <c r="L12">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="M12">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="N12">
-        <v>3.1</v>
+        <v>5.3</v>
       </c>
       <c r="O12">
-        <v>1.46</v>
+        <v>1.2</v>
       </c>
       <c r="P12">
-        <v>1.7</v>
+        <v>2.48</v>
       </c>
       <c r="Q12">
-        <v>2.4</v>
+        <v>1.62</v>
       </c>
       <c r="R12">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="S12">
-        <v>4.7</v>
+        <v>2.54</v>
       </c>
       <c r="T12">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="U12">
-        <v>1.89</v>
+        <v>2.28</v>
       </c>
       <c r="V12">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="W12">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="X12">
+        <v>29</v>
+      </c>
+      <c r="Y12">
+        <v>42</v>
+      </c>
+      <c r="Z12">
+        <v>60</v>
+      </c>
+      <c r="AA12">
+        <v>700</v>
+      </c>
+      <c r="AB12">
+        <v>12</v>
+      </c>
+      <c r="AC12">
+        <v>11</v>
+      </c>
+      <c r="AD12">
+        <v>44</v>
+      </c>
+      <c r="AE12">
+        <v>85</v>
+      </c>
+      <c r="AF12">
+        <v>12</v>
+      </c>
+      <c r="AG12">
         <v>10.5</v>
       </c>
-      <c r="Y12">
-        <v>12.5</v>
-      </c>
-      <c r="Z12">
-        <v>32</v>
-      </c>
-      <c r="AA12">
-        <v>110</v>
-      </c>
-      <c r="AB12">
-        <v>7.4</v>
-      </c>
-      <c r="AC12">
-        <v>7.8</v>
-      </c>
-      <c r="AD12">
+      <c r="AH12">
+        <v>23</v>
+      </c>
+      <c r="AI12">
+        <v>70</v>
+      </c>
+      <c r="AJ12">
+        <v>21</v>
+      </c>
+      <c r="AK12">
+        <v>19.5</v>
+      </c>
+      <c r="AL12">
+        <v>34</v>
+      </c>
+      <c r="AM12">
+        <v>95</v>
+      </c>
+      <c r="AN12">
+        <v>7.2</v>
+      </c>
+      <c r="AO12">
+        <v>70</v>
+      </c>
+      <c r="AP12">
         <v>17.5</v>
       </c>
-      <c r="AE12">
-        <v>70</v>
-      </c>
-      <c r="AF12">
-        <v>11</v>
-      </c>
-      <c r="AG12">
-        <v>11</v>
-      </c>
-      <c r="AH12">
-        <v>22</v>
-      </c>
-      <c r="AI12">
-        <v>95</v>
-      </c>
-      <c r="AJ12">
-        <v>24</v>
-      </c>
-      <c r="AK12">
-        <v>24</v>
-      </c>
-      <c r="AL12">
-        <v>50</v>
-      </c>
-      <c r="AM12">
-        <v>180</v>
-      </c>
-      <c r="AN12">
-        <v>20</v>
-      </c>
-      <c r="AO12">
-        <v>130</v>
-      </c>
-      <c r="AP12">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AQ12">
-        <v>11.5</v>
+        <v>5.6</v>
       </c>
       <c r="AR12">
-        <v>28</v>
+        <v>6.4</v>
       </c>
       <c r="AS12">
-        <v>38</v>
+        <v>6.8</v>
       </c>
       <c r="AT12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AU12">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV12">
-        <v>16.5</v>
+        <v>5.4</v>
       </c>
       <c r="AW12">
-        <v>60</v>
+        <v>6.6</v>
       </c>
       <c r="AX12">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ12">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="BA12">
-        <v>65</v>
+        <v>6.4</v>
       </c>
       <c r="BB12">
-        <v>22</v>
+        <v>14.5</v>
       </c>
       <c r="BC12">
-        <v>22</v>
+        <v>8.4</v>
       </c>
       <c r="BD12">
-        <v>46</v>
+        <v>14.5</v>
       </c>
       <c r="BE12">
-        <v>100</v>
+        <v>6.6</v>
       </c>
       <c r="BF12">
-        <v>19.5</v>
+        <v>6.2</v>
       </c>
       <c r="BG12">
-        <v>75</v>
+        <v>6.4</v>
       </c>
       <c r="BH12">
-        <v>2.94</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
-        <v>2.8</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BL12">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="BM12">
-        <v>16</v>
+        <v>1.04</v>
       </c>
       <c r="BN12">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BP12">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>13</v>
+        <v>1.04</v>
       </c>
       <c r="BR12">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT12">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BV12">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BX12">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3710,482 +3701,482 @@
         <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E13" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F13">
-        <v>1.57</v>
+        <v>1.31</v>
       </c>
       <c r="G13">
-        <v>1.66</v>
+        <v>1.37</v>
       </c>
       <c r="H13">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="I13">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="J13">
-        <v>3.95</v>
+        <v>5.6</v>
       </c>
       <c r="K13">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="L13">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M13">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N13">
-        <v>1.98</v>
+        <v>6.2</v>
       </c>
       <c r="O13">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="P13">
-        <v>1.98</v>
+        <v>2.88</v>
       </c>
       <c r="Q13">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="R13">
-        <v>1.46</v>
+        <v>1.75</v>
       </c>
       <c r="S13">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="T13">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="U13">
-        <v>1.11</v>
+        <v>1.97</v>
       </c>
       <c r="V13">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W13">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="X13">
-        <v>950</v>
+        <v>75</v>
       </c>
       <c r="Y13">
-        <v>950</v>
+        <v>100</v>
       </c>
       <c r="Z13">
-        <v>220</v>
+        <v>450</v>
       </c>
       <c r="AA13">
-        <v>700</v>
+        <v>370</v>
       </c>
       <c r="AB13">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AC13">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="AD13">
-        <v>950</v>
+        <v>40</v>
       </c>
       <c r="AE13">
-        <v>400</v>
+        <v>160</v>
       </c>
       <c r="AF13">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AG13">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AH13">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="AI13">
         <v>320</v>
       </c>
       <c r="AJ13">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AK13">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AL13">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AM13">
-        <v>580</v>
+        <v>260</v>
       </c>
       <c r="AN13">
-        <v>29</v>
+        <v>4.4</v>
       </c>
       <c r="AO13">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AP13">
-        <v>1.93</v>
+        <v>6.2</v>
       </c>
       <c r="AQ13">
-        <v>1.91</v>
+        <v>20</v>
       </c>
       <c r="AR13">
-        <v>1.97</v>
+        <v>7.4</v>
       </c>
       <c r="AS13">
-        <v>2</v>
+        <v>7.8</v>
       </c>
       <c r="AT13">
-        <v>1.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU13">
-        <v>5.8</v>
+        <v>12</v>
       </c>
       <c r="AV13">
-        <v>1.92</v>
+        <v>24</v>
       </c>
       <c r="AW13">
-        <v>1.98</v>
+        <v>7.6</v>
       </c>
       <c r="AX13">
-        <v>1.85</v>
+        <v>6.2</v>
       </c>
       <c r="AY13">
-        <v>1.77</v>
+        <v>6.4</v>
       </c>
       <c r="AZ13">
-        <v>1.9</v>
+        <v>16</v>
       </c>
       <c r="BA13">
-        <v>1.98</v>
+        <v>7.4</v>
       </c>
       <c r="BB13">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="BC13">
-        <v>1.87</v>
+        <v>11.5</v>
       </c>
       <c r="BD13">
-        <v>1.94</v>
+        <v>19</v>
       </c>
       <c r="BE13">
-        <v>1.99</v>
+        <v>7.4</v>
       </c>
       <c r="BF13">
-        <v>1.93</v>
+        <v>3.6</v>
       </c>
       <c r="BG13">
-        <v>1.97</v>
+        <v>13.5</v>
       </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BI13">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK13">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BN13">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO13">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BP13">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ13">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BR13">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS13">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BU13">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BZ13">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA13">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B14" t="s">
         <v>90</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E14" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F14">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="G14">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="H14">
-        <v>8.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="I14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J14">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="K14">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="L14">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="M14">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N14">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="O14">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="P14">
-        <v>2.74</v>
+        <v>3.2</v>
       </c>
       <c r="Q14">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R14">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="S14">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="T14">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="U14">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="V14">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="W14">
-        <v>3.55</v>
+        <v>4.9</v>
       </c>
       <c r="X14">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="Y14">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="Z14">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="AA14">
-        <v>390</v>
+        <v>560</v>
       </c>
       <c r="AB14">
         <v>13</v>
       </c>
       <c r="AC14">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AD14">
         <v>55</v>
       </c>
       <c r="AE14">
-        <v>170</v>
+        <v>270</v>
       </c>
       <c r="AF14">
+        <v>9</v>
+      </c>
+      <c r="AG14">
         <v>11</v>
       </c>
-      <c r="AG14">
+      <c r="AH14">
+        <v>29</v>
+      </c>
+      <c r="AI14">
+        <v>150</v>
+      </c>
+      <c r="AJ14">
+        <v>10.5</v>
+      </c>
+      <c r="AK14">
         <v>12</v>
       </c>
-      <c r="AH14">
-        <v>28</v>
-      </c>
-      <c r="AI14">
-        <v>320</v>
-      </c>
-      <c r="AJ14">
+      <c r="AL14">
+        <v>32</v>
+      </c>
+      <c r="AM14">
+        <v>130</v>
+      </c>
+      <c r="AN14">
+        <v>3.45</v>
+      </c>
+      <c r="AO14">
+        <v>250</v>
+      </c>
+      <c r="AP14">
+        <v>34</v>
+      </c>
+      <c r="AQ14">
+        <v>50</v>
+      </c>
+      <c r="AR14">
+        <v>120</v>
+      </c>
+      <c r="AS14">
+        <v>120</v>
+      </c>
+      <c r="AT14">
         <v>12.5</v>
       </c>
-      <c r="AK14">
-        <v>15</v>
-      </c>
-      <c r="AL14">
-        <v>34</v>
-      </c>
-      <c r="AM14">
-        <v>260</v>
-      </c>
-      <c r="AN14">
-        <v>4.4</v>
-      </c>
-      <c r="AO14">
-        <v>170</v>
-      </c>
-      <c r="AP14">
-        <v>6.2</v>
-      </c>
-      <c r="AQ14">
-        <v>20</v>
-      </c>
-      <c r="AR14">
-        <v>7.2</v>
-      </c>
-      <c r="AS14">
-        <v>7.6</v>
-      </c>
-      <c r="AT14">
-        <v>7.6</v>
-      </c>
       <c r="AU14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AV14">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="AW14">
-        <v>7.4</v>
+        <v>150</v>
       </c>
       <c r="AX14">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY14">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="AZ14">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="BA14">
-        <v>7.2</v>
+        <v>120</v>
       </c>
       <c r="BB14">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC14">
         <v>11.5</v>
       </c>
       <c r="BD14">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="BE14">
-        <v>7.2</v>
+        <v>100</v>
       </c>
       <c r="BF14">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="BG14">
+        <v>140</v>
+      </c>
+      <c r="BH14">
+        <v>5.3</v>
+      </c>
+      <c r="BI14">
+        <v>4.8</v>
+      </c>
+      <c r="BJ14">
+        <v>11.5</v>
+      </c>
+      <c r="BK14">
+        <v>10</v>
+      </c>
+      <c r="BL14">
+        <v>130</v>
+      </c>
+      <c r="BM14">
+        <v>14</v>
+      </c>
+      <c r="BN14">
+        <v>4.1</v>
+      </c>
+      <c r="BO14">
+        <v>3.8</v>
+      </c>
+      <c r="BP14">
+        <v>6.6</v>
+      </c>
+      <c r="BQ14">
+        <v>6.2</v>
+      </c>
+      <c r="BR14">
+        <v>19.5</v>
+      </c>
+      <c r="BS14">
+        <v>16.5</v>
+      </c>
+      <c r="BT14">
+        <v>15.5</v>
+      </c>
+      <c r="BU14">
+        <v>13</v>
+      </c>
+      <c r="BV14">
+        <v>100</v>
+      </c>
+      <c r="BW14">
         <v>13.5</v>
       </c>
-      <c r="BH14">
-        <v>5.8</v>
-      </c>
-      <c r="BI14">
-        <v>2.64</v>
-      </c>
-      <c r="BJ14">
-        <v>13.5</v>
-      </c>
-      <c r="BK14">
-        <v>3.55</v>
-      </c>
-      <c r="BL14">
-        <v>1000</v>
-      </c>
-      <c r="BM14">
-        <v>4.6</v>
-      </c>
-      <c r="BN14">
-        <v>4.8</v>
-      </c>
-      <c r="BO14">
-        <v>2.4</v>
-      </c>
-      <c r="BP14">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BQ14">
-        <v>3.1</v>
-      </c>
-      <c r="BR14">
-        <v>24</v>
-      </c>
-      <c r="BS14">
-        <v>4</v>
-      </c>
-      <c r="BT14">
-        <v>16.5</v>
-      </c>
-      <c r="BU14">
-        <v>3.7</v>
-      </c>
-      <c r="BV14">
-        <v>1000</v>
-      </c>
-      <c r="BW14">
-        <v>4.6</v>
-      </c>
       <c r="BX14">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY14">
-        <v>4.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ14">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CA14">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="CB14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B15" t="s">
         <v>90</v>
@@ -4194,294 +4185,294 @@
         <v>101</v>
       </c>
       <c r="D15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E15" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F15">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="G15">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="H15">
+        <v>9.4</v>
+      </c>
+      <c r="I15">
+        <v>11</v>
+      </c>
+      <c r="J15">
+        <v>3.9</v>
+      </c>
+      <c r="K15">
+        <v>4.4</v>
+      </c>
+      <c r="L15">
+        <v>1.54</v>
+      </c>
+      <c r="M15">
+        <v>1.11</v>
+      </c>
+      <c r="N15">
+        <v>2.82</v>
+      </c>
+      <c r="O15">
+        <v>1.49</v>
+      </c>
+      <c r="P15">
+        <v>1.6</v>
+      </c>
+      <c r="Q15">
+        <v>2.5</v>
+      </c>
+      <c r="R15">
+        <v>1.21</v>
+      </c>
+      <c r="S15">
+        <v>5</v>
+      </c>
+      <c r="T15">
+        <v>2.58</v>
+      </c>
+      <c r="U15">
+        <v>1.55</v>
+      </c>
+      <c r="V15">
+        <v>1.11</v>
+      </c>
+      <c r="W15">
+        <v>2.8</v>
+      </c>
+      <c r="X15">
+        <v>11.5</v>
+      </c>
+      <c r="Y15">
+        <v>26</v>
+      </c>
+      <c r="Z15">
+        <v>110</v>
+      </c>
+      <c r="AA15">
+        <v>1000</v>
+      </c>
+      <c r="AB15">
+        <v>6.4</v>
+      </c>
+      <c r="AC15">
+        <v>10</v>
+      </c>
+      <c r="AD15">
+        <v>48</v>
+      </c>
+      <c r="AE15">
+        <v>310</v>
+      </c>
+      <c r="AF15">
+        <v>7.4</v>
+      </c>
+      <c r="AG15">
         <v>13</v>
       </c>
-      <c r="I15">
-        <v>13.5</v>
-      </c>
-      <c r="J15">
-        <v>7</v>
-      </c>
-      <c r="K15">
-        <v>7.2</v>
-      </c>
-      <c r="L15">
-        <v>1.25</v>
-      </c>
-      <c r="M15">
-        <v>1.02</v>
-      </c>
-      <c r="N15">
-        <v>7.6</v>
-      </c>
-      <c r="O15">
-        <v>1.14</v>
-      </c>
-      <c r="P15">
-        <v>3.1</v>
-      </c>
-      <c r="Q15">
-        <v>1.45</v>
-      </c>
-      <c r="R15">
-        <v>1.87</v>
-      </c>
-      <c r="S15">
-        <v>2.1</v>
-      </c>
-      <c r="T15">
-        <v>1.9</v>
-      </c>
-      <c r="U15">
-        <v>2.06</v>
-      </c>
-      <c r="V15">
-        <v>1.08</v>
-      </c>
-      <c r="W15">
-        <v>4.6</v>
-      </c>
-      <c r="X15">
-        <v>40</v>
-      </c>
-      <c r="Y15">
-        <v>60</v>
-      </c>
-      <c r="Z15">
-        <v>1000</v>
-      </c>
-      <c r="AA15">
-        <v>490</v>
-      </c>
-      <c r="AB15">
-        <v>12.5</v>
-      </c>
-      <c r="AC15">
-        <v>16</v>
-      </c>
-      <c r="AD15">
-        <v>46</v>
-      </c>
-      <c r="AE15">
-        <v>180</v>
-      </c>
-      <c r="AF15">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AG15">
-        <v>11</v>
-      </c>
       <c r="AH15">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="AI15">
-        <v>130</v>
+        <v>290</v>
       </c>
       <c r="AJ15">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="AK15">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="AL15">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="AM15">
-        <v>130</v>
+        <v>420</v>
       </c>
       <c r="AN15">
-        <v>3.6</v>
+        <v>13</v>
       </c>
       <c r="AO15">
         <v>1000</v>
       </c>
       <c r="AP15">
-        <v>34</v>
+        <v>7.8</v>
       </c>
       <c r="AQ15">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="AR15">
-        <v>110</v>
+        <v>6.2</v>
       </c>
       <c r="AS15">
-        <v>100</v>
+        <v>6.6</v>
       </c>
       <c r="AT15">
-        <v>11.5</v>
+        <v>4.4</v>
       </c>
       <c r="AU15">
-        <v>15</v>
+        <v>8.6</v>
       </c>
       <c r="AV15">
-        <v>42</v>
+        <v>5.8</v>
       </c>
       <c r="AW15">
-        <v>140</v>
+        <v>6.4</v>
       </c>
       <c r="AX15">
-        <v>8.6</v>
+        <v>5.7</v>
       </c>
       <c r="AY15">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ15">
+        <v>5.7</v>
+      </c>
+      <c r="BA15">
+        <v>6.4</v>
+      </c>
+      <c r="BB15">
         <v>10</v>
       </c>
-      <c r="AZ15">
-        <v>28</v>
-      </c>
-      <c r="BA15">
-        <v>100</v>
-      </c>
-      <c r="BB15">
+      <c r="BC15">
+        <v>16.5</v>
+      </c>
+      <c r="BD15">
+        <v>6</v>
+      </c>
+      <c r="BE15">
+        <v>6.4</v>
+      </c>
+      <c r="BF15">
         <v>9.800000000000001</v>
       </c>
-      <c r="BC15">
-        <v>11</v>
-      </c>
-      <c r="BD15">
-        <v>30</v>
-      </c>
-      <c r="BE15">
-        <v>100</v>
-      </c>
-      <c r="BF15">
-        <v>3.5</v>
-      </c>
       <c r="BG15">
-        <v>140</v>
+        <v>6.6</v>
       </c>
       <c r="BH15">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BL15">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="BM15">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN15">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP15">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR15">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS15">
-        <v>16</v>
+        <v>1.04</v>
       </c>
       <c r="BT15">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BV15">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BX15">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B16" t="s">
         <v>90</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E16" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F16">
-        <v>1.35</v>
+        <v>3.55</v>
       </c>
       <c r="G16">
-        <v>1.55</v>
+        <v>4.2</v>
       </c>
       <c r="H16">
-        <v>7.6</v>
+        <v>1.77</v>
       </c>
       <c r="I16">
-        <v>990</v>
+        <v>1.88</v>
       </c>
       <c r="J16">
-        <v>3.05</v>
+        <v>4.7</v>
       </c>
       <c r="K16">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="L16">
+        <v>1.16</v>
+      </c>
+      <c r="M16">
         <v>1.01</v>
       </c>
-      <c r="M16">
-        <v>1.1</v>
-      </c>
       <c r="N16">
-        <v>2.8</v>
+        <v>10.5</v>
       </c>
       <c r="O16">
-        <v>1.47</v>
+        <v>1.08</v>
       </c>
       <c r="P16">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="Q16">
-        <v>2.4</v>
+        <v>1.26</v>
       </c>
       <c r="R16">
-        <v>1.22</v>
+        <v>2.3</v>
       </c>
       <c r="S16">
-        <v>4.8</v>
+        <v>1.67</v>
       </c>
       <c r="T16">
         <v>1.11</v>
@@ -4490,118 +4481,118 @@
         <v>1.11</v>
       </c>
       <c r="V16">
-        <v>1.02</v>
+        <v>2.12</v>
       </c>
       <c r="W16">
-        <v>2.8</v>
+        <v>1.33</v>
       </c>
       <c r="X16">
-        <v>12</v>
+        <v>950</v>
       </c>
       <c r="Y16">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="Z16">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AA16">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="AB16">
-        <v>5.7</v>
+        <v>950</v>
       </c>
       <c r="AC16">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AD16">
-        <v>48</v>
+        <v>970</v>
       </c>
       <c r="AE16">
-        <v>300</v>
+        <v>970</v>
       </c>
       <c r="AF16">
-        <v>7.4</v>
+        <v>500</v>
       </c>
       <c r="AG16">
-        <v>13</v>
+        <v>950</v>
       </c>
       <c r="AH16">
-        <v>44</v>
+        <v>970</v>
       </c>
       <c r="AI16">
-        <v>280</v>
+        <v>500</v>
       </c>
       <c r="AJ16">
-        <v>15.5</v>
+        <v>900</v>
       </c>
       <c r="AK16">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AL16">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AM16">
-        <v>400</v>
+        <v>580</v>
       </c>
       <c r="AN16">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP16">
-        <v>8</v>
+        <v>1.51</v>
       </c>
       <c r="AQ16">
-        <v>19</v>
+        <v>1.49</v>
       </c>
       <c r="AR16">
-        <v>6</v>
+        <v>1.48</v>
       </c>
       <c r="AS16">
-        <v>6.4</v>
+        <v>1.48</v>
       </c>
       <c r="AT16">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="AU16">
-        <v>8.800000000000001</v>
+        <v>1.47</v>
       </c>
       <c r="AV16">
-        <v>5.7</v>
+        <v>1.44</v>
       </c>
       <c r="AW16">
-        <v>6.2</v>
+        <v>1.49</v>
       </c>
       <c r="AX16">
-        <v>6.4</v>
+        <v>1.51</v>
       </c>
       <c r="AY16">
-        <v>9.6</v>
+        <v>1.47</v>
       </c>
       <c r="AZ16">
-        <v>5.6</v>
+        <v>1.45</v>
       </c>
       <c r="BA16">
-        <v>6.2</v>
+        <v>1.47</v>
       </c>
       <c r="BB16">
-        <v>11.5</v>
+        <v>1.52</v>
       </c>
       <c r="BC16">
-        <v>18.5</v>
+        <v>1.5</v>
       </c>
       <c r="BD16">
-        <v>6</v>
+        <v>1.49</v>
       </c>
       <c r="BE16">
-        <v>6.2</v>
+        <v>1.52</v>
       </c>
       <c r="BF16">
-        <v>11</v>
+        <v>1.55</v>
       </c>
       <c r="BG16">
-        <v>6.4</v>
+        <v>1.38</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4658,13 +4649,13 @@
         <v>1.04</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA16">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4678,52 +4669,52 @@
         <v>102</v>
       </c>
       <c r="D17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E17" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F17">
-        <v>2.66</v>
+        <v>2.2</v>
       </c>
       <c r="G17">
-        <v>990</v>
+        <v>2.28</v>
       </c>
       <c r="H17">
-        <v>1.29</v>
+        <v>3.45</v>
       </c>
       <c r="I17">
-        <v>2.46</v>
+        <v>38</v>
       </c>
       <c r="J17">
-        <v>4.6</v>
+        <v>2.52</v>
       </c>
       <c r="K17">
-        <v>11</v>
+        <v>3.7</v>
       </c>
       <c r="L17">
         <v>1.01</v>
       </c>
       <c r="M17">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N17">
-        <v>1.93</v>
+        <v>1.32</v>
       </c>
       <c r="O17">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="P17">
-        <v>1.93</v>
+        <v>1.32</v>
       </c>
       <c r="Q17">
-        <v>1.06</v>
+        <v>1.5</v>
       </c>
       <c r="R17">
-        <v>1.93</v>
+        <v>1.18</v>
       </c>
       <c r="S17">
-        <v>1.06</v>
+        <v>1.5</v>
       </c>
       <c r="T17">
         <v>1.11</v>
@@ -4732,10 +4723,10 @@
         <v>1.11</v>
       </c>
       <c r="V17">
-        <v>1.95</v>
+        <v>1.18</v>
       </c>
       <c r="W17">
-        <v>1.22</v>
+        <v>1.78</v>
       </c>
       <c r="X17">
         <v>950</v>
@@ -4753,13 +4744,13 @@
         <v>950</v>
       </c>
       <c r="AC17">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AD17">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AE17">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AF17">
         <v>500</v>
@@ -4768,13 +4759,13 @@
         <v>950</v>
       </c>
       <c r="AH17">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AI17">
         <v>500</v>
       </c>
       <c r="AJ17">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK17">
         <v>500</v>
@@ -4783,67 +4774,67 @@
         <v>500</v>
       </c>
       <c r="AM17">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN17">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AO17">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AP17">
-        <v>1.47</v>
+        <v>1.17</v>
       </c>
       <c r="AQ17">
-        <v>1.45</v>
+        <v>1.17</v>
       </c>
       <c r="AR17">
-        <v>1.48</v>
+        <v>1.16</v>
       </c>
       <c r="AS17">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="AT17">
-        <v>1.46</v>
+        <v>1.14</v>
       </c>
       <c r="AU17">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="AV17">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="AW17">
-        <v>1.45</v>
+        <v>1.16</v>
       </c>
       <c r="AX17">
-        <v>1.46</v>
+        <v>1.17</v>
       </c>
       <c r="AY17">
-        <v>1.42</v>
+        <v>1.13</v>
       </c>
       <c r="AZ17">
-        <v>1.41</v>
+        <v>1.17</v>
       </c>
       <c r="BA17">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="BB17">
-        <v>1.48</v>
+        <v>1.16</v>
       </c>
       <c r="BC17">
-        <v>1.46</v>
+        <v>1.15</v>
       </c>
       <c r="BD17">
-        <v>1.45</v>
+        <v>1.16</v>
       </c>
       <c r="BE17">
-        <v>1.48</v>
+        <v>1.17</v>
       </c>
       <c r="BF17">
         <v>1.55</v>
       </c>
       <c r="BG17">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -4900,72 +4891,72 @@
         <v>1.04</v>
       </c>
       <c r="BZ17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA17">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB17" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B18" t="s">
         <v>90</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D18" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E18" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F18">
-        <v>2.2</v>
+        <v>2.86</v>
       </c>
       <c r="G18">
-        <v>2.28</v>
+        <v>21</v>
       </c>
       <c r="H18">
-        <v>3.45</v>
+        <v>1.6</v>
       </c>
       <c r="I18">
-        <v>38</v>
+        <v>2.44</v>
       </c>
       <c r="J18">
-        <v>2.1</v>
+        <v>2.84</v>
       </c>
       <c r="K18">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="L18">
         <v>1.01</v>
       </c>
       <c r="M18">
+        <v>1.07</v>
+      </c>
+      <c r="N18">
+        <v>1.3</v>
+      </c>
+      <c r="O18">
         <v>1.08</v>
       </c>
-      <c r="N18">
-        <v>1.28</v>
-      </c>
-      <c r="O18">
-        <v>1.13</v>
-      </c>
       <c r="P18">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q18">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="R18">
         <v>1.18</v>
       </c>
       <c r="S18">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="T18">
         <v>1.11</v>
@@ -4974,28 +4965,28 @@
         <v>1.11</v>
       </c>
       <c r="V18">
+        <v>1.72</v>
+      </c>
+      <c r="W18">
         <v>1.17</v>
-      </c>
-      <c r="W18">
-        <v>1.78</v>
       </c>
       <c r="X18">
         <v>950</v>
       </c>
       <c r="Y18">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z18">
         <v>500</v>
       </c>
       <c r="AA18">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB18">
         <v>950</v>
       </c>
       <c r="AC18">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AD18">
         <v>950</v>
@@ -5016,7 +5007,7 @@
         <v>500</v>
       </c>
       <c r="AJ18">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK18">
         <v>500</v>
@@ -5034,58 +5025,58 @@
         <v>500</v>
       </c>
       <c r="AP18">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AQ18">
-        <v>1.17</v>
+        <v>3.85</v>
       </c>
       <c r="AR18">
-        <v>1.16</v>
+        <v>5.1</v>
       </c>
       <c r="AS18">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="AT18">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AU18">
-        <v>1.14</v>
+        <v>5.1</v>
       </c>
       <c r="AV18">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AW18">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="AX18">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AY18">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AZ18">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="BA18">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="BB18">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="BC18">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="BD18">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="BE18">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="BF18">
         <v>1.55</v>
       </c>
       <c r="BG18">
-        <v>1.17</v>
+        <v>5.5</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5148,66 +5139,66 @@
         <v>1.04</v>
       </c>
       <c r="CB18" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B19" t="s">
         <v>90</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D19" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E19" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F19">
-        <v>3.05</v>
+        <v>1.07</v>
       </c>
       <c r="G19">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="H19">
-        <v>1.59</v>
+        <v>1.07</v>
       </c>
       <c r="I19">
-        <v>2.44</v>
+        <v>990</v>
       </c>
       <c r="J19">
-        <v>2.84</v>
+        <v>1.09</v>
       </c>
       <c r="K19">
-        <v>8.6</v>
+        <v>950</v>
       </c>
       <c r="L19">
         <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N19">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="O19">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="P19">
         <v>1.25</v>
       </c>
       <c r="Q19">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="R19">
         <v>1.18</v>
       </c>
       <c r="S19">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T19">
         <v>1.11</v>
@@ -5216,118 +5207,118 @@
         <v>1.11</v>
       </c>
       <c r="V19">
-        <v>1.69</v>
+        <v>1.02</v>
       </c>
       <c r="W19">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="X19">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Y19">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z19">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AA19">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB19">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AC19">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD19">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE19">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AF19">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AG19">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AH19">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI19">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ19">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AK19">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AL19">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AM19">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AN19">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AO19">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AP19">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AR19">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AS19">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AT19">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AU19">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AV19">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AW19">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AX19">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AY19">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BA19">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BB19">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BC19">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BD19">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BE19">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BF19">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="BG19">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5390,12 +5381,12 @@
         <v>1.04</v>
       </c>
       <c r="CB19" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B20" t="s">
         <v>90</v>
@@ -5404,240 +5395,240 @@
         <v>103</v>
       </c>
       <c r="D20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E20" t="s">
+        <v>143</v>
+      </c>
+      <c r="F20">
+        <v>1.98</v>
+      </c>
+      <c r="G20">
+        <v>2.06</v>
+      </c>
+      <c r="H20">
+        <v>3.65</v>
+      </c>
+      <c r="I20">
+        <v>4.1</v>
+      </c>
+      <c r="J20">
+        <v>3.9</v>
+      </c>
+      <c r="K20">
+        <v>4.3</v>
+      </c>
+      <c r="L20">
+        <v>1.27</v>
+      </c>
+      <c r="M20">
+        <v>1.04</v>
+      </c>
+      <c r="N20">
+        <v>5.9</v>
+      </c>
+      <c r="O20">
+        <v>1.18</v>
+      </c>
+      <c r="P20">
+        <v>2.7</v>
+      </c>
+      <c r="Q20">
+        <v>1.53</v>
+      </c>
+      <c r="R20">
+        <v>1.68</v>
+      </c>
+      <c r="S20">
+        <v>2.34</v>
+      </c>
+      <c r="T20">
+        <v>1.5</v>
+      </c>
+      <c r="U20">
+        <v>2.52</v>
+      </c>
+      <c r="V20">
+        <v>1.33</v>
+      </c>
+      <c r="W20">
+        <v>1.94</v>
+      </c>
+      <c r="X20">
+        <v>29</v>
+      </c>
+      <c r="Y20">
+        <v>23</v>
+      </c>
+      <c r="Z20">
+        <v>34</v>
+      </c>
+      <c r="AA20">
+        <v>160</v>
+      </c>
+      <c r="AB20">
+        <v>15.5</v>
+      </c>
+      <c r="AC20">
+        <v>11.5</v>
+      </c>
+      <c r="AD20">
+        <v>17.5</v>
+      </c>
+      <c r="AE20">
+        <v>38</v>
+      </c>
+      <c r="AF20">
+        <v>17</v>
+      </c>
+      <c r="AG20">
+        <v>12</v>
+      </c>
+      <c r="AH20">
+        <v>16.5</v>
+      </c>
+      <c r="AI20">
+        <v>40</v>
+      </c>
+      <c r="AJ20">
+        <v>25</v>
+      </c>
+      <c r="AK20">
+        <v>19</v>
+      </c>
+      <c r="AL20">
+        <v>27</v>
+      </c>
+      <c r="AM20">
+        <v>200</v>
+      </c>
+      <c r="AN20">
+        <v>9.6</v>
+      </c>
+      <c r="AO20">
+        <v>26</v>
+      </c>
+      <c r="AP20">
+        <v>11.5</v>
+      </c>
+      <c r="AQ20">
+        <v>17.5</v>
+      </c>
+      <c r="AR20">
+        <v>17</v>
+      </c>
+      <c r="AS20">
+        <v>7.6</v>
+      </c>
+      <c r="AT20">
+        <v>12</v>
+      </c>
+      <c r="AU20">
+        <v>8.6</v>
+      </c>
+      <c r="AV20">
+        <v>13</v>
+      </c>
+      <c r="AW20">
+        <v>18.5</v>
+      </c>
+      <c r="AX20">
+        <v>13.5</v>
+      </c>
+      <c r="AY20">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ20">
+        <v>12.5</v>
+      </c>
+      <c r="BA20">
+        <v>21</v>
+      </c>
+      <c r="BB20">
+        <v>20</v>
+      </c>
+      <c r="BC20">
+        <v>15</v>
+      </c>
+      <c r="BD20">
+        <v>21</v>
+      </c>
+      <c r="BE20">
+        <v>8</v>
+      </c>
+      <c r="BF20">
+        <v>7.4</v>
+      </c>
+      <c r="BG20">
+        <v>19.5</v>
+      </c>
+      <c r="BH20">
+        <v>1000</v>
+      </c>
+      <c r="BI20">
+        <v>1.04</v>
+      </c>
+      <c r="BJ20">
+        <v>1000</v>
+      </c>
+      <c r="BK20">
+        <v>1.04</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>1.04</v>
+      </c>
+      <c r="BN20">
+        <v>1000</v>
+      </c>
+      <c r="BO20">
+        <v>1.04</v>
+      </c>
+      <c r="BP20">
+        <v>1000</v>
+      </c>
+      <c r="BQ20">
+        <v>1.04</v>
+      </c>
+      <c r="BR20">
+        <v>1000</v>
+      </c>
+      <c r="BS20">
+        <v>1.04</v>
+      </c>
+      <c r="BT20">
+        <v>1000</v>
+      </c>
+      <c r="BU20">
+        <v>1.04</v>
+      </c>
+      <c r="BV20">
+        <v>1000</v>
+      </c>
+      <c r="BW20">
+        <v>1.04</v>
+      </c>
+      <c r="BX20">
+        <v>1000</v>
+      </c>
+      <c r="BY20">
+        <v>1.04</v>
+      </c>
+      <c r="BZ20">
+        <v>1000</v>
+      </c>
+      <c r="CA20">
+        <v>1.04</v>
+      </c>
+      <c r="CB20" t="s">
         <v>145</v>
-      </c>
-      <c r="F20">
-        <v>1.07</v>
-      </c>
-      <c r="G20">
-        <v>990</v>
-      </c>
-      <c r="H20">
-        <v>1.07</v>
-      </c>
-      <c r="I20">
-        <v>990</v>
-      </c>
-      <c r="J20">
-        <v>1.09</v>
-      </c>
-      <c r="K20">
-        <v>950</v>
-      </c>
-      <c r="L20">
-        <v>1.01</v>
-      </c>
-      <c r="M20">
-        <v>1.01</v>
-      </c>
-      <c r="N20">
-        <v>1.26</v>
-      </c>
-      <c r="O20">
-        <v>1.02</v>
-      </c>
-      <c r="P20">
-        <v>1.25</v>
-      </c>
-      <c r="Q20">
-        <v>1.4</v>
-      </c>
-      <c r="R20">
-        <v>1.18</v>
-      </c>
-      <c r="S20">
-        <v>1.4</v>
-      </c>
-      <c r="T20">
-        <v>1.11</v>
-      </c>
-      <c r="U20">
-        <v>1.11</v>
-      </c>
-      <c r="V20">
-        <v>1.02</v>
-      </c>
-      <c r="W20">
-        <v>1.02</v>
-      </c>
-      <c r="X20">
-        <v>1000</v>
-      </c>
-      <c r="Y20">
-        <v>1000</v>
-      </c>
-      <c r="Z20">
-        <v>1000</v>
-      </c>
-      <c r="AA20">
-        <v>1000</v>
-      </c>
-      <c r="AB20">
-        <v>1000</v>
-      </c>
-      <c r="AC20">
-        <v>1000</v>
-      </c>
-      <c r="AD20">
-        <v>1000</v>
-      </c>
-      <c r="AE20">
-        <v>1000</v>
-      </c>
-      <c r="AF20">
-        <v>1000</v>
-      </c>
-      <c r="AG20">
-        <v>1000</v>
-      </c>
-      <c r="AH20">
-        <v>1000</v>
-      </c>
-      <c r="AI20">
-        <v>1000</v>
-      </c>
-      <c r="AJ20">
-        <v>1000</v>
-      </c>
-      <c r="AK20">
-        <v>1000</v>
-      </c>
-      <c r="AL20">
-        <v>1000</v>
-      </c>
-      <c r="AM20">
-        <v>1000</v>
-      </c>
-      <c r="AN20">
-        <v>1000</v>
-      </c>
-      <c r="AO20">
-        <v>1000</v>
-      </c>
-      <c r="AP20">
-        <v>1.01</v>
-      </c>
-      <c r="AQ20">
-        <v>1.01</v>
-      </c>
-      <c r="AR20">
-        <v>1.01</v>
-      </c>
-      <c r="AS20">
-        <v>1.01</v>
-      </c>
-      <c r="AT20">
-        <v>1.01</v>
-      </c>
-      <c r="AU20">
-        <v>1.01</v>
-      </c>
-      <c r="AV20">
-        <v>1.01</v>
-      </c>
-      <c r="AW20">
-        <v>1.01</v>
-      </c>
-      <c r="AX20">
-        <v>1.01</v>
-      </c>
-      <c r="AY20">
-        <v>1.01</v>
-      </c>
-      <c r="AZ20">
-        <v>1.01</v>
-      </c>
-      <c r="BA20">
-        <v>1.01</v>
-      </c>
-      <c r="BB20">
-        <v>1.01</v>
-      </c>
-      <c r="BC20">
-        <v>1.01</v>
-      </c>
-      <c r="BD20">
-        <v>1.01</v>
-      </c>
-      <c r="BE20">
-        <v>1.01</v>
-      </c>
-      <c r="BF20">
-        <v>1.01</v>
-      </c>
-      <c r="BG20">
-        <v>1.01</v>
-      </c>
-      <c r="BH20">
-        <v>1000</v>
-      </c>
-      <c r="BI20">
-        <v>1.04</v>
-      </c>
-      <c r="BJ20">
-        <v>1000</v>
-      </c>
-      <c r="BK20">
-        <v>1.04</v>
-      </c>
-      <c r="BL20">
-        <v>1000</v>
-      </c>
-      <c r="BM20">
-        <v>1.04</v>
-      </c>
-      <c r="BN20">
-        <v>1000</v>
-      </c>
-      <c r="BO20">
-        <v>1.04</v>
-      </c>
-      <c r="BP20">
-        <v>1000</v>
-      </c>
-      <c r="BQ20">
-        <v>1.04</v>
-      </c>
-      <c r="BR20">
-        <v>1000</v>
-      </c>
-      <c r="BS20">
-        <v>1.04</v>
-      </c>
-      <c r="BT20">
-        <v>1000</v>
-      </c>
-      <c r="BU20">
-        <v>1.04</v>
-      </c>
-      <c r="BV20">
-        <v>1000</v>
-      </c>
-      <c r="BW20">
-        <v>1.04</v>
-      </c>
-      <c r="BX20">
-        <v>1000</v>
-      </c>
-      <c r="BY20">
-        <v>1.04</v>
-      </c>
-      <c r="BZ20">
-        <v>1000</v>
-      </c>
-      <c r="CA20">
-        <v>1.04</v>
-      </c>
-      <c r="CB20" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B21" t="s">
         <v>90</v>
@@ -5646,477 +5637,235 @@
         <v>104</v>
       </c>
       <c r="D21" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E21" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F21">
-        <v>1.98</v>
+        <v>3.8</v>
       </c>
       <c r="G21">
-        <v>2.12</v>
+        <v>4.1</v>
       </c>
       <c r="H21">
-        <v>3.4</v>
+        <v>2.22</v>
       </c>
       <c r="I21">
-        <v>4.2</v>
+        <v>2.34</v>
       </c>
       <c r="J21">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="K21">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="L21">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M21">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="N21">
-        <v>1.1</v>
+        <v>3.05</v>
       </c>
       <c r="O21">
-        <v>1.16</v>
+        <v>1.45</v>
       </c>
       <c r="P21">
+        <v>1.66</v>
+      </c>
+      <c r="Q21">
         <v>2.42</v>
       </c>
-      <c r="Q21">
-        <v>1.54</v>
-      </c>
       <c r="R21">
-        <v>1.57</v>
+        <v>1.24</v>
       </c>
       <c r="S21">
-        <v>2.34</v>
+        <v>4.7</v>
       </c>
       <c r="T21">
-        <v>1.49</v>
+        <v>1.97</v>
       </c>
       <c r="U21">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="V21">
-        <v>1.31</v>
+        <v>1.75</v>
       </c>
       <c r="W21">
-        <v>1.89</v>
+        <v>1.32</v>
       </c>
       <c r="X21">
+        <v>10.5</v>
+      </c>
+      <c r="Y21">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z21">
+        <v>13.5</v>
+      </c>
+      <c r="AA21">
+        <v>32</v>
+      </c>
+      <c r="AB21">
+        <v>13.5</v>
+      </c>
+      <c r="AC21">
+        <v>7.4</v>
+      </c>
+      <c r="AD21">
+        <v>13.5</v>
+      </c>
+      <c r="AE21">
+        <v>29</v>
+      </c>
+      <c r="AF21">
         <v>27</v>
       </c>
-      <c r="Y21">
-        <v>22</v>
-      </c>
-      <c r="Z21">
+      <c r="AG21">
+        <v>17</v>
+      </c>
+      <c r="AH21">
+        <v>24</v>
+      </c>
+      <c r="AI21">
+        <v>60</v>
+      </c>
+      <c r="AJ21">
+        <v>100</v>
+      </c>
+      <c r="AK21">
+        <v>65</v>
+      </c>
+      <c r="AL21">
+        <v>85</v>
+      </c>
+      <c r="AM21">
+        <v>170</v>
+      </c>
+      <c r="AN21">
+        <v>85</v>
+      </c>
+      <c r="AO21">
         <v>32</v>
       </c>
-      <c r="AA21">
-        <v>70</v>
-      </c>
-      <c r="AB21">
-        <v>15</v>
-      </c>
-      <c r="AC21">
-        <v>11</v>
-      </c>
-      <c r="AD21">
-        <v>17.5</v>
-      </c>
-      <c r="AE21">
+      <c r="AP21">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ21">
+        <v>6.2</v>
+      </c>
+      <c r="AR21">
+        <v>12</v>
+      </c>
+      <c r="AS21">
+        <v>26</v>
+      </c>
+      <c r="AT21">
+        <v>10</v>
+      </c>
+      <c r="AU21">
+        <v>5.8</v>
+      </c>
+      <c r="AV21">
+        <v>10</v>
+      </c>
+      <c r="AW21">
+        <v>6</v>
+      </c>
+      <c r="AX21">
+        <v>19.5</v>
+      </c>
+      <c r="AY21">
+        <v>14</v>
+      </c>
+      <c r="AZ21">
+        <v>18</v>
+      </c>
+      <c r="BA21">
+        <v>6.8</v>
+      </c>
+      <c r="BB21">
+        <v>7.2</v>
+      </c>
+      <c r="BC21">
+        <v>6.8</v>
+      </c>
+      <c r="BD21">
+        <v>7</v>
+      </c>
+      <c r="BE21">
+        <v>7.4</v>
+      </c>
+      <c r="BF21">
+        <v>7</v>
+      </c>
+      <c r="BG21">
+        <v>19.5</v>
+      </c>
+      <c r="BH21">
+        <v>3.25</v>
+      </c>
+      <c r="BI21">
+        <v>2.46</v>
+      </c>
+      <c r="BJ21">
+        <v>12</v>
+      </c>
+      <c r="BK21">
+        <v>4</v>
+      </c>
+      <c r="BL21">
+        <v>1000</v>
+      </c>
+      <c r="BM21">
+        <v>5.9</v>
+      </c>
+      <c r="BN21">
+        <v>7.8</v>
+      </c>
+      <c r="BO21">
+        <v>5.4</v>
+      </c>
+      <c r="BP21">
         <v>40</v>
       </c>
-      <c r="AF21">
-        <v>16.5</v>
-      </c>
-      <c r="AG21">
-        <v>12</v>
-      </c>
-      <c r="AH21">
-        <v>17</v>
-      </c>
-      <c r="AI21">
-        <v>40</v>
-      </c>
-      <c r="AJ21">
-        <v>26</v>
-      </c>
-      <c r="AK21">
-        <v>19.5</v>
-      </c>
-      <c r="AL21">
-        <v>29</v>
-      </c>
-      <c r="AM21">
-        <v>65</v>
-      </c>
-      <c r="AN21">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AO21">
-        <v>29</v>
-      </c>
-      <c r="AP21">
-        <v>20</v>
-      </c>
-      <c r="AQ21">
-        <v>16.5</v>
-      </c>
-      <c r="AR21">
-        <v>7.2</v>
-      </c>
-      <c r="AS21">
-        <v>7</v>
-      </c>
-      <c r="AT21">
-        <v>10.5</v>
-      </c>
-      <c r="AU21">
-        <v>8.4</v>
-      </c>
-      <c r="AV21">
-        <v>13</v>
-      </c>
-      <c r="AW21">
-        <v>7.4</v>
-      </c>
-      <c r="AX21">
-        <v>12.5</v>
-      </c>
-      <c r="AY21">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ21">
-        <v>12</v>
-      </c>
-      <c r="BA21">
-        <v>7.4</v>
-      </c>
-      <c r="BB21">
-        <v>19</v>
-      </c>
-      <c r="BC21">
-        <v>15</v>
-      </c>
-      <c r="BD21">
+      <c r="BQ21">
+        <v>5.3</v>
+      </c>
+      <c r="BR21">
+        <v>60</v>
+      </c>
+      <c r="BS21">
+        <v>5.5</v>
+      </c>
+      <c r="BT21">
+        <v>5.6</v>
+      </c>
+      <c r="BU21">
+        <v>3.95</v>
+      </c>
+      <c r="BV21">
         <v>21</v>
       </c>
-      <c r="BE21">
-        <v>8</v>
-      </c>
-      <c r="BF21">
-        <v>7.6</v>
-      </c>
-      <c r="BG21">
-        <v>19</v>
-      </c>
-      <c r="BH21">
-        <v>1000</v>
-      </c>
-      <c r="BI21">
-        <v>1.04</v>
-      </c>
-      <c r="BJ21">
-        <v>1000</v>
-      </c>
-      <c r="BK21">
-        <v>1.04</v>
-      </c>
-      <c r="BL21">
-        <v>1000</v>
-      </c>
-      <c r="BM21">
-        <v>1.04</v>
-      </c>
-      <c r="BN21">
-        <v>1000</v>
-      </c>
-      <c r="BO21">
-        <v>1.04</v>
-      </c>
-      <c r="BP21">
-        <v>1000</v>
-      </c>
-      <c r="BQ21">
-        <v>1.04</v>
-      </c>
-      <c r="BR21">
-        <v>1000</v>
-      </c>
-      <c r="BS21">
-        <v>1.04</v>
-      </c>
-      <c r="BT21">
-        <v>1000</v>
-      </c>
-      <c r="BU21">
-        <v>1.04</v>
-      </c>
-      <c r="BV21">
-        <v>1000</v>
-      </c>
       <c r="BW21">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BX21">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY21">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BZ21">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="CA21">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="CB21" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="22" spans="1:80">
-      <c r="A22" t="s">
-        <v>80</v>
-      </c>
-      <c r="B22" t="s">
-        <v>90</v>
-      </c>
-      <c r="C22" t="s">
-        <v>105</v>
-      </c>
-      <c r="D22" t="s">
-        <v>126</v>
-      </c>
-      <c r="E22" t="s">
-        <v>147</v>
-      </c>
-      <c r="F22">
-        <v>3.75</v>
-      </c>
-      <c r="G22">
-        <v>4.1</v>
-      </c>
-      <c r="H22">
-        <v>2.2</v>
-      </c>
-      <c r="I22">
-        <v>2.38</v>
-      </c>
-      <c r="J22">
-        <v>3.1</v>
-      </c>
-      <c r="K22">
-        <v>3.4</v>
-      </c>
-      <c r="L22">
-        <v>1.5</v>
-      </c>
-      <c r="M22">
-        <v>1.1</v>
-      </c>
-      <c r="N22">
-        <v>2.9</v>
-      </c>
-      <c r="O22">
-        <v>1.44</v>
-      </c>
-      <c r="P22">
-        <v>1.64</v>
-      </c>
-      <c r="Q22">
-        <v>2.2</v>
-      </c>
-      <c r="R22">
-        <v>1.24</v>
-      </c>
-      <c r="S22">
-        <v>4.4</v>
-      </c>
-      <c r="T22">
-        <v>1.84</v>
-      </c>
-      <c r="U22">
-        <v>1.89</v>
-      </c>
-      <c r="V22">
-        <v>1.73</v>
-      </c>
-      <c r="W22">
-        <v>1.32</v>
-      </c>
-      <c r="X22">
-        <v>10.5</v>
-      </c>
-      <c r="Y22">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Z22">
-        <v>13.5</v>
-      </c>
-      <c r="AA22">
-        <v>38</v>
-      </c>
-      <c r="AB22">
-        <v>13.5</v>
-      </c>
-      <c r="AC22">
-        <v>7.6</v>
-      </c>
-      <c r="AD22">
-        <v>13.5</v>
-      </c>
-      <c r="AE22">
-        <v>34</v>
-      </c>
-      <c r="AF22">
-        <v>32</v>
-      </c>
-      <c r="AG22">
-        <v>19</v>
-      </c>
-      <c r="AH22">
-        <v>24</v>
-      </c>
-      <c r="AI22">
-        <v>60</v>
-      </c>
-      <c r="AJ22">
-        <v>100</v>
-      </c>
-      <c r="AK22">
-        <v>65</v>
-      </c>
-      <c r="AL22">
-        <v>85</v>
-      </c>
-      <c r="AM22">
-        <v>170</v>
-      </c>
-      <c r="AN22">
-        <v>85</v>
-      </c>
-      <c r="AO22">
-        <v>32</v>
-      </c>
-      <c r="AP22">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ22">
-        <v>6.2</v>
-      </c>
-      <c r="AR22">
-        <v>12</v>
-      </c>
-      <c r="AS22">
-        <v>26</v>
-      </c>
-      <c r="AT22">
-        <v>10</v>
-      </c>
-      <c r="AU22">
-        <v>5.8</v>
-      </c>
-      <c r="AV22">
-        <v>10</v>
-      </c>
-      <c r="AW22">
-        <v>5.3</v>
-      </c>
-      <c r="AX22">
-        <v>19.5</v>
-      </c>
-      <c r="AY22">
-        <v>12.5</v>
-      </c>
-      <c r="AZ22">
-        <v>18</v>
-      </c>
-      <c r="BA22">
-        <v>5.7</v>
-      </c>
-      <c r="BB22">
-        <v>5.9</v>
-      </c>
-      <c r="BC22">
-        <v>5.7</v>
-      </c>
-      <c r="BD22">
-        <v>5.8</v>
-      </c>
-      <c r="BE22">
-        <v>6</v>
-      </c>
-      <c r="BF22">
-        <v>5.8</v>
-      </c>
-      <c r="BG22">
-        <v>19.5</v>
-      </c>
-      <c r="BH22">
-        <v>3.25</v>
-      </c>
-      <c r="BI22">
-        <v>2.46</v>
-      </c>
-      <c r="BJ22">
-        <v>12</v>
-      </c>
-      <c r="BK22">
-        <v>4</v>
-      </c>
-      <c r="BL22">
-        <v>1000</v>
-      </c>
-      <c r="BM22">
-        <v>5.9</v>
-      </c>
-      <c r="BN22">
-        <v>7.8</v>
-      </c>
-      <c r="BO22">
-        <v>5.4</v>
-      </c>
-      <c r="BP22">
-        <v>40</v>
-      </c>
-      <c r="BQ22">
-        <v>5.3</v>
-      </c>
-      <c r="BR22">
-        <v>60</v>
-      </c>
-      <c r="BS22">
-        <v>5.5</v>
-      </c>
-      <c r="BT22">
-        <v>5.6</v>
-      </c>
-      <c r="BU22">
-        <v>3.95</v>
-      </c>
-      <c r="BV22">
-        <v>21</v>
-      </c>
-      <c r="BW22">
-        <v>4.7</v>
-      </c>
-      <c r="BX22">
-        <v>44</v>
-      </c>
-      <c r="BY22">
-        <v>5.4</v>
-      </c>
-      <c r="BZ22">
-        <v>44</v>
-      </c>
-      <c r="CA22">
-        <v>5.4</v>
-      </c>
-      <c r="CB22" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
@@ -451,7 +451,7 @@
     <t>Millonarios</t>
   </si>
   <si>
-    <t>2026-08-27 01:57:44</t>
+    <t>2026-08-27 04:12:49</t>
   </si>
 </sst>
 </file>
@@ -1045,37 +1045,37 @@
         <v>125</v>
       </c>
       <c r="F2">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="G2">
         <v>2.42</v>
       </c>
       <c r="H2">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I2">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J2">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="K2">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="L2">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="M2">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="N2">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="O2">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="P2">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Q2">
         <v>3.5</v>
@@ -1114,7 +1114,7 @@
         <v>14</v>
       </c>
       <c r="AC2">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AD2">
         <v>950</v>
@@ -1153,58 +1153,58 @@
         <v>600</v>
       </c>
       <c r="AP2">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AQ2">
-        <v>2.04</v>
+        <v>1.71</v>
       </c>
       <c r="AR2">
-        <v>2.24</v>
+        <v>1.86</v>
       </c>
       <c r="AS2">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="AT2">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="AU2">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AV2">
         <v>14.5</v>
       </c>
       <c r="AW2">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="AX2">
-        <v>2.08</v>
+        <v>1.74</v>
       </c>
       <c r="AY2">
-        <v>2.14</v>
+        <v>1.77</v>
       </c>
       <c r="AZ2">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="BA2">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="BB2">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="BC2">
-        <v>2.22</v>
+        <v>1.83</v>
       </c>
       <c r="BD2">
-        <v>2.28</v>
+        <v>1.87</v>
       </c>
       <c r="BE2">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="BF2">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="BG2">
-        <v>2.24</v>
+        <v>1.86</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1287,16 +1287,16 @@
         <v>126</v>
       </c>
       <c r="F3">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="H3">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="I3">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="J3">
         <v>3.85</v>
@@ -1311,13 +1311,13 @@
         <v>1.04</v>
       </c>
       <c r="N3">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O3">
         <v>1.2</v>
       </c>
       <c r="P3">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q3">
         <v>1.6</v>
@@ -1332,16 +1332,16 @@
         <v>1.55</v>
       </c>
       <c r="U3">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="V3">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W3">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X3">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Y3">
         <v>16</v>
@@ -1353,7 +1353,7 @@
         <v>36</v>
       </c>
       <c r="AB3">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC3">
         <v>10</v>
@@ -1377,7 +1377,7 @@
         <v>32</v>
       </c>
       <c r="AJ3">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AK3">
         <v>29</v>
@@ -1386,13 +1386,13 @@
         <v>34</v>
       </c>
       <c r="AM3">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AN3">
         <v>18</v>
       </c>
       <c r="AO3">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AP3">
         <v>20</v>
@@ -1407,7 +1407,7 @@
         <v>16</v>
       </c>
       <c r="AT3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AU3">
         <v>8.6</v>
@@ -1467,10 +1467,10 @@
         <v>5.3</v>
       </c>
       <c r="BN3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BO3">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BP3">
         <v>23</v>
@@ -1491,10 +1491,10 @@
         <v>4.6</v>
       </c>
       <c r="BV3">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BW3">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BX3">
         <v>28</v>
@@ -1503,10 +1503,10 @@
         <v>4.7</v>
       </c>
       <c r="BZ3">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="CA3">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="CB3" t="s">
         <v>145</v>
@@ -1529,19 +1529,19 @@
         <v>127</v>
       </c>
       <c r="F4">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="G4">
         <v>1.65</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K4">
         <v>4.7</v>
@@ -1550,10 +1550,10 @@
         <v>1.39</v>
       </c>
       <c r="M4">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N4">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="O4">
         <v>1.29</v>
@@ -1562,34 +1562,34 @@
         <v>2.04</v>
       </c>
       <c r="Q4">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R4">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="S4">
         <v>3.25</v>
       </c>
       <c r="T4">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="U4">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V4">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W4">
         <v>2.52</v>
       </c>
       <c r="X4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Y4">
         <v>23</v>
       </c>
       <c r="Z4">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AA4">
         <v>700</v>
@@ -1598,7 +1598,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD4">
         <v>32</v>
@@ -1607,10 +1607,10 @@
         <v>700</v>
       </c>
       <c r="AF4">
+        <v>9.6</v>
+      </c>
+      <c r="AG4">
         <v>10.5</v>
-      </c>
-      <c r="AG4">
-        <v>11.5</v>
       </c>
       <c r="AH4">
         <v>25</v>
@@ -1619,10 +1619,10 @@
         <v>700</v>
       </c>
       <c r="AJ4">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AK4">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AL4">
         <v>46</v>
@@ -1637,61 +1637,61 @@
         <v>700</v>
       </c>
       <c r="AP4">
-        <v>13</v>
+        <v>5.7</v>
       </c>
       <c r="AQ4">
-        <v>18.5</v>
+        <v>6.2</v>
       </c>
       <c r="AR4">
         <v>7.6</v>
       </c>
       <c r="AS4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT4">
+        <v>4.5</v>
+      </c>
+      <c r="AU4">
+        <v>5</v>
+      </c>
+      <c r="AV4">
+        <v>6.4</v>
+      </c>
+      <c r="AW4">
+        <v>8</v>
+      </c>
+      <c r="AX4">
+        <v>4.8</v>
+      </c>
+      <c r="AY4">
+        <v>5</v>
+      </c>
+      <c r="AZ4">
+        <v>6.2</v>
+      </c>
+      <c r="BA4">
+        <v>7.8</v>
+      </c>
+      <c r="BB4">
+        <v>6</v>
+      </c>
+      <c r="BC4">
+        <v>6.4</v>
+      </c>
+      <c r="BD4">
         <v>7.2</v>
       </c>
-      <c r="AT4">
-        <v>6.8</v>
-      </c>
-      <c r="AU4">
-        <v>8.4</v>
-      </c>
-      <c r="AV4">
-        <v>12.5</v>
-      </c>
-      <c r="AW4">
-        <v>7</v>
-      </c>
-      <c r="AX4">
-        <v>7.8</v>
-      </c>
-      <c r="AY4">
-        <v>8.6</v>
-      </c>
-      <c r="AZ4">
-        <v>20</v>
-      </c>
-      <c r="BA4">
-        <v>7</v>
-      </c>
-      <c r="BB4">
-        <v>12.5</v>
-      </c>
-      <c r="BC4">
-        <v>14.5</v>
-      </c>
-      <c r="BD4">
-        <v>14.5</v>
-      </c>
       <c r="BE4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BF4">
+        <v>4.8</v>
+      </c>
+      <c r="BG4">
         <v>8</v>
       </c>
-      <c r="BG4">
-        <v>7</v>
-      </c>
       <c r="BH4">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BI4">
         <v>2.9</v>
@@ -1700,49 +1700,49 @@
         <v>13</v>
       </c>
       <c r="BK4">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BN4">
         <v>4.5</v>
       </c>
       <c r="BO4">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="BP4">
         <v>12</v>
       </c>
       <c r="BQ4">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BR4">
         <v>32</v>
       </c>
       <c r="BS4">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BT4">
         <v>12</v>
       </c>
       <c r="BU4">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -1771,10 +1771,10 @@
         <v>128</v>
       </c>
       <c r="F5">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="G5">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="H5">
         <v>1.77</v>
@@ -1783,190 +1783,190 @@
         <v>1.91</v>
       </c>
       <c r="J5">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L5">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M5">
         <v>1.07</v>
       </c>
       <c r="N5">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O5">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="P5">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q5">
         <v>1.92</v>
       </c>
       <c r="R5">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S5">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="T5">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="U5">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="V5">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="W5">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X5">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z5">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA5">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AB5">
+        <v>18</v>
+      </c>
+      <c r="AC5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD5">
+        <v>10.5</v>
+      </c>
+      <c r="AE5">
+        <v>20</v>
+      </c>
+      <c r="AF5">
+        <v>42</v>
+      </c>
+      <c r="AG5">
         <v>21</v>
       </c>
-      <c r="AC5">
-        <v>9</v>
-      </c>
-      <c r="AD5">
-        <v>12.5</v>
-      </c>
-      <c r="AE5">
-        <v>24</v>
-      </c>
-      <c r="AF5">
-        <v>48</v>
-      </c>
-      <c r="AG5">
-        <v>24</v>
-      </c>
       <c r="AH5">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI5">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AJ5">
         <v>470</v>
       </c>
       <c r="AK5">
+        <v>80</v>
+      </c>
+      <c r="AL5">
         <v>85</v>
       </c>
-      <c r="AL5">
-        <v>90</v>
-      </c>
       <c r="AM5">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="AN5">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AO5">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="AP5">
+        <v>6</v>
+      </c>
+      <c r="AQ5">
+        <v>5.1</v>
+      </c>
+      <c r="AR5">
+        <v>5.2</v>
+      </c>
+      <c r="AS5">
+        <v>9</v>
+      </c>
+      <c r="AT5">
+        <v>6.2</v>
+      </c>
+      <c r="AU5">
+        <v>5.1</v>
+      </c>
+      <c r="AV5">
+        <v>7</v>
+      </c>
+      <c r="AW5">
+        <v>9</v>
+      </c>
+      <c r="AX5">
+        <v>7.8</v>
+      </c>
+      <c r="AY5">
+        <v>9</v>
+      </c>
+      <c r="AZ5">
+        <v>9</v>
+      </c>
+      <c r="BA5">
+        <v>7.6</v>
+      </c>
+      <c r="BB5">
+        <v>9</v>
+      </c>
+      <c r="BC5">
+        <v>8.6</v>
+      </c>
+      <c r="BD5">
+        <v>8.6</v>
+      </c>
+      <c r="BE5">
+        <v>9</v>
+      </c>
+      <c r="BF5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG5">
+        <v>5.3</v>
+      </c>
+      <c r="BH5">
+        <v>4</v>
+      </c>
+      <c r="BI5">
+        <v>3.05</v>
+      </c>
+      <c r="BJ5">
         <v>12</v>
       </c>
-      <c r="AQ5">
-        <v>7.4</v>
-      </c>
-      <c r="AR5">
-        <v>9.4</v>
-      </c>
-      <c r="AS5">
-        <v>4</v>
-      </c>
-      <c r="AT5">
-        <v>3.9</v>
-      </c>
-      <c r="AU5">
-        <v>7.4</v>
-      </c>
-      <c r="AV5">
-        <v>8.6</v>
-      </c>
-      <c r="AW5">
-        <v>4</v>
-      </c>
-      <c r="AX5">
-        <v>4.3</v>
-      </c>
-      <c r="AY5">
-        <v>4</v>
-      </c>
-      <c r="AZ5">
-        <v>4</v>
-      </c>
-      <c r="BA5">
-        <v>4.3</v>
-      </c>
-      <c r="BB5">
-        <v>4.6</v>
-      </c>
-      <c r="BC5">
-        <v>4.5</v>
-      </c>
-      <c r="BD5">
-        <v>4.5</v>
-      </c>
-      <c r="BE5">
-        <v>4.6</v>
-      </c>
-      <c r="BF5">
-        <v>4.5</v>
-      </c>
-      <c r="BG5">
-        <v>3.8</v>
-      </c>
-      <c r="BH5">
-        <v>3.5</v>
-      </c>
-      <c r="BI5">
-        <v>3</v>
-      </c>
-      <c r="BJ5">
-        <v>12.5</v>
-      </c>
       <c r="BK5">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="BN5">
         <v>10</v>
       </c>
       <c r="BO5">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="BP5">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="BR5">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BS5">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="BT5">
         <v>5.2</v>
@@ -1975,16 +1975,16 @@
         <v>3.45</v>
       </c>
       <c r="BV5">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BW5">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="BX5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY5">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="BZ5">
         <v>0</v>
@@ -2031,19 +2031,19 @@
         <v>4.3</v>
       </c>
       <c r="L6">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M6">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N6">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O6">
         <v>1.2</v>
       </c>
       <c r="P6">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q6">
         <v>1.59</v>
@@ -2052,7 +2052,7 @@
         <v>1.6</v>
       </c>
       <c r="S6">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="T6">
         <v>1.57</v>
@@ -2094,16 +2094,16 @@
         <v>34</v>
       </c>
       <c r="AG6">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH6">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI6">
         <v>26</v>
       </c>
       <c r="AJ6">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AK6">
         <v>42</v>
@@ -2169,7 +2169,7 @@
         <v>46</v>
       </c>
       <c r="BF6">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BG6">
         <v>8</v>
@@ -2190,10 +2190,10 @@
         <v>95</v>
       </c>
       <c r="BM6">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BN6">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BO6">
         <v>5.7</v>
@@ -2202,13 +2202,13 @@
         <v>30</v>
       </c>
       <c r="BQ6">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BR6">
         <v>38</v>
       </c>
       <c r="BS6">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BT6">
         <v>6.2</v>
@@ -2220,13 +2220,13 @@
         <v>13.5</v>
       </c>
       <c r="BW6">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="BX6">
         <v>26</v>
       </c>
       <c r="BY6">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BZ6">
         <v>18.5</v>
@@ -2255,13 +2255,13 @@
         <v>130</v>
       </c>
       <c r="F7">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="G7">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="H7">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="I7">
         <v>17.5</v>
@@ -2270,13 +2270,13 @@
         <v>5.7</v>
       </c>
       <c r="K7">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="L7">
         <v>1.4</v>
       </c>
       <c r="M7">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N7">
         <v>4</v>
@@ -2288,7 +2288,7 @@
         <v>2.04</v>
       </c>
       <c r="Q7">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R7">
         <v>1.38</v>
@@ -2297,31 +2297,31 @@
         <v>3.45</v>
       </c>
       <c r="T7">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="U7">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="V7">
         <v>1.06</v>
       </c>
       <c r="W7">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="X7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y7">
         <v>85</v>
       </c>
       <c r="Z7">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AA7">
         <v>1000</v>
       </c>
       <c r="AB7">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AC7">
         <v>14</v>
@@ -2330,31 +2330,31 @@
         <v>160</v>
       </c>
       <c r="AE7">
-        <v>490</v>
+        <v>530</v>
       </c>
       <c r="AF7">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AG7">
         <v>12</v>
       </c>
       <c r="AH7">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AI7">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="AJ7">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AK7">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL7">
-        <v>160</v>
+        <v>330</v>
       </c>
       <c r="AM7">
-        <v>430</v>
+        <v>380</v>
       </c>
       <c r="AN7">
         <v>6.6</v>
@@ -2363,28 +2363,28 @@
         <v>1000</v>
       </c>
       <c r="AP7">
+        <v>14.5</v>
+      </c>
+      <c r="AQ7">
+        <v>19.5</v>
+      </c>
+      <c r="AR7">
+        <v>10</v>
+      </c>
+      <c r="AS7">
         <v>10.5</v>
       </c>
-      <c r="AQ7">
-        <v>14.5</v>
-      </c>
-      <c r="AR7">
-        <v>11.5</v>
-      </c>
-      <c r="AS7">
-        <v>12.5</v>
-      </c>
       <c r="AT7">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU7">
         <v>11.5</v>
       </c>
       <c r="AV7">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AW7">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AX7">
         <v>5.8</v>
@@ -2393,88 +2393,88 @@
         <v>10</v>
       </c>
       <c r="AZ7">
+        <v>17.5</v>
+      </c>
+      <c r="BA7">
         <v>10</v>
       </c>
-      <c r="BA7">
-        <v>12</v>
-      </c>
       <c r="BB7">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC7">
         <v>15</v>
       </c>
       <c r="BD7">
+        <v>9</v>
+      </c>
+      <c r="BE7">
+        <v>10</v>
+      </c>
+      <c r="BF7">
+        <v>5.7</v>
+      </c>
+      <c r="BG7">
+        <v>11.5</v>
+      </c>
+      <c r="BH7">
+        <v>4.2</v>
+      </c>
+      <c r="BI7">
+        <v>2.9</v>
+      </c>
+      <c r="BJ7">
+        <v>15.5</v>
+      </c>
+      <c r="BK7">
+        <v>5.3</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>8</v>
+      </c>
+      <c r="BN7">
+        <v>3.55</v>
+      </c>
+      <c r="BO7">
+        <v>3</v>
+      </c>
+      <c r="BP7">
+        <v>7.8</v>
+      </c>
+      <c r="BQ7">
+        <v>4</v>
+      </c>
+      <c r="BR7">
+        <v>32</v>
+      </c>
+      <c r="BS7">
+        <v>6.4</v>
+      </c>
+      <c r="BT7">
+        <v>18</v>
+      </c>
+      <c r="BU7">
+        <v>5.6</v>
+      </c>
+      <c r="BV7">
+        <v>1000</v>
+      </c>
+      <c r="BW7">
+        <v>7.8</v>
+      </c>
+      <c r="BX7">
+        <v>1000</v>
+      </c>
+      <c r="BY7">
+        <v>7.8</v>
+      </c>
+      <c r="BZ7">
+        <v>15</v>
+      </c>
+      <c r="CA7">
         <v>10.5</v>
-      </c>
-      <c r="BE7">
-        <v>12</v>
-      </c>
-      <c r="BF7">
-        <v>5.4</v>
-      </c>
-      <c r="BG7">
-        <v>13.5</v>
-      </c>
-      <c r="BH7">
-        <v>1000</v>
-      </c>
-      <c r="BI7">
-        <v>1.04</v>
-      </c>
-      <c r="BJ7">
-        <v>1000</v>
-      </c>
-      <c r="BK7">
-        <v>1.04</v>
-      </c>
-      <c r="BL7">
-        <v>1000</v>
-      </c>
-      <c r="BM7">
-        <v>1.04</v>
-      </c>
-      <c r="BN7">
-        <v>1000</v>
-      </c>
-      <c r="BO7">
-        <v>1.04</v>
-      </c>
-      <c r="BP7">
-        <v>1000</v>
-      </c>
-      <c r="BQ7">
-        <v>1.04</v>
-      </c>
-      <c r="BR7">
-        <v>1000</v>
-      </c>
-      <c r="BS7">
-        <v>1.04</v>
-      </c>
-      <c r="BT7">
-        <v>1000</v>
-      </c>
-      <c r="BU7">
-        <v>1.04</v>
-      </c>
-      <c r="BV7">
-        <v>1000</v>
-      </c>
-      <c r="BW7">
-        <v>1.04</v>
-      </c>
-      <c r="BX7">
-        <v>1000</v>
-      </c>
-      <c r="BY7">
-        <v>1.04</v>
-      </c>
-      <c r="BZ7">
-        <v>1000</v>
-      </c>
-      <c r="CA7">
-        <v>1.04</v>
       </c>
       <c r="CB7" t="s">
         <v>145</v>
@@ -2500,16 +2500,16 @@
         <v>4.2</v>
       </c>
       <c r="G8">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H8">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I8">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="J8">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K8">
         <v>3.05</v>
@@ -2524,40 +2524,40 @@
         <v>2.52</v>
       </c>
       <c r="O8">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="P8">
         <v>1.47</v>
       </c>
       <c r="Q8">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="R8">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S8">
         <v>6.2</v>
       </c>
       <c r="T8">
-        <v>2.24</v>
+        <v>2.02</v>
       </c>
       <c r="U8">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V8">
         <v>1.75</v>
       </c>
       <c r="W8">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X8">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="Y8">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="Z8">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA8">
         <v>40</v>
@@ -2572,151 +2572,151 @@
         <v>12.5</v>
       </c>
       <c r="AE8">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF8">
         <v>36</v>
       </c>
       <c r="AG8">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="AH8">
         <v>32</v>
       </c>
       <c r="AI8">
-        <v>190</v>
+        <v>90</v>
       </c>
       <c r="AJ8">
         <v>900</v>
       </c>
       <c r="AK8">
-        <v>440</v>
+        <v>230</v>
       </c>
       <c r="AL8">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="AM8">
         <v>500</v>
       </c>
       <c r="AN8">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO8">
         <v>44</v>
       </c>
       <c r="AP8">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AQ8">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AR8">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AS8">
-        <v>5.9</v>
+        <v>23</v>
       </c>
       <c r="AT8">
         <v>9.4</v>
       </c>
       <c r="AU8">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV8">
         <v>10.5</v>
       </c>
       <c r="AW8">
-        <v>5.9</v>
+        <v>23</v>
       </c>
       <c r="AX8">
-        <v>5.8</v>
+        <v>23</v>
       </c>
       <c r="AY8">
         <v>16.5</v>
       </c>
       <c r="AZ8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA8">
-        <v>6.4</v>
+        <v>46</v>
       </c>
       <c r="BB8">
-        <v>6.6</v>
+        <v>70</v>
       </c>
       <c r="BC8">
-        <v>6.4</v>
+        <v>50</v>
       </c>
       <c r="BD8">
-        <v>6.4</v>
+        <v>60</v>
       </c>
       <c r="BE8">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF8">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG8">
-        <v>5.9</v>
+        <v>25</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>2.94</v>
       </c>
       <c r="BI8">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK8">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BO8">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BQ8">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BS8">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BU8">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW8">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY8">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="CA8">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="CB8" t="s">
         <v>145</v>
@@ -2739,52 +2739,52 @@
         <v>132</v>
       </c>
       <c r="F9">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="G9">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="H9">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="I9">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="J9">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K9">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="L9">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M9">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N9">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O9">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P9">
+        <v>1.83</v>
+      </c>
+      <c r="Q9">
+        <v>2.08</v>
+      </c>
+      <c r="R9">
+        <v>1.31</v>
+      </c>
+      <c r="S9">
+        <v>3.7</v>
+      </c>
+      <c r="T9">
         <v>1.79</v>
       </c>
-      <c r="Q9">
+      <c r="U9">
         <v>2.06</v>
-      </c>
-      <c r="R9">
-        <v>1.29</v>
-      </c>
-      <c r="S9">
-        <v>3.75</v>
-      </c>
-      <c r="T9">
-        <v>1.11</v>
-      </c>
-      <c r="U9">
-        <v>1.11</v>
       </c>
       <c r="V9">
         <v>1.55</v>
@@ -2793,172 +2793,172 @@
         <v>1.48</v>
       </c>
       <c r="X9">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Y9">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Z9">
-        <v>500</v>
+        <v>18.5</v>
       </c>
       <c r="AA9">
-        <v>900</v>
+        <v>55</v>
       </c>
       <c r="AB9">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AC9">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="AD9">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AE9">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="AF9">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AG9">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AH9">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AI9">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AJ9">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AK9">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="AL9">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AM9">
         <v>580</v>
       </c>
       <c r="AN9">
-        <v>500</v>
+        <v>46</v>
       </c>
       <c r="AO9">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AP9">
-        <v>1.68</v>
+        <v>5.4</v>
       </c>
       <c r="AQ9">
-        <v>1.68</v>
+        <v>6.2</v>
       </c>
       <c r="AR9">
-        <v>1.79</v>
+        <v>6</v>
       </c>
       <c r="AS9">
-        <v>1.8</v>
+        <v>7.4</v>
       </c>
       <c r="AT9">
-        <v>1.67</v>
+        <v>5</v>
       </c>
       <c r="AU9">
-        <v>1.62</v>
+        <v>4.2</v>
       </c>
       <c r="AV9">
-        <v>1.72</v>
+        <v>8.4</v>
       </c>
       <c r="AW9">
-        <v>1.79</v>
+        <v>7</v>
       </c>
       <c r="AX9">
-        <v>1.75</v>
+        <v>6.2</v>
       </c>
       <c r="AY9">
-        <v>1.7</v>
+        <v>5.5</v>
       </c>
       <c r="AZ9">
-        <v>1.77</v>
+        <v>6</v>
       </c>
       <c r="BA9">
-        <v>1.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB9">
-        <v>1.8</v>
+        <v>7.6</v>
       </c>
       <c r="BC9">
-        <v>1.79</v>
+        <v>7.2</v>
       </c>
       <c r="BD9">
-        <v>1.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE9">
-        <v>1.82</v>
+        <v>8.4</v>
       </c>
       <c r="BF9">
-        <v>1.78</v>
+        <v>7.2</v>
       </c>
       <c r="BG9">
+        <v>7</v>
+      </c>
+      <c r="BH9">
+        <v>3.35</v>
+      </c>
+      <c r="BI9">
+        <v>2.68</v>
+      </c>
+      <c r="BJ9">
+        <v>10</v>
+      </c>
+      <c r="BK9">
+        <v>5</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>2.46</v>
+      </c>
+      <c r="BN9">
         <v>6.2</v>
       </c>
-      <c r="BH9">
-        <v>1000</v>
-      </c>
-      <c r="BI9">
-        <v>1.04</v>
-      </c>
-      <c r="BJ9">
-        <v>1000</v>
-      </c>
-      <c r="BK9">
-        <v>1.04</v>
-      </c>
-      <c r="BL9">
-        <v>1000</v>
-      </c>
-      <c r="BM9">
-        <v>1.04</v>
-      </c>
-      <c r="BN9">
-        <v>1000</v>
-      </c>
       <c r="BO9">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ9">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU9">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW9">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA9">
-        <v>1.04</v>
+        <v>2.34</v>
       </c>
       <c r="CB9" t="s">
         <v>145</v>
@@ -2981,7 +2981,7 @@
         <v>133</v>
       </c>
       <c r="F10">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="G10">
         <v>1.86</v>
@@ -2993,7 +2993,7 @@
         <v>6.6</v>
       </c>
       <c r="J10">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K10">
         <v>3.7</v>
@@ -3011,19 +3011,19 @@
         <v>1.49</v>
       </c>
       <c r="P10">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q10">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R10">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S10">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="T10">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U10">
         <v>1.71</v>
@@ -3035,7 +3035,7 @@
         <v>2.16</v>
       </c>
       <c r="X10">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y10">
         <v>15.5</v>
@@ -3053,7 +3053,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD10">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="AE10">
         <v>700</v>
@@ -3062,19 +3062,19 @@
         <v>9.6</v>
       </c>
       <c r="AG10">
+        <v>11</v>
+      </c>
+      <c r="AH10">
         <v>36</v>
-      </c>
-      <c r="AH10">
-        <v>65</v>
       </c>
       <c r="AI10">
         <v>700</v>
       </c>
       <c r="AJ10">
+        <v>24</v>
+      </c>
+      <c r="AK10">
         <v>34</v>
-      </c>
-      <c r="AK10">
-        <v>65</v>
       </c>
       <c r="AL10">
         <v>70</v>
@@ -3089,16 +3089,16 @@
         <v>700</v>
       </c>
       <c r="AP10">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ10">
         <v>13</v>
       </c>
       <c r="AR10">
-        <v>8.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="AS10">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT10">
         <v>5.7</v>
@@ -3110,7 +3110,7 @@
         <v>18</v>
       </c>
       <c r="AW10">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="AX10">
         <v>8.4</v>
@@ -3119,10 +3119,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ10">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="BA10">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="BB10">
         <v>17</v>
@@ -3131,16 +3131,16 @@
         <v>20</v>
       </c>
       <c r="BD10">
-        <v>8.4</v>
+        <v>32</v>
       </c>
       <c r="BE10">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF10">
         <v>16</v>
       </c>
       <c r="BG10">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH10">
         <v>3.3</v>
@@ -3223,13 +3223,13 @@
         <v>134</v>
       </c>
       <c r="F11">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G11">
         <v>2.06</v>
       </c>
       <c r="H11">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I11">
         <v>4.5</v>
@@ -3247,7 +3247,7 @@
         <v>1.1</v>
       </c>
       <c r="N11">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O11">
         <v>1.46</v>
@@ -3268,7 +3268,7 @@
         <v>2.08</v>
       </c>
       <c r="U11">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="V11">
         <v>1.28</v>
@@ -3283,16 +3283,16 @@
         <v>12.5</v>
       </c>
       <c r="Z11">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA11">
         <v>110</v>
       </c>
       <c r="AB11">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC11">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD11">
         <v>17.5</v>
@@ -3304,13 +3304,13 @@
         <v>11</v>
       </c>
       <c r="AG11">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH11">
         <v>22</v>
       </c>
       <c r="AI11">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AJ11">
         <v>25</v>
@@ -3319,16 +3319,16 @@
         <v>24</v>
       </c>
       <c r="AL11">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM11">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AN11">
         <v>20</v>
       </c>
       <c r="AO11">
-        <v>490</v>
+        <v>110</v>
       </c>
       <c r="AP11">
         <v>9.800000000000001</v>
@@ -3340,7 +3340,7 @@
         <v>28</v>
       </c>
       <c r="AS11">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AT11">
         <v>7</v>
@@ -3361,13 +3361,13 @@
         <v>10</v>
       </c>
       <c r="AZ11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA11">
         <v>75</v>
       </c>
       <c r="BB11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC11">
         <v>22</v>
@@ -3379,34 +3379,34 @@
         <v>100</v>
       </c>
       <c r="BF11">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BG11">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BH11">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="BI11">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="BJ11">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK11">
         <v>9.800000000000001</v>
       </c>
       <c r="BL11">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="BM11">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BN11">
         <v>4.5</v>
       </c>
       <c r="BO11">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP11">
         <v>16</v>
@@ -3418,7 +3418,7 @@
         <v>34</v>
       </c>
       <c r="BS11">
-        <v>12.5</v>
+        <v>30</v>
       </c>
       <c r="BT11">
         <v>7.6</v>
@@ -3430,19 +3430,19 @@
         <v>42</v>
       </c>
       <c r="BW11">
-        <v>13.5</v>
+        <v>36</v>
       </c>
       <c r="BX11">
         <v>60</v>
       </c>
       <c r="BY11">
-        <v>15.5</v>
+        <v>22</v>
       </c>
       <c r="BZ11">
         <v>34</v>
       </c>
       <c r="CA11">
-        <v>12.5</v>
+        <v>30</v>
       </c>
       <c r="CB11" t="s">
         <v>145</v>
@@ -3465,16 +3465,16 @@
         <v>135</v>
       </c>
       <c r="F12">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G12">
         <v>1.66</v>
       </c>
       <c r="H12">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I12">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J12">
         <v>4.4</v>
@@ -3489,22 +3489,22 @@
         <v>1.04</v>
       </c>
       <c r="N12">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O12">
         <v>1.2</v>
       </c>
       <c r="P12">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q12">
         <v>1.62</v>
       </c>
       <c r="R12">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S12">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="T12">
         <v>1.68</v>
@@ -3555,10 +3555,10 @@
         <v>70</v>
       </c>
       <c r="AJ12">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK12">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL12">
         <v>34</v>
@@ -3567,22 +3567,22 @@
         <v>95</v>
       </c>
       <c r="AN12">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AO12">
         <v>70</v>
       </c>
       <c r="AP12">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ12">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AR12">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS12">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT12">
         <v>10</v>
@@ -3591,10 +3591,10 @@
         <v>9.6</v>
       </c>
       <c r="AV12">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AW12">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AX12">
         <v>10.5</v>
@@ -3603,88 +3603,88 @@
         <v>9</v>
       </c>
       <c r="AZ12">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BA12">
-        <v>6.4</v>
+        <v>40</v>
       </c>
       <c r="BB12">
         <v>14.5</v>
       </c>
       <c r="BC12">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="BD12">
         <v>14.5</v>
       </c>
       <c r="BE12">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF12">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BG12">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH12">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BI12">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BJ12">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK12">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BN12">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO12">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BP12">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ12">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BR12">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS12">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BT12">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU12">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BV12">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW12">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BX12">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY12">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BZ12">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="CA12">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="CB12" t="s">
         <v>145</v>
@@ -3710,7 +3710,7 @@
         <v>1.31</v>
       </c>
       <c r="G13">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="H13">
         <v>8</v>
@@ -3722,7 +3722,7 @@
         <v>5.6</v>
       </c>
       <c r="K13">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="L13">
         <v>1.24</v>
@@ -3731,28 +3731,28 @@
         <v>1.03</v>
       </c>
       <c r="N13">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O13">
         <v>1.15</v>
       </c>
       <c r="P13">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="Q13">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="R13">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="S13">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="T13">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U13">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V13">
         <v>1.09</v>
@@ -3770,7 +3770,7 @@
         <v>450</v>
       </c>
       <c r="AA13">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="AB13">
         <v>13</v>
@@ -3779,10 +3779,10 @@
         <v>16</v>
       </c>
       <c r="AD13">
-        <v>40</v>
+        <v>950</v>
       </c>
       <c r="AE13">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AF13">
         <v>11</v>
@@ -3803,40 +3803,40 @@
         <v>15</v>
       </c>
       <c r="AL13">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AM13">
         <v>260</v>
       </c>
       <c r="AN13">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AO13">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AP13">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ13">
-        <v>20</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR13">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AS13">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT13">
         <v>7.6</v>
       </c>
       <c r="AU13">
-        <v>12</v>
+        <v>5.5</v>
       </c>
       <c r="AV13">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="AW13">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX13">
         <v>6.2</v>
@@ -3845,82 +3845,82 @@
         <v>6.4</v>
       </c>
       <c r="AZ13">
-        <v>16</v>
+        <v>6.4</v>
       </c>
       <c r="BA13">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB13">
         <v>7</v>
       </c>
       <c r="BC13">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="BD13">
-        <v>19</v>
+        <v>6.6</v>
       </c>
       <c r="BE13">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BF13">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="BG13">
-        <v>13.5</v>
+        <v>8</v>
       </c>
       <c r="BH13">
+        <v>5.8</v>
+      </c>
+      <c r="BI13">
+        <v>3.8</v>
+      </c>
+      <c r="BJ13">
+        <v>12</v>
+      </c>
+      <c r="BK13">
+        <v>8.4</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
         <v>5.9</v>
       </c>
-      <c r="BI13">
-        <v>3.85</v>
-      </c>
-      <c r="BJ13">
-        <v>13.5</v>
-      </c>
-      <c r="BK13">
-        <v>3.5</v>
-      </c>
-      <c r="BL13">
-        <v>1000</v>
-      </c>
-      <c r="BM13">
-        <v>4.5</v>
-      </c>
       <c r="BN13">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="BO13">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="BP13">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BQ13">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BR13">
         <v>24</v>
       </c>
       <c r="BS13">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="BT13">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BU13">
-        <v>3.6</v>
+        <v>10</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="BZ13">
         <v>0</v>
@@ -3955,16 +3955,16 @@
         <v>1.26</v>
       </c>
       <c r="H14">
+        <v>14</v>
+      </c>
+      <c r="I14">
         <v>14.5</v>
       </c>
-      <c r="I14">
-        <v>15</v>
-      </c>
       <c r="J14">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="K14">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="L14">
         <v>1.24</v>
@@ -3973,28 +3973,28 @@
         <v>1.02</v>
       </c>
       <c r="N14">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O14">
         <v>1.13</v>
       </c>
       <c r="P14">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q14">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="R14">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="S14">
+        <v>2.04</v>
+      </c>
+      <c r="T14">
+        <v>1.9</v>
+      </c>
+      <c r="U14">
         <v>2.06</v>
-      </c>
-      <c r="T14">
-        <v>1.91</v>
-      </c>
-      <c r="U14">
-        <v>2.04</v>
       </c>
       <c r="V14">
         <v>1.07</v>
@@ -4015,46 +4015,46 @@
         <v>560</v>
       </c>
       <c r="AB14">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC14">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AD14">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AE14">
-        <v>270</v>
+        <v>190</v>
       </c>
       <c r="AF14">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG14">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH14">
         <v>29</v>
       </c>
       <c r="AI14">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ14">
         <v>10.5</v>
       </c>
       <c r="AK14">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AL14">
         <v>32</v>
       </c>
       <c r="AM14">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN14">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AO14">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="AP14">
         <v>34</v>
@@ -4066,37 +4066,37 @@
         <v>120</v>
       </c>
       <c r="AS14">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AT14">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU14">
         <v>16</v>
       </c>
       <c r="AV14">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AW14">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AX14">
         <v>8.800000000000001</v>
       </c>
       <c r="AY14">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA14">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BB14">
         <v>9.800000000000001</v>
       </c>
       <c r="BC14">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BD14">
         <v>30</v>
@@ -4105,19 +4105,19 @@
         <v>100</v>
       </c>
       <c r="BF14">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="BG14">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="BH14">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BI14">
         <v>4.8</v>
       </c>
       <c r="BJ14">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK14">
         <v>10</v>
@@ -4126,19 +4126,19 @@
         <v>130</v>
       </c>
       <c r="BM14">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BN14">
         <v>4.1</v>
       </c>
       <c r="BO14">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BP14">
         <v>6.6</v>
       </c>
       <c r="BQ14">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR14">
         <v>19.5</v>
@@ -4150,13 +4150,13 @@
         <v>15.5</v>
       </c>
       <c r="BU14">
+        <v>13.5</v>
+      </c>
+      <c r="BV14">
+        <v>85</v>
+      </c>
+      <c r="BW14">
         <v>13</v>
-      </c>
-      <c r="BV14">
-        <v>100</v>
-      </c>
-      <c r="BW14">
-        <v>13.5</v>
       </c>
       <c r="BX14">
         <v>70</v>
@@ -4168,7 +4168,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="CA14">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="CB14" t="s">
         <v>145</v>
@@ -4191,16 +4191,16 @@
         <v>138</v>
       </c>
       <c r="F15">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="G15">
         <v>1.55</v>
       </c>
       <c r="H15">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="I15">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="J15">
         <v>3.9</v>
@@ -4212,73 +4212,73 @@
         <v>1.54</v>
       </c>
       <c r="M15">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N15">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="O15">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P15">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q15">
+        <v>2.48</v>
+      </c>
+      <c r="R15">
+        <v>1.22</v>
+      </c>
+      <c r="S15">
+        <v>4.8</v>
+      </c>
+      <c r="T15">
         <v>2.5</v>
       </c>
-      <c r="R15">
-        <v>1.21</v>
-      </c>
-      <c r="S15">
-        <v>5</v>
-      </c>
-      <c r="T15">
-        <v>2.58</v>
-      </c>
       <c r="U15">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="V15">
         <v>1.11</v>
       </c>
       <c r="W15">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="X15">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y15">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z15">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AA15">
-        <v>1000</v>
+        <v>570</v>
       </c>
       <c r="AB15">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AC15">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD15">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AE15">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="AF15">
         <v>7.4</v>
       </c>
       <c r="AG15">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH15">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AI15">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="AJ15">
         <v>15.5</v>
@@ -4287,10 +4287,10 @@
         <v>25</v>
       </c>
       <c r="AL15">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM15">
-        <v>420</v>
+        <v>380</v>
       </c>
       <c r="AN15">
         <v>13</v>
@@ -4299,118 +4299,118 @@
         <v>1000</v>
       </c>
       <c r="AP15">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ15">
         <v>19</v>
       </c>
       <c r="AR15">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AS15">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT15">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AU15">
         <v>8.6</v>
       </c>
       <c r="AV15">
+        <v>6.4</v>
+      </c>
+      <c r="AW15">
+        <v>7.4</v>
+      </c>
+      <c r="AX15">
         <v>5.8</v>
       </c>
-      <c r="AW15">
+      <c r="AY15">
+        <v>9.6</v>
+      </c>
+      <c r="AZ15">
         <v>6.4</v>
       </c>
-      <c r="AX15">
-        <v>5.7</v>
-      </c>
-      <c r="AY15">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ15">
-        <v>5.7</v>
-      </c>
       <c r="BA15">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BB15">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BC15">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD15">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BE15">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BF15">
         <v>9.800000000000001</v>
       </c>
       <c r="BG15">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BH15">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI15">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="BJ15">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BK15">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BN15">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BO15">
-        <v>1.04</v>
+        <v>2.98</v>
       </c>
       <c r="BP15">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ15">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BR15">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS15">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BT15">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BU15">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BZ15">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA15">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="CB15" t="s">
         <v>145</v>
@@ -4433,7 +4433,7 @@
         <v>139</v>
       </c>
       <c r="F16">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="G16">
         <v>4.2</v>
@@ -4442,31 +4442,31 @@
         <v>1.77</v>
       </c>
       <c r="I16">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="J16">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="K16">
         <v>5.6</v>
       </c>
       <c r="L16">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="M16">
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>10.5</v>
+        <v>3.45</v>
       </c>
       <c r="O16">
         <v>1.08</v>
       </c>
       <c r="P16">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Q16">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="R16">
         <v>2.3</v>
@@ -4475,10 +4475,10 @@
         <v>1.67</v>
       </c>
       <c r="T16">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="U16">
-        <v>1.11</v>
+        <v>3.1</v>
       </c>
       <c r="V16">
         <v>2.12</v>
@@ -4487,166 +4487,166 @@
         <v>1.33</v>
       </c>
       <c r="X16">
-        <v>950</v>
+        <v>160</v>
       </c>
       <c r="Y16">
-        <v>950</v>
+        <v>30</v>
       </c>
       <c r="Z16">
+        <v>26</v>
+      </c>
+      <c r="AA16">
+        <v>29</v>
+      </c>
+      <c r="AB16">
+        <v>46</v>
+      </c>
+      <c r="AC16">
+        <v>16.5</v>
+      </c>
+      <c r="AD16">
+        <v>15.5</v>
+      </c>
+      <c r="AE16">
+        <v>19.5</v>
+      </c>
+      <c r="AF16">
+        <v>120</v>
+      </c>
+      <c r="AG16">
+        <v>23</v>
+      </c>
+      <c r="AH16">
+        <v>17.5</v>
+      </c>
+      <c r="AI16">
+        <v>23</v>
+      </c>
+      <c r="AJ16">
         <v>500</v>
       </c>
-      <c r="AA16">
-        <v>900</v>
-      </c>
-      <c r="AB16">
-        <v>950</v>
-      </c>
-      <c r="AC16">
-        <v>970</v>
-      </c>
-      <c r="AD16">
-        <v>970</v>
-      </c>
-      <c r="AE16">
-        <v>970</v>
-      </c>
-      <c r="AF16">
-        <v>500</v>
-      </c>
-      <c r="AG16">
-        <v>950</v>
-      </c>
-      <c r="AH16">
-        <v>970</v>
-      </c>
-      <c r="AI16">
-        <v>500</v>
-      </c>
-      <c r="AJ16">
-        <v>900</v>
-      </c>
       <c r="AK16">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AL16">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AM16">
-        <v>580</v>
+        <v>42</v>
       </c>
       <c r="AN16">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AO16">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="AP16">
-        <v>1.51</v>
+        <v>5.4</v>
       </c>
       <c r="AQ16">
-        <v>1.49</v>
+        <v>4.9</v>
       </c>
       <c r="AR16">
-        <v>1.48</v>
+        <v>4.8</v>
       </c>
       <c r="AS16">
-        <v>1.48</v>
+        <v>4.9</v>
       </c>
       <c r="AT16">
-        <v>1.5</v>
+        <v>5.2</v>
       </c>
       <c r="AU16">
-        <v>1.47</v>
+        <v>4.3</v>
       </c>
       <c r="AV16">
-        <v>1.44</v>
+        <v>4.3</v>
       </c>
       <c r="AW16">
-        <v>1.49</v>
+        <v>4.5</v>
       </c>
       <c r="AX16">
-        <v>1.51</v>
+        <v>5.3</v>
       </c>
       <c r="AY16">
-        <v>1.47</v>
+        <v>4.7</v>
       </c>
       <c r="AZ16">
-        <v>1.45</v>
+        <v>4.4</v>
       </c>
       <c r="BA16">
-        <v>1.47</v>
+        <v>4.7</v>
       </c>
       <c r="BB16">
-        <v>1.52</v>
+        <v>5.5</v>
       </c>
       <c r="BC16">
-        <v>1.5</v>
+        <v>5.2</v>
       </c>
       <c r="BD16">
-        <v>1.49</v>
+        <v>5</v>
       </c>
       <c r="BE16">
-        <v>1.52</v>
+        <v>5.2</v>
       </c>
       <c r="BF16">
-        <v>1.55</v>
+        <v>4.4</v>
       </c>
       <c r="BG16">
-        <v>1.38</v>
+        <v>2.7</v>
       </c>
       <c r="BH16">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BI16">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BJ16">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK16">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BL16">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BM16">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BN16">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BO16">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BP16">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BQ16">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS16">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU16">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BW16">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BY16">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BZ16">
         <v>0</v>
@@ -4675,64 +4675,64 @@
         <v>140</v>
       </c>
       <c r="F17">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="G17">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="H17">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="I17">
-        <v>38</v>
+        <v>5.5</v>
       </c>
       <c r="J17">
-        <v>2.52</v>
+        <v>3.1</v>
       </c>
       <c r="K17">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="L17">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M17">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="N17">
-        <v>1.32</v>
+        <v>2.42</v>
       </c>
       <c r="O17">
-        <v>1.13</v>
+        <v>1.48</v>
       </c>
       <c r="P17">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="Q17">
-        <v>1.5</v>
+        <v>2.02</v>
       </c>
       <c r="R17">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S17">
-        <v>1.5</v>
+        <v>4.7</v>
       </c>
       <c r="T17">
-        <v>1.11</v>
+        <v>2.08</v>
       </c>
       <c r="U17">
-        <v>1.11</v>
+        <v>1.74</v>
       </c>
       <c r="V17">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="W17">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X17">
-        <v>950</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y17">
-        <v>950</v>
+        <v>13.5</v>
       </c>
       <c r="Z17">
         <v>500</v>
@@ -4741,160 +4741,160 @@
         <v>900</v>
       </c>
       <c r="AB17">
-        <v>950</v>
+        <v>7</v>
       </c>
       <c r="AC17">
-        <v>500</v>
+        <v>8</v>
       </c>
       <c r="AD17">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="AE17">
         <v>500</v>
       </c>
       <c r="AF17">
+        <v>11.5</v>
+      </c>
+      <c r="AG17">
+        <v>11.5</v>
+      </c>
+      <c r="AH17">
         <v>500</v>
-      </c>
-      <c r="AG17">
-        <v>950</v>
-      </c>
-      <c r="AH17">
-        <v>950</v>
       </c>
       <c r="AI17">
         <v>500</v>
       </c>
       <c r="AJ17">
-        <v>900</v>
+        <v>27</v>
       </c>
       <c r="AK17">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AL17">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AM17">
         <v>500</v>
       </c>
       <c r="AN17">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="AO17">
         <v>500</v>
       </c>
       <c r="AP17">
-        <v>1.17</v>
+        <v>4.7</v>
       </c>
       <c r="AQ17">
-        <v>1.17</v>
+        <v>5.4</v>
       </c>
       <c r="AR17">
-        <v>1.16</v>
+        <v>7.2</v>
       </c>
       <c r="AS17">
-        <v>1.16</v>
+        <v>8.6</v>
       </c>
       <c r="AT17">
-        <v>1.14</v>
+        <v>3.95</v>
       </c>
       <c r="AU17">
-        <v>1.14</v>
+        <v>4.2</v>
       </c>
       <c r="AV17">
-        <v>1.15</v>
+        <v>6.4</v>
       </c>
       <c r="AW17">
-        <v>1.16</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX17">
-        <v>1.17</v>
+        <v>5</v>
       </c>
       <c r="AY17">
-        <v>1.13</v>
+        <v>5</v>
       </c>
       <c r="AZ17">
-        <v>1.17</v>
+        <v>6.6</v>
       </c>
       <c r="BA17">
-        <v>1.17</v>
+        <v>8.4</v>
       </c>
       <c r="BB17">
-        <v>1.16</v>
+        <v>6.8</v>
       </c>
       <c r="BC17">
-        <v>1.15</v>
+        <v>6.8</v>
       </c>
       <c r="BD17">
-        <v>1.16</v>
+        <v>7.8</v>
       </c>
       <c r="BE17">
-        <v>1.17</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF17">
-        <v>1.55</v>
+        <v>6.6</v>
       </c>
       <c r="BG17">
-        <v>1.17</v>
+        <v>8.6</v>
       </c>
       <c r="BH17">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="BI17">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="BJ17">
         <v>1000</v>
       </c>
       <c r="BK17">
-        <v>1.04</v>
+        <v>1.45</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>1.04</v>
+        <v>1.45</v>
       </c>
       <c r="BN17">
         <v>1000</v>
       </c>
       <c r="BO17">
-        <v>1.04</v>
+        <v>1.45</v>
       </c>
       <c r="BP17">
         <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>1.04</v>
+        <v>1.45</v>
       </c>
       <c r="BR17">
         <v>1000</v>
       </c>
       <c r="BS17">
-        <v>1.04</v>
+        <v>1.45</v>
       </c>
       <c r="BT17">
         <v>1000</v>
       </c>
       <c r="BU17">
-        <v>1.04</v>
+        <v>1.45</v>
       </c>
       <c r="BV17">
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>1.04</v>
+        <v>1.45</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>1.04</v>
+        <v>1.45</v>
       </c>
       <c r="BZ17">
         <v>1000</v>
       </c>
       <c r="CA17">
-        <v>1.04</v>
+        <v>1.45</v>
       </c>
       <c r="CB17" t="s">
         <v>145</v>
@@ -4917,97 +4917,97 @@
         <v>141</v>
       </c>
       <c r="F18">
-        <v>2.86</v>
+        <v>3.9</v>
       </c>
       <c r="G18">
-        <v>21</v>
+        <v>4.6</v>
       </c>
       <c r="H18">
-        <v>1.6</v>
+        <v>2.14</v>
       </c>
       <c r="I18">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="J18">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="K18">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="L18">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="M18">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="N18">
-        <v>1.3</v>
+        <v>2.52</v>
       </c>
       <c r="O18">
-        <v>1.08</v>
+        <v>1.56</v>
       </c>
       <c r="P18">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="Q18">
-        <v>1.47</v>
+        <v>2.7</v>
       </c>
       <c r="R18">
         <v>1.18</v>
       </c>
       <c r="S18">
-        <v>1.46</v>
+        <v>5.7</v>
       </c>
       <c r="T18">
-        <v>1.11</v>
+        <v>2.14</v>
       </c>
       <c r="U18">
-        <v>1.11</v>
+        <v>1.71</v>
       </c>
       <c r="V18">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="W18">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="X18">
-        <v>950</v>
+        <v>8.6</v>
       </c>
       <c r="Y18">
-        <v>970</v>
+        <v>7.2</v>
       </c>
       <c r="Z18">
-        <v>500</v>
+        <v>15.5</v>
       </c>
       <c r="AA18">
         <v>900</v>
       </c>
       <c r="AB18">
-        <v>950</v>
+        <v>11.5</v>
       </c>
       <c r="AC18">
-        <v>970</v>
+        <v>7.6</v>
       </c>
       <c r="AD18">
-        <v>950</v>
+        <v>14.5</v>
       </c>
       <c r="AE18">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AF18">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AG18">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="AH18">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="AI18">
         <v>500</v>
       </c>
       <c r="AJ18">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK18">
         <v>500</v>
@@ -5025,118 +5025,118 @@
         <v>500</v>
       </c>
       <c r="AP18">
-        <v>1.07</v>
+        <v>6.2</v>
       </c>
       <c r="AQ18">
-        <v>3.85</v>
+        <v>5.9</v>
       </c>
       <c r="AR18">
-        <v>5.1</v>
+        <v>10.5</v>
       </c>
       <c r="AS18">
-        <v>1.07</v>
+        <v>9</v>
       </c>
       <c r="AT18">
-        <v>1.07</v>
+        <v>8</v>
       </c>
       <c r="AU18">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AV18">
-        <v>1.07</v>
+        <v>10</v>
       </c>
       <c r="AW18">
-        <v>1.05</v>
+        <v>14.5</v>
       </c>
       <c r="AX18">
-        <v>1.07</v>
+        <v>20</v>
       </c>
       <c r="AY18">
-        <v>1.07</v>
+        <v>13.5</v>
       </c>
       <c r="AZ18">
-        <v>1.07</v>
+        <v>18</v>
       </c>
       <c r="BA18">
-        <v>1.07</v>
+        <v>6.4</v>
       </c>
       <c r="BB18">
-        <v>1.07</v>
+        <v>6.8</v>
       </c>
       <c r="BC18">
-        <v>1.07</v>
+        <v>6.6</v>
       </c>
       <c r="BD18">
-        <v>1.07</v>
+        <v>6.8</v>
       </c>
       <c r="BE18">
-        <v>1.07</v>
+        <v>7</v>
       </c>
       <c r="BF18">
-        <v>1.55</v>
+        <v>6.8</v>
       </c>
       <c r="BG18">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BH18">
-        <v>1000</v>
+        <v>2.76</v>
       </c>
       <c r="BI18">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="BJ18">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK18">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN18">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO18">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BP18">
         <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BR18">
         <v>1000</v>
       </c>
       <c r="BS18">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BT18">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BU18">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BV18">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BW18">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ18">
         <v>1000</v>
       </c>
       <c r="CA18">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="CB18" t="s">
         <v>145</v>
@@ -5159,226 +5159,226 @@
         <v>142</v>
       </c>
       <c r="F19">
-        <v>1.07</v>
+        <v>2.9</v>
       </c>
       <c r="G19">
-        <v>990</v>
+        <v>3.25</v>
       </c>
       <c r="H19">
-        <v>1.07</v>
+        <v>2.76</v>
       </c>
       <c r="I19">
-        <v>990</v>
+        <v>3.1</v>
       </c>
       <c r="J19">
-        <v>1.09</v>
+        <v>2.88</v>
       </c>
       <c r="K19">
-        <v>950</v>
+        <v>3.25</v>
       </c>
       <c r="L19">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M19">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N19">
-        <v>1.26</v>
+        <v>2.42</v>
       </c>
       <c r="O19">
-        <v>1.02</v>
+        <v>1.48</v>
       </c>
       <c r="P19">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="Q19">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="R19">
         <v>1.18</v>
       </c>
       <c r="S19">
+        <v>4.9</v>
+      </c>
+      <c r="T19">
+        <v>1.95</v>
+      </c>
+      <c r="U19">
+        <v>1.69</v>
+      </c>
+      <c r="V19">
+        <v>1.47</v>
+      </c>
+      <c r="W19">
+        <v>1.44</v>
+      </c>
+      <c r="X19">
+        <v>8.6</v>
+      </c>
+      <c r="Y19">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z19">
+        <v>21</v>
+      </c>
+      <c r="AA19">
+        <v>60</v>
+      </c>
+      <c r="AB19">
+        <v>10</v>
+      </c>
+      <c r="AC19">
+        <v>8</v>
+      </c>
+      <c r="AD19">
+        <v>16</v>
+      </c>
+      <c r="AE19">
+        <v>50</v>
+      </c>
+      <c r="AF19">
+        <v>22</v>
+      </c>
+      <c r="AG19">
+        <v>16.5</v>
+      </c>
+      <c r="AH19">
+        <v>26</v>
+      </c>
+      <c r="AI19">
+        <v>80</v>
+      </c>
+      <c r="AJ19">
+        <v>65</v>
+      </c>
+      <c r="AK19">
+        <v>55</v>
+      </c>
+      <c r="AL19">
+        <v>85</v>
+      </c>
+      <c r="AM19">
+        <v>500</v>
+      </c>
+      <c r="AN19">
+        <v>70</v>
+      </c>
+      <c r="AO19">
+        <v>60</v>
+      </c>
+      <c r="AP19">
+        <v>6.8</v>
+      </c>
+      <c r="AQ19">
+        <v>6.6</v>
+      </c>
+      <c r="AR19">
+        <v>13.5</v>
+      </c>
+      <c r="AS19">
+        <v>5.3</v>
+      </c>
+      <c r="AT19">
+        <v>7</v>
+      </c>
+      <c r="AU19">
+        <v>5.5</v>
+      </c>
+      <c r="AV19">
+        <v>10.5</v>
+      </c>
+      <c r="AW19">
+        <v>5.2</v>
+      </c>
+      <c r="AX19">
+        <v>14.5</v>
+      </c>
+      <c r="AY19">
+        <v>10.5</v>
+      </c>
+      <c r="AZ19">
+        <v>16.5</v>
+      </c>
+      <c r="BA19">
+        <v>5.4</v>
+      </c>
+      <c r="BB19">
+        <v>5.3</v>
+      </c>
+      <c r="BC19">
+        <v>5.2</v>
+      </c>
+      <c r="BD19">
+        <v>5.4</v>
+      </c>
+      <c r="BE19">
+        <v>5.6</v>
+      </c>
+      <c r="BF19">
+        <v>5.3</v>
+      </c>
+      <c r="BG19">
+        <v>5.3</v>
+      </c>
+      <c r="BH19">
+        <v>3.6</v>
+      </c>
+      <c r="BI19">
+        <v>2</v>
+      </c>
+      <c r="BJ19">
+        <v>1000</v>
+      </c>
+      <c r="BK19">
         <v>1.4</v>
       </c>
-      <c r="T19">
-        <v>1.11</v>
-      </c>
-      <c r="U19">
-        <v>1.11</v>
-      </c>
-      <c r="V19">
-        <v>1.02</v>
-      </c>
-      <c r="W19">
-        <v>1.02</v>
-      </c>
-      <c r="X19">
-        <v>1000</v>
-      </c>
-      <c r="Y19">
-        <v>1000</v>
-      </c>
-      <c r="Z19">
-        <v>1000</v>
-      </c>
-      <c r="AA19">
-        <v>1000</v>
-      </c>
-      <c r="AB19">
-        <v>1000</v>
-      </c>
-      <c r="AC19">
-        <v>1000</v>
-      </c>
-      <c r="AD19">
-        <v>1000</v>
-      </c>
-      <c r="AE19">
-        <v>1000</v>
-      </c>
-      <c r="AF19">
-        <v>1000</v>
-      </c>
-      <c r="AG19">
-        <v>1000</v>
-      </c>
-      <c r="AH19">
-        <v>1000</v>
-      </c>
-      <c r="AI19">
-        <v>1000</v>
-      </c>
-      <c r="AJ19">
-        <v>1000</v>
-      </c>
-      <c r="AK19">
-        <v>1000</v>
-      </c>
-      <c r="AL19">
-        <v>1000</v>
-      </c>
-      <c r="AM19">
-        <v>1000</v>
-      </c>
-      <c r="AN19">
-        <v>1000</v>
-      </c>
-      <c r="AO19">
-        <v>1000</v>
-      </c>
-      <c r="AP19">
-        <v>1.01</v>
-      </c>
-      <c r="AQ19">
-        <v>1.01</v>
-      </c>
-      <c r="AR19">
-        <v>1.01</v>
-      </c>
-      <c r="AS19">
-        <v>1.01</v>
-      </c>
-      <c r="AT19">
-        <v>1.01</v>
-      </c>
-      <c r="AU19">
-        <v>1.01</v>
-      </c>
-      <c r="AV19">
-        <v>1.01</v>
-      </c>
-      <c r="AW19">
-        <v>1.01</v>
-      </c>
-      <c r="AX19">
-        <v>1.01</v>
-      </c>
-      <c r="AY19">
-        <v>1.01</v>
-      </c>
-      <c r="AZ19">
-        <v>1.01</v>
-      </c>
-      <c r="BA19">
-        <v>1.01</v>
-      </c>
-      <c r="BB19">
-        <v>1.01</v>
-      </c>
-      <c r="BC19">
-        <v>1.01</v>
-      </c>
-      <c r="BD19">
-        <v>1.01</v>
-      </c>
-      <c r="BE19">
-        <v>1.01</v>
-      </c>
-      <c r="BF19">
-        <v>1.01</v>
-      </c>
-      <c r="BG19">
-        <v>1.01</v>
-      </c>
-      <c r="BH19">
-        <v>1000</v>
-      </c>
-      <c r="BI19">
-        <v>1.04</v>
-      </c>
-      <c r="BJ19">
-        <v>1000</v>
-      </c>
-      <c r="BK19">
-        <v>1.04</v>
-      </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="BN19">
         <v>1000</v>
       </c>
       <c r="BO19">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="BP19">
         <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="BT19">
         <v>1000</v>
       </c>
       <c r="BU19">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="BV19">
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="BZ19">
         <v>1000</v>
       </c>
       <c r="CA19">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="CB19" t="s">
         <v>145</v>
@@ -5404,16 +5404,16 @@
         <v>1.98</v>
       </c>
       <c r="G20">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H20">
         <v>3.65</v>
       </c>
       <c r="I20">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J20">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K20">
         <v>4.3</v>
@@ -5425,46 +5425,46 @@
         <v>1.04</v>
       </c>
       <c r="N20">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="O20">
         <v>1.18</v>
       </c>
       <c r="P20">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="Q20">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="R20">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="S20">
         <v>2.34</v>
       </c>
       <c r="T20">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="U20">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="V20">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W20">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X20">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y20">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z20">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA20">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AB20">
         <v>15.5</v>
@@ -5473,7 +5473,7 @@
         <v>11.5</v>
       </c>
       <c r="AD20">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE20">
         <v>38</v>
@@ -5500,127 +5500,127 @@
         <v>27</v>
       </c>
       <c r="AM20">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="AN20">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO20">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP20">
-        <v>11.5</v>
+        <v>6.8</v>
       </c>
       <c r="AQ20">
-        <v>17.5</v>
+        <v>6.8</v>
       </c>
       <c r="AR20">
-        <v>17</v>
+        <v>6.6</v>
       </c>
       <c r="AS20">
+        <v>7.4</v>
+      </c>
+      <c r="AT20">
         <v>7.6</v>
       </c>
-      <c r="AT20">
-        <v>12</v>
-      </c>
       <c r="AU20">
-        <v>8.6</v>
+        <v>5.1</v>
       </c>
       <c r="AV20">
-        <v>13</v>
+        <v>6.2</v>
       </c>
       <c r="AW20">
-        <v>18.5</v>
+        <v>6.8</v>
       </c>
       <c r="AX20">
+        <v>6.2</v>
+      </c>
+      <c r="AY20">
+        <v>7.8</v>
+      </c>
+      <c r="AZ20">
+        <v>8.4</v>
+      </c>
+      <c r="BA20">
+        <v>6.8</v>
+      </c>
+      <c r="BB20">
+        <v>6.4</v>
+      </c>
+      <c r="BC20">
+        <v>9</v>
+      </c>
+      <c r="BD20">
+        <v>6.6</v>
+      </c>
+      <c r="BE20">
+        <v>7.2</v>
+      </c>
+      <c r="BF20">
+        <v>4.4</v>
+      </c>
+      <c r="BG20">
+        <v>6.2</v>
+      </c>
+      <c r="BH20">
+        <v>5</v>
+      </c>
+      <c r="BI20">
+        <v>3.75</v>
+      </c>
+      <c r="BJ20">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK20">
+        <v>6.8</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>7.4</v>
+      </c>
+      <c r="BN20">
+        <v>5.6</v>
+      </c>
+      <c r="BO20">
+        <v>4.5</v>
+      </c>
+      <c r="BP20">
         <v>13.5</v>
       </c>
-      <c r="AY20">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ20">
-        <v>12.5</v>
-      </c>
-      <c r="BA20">
-        <v>21</v>
-      </c>
-      <c r="BB20">
-        <v>20</v>
-      </c>
-      <c r="BC20">
-        <v>15</v>
-      </c>
-      <c r="BD20">
-        <v>21</v>
-      </c>
-      <c r="BE20">
-        <v>8</v>
-      </c>
-      <c r="BF20">
-        <v>7.4</v>
-      </c>
-      <c r="BG20">
-        <v>19.5</v>
-      </c>
-      <c r="BH20">
-        <v>1000</v>
-      </c>
-      <c r="BI20">
-        <v>1.04</v>
-      </c>
-      <c r="BJ20">
-        <v>1000</v>
-      </c>
-      <c r="BK20">
-        <v>1.04</v>
-      </c>
-      <c r="BL20">
-        <v>1000</v>
-      </c>
-      <c r="BM20">
-        <v>1.04</v>
-      </c>
-      <c r="BN20">
-        <v>1000</v>
-      </c>
-      <c r="BO20">
-        <v>1.04</v>
-      </c>
-      <c r="BP20">
-        <v>1000</v>
-      </c>
       <c r="BQ20">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR20">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS20">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BT20">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU20">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BV20">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW20">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BX20">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY20">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BZ20">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="CA20">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="CB20" t="s">
         <v>145</v>
@@ -5643,7 +5643,7 @@
         <v>144</v>
       </c>
       <c r="F21">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="G21">
         <v>4.1</v>
@@ -5652,10 +5652,10 @@
         <v>2.22</v>
       </c>
       <c r="I21">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="J21">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K21">
         <v>3.35</v>
@@ -5664,43 +5664,43 @@
         <v>1.51</v>
       </c>
       <c r="M21">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N21">
         <v>3.05</v>
       </c>
       <c r="O21">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P21">
         <v>1.66</v>
       </c>
       <c r="Q21">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="R21">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S21">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="T21">
         <v>1.97</v>
       </c>
       <c r="U21">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V21">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W21">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X21">
         <v>10.5</v>
       </c>
       <c r="Y21">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z21">
         <v>13.5</v>
@@ -5712,19 +5712,19 @@
         <v>13.5</v>
       </c>
       <c r="AC21">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD21">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE21">
         <v>29</v>
       </c>
       <c r="AF21">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AG21">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AH21">
         <v>24</v>
@@ -5733,7 +5733,7 @@
         <v>60</v>
       </c>
       <c r="AJ21">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AK21">
         <v>65</v>
@@ -5748,16 +5748,16 @@
         <v>85</v>
       </c>
       <c r="AO21">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AP21">
         <v>9.199999999999999</v>
       </c>
       <c r="AQ21">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AR21">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AS21">
         <v>26</v>
@@ -5772,7 +5772,7 @@
         <v>10</v>
       </c>
       <c r="AW21">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AX21">
         <v>19.5</v>
@@ -5784,22 +5784,22 @@
         <v>18</v>
       </c>
       <c r="BA21">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB21">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BC21">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BD21">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BE21">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BF21">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BG21">
         <v>19.5</v>
@@ -5808,61 +5808,61 @@
         <v>3.25</v>
       </c>
       <c r="BI21">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="BJ21">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BK21">
-        <v>4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>5.9</v>
+        <v>10</v>
       </c>
       <c r="BN21">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BO21">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BP21">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BQ21">
-        <v>5.3</v>
+        <v>8.4</v>
       </c>
       <c r="BR21">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BS21">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="BT21">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="BU21">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BV21">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BW21">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BX21">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="BY21">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="BZ21">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="CA21">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="CB21" t="s">
         <v>145</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
@@ -451,7 +451,7 @@
     <t>Millonarios</t>
   </si>
   <si>
-    <t>2026-08-27 04:12:49</t>
+    <t>2026-08-27 06:29:22</t>
   </si>
 </sst>
 </file>
@@ -1045,16 +1045,16 @@
         <v>125</v>
       </c>
       <c r="F2">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G2">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H2">
         <v>4.7</v>
       </c>
       <c r="I2">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J2">
         <v>2.62</v>
@@ -1063,28 +1063,28 @@
         <v>2.76</v>
       </c>
       <c r="L2">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="M2">
         <v>1.2</v>
       </c>
       <c r="N2">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="O2">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="P2">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Q2">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="R2">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S2">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="T2">
         <v>1.11</v>
@@ -1153,58 +1153,58 @@
         <v>600</v>
       </c>
       <c r="AP2">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AQ2">
-        <v>1.71</v>
+        <v>7.8</v>
       </c>
       <c r="AR2">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AS2">
         <v>1.88</v>
       </c>
       <c r="AT2">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AU2">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AV2">
         <v>14.5</v>
       </c>
       <c r="AW2">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AX2">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AY2">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AZ2">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="BA2">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="BB2">
         <v>1.88</v>
       </c>
       <c r="BC2">
+        <v>1.79</v>
+      </c>
+      <c r="BD2">
         <v>1.83</v>
       </c>
-      <c r="BD2">
-        <v>1.87</v>
-      </c>
       <c r="BE2">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="BF2">
         <v>1.84</v>
       </c>
       <c r="BG2">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1287,22 +1287,22 @@
         <v>126</v>
       </c>
       <c r="F3">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="G3">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="H3">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="I3">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="J3">
         <v>3.85</v>
       </c>
       <c r="K3">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L3">
         <v>1.3</v>
@@ -1311,13 +1311,13 @@
         <v>1.04</v>
       </c>
       <c r="N3">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O3">
         <v>1.2</v>
       </c>
       <c r="P3">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="Q3">
         <v>1.6</v>
@@ -1326,7 +1326,7 @@
         <v>1.6</v>
       </c>
       <c r="S3">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T3">
         <v>1.55</v>
@@ -1335,7 +1335,7 @@
         <v>2.58</v>
       </c>
       <c r="V3">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W3">
         <v>1.52</v>
@@ -1392,13 +1392,13 @@
         <v>18</v>
       </c>
       <c r="AO3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AP3">
         <v>20</v>
       </c>
       <c r="AQ3">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR3">
         <v>17</v>
@@ -1434,13 +1434,13 @@
         <v>19.5</v>
       </c>
       <c r="BC3">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="BD3">
         <v>15</v>
       </c>
       <c r="BE3">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BF3">
         <v>14.5</v>
@@ -1449,7 +1449,7 @@
         <v>11.5</v>
       </c>
       <c r="BH3">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BI3">
         <v>3.5</v>
@@ -1467,16 +1467,16 @@
         <v>5.3</v>
       </c>
       <c r="BN3">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BO3">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BP3">
         <v>23</v>
       </c>
       <c r="BQ3">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BR3">
         <v>30</v>
@@ -1529,67 +1529,67 @@
         <v>127</v>
       </c>
       <c r="F4">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="G4">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="H4">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="I4">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="J4">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K4">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="L4">
         <v>1.39</v>
       </c>
       <c r="M4">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N4">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="O4">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P4">
         <v>2.04</v>
       </c>
       <c r="Q4">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="R4">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S4">
         <v>3.25</v>
       </c>
       <c r="T4">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="U4">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="V4">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="W4">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="X4">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Z4">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AA4">
         <v>700</v>
@@ -1607,22 +1607,22 @@
         <v>700</v>
       </c>
       <c r="AF4">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AG4">
         <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AI4">
         <v>700</v>
       </c>
       <c r="AJ4">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AK4">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL4">
         <v>46</v>
@@ -1631,91 +1631,91 @@
         <v>700</v>
       </c>
       <c r="AN4">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AO4">
-        <v>700</v>
+        <v>220</v>
       </c>
       <c r="AP4">
-        <v>5.7</v>
+        <v>13.5</v>
       </c>
       <c r="AQ4">
-        <v>6.2</v>
+        <v>18.5</v>
       </c>
       <c r="AR4">
+        <v>9</v>
+      </c>
+      <c r="AS4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT4">
+        <v>6.8</v>
+      </c>
+      <c r="AU4">
+        <v>8.6</v>
+      </c>
+      <c r="AV4">
+        <v>19.5</v>
+      </c>
+      <c r="AW4">
+        <v>9.4</v>
+      </c>
+      <c r="AX4">
         <v>7.6</v>
       </c>
-      <c r="AS4">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT4">
-        <v>4.5</v>
-      </c>
-      <c r="AU4">
-        <v>5</v>
-      </c>
-      <c r="AV4">
-        <v>6.4</v>
-      </c>
-      <c r="AW4">
-        <v>8</v>
-      </c>
-      <c r="AX4">
-        <v>4.8</v>
-      </c>
       <c r="AY4">
-        <v>5</v>
+        <v>8.6</v>
       </c>
       <c r="AZ4">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="BA4">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BB4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="BC4">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="BD4">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE4">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BF4">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG4">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH4">
         <v>3.95</v>
       </c>
       <c r="BI4">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BJ4">
         <v>13</v>
       </c>
       <c r="BK4">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BN4">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO4">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="BP4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BQ4">
         <v>3.85</v>
@@ -1724,25 +1724,25 @@
         <v>32</v>
       </c>
       <c r="BS4">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BT4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BU4">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -1771,220 +1771,220 @@
         <v>128</v>
       </c>
       <c r="F5">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="G5">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="H5">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="I5">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="J5">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K5">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L5">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="M5">
         <v>1.07</v>
       </c>
       <c r="N5">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="O5">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="P5">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="Q5">
+        <v>1.98</v>
+      </c>
+      <c r="R5">
+        <v>1.34</v>
+      </c>
+      <c r="S5">
+        <v>3.5</v>
+      </c>
+      <c r="T5">
         <v>1.92</v>
       </c>
-      <c r="R5">
-        <v>1.36</v>
-      </c>
-      <c r="S5">
-        <v>3.25</v>
-      </c>
-      <c r="T5">
-        <v>1.69</v>
-      </c>
       <c r="U5">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="V5">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="W5">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X5">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y5">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="Z5">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AA5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AC5">
         <v>9.199999999999999</v>
       </c>
       <c r="AD5">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AE5">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AF5">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AG5">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AH5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI5">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AJ5">
-        <v>470</v>
+        <v>700</v>
       </c>
       <c r="AK5">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AL5">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AM5">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AN5">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AO5">
         <v>12</v>
       </c>
       <c r="AP5">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AQ5">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="AR5">
-        <v>5.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS5">
-        <v>9</v>
+        <v>15.5</v>
       </c>
       <c r="AT5">
-        <v>6.2</v>
+        <v>15.5</v>
       </c>
       <c r="AU5">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="AV5">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="AW5">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AX5">
-        <v>7.8</v>
+        <v>30</v>
       </c>
       <c r="AY5">
-        <v>9</v>
+        <v>18.5</v>
       </c>
       <c r="AZ5">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="BA5">
-        <v>7.6</v>
+        <v>26</v>
       </c>
       <c r="BB5">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="BC5">
-        <v>8.6</v>
+        <v>44</v>
       </c>
       <c r="BD5">
-        <v>8.6</v>
+        <v>44</v>
       </c>
       <c r="BE5">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="BF5">
-        <v>8.800000000000001</v>
+        <v>50</v>
       </c>
       <c r="BG5">
-        <v>5.3</v>
+        <v>9.6</v>
       </c>
       <c r="BH5">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BI5">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="BJ5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK5">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BN5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BO5">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BQ5">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BR5">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BS5">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BT5">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BU5">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="BV5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BW5">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="BX5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BY5">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BZ5">
         <v>0</v>
@@ -2013,13 +2013,13 @@
         <v>129</v>
       </c>
       <c r="F6">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="H6">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="I6">
         <v>2.02</v>
@@ -2031,40 +2031,40 @@
         <v>4.3</v>
       </c>
       <c r="L6">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M6">
         <v>1.04</v>
       </c>
       <c r="N6">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O6">
         <v>1.2</v>
       </c>
       <c r="P6">
+        <v>2.52</v>
+      </c>
+      <c r="Q6">
+        <v>1.6</v>
+      </c>
+      <c r="R6">
+        <v>1.61</v>
+      </c>
+      <c r="S6">
         <v>2.5</v>
       </c>
-      <c r="Q6">
-        <v>1.59</v>
-      </c>
-      <c r="R6">
+      <c r="T6">
         <v>1.6</v>
       </c>
-      <c r="S6">
+      <c r="U6">
         <v>2.46</v>
-      </c>
-      <c r="T6">
-        <v>1.57</v>
-      </c>
-      <c r="U6">
-        <v>2.48</v>
       </c>
       <c r="V6">
         <v>1.98</v>
       </c>
       <c r="W6">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X6">
         <v>24</v>
@@ -2076,16 +2076,16 @@
         <v>15.5</v>
       </c>
       <c r="AA6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB6">
         <v>22</v>
       </c>
       <c r="AC6">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AE6">
         <v>19</v>
@@ -2100,25 +2100,25 @@
         <v>15.5</v>
       </c>
       <c r="AI6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ6">
         <v>80</v>
       </c>
       <c r="AK6">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL6">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AM6">
         <v>200</v>
       </c>
       <c r="AN6">
-        <v>30</v>
+        <v>970</v>
       </c>
       <c r="AO6">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP6">
         <v>20</v>
@@ -2139,13 +2139,13 @@
         <v>8.4</v>
       </c>
       <c r="AV6">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW6">
         <v>16</v>
       </c>
       <c r="AX6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY6">
         <v>15</v>
@@ -2160,7 +2160,7 @@
         <v>46</v>
       </c>
       <c r="BC6">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BD6">
         <v>29</v>
@@ -2172,7 +2172,7 @@
         <v>18</v>
       </c>
       <c r="BG6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH6">
         <v>5.1</v>
@@ -2181,7 +2181,7 @@
         <v>3.35</v>
       </c>
       <c r="BJ6">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK6">
         <v>6.8</v>
@@ -2196,19 +2196,19 @@
         <v>7.4</v>
       </c>
       <c r="BO6">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BP6">
         <v>30</v>
       </c>
       <c r="BQ6">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BR6">
         <v>38</v>
       </c>
       <c r="BS6">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BT6">
         <v>6.2</v>
@@ -2220,16 +2220,16 @@
         <v>13.5</v>
       </c>
       <c r="BW6">
-        <v>10</v>
+        <v>4.4</v>
       </c>
       <c r="BX6">
         <v>26</v>
       </c>
       <c r="BY6">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BZ6">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="CA6">
         <v>4.7</v>
@@ -2255,22 +2255,22 @@
         <v>130</v>
       </c>
       <c r="F7">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="G7">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="H7">
+        <v>13</v>
+      </c>
+      <c r="I7">
         <v>15.5</v>
       </c>
-      <c r="I7">
-        <v>17.5</v>
-      </c>
       <c r="J7">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="K7">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="L7">
         <v>1.4</v>
@@ -2279,124 +2279,124 @@
         <v>1.06</v>
       </c>
       <c r="N7">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="O7">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="P7">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="Q7">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="R7">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S7">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="T7">
-        <v>2.54</v>
+        <v>2.32</v>
       </c>
       <c r="U7">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="V7">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W7">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="X7">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y7">
         <v>85</v>
       </c>
       <c r="Z7">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>850</v>
       </c>
       <c r="AB7">
         <v>7</v>
       </c>
       <c r="AC7">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD7">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="AE7">
-        <v>530</v>
+        <v>350</v>
       </c>
       <c r="AF7">
         <v>6.8</v>
       </c>
       <c r="AG7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH7">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AI7">
-        <v>390</v>
+        <v>350</v>
       </c>
       <c r="AJ7">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AK7">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL7">
-        <v>330</v>
+        <v>60</v>
       </c>
       <c r="AM7">
         <v>380</v>
       </c>
       <c r="AN7">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>680</v>
       </c>
       <c r="AP7">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AQ7">
-        <v>19.5</v>
+        <v>28</v>
       </c>
       <c r="AR7">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AS7">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AT7">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AV7">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="AW7">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AX7">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AY7">
         <v>10</v>
       </c>
       <c r="AZ7">
-        <v>17.5</v>
+        <v>36</v>
       </c>
       <c r="BA7">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BB7">
         <v>8.199999999999999</v>
@@ -2405,76 +2405,76 @@
         <v>15</v>
       </c>
       <c r="BD7">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BE7">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BF7">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BG7">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH7">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI7">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="BJ7">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BK7">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="BN7">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="BO7">
         <v>3</v>
       </c>
       <c r="BP7">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ7">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="BR7">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="BT7">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BU7">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>7.8</v>
+        <v>5.4</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>7.8</v>
+        <v>5.4</v>
       </c>
       <c r="BZ7">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="CA7">
-        <v>10.5</v>
+        <v>4.2</v>
       </c>
       <c r="CB7" t="s">
         <v>145</v>
@@ -2503,7 +2503,7 @@
         <v>4.5</v>
       </c>
       <c r="H8">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="I8">
         <v>2.34</v>
@@ -2521,16 +2521,16 @@
         <v>1.15</v>
       </c>
       <c r="N8">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="O8">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="P8">
         <v>1.47</v>
       </c>
       <c r="Q8">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="R8">
         <v>1.16</v>
@@ -2539,7 +2539,7 @@
         <v>6.2</v>
       </c>
       <c r="T8">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="U8">
         <v>1.69</v>
@@ -2557,10 +2557,10 @@
         <v>6.6</v>
       </c>
       <c r="Z8">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AA8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB8">
         <v>11</v>
@@ -2572,7 +2572,7 @@
         <v>12.5</v>
       </c>
       <c r="AE8">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF8">
         <v>36</v>
@@ -2584,13 +2584,13 @@
         <v>32</v>
       </c>
       <c r="AI8">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ8">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK8">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="AL8">
         <v>460</v>
@@ -2602,7 +2602,7 @@
         <v>600</v>
       </c>
       <c r="AO8">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AP8">
         <v>6.8</v>
@@ -2626,7 +2626,7 @@
         <v>10.5</v>
       </c>
       <c r="AW8">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AX8">
         <v>23</v>
@@ -2647,16 +2647,16 @@
         <v>50</v>
       </c>
       <c r="BD8">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BE8">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF8">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BH8">
         <v>2.94</v>
@@ -2668,13 +2668,13 @@
         <v>14.5</v>
       </c>
       <c r="BK8">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BN8">
         <v>8.6</v>
@@ -2686,16 +2686,16 @@
         <v>55</v>
       </c>
       <c r="BQ8">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="BR8">
         <v>90</v>
       </c>
       <c r="BS8">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="BT8">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BU8">
         <v>3.7</v>
@@ -2704,19 +2704,19 @@
         <v>25</v>
       </c>
       <c r="BW8">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BX8">
         <v>60</v>
       </c>
       <c r="BY8">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="BZ8">
         <v>70</v>
       </c>
       <c r="CA8">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="CB8" t="s">
         <v>145</v>
@@ -2739,16 +2739,16 @@
         <v>132</v>
       </c>
       <c r="F9">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G9">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H9">
         <v>2.6</v>
       </c>
       <c r="I9">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="J9">
         <v>3.3</v>
@@ -2760,7 +2760,7 @@
         <v>1.44</v>
       </c>
       <c r="M9">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N9">
         <v>3.4</v>
@@ -2775,34 +2775,34 @@
         <v>2.08</v>
       </c>
       <c r="R9">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S9">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="T9">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="U9">
         <v>2.06</v>
       </c>
       <c r="V9">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W9">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X9">
         <v>13.5</v>
       </c>
       <c r="Y9">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z9">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA9">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB9">
         <v>11.5</v>
@@ -2814,151 +2814,151 @@
         <v>13</v>
       </c>
       <c r="AE9">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AF9">
         <v>21</v>
       </c>
       <c r="AG9">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH9">
         <v>18.5</v>
       </c>
       <c r="AI9">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="AJ9">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AK9">
         <v>50</v>
       </c>
       <c r="AL9">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="AM9">
         <v>580</v>
       </c>
       <c r="AN9">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AO9">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AP9">
-        <v>5.4</v>
+        <v>10.5</v>
       </c>
       <c r="AQ9">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AR9">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="AS9">
-        <v>7.4</v>
+        <v>29</v>
       </c>
       <c r="AT9">
-        <v>5</v>
+        <v>9.4</v>
       </c>
       <c r="AU9">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV9">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AW9">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="AX9">
-        <v>6.2</v>
+        <v>17</v>
       </c>
       <c r="AY9">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="AZ9">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="BA9">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="BB9">
-        <v>7.6</v>
+        <v>32</v>
       </c>
       <c r="BC9">
-        <v>7.2</v>
+        <v>24</v>
       </c>
       <c r="BD9">
-        <v>7.6</v>
+        <v>32</v>
       </c>
       <c r="BE9">
-        <v>8.4</v>
+        <v>75</v>
       </c>
       <c r="BF9">
-        <v>7.2</v>
+        <v>22</v>
       </c>
       <c r="BG9">
-        <v>7</v>
+        <v>17.5</v>
       </c>
       <c r="BH9">
         <v>3.35</v>
       </c>
       <c r="BI9">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="BJ9">
         <v>10</v>
       </c>
       <c r="BK9">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>2.46</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN9">
         <v>6.2</v>
       </c>
       <c r="BO9">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="BP9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BQ9">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>2.36</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT9">
         <v>5.9</v>
       </c>
       <c r="BU9">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="BV9">
         <v>23</v>
       </c>
       <c r="BW9">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>2.36</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ9">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>2.34</v>
+        <v>7.8</v>
       </c>
       <c r="CB9" t="s">
         <v>145</v>
@@ -2993,13 +2993,13 @@
         <v>6.6</v>
       </c>
       <c r="J10">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K10">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L10">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="M10">
         <v>1.11</v>
@@ -3008,34 +3008,34 @@
         <v>2.84</v>
       </c>
       <c r="O10">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P10">
         <v>1.6</v>
       </c>
       <c r="Q10">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="R10">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S10">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T10">
         <v>2.2</v>
       </c>
       <c r="U10">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V10">
         <v>1.19</v>
       </c>
       <c r="W10">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X10">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y10">
         <v>15.5</v>
@@ -3074,7 +3074,7 @@
         <v>24</v>
       </c>
       <c r="AK10">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL10">
         <v>70</v>
@@ -3098,7 +3098,7 @@
         <v>30</v>
       </c>
       <c r="AS10">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AT10">
         <v>5.7</v>
@@ -3122,7 +3122,7 @@
         <v>22</v>
       </c>
       <c r="BA10">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="BB10">
         <v>17</v>
@@ -3134,13 +3134,13 @@
         <v>32</v>
       </c>
       <c r="BE10">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF10">
         <v>16</v>
       </c>
       <c r="BG10">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BH10">
         <v>3.3</v>
@@ -3185,13 +3185,13 @@
         <v>3.45</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BW10">
         <v>4.8</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BY10">
         <v>4.8</v>
@@ -3235,13 +3235,13 @@
         <v>4.5</v>
       </c>
       <c r="J11">
+        <v>3.45</v>
+      </c>
+      <c r="K11">
         <v>3.5</v>
       </c>
-      <c r="K11">
-        <v>3.55</v>
-      </c>
       <c r="L11">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M11">
         <v>1.1</v>
@@ -3280,7 +3280,7 @@
         <v>10.5</v>
       </c>
       <c r="Y11">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z11">
         <v>30</v>
@@ -3289,7 +3289,7 @@
         <v>110</v>
       </c>
       <c r="AB11">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AC11">
         <v>7.6</v>
@@ -3304,7 +3304,7 @@
         <v>11</v>
       </c>
       <c r="AG11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH11">
         <v>22</v>
@@ -3313,7 +3313,7 @@
         <v>95</v>
       </c>
       <c r="AJ11">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK11">
         <v>24</v>
@@ -3325,7 +3325,7 @@
         <v>160</v>
       </c>
       <c r="AN11">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AO11">
         <v>110</v>
@@ -3334,7 +3334,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ11">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR11">
         <v>28</v>
@@ -3343,10 +3343,10 @@
         <v>95</v>
       </c>
       <c r="AT11">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU11">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV11">
         <v>16.5</v>
@@ -3361,10 +3361,10 @@
         <v>10</v>
       </c>
       <c r="AZ11">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA11">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BB11">
         <v>23</v>
@@ -3376,22 +3376,22 @@
         <v>46</v>
       </c>
       <c r="BE11">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="BF11">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BG11">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="BH11">
         <v>2.86</v>
       </c>
       <c r="BI11">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="BJ11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK11">
         <v>9.800000000000001</v>
@@ -3400,25 +3400,25 @@
         <v>200</v>
       </c>
       <c r="BM11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BN11">
         <v>4.5</v>
       </c>
       <c r="BO11">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP11">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BQ11">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BR11">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BS11">
-        <v>30</v>
+        <v>14.5</v>
       </c>
       <c r="BT11">
         <v>7.6</v>
@@ -3436,10 +3436,10 @@
         <v>60</v>
       </c>
       <c r="BY11">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="BZ11">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CA11">
         <v>30</v>
@@ -3465,16 +3465,16 @@
         <v>135</v>
       </c>
       <c r="F12">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="G12">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="H12">
         <v>5.3</v>
       </c>
       <c r="I12">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="J12">
         <v>4.4</v>
@@ -3501,7 +3501,7 @@
         <v>1.62</v>
       </c>
       <c r="R12">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S12">
         <v>2.52</v>
@@ -3510,7 +3510,7 @@
         <v>1.68</v>
       </c>
       <c r="U12">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V12">
         <v>1.01</v>
@@ -3522,13 +3522,13 @@
         <v>29</v>
       </c>
       <c r="Y12">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="Z12">
         <v>60</v>
       </c>
       <c r="AA12">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB12">
         <v>12</v>
@@ -3555,7 +3555,7 @@
         <v>70</v>
       </c>
       <c r="AJ12">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK12">
         <v>19</v>
@@ -3570,13 +3570,13 @@
         <v>7</v>
       </c>
       <c r="AO12">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP12">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="AQ12">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AR12">
         <v>6.8</v>
@@ -3591,10 +3591,10 @@
         <v>9.6</v>
       </c>
       <c r="AV12">
-        <v>5.7</v>
+        <v>10</v>
       </c>
       <c r="AW12">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AX12">
         <v>10.5</v>
@@ -3603,7 +3603,7 @@
         <v>9</v>
       </c>
       <c r="AZ12">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BA12">
         <v>40</v>
@@ -3618,13 +3618,13 @@
         <v>14.5</v>
       </c>
       <c r="BE12">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BF12">
         <v>6</v>
       </c>
       <c r="BG12">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH12">
         <v>5.1</v>
@@ -3642,7 +3642,7 @@
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BN12">
         <v>5.4</v>
@@ -3654,22 +3654,22 @@
         <v>12.5</v>
       </c>
       <c r="BQ12">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BR12">
         <v>25</v>
       </c>
       <c r="BS12">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BT12">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU12">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BV12">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BW12">
         <v>4.2</v>
@@ -3678,13 +3678,13 @@
         <v>50</v>
       </c>
       <c r="BY12">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BZ12">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="CA12">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="CB12" t="s">
         <v>145</v>
@@ -3713,16 +3713,16 @@
         <v>1.36</v>
       </c>
       <c r="H13">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I13">
         <v>11.5</v>
       </c>
       <c r="J13">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="K13">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="L13">
         <v>1.24</v>
@@ -3737,31 +3737,31 @@
         <v>1.15</v>
       </c>
       <c r="P13">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="Q13">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="R13">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="S13">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="T13">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U13">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="V13">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W13">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="X13">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="Y13">
         <v>100</v>
@@ -3779,7 +3779,7 @@
         <v>16</v>
       </c>
       <c r="AD13">
-        <v>950</v>
+        <v>40</v>
       </c>
       <c r="AE13">
         <v>150</v>
@@ -3815,7 +3815,7 @@
         <v>150</v>
       </c>
       <c r="AP13">
-        <v>6.6</v>
+        <v>22</v>
       </c>
       <c r="AQ13">
         <v>9.199999999999999</v>
@@ -3827,100 +3827,100 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AT13">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="AU13">
-        <v>5.5</v>
+        <v>12</v>
       </c>
       <c r="AV13">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW13">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AX13">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="AY13">
-        <v>6.4</v>
+        <v>9.4</v>
       </c>
       <c r="AZ13">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="BA13">
         <v>7.8</v>
       </c>
       <c r="BB13">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC13">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BD13">
-        <v>6.6</v>
+        <v>18</v>
       </c>
       <c r="BE13">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BF13">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="BG13">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH13">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="BI13">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="BJ13">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BK13">
-        <v>8.4</v>
+        <v>5</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BN13">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BO13">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP13">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BQ13">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BR13">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BS13">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BT13">
         <v>14.5</v>
       </c>
       <c r="BU13">
-        <v>10</v>
+        <v>4.8</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BZ13">
         <v>0</v>
@@ -3955,19 +3955,19 @@
         <v>1.26</v>
       </c>
       <c r="H14">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="I14">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="J14">
+        <v>7.4</v>
+      </c>
+      <c r="K14">
         <v>7.6</v>
       </c>
-      <c r="K14">
-        <v>7.8</v>
-      </c>
       <c r="L14">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M14">
         <v>1.02</v>
@@ -3982,25 +3982,25 @@
         <v>3.3</v>
       </c>
       <c r="Q14">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="R14">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="S14">
         <v>2.04</v>
       </c>
       <c r="T14">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U14">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V14">
         <v>1.07</v>
       </c>
       <c r="W14">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="X14">
         <v>38</v>
@@ -4012,7 +4012,7 @@
         <v>150</v>
       </c>
       <c r="AA14">
-        <v>560</v>
+        <v>600</v>
       </c>
       <c r="AB14">
         <v>13.5</v>
@@ -4024,13 +4024,13 @@
         <v>48</v>
       </c>
       <c r="AE14">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AF14">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG14">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH14">
         <v>29</v>
@@ -4039,25 +4039,25 @@
         <v>140</v>
       </c>
       <c r="AJ14">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AK14">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AL14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM14">
         <v>120</v>
       </c>
       <c r="AN14">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AO14">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AP14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AQ14">
         <v>50</v>
@@ -4066,19 +4066,19 @@
         <v>120</v>
       </c>
       <c r="AS14">
-        <v>110</v>
+        <v>220</v>
       </c>
       <c r="AT14">
         <v>13</v>
       </c>
       <c r="AU14">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AV14">
         <v>46</v>
       </c>
       <c r="AW14">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AX14">
         <v>8.800000000000001</v>
@@ -4090,16 +4090,16 @@
         <v>28</v>
       </c>
       <c r="BA14">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="BB14">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BC14">
         <v>11</v>
       </c>
       <c r="BD14">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BE14">
         <v>100</v>
@@ -4108,31 +4108,31 @@
         <v>3.25</v>
       </c>
       <c r="BG14">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="BH14">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BI14">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BJ14">
         <v>12</v>
       </c>
       <c r="BK14">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BL14">
         <v>130</v>
       </c>
       <c r="BM14">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN14">
         <v>4.1</v>
       </c>
       <c r="BO14">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BP14">
         <v>6.6</v>
@@ -4141,34 +4141,34 @@
         <v>6</v>
       </c>
       <c r="BR14">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BS14">
         <v>16.5</v>
       </c>
       <c r="BT14">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BU14">
         <v>13.5</v>
       </c>
       <c r="BV14">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="BW14">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="BX14">
         <v>70</v>
       </c>
       <c r="BY14">
-        <v>12.5</v>
+        <v>46</v>
       </c>
       <c r="BZ14">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="CA14">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="CB14" t="s">
         <v>145</v>
@@ -4197,55 +4197,55 @@
         <v>1.55</v>
       </c>
       <c r="H15">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="I15">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="J15">
         <v>3.9</v>
       </c>
       <c r="K15">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L15">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="M15">
         <v>1.1</v>
       </c>
       <c r="N15">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="O15">
         <v>1.48</v>
       </c>
       <c r="P15">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q15">
         <v>2.48</v>
       </c>
       <c r="R15">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S15">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T15">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="U15">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="V15">
         <v>1.11</v>
       </c>
       <c r="W15">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="X15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y15">
         <v>25</v>
@@ -4254,10 +4254,10 @@
         <v>100</v>
       </c>
       <c r="AA15">
-        <v>570</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AC15">
         <v>9.800000000000001</v>
@@ -4266,19 +4266,19 @@
         <v>46</v>
       </c>
       <c r="AE15">
-        <v>290</v>
+        <v>370</v>
       </c>
       <c r="AF15">
         <v>7.4</v>
       </c>
       <c r="AG15">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH15">
         <v>42</v>
       </c>
       <c r="AI15">
-        <v>270</v>
+        <v>360</v>
       </c>
       <c r="AJ15">
         <v>15.5</v>
@@ -4287,7 +4287,7 @@
         <v>25</v>
       </c>
       <c r="AL15">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AM15">
         <v>380</v>
@@ -4299,67 +4299,67 @@
         <v>1000</v>
       </c>
       <c r="AP15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ15">
         <v>19</v>
       </c>
       <c r="AR15">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="AS15">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AT15">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AU15">
         <v>8.6</v>
       </c>
       <c r="AV15">
+        <v>27</v>
+      </c>
+      <c r="AW15">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX15">
         <v>6.4</v>
-      </c>
-      <c r="AW15">
-        <v>7.4</v>
-      </c>
-      <c r="AX15">
-        <v>5.8</v>
       </c>
       <c r="AY15">
         <v>9.6</v>
       </c>
       <c r="AZ15">
-        <v>6.4</v>
+        <v>27</v>
       </c>
       <c r="BA15">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB15">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC15">
         <v>18.5</v>
       </c>
       <c r="BD15">
-        <v>6.8</v>
+        <v>32</v>
       </c>
       <c r="BE15">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF15">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BG15">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH15">
         <v>3.25</v>
       </c>
       <c r="BI15">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BJ15">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BK15">
         <v>4.4</v>
@@ -4371,25 +4371,25 @@
         <v>6</v>
       </c>
       <c r="BN15">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BO15">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="BP15">
         <v>12</v>
       </c>
       <c r="BQ15">
-        <v>6.8</v>
+        <v>4</v>
       </c>
       <c r="BR15">
         <v>44</v>
       </c>
       <c r="BS15">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BT15">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BU15">
         <v>4.3</v>
@@ -4398,13 +4398,13 @@
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BZ15">
         <v>32</v>
@@ -4433,7 +4433,7 @@
         <v>139</v>
       </c>
       <c r="F16">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="G16">
         <v>4.2</v>
@@ -4442,7 +4442,7 @@
         <v>1.77</v>
       </c>
       <c r="I16">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="J16">
         <v>5.1</v>
@@ -4457,31 +4457,31 @@
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>3.45</v>
+        <v>10.5</v>
       </c>
       <c r="O16">
         <v>1.08</v>
       </c>
       <c r="P16">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q16">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="R16">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S16">
         <v>1.67</v>
       </c>
       <c r="T16">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="U16">
         <v>3.1</v>
       </c>
       <c r="V16">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="W16">
         <v>1.33</v>
@@ -4502,10 +4502,10 @@
         <v>46</v>
       </c>
       <c r="AC16">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AD16">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE16">
         <v>19.5</v>
@@ -4529,7 +4529,7 @@
         <v>42</v>
       </c>
       <c r="AL16">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM16">
         <v>42</v>
@@ -4541,73 +4541,73 @@
         <v>5</v>
       </c>
       <c r="AP16">
+        <v>5.3</v>
+      </c>
+      <c r="AQ16">
+        <v>19.5</v>
+      </c>
+      <c r="AR16">
+        <v>16.5</v>
+      </c>
+      <c r="AS16">
+        <v>19</v>
+      </c>
+      <c r="AT16">
+        <v>5.1</v>
+      </c>
+      <c r="AU16">
+        <v>12</v>
+      </c>
+      <c r="AV16">
+        <v>10</v>
+      </c>
+      <c r="AW16">
+        <v>12.5</v>
+      </c>
+      <c r="AX16">
+        <v>5.2</v>
+      </c>
+      <c r="AY16">
+        <v>15</v>
+      </c>
+      <c r="AZ16">
+        <v>11.5</v>
+      </c>
+      <c r="BA16">
+        <v>15</v>
+      </c>
+      <c r="BB16">
         <v>5.4</v>
       </c>
-      <c r="AQ16">
+      <c r="BC16">
+        <v>5</v>
+      </c>
+      <c r="BD16">
         <v>4.9</v>
       </c>
-      <c r="AR16">
-        <v>4.8</v>
-      </c>
-      <c r="AS16">
-        <v>4.9</v>
-      </c>
-      <c r="AT16">
-        <v>5.2</v>
-      </c>
-      <c r="AU16">
-        <v>4.3</v>
-      </c>
-      <c r="AV16">
-        <v>4.3</v>
-      </c>
-      <c r="AW16">
-        <v>4.5</v>
-      </c>
-      <c r="AX16">
-        <v>5.3</v>
-      </c>
-      <c r="AY16">
-        <v>4.7</v>
-      </c>
-      <c r="AZ16">
-        <v>4.4</v>
-      </c>
-      <c r="BA16">
-        <v>4.7</v>
-      </c>
-      <c r="BB16">
-        <v>5.5</v>
-      </c>
-      <c r="BC16">
-        <v>5.2</v>
-      </c>
-      <c r="BD16">
+      <c r="BE16">
         <v>5</v>
       </c>
-      <c r="BE16">
-        <v>5.2</v>
-      </c>
       <c r="BF16">
-        <v>4.4</v>
+        <v>12.5</v>
       </c>
       <c r="BG16">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="BH16">
         <v>7.6</v>
       </c>
       <c r="BI16">
-        <v>3.15</v>
+        <v>5.2</v>
       </c>
       <c r="BJ16">
         <v>9.4</v>
       </c>
       <c r="BK16">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BL16">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BM16">
         <v>4.9</v>
@@ -4628,7 +4628,7 @@
         <v>26</v>
       </c>
       <c r="BS16">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BT16">
         <v>6.8</v>
@@ -4640,7 +4640,7 @@
         <v>13</v>
       </c>
       <c r="BW16">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BX16">
         <v>17.5</v>
@@ -4675,148 +4675,148 @@
         <v>140</v>
       </c>
       <c r="F17">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="G17">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="H17">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I17">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="J17">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="K17">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L17">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="M17">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N17">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="O17">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P17">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q17">
+        <v>2.2</v>
+      </c>
+      <c r="R17">
+        <v>1.2</v>
+      </c>
+      <c r="S17">
+        <v>3.45</v>
+      </c>
+      <c r="T17">
         <v>2.02</v>
       </c>
-      <c r="R17">
-        <v>1.21</v>
-      </c>
-      <c r="S17">
-        <v>4.7</v>
-      </c>
-      <c r="T17">
-        <v>2.08</v>
-      </c>
       <c r="U17">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="V17">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W17">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="X17">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Y17">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z17">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AA17">
         <v>900</v>
       </c>
       <c r="AB17">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AC17">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD17">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE17">
         <v>500</v>
       </c>
       <c r="AF17">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG17">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH17">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AI17">
         <v>500</v>
       </c>
       <c r="AJ17">
-        <v>27</v>
+        <v>160</v>
       </c>
       <c r="AK17">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="AL17">
         <v>130</v>
       </c>
       <c r="AM17">
+        <v>580</v>
+      </c>
+      <c r="AN17">
         <v>500</v>
       </c>
-      <c r="AN17">
-        <v>25</v>
-      </c>
       <c r="AO17">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP17">
         <v>4.7</v>
       </c>
       <c r="AQ17">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AR17">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AS17">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT17">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AU17">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AV17">
+        <v>6.2</v>
+      </c>
+      <c r="AW17">
+        <v>8</v>
+      </c>
+      <c r="AX17">
+        <v>5.2</v>
+      </c>
+      <c r="AY17">
+        <v>5.1</v>
+      </c>
+      <c r="AZ17">
         <v>6.4</v>
       </c>
-      <c r="AW17">
+      <c r="BA17">
         <v>8.199999999999999</v>
-      </c>
-      <c r="AX17">
-        <v>5</v>
-      </c>
-      <c r="AY17">
-        <v>5</v>
-      </c>
-      <c r="AZ17">
-        <v>6.6</v>
-      </c>
-      <c r="BA17">
-        <v>8.4</v>
       </c>
       <c r="BB17">
         <v>6.8</v>
@@ -4828,13 +4828,13 @@
         <v>7.8</v>
       </c>
       <c r="BE17">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BF17">
         <v>6.6</v>
       </c>
       <c r="BG17">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH17">
         <v>3.3</v>
@@ -4920,37 +4920,37 @@
         <v>3.9</v>
       </c>
       <c r="G18">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H18">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I18">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="J18">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="K18">
         <v>3.3</v>
       </c>
       <c r="L18">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="M18">
         <v>1.13</v>
       </c>
       <c r="N18">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="O18">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P18">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="Q18">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="R18">
         <v>1.18</v>
@@ -4965,13 +4965,13 @@
         <v>1.71</v>
       </c>
       <c r="V18">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W18">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X18">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y18">
         <v>7.2</v>
@@ -4989,13 +4989,13 @@
         <v>7.6</v>
       </c>
       <c r="AD18">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AE18">
         <v>65</v>
       </c>
       <c r="AF18">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="AG18">
         <v>23</v>
@@ -5016,16 +5016,16 @@
         <v>500</v>
       </c>
       <c r="AM18">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN18">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO18">
         <v>500</v>
       </c>
       <c r="AP18">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AQ18">
         <v>5.9</v>
@@ -5037,7 +5037,7 @@
         <v>9</v>
       </c>
       <c r="AT18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU18">
         <v>6.2</v>
@@ -5049,55 +5049,55 @@
         <v>14.5</v>
       </c>
       <c r="AX18">
+        <v>21</v>
+      </c>
+      <c r="AY18">
+        <v>15.5</v>
+      </c>
+      <c r="AZ18">
         <v>20</v>
       </c>
-      <c r="AY18">
-        <v>13.5</v>
-      </c>
-      <c r="AZ18">
-        <v>18</v>
-      </c>
       <c r="BA18">
+        <v>7</v>
+      </c>
+      <c r="BB18">
+        <v>7.2</v>
+      </c>
+      <c r="BC18">
+        <v>7.2</v>
+      </c>
+      <c r="BD18">
+        <v>7.2</v>
+      </c>
+      <c r="BE18">
+        <v>7.6</v>
+      </c>
+      <c r="BF18">
+        <v>7.4</v>
+      </c>
+      <c r="BG18">
         <v>6.4</v>
       </c>
-      <c r="BB18">
-        <v>6.8</v>
-      </c>
-      <c r="BC18">
-        <v>6.6</v>
-      </c>
-      <c r="BD18">
-        <v>6.8</v>
-      </c>
-      <c r="BE18">
-        <v>7</v>
-      </c>
-      <c r="BF18">
-        <v>6.8</v>
-      </c>
-      <c r="BG18">
-        <v>6</v>
-      </c>
       <c r="BH18">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="BI18">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="BJ18">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK18">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN18">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BO18">
         <v>5.4</v>
@@ -5106,7 +5106,7 @@
         <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR18">
         <v>1000</v>
@@ -5121,10 +5121,10 @@
         <v>3.7</v>
       </c>
       <c r="BV18">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BW18">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX18">
         <v>1000</v>
@@ -5136,7 +5136,7 @@
         <v>1000</v>
       </c>
       <c r="CA18">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB18" t="s">
         <v>145</v>
@@ -5159,16 +5159,16 @@
         <v>142</v>
       </c>
       <c r="F19">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="G19">
         <v>3.25</v>
       </c>
       <c r="H19">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="I19">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J19">
         <v>2.88</v>
@@ -5177,43 +5177,43 @@
         <v>3.25</v>
       </c>
       <c r="L19">
-        <v>1.3</v>
+        <v>1.52</v>
       </c>
       <c r="M19">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N19">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="O19">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="P19">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q19">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="R19">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S19">
         <v>4.9</v>
       </c>
       <c r="T19">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="U19">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V19">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W19">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X19">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y19">
         <v>9.800000000000001</v>
@@ -5225,7 +5225,7 @@
         <v>60</v>
       </c>
       <c r="AB19">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC19">
         <v>8</v>
@@ -5255,70 +5255,70 @@
         <v>55</v>
       </c>
       <c r="AL19">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM19">
         <v>500</v>
       </c>
       <c r="AN19">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AO19">
         <v>60</v>
       </c>
       <c r="AP19">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ19">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR19">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AS19">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AT19">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AU19">
+        <v>6.2</v>
+      </c>
+      <c r="AV19">
+        <v>11.5</v>
+      </c>
+      <c r="AW19">
+        <v>5.4</v>
+      </c>
+      <c r="AX19">
+        <v>16.5</v>
+      </c>
+      <c r="AY19">
+        <v>12</v>
+      </c>
+      <c r="AZ19">
+        <v>19</v>
+      </c>
+      <c r="BA19">
+        <v>5.2</v>
+      </c>
+      <c r="BB19">
         <v>5.5</v>
       </c>
-      <c r="AV19">
-        <v>10.5</v>
-      </c>
-      <c r="AW19">
+      <c r="BC19">
+        <v>5.4</v>
+      </c>
+      <c r="BD19">
         <v>5.2</v>
       </c>
-      <c r="AX19">
-        <v>14.5</v>
-      </c>
-      <c r="AY19">
-        <v>10.5</v>
-      </c>
-      <c r="AZ19">
-        <v>16.5</v>
-      </c>
-      <c r="BA19">
-        <v>5.4</v>
-      </c>
-      <c r="BB19">
-        <v>5.3</v>
-      </c>
-      <c r="BC19">
-        <v>5.2</v>
-      </c>
-      <c r="BD19">
-        <v>5.4</v>
-      </c>
       <c r="BE19">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BF19">
-        <v>5.3</v>
+        <v>8.6</v>
       </c>
       <c r="BG19">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BH19">
         <v>3.6</v>
@@ -5413,7 +5413,7 @@
         <v>4.2</v>
       </c>
       <c r="J20">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K20">
         <v>4.3</v>
@@ -5425,13 +5425,13 @@
         <v>1.04</v>
       </c>
       <c r="N20">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O20">
         <v>1.18</v>
       </c>
       <c r="P20">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="Q20">
         <v>1.58</v>
@@ -5443,7 +5443,7 @@
         <v>2.34</v>
       </c>
       <c r="T20">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="U20">
         <v>2.54</v>
@@ -5455,13 +5455,13 @@
         <v>1.96</v>
       </c>
       <c r="X20">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="Y20">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z20">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA20">
         <v>75</v>
@@ -5470,10 +5470,10 @@
         <v>15.5</v>
       </c>
       <c r="AC20">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD20">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE20">
         <v>38</v>
@@ -5503,70 +5503,70 @@
         <v>60</v>
       </c>
       <c r="AN20">
+        <v>9.6</v>
+      </c>
+      <c r="AO20">
+        <v>27</v>
+      </c>
+      <c r="AP20">
+        <v>21</v>
+      </c>
+      <c r="AQ20">
+        <v>18</v>
+      </c>
+      <c r="AR20">
+        <v>14.5</v>
+      </c>
+      <c r="AS20">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT20">
+        <v>12</v>
+      </c>
+      <c r="AU20">
         <v>8.800000000000001</v>
       </c>
-      <c r="AO20">
-        <v>25</v>
-      </c>
-      <c r="AP20">
-        <v>6.8</v>
-      </c>
-      <c r="AQ20">
-        <v>6.8</v>
-      </c>
-      <c r="AR20">
-        <v>6.6</v>
-      </c>
-      <c r="AS20">
-        <v>7.4</v>
-      </c>
-      <c r="AT20">
-        <v>7.6</v>
-      </c>
-      <c r="AU20">
-        <v>5.1</v>
-      </c>
       <c r="AV20">
-        <v>6.2</v>
+        <v>13.5</v>
       </c>
       <c r="AW20">
-        <v>6.8</v>
+        <v>26</v>
       </c>
       <c r="AX20">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="AY20">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ20">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="BA20">
-        <v>6.8</v>
+        <v>27</v>
       </c>
       <c r="BB20">
-        <v>6.4</v>
+        <v>19</v>
       </c>
       <c r="BC20">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="BD20">
-        <v>6.6</v>
+        <v>20</v>
       </c>
       <c r="BE20">
-        <v>7.2</v>
+        <v>28</v>
       </c>
       <c r="BF20">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BG20">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="BH20">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BI20">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BJ20">
         <v>9.199999999999999</v>
@@ -5575,7 +5575,7 @@
         <v>6.8</v>
       </c>
       <c r="BL20">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BM20">
         <v>7.4</v>
@@ -5587,40 +5587,40 @@
         <v>4.5</v>
       </c>
       <c r="BP20">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BQ20">
-        <v>9.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="BR20">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BS20">
         <v>6</v>
       </c>
       <c r="BT20">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU20">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV20">
         <v>27</v>
       </c>
       <c r="BW20">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BX20">
         <v>32</v>
       </c>
       <c r="BY20">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BZ20">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="CA20">
-        <v>5.2</v>
+        <v>10</v>
       </c>
       <c r="CB20" t="s">
         <v>145</v>
@@ -5643,55 +5643,55 @@
         <v>144</v>
       </c>
       <c r="F21">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G21">
         <v>4.1</v>
       </c>
       <c r="H21">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="I21">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="J21">
         <v>3.3</v>
       </c>
       <c r="K21">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L21">
         <v>1.51</v>
       </c>
       <c r="M21">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N21">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O21">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P21">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q21">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="R21">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S21">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T21">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="U21">
         <v>1.89</v>
       </c>
       <c r="V21">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="W21">
         <v>1.33</v>
@@ -5700,7 +5700,7 @@
         <v>10.5</v>
       </c>
       <c r="Y21">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Z21">
         <v>13.5</v>
@@ -5712,13 +5712,13 @@
         <v>13.5</v>
       </c>
       <c r="AC21">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD21">
         <v>13</v>
       </c>
       <c r="AE21">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AF21">
         <v>32</v>
@@ -5727,7 +5727,7 @@
         <v>19.5</v>
       </c>
       <c r="AH21">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI21">
         <v>60</v>
@@ -5751,22 +5751,22 @@
         <v>26</v>
       </c>
       <c r="AP21">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ21">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AR21">
         <v>11.5</v>
       </c>
       <c r="AS21">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="AT21">
         <v>10</v>
       </c>
       <c r="AU21">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV21">
         <v>10</v>
@@ -5784,22 +5784,22 @@
         <v>18</v>
       </c>
       <c r="BA21">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB21">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC21">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BD21">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BE21">
+        <v>8.4</v>
+      </c>
+      <c r="BF21">
         <v>8</v>
-      </c>
-      <c r="BF21">
-        <v>7.6</v>
       </c>
       <c r="BG21">
         <v>19.5</v>
@@ -5808,7 +5808,7 @@
         <v>3.25</v>
       </c>
       <c r="BI21">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BJ21">
         <v>10.5</v>
@@ -5820,28 +5820,28 @@
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN21">
         <v>7</v>
       </c>
       <c r="BO21">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BP21">
         <v>36</v>
       </c>
       <c r="BQ21">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BR21">
         <v>55</v>
       </c>
       <c r="BS21">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BT21">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BU21">
         <v>4.3</v>
@@ -5850,19 +5850,19 @@
         <v>18</v>
       </c>
       <c r="BW21">
-        <v>6.8</v>
+        <v>14</v>
       </c>
       <c r="BX21">
         <v>38</v>
       </c>
       <c r="BY21">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ21">
         <v>38</v>
       </c>
       <c r="CA21">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB21" t="s">
         <v>145</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
@@ -451,7 +451,7 @@
     <t>Millonarios</t>
   </si>
   <si>
-    <t>2026-08-27 06:29:22</t>
+    <t>2026-08-27 08:48:05</t>
   </si>
 </sst>
 </file>
@@ -1045,64 +1045,64 @@
         <v>125</v>
       </c>
       <c r="F2">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G2">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H2">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="J2">
         <v>2.62</v>
       </c>
       <c r="K2">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="L2">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="M2">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="N2">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="O2">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="P2">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Q2">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="R2">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="S2">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="T2">
-        <v>1.11</v>
+        <v>2.46</v>
       </c>
       <c r="U2">
-        <v>1.11</v>
+        <v>1.47</v>
       </c>
       <c r="V2">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W2">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="X2">
         <v>970</v>
       </c>
       <c r="Y2">
-        <v>970</v>
+        <v>30</v>
       </c>
       <c r="Z2">
         <v>500</v>
@@ -1111,7 +1111,7 @@
         <v>900</v>
       </c>
       <c r="AB2">
-        <v>14</v>
+        <v>7.2</v>
       </c>
       <c r="AC2">
         <v>9</v>
@@ -1123,7 +1123,7 @@
         <v>500</v>
       </c>
       <c r="AF2">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AG2">
         <v>970</v>
@@ -1153,58 +1153,58 @@
         <v>600</v>
       </c>
       <c r="AP2">
-        <v>1.84</v>
+        <v>4.6</v>
       </c>
       <c r="AQ2">
-        <v>7.8</v>
+        <v>2.44</v>
       </c>
       <c r="AR2">
-        <v>1.82</v>
+        <v>2.72</v>
       </c>
       <c r="AS2">
-        <v>1.88</v>
+        <v>2.8</v>
       </c>
       <c r="AT2">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="AU2">
-        <v>1.52</v>
+        <v>5.1</v>
       </c>
       <c r="AV2">
-        <v>14.5</v>
+        <v>2.56</v>
       </c>
       <c r="AW2">
-        <v>1.84</v>
+        <v>2.8</v>
       </c>
       <c r="AX2">
-        <v>1.7</v>
+        <v>2.44</v>
       </c>
       <c r="AY2">
-        <v>1.73</v>
+        <v>2.68</v>
       </c>
       <c r="AZ2">
-        <v>1.83</v>
+        <v>2.78</v>
       </c>
       <c r="BA2">
-        <v>1.84</v>
+        <v>2.8</v>
       </c>
       <c r="BB2">
-        <v>1.88</v>
+        <v>2.8</v>
       </c>
       <c r="BC2">
-        <v>1.79</v>
+        <v>2.68</v>
       </c>
       <c r="BD2">
-        <v>1.83</v>
+        <v>2.78</v>
       </c>
       <c r="BE2">
-        <v>1.84</v>
+        <v>2.74</v>
       </c>
       <c r="BF2">
-        <v>1.84</v>
+        <v>2.74</v>
       </c>
       <c r="BG2">
-        <v>1.82</v>
+        <v>2.7</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1296,91 +1296,91 @@
         <v>2.46</v>
       </c>
       <c r="I3">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="J3">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L3">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="M3">
         <v>1.04</v>
       </c>
       <c r="N3">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="O3">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P3">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="Q3">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="R3">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="S3">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="T3">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="U3">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="V3">
         <v>1.64</v>
       </c>
       <c r="W3">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB3">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AC3">
         <v>10</v>
       </c>
       <c r="AD3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH3">
         <v>15.5</v>
       </c>
       <c r="AI3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AJ3">
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AL3">
         <v>34</v>
@@ -1389,25 +1389,25 @@
         <v>75</v>
       </c>
       <c r="AN3">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AO3">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AP3">
         <v>20</v>
       </c>
       <c r="AQ3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS3">
         <v>16</v>
       </c>
       <c r="AT3">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU3">
         <v>8.6</v>
@@ -1419,7 +1419,7 @@
         <v>19.5</v>
       </c>
       <c r="AX3">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AY3">
         <v>11</v>
@@ -1431,10 +1431,10 @@
         <v>24</v>
       </c>
       <c r="BB3">
-        <v>19.5</v>
+        <v>36</v>
       </c>
       <c r="BC3">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="BD3">
         <v>15</v>
@@ -1446,43 +1446,43 @@
         <v>14.5</v>
       </c>
       <c r="BG3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH3">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI3">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BJ3">
         <v>9.800000000000001</v>
       </c>
       <c r="BK3">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="BL3">
         <v>85</v>
       </c>
       <c r="BM3">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BN3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BO3">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BP3">
         <v>23</v>
       </c>
       <c r="BQ3">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BR3">
         <v>30</v>
       </c>
       <c r="BS3">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BT3">
         <v>6.6</v>
@@ -1491,22 +1491,22 @@
         <v>4.6</v>
       </c>
       <c r="BV3">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BW3">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BX3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BY3">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BZ3">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="CA3">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="CB3" t="s">
         <v>145</v>
@@ -1529,100 +1529,100 @@
         <v>127</v>
       </c>
       <c r="F4">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="G4">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="I4">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="K4">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="L4">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M4">
         <v>1.06</v>
       </c>
       <c r="N4">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="O4">
         <v>1.3</v>
       </c>
       <c r="P4">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="Q4">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="R4">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S4">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T4">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="U4">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V4">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="W4">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="X4">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y4">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Z4">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA4">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB4">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD4">
         <v>32</v>
       </c>
       <c r="AE4">
-        <v>700</v>
+        <v>260</v>
       </c>
       <c r="AF4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG4">
         <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AI4">
-        <v>700</v>
+        <v>120</v>
       </c>
       <c r="AJ4">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AK4">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AL4">
         <v>46</v>
@@ -1631,118 +1631,118 @@
         <v>700</v>
       </c>
       <c r="AN4">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AO4">
-        <v>220</v>
+        <v>160</v>
       </c>
       <c r="AP4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ4">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AR4">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="AS4">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT4">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AU4">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV4">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW4">
-        <v>9.4</v>
+        <v>50</v>
       </c>
       <c r="AX4">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY4">
         <v>8.6</v>
       </c>
       <c r="AZ4">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BA4">
-        <v>8.6</v>
+        <v>46</v>
       </c>
       <c r="BB4">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BC4">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD4">
-        <v>9.199999999999999</v>
+        <v>25</v>
       </c>
       <c r="BE4">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF4">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BG4">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH4">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BI4">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="BJ4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK4">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BN4">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BO4">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="BP4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BQ4">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BR4">
         <v>32</v>
       </c>
       <c r="BS4">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BT4">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BU4">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -1771,169 +1771,169 @@
         <v>128</v>
       </c>
       <c r="F5">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="H5">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="I5">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J5">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="K5">
+        <v>3.8</v>
+      </c>
+      <c r="L5">
+        <v>1.51</v>
+      </c>
+      <c r="M5">
+        <v>1.09</v>
+      </c>
+      <c r="N5">
+        <v>3.15</v>
+      </c>
+      <c r="O5">
+        <v>1.4</v>
+      </c>
+      <c r="P5">
+        <v>1.71</v>
+      </c>
+      <c r="Q5">
+        <v>2.24</v>
+      </c>
+      <c r="R5">
+        <v>1.26</v>
+      </c>
+      <c r="S5">
         <v>4.3</v>
       </c>
-      <c r="L5">
-        <v>1.45</v>
-      </c>
-      <c r="M5">
-        <v>1.07</v>
-      </c>
-      <c r="N5">
-        <v>3.65</v>
-      </c>
-      <c r="O5">
-        <v>1.32</v>
-      </c>
-      <c r="P5">
-        <v>1.94</v>
-      </c>
-      <c r="Q5">
-        <v>1.98</v>
-      </c>
-      <c r="R5">
-        <v>1.34</v>
-      </c>
-      <c r="S5">
-        <v>3.5</v>
-      </c>
       <c r="T5">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="U5">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="V5">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="W5">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X5">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="Y5">
-        <v>9.6</v>
+        <v>7.6</v>
       </c>
       <c r="Z5">
         <v>10.5</v>
       </c>
       <c r="AA5">
+        <v>25</v>
+      </c>
+      <c r="AB5">
+        <v>16</v>
+      </c>
+      <c r="AC5">
+        <v>8.6</v>
+      </c>
+      <c r="AD5">
+        <v>12.5</v>
+      </c>
+      <c r="AE5">
+        <v>23</v>
+      </c>
+      <c r="AF5">
+        <v>50</v>
+      </c>
+      <c r="AG5">
         <v>22</v>
       </c>
-      <c r="AB5">
-        <v>19</v>
-      </c>
-      <c r="AC5">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD5">
-        <v>12</v>
-      </c>
-      <c r="AE5">
-        <v>19.5</v>
-      </c>
-      <c r="AF5">
-        <v>46</v>
-      </c>
-      <c r="AG5">
+      <c r="AH5">
         <v>23</v>
       </c>
-      <c r="AH5">
-        <v>22</v>
-      </c>
       <c r="AI5">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AJ5">
-        <v>700</v>
+        <v>470</v>
       </c>
       <c r="AK5">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AL5">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AM5">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AN5">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="AO5">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="AP5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AQ5">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AR5">
         <v>8.800000000000001</v>
       </c>
       <c r="AS5">
+        <v>17</v>
+      </c>
+      <c r="AT5">
+        <v>13</v>
+      </c>
+      <c r="AU5">
+        <v>7</v>
+      </c>
+      <c r="AV5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW5">
+        <v>18.5</v>
+      </c>
+      <c r="AX5">
+        <v>7.8</v>
+      </c>
+      <c r="AY5">
+        <v>18</v>
+      </c>
+      <c r="AZ5">
+        <v>18.5</v>
+      </c>
+      <c r="BA5">
+        <v>34</v>
+      </c>
+      <c r="BB5">
+        <v>7.6</v>
+      </c>
+      <c r="BC5">
+        <v>12.5</v>
+      </c>
+      <c r="BD5">
+        <v>15</v>
+      </c>
+      <c r="BE5">
         <v>15.5</v>
       </c>
-      <c r="AT5">
-        <v>15.5</v>
-      </c>
-      <c r="AU5">
-        <v>7.8</v>
-      </c>
-      <c r="AV5">
-        <v>8.6</v>
-      </c>
-      <c r="AW5">
-        <v>16</v>
-      </c>
-      <c r="AX5">
-        <v>30</v>
-      </c>
-      <c r="AY5">
-        <v>18.5</v>
-      </c>
-      <c r="AZ5">
-        <v>18</v>
-      </c>
-      <c r="BA5">
-        <v>26</v>
-      </c>
-      <c r="BB5">
-        <v>28</v>
-      </c>
-      <c r="BC5">
-        <v>44</v>
-      </c>
-      <c r="BD5">
-        <v>44</v>
-      </c>
-      <c r="BE5">
-        <v>29</v>
-      </c>
       <c r="BF5">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="BG5">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="BH5">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="BI5">
         <v>2.74</v>
@@ -1942,49 +1942,49 @@
         <v>12.5</v>
       </c>
       <c r="BK5">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BN5">
         <v>10.5</v>
       </c>
       <c r="BO5">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BP5">
         <v>60</v>
       </c>
       <c r="BQ5">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BR5">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BS5">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BT5">
         <v>4.9</v>
       </c>
       <c r="BU5">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BV5">
         <v>14</v>
       </c>
       <c r="BW5">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BX5">
         <v>34</v>
       </c>
       <c r="BY5">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BZ5">
         <v>0</v>
@@ -2058,7 +2058,7 @@
         <v>1.6</v>
       </c>
       <c r="U6">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="V6">
         <v>1.98</v>
@@ -2109,13 +2109,13 @@
         <v>44</v>
       </c>
       <c r="AL6">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="AM6">
         <v>200</v>
       </c>
       <c r="AN6">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AO6">
         <v>9.800000000000001</v>
@@ -2145,7 +2145,7 @@
         <v>16</v>
       </c>
       <c r="AX6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY6">
         <v>15</v>
@@ -2172,16 +2172,16 @@
         <v>18</v>
       </c>
       <c r="BG6">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH6">
         <v>5.1</v>
       </c>
       <c r="BI6">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BJ6">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK6">
         <v>6.8</v>
@@ -2190,28 +2190,28 @@
         <v>95</v>
       </c>
       <c r="BM6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BN6">
         <v>7.4</v>
       </c>
       <c r="BO6">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BP6">
         <v>30</v>
       </c>
       <c r="BQ6">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BR6">
         <v>38</v>
       </c>
       <c r="BS6">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BT6">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="BU6">
         <v>4.6</v>
@@ -2220,19 +2220,19 @@
         <v>13.5</v>
       </c>
       <c r="BW6">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BX6">
         <v>26</v>
       </c>
       <c r="BY6">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BZ6">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="CA6">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="CB6" t="s">
         <v>145</v>
@@ -2258,16 +2258,16 @@
         <v>1.32</v>
       </c>
       <c r="G7">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="H7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I7">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="J7">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K7">
         <v>5.8</v>
@@ -2279,58 +2279,58 @@
         <v>1.06</v>
       </c>
       <c r="N7">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="O7">
         <v>1.33</v>
       </c>
       <c r="P7">
+        <v>1.99</v>
+      </c>
+      <c r="Q7">
         <v>1.96</v>
       </c>
-      <c r="Q7">
-        <v>1.97</v>
-      </c>
       <c r="R7">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S7">
         <v>3.55</v>
       </c>
       <c r="T7">
-        <v>2.32</v>
+        <v>2.52</v>
       </c>
       <c r="U7">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="V7">
         <v>1.07</v>
       </c>
       <c r="W7">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="X7">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y7">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="Z7">
         <v>150</v>
       </c>
       <c r="AA7">
-        <v>850</v>
+        <v>770</v>
       </c>
       <c r="AB7">
         <v>7</v>
       </c>
       <c r="AC7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD7">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="AE7">
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="AF7">
         <v>6.8</v>
@@ -2339,13 +2339,13 @@
         <v>11</v>
       </c>
       <c r="AH7">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AI7">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="AJ7">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AK7">
         <v>17</v>
@@ -2354,40 +2354,40 @@
         <v>60</v>
       </c>
       <c r="AM7">
-        <v>380</v>
+        <v>330</v>
       </c>
       <c r="AN7">
         <v>7</v>
       </c>
       <c r="AO7">
-        <v>680</v>
+        <v>570</v>
       </c>
       <c r="AP7">
         <v>13</v>
       </c>
       <c r="AQ7">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AR7">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AS7">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AT7">
         <v>6.2</v>
       </c>
       <c r="AU7">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AV7">
         <v>46</v>
       </c>
       <c r="AW7">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AX7">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AY7">
         <v>10</v>
@@ -2396,34 +2396,34 @@
         <v>36</v>
       </c>
       <c r="BA7">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BB7">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC7">
         <v>15</v>
       </c>
       <c r="BD7">
-        <v>10.5</v>
+        <v>48</v>
       </c>
       <c r="BE7">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BF7">
         <v>6</v>
       </c>
       <c r="BG7">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH7">
         <v>4.1</v>
       </c>
       <c r="BI7">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BJ7">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BK7">
         <v>4.3</v>
@@ -2432,7 +2432,7 @@
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BN7">
         <v>3.9</v>
@@ -2453,28 +2453,28 @@
         <v>4.8</v>
       </c>
       <c r="BT7">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BU7">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BZ7">
         <v>17.5</v>
       </c>
       <c r="CA7">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="CB7" t="s">
         <v>145</v>
@@ -2503,19 +2503,19 @@
         <v>4.5</v>
       </c>
       <c r="H8">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I8">
         <v>2.34</v>
       </c>
       <c r="J8">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K8">
         <v>3.05</v>
       </c>
       <c r="L8">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="M8">
         <v>1.15</v>
@@ -2524,7 +2524,7 @@
         <v>2.5</v>
       </c>
       <c r="O8">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="P8">
         <v>1.47</v>
@@ -2536,7 +2536,7 @@
         <v>1.16</v>
       </c>
       <c r="S8">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T8">
         <v>2.24</v>
@@ -2545,55 +2545,55 @@
         <v>1.69</v>
       </c>
       <c r="V8">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="W8">
         <v>1.29</v>
       </c>
       <c r="X8">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y8">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="Z8">
         <v>13</v>
       </c>
       <c r="AA8">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AB8">
         <v>11</v>
       </c>
       <c r="AC8">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD8">
         <v>12.5</v>
       </c>
       <c r="AE8">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF8">
         <v>36</v>
       </c>
       <c r="AG8">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AH8">
         <v>32</v>
       </c>
       <c r="AI8">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="AJ8">
+        <v>900</v>
+      </c>
+      <c r="AK8">
+        <v>230</v>
+      </c>
+      <c r="AL8">
         <v>500</v>
-      </c>
-      <c r="AK8">
-        <v>110</v>
-      </c>
-      <c r="AL8">
-        <v>460</v>
       </c>
       <c r="AM8">
         <v>500</v>
@@ -2602,10 +2602,10 @@
         <v>600</v>
       </c>
       <c r="AO8">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AP8">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ8">
         <v>5.8</v>
@@ -2614,7 +2614,7 @@
         <v>10.5</v>
       </c>
       <c r="AS8">
-        <v>23</v>
+        <v>15.5</v>
       </c>
       <c r="AT8">
         <v>9.4</v>
@@ -2626,46 +2626,46 @@
         <v>10.5</v>
       </c>
       <c r="AW8">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="AX8">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="AY8">
         <v>16.5</v>
       </c>
       <c r="AZ8">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="BA8">
-        <v>46</v>
+        <v>7.6</v>
       </c>
       <c r="BB8">
-        <v>70</v>
+        <v>7.8</v>
       </c>
       <c r="BC8">
-        <v>50</v>
+        <v>7.6</v>
       </c>
       <c r="BD8">
-        <v>65</v>
+        <v>7.8</v>
       </c>
       <c r="BE8">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="BF8">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="BG8">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="BH8">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="BI8">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="BJ8">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BK8">
         <v>3.8</v>
@@ -2674,7 +2674,7 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BN8">
         <v>8.6</v>
@@ -2683,7 +2683,7 @@
         <v>5.4</v>
       </c>
       <c r="BP8">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BQ8">
         <v>4.7</v>
@@ -2692,7 +2692,7 @@
         <v>90</v>
       </c>
       <c r="BS8">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BT8">
         <v>5.6</v>
@@ -2704,7 +2704,7 @@
         <v>25</v>
       </c>
       <c r="BW8">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BX8">
         <v>60</v>
@@ -2739,46 +2739,46 @@
         <v>132</v>
       </c>
       <c r="F9">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="G9">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="H9">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="I9">
-        <v>2.78</v>
+        <v>2.52</v>
       </c>
       <c r="J9">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K9">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L9">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M9">
         <v>1.08</v>
       </c>
       <c r="N9">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O9">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P9">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q9">
         <v>2.08</v>
       </c>
       <c r="R9">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S9">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="T9">
         <v>1.84</v>
@@ -2787,10 +2787,10 @@
         <v>2.06</v>
       </c>
       <c r="V9">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="W9">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="X9">
         <v>13.5</v>
@@ -2799,154 +2799,154 @@
         <v>10.5</v>
       </c>
       <c r="Z9">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA9">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AB9">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AC9">
         <v>8</v>
       </c>
       <c r="AD9">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE9">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AF9">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AG9">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH9">
         <v>18.5</v>
       </c>
       <c r="AI9">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ9">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AK9">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AL9">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AM9">
         <v>580</v>
       </c>
       <c r="AN9">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AO9">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AP9">
+        <v>11</v>
+      </c>
+      <c r="AQ9">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR9">
+        <v>13.5</v>
+      </c>
+      <c r="AS9">
+        <v>25</v>
+      </c>
+      <c r="AT9">
         <v>10.5</v>
-      </c>
-      <c r="AQ9">
-        <v>9</v>
-      </c>
-      <c r="AR9">
-        <v>14.5</v>
-      </c>
-      <c r="AS9">
-        <v>29</v>
-      </c>
-      <c r="AT9">
-        <v>9.4</v>
       </c>
       <c r="AU9">
         <v>6.6</v>
       </c>
       <c r="AV9">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX9">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AY9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ9">
         <v>15</v>
       </c>
       <c r="BA9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB9">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BC9">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BD9">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE9">
         <v>75</v>
       </c>
       <c r="BF9">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BG9">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BH9">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BI9">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BJ9">
         <v>10</v>
       </c>
       <c r="BK9">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN9">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BO9">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BP9">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BQ9">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT9">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="BU9">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BV9">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BW9">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BX9">
         <v>1000</v>
@@ -2958,7 +2958,7 @@
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="CB9" t="s">
         <v>145</v>
@@ -2984,7 +2984,7 @@
         <v>1.78</v>
       </c>
       <c r="G10">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H10">
         <v>5.7</v>
@@ -2993,19 +2993,19 @@
         <v>6.6</v>
       </c>
       <c r="J10">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K10">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L10">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M10">
         <v>1.11</v>
       </c>
       <c r="N10">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="O10">
         <v>1.48</v>
@@ -3020,7 +3020,7 @@
         <v>1.21</v>
       </c>
       <c r="S10">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="T10">
         <v>2.2</v>
@@ -3029,7 +3029,7 @@
         <v>1.72</v>
       </c>
       <c r="V10">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W10">
         <v>2.14</v>
@@ -3041,7 +3041,7 @@
         <v>15.5</v>
       </c>
       <c r="Z10">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA10">
         <v>900</v>
@@ -3056,7 +3056,7 @@
         <v>30</v>
       </c>
       <c r="AE10">
-        <v>700</v>
+        <v>480</v>
       </c>
       <c r="AF10">
         <v>9.6</v>
@@ -3068,16 +3068,16 @@
         <v>36</v>
       </c>
       <c r="AI10">
-        <v>700</v>
+        <v>450</v>
       </c>
       <c r="AJ10">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK10">
         <v>36</v>
       </c>
       <c r="AL10">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM10">
         <v>580</v>
@@ -3098,7 +3098,7 @@
         <v>30</v>
       </c>
       <c r="AS10">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT10">
         <v>5.7</v>
@@ -3122,7 +3122,7 @@
         <v>22</v>
       </c>
       <c r="BA10">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB10">
         <v>17</v>
@@ -3140,13 +3140,13 @@
         <v>16</v>
       </c>
       <c r="BG10">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH10">
         <v>3.3</v>
       </c>
       <c r="BI10">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="BJ10">
         <v>14.5</v>
@@ -3158,7 +3158,7 @@
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BN10">
         <v>4.8</v>
@@ -3170,10 +3170,10 @@
         <v>16.5</v>
       </c>
       <c r="BQ10">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BR10">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BS10">
         <v>4.5</v>
@@ -3188,7 +3188,7 @@
         <v>80</v>
       </c>
       <c r="BW10">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BX10">
         <v>100</v>
@@ -3197,7 +3197,7 @@
         <v>4.8</v>
       </c>
       <c r="BZ10">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="CA10">
         <v>4.5</v>
@@ -3241,61 +3241,61 @@
         <v>3.5</v>
       </c>
       <c r="L11">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="M11">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N11">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O11">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="P11">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q11">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="R11">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S11">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T11">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="U11">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="V11">
         <v>1.28</v>
       </c>
       <c r="W11">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="X11">
         <v>10.5</v>
       </c>
       <c r="Y11">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z11">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA11">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AB11">
         <v>7.4</v>
       </c>
       <c r="AC11">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD11">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE11">
         <v>70</v>
@@ -3307,19 +3307,19 @@
         <v>11</v>
       </c>
       <c r="AH11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI11">
         <v>95</v>
       </c>
       <c r="AJ11">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK11">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL11">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AM11">
         <v>160</v>
@@ -3328,13 +3328,13 @@
         <v>22</v>
       </c>
       <c r="AO11">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AP11">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR11">
         <v>28</v>
@@ -3343,13 +3343,13 @@
         <v>95</v>
       </c>
       <c r="AT11">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU11">
         <v>7.2</v>
       </c>
       <c r="AV11">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW11">
         <v>60</v>
@@ -3361,7 +3361,7 @@
         <v>10</v>
       </c>
       <c r="AZ11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA11">
         <v>80</v>
@@ -3382,13 +3382,13 @@
         <v>19.5</v>
       </c>
       <c r="BG11">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="BH11">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="BI11">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="BJ11">
         <v>11</v>
@@ -3397,10 +3397,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BL11">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="BM11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BN11">
         <v>4.5</v>
@@ -3409,37 +3409,37 @@
         <v>4.2</v>
       </c>
       <c r="BP11">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BQ11">
         <v>14</v>
       </c>
       <c r="BR11">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BS11">
-        <v>14.5</v>
+        <v>32</v>
       </c>
       <c r="BT11">
         <v>7.6</v>
       </c>
       <c r="BU11">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BV11">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BW11">
         <v>36</v>
       </c>
       <c r="BX11">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="BY11">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BZ11">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CA11">
         <v>30</v>
@@ -3465,16 +3465,16 @@
         <v>135</v>
       </c>
       <c r="F12">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="G12">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="H12">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I12">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="J12">
         <v>4.4</v>
@@ -3495,7 +3495,7 @@
         <v>1.2</v>
       </c>
       <c r="P12">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q12">
         <v>1.62</v>
@@ -3507,10 +3507,10 @@
         <v>2.52</v>
       </c>
       <c r="T12">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U12">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V12">
         <v>1.01</v>
@@ -3519,10 +3519,10 @@
         <v>1.01</v>
       </c>
       <c r="X12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y12">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="Z12">
         <v>60</v>
@@ -3537,7 +3537,7 @@
         <v>11</v>
       </c>
       <c r="AD12">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AE12">
         <v>85</v>
@@ -3549,7 +3549,7 @@
         <v>10.5</v>
       </c>
       <c r="AH12">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI12">
         <v>70</v>
@@ -3576,13 +3576,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ12">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="AR12">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AS12">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AT12">
         <v>10</v>
@@ -3591,10 +3591,10 @@
         <v>9.6</v>
       </c>
       <c r="AV12">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW12">
-        <v>6.8</v>
+        <v>24</v>
       </c>
       <c r="AX12">
         <v>10.5</v>
@@ -3615,16 +3615,16 @@
         <v>13.5</v>
       </c>
       <c r="BD12">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BE12">
-        <v>7.6</v>
+        <v>28</v>
       </c>
       <c r="BF12">
         <v>6</v>
       </c>
       <c r="BG12">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="BH12">
         <v>5.1</v>
@@ -3707,19 +3707,19 @@
         <v>136</v>
       </c>
       <c r="F13">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="G13">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="H13">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="I13">
         <v>11.5</v>
       </c>
       <c r="J13">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="K13">
         <v>7</v>
@@ -3728,28 +3728,28 @@
         <v>1.24</v>
       </c>
       <c r="M13">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N13">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O13">
         <v>1.15</v>
       </c>
       <c r="P13">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="Q13">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="R13">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="S13">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="T13">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U13">
         <v>1.99</v>
@@ -3758,31 +3758,31 @@
         <v>1.1</v>
       </c>
       <c r="W13">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="X13">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="Y13">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="Z13">
         <v>450</v>
       </c>
       <c r="AA13">
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="AB13">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC13">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AD13">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AE13">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF13">
         <v>11</v>
@@ -3797,130 +3797,130 @@
         <v>320</v>
       </c>
       <c r="AJ13">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AK13">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL13">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AM13">
         <v>260</v>
       </c>
       <c r="AN13">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AO13">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AP13">
-        <v>22</v>
+        <v>8.4</v>
       </c>
       <c r="AQ13">
-        <v>9.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="AR13">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AS13">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AT13">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU13">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AV13">
-        <v>8.800000000000001</v>
+        <v>27</v>
       </c>
       <c r="AW13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX13">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AY13">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ13">
         <v>20</v>
       </c>
       <c r="BA13">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BB13">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC13">
         <v>11</v>
       </c>
       <c r="BD13">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="BE13">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF13">
         <v>3.5</v>
       </c>
       <c r="BG13">
-        <v>8.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="BH13">
         <v>5.3</v>
       </c>
       <c r="BI13">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BJ13">
         <v>13</v>
       </c>
       <c r="BK13">
-        <v>5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BN13">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BO13">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="BP13">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BQ13">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="BR13">
         <v>23</v>
       </c>
       <c r="BS13">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT13">
         <v>14.5</v>
       </c>
       <c r="BU13">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BZ13">
         <v>0</v>
@@ -3949,16 +3949,16 @@
         <v>137</v>
       </c>
       <c r="F14">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="G14">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="H14">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="I14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J14">
         <v>7.4</v>
@@ -3967,7 +3967,7 @@
         <v>7.6</v>
       </c>
       <c r="L14">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M14">
         <v>1.02</v>
@@ -3982,52 +3982,52 @@
         <v>3.3</v>
       </c>
       <c r="Q14">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="R14">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="S14">
         <v>2.04</v>
       </c>
       <c r="T14">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="U14">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V14">
         <v>1.07</v>
       </c>
       <c r="W14">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="X14">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Y14">
         <v>60</v>
       </c>
       <c r="Z14">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AA14">
-        <v>600</v>
+        <v>540</v>
       </c>
       <c r="AB14">
         <v>13.5</v>
       </c>
       <c r="AC14">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AD14">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AE14">
         <v>180</v>
       </c>
       <c r="AF14">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AG14">
         <v>11</v>
@@ -4036,52 +4036,52 @@
         <v>29</v>
       </c>
       <c r="AI14">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AJ14">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AK14">
         <v>12</v>
       </c>
       <c r="AL14">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AM14">
         <v>120</v>
       </c>
       <c r="AN14">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AO14">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="AP14">
         <v>36</v>
       </c>
       <c r="AQ14">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AR14">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AS14">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="AT14">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU14">
         <v>16.5</v>
       </c>
       <c r="AV14">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AW14">
         <v>160</v>
       </c>
       <c r="AX14">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY14">
         <v>10.5</v>
@@ -4090,49 +4090,49 @@
         <v>28</v>
       </c>
       <c r="BA14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="BB14">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BC14">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BD14">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BE14">
         <v>100</v>
       </c>
       <c r="BF14">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BG14">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="BH14">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BI14">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BJ14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BK14">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BL14">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="BM14">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="BN14">
         <v>4.1</v>
       </c>
       <c r="BO14">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BP14">
         <v>6.6</v>
@@ -4141,28 +4141,28 @@
         <v>6</v>
       </c>
       <c r="BR14">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BS14">
+        <v>16</v>
+      </c>
+      <c r="BT14">
+        <v>15</v>
+      </c>
+      <c r="BU14">
+        <v>13</v>
+      </c>
+      <c r="BV14">
+        <v>80</v>
+      </c>
+      <c r="BW14">
+        <v>17</v>
+      </c>
+      <c r="BX14">
+        <v>65</v>
+      </c>
+      <c r="BY14">
         <v>16.5</v>
-      </c>
-      <c r="BT14">
-        <v>16</v>
-      </c>
-      <c r="BU14">
-        <v>13.5</v>
-      </c>
-      <c r="BV14">
-        <v>110</v>
-      </c>
-      <c r="BW14">
-        <v>65</v>
-      </c>
-      <c r="BX14">
-        <v>70</v>
-      </c>
-      <c r="BY14">
-        <v>46</v>
       </c>
       <c r="BZ14">
         <v>8</v>
@@ -4194,16 +4194,16 @@
         <v>1.51</v>
       </c>
       <c r="G15">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="H15">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="I15">
         <v>11</v>
       </c>
       <c r="J15">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K15">
         <v>4.3</v>
@@ -4212,13 +4212,13 @@
         <v>1.53</v>
       </c>
       <c r="M15">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N15">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="O15">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P15">
         <v>1.6</v>
@@ -4233,16 +4233,16 @@
         <v>5</v>
       </c>
       <c r="T15">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="U15">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="V15">
         <v>1.11</v>
       </c>
       <c r="W15">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="X15">
         <v>11</v>
@@ -4257,7 +4257,7 @@
         <v>1000</v>
       </c>
       <c r="AB15">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AC15">
         <v>9.800000000000001</v>
@@ -4266,7 +4266,7 @@
         <v>46</v>
       </c>
       <c r="AE15">
-        <v>370</v>
+        <v>330</v>
       </c>
       <c r="AF15">
         <v>7.4</v>
@@ -4278,7 +4278,7 @@
         <v>42</v>
       </c>
       <c r="AI15">
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="AJ15">
         <v>15.5</v>
@@ -4299,19 +4299,19 @@
         <v>1000</v>
       </c>
       <c r="AP15">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AQ15">
         <v>19</v>
       </c>
       <c r="AR15">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AS15">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT15">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AU15">
         <v>8.6</v>
@@ -4320,7 +4320,7 @@
         <v>27</v>
       </c>
       <c r="AW15">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AX15">
         <v>6.4</v>
@@ -4332,85 +4332,85 @@
         <v>27</v>
       </c>
       <c r="BA15">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB15">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC15">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD15">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE15">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF15">
         <v>11</v>
       </c>
       <c r="BG15">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH15">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI15">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BJ15">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BK15">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BN15">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="BO15">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="BP15">
         <v>12</v>
       </c>
       <c r="BQ15">
-        <v>4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR15">
         <v>44</v>
       </c>
       <c r="BS15">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BT15">
         <v>15</v>
       </c>
       <c r="BU15">
-        <v>4.3</v>
+        <v>10</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BZ15">
         <v>32</v>
       </c>
       <c r="CA15">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="CB15" t="s">
         <v>145</v>
@@ -4436,7 +4436,7 @@
         <v>3.65</v>
       </c>
       <c r="G16">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H16">
         <v>1.77</v>
@@ -4472,7 +4472,7 @@
         <v>2.28</v>
       </c>
       <c r="S16">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="T16">
         <v>1.34</v>
@@ -4490,70 +4490,70 @@
         <v>160</v>
       </c>
       <c r="Y16">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="Z16">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AA16">
         <v>29</v>
       </c>
       <c r="AB16">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AC16">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AD16">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE16">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AF16">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="AG16">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AH16">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AI16">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AJ16">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AK16">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AL16">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AM16">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AN16">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AO16">
         <v>5</v>
       </c>
       <c r="AP16">
-        <v>5.3</v>
+        <v>29</v>
       </c>
       <c r="AQ16">
         <v>19.5</v>
       </c>
       <c r="AR16">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AS16">
         <v>19</v>
       </c>
       <c r="AT16">
-        <v>5.1</v>
+        <v>29</v>
       </c>
       <c r="AU16">
         <v>12</v>
@@ -4565,34 +4565,34 @@
         <v>12.5</v>
       </c>
       <c r="AX16">
-        <v>5.2</v>
+        <v>38</v>
       </c>
       <c r="AY16">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AZ16">
         <v>11.5</v>
       </c>
       <c r="BA16">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BB16">
-        <v>5.4</v>
+        <v>50</v>
       </c>
       <c r="BC16">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="BD16">
-        <v>4.9</v>
+        <v>20</v>
       </c>
       <c r="BE16">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="BF16">
         <v>12.5</v>
       </c>
       <c r="BG16">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BH16">
         <v>7.6</v>
@@ -4675,100 +4675,100 @@
         <v>140</v>
       </c>
       <c r="F17">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="G17">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="H17">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="I17">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J17">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="K17">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L17">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="M17">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N17">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="O17">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="P17">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="Q17">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="R17">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S17">
-        <v>3.45</v>
+        <v>5.3</v>
       </c>
       <c r="T17">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="U17">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="V17">
         <v>1.25</v>
       </c>
       <c r="W17">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="X17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y17">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z17">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="AA17">
         <v>900</v>
       </c>
       <c r="AB17">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC17">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD17">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AE17">
         <v>500</v>
       </c>
       <c r="AF17">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG17">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH17">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AI17">
         <v>500</v>
       </c>
       <c r="AJ17">
-        <v>160</v>
+        <v>28</v>
       </c>
       <c r="AK17">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="AL17">
         <v>130</v>
@@ -4777,64 +4777,64 @@
         <v>580</v>
       </c>
       <c r="AN17">
+        <v>28</v>
+      </c>
+      <c r="AO17">
         <v>500</v>
       </c>
-      <c r="AO17">
-        <v>600</v>
-      </c>
       <c r="AP17">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="AQ17">
-        <v>5.3</v>
+        <v>10.5</v>
       </c>
       <c r="AR17">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="AS17">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT17">
+        <v>6.2</v>
+      </c>
+      <c r="AU17">
+        <v>6.4</v>
+      </c>
+      <c r="AV17">
+        <v>17</v>
+      </c>
+      <c r="AW17">
+        <v>60</v>
+      </c>
+      <c r="AX17">
+        <v>9.6</v>
+      </c>
+      <c r="AY17">
+        <v>9.6</v>
+      </c>
+      <c r="AZ17">
+        <v>21</v>
+      </c>
+      <c r="BA17">
+        <v>10</v>
+      </c>
+      <c r="BB17">
         <v>8.4</v>
       </c>
-      <c r="AT17">
-        <v>4.1</v>
-      </c>
-      <c r="AU17">
-        <v>4.1</v>
-      </c>
-      <c r="AV17">
-        <v>6.2</v>
-      </c>
-      <c r="AW17">
-        <v>8</v>
-      </c>
-      <c r="AX17">
-        <v>5.2</v>
-      </c>
-      <c r="AY17">
-        <v>5.1</v>
-      </c>
-      <c r="AZ17">
-        <v>6.4</v>
-      </c>
-      <c r="BA17">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB17">
-        <v>6.8</v>
-      </c>
       <c r="BC17">
-        <v>6.8</v>
+        <v>24</v>
       </c>
       <c r="BD17">
-        <v>7.8</v>
+        <v>46</v>
       </c>
       <c r="BE17">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BF17">
-        <v>6.6</v>
+        <v>20</v>
       </c>
       <c r="BG17">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BH17">
         <v>3.3</v>
@@ -4920,55 +4920,55 @@
         <v>3.9</v>
       </c>
       <c r="G18">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H18">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="I18">
         <v>2.34</v>
       </c>
       <c r="J18">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K18">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L18">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="M18">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N18">
         <v>2.5</v>
       </c>
       <c r="O18">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P18">
         <v>1.48</v>
       </c>
       <c r="Q18">
-        <v>2.64</v>
+        <v>2.84</v>
       </c>
       <c r="R18">
         <v>1.18</v>
       </c>
       <c r="S18">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="T18">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U18">
         <v>1.71</v>
       </c>
       <c r="V18">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="W18">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X18">
         <v>8.4</v>
@@ -4980,31 +4980,31 @@
         <v>15.5</v>
       </c>
       <c r="AA18">
-        <v>900</v>
+        <v>42</v>
       </c>
       <c r="AB18">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC18">
         <v>7.6</v>
       </c>
       <c r="AD18">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE18">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AF18">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AG18">
         <v>23</v>
       </c>
       <c r="AH18">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AI18">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AJ18">
         <v>900</v>
@@ -5022,7 +5022,7 @@
         <v>600</v>
       </c>
       <c r="AO18">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AP18">
         <v>7</v>
@@ -5031,55 +5031,55 @@
         <v>5.9</v>
       </c>
       <c r="AR18">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS18">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="AT18">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU18">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV18">
         <v>10</v>
       </c>
       <c r="AW18">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="AX18">
         <v>21</v>
       </c>
       <c r="AY18">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AZ18">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA18">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="BB18">
-        <v>7.2</v>
+        <v>65</v>
       </c>
       <c r="BC18">
-        <v>7.2</v>
+        <v>42</v>
       </c>
       <c r="BD18">
-        <v>7.2</v>
+        <v>55</v>
       </c>
       <c r="BE18">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BF18">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BG18">
-        <v>6.4</v>
+        <v>22</v>
       </c>
       <c r="BH18">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="BI18">
         <v>2.36</v>
@@ -5088,7 +5088,7 @@
         <v>12.5</v>
       </c>
       <c r="BK18">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL18">
         <v>1000</v>
@@ -5106,13 +5106,13 @@
         <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BR18">
         <v>1000</v>
       </c>
       <c r="BS18">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BT18">
         <v>5</v>
@@ -5130,13 +5130,13 @@
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ18">
         <v>1000</v>
       </c>
       <c r="CA18">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CB18" t="s">
         <v>145</v>
@@ -5159,55 +5159,55 @@
         <v>142</v>
       </c>
       <c r="F19">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="G19">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H19">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="I19">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="J19">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="K19">
         <v>3.25</v>
       </c>
       <c r="L19">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="M19">
         <v>1.12</v>
       </c>
       <c r="N19">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="O19">
         <v>1.53</v>
       </c>
       <c r="P19">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="Q19">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="R19">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S19">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="T19">
         <v>2.04</v>
       </c>
       <c r="U19">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="V19">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W19">
         <v>1.45</v>
@@ -5216,37 +5216,37 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Y19">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Z19">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AA19">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="AB19">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC19">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AD19">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AE19">
-        <v>50</v>
+        <v>280</v>
       </c>
       <c r="AF19">
+        <v>19.5</v>
+      </c>
+      <c r="AG19">
+        <v>15</v>
+      </c>
+      <c r="AH19">
         <v>22</v>
       </c>
-      <c r="AG19">
-        <v>16.5</v>
-      </c>
-      <c r="AH19">
-        <v>26</v>
-      </c>
       <c r="AI19">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ19">
         <v>65</v>
@@ -5264,7 +5264,7 @@
         <v>65</v>
       </c>
       <c r="AO19">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP19">
         <v>7.6</v>
@@ -5276,10 +5276,10 @@
         <v>15</v>
       </c>
       <c r="AS19">
-        <v>5.5</v>
+        <v>16</v>
       </c>
       <c r="AT19">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU19">
         <v>6.2</v>
@@ -5288,7 +5288,7 @@
         <v>11.5</v>
       </c>
       <c r="AW19">
-        <v>5.4</v>
+        <v>20</v>
       </c>
       <c r="AX19">
         <v>16.5</v>
@@ -5300,85 +5300,85 @@
         <v>19</v>
       </c>
       <c r="BA19">
-        <v>5.2</v>
+        <v>11</v>
       </c>
       <c r="BB19">
-        <v>5.5</v>
+        <v>25</v>
       </c>
       <c r="BC19">
-        <v>5.4</v>
+        <v>20</v>
       </c>
       <c r="BD19">
-        <v>5.2</v>
+        <v>11</v>
       </c>
       <c r="BE19">
-        <v>5.9</v>
+        <v>10.5</v>
       </c>
       <c r="BF19">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG19">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="BH19">
-        <v>3.6</v>
+        <v>2.76</v>
       </c>
       <c r="BI19">
-        <v>2</v>
+        <v>2.48</v>
       </c>
       <c r="BJ19">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK19">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>1.4</v>
+        <v>7</v>
       </c>
       <c r="BN19">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO19">
-        <v>1.4</v>
+        <v>4.7</v>
       </c>
       <c r="BP19">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ19">
-        <v>1.4</v>
+        <v>6</v>
       </c>
       <c r="BR19">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS19">
-        <v>1.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT19">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU19">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="BV19">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW19">
-        <v>1.4</v>
+        <v>5.9</v>
       </c>
       <c r="BX19">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY19">
-        <v>1.4</v>
+        <v>6.4</v>
       </c>
       <c r="BZ19">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA19">
-        <v>1.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB19" t="s">
         <v>145</v>
@@ -5407,46 +5407,46 @@
         <v>2.04</v>
       </c>
       <c r="H20">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I20">
         <v>4.2</v>
       </c>
       <c r="J20">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K20">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L20">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="M20">
         <v>1.04</v>
       </c>
       <c r="N20">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="O20">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="P20">
+        <v>2.38</v>
+      </c>
+      <c r="Q20">
+        <v>1.64</v>
+      </c>
+      <c r="R20">
+        <v>1.54</v>
+      </c>
+      <c r="S20">
         <v>2.62</v>
       </c>
-      <c r="Q20">
-        <v>1.58</v>
-      </c>
-      <c r="R20">
-        <v>1.66</v>
-      </c>
-      <c r="S20">
-        <v>2.34</v>
-      </c>
       <c r="T20">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="U20">
-        <v>2.54</v>
+        <v>2.3</v>
       </c>
       <c r="V20">
         <v>1.32</v>
@@ -5455,172 +5455,172 @@
         <v>1.96</v>
       </c>
       <c r="X20">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="Y20">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="Z20">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA20">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AB20">
+        <v>13</v>
+      </c>
+      <c r="AC20">
+        <v>9.4</v>
+      </c>
+      <c r="AD20">
+        <v>18</v>
+      </c>
+      <c r="AE20">
+        <v>44</v>
+      </c>
+      <c r="AF20">
         <v>15.5</v>
-      </c>
-      <c r="AC20">
-        <v>11</v>
-      </c>
-      <c r="AD20">
-        <v>17.5</v>
-      </c>
-      <c r="AE20">
-        <v>38</v>
-      </c>
-      <c r="AF20">
-        <v>17</v>
       </c>
       <c r="AG20">
         <v>12</v>
       </c>
       <c r="AH20">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AI20">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AJ20">
         <v>25</v>
       </c>
       <c r="AK20">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AL20">
+        <v>32</v>
+      </c>
+      <c r="AM20">
+        <v>200</v>
+      </c>
+      <c r="AN20">
+        <v>11.5</v>
+      </c>
+      <c r="AO20">
+        <v>36</v>
+      </c>
+      <c r="AP20">
+        <v>17.5</v>
+      </c>
+      <c r="AQ20">
+        <v>15.5</v>
+      </c>
+      <c r="AR20">
+        <v>25</v>
+      </c>
+      <c r="AS20">
+        <v>48</v>
+      </c>
+      <c r="AT20">
+        <v>10</v>
+      </c>
+      <c r="AU20">
+        <v>7.4</v>
+      </c>
+      <c r="AV20">
+        <v>14</v>
+      </c>
+      <c r="AW20">
         <v>27</v>
       </c>
-      <c r="AM20">
-        <v>60</v>
-      </c>
-      <c r="AN20">
-        <v>9.6</v>
-      </c>
-      <c r="AO20">
-        <v>27</v>
-      </c>
-      <c r="AP20">
-        <v>21</v>
-      </c>
-      <c r="AQ20">
-        <v>18</v>
-      </c>
-      <c r="AR20">
-        <v>14.5</v>
-      </c>
-      <c r="AS20">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT20">
+      <c r="AX20">
         <v>12</v>
       </c>
-      <c r="AU20">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV20">
-        <v>13.5</v>
-      </c>
-      <c r="AW20">
-        <v>26</v>
-      </c>
-      <c r="AX20">
-        <v>13</v>
-      </c>
       <c r="AY20">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ20">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BA20">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BB20">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BC20">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD20">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BE20">
         <v>28</v>
       </c>
       <c r="BF20">
-        <v>4.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG20">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="BH20">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BI20">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="BJ20">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BK20">
         <v>6.8</v>
       </c>
       <c r="BL20">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BM20">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BN20">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BO20">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BP20">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BQ20">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BR20">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BS20">
+        <v>6.6</v>
+      </c>
+      <c r="BT20">
+        <v>7.8</v>
+      </c>
+      <c r="BU20">
         <v>6</v>
       </c>
-      <c r="BT20">
-        <v>8</v>
-      </c>
-      <c r="BU20">
-        <v>6.2</v>
-      </c>
       <c r="BV20">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BW20">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BX20">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BY20">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BZ20">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="CA20">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="CB20" t="s">
         <v>145</v>
@@ -5643,88 +5643,88 @@
         <v>144</v>
       </c>
       <c r="F21">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="G21">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="H21">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="I21">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="J21">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="K21">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L21">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="M21">
         <v>1.11</v>
       </c>
       <c r="N21">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="O21">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="P21">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q21">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="R21">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S21">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T21">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U21">
         <v>1.89</v>
       </c>
       <c r="V21">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="W21">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X21">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z21">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA21">
+        <v>38</v>
+      </c>
+      <c r="AB21">
+        <v>11</v>
+      </c>
+      <c r="AC21">
+        <v>7.2</v>
+      </c>
+      <c r="AD21">
+        <v>12</v>
+      </c>
+      <c r="AE21">
         <v>32</v>
       </c>
-      <c r="AB21">
-        <v>13.5</v>
-      </c>
-      <c r="AC21">
-        <v>7.4</v>
-      </c>
-      <c r="AD21">
-        <v>13</v>
-      </c>
-      <c r="AE21">
-        <v>34</v>
-      </c>
       <c r="AF21">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AG21">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="AH21">
         <v>21</v>
@@ -5733,37 +5733,37 @@
         <v>60</v>
       </c>
       <c r="AJ21">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AK21">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AL21">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM21">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AN21">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AO21">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="AP21">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AQ21">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR21">
         <v>11.5</v>
       </c>
       <c r="AS21">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="AT21">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AU21">
         <v>6.4</v>
@@ -5772,43 +5772,43 @@
         <v>10</v>
       </c>
       <c r="AW21">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX21">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AY21">
         <v>14</v>
       </c>
       <c r="AZ21">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA21">
-        <v>7.8</v>
+        <v>40</v>
       </c>
       <c r="BB21">
-        <v>8.199999999999999</v>
+        <v>55</v>
       </c>
       <c r="BC21">
-        <v>7.8</v>
+        <v>38</v>
       </c>
       <c r="BD21">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="BE21">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BF21">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="BG21">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BH21">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BI21">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="BJ21">
         <v>10.5</v>
@@ -5820,49 +5820,49 @@
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BN21">
         <v>7</v>
       </c>
       <c r="BO21">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BP21">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BQ21">
+        <v>7.8</v>
+      </c>
+      <c r="BR21">
+        <v>60</v>
+      </c>
+      <c r="BS21">
         <v>8.6</v>
       </c>
-      <c r="BR21">
-        <v>55</v>
-      </c>
-      <c r="BS21">
-        <v>9.4</v>
-      </c>
       <c r="BT21">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BU21">
         <v>4.3</v>
       </c>
       <c r="BV21">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BW21">
-        <v>14</v>
+        <v>6.6</v>
       </c>
       <c r="BX21">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="BY21">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ21">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="CA21">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB21" t="s">
         <v>145</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-27.xlsx
@@ -451,7 +451,7 @@
     <t>Millonarios</t>
   </si>
   <si>
-    <t>2026-08-27 08:48:05</t>
+    <t>2026-08-27 11:09:01</t>
   </si>
 </sst>
 </file>
@@ -1045,166 +1045,166 @@
         <v>125</v>
       </c>
       <c r="F2">
-        <v>2.28</v>
+        <v>2.56</v>
       </c>
       <c r="G2">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="I2">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="J2">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="K2">
-        <v>2.72</v>
+        <v>2.54</v>
       </c>
       <c r="L2">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="M2">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="N2">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="O2">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
       <c r="P2">
         <v>1.33</v>
       </c>
       <c r="Q2">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="R2">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="S2">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="T2">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="U2">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="V2">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="W2">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="X2">
-        <v>970</v>
+        <v>5.1</v>
       </c>
       <c r="Y2">
-        <v>30</v>
+        <v>9.4</v>
       </c>
       <c r="Z2">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AA2">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="AB2">
         <v>7.2</v>
       </c>
       <c r="AC2">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="AD2">
-        <v>950</v>
+        <v>22</v>
       </c>
       <c r="AE2">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AF2">
-        <v>38</v>
+        <v>14.5</v>
       </c>
       <c r="AG2">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AH2">
-        <v>950</v>
+        <v>55</v>
       </c>
       <c r="AI2">
-        <v>500</v>
+        <v>190</v>
       </c>
       <c r="AJ2">
-        <v>900</v>
+        <v>60</v>
       </c>
       <c r="AK2">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AL2">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AM2">
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="AN2">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO2">
-        <v>600</v>
+        <v>230</v>
       </c>
       <c r="AP2">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AQ2">
-        <v>2.44</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR2">
-        <v>2.72</v>
+        <v>26</v>
       </c>
       <c r="AS2">
-        <v>2.8</v>
+        <v>10</v>
       </c>
       <c r="AT2">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="AU2">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="AV2">
-        <v>2.56</v>
+        <v>17.5</v>
       </c>
       <c r="AW2">
-        <v>2.8</v>
+        <v>42</v>
       </c>
       <c r="AX2">
-        <v>2.44</v>
+        <v>12</v>
       </c>
       <c r="AY2">
-        <v>2.68</v>
+        <v>13</v>
       </c>
       <c r="AZ2">
-        <v>2.78</v>
+        <v>8.4</v>
       </c>
       <c r="BA2">
-        <v>2.8</v>
+        <v>10</v>
       </c>
       <c r="BB2">
-        <v>2.8</v>
+        <v>30</v>
       </c>
       <c r="BC2">
-        <v>2.68</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD2">
-        <v>2.78</v>
+        <v>10.5</v>
       </c>
       <c r="BE2">
-        <v>2.74</v>
+        <v>10</v>
       </c>
       <c r="BF2">
-        <v>2.74</v>
+        <v>17.5</v>
       </c>
       <c r="BG2">
-        <v>2.7</v>
+        <v>9.6</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1287,61 +1287,61 @@
         <v>126</v>
       </c>
       <c r="F3">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="G3">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="H3">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I3">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="J3">
+        <v>3.8</v>
+      </c>
+      <c r="K3">
         <v>3.95</v>
       </c>
-      <c r="K3">
-        <v>4.1</v>
-      </c>
       <c r="L3">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M3">
         <v>1.04</v>
       </c>
       <c r="N3">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O3">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P3">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q3">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R3">
+        <v>1.56</v>
+      </c>
+      <c r="S3">
+        <v>2.66</v>
+      </c>
+      <c r="T3">
         <v>1.55</v>
       </c>
-      <c r="S3">
-        <v>2.68</v>
-      </c>
-      <c r="T3">
-        <v>1.58</v>
-      </c>
       <c r="U3">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V3">
         <v>1.64</v>
       </c>
       <c r="W3">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="X3">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="Y3">
         <v>15</v>
@@ -1350,163 +1350,163 @@
         <v>19</v>
       </c>
       <c r="AA3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AB3">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AC3">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF3">
         <v>23</v>
       </c>
       <c r="AG3">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH3">
         <v>15.5</v>
       </c>
       <c r="AI3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ3">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AK3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL3">
         <v>34</v>
       </c>
       <c r="AM3">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO3">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AP3">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR3">
         <v>16</v>
       </c>
       <c r="AS3">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="AT3">
         <v>13.5</v>
       </c>
       <c r="AU3">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV3">
         <v>10</v>
       </c>
       <c r="AW3">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AX3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ3">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BB3">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="BC3">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="BD3">
+        <v>28</v>
+      </c>
+      <c r="BE3">
+        <v>46</v>
+      </c>
+      <c r="BF3">
+        <v>16</v>
+      </c>
+      <c r="BG3">
         <v>15</v>
       </c>
-      <c r="BE3">
-        <v>25</v>
-      </c>
-      <c r="BF3">
-        <v>14.5</v>
-      </c>
-      <c r="BG3">
-        <v>12</v>
-      </c>
       <c r="BH3">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BI3">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="BJ3">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK3">
-        <v>3.8</v>
+        <v>7</v>
       </c>
       <c r="BL3">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BM3">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="BN3">
         <v>7.2</v>
       </c>
       <c r="BO3">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BP3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BQ3">
-        <v>4.8</v>
+        <v>14.5</v>
       </c>
       <c r="BR3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BS3">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BT3">
         <v>6.6</v>
       </c>
       <c r="BU3">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BV3">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BW3">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BX3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BY3">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BZ3">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="CA3">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB3" t="s">
         <v>145</v>
@@ -1529,22 +1529,22 @@
         <v>127</v>
       </c>
       <c r="F4">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="G4">
         <v>1.7</v>
       </c>
       <c r="H4">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="I4">
         <v>7</v>
       </c>
       <c r="J4">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K4">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L4">
         <v>1.4</v>
@@ -1556,7 +1556,7 @@
         <v>3.8</v>
       </c>
       <c r="O4">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P4">
         <v>1.95</v>
@@ -1574,7 +1574,7 @@
         <v>1.92</v>
       </c>
       <c r="U4">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="V4">
         <v>1.17</v>
@@ -1583,10 +1583,10 @@
         <v>2.4</v>
       </c>
       <c r="X4">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="Z4">
         <v>60</v>
@@ -1598,10 +1598,10 @@
         <v>8.4</v>
       </c>
       <c r="AC4">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD4">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AE4">
         <v>260</v>
@@ -1616,7 +1616,7 @@
         <v>23</v>
       </c>
       <c r="AI4">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AJ4">
         <v>16</v>
@@ -1625,7 +1625,7 @@
         <v>18</v>
       </c>
       <c r="AL4">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AM4">
         <v>700</v>
@@ -1634,7 +1634,7 @@
         <v>10.5</v>
       </c>
       <c r="AO4">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AP4">
         <v>13</v>
@@ -1646,13 +1646,13 @@
         <v>36</v>
       </c>
       <c r="AS4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU4">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV4">
         <v>20</v>
@@ -1664,7 +1664,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AY4">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ4">
         <v>19.5</v>
@@ -1685,16 +1685,16 @@
         <v>10.5</v>
       </c>
       <c r="BF4">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH4">
         <v>3.9</v>
       </c>
       <c r="BI4">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="BJ4">
         <v>12.5</v>
@@ -1771,22 +1771,22 @@
         <v>128</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="G5">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="H5">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="I5">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="J5">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K5">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="L5">
         <v>1.51</v>
@@ -1801,46 +1801,46 @@
         <v>1.4</v>
       </c>
       <c r="P5">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q5">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="R5">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S5">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="T5">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U5">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V5">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="W5">
         <v>1.22</v>
       </c>
       <c r="X5">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y5">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z5">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AA5">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AB5">
         <v>16</v>
       </c>
       <c r="AC5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD5">
         <v>12.5</v>
@@ -1849,7 +1849,7 @@
         <v>23</v>
       </c>
       <c r="AF5">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AG5">
         <v>22</v>
@@ -1858,16 +1858,16 @@
         <v>23</v>
       </c>
       <c r="AI5">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ5">
         <v>470</v>
       </c>
       <c r="AK5">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AL5">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AM5">
         <v>500</v>
@@ -1879,16 +1879,16 @@
         <v>16.5</v>
       </c>
       <c r="AP5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ5">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AR5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AS5">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AT5">
         <v>13</v>
@@ -1903,7 +1903,7 @@
         <v>18.5</v>
       </c>
       <c r="AX5">
-        <v>7.8</v>
+        <v>30</v>
       </c>
       <c r="AY5">
         <v>18</v>
@@ -1915,7 +1915,7 @@
         <v>34</v>
       </c>
       <c r="BB5">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC5">
         <v>12.5</v>
@@ -1930,61 +1930,61 @@
         <v>12</v>
       </c>
       <c r="BG5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BH5">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="BI5">
-        <v>2.74</v>
+        <v>2.48</v>
       </c>
       <c r="BJ5">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BK5">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="BN5">
         <v>10.5</v>
       </c>
       <c r="BO5">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="BP5">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BQ5">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BR5">
         <v>80</v>
       </c>
       <c r="BS5">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BT5">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BU5">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BV5">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BW5">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX5">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BY5">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BZ5">
         <v>0</v>
@@ -2013,16 +2013,16 @@
         <v>129</v>
       </c>
       <c r="F6">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="G6">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="H6">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="I6">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="J6">
         <v>3.95</v>
@@ -2031,7 +2031,7 @@
         <v>4.3</v>
       </c>
       <c r="L6">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M6">
         <v>1.04</v>
@@ -2043,40 +2043,40 @@
         <v>1.2</v>
       </c>
       <c r="P6">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q6">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="R6">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="S6">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="T6">
         <v>1.6</v>
       </c>
       <c r="U6">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="V6">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="W6">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="X6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y6">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z6">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA6">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AB6">
         <v>22</v>
@@ -2085,40 +2085,40 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE6">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AF6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AG6">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AH6">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI6">
         <v>27</v>
       </c>
       <c r="AJ6">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AK6">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AL6">
         <v>46</v>
       </c>
       <c r="AM6">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="AN6">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AO6">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AP6">
         <v>20</v>
@@ -2145,10 +2145,10 @@
         <v>16</v>
       </c>
       <c r="AX6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY6">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AZ6">
         <v>13</v>
@@ -2157,82 +2157,82 @@
         <v>22</v>
       </c>
       <c r="BB6">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BC6">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BD6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE6">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BF6">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BG6">
         <v>8.4</v>
       </c>
       <c r="BH6">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BI6">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BJ6">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BK6">
         <v>6.8</v>
       </c>
       <c r="BL6">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BM6">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="BN6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BO6">
-        <v>5.5</v>
+        <v>3.35</v>
       </c>
       <c r="BP6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BQ6">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="BR6">
         <v>38</v>
       </c>
       <c r="BS6">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="BT6">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BU6">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BV6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BW6">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="BX6">
         <v>26</v>
       </c>
       <c r="BY6">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="BZ6">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="CA6">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="CB6" t="s">
         <v>145</v>
@@ -2255,226 +2255,226 @@
         <v>130</v>
       </c>
       <c r="F7">
+        <v>1.42</v>
+      </c>
+      <c r="G7">
+        <v>1.44</v>
+      </c>
+      <c r="H7">
+        <v>10</v>
+      </c>
+      <c r="I7">
+        <v>10.5</v>
+      </c>
+      <c r="J7">
+        <v>4.7</v>
+      </c>
+      <c r="K7">
+        <v>5</v>
+      </c>
+      <c r="L7">
+        <v>1.41</v>
+      </c>
+      <c r="M7">
+        <v>1.07</v>
+      </c>
+      <c r="N7">
+        <v>3.65</v>
+      </c>
+      <c r="O7">
+        <v>1.35</v>
+      </c>
+      <c r="P7">
+        <v>1.9</v>
+      </c>
+      <c r="Q7">
+        <v>2.06</v>
+      </c>
+      <c r="R7">
         <v>1.32</v>
       </c>
-      <c r="G7">
-        <v>1.34</v>
-      </c>
-      <c r="H7">
-        <v>14</v>
-      </c>
-      <c r="I7">
-        <v>15</v>
-      </c>
-      <c r="J7">
-        <v>5.5</v>
-      </c>
-      <c r="K7">
-        <v>5.8</v>
-      </c>
-      <c r="L7">
-        <v>1.4</v>
-      </c>
-      <c r="M7">
-        <v>1.06</v>
-      </c>
-      <c r="N7">
-        <v>3.9</v>
-      </c>
-      <c r="O7">
-        <v>1.33</v>
-      </c>
-      <c r="P7">
-        <v>1.99</v>
-      </c>
-      <c r="Q7">
-        <v>1.96</v>
-      </c>
-      <c r="R7">
-        <v>1.36</v>
-      </c>
       <c r="S7">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="T7">
-        <v>2.52</v>
+        <v>2.34</v>
       </c>
       <c r="U7">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="V7">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="W7">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="X7">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y7">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="Z7">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="AA7">
-        <v>770</v>
+        <v>480</v>
       </c>
       <c r="AB7">
         <v>7</v>
       </c>
       <c r="AC7">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AD7">
-        <v>160</v>
+        <v>42</v>
       </c>
       <c r="AE7">
-        <v>450</v>
+        <v>230</v>
       </c>
       <c r="AF7">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AG7">
         <v>11</v>
       </c>
       <c r="AH7">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AI7">
-        <v>330</v>
+        <v>200</v>
       </c>
       <c r="AJ7">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="AK7">
         <v>17</v>
       </c>
       <c r="AL7">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM7">
-        <v>330</v>
+        <v>790</v>
       </c>
       <c r="AN7">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AO7">
-        <v>570</v>
+        <v>430</v>
       </c>
       <c r="AP7">
         <v>13</v>
       </c>
       <c r="AQ7">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AR7">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="AS7">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AT7">
         <v>6.2</v>
       </c>
       <c r="AU7">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV7">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AW7">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AX7">
         <v>6</v>
       </c>
       <c r="AY7">
+        <v>9.4</v>
+      </c>
+      <c r="AZ7">
+        <v>30</v>
+      </c>
+      <c r="BA7">
+        <v>11.5</v>
+      </c>
+      <c r="BB7">
         <v>10</v>
-      </c>
-      <c r="AZ7">
-        <v>36</v>
-      </c>
-      <c r="BA7">
-        <v>13.5</v>
-      </c>
-      <c r="BB7">
-        <v>8.800000000000001</v>
       </c>
       <c r="BC7">
         <v>15</v>
       </c>
       <c r="BD7">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BE7">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BF7">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BG7">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BH7">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI7">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="BJ7">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="BK7">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BN7">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BO7">
         <v>3</v>
       </c>
       <c r="BP7">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BQ7">
-        <v>5.8</v>
+        <v>3.7</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS7">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BT7">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BU7">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BZ7">
         <v>17.5</v>
       </c>
       <c r="CA7">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="CB7" t="s">
         <v>145</v>
@@ -2497,31 +2497,31 @@
         <v>131</v>
       </c>
       <c r="F8">
+        <v>3.95</v>
+      </c>
+      <c r="G8">
         <v>4.2</v>
       </c>
-      <c r="G8">
-        <v>4.5</v>
-      </c>
       <c r="H8">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="I8">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="J8">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="K8">
         <v>3.05</v>
       </c>
       <c r="L8">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="M8">
         <v>1.15</v>
       </c>
       <c r="N8">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O8">
         <v>1.63</v>
@@ -2530,13 +2530,13 @@
         <v>1.47</v>
       </c>
       <c r="Q8">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="R8">
         <v>1.16</v>
       </c>
       <c r="S8">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="T8">
         <v>2.24</v>
@@ -2545,25 +2545,25 @@
         <v>1.69</v>
       </c>
       <c r="V8">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="W8">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="X8">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Y8">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="Z8">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AB8">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC8">
         <v>7.2</v>
@@ -2575,25 +2575,25 @@
         <v>44</v>
       </c>
       <c r="AF8">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AG8">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="AH8">
         <v>32</v>
       </c>
       <c r="AI8">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="AJ8">
-        <v>900</v>
+        <v>150</v>
       </c>
       <c r="AK8">
-        <v>230</v>
+        <v>95</v>
       </c>
       <c r="AL8">
-        <v>500</v>
+        <v>260</v>
       </c>
       <c r="AM8">
         <v>500</v>
@@ -2602,22 +2602,22 @@
         <v>600</v>
       </c>
       <c r="AO8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AP8">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ8">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AR8">
         <v>10.5</v>
       </c>
       <c r="AS8">
-        <v>15.5</v>
+        <v>27</v>
       </c>
       <c r="AT8">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU8">
         <v>6.4</v>
@@ -2626,37 +2626,37 @@
         <v>10.5</v>
       </c>
       <c r="AW8">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="AX8">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AY8">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AZ8">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="BA8">
+        <v>46</v>
+      </c>
+      <c r="BB8">
+        <v>65</v>
+      </c>
+      <c r="BC8">
+        <v>50</v>
+      </c>
+      <c r="BD8">
+        <v>70</v>
+      </c>
+      <c r="BE8">
+        <v>9.4</v>
+      </c>
+      <c r="BF8">
         <v>7.6</v>
       </c>
-      <c r="BB8">
-        <v>7.8</v>
-      </c>
-      <c r="BC8">
-        <v>7.6</v>
-      </c>
-      <c r="BD8">
-        <v>7.8</v>
-      </c>
-      <c r="BE8">
-        <v>8</v>
-      </c>
-      <c r="BF8">
-        <v>8</v>
-      </c>
       <c r="BG8">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="BH8">
         <v>2.92</v>
@@ -2665,58 +2665,58 @@
         <v>2.12</v>
       </c>
       <c r="BJ8">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BK8">
-        <v>3.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
+        <v>7.4</v>
+      </c>
+      <c r="BN8">
+        <v>7</v>
+      </c>
+      <c r="BO8">
+        <v>3.6</v>
+      </c>
+      <c r="BP8">
+        <v>55</v>
+      </c>
+      <c r="BQ8">
+        <v>6.6</v>
+      </c>
+      <c r="BR8">
+        <v>85</v>
+      </c>
+      <c r="BS8">
+        <v>6.8</v>
+      </c>
+      <c r="BT8">
         <v>5</v>
       </c>
-      <c r="BN8">
-        <v>8.6</v>
-      </c>
-      <c r="BO8">
-        <v>5.4</v>
-      </c>
-      <c r="BP8">
-        <v>60</v>
-      </c>
-      <c r="BQ8">
-        <v>4.7</v>
-      </c>
-      <c r="BR8">
-        <v>90</v>
-      </c>
-      <c r="BS8">
-        <v>4.8</v>
-      </c>
-      <c r="BT8">
-        <v>5.6</v>
-      </c>
       <c r="BU8">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="BV8">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BW8">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="BX8">
         <v>60</v>
       </c>
       <c r="BY8">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="BZ8">
         <v>70</v>
       </c>
       <c r="CA8">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="CB8" t="s">
         <v>145</v>
@@ -2739,7 +2739,7 @@
         <v>132</v>
       </c>
       <c r="F9">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="G9">
         <v>3.45</v>
@@ -2748,13 +2748,13 @@
         <v>2.36</v>
       </c>
       <c r="I9">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="J9">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K9">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L9">
         <v>1.43</v>
@@ -2769,10 +2769,10 @@
         <v>1.35</v>
       </c>
       <c r="P9">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q9">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R9">
         <v>1.31</v>
@@ -2787,10 +2787,10 @@
         <v>2.06</v>
       </c>
       <c r="V9">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="W9">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X9">
         <v>13.5</v>
@@ -2802,7 +2802,7 @@
         <v>16</v>
       </c>
       <c r="AA9">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB9">
         <v>13</v>
@@ -2817,7 +2817,7 @@
         <v>38</v>
       </c>
       <c r="AF9">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AG9">
         <v>14.5</v>
@@ -2829,13 +2829,13 @@
         <v>60</v>
       </c>
       <c r="AJ9">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AK9">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AL9">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM9">
         <v>580</v>
@@ -2844,7 +2844,7 @@
         <v>500</v>
       </c>
       <c r="AO9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP9">
         <v>11</v>
@@ -2856,7 +2856,7 @@
         <v>13.5</v>
       </c>
       <c r="AS9">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AT9">
         <v>10.5</v>
@@ -2871,7 +2871,7 @@
         <v>22</v>
       </c>
       <c r="AX9">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AY9">
         <v>12</v>
@@ -2883,10 +2883,10 @@
         <v>29</v>
       </c>
       <c r="BB9">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BC9">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD9">
         <v>34</v>
@@ -2895,7 +2895,7 @@
         <v>75</v>
       </c>
       <c r="BF9">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BG9">
         <v>18.5</v>
@@ -2904,7 +2904,7 @@
         <v>3.4</v>
       </c>
       <c r="BI9">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="BJ9">
         <v>10</v>
@@ -2925,7 +2925,7 @@
         <v>5.1</v>
       </c>
       <c r="BP9">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BQ9">
         <v>7.8</v>
@@ -2940,22 +2940,22 @@
         <v>5.4</v>
       </c>
       <c r="BU9">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BV9">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BW9">
         <v>6.8</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY9">
         <v>8.199999999999999</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="CA9">
         <v>8</v>
@@ -2981,226 +2981,226 @@
         <v>133</v>
       </c>
       <c r="F10">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="G10">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="H10">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="I10">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="J10">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="K10">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="L10">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="M10">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N10">
-        <v>2.96</v>
+        <v>1.01</v>
       </c>
       <c r="O10">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="P10">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="Q10">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="R10">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="S10">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="T10">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="U10">
-        <v>1.72</v>
+        <v>1.51</v>
       </c>
       <c r="V10">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="W10">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="X10">
-        <v>11.5</v>
+        <v>950</v>
       </c>
       <c r="Y10">
-        <v>15.5</v>
+        <v>23</v>
       </c>
       <c r="Z10">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AA10">
         <v>900</v>
       </c>
       <c r="AB10">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AC10">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD10">
-        <v>30</v>
+        <v>950</v>
       </c>
       <c r="AE10">
-        <v>480</v>
+        <v>700</v>
       </c>
       <c r="AF10">
-        <v>9.6</v>
+        <v>16</v>
       </c>
       <c r="AG10">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH10">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AI10">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="AJ10">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AK10">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AL10">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AM10">
         <v>580</v>
       </c>
       <c r="AN10">
-        <v>23</v>
+        <v>13.5</v>
       </c>
       <c r="AO10">
-        <v>700</v>
+        <v>420</v>
       </c>
       <c r="AP10">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AQ10">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="AR10">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AS10">
-        <v>9.6</v>
+        <v>6.6</v>
       </c>
       <c r="AT10">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="AU10">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AV10">
+        <v>11.5</v>
+      </c>
+      <c r="AW10">
+        <v>6.4</v>
+      </c>
+      <c r="AX10">
+        <v>6.8</v>
+      </c>
+      <c r="AY10">
+        <v>6.4</v>
+      </c>
+      <c r="AZ10">
+        <v>19.5</v>
+      </c>
+      <c r="BA10">
+        <v>6.4</v>
+      </c>
+      <c r="BB10">
+        <v>12.5</v>
+      </c>
+      <c r="BC10">
         <v>18</v>
       </c>
-      <c r="AW10">
-        <v>55</v>
-      </c>
-      <c r="AX10">
-        <v>8.4</v>
-      </c>
-      <c r="AY10">
-        <v>9.4</v>
-      </c>
-      <c r="AZ10">
-        <v>22</v>
-      </c>
-      <c r="BA10">
-        <v>40</v>
-      </c>
-      <c r="BB10">
-        <v>17</v>
-      </c>
-      <c r="BC10">
+      <c r="BD10">
         <v>20</v>
       </c>
-      <c r="BD10">
-        <v>32</v>
-      </c>
       <c r="BE10">
-        <v>10</v>
+        <v>6.4</v>
       </c>
       <c r="BF10">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="BG10">
-        <v>9.6</v>
+        <v>6.6</v>
       </c>
       <c r="BH10">
         <v>3.3</v>
       </c>
       <c r="BI10">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="BJ10">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BK10">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
+        <v>5.5</v>
+      </c>
+      <c r="BN10">
+        <v>4.3</v>
+      </c>
+      <c r="BO10">
+        <v>2.98</v>
+      </c>
+      <c r="BP10">
+        <v>13</v>
+      </c>
+      <c r="BQ10">
+        <v>3.9</v>
+      </c>
+      <c r="BR10">
+        <v>42</v>
+      </c>
+      <c r="BS10">
         <v>4.9</v>
       </c>
-      <c r="BN10">
+      <c r="BT10">
+        <v>13.5</v>
+      </c>
+      <c r="BU10">
+        <v>3.95</v>
+      </c>
+      <c r="BV10">
+        <v>1000</v>
+      </c>
+      <c r="BW10">
+        <v>5.4</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
+        <v>5.4</v>
+      </c>
+      <c r="BZ10">
+        <v>32</v>
+      </c>
+      <c r="CA10">
         <v>4.8</v>
-      </c>
-      <c r="BO10">
-        <v>3.2</v>
-      </c>
-      <c r="BP10">
-        <v>16.5</v>
-      </c>
-      <c r="BQ10">
-        <v>3.85</v>
-      </c>
-      <c r="BR10">
-        <v>46</v>
-      </c>
-      <c r="BS10">
-        <v>4.5</v>
-      </c>
-      <c r="BT10">
-        <v>11</v>
-      </c>
-      <c r="BU10">
-        <v>3.45</v>
-      </c>
-      <c r="BV10">
-        <v>80</v>
-      </c>
-      <c r="BW10">
-        <v>4.7</v>
-      </c>
-      <c r="BX10">
-        <v>100</v>
-      </c>
-      <c r="BY10">
-        <v>4.8</v>
-      </c>
-      <c r="BZ10">
-        <v>44</v>
-      </c>
-      <c r="CA10">
-        <v>4.5</v>
       </c>
       <c r="CB10" t="s">
         <v>145</v>
@@ -3223,58 +3223,58 @@
         <v>134</v>
       </c>
       <c r="F11">
+        <v>2.02</v>
+      </c>
+      <c r="G11">
         <v>2.04</v>
       </c>
-      <c r="G11">
-        <v>2.06</v>
-      </c>
       <c r="H11">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I11">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J11">
+        <v>3.4</v>
+      </c>
+      <c r="K11">
         <v>3.45</v>
       </c>
-      <c r="K11">
-        <v>3.5</v>
-      </c>
       <c r="L11">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="M11">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N11">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O11">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="P11">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Q11">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="R11">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S11">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="T11">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="U11">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V11">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W11">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="X11">
         <v>10.5</v>
@@ -3286,13 +3286,13 @@
         <v>32</v>
       </c>
       <c r="AA11">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB11">
         <v>7.4</v>
       </c>
       <c r="AC11">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD11">
         <v>18</v>
@@ -3310,13 +3310,13 @@
         <v>23</v>
       </c>
       <c r="AI11">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AJ11">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK11">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL11">
         <v>50</v>
@@ -3325,25 +3325,25 @@
         <v>160</v>
       </c>
       <c r="AN11">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AO11">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AP11">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AQ11">
         <v>11.5</v>
       </c>
       <c r="AR11">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS11">
         <v>95</v>
       </c>
       <c r="AT11">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU11">
         <v>7.2</v>
@@ -3364,10 +3364,10 @@
         <v>21</v>
       </c>
       <c r="BA11">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BB11">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC11">
         <v>22</v>
@@ -3376,34 +3376,34 @@
         <v>46</v>
       </c>
       <c r="BE11">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="BF11">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BG11">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="BH11">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="BI11">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="BJ11">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK11">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BL11">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="BM11">
-        <v>23</v>
+        <v>160</v>
       </c>
       <c r="BN11">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BO11">
         <v>4.2</v>
@@ -3415,16 +3415,16 @@
         <v>14</v>
       </c>
       <c r="BR11">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS11">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BT11">
         <v>7.6</v>
       </c>
       <c r="BU11">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BV11">
         <v>44</v>
@@ -3433,16 +3433,16 @@
         <v>36</v>
       </c>
       <c r="BX11">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BY11">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BZ11">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="CA11">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="CB11" t="s">
         <v>145</v>
@@ -3465,10 +3465,10 @@
         <v>135</v>
       </c>
       <c r="F12">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="G12">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="H12">
         <v>5.2</v>
@@ -3489,28 +3489,28 @@
         <v>1.04</v>
       </c>
       <c r="N12">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O12">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P12">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="Q12">
         <v>1.62</v>
       </c>
       <c r="R12">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="S12">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="T12">
-        <v>1.67</v>
+        <v>1.11</v>
       </c>
       <c r="U12">
-        <v>2.28</v>
+        <v>1.98</v>
       </c>
       <c r="V12">
         <v>1.01</v>
@@ -3519,55 +3519,55 @@
         <v>1.01</v>
       </c>
       <c r="X12">
-        <v>30</v>
+        <v>950</v>
       </c>
       <c r="Y12">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="Z12">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="AA12">
         <v>900</v>
       </c>
       <c r="AB12">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC12">
         <v>11</v>
       </c>
       <c r="AD12">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="AE12">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="AF12">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG12">
         <v>10.5</v>
       </c>
       <c r="AH12">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="AI12">
         <v>70</v>
       </c>
       <c r="AJ12">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AK12">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AL12">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AM12">
-        <v>95</v>
+        <v>320</v>
       </c>
       <c r="AN12">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AO12">
         <v>65</v>
@@ -3576,37 +3576,37 @@
         <v>11.5</v>
       </c>
       <c r="AQ12">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AR12">
         <v>7.4</v>
       </c>
       <c r="AS12">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT12">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU12">
         <v>9.6</v>
       </c>
       <c r="AV12">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW12">
-        <v>24</v>
+        <v>7.6</v>
       </c>
       <c r="AX12">
         <v>10.5</v>
       </c>
       <c r="AY12">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ12">
         <v>16</v>
       </c>
       <c r="BA12">
-        <v>40</v>
+        <v>7.6</v>
       </c>
       <c r="BB12">
         <v>14.5</v>
@@ -3615,76 +3615,76 @@
         <v>13.5</v>
       </c>
       <c r="BD12">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BE12">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BF12">
         <v>6</v>
       </c>
       <c r="BG12">
-        <v>20</v>
+        <v>7.6</v>
       </c>
       <c r="BH12">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BI12">
+        <v>3.5</v>
+      </c>
+      <c r="BJ12">
+        <v>11</v>
+      </c>
+      <c r="BK12">
         <v>3.4</v>
-      </c>
-      <c r="BJ12">
-        <v>11.5</v>
-      </c>
-      <c r="BK12">
-        <v>3.3</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BN12">
         <v>5.4</v>
       </c>
       <c r="BO12">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP12">
         <v>12.5</v>
       </c>
       <c r="BQ12">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="BR12">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS12">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BT12">
         <v>11</v>
       </c>
       <c r="BU12">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="BV12">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BW12">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BX12">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BY12">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BZ12">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CA12">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="CB12" t="s">
         <v>145</v>
@@ -3707,25 +3707,25 @@
         <v>136</v>
       </c>
       <c r="F13">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="G13">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="H13">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="I13">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="J13">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="K13">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="L13">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M13">
         <v>1.02</v>
@@ -3734,7 +3734,7 @@
         <v>6.6</v>
       </c>
       <c r="O13">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P13">
         <v>3.05</v>
@@ -3743,46 +3743,46 @@
         <v>1.44</v>
       </c>
       <c r="R13">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="S13">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="T13">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U13">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="V13">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W13">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="X13">
-        <v>46</v>
+        <v>950</v>
       </c>
       <c r="Y13">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="Z13">
-        <v>450</v>
+        <v>120</v>
       </c>
       <c r="AA13">
-        <v>320</v>
+        <v>400</v>
       </c>
       <c r="AB13">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC13">
         <v>15.5</v>
       </c>
       <c r="AD13">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AE13">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AF13">
         <v>11</v>
@@ -3791,10 +3791,10 @@
         <v>12</v>
       </c>
       <c r="AH13">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="AI13">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="AJ13">
         <v>12</v>
@@ -3803,13 +3803,13 @@
         <v>14.5</v>
       </c>
       <c r="AL13">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AM13">
-        <v>260</v>
+        <v>130</v>
       </c>
       <c r="AN13">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="AO13">
         <v>160</v>
@@ -3821,19 +3821,19 @@
         <v>32</v>
       </c>
       <c r="AR13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS13">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT13">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU13">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AV13">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW13">
         <v>10</v>
@@ -3842,85 +3842,85 @@
         <v>9</v>
       </c>
       <c r="AY13">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ13">
+        <v>21</v>
+      </c>
+      <c r="BA13">
+        <v>10</v>
+      </c>
+      <c r="BB13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC13">
+        <v>11.5</v>
+      </c>
+      <c r="BD13">
         <v>20</v>
       </c>
-      <c r="BA13">
-        <v>9</v>
-      </c>
-      <c r="BB13">
+      <c r="BE13">
         <v>10</v>
       </c>
-      <c r="BC13">
-        <v>11</v>
-      </c>
-      <c r="BD13">
-        <v>23</v>
-      </c>
-      <c r="BE13">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BF13">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BG13">
         <v>15</v>
       </c>
       <c r="BH13">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BI13">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BJ13">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BK13">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BN13">
         <v>4.3</v>
       </c>
       <c r="BO13">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BP13">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BQ13">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BR13">
         <v>23</v>
       </c>
       <c r="BS13">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT13">
         <v>14.5</v>
       </c>
       <c r="BU13">
-        <v>5.6</v>
+        <v>9.6</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BZ13">
         <v>0</v>
@@ -3949,25 +3949,25 @@
         <v>137</v>
       </c>
       <c r="F14">
+        <v>1.25</v>
+      </c>
+      <c r="G14">
         <v>1.26</v>
-      </c>
-      <c r="G14">
-        <v>1.27</v>
       </c>
       <c r="H14">
         <v>13.5</v>
       </c>
       <c r="I14">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="J14">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="K14">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="L14">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M14">
         <v>1.02</v>
@@ -3979,40 +3979,40 @@
         <v>1.13</v>
       </c>
       <c r="P14">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q14">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="R14">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="S14">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="T14">
         <v>1.86</v>
       </c>
       <c r="U14">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V14">
         <v>1.07</v>
       </c>
       <c r="W14">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="X14">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Y14">
         <v>60</v>
       </c>
       <c r="Z14">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AA14">
-        <v>540</v>
+        <v>630</v>
       </c>
       <c r="AB14">
         <v>13.5</v>
@@ -4021,10 +4021,10 @@
         <v>17.5</v>
       </c>
       <c r="AD14">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AE14">
-        <v>180</v>
+        <v>230</v>
       </c>
       <c r="AF14">
         <v>9.4</v>
@@ -4048,10 +4048,10 @@
         <v>28</v>
       </c>
       <c r="AM14">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN14">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AO14">
         <v>170</v>
@@ -4063,22 +4063,22 @@
         <v>55</v>
       </c>
       <c r="AR14">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AS14">
-        <v>110</v>
+        <v>440</v>
       </c>
       <c r="AT14">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU14">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AV14">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AW14">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AX14">
         <v>9.199999999999999</v>
@@ -4108,7 +4108,7 @@
         <v>3.3</v>
       </c>
       <c r="BG14">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="BH14">
         <v>5.4</v>
@@ -4117,16 +4117,16 @@
         <v>5</v>
       </c>
       <c r="BJ14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BK14">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BL14">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="BM14">
-        <v>18.5</v>
+        <v>110</v>
       </c>
       <c r="BN14">
         <v>4.1</v>
@@ -4135,40 +4135,40 @@
         <v>3.85</v>
       </c>
       <c r="BP14">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BQ14">
         <v>6</v>
       </c>
       <c r="BR14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BS14">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BT14">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BU14">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BV14">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="BW14">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BX14">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BY14">
-        <v>16.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CA14">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB14" t="s">
         <v>145</v>
@@ -4191,76 +4191,76 @@
         <v>138</v>
       </c>
       <c r="F15">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="G15">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="H15">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="I15">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="J15">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="K15">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L15">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M15">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N15">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="O15">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P15">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Q15">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="R15">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S15">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T15">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="U15">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="V15">
         <v>1.11</v>
       </c>
       <c r="W15">
-        <v>2.78</v>
+        <v>2.58</v>
       </c>
       <c r="X15">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y15">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Z15">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AA15">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AB15">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC15">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD15">
         <v>46</v>
@@ -4269,148 +4269,148 @@
         <v>330</v>
       </c>
       <c r="AF15">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AG15">
         <v>11.5</v>
       </c>
       <c r="AH15">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AI15">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="AJ15">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AK15">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AL15">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM15">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="AN15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO15">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AP15">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AQ15">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR15">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="AS15">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AT15">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AU15">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AV15">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW15">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AX15">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY15">
         <v>9.6</v>
       </c>
       <c r="AZ15">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB15">
+        <v>12.5</v>
+      </c>
+      <c r="BC15">
+        <v>19.5</v>
+      </c>
+      <c r="BD15">
+        <v>30</v>
+      </c>
+      <c r="BE15">
+        <v>8</v>
+      </c>
+      <c r="BF15">
         <v>11.5</v>
       </c>
-      <c r="BC15">
-        <v>19</v>
-      </c>
-      <c r="BD15">
-        <v>34</v>
-      </c>
-      <c r="BE15">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF15">
-        <v>11</v>
-      </c>
       <c r="BG15">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="BH15">
         <v>3.2</v>
       </c>
       <c r="BI15">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BJ15">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BK15">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BN15">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="BO15">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="BP15">
         <v>12</v>
       </c>
       <c r="BQ15">
-        <v>8.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="BR15">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BS15">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="BT15">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BU15">
-        <v>10</v>
+        <v>4.4</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BZ15">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="CA15">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="CB15" t="s">
         <v>145</v>
@@ -4463,19 +4463,19 @@
         <v>1.08</v>
       </c>
       <c r="P16">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Q16">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="R16">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S16">
         <v>1.68</v>
       </c>
       <c r="T16">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="U16">
         <v>3.1</v>
@@ -4496,10 +4496,10 @@
         <v>23</v>
       </c>
       <c r="AA16">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AB16">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AC16">
         <v>16.5</v>
@@ -4511,7 +4511,7 @@
         <v>17.5</v>
       </c>
       <c r="AF16">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="AG16">
         <v>21</v>
@@ -4523,25 +4523,25 @@
         <v>21</v>
       </c>
       <c r="AJ16">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AK16">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="AL16">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="AM16">
-        <v>48</v>
+        <v>200</v>
       </c>
       <c r="AN16">
         <v>16</v>
       </c>
       <c r="AO16">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AP16">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="AQ16">
         <v>19.5</v>
@@ -4553,7 +4553,7 @@
         <v>19</v>
       </c>
       <c r="AT16">
-        <v>29</v>
+        <v>7.4</v>
       </c>
       <c r="AU16">
         <v>12</v>
@@ -4565,7 +4565,7 @@
         <v>12.5</v>
       </c>
       <c r="AX16">
-        <v>38</v>
+        <v>7.8</v>
       </c>
       <c r="AY16">
         <v>16.5</v>
@@ -4577,16 +4577,16 @@
         <v>16.5</v>
       </c>
       <c r="BB16">
-        <v>50</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC16">
-        <v>23</v>
+        <v>14.5</v>
       </c>
       <c r="BD16">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="BE16">
-        <v>30</v>
+        <v>15.5</v>
       </c>
       <c r="BF16">
         <v>12.5</v>
@@ -4598,16 +4598,16 @@
         <v>7.6</v>
       </c>
       <c r="BI16">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BJ16">
         <v>9.4</v>
       </c>
       <c r="BK16">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BL16">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BM16">
         <v>4.9</v>
@@ -4616,37 +4616,37 @@
         <v>10.5</v>
       </c>
       <c r="BO16">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP16">
         <v>28</v>
       </c>
       <c r="BQ16">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BR16">
         <v>26</v>
       </c>
       <c r="BS16">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BT16">
         <v>6.8</v>
       </c>
       <c r="BU16">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="BV16">
         <v>13</v>
       </c>
       <c r="BW16">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BX16">
         <v>17.5</v>
       </c>
       <c r="BY16">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BZ16">
         <v>0</v>
@@ -4681,97 +4681,97 @@
         <v>2.12</v>
       </c>
       <c r="H17">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="I17">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J17">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K17">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L17">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="M17">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N17">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="O17">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="P17">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="Q17">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="R17">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S17">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="T17">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="U17">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="V17">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W17">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X17">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="Y17">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z17">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AA17">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="AB17">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC17">
         <v>8</v>
       </c>
       <c r="AD17">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE17">
         <v>500</v>
       </c>
       <c r="AF17">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG17">
         <v>11.5</v>
       </c>
       <c r="AH17">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI17">
-        <v>500</v>
+        <v>260</v>
       </c>
       <c r="AJ17">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AK17">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AL17">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="AM17">
         <v>580</v>
@@ -4780,7 +4780,7 @@
         <v>28</v>
       </c>
       <c r="AO17">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AP17">
         <v>7.4</v>
@@ -4792,22 +4792,22 @@
         <v>26</v>
       </c>
       <c r="AS17">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AT17">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AU17">
         <v>6.4</v>
       </c>
       <c r="AV17">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW17">
         <v>60</v>
       </c>
       <c r="AX17">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AY17">
         <v>9.6</v>
@@ -4816,85 +4816,85 @@
         <v>21</v>
       </c>
       <c r="BA17">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB17">
-        <v>8.4</v>
+        <v>21</v>
       </c>
       <c r="BC17">
         <v>24</v>
       </c>
       <c r="BD17">
-        <v>46</v>
+        <v>10.5</v>
       </c>
       <c r="BE17">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF17">
         <v>20</v>
       </c>
       <c r="BG17">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH17">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="BI17">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="BJ17">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK17">
-        <v>1.45</v>
+        <v>5.6</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>1.45</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN17">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO17">
-        <v>1.45</v>
+        <v>3.45</v>
       </c>
       <c r="BP17">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ17">
-        <v>1.45</v>
+        <v>6.4</v>
       </c>
       <c r="BR17">
         <v>1000</v>
       </c>
       <c r="BS17">
-        <v>1.45</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT17">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU17">
-        <v>1.45</v>
+        <v>4.6</v>
       </c>
       <c r="BV17">
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>1.45</v>
+        <v>8.6</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>1.45</v>
+        <v>9</v>
       </c>
       <c r="BZ17">
         <v>1000</v>
       </c>
       <c r="CA17">
-        <v>1.45</v>
+        <v>8.4</v>
       </c>
       <c r="CB17" t="s">
         <v>145</v>
@@ -4917,127 +4917,127 @@
         <v>141</v>
       </c>
       <c r="F18">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="G18">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="H18">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="I18">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="J18">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="K18">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="L18">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="M18">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="N18">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="O18">
+        <v>1.51</v>
+      </c>
+      <c r="P18">
         <v>1.58</v>
       </c>
-      <c r="P18">
-        <v>1.48</v>
-      </c>
       <c r="Q18">
-        <v>2.84</v>
+        <v>2.52</v>
       </c>
       <c r="R18">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S18">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="T18">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="U18">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="V18">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="W18">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X18">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="Y18">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="Z18">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AA18">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB18">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AC18">
         <v>7.6</v>
       </c>
       <c r="AD18">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE18">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AF18">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AG18">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AH18">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AI18">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="AJ18">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="AK18">
+        <v>95</v>
+      </c>
+      <c r="AL18">
+        <v>260</v>
+      </c>
+      <c r="AM18">
         <v>500</v>
       </c>
-      <c r="AL18">
-        <v>500</v>
-      </c>
-      <c r="AM18">
-        <v>580</v>
-      </c>
       <c r="AN18">
-        <v>600</v>
+        <v>190</v>
       </c>
       <c r="AO18">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="AP18">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AQ18">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AR18">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AS18">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT18">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AU18">
         <v>6.4</v>
@@ -5049,94 +5049,94 @@
         <v>21</v>
       </c>
       <c r="AX18">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY18">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ18">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA18">
+        <v>38</v>
+      </c>
+      <c r="BB18">
+        <v>60</v>
+      </c>
+      <c r="BC18">
         <v>40</v>
       </c>
-      <c r="BB18">
-        <v>65</v>
-      </c>
-      <c r="BC18">
-        <v>42</v>
-      </c>
       <c r="BD18">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BE18">
-        <v>8.6</v>
+        <v>28</v>
       </c>
       <c r="BF18">
-        <v>8.4</v>
+        <v>70</v>
       </c>
       <c r="BG18">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BH18">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="BI18">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="BJ18">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BK18">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN18">
         <v>7.4</v>
       </c>
       <c r="BO18">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BP18">
         <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BR18">
         <v>1000</v>
       </c>
       <c r="BS18">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BT18">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BU18">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BV18">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BW18">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BZ18">
         <v>1000</v>
       </c>
       <c r="CA18">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="CB18" t="s">
         <v>145</v>
@@ -5159,16 +5159,16 @@
         <v>142</v>
       </c>
       <c r="F19">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="G19">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="H19">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="I19">
-        <v>2.96</v>
+        <v>2.82</v>
       </c>
       <c r="J19">
         <v>2.94</v>
@@ -5177,208 +5177,208 @@
         <v>3.25</v>
       </c>
       <c r="L19">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="M19">
         <v>1.12</v>
       </c>
       <c r="N19">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="O19">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="P19">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="Q19">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="R19">
         <v>1.2</v>
       </c>
       <c r="S19">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="T19">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U19">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="V19">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="W19">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="X19">
         <v>8.800000000000001</v>
       </c>
       <c r="Y19">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z19">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA19">
-        <v>220</v>
+        <v>46</v>
       </c>
       <c r="AB19">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AC19">
         <v>7.2</v>
       </c>
       <c r="AD19">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE19">
-        <v>280</v>
+        <v>120</v>
       </c>
       <c r="AF19">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AG19">
         <v>15</v>
       </c>
       <c r="AH19">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI19">
         <v>75</v>
       </c>
       <c r="AJ19">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AK19">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AL19">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AM19">
         <v>500</v>
       </c>
       <c r="AN19">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AO19">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AP19">
-        <v>7.6</v>
+        <v>4.4</v>
       </c>
       <c r="AQ19">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR19">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AS19">
         <v>16</v>
       </c>
       <c r="AT19">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU19">
         <v>6.2</v>
       </c>
       <c r="AV19">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW19">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AX19">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AY19">
         <v>12</v>
       </c>
       <c r="AZ19">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA19">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="BB19">
-        <v>25</v>
+        <v>7.4</v>
       </c>
       <c r="BC19">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BD19">
-        <v>11</v>
+        <v>6.6</v>
       </c>
       <c r="BE19">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="BF19">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BG19">
         <v>11</v>
       </c>
       <c r="BH19">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="BI19">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="BJ19">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK19">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="BN19">
         <v>6.8</v>
       </c>
       <c r="BO19">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BP19">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BQ19">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BR19">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BS19">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT19">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BU19">
         <v>4.4</v>
       </c>
       <c r="BV19">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="BW19">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BX19">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BY19">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ19">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="CA19">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB19" t="s">
         <v>145</v>
@@ -5401,64 +5401,64 @@
         <v>143</v>
       </c>
       <c r="F20">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G20">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="H20">
+        <v>3.75</v>
+      </c>
+      <c r="I20">
+        <v>4.3</v>
+      </c>
+      <c r="J20">
         <v>3.7</v>
       </c>
-      <c r="I20">
-        <v>4.2</v>
-      </c>
-      <c r="J20">
-        <v>3.85</v>
-      </c>
       <c r="K20">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L20">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="M20">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N20">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="O20">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="P20">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="Q20">
+        <v>1.73</v>
+      </c>
+      <c r="R20">
+        <v>1.49</v>
+      </c>
+      <c r="S20">
+        <v>2.84</v>
+      </c>
+      <c r="T20">
         <v>1.64</v>
       </c>
-      <c r="R20">
-        <v>1.54</v>
-      </c>
-      <c r="S20">
-        <v>2.62</v>
-      </c>
-      <c r="T20">
-        <v>1.59</v>
-      </c>
       <c r="U20">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="V20">
         <v>1.32</v>
       </c>
       <c r="W20">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="X20">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Y20">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z20">
         <v>32</v>
@@ -5467,136 +5467,136 @@
         <v>85</v>
       </c>
       <c r="AB20">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AC20">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD20">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE20">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AF20">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG20">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH20">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI20">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AJ20">
         <v>25</v>
       </c>
       <c r="AK20">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL20">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM20">
-        <v>200</v>
+        <v>85</v>
       </c>
       <c r="AN20">
+        <v>12</v>
+      </c>
+      <c r="AO20">
+        <v>42</v>
+      </c>
+      <c r="AP20">
         <v>11.5</v>
       </c>
-      <c r="AO20">
-        <v>36</v>
-      </c>
-      <c r="AP20">
-        <v>17.5</v>
-      </c>
       <c r="AQ20">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR20">
         <v>25</v>
       </c>
       <c r="AS20">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="AT20">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU20">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV20">
         <v>14</v>
       </c>
       <c r="AW20">
-        <v>27</v>
+        <v>19.5</v>
       </c>
       <c r="AX20">
-        <v>12</v>
+        <v>6.2</v>
       </c>
       <c r="AY20">
         <v>9</v>
       </c>
       <c r="AZ20">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA20">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BB20">
-        <v>19.5</v>
+        <v>7.2</v>
       </c>
       <c r="BC20">
         <v>16</v>
       </c>
       <c r="BD20">
+        <v>21</v>
+      </c>
+      <c r="BE20">
         <v>23</v>
       </c>
-      <c r="BE20">
-        <v>28</v>
-      </c>
       <c r="BF20">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG20">
-        <v>14.5</v>
+        <v>30</v>
       </c>
       <c r="BH20">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BI20">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BJ20">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BK20">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN20">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BO20">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="BP20">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ20">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BR20">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BS20">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BT20">
         <v>7.8</v>
@@ -5605,22 +5605,22 @@
         <v>6</v>
       </c>
       <c r="BV20">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BW20">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BX20">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BY20">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BZ20">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="CA20">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="CB20" t="s">
         <v>145</v>
@@ -5643,226 +5643,226 @@
         <v>144</v>
       </c>
       <c r="F21">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="G21">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="H21">
         <v>2.34</v>
       </c>
       <c r="I21">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="J21">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K21">
         <v>3.35</v>
       </c>
       <c r="L21">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="M21">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N21">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="O21">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="P21">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="Q21">
-        <v>2.48</v>
+        <v>2.22</v>
       </c>
       <c r="R21">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="S21">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="T21">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="U21">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="V21">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="W21">
         <v>1.35</v>
       </c>
       <c r="X21">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="Y21">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z21">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA21">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AB21">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AC21">
         <v>7.2</v>
       </c>
       <c r="AD21">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE21">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AF21">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG21">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH21">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI21">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ21">
         <v>90</v>
       </c>
       <c r="AK21">
+        <v>60</v>
+      </c>
+      <c r="AL21">
         <v>75</v>
       </c>
-      <c r="AL21">
-        <v>80</v>
-      </c>
       <c r="AM21">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="AN21">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AO21">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AP21">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ21">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AR21">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AS21">
         <v>24</v>
       </c>
       <c r="AT21">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AU21">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV21">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW21">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AX21">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY21">
         <v>14</v>
       </c>
       <c r="AZ21">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BA21">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BB21">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BC21">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BD21">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BE21">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="BF21">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BG21">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BH21">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="BI21">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="BJ21">
+        <v>10</v>
+      </c>
+      <c r="BK21">
+        <v>5.4</v>
+      </c>
+      <c r="BL21">
+        <v>170</v>
+      </c>
+      <c r="BM21">
         <v>10.5</v>
       </c>
-      <c r="BK21">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BL21">
-        <v>1000</v>
-      </c>
-      <c r="BM21">
-        <v>9.6</v>
-      </c>
       <c r="BN21">
+        <v>6.8</v>
+      </c>
+      <c r="BO21">
+        <v>5.2</v>
+      </c>
+      <c r="BP21">
+        <v>32</v>
+      </c>
+      <c r="BQ21">
+        <v>8.4</v>
+      </c>
+      <c r="BR21">
+        <v>46</v>
+      </c>
+      <c r="BS21">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT21">
+        <v>5.1</v>
+      </c>
+      <c r="BU21">
+        <v>4.5</v>
+      </c>
+      <c r="BV21">
+        <v>18</v>
+      </c>
+      <c r="BW21">
         <v>7</v>
       </c>
-      <c r="BO21">
-        <v>6</v>
-      </c>
-      <c r="BP21">
+      <c r="BX21">
         <v>34</v>
       </c>
-      <c r="BQ21">
-        <v>7.8</v>
-      </c>
-      <c r="BR21">
-        <v>60</v>
-      </c>
-      <c r="BS21">
+      <c r="BY21">
         <v>8.6</v>
       </c>
-      <c r="BT21">
-        <v>5</v>
-      </c>
-      <c r="BU21">
-        <v>4.3</v>
-      </c>
-      <c r="BV21">
-        <v>20</v>
-      </c>
-      <c r="BW21">
-        <v>6.6</v>
-      </c>
-      <c r="BX21">
-        <v>46</v>
-      </c>
-      <c r="BY21">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BZ21">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="CA21">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="CB21" t="s">
         <v>145</v>
